--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050111-1\ＪＯＢ050111-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050117-1\ＪＯＢ050117-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21780" windowHeight="10305"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CR$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CR$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$ER$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$ER$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CS$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CT$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$ES$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$ET$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="418">
   <si>
     <t>都道府県</t>
   </si>
@@ -4514,6 +4514,18 @@
     <t>R5</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1/9(月)～
+1/15(日)分
+【1月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1/10(月)～
+1/16(日)分
+【1月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4877,7 +4889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5010,9 +5022,6 @@
     <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -5094,13 +5103,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5130,7 +5145,16 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9317,7 +9341,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:ES61"/>
+  <dimension ref="A1:ET61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9331,11 +9355,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="148" width="10.875" style="1" customWidth="1"/>
-    <col min="149" max="16384" width="8.625" style="1"/>
+    <col min="106" max="149" width="10.875" style="1" customWidth="1"/>
+    <col min="150" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:149" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:150" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9410,919 +9434,926 @@
       <c r="EO1" s="19"/>
       <c r="EP1" s="19"/>
       <c r="EQ1" s="19"/>
-      <c r="ER1" s="19" t="s">
+      <c r="ER1" s="19"/>
+      <c r="ES1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:149" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="68" t="s">
+    <row r="2" spans="1:150" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="Z2" s="69"/>
-      <c r="AA2" s="69"/>
-      <c r="AB2" s="69"/>
-      <c r="AC2" s="69"/>
-      <c r="AD2" s="69"/>
-      <c r="AE2" s="69"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="69"/>
-      <c r="AH2" s="69"/>
-      <c r="AI2" s="69"/>
-      <c r="AJ2" s="69"/>
-      <c r="AK2" s="69"/>
-      <c r="AL2" s="69"/>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69"/>
-      <c r="AO2" s="69"/>
-      <c r="AP2" s="69"/>
-      <c r="AQ2" s="69"/>
-      <c r="AR2" s="69"/>
-      <c r="AS2" s="69"/>
-      <c r="AT2" s="69"/>
-      <c r="AU2" s="69"/>
-      <c r="AV2" s="69"/>
-      <c r="AW2" s="69"/>
-      <c r="AX2" s="69"/>
-      <c r="AY2" s="69"/>
-      <c r="AZ2" s="69"/>
-      <c r="BA2" s="69"/>
-      <c r="BB2" s="69"/>
-      <c r="BC2" s="69"/>
-      <c r="BD2" s="69" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="68"/>
+      <c r="BD2" s="68" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="69"/>
-      <c r="BF2" s="69"/>
-      <c r="BG2" s="69"/>
-      <c r="BH2" s="69"/>
-      <c r="BI2" s="69"/>
-      <c r="BJ2" s="69"/>
-      <c r="BK2" s="69"/>
-      <c r="BL2" s="69"/>
-      <c r="BM2" s="69"/>
-      <c r="BN2" s="69"/>
-      <c r="BO2" s="69"/>
-      <c r="BP2" s="69"/>
-      <c r="BQ2" s="69"/>
-      <c r="BR2" s="69"/>
-      <c r="BS2" s="69"/>
-      <c r="BT2" s="69"/>
-      <c r="BU2" s="69"/>
-      <c r="BV2" s="69"/>
-      <c r="BW2" s="69"/>
-      <c r="BX2" s="69"/>
-      <c r="BY2" s="69"/>
-      <c r="BZ2" s="69"/>
-      <c r="CA2" s="69"/>
-      <c r="CB2" s="69"/>
-      <c r="CC2" s="69"/>
-      <c r="CD2" s="69"/>
-      <c r="CE2" s="69"/>
-      <c r="CF2" s="69"/>
-      <c r="CG2" s="69"/>
-      <c r="CH2" s="69"/>
-      <c r="CI2" s="69"/>
-      <c r="CJ2" s="69"/>
-      <c r="CK2" s="69"/>
-      <c r="CL2" s="69"/>
-      <c r="CM2" s="69"/>
-      <c r="CN2" s="69"/>
-      <c r="CO2" s="69"/>
-      <c r="CP2" s="69"/>
-      <c r="CQ2" s="69"/>
-      <c r="CR2" s="69"/>
-      <c r="CS2" s="69"/>
-      <c r="CT2" s="69"/>
-      <c r="CU2" s="69"/>
-      <c r="CV2" s="69"/>
-      <c r="CW2" s="69"/>
-      <c r="CX2" s="69"/>
-      <c r="CY2" s="69"/>
-      <c r="CZ2" s="69"/>
-      <c r="DA2" s="69"/>
-      <c r="DB2" s="69"/>
-      <c r="DC2" s="69"/>
-      <c r="DD2" s="69"/>
-      <c r="DE2" s="74" t="s">
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="68"/>
+      <c r="BG2" s="68"/>
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="68"/>
+      <c r="BJ2" s="68"/>
+      <c r="BK2" s="68"/>
+      <c r="BL2" s="68"/>
+      <c r="BM2" s="68"/>
+      <c r="BN2" s="68"/>
+      <c r="BO2" s="68"/>
+      <c r="BP2" s="68"/>
+      <c r="BQ2" s="68"/>
+      <c r="BR2" s="68"/>
+      <c r="BS2" s="68"/>
+      <c r="BT2" s="68"/>
+      <c r="BU2" s="68"/>
+      <c r="BV2" s="68"/>
+      <c r="BW2" s="68"/>
+      <c r="BX2" s="68"/>
+      <c r="BY2" s="68"/>
+      <c r="BZ2" s="68"/>
+      <c r="CA2" s="68"/>
+      <c r="CB2" s="68"/>
+      <c r="CC2" s="68"/>
+      <c r="CD2" s="68"/>
+      <c r="CE2" s="68"/>
+      <c r="CF2" s="68"/>
+      <c r="CG2" s="68"/>
+      <c r="CH2" s="68"/>
+      <c r="CI2" s="68"/>
+      <c r="CJ2" s="68"/>
+      <c r="CK2" s="68"/>
+      <c r="CL2" s="68"/>
+      <c r="CM2" s="68"/>
+      <c r="CN2" s="68"/>
+      <c r="CO2" s="68"/>
+      <c r="CP2" s="68"/>
+      <c r="CQ2" s="68"/>
+      <c r="CR2" s="68"/>
+      <c r="CS2" s="68"/>
+      <c r="CT2" s="68"/>
+      <c r="CU2" s="68"/>
+      <c r="CV2" s="68"/>
+      <c r="CW2" s="68"/>
+      <c r="CX2" s="68"/>
+      <c r="CY2" s="68"/>
+      <c r="CZ2" s="68"/>
+      <c r="DA2" s="68"/>
+      <c r="DB2" s="68"/>
+      <c r="DC2" s="68"/>
+      <c r="DD2" s="68"/>
+      <c r="DE2" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="74"/>
-      <c r="DG2" s="74"/>
-      <c r="DH2" s="74"/>
-      <c r="DI2" s="74"/>
-      <c r="DJ2" s="74"/>
-      <c r="DK2" s="74"/>
-      <c r="DL2" s="74"/>
-      <c r="DM2" s="74"/>
-      <c r="DN2" s="74"/>
-      <c r="DO2" s="74"/>
-      <c r="DP2" s="74"/>
-      <c r="DQ2" s="74"/>
-      <c r="DR2" s="74"/>
-      <c r="DS2" s="74"/>
-      <c r="DT2" s="74"/>
-      <c r="DU2" s="74"/>
-      <c r="DV2" s="74"/>
-      <c r="DW2" s="74"/>
-      <c r="DX2" s="74"/>
-      <c r="DY2" s="74"/>
-      <c r="DZ2" s="74"/>
-      <c r="EA2" s="74"/>
-      <c r="EB2" s="74"/>
-      <c r="EC2" s="74"/>
-      <c r="ED2" s="74"/>
-      <c r="EE2" s="74"/>
-      <c r="EF2" s="74"/>
-      <c r="EG2" s="74"/>
-      <c r="EH2" s="74"/>
-      <c r="EI2" s="74"/>
-      <c r="EJ2" s="74"/>
-      <c r="EK2" s="74"/>
-      <c r="EL2" s="74"/>
-      <c r="EM2" s="74"/>
-      <c r="EN2" s="74"/>
-      <c r="EO2" s="74"/>
-      <c r="EP2" s="74"/>
-      <c r="EQ2" s="74"/>
-      <c r="ER2" s="74"/>
+      <c r="DF2" s="68"/>
+      <c r="DG2" s="68"/>
+      <c r="DH2" s="68"/>
+      <c r="DI2" s="68"/>
+      <c r="DJ2" s="68"/>
+      <c r="DK2" s="68"/>
+      <c r="DL2" s="68"/>
+      <c r="DM2" s="68"/>
+      <c r="DN2" s="68"/>
+      <c r="DO2" s="68"/>
+      <c r="DP2" s="68"/>
+      <c r="DQ2" s="68"/>
+      <c r="DR2" s="68"/>
+      <c r="DS2" s="68"/>
+      <c r="DT2" s="68"/>
+      <c r="DU2" s="68"/>
+      <c r="DV2" s="68"/>
+      <c r="DW2" s="68"/>
+      <c r="DX2" s="68"/>
+      <c r="DY2" s="68"/>
+      <c r="DZ2" s="68"/>
+      <c r="EA2" s="68"/>
+      <c r="EB2" s="68"/>
+      <c r="EC2" s="68"/>
+      <c r="ED2" s="68"/>
+      <c r="EE2" s="68"/>
+      <c r="EF2" s="68"/>
+      <c r="EG2" s="68"/>
+      <c r="EH2" s="68"/>
+      <c r="EI2" s="68"/>
+      <c r="EJ2" s="68"/>
+      <c r="EK2" s="68"/>
+      <c r="EL2" s="68"/>
+      <c r="EM2" s="68"/>
+      <c r="EN2" s="68"/>
+      <c r="EO2" s="68"/>
+      <c r="EP2" s="68"/>
+      <c r="EQ2" s="68"/>
+      <c r="ER2" s="68"/>
+      <c r="ES2" s="71"/>
     </row>
-    <row r="3" spans="1:149" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="65" t="s">
+    <row r="3" spans="1:150" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="64" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="65"/>
-      <c r="AM3" s="65"/>
-      <c r="AN3" s="65"/>
-      <c r="AO3" s="65"/>
-      <c r="AP3" s="65"/>
-      <c r="AQ3" s="65"/>
-      <c r="AR3" s="66" t="s">
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="64"/>
+      <c r="AA3" s="64"/>
+      <c r="AB3" s="64"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="64"/>
+      <c r="AE3" s="64"/>
+      <c r="AF3" s="64"/>
+      <c r="AG3" s="64"/>
+      <c r="AH3" s="64"/>
+      <c r="AI3" s="64"/>
+      <c r="AJ3" s="64"/>
+      <c r="AK3" s="64"/>
+      <c r="AL3" s="64"/>
+      <c r="AM3" s="64"/>
+      <c r="AN3" s="64"/>
+      <c r="AO3" s="64"/>
+      <c r="AP3" s="64"/>
+      <c r="AQ3" s="64"/>
+      <c r="AR3" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="AS3" s="67"/>
-      <c r="AT3" s="67"/>
-      <c r="AU3" s="67"/>
-      <c r="AV3" s="67"/>
-      <c r="AW3" s="67"/>
-      <c r="AX3" s="67"/>
-      <c r="AY3" s="67"/>
-      <c r="AZ3" s="67"/>
-      <c r="BA3" s="67"/>
-      <c r="BB3" s="67"/>
-      <c r="BC3" s="67"/>
-      <c r="BD3" s="67" t="s">
+      <c r="AS3" s="66"/>
+      <c r="AT3" s="66"/>
+      <c r="AU3" s="66"/>
+      <c r="AV3" s="66"/>
+      <c r="AW3" s="66"/>
+      <c r="AX3" s="66"/>
+      <c r="AY3" s="66"/>
+      <c r="AZ3" s="66"/>
+      <c r="BA3" s="66"/>
+      <c r="BB3" s="66"/>
+      <c r="BC3" s="66"/>
+      <c r="BD3" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="67"/>
-      <c r="BR3" s="67"/>
-      <c r="BS3" s="67"/>
-      <c r="BT3" s="67"/>
-      <c r="BU3" s="67"/>
-      <c r="BV3" s="67"/>
-      <c r="BW3" s="67"/>
-      <c r="BX3" s="67"/>
-      <c r="BY3" s="67"/>
-      <c r="BZ3" s="67"/>
-      <c r="CA3" s="67"/>
-      <c r="CB3" s="67"/>
-      <c r="CC3" s="67"/>
-      <c r="CD3" s="67"/>
-      <c r="CE3" s="67"/>
-      <c r="CF3" s="67"/>
-      <c r="CG3" s="67"/>
-      <c r="CH3" s="67"/>
-      <c r="CI3" s="67"/>
-      <c r="CJ3" s="67"/>
-      <c r="CK3" s="67"/>
-      <c r="CL3" s="67"/>
-      <c r="CM3" s="67"/>
-      <c r="CN3" s="67"/>
-      <c r="CO3" s="67"/>
-      <c r="CP3" s="67"/>
-      <c r="CQ3" s="71"/>
-      <c r="CR3" s="65" t="s">
+      <c r="BE3" s="66"/>
+      <c r="BF3" s="66"/>
+      <c r="BG3" s="66"/>
+      <c r="BH3" s="66"/>
+      <c r="BI3" s="66"/>
+      <c r="BJ3" s="66"/>
+      <c r="BK3" s="66"/>
+      <c r="BL3" s="66"/>
+      <c r="BM3" s="66"/>
+      <c r="BN3" s="66"/>
+      <c r="BO3" s="66"/>
+      <c r="BP3" s="66"/>
+      <c r="BQ3" s="66"/>
+      <c r="BR3" s="66"/>
+      <c r="BS3" s="66"/>
+      <c r="BT3" s="66"/>
+      <c r="BU3" s="66"/>
+      <c r="BV3" s="66"/>
+      <c r="BW3" s="66"/>
+      <c r="BX3" s="66"/>
+      <c r="BY3" s="66"/>
+      <c r="BZ3" s="66"/>
+      <c r="CA3" s="66"/>
+      <c r="CB3" s="66"/>
+      <c r="CC3" s="66"/>
+      <c r="CD3" s="66"/>
+      <c r="CE3" s="66"/>
+      <c r="CF3" s="66"/>
+      <c r="CG3" s="66"/>
+      <c r="CH3" s="66"/>
+      <c r="CI3" s="66"/>
+      <c r="CJ3" s="66"/>
+      <c r="CK3" s="66"/>
+      <c r="CL3" s="66"/>
+      <c r="CM3" s="66"/>
+      <c r="CN3" s="66"/>
+      <c r="CO3" s="66"/>
+      <c r="CP3" s="66"/>
+      <c r="CQ3" s="70"/>
+      <c r="CR3" s="64" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="65"/>
-      <c r="CT3" s="65"/>
-      <c r="CU3" s="65"/>
-      <c r="CV3" s="65"/>
-      <c r="CW3" s="65"/>
-      <c r="CX3" s="65"/>
-      <c r="CY3" s="65"/>
-      <c r="CZ3" s="65"/>
-      <c r="DA3" s="65"/>
-      <c r="DB3" s="65"/>
-      <c r="DC3" s="65"/>
-      <c r="DD3" s="66"/>
-      <c r="DE3" s="66" t="s">
+      <c r="CS3" s="64"/>
+      <c r="CT3" s="64"/>
+      <c r="CU3" s="64"/>
+      <c r="CV3" s="64"/>
+      <c r="CW3" s="64"/>
+      <c r="CX3" s="64"/>
+      <c r="CY3" s="64"/>
+      <c r="CZ3" s="64"/>
+      <c r="DA3" s="64"/>
+      <c r="DB3" s="64"/>
+      <c r="DC3" s="64"/>
+      <c r="DD3" s="65"/>
+      <c r="DE3" s="65" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="67"/>
-      <c r="DG3" s="67"/>
-      <c r="DH3" s="67"/>
-      <c r="DI3" s="67"/>
-      <c r="DJ3" s="67"/>
-      <c r="DK3" s="67"/>
-      <c r="DL3" s="67"/>
-      <c r="DM3" s="67"/>
-      <c r="DN3" s="67"/>
-      <c r="DO3" s="67"/>
-      <c r="DP3" s="67"/>
-      <c r="DQ3" s="67"/>
-      <c r="DR3" s="67"/>
-      <c r="DS3" s="67"/>
-      <c r="DT3" s="67"/>
-      <c r="DU3" s="67"/>
-      <c r="DV3" s="67"/>
-      <c r="DW3" s="67"/>
-      <c r="DX3" s="67"/>
-      <c r="DY3" s="67"/>
-      <c r="DZ3" s="67"/>
-      <c r="EA3" s="67"/>
-      <c r="EB3" s="67"/>
-      <c r="EC3" s="67"/>
-      <c r="ED3" s="67"/>
-      <c r="EE3" s="67"/>
-      <c r="EF3" s="67"/>
-      <c r="EG3" s="67"/>
-      <c r="EH3" s="67"/>
-      <c r="EI3" s="67"/>
-      <c r="EJ3" s="67"/>
-      <c r="EK3" s="67"/>
-      <c r="EL3" s="67"/>
-      <c r="EM3" s="67"/>
-      <c r="EN3" s="67"/>
-      <c r="EO3" s="67"/>
-      <c r="EP3" s="67"/>
-      <c r="EQ3" s="71"/>
-      <c r="ER3" s="44" t="s">
+      <c r="DF3" s="66"/>
+      <c r="DG3" s="66"/>
+      <c r="DH3" s="66"/>
+      <c r="DI3" s="66"/>
+      <c r="DJ3" s="66"/>
+      <c r="DK3" s="66"/>
+      <c r="DL3" s="66"/>
+      <c r="DM3" s="66"/>
+      <c r="DN3" s="66"/>
+      <c r="DO3" s="66"/>
+      <c r="DP3" s="66"/>
+      <c r="DQ3" s="66"/>
+      <c r="DR3" s="66"/>
+      <c r="DS3" s="66"/>
+      <c r="DT3" s="66"/>
+      <c r="DU3" s="66"/>
+      <c r="DV3" s="66"/>
+      <c r="DW3" s="66"/>
+      <c r="DX3" s="66"/>
+      <c r="DY3" s="66"/>
+      <c r="DZ3" s="66"/>
+      <c r="EA3" s="66"/>
+      <c r="EB3" s="66"/>
+      <c r="EC3" s="66"/>
+      <c r="ED3" s="66"/>
+      <c r="EE3" s="66"/>
+      <c r="EF3" s="66"/>
+      <c r="EG3" s="66"/>
+      <c r="EH3" s="66"/>
+      <c r="EI3" s="66"/>
+      <c r="EJ3" s="66"/>
+      <c r="EK3" s="66"/>
+      <c r="EL3" s="66"/>
+      <c r="EM3" s="66"/>
+      <c r="EN3" s="66"/>
+      <c r="EO3" s="66"/>
+      <c r="EP3" s="66"/>
+      <c r="EQ3" s="70"/>
+      <c r="ER3" s="72" t="s">
         <v>415</v>
       </c>
+      <c r="ES3" s="73"/>
     </row>
-    <row r="4" spans="1:149" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="45" t="s">
+    <row r="4" spans="1:150" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="45" t="s">
+      <c r="K4" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="L4" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="N4" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="45" t="s">
+      <c r="P4" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="Q4" s="45" t="s">
+      <c r="Q4" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="R4" s="58" t="s">
+      <c r="R4" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="45" t="s">
+      <c r="T4" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="U4" s="58" t="s">
+      <c r="U4" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="58" t="s">
+      <c r="V4" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="W4" s="58" t="s">
+      <c r="W4" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="X4" s="58" t="s">
+      <c r="X4" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="Y4" s="58" t="s">
+      <c r="Y4" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="58" t="s">
+      <c r="Z4" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="AA4" s="45" t="s">
+      <c r="AA4" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="45" t="s">
+      <c r="AC4" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="AD4" s="45" t="s">
+      <c r="AD4" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="AE4" s="45" t="s">
+      <c r="AE4" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="AF4" s="45" t="s">
+      <c r="AF4" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="AG4" s="45" t="s">
+      <c r="AG4" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="AH4" s="45" t="s">
+      <c r="AH4" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="AI4" s="45" t="s">
+      <c r="AI4" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="AJ4" s="45" t="s">
+      <c r="AJ4" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="AK4" s="45" t="s">
+      <c r="AK4" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="AL4" s="45" t="s">
+      <c r="AL4" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="AM4" s="45" t="s">
+      <c r="AM4" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="AN4" s="45" t="s">
+      <c r="AN4" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="AO4" s="45" t="s">
+      <c r="AO4" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="AP4" s="45" t="s">
+      <c r="AP4" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="AQ4" s="45" t="s">
+      <c r="AQ4" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" s="47" t="s">
+      <c r="AR4" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="AS4" s="47" t="s">
+      <c r="AS4" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="47" t="s">
+      <c r="AT4" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="47" t="s">
+      <c r="AU4" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="47" t="s">
+      <c r="AV4" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="47" t="s">
+      <c r="AW4" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="AX4" s="47" t="s">
+      <c r="AX4" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="AY4" s="47" t="s">
+      <c r="AY4" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="AZ4" s="47" t="s">
+      <c r="AZ4" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="BA4" s="47" t="s">
+      <c r="BA4" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="BB4" s="47" t="s">
+      <c r="BB4" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="BC4" s="47" t="s">
+      <c r="BC4" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="46" t="s">
+      <c r="BF4" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="46" t="s">
+      <c r="BG4" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="BH4" s="46" t="s">
+      <c r="BH4" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="BI4" s="46" t="s">
+      <c r="BI4" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="46" t="s">
+      <c r="BJ4" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="46" t="s">
+      <c r="BK4" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="50" t="s">
+      <c r="BL4" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="50" t="s">
+      <c r="BM4" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="BN4" s="46" t="s">
+      <c r="BN4" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="BO4" s="46" t="s">
+      <c r="BO4" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="BP4" s="46" t="s">
+      <c r="BP4" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="BQ4" s="46" t="s">
+      <c r="BQ4" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="BR4" s="46" t="s">
+      <c r="BR4" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="BS4" s="46" t="s">
+      <c r="BS4" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="BT4" s="46" t="s">
+      <c r="BT4" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="BU4" s="50" t="s">
+      <c r="BU4" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="BV4" s="50" t="s">
+      <c r="BV4" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="BW4" s="50" t="s">
+      <c r="BW4" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="BX4" s="50" t="s">
+      <c r="BX4" s="49" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="50" t="s">
+      <c r="BY4" s="49" t="s">
         <v>225</v>
       </c>
-      <c r="BZ4" s="46" t="s">
+      <c r="BZ4" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="CA4" s="46" t="s">
+      <c r="CA4" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="CB4" s="46" t="s">
+      <c r="CB4" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="CC4" s="46" t="s">
+      <c r="CC4" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="CD4" s="46" t="s">
+      <c r="CD4" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="CE4" s="48" t="s">
+      <c r="CE4" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="CF4" s="48" t="s">
+      <c r="CF4" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="CG4" s="48" t="s">
+      <c r="CG4" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="CH4" s="48" t="s">
+      <c r="CH4" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="CI4" s="48" t="s">
+      <c r="CI4" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="CJ4" s="48" t="s">
+      <c r="CJ4" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="CK4" s="48" t="s">
+      <c r="CK4" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="CL4" s="48" t="s">
+      <c r="CL4" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="CM4" s="48" t="s">
+      <c r="CM4" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="CN4" s="48" t="s">
+      <c r="CN4" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="CO4" s="48" t="s">
+      <c r="CO4" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="CP4" s="48" t="s">
+      <c r="CP4" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="CQ4" s="48" t="s">
+      <c r="CQ4" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="CR4" s="48" t="s">
+      <c r="CR4" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="CS4" s="48" t="s">
+      <c r="CS4" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="CT4" s="48" t="s">
+      <c r="CT4" s="47" t="s">
         <v>286</v>
       </c>
-      <c r="CU4" s="48" t="s">
+      <c r="CU4" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="CV4" s="48" t="s">
+      <c r="CV4" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="CW4" s="48" t="s">
+      <c r="CW4" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="CX4" s="48" t="s">
+      <c r="CX4" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="CY4" s="48" t="s">
+      <c r="CY4" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="CZ4" s="48" t="s">
+      <c r="CZ4" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="DA4" s="48" t="s">
+      <c r="DA4" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="DB4" s="48" t="s">
+      <c r="DB4" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="DC4" s="48" t="s">
+      <c r="DC4" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="72" t="s">
+      <c r="DD4" s="74" t="s">
         <v>305</v>
       </c>
-      <c r="DE4" s="70" t="s">
+      <c r="DE4" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="DF4" s="70" t="s">
+      <c r="DF4" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="DG4" s="70" t="s">
+      <c r="DG4" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="DH4" s="70" t="s">
+      <c r="DH4" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="DI4" s="70" t="s">
+      <c r="DI4" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="DJ4" s="70" t="s">
+      <c r="DJ4" s="69" t="s">
         <v>318</v>
       </c>
-      <c r="DK4" s="70" t="s">
+      <c r="DK4" s="69" t="s">
         <v>326</v>
       </c>
-      <c r="DL4" s="70" t="s">
+      <c r="DL4" s="69" t="s">
         <v>328</v>
       </c>
-      <c r="DM4" s="70" t="s">
+      <c r="DM4" s="69" t="s">
         <v>330</v>
       </c>
-      <c r="DN4" s="70" t="s">
+      <c r="DN4" s="69" t="s">
         <v>332</v>
       </c>
-      <c r="DO4" s="70" t="s">
+      <c r="DO4" s="69" t="s">
         <v>334</v>
       </c>
-      <c r="DP4" s="70" t="s">
+      <c r="DP4" s="69" t="s">
         <v>336</v>
       </c>
-      <c r="DQ4" s="70" t="s">
+      <c r="DQ4" s="69" t="s">
         <v>338</v>
       </c>
-      <c r="DR4" s="70" t="s">
+      <c r="DR4" s="69" t="s">
         <v>341</v>
       </c>
-      <c r="DS4" s="70" t="s">
+      <c r="DS4" s="69" t="s">
         <v>345</v>
       </c>
-      <c r="DT4" s="70" t="s">
+      <c r="DT4" s="69" t="s">
         <v>349</v>
       </c>
-      <c r="DU4" s="70" t="s">
+      <c r="DU4" s="69" t="s">
         <v>352</v>
       </c>
-      <c r="DV4" s="70" t="s">
+      <c r="DV4" s="69" t="s">
         <v>354</v>
       </c>
-      <c r="DW4" s="70" t="s">
+      <c r="DW4" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="DX4" s="70" t="s">
+      <c r="DX4" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="DY4" s="70" t="s">
+      <c r="DY4" s="69" t="s">
         <v>361</v>
       </c>
-      <c r="DZ4" s="70" t="s">
+      <c r="DZ4" s="69" t="s">
         <v>363</v>
       </c>
-      <c r="EA4" s="70" t="s">
+      <c r="EA4" s="69" t="s">
         <v>371</v>
       </c>
-      <c r="EB4" s="70" t="s">
+      <c r="EB4" s="69" t="s">
         <v>375</v>
       </c>
-      <c r="EC4" s="70" t="s">
+      <c r="EC4" s="69" t="s">
         <v>379</v>
       </c>
-      <c r="ED4" s="70" t="s">
+      <c r="ED4" s="69" t="s">
         <v>381</v>
       </c>
-      <c r="EE4" s="70" t="s">
+      <c r="EE4" s="69" t="s">
         <v>384</v>
       </c>
-      <c r="EF4" s="70" t="s">
+      <c r="EF4" s="69" t="s">
         <v>386</v>
       </c>
-      <c r="EG4" s="70" t="s">
+      <c r="EG4" s="69" t="s">
         <v>389</v>
       </c>
-      <c r="EH4" s="70" t="s">
+      <c r="EH4" s="69" t="s">
         <v>391</v>
       </c>
-      <c r="EI4" s="70" t="s">
+      <c r="EI4" s="69" t="s">
         <v>393</v>
       </c>
-      <c r="EJ4" s="70" t="s">
+      <c r="EJ4" s="69" t="s">
         <v>395</v>
       </c>
-      <c r="EK4" s="70" t="s">
+      <c r="EK4" s="69" t="s">
         <v>398</v>
       </c>
-      <c r="EL4" s="70" t="s">
+      <c r="EL4" s="69" t="s">
         <v>400</v>
       </c>
-      <c r="EM4" s="70" t="s">
+      <c r="EM4" s="69" t="s">
         <v>402</v>
       </c>
-      <c r="EN4" s="70" t="s">
+      <c r="EN4" s="69" t="s">
         <v>404</v>
       </c>
-      <c r="EO4" s="70" t="s">
+      <c r="EO4" s="69" t="s">
         <v>407</v>
       </c>
-      <c r="EP4" s="70" t="s">
+      <c r="EP4" s="69" t="s">
         <v>409</v>
       </c>
-      <c r="EQ4" s="70" t="s">
+      <c r="EQ4" s="69" t="s">
         <v>411</v>
       </c>
-      <c r="ER4" s="70" t="s">
+      <c r="ER4" s="69" t="s">
         <v>412</v>
       </c>
+      <c r="ES4" s="69" t="s">
+        <v>416</v>
+      </c>
     </row>
-    <row r="5" spans="1:149" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="47"/>
-      <c r="AS5" s="47"/>
-      <c r="AT5" s="47"/>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="47"/>
-      <c r="BA5" s="47"/>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="47"/>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="51"/>
-      <c r="BM5" s="51"/>
-      <c r="BN5" s="47"/>
-      <c r="BO5" s="47"/>
-      <c r="BP5" s="47"/>
-      <c r="BQ5" s="47"/>
-      <c r="BR5" s="47"/>
-      <c r="BS5" s="47"/>
-      <c r="BT5" s="47"/>
-      <c r="BU5" s="51"/>
-      <c r="BV5" s="51"/>
-      <c r="BW5" s="51"/>
-      <c r="BX5" s="51"/>
-      <c r="BY5" s="51"/>
-      <c r="BZ5" s="47"/>
-      <c r="CA5" s="47"/>
-      <c r="CB5" s="47"/>
-      <c r="CC5" s="47"/>
-      <c r="CD5" s="47"/>
-      <c r="CE5" s="49"/>
-      <c r="CF5" s="49"/>
-      <c r="CG5" s="49"/>
-      <c r="CH5" s="49"/>
-      <c r="CI5" s="49"/>
-      <c r="CJ5" s="49"/>
-      <c r="CK5" s="49"/>
-      <c r="CL5" s="49"/>
-      <c r="CM5" s="49"/>
-      <c r="CN5" s="49"/>
-      <c r="CO5" s="49"/>
-      <c r="CP5" s="49"/>
-      <c r="CQ5" s="49"/>
-      <c r="CR5" s="49"/>
-      <c r="CS5" s="49"/>
-      <c r="CT5" s="49"/>
-      <c r="CU5" s="49"/>
-      <c r="CV5" s="49"/>
-      <c r="CW5" s="49"/>
-      <c r="CX5" s="49"/>
-      <c r="CY5" s="49"/>
-      <c r="CZ5" s="49"/>
-      <c r="DA5" s="49"/>
-      <c r="DB5" s="49"/>
-      <c r="DC5" s="49"/>
-      <c r="DD5" s="73"/>
-      <c r="DE5" s="49"/>
-      <c r="DF5" s="49"/>
-      <c r="DG5" s="49"/>
-      <c r="DH5" s="49"/>
-      <c r="DI5" s="49"/>
-      <c r="DJ5" s="49"/>
-      <c r="DK5" s="49"/>
-      <c r="DL5" s="49"/>
-      <c r="DM5" s="49"/>
-      <c r="DN5" s="49"/>
-      <c r="DO5" s="49"/>
-      <c r="DP5" s="49"/>
-      <c r="DQ5" s="49"/>
-      <c r="DR5" s="49"/>
-      <c r="DS5" s="49"/>
-      <c r="DT5" s="49"/>
-      <c r="DU5" s="49"/>
-      <c r="DV5" s="49"/>
-      <c r="DW5" s="49"/>
-      <c r="DX5" s="49"/>
-      <c r="DY5" s="49"/>
-      <c r="DZ5" s="49"/>
-      <c r="EA5" s="49"/>
-      <c r="EB5" s="49"/>
-      <c r="EC5" s="70"/>
-      <c r="ED5" s="70"/>
-      <c r="EE5" s="70"/>
-      <c r="EF5" s="70"/>
-      <c r="EG5" s="70"/>
-      <c r="EH5" s="70"/>
-      <c r="EI5" s="70"/>
-      <c r="EJ5" s="70"/>
-      <c r="EK5" s="70"/>
-      <c r="EL5" s="70"/>
-      <c r="EM5" s="70"/>
-      <c r="EN5" s="70"/>
-      <c r="EO5" s="70"/>
-      <c r="EP5" s="70"/>
-      <c r="EQ5" s="70"/>
-      <c r="ER5" s="70"/>
+    <row r="5" spans="1:150" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="63"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="45"/>
+      <c r="AD5" s="45"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AQ5" s="45"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="50"/>
+      <c r="BM5" s="50"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="50"/>
+      <c r="BV5" s="50"/>
+      <c r="BW5" s="50"/>
+      <c r="BX5" s="50"/>
+      <c r="BY5" s="50"/>
+      <c r="BZ5" s="46"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="48"/>
+      <c r="CF5" s="48"/>
+      <c r="CG5" s="48"/>
+      <c r="CH5" s="48"/>
+      <c r="CI5" s="48"/>
+      <c r="CJ5" s="48"/>
+      <c r="CK5" s="48"/>
+      <c r="CL5" s="48"/>
+      <c r="CM5" s="48"/>
+      <c r="CN5" s="48"/>
+      <c r="CO5" s="48"/>
+      <c r="CP5" s="48"/>
+      <c r="CQ5" s="48"/>
+      <c r="CR5" s="48"/>
+      <c r="CS5" s="48"/>
+      <c r="CT5" s="48"/>
+      <c r="CU5" s="48"/>
+      <c r="CV5" s="48"/>
+      <c r="CW5" s="48"/>
+      <c r="CX5" s="48"/>
+      <c r="CY5" s="48"/>
+      <c r="CZ5" s="48"/>
+      <c r="DA5" s="48"/>
+      <c r="DB5" s="48"/>
+      <c r="DC5" s="48"/>
+      <c r="DD5" s="75"/>
+      <c r="DE5" s="48"/>
+      <c r="DF5" s="48"/>
+      <c r="DG5" s="48"/>
+      <c r="DH5" s="48"/>
+      <c r="DI5" s="48"/>
+      <c r="DJ5" s="48"/>
+      <c r="DK5" s="48"/>
+      <c r="DL5" s="48"/>
+      <c r="DM5" s="48"/>
+      <c r="DN5" s="48"/>
+      <c r="DO5" s="48"/>
+      <c r="DP5" s="48"/>
+      <c r="DQ5" s="48"/>
+      <c r="DR5" s="48"/>
+      <c r="DS5" s="48"/>
+      <c r="DT5" s="48"/>
+      <c r="DU5" s="48"/>
+      <c r="DV5" s="48"/>
+      <c r="DW5" s="48"/>
+      <c r="DX5" s="48"/>
+      <c r="DY5" s="48"/>
+      <c r="DZ5" s="48"/>
+      <c r="EA5" s="48"/>
+      <c r="EB5" s="48"/>
+      <c r="EC5" s="69"/>
+      <c r="ED5" s="69"/>
+      <c r="EE5" s="69"/>
+      <c r="EF5" s="69"/>
+      <c r="EG5" s="69"/>
+      <c r="EH5" s="69"/>
+      <c r="EI5" s="69"/>
+      <c r="EJ5" s="69"/>
+      <c r="EK5" s="69"/>
+      <c r="EL5" s="69"/>
+      <c r="EM5" s="69"/>
+      <c r="EN5" s="69"/>
+      <c r="EO5" s="69"/>
+      <c r="EP5" s="69"/>
+      <c r="EQ5" s="69"/>
+      <c r="ER5" s="69"/>
+      <c r="ES5" s="69"/>
     </row>
-    <row r="6" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10765,9 +10796,12 @@
       <c r="ER6" s="28">
         <v>144</v>
       </c>
-      <c r="ES6" s="1"/>
+      <c r="ES6" s="28">
+        <v>187</v>
+      </c>
+      <c r="ET6" s="1"/>
     </row>
-    <row r="7" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11209,8 +11243,11 @@
       <c r="ER7" s="15">
         <v>6</v>
       </c>
+      <c r="ES7" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11652,8 +11689,11 @@
       <c r="ER8" s="28">
         <v>42</v>
       </c>
+      <c r="ES8" s="28">
+        <v>51</v>
+      </c>
     </row>
-    <row r="9" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12096,8 +12136,11 @@
       <c r="ER9" s="15">
         <v>124</v>
       </c>
+      <c r="ES9" s="15">
+        <v>132</v>
+      </c>
     </row>
-    <row r="10" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12537,8 +12580,11 @@
       <c r="ER10" s="15">
         <v>2</v>
       </c>
+      <c r="ES10" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -12980,8 +13026,11 @@
       <c r="ER11" s="15">
         <v>15</v>
       </c>
+      <c r="ES11" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13423,8 +13472,11 @@
       <c r="ER12" s="15">
         <v>10</v>
       </c>
+      <c r="ES12" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="13" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -13866,9 +13918,12 @@
       <c r="ER13" s="15">
         <v>67</v>
       </c>
-      <c r="ES13" s="1"/>
+      <c r="ES13" s="15">
+        <v>42</v>
+      </c>
+      <c r="ET13" s="1"/>
     </row>
-    <row r="14" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14310,8 +14365,11 @@
       <c r="ER14" s="15">
         <v>40</v>
       </c>
+      <c r="ES14" s="15">
+        <v>52</v>
+      </c>
     </row>
-    <row r="15" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -14753,8 +14811,11 @@
       <c r="ER15" s="15">
         <v>14</v>
       </c>
+      <c r="ES15" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="16" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15197,9 +15258,12 @@
       <c r="ER16" s="28">
         <v>217</v>
       </c>
-      <c r="ES16" s="1"/>
+      <c r="ES16" s="28">
+        <v>256</v>
+      </c>
+      <c r="ET16" s="1"/>
     </row>
-    <row r="17" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15641,9 +15705,12 @@
       <c r="ER17" s="15">
         <v>223</v>
       </c>
-      <c r="ES17" s="1"/>
+      <c r="ES17" s="15">
+        <v>245</v>
+      </c>
+      <c r="ET17" s="1"/>
     </row>
-    <row r="18" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16086,11 +16153,14 @@
       <c r="ER18" s="34">
         <v>3248</v>
       </c>
-      <c r="ES18" s="1"/>
+      <c r="ES18" s="34">
+        <v>3403</v>
+      </c>
+      <c r="ET18" s="1"/>
     </row>
-    <row r="19" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="53" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -16531,11 +16601,14 @@
       <c r="ER19" s="15">
         <v>112</v>
       </c>
-      <c r="ES19" s="1"/>
+      <c r="ES19" s="15">
+        <v>170</v>
+      </c>
+      <c r="ET19" s="1"/>
     </row>
-    <row r="20" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="54"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -16974,11 +17047,14 @@
       <c r="ER20" s="28">
         <v>510</v>
       </c>
-      <c r="ES20" s="1"/>
+      <c r="ES20" s="28">
+        <v>541</v>
+      </c>
+      <c r="ET20" s="1"/>
     </row>
-    <row r="21" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="54"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -17417,9 +17493,12 @@
       <c r="ER21" s="15">
         <v>40</v>
       </c>
-      <c r="ES21" s="1"/>
+      <c r="ES21" s="15">
+        <v>61</v>
+      </c>
+      <c r="ET21" s="1"/>
     </row>
-    <row r="22" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -17861,8 +17940,11 @@
       <c r="ER22" s="15">
         <v>11</v>
       </c>
+      <c r="ES22" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18304,8 +18386,11 @@
       <c r="ER23" s="15">
         <v>5</v>
       </c>
+      <c r="ES23" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="24" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -18747,9 +18832,12 @@
       <c r="ER24" s="15">
         <v>18</v>
       </c>
-      <c r="ES24" s="1"/>
+      <c r="ES24" s="15">
+        <v>33</v>
+      </c>
+      <c r="ET24" s="1"/>
     </row>
-    <row r="25" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19191,8 +19279,11 @@
       <c r="ER25" s="15">
         <v>3</v>
       </c>
+      <c r="ES25" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="26" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -19634,8 +19725,11 @@
       <c r="ER26" s="15">
         <v>21</v>
       </c>
+      <c r="ES26" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="27" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20077,8 +20171,11 @@
       <c r="ER27" s="15">
         <v>0</v>
       </c>
+      <c r="ES27" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -20520,10 +20617,13 @@
       <c r="ER28" s="15">
         <v>0</v>
       </c>
-      <c r="ES28" s="1"/>
+      <c r="ES28" s="15">
+        <v>13</v>
+      </c>
+      <c r="ET28" s="1"/>
     </row>
-    <row r="29" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="55" t="s">
+    <row r="29" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="54" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -20964,9 +21064,12 @@
       <c r="ER29" s="15">
         <v>11</v>
       </c>
+      <c r="ES29" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="55"/>
+    <row r="30" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="54"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -21405,8 +21508,11 @@
       <c r="ER30" s="15">
         <v>79</v>
       </c>
+      <c r="ES30" s="15">
+        <v>88</v>
+      </c>
     </row>
-    <row r="31" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -21849,9 +21955,12 @@
       <c r="ER31" s="15">
         <v>294</v>
       </c>
-      <c r="ES31" s="1"/>
+      <c r="ES31" s="15">
+        <v>316</v>
+      </c>
+      <c r="ET31" s="1"/>
     </row>
-    <row r="32" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22293,8 +22402,11 @@
       <c r="ER32" s="15">
         <v>9</v>
       </c>
+      <c r="ES32" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="33" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -22736,8 +22848,11 @@
       <c r="ER33" s="15">
         <v>0</v>
       </c>
+      <c r="ES33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23180,11 +23295,14 @@
       <c r="ER34" s="15">
         <v>177</v>
       </c>
-      <c r="ES34" s="1"/>
+      <c r="ES34" s="15">
+        <v>240</v>
+      </c>
+      <c r="ET34" s="1"/>
     </row>
-    <row r="35" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="53" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -23625,10 +23743,13 @@
       <c r="ER35" s="15">
         <v>631</v>
       </c>
-      <c r="ES35" s="1"/>
+      <c r="ES35" s="15">
+        <v>676</v>
+      </c>
+      <c r="ET35" s="1"/>
     </row>
-    <row r="36" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="54"/>
+    <row r="36" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="53"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -24067,9 +24188,12 @@
       <c r="ER36" s="28">
         <v>130</v>
       </c>
-      <c r="ES36" s="1"/>
+      <c r="ES36" s="28">
+        <v>148</v>
+      </c>
+      <c r="ET36" s="1"/>
     </row>
-    <row r="37" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -24512,9 +24636,12 @@
       <c r="ER37" s="15">
         <v>126</v>
       </c>
-      <c r="ES37" s="1"/>
+      <c r="ES37" s="15">
+        <v>208</v>
+      </c>
+      <c r="ET37" s="1"/>
     </row>
-    <row r="38" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -24956,8 +25083,11 @@
       <c r="ER38" s="15">
         <v>46</v>
       </c>
+      <c r="ES38" s="15">
+        <v>45</v>
+      </c>
     </row>
-    <row r="39" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -25399,8 +25529,11 @@
       <c r="ER39" s="15">
         <v>31</v>
       </c>
+      <c r="ES39" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="40" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -25842,8 +25975,11 @@
       <c r="ER40" s="15">
         <v>0</v>
       </c>
+      <c r="ES40" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -26285,8 +26421,11 @@
       <c r="ER41" s="15">
         <v>1</v>
       </c>
+      <c r="ES41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -26728,8 +26867,11 @@
       <c r="ER42" s="15">
         <v>58</v>
       </c>
+      <c r="ES42" s="15">
+        <v>77</v>
+      </c>
     </row>
-    <row r="43" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27171,8 +27313,11 @@
       <c r="ER43" s="28">
         <v>129</v>
       </c>
+      <c r="ES43" s="28">
+        <v>133</v>
+      </c>
     </row>
-    <row r="44" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -27614,8 +27759,11 @@
       <c r="ER44" s="15">
         <v>8</v>
       </c>
+      <c r="ES44" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28057,9 +28205,12 @@
       <c r="ER45" s="15">
         <v>54</v>
       </c>
-      <c r="ES45" s="1"/>
+      <c r="ES45" s="15">
+        <v>39</v>
+      </c>
+      <c r="ET45" s="1"/>
     </row>
-    <row r="46" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -28501,8 +28652,11 @@
       <c r="ER46" s="15">
         <v>72</v>
       </c>
+      <c r="ES46" s="15">
+        <v>66</v>
+      </c>
     </row>
-    <row r="47" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -28944,8 +29098,11 @@
       <c r="ER47" s="15">
         <v>7</v>
       </c>
+      <c r="ES47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -29387,10 +29544,13 @@
       <c r="ER48" s="15">
         <v>60</v>
       </c>
+      <c r="ES48" s="15">
+        <v>46</v>
+      </c>
     </row>
-    <row r="49" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="53" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -29831,10 +29991,13 @@
       <c r="ER49" s="15">
         <v>278</v>
       </c>
-      <c r="ES49" s="1"/>
+      <c r="ES49" s="15">
+        <v>271</v>
+      </c>
+      <c r="ET49" s="1"/>
     </row>
-    <row r="50" spans="1:149" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="54"/>
+    <row r="50" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="53"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -30273,9 +30436,12 @@
       <c r="ER50" s="15">
         <v>159</v>
       </c>
-      <c r="ES50" s="1"/>
+      <c r="ES50" s="15">
+        <v>160</v>
+      </c>
+      <c r="ET50" s="1"/>
     </row>
-    <row r="51" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -30717,8 +30883,11 @@
       <c r="ER51" s="15">
         <v>34</v>
       </c>
+      <c r="ES51" s="15">
+        <v>34</v>
+      </c>
     </row>
-    <row r="52" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -31160,8 +31329,11 @@
       <c r="ER52" s="15">
         <v>62</v>
       </c>
+      <c r="ES52" s="15">
+        <v>56</v>
+      </c>
     </row>
-    <row r="53" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -31603,8 +31775,11 @@
       <c r="ER53" s="15">
         <v>142</v>
       </c>
+      <c r="ES53" s="15">
+        <v>106</v>
+      </c>
     </row>
-    <row r="54" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -32046,8 +32221,11 @@
       <c r="ER54" s="15">
         <v>44</v>
       </c>
+      <c r="ES54" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="55" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -32489,8 +32667,11 @@
       <c r="ER55" s="15">
         <v>38</v>
       </c>
+      <c r="ES55" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="56" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -32932,8 +33113,11 @@
       <c r="ER56" s="15">
         <v>4</v>
       </c>
+      <c r="ES56" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="57" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -33375,8 +33559,11 @@
       <c r="ER57" s="15">
         <v>2</v>
       </c>
+      <c r="ES57" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -33854,7 +34041,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:ER58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:ES58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -33961,8 +34148,12 @@
         <f t="shared" si="10"/>
         <v>7558</v>
       </c>
+      <c r="ES58" s="14">
+        <f t="shared" si="10"/>
+        <v>8161</v>
+      </c>
     </row>
-    <row r="59" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -34046,7 +34237,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -34130,30 +34321,30 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:149" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="52"/>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
-      <c r="M61" s="53"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="53"/>
-      <c r="P61" s="53"/>
-      <c r="Q61" s="53"/>
-      <c r="R61" s="53"/>
-      <c r="S61" s="53"/>
-      <c r="T61" s="53"/>
-      <c r="U61" s="53"/>
-      <c r="V61" s="53"/>
-      <c r="W61" s="53"/>
+      <c r="D61" s="51"/>
+      <c r="E61" s="52"/>
+      <c r="F61" s="52"/>
+      <c r="G61" s="52"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
+      <c r="K61" s="52"/>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
+      <c r="N61" s="52"/>
+      <c r="O61" s="52"/>
+      <c r="P61" s="52"/>
+      <c r="Q61" s="52"/>
+      <c r="R61" s="52"/>
+      <c r="S61" s="52"/>
+      <c r="T61" s="52"/>
+      <c r="U61" s="52"/>
+      <c r="V61" s="52"/>
+      <c r="W61" s="52"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -34215,7 +34406,7 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="163">
     <mergeCell ref="EQ4:EQ5"/>
     <mergeCell ref="EP4:EP5"/>
     <mergeCell ref="EO4:EO5"/>
@@ -34223,9 +34414,13 @@
     <mergeCell ref="EM4:EM5"/>
     <mergeCell ref="EL4:EL5"/>
     <mergeCell ref="EJ4:EJ5"/>
-    <mergeCell ref="DE2:ER2"/>
     <mergeCell ref="ER4:ER5"/>
     <mergeCell ref="DE3:EQ3"/>
+    <mergeCell ref="DT4:DT5"/>
+    <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="DE2:ES2"/>
+    <mergeCell ref="ER3:ES3"/>
+    <mergeCell ref="ES4:ES5"/>
     <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="DD4:DD5"/>
@@ -34271,8 +34466,6 @@
     <mergeCell ref="DW4:DW5"/>
     <mergeCell ref="DV4:DV5"/>
     <mergeCell ref="DU4:DU5"/>
-    <mergeCell ref="DT4:DT5"/>
-    <mergeCell ref="DP4:DP5"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="D2:BC2"/>
     <mergeCell ref="DO4:DO5"/>
@@ -34389,7 +34582,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:ER57">
+  <conditionalFormatting sqref="DP6:ES57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -34409,7 +34602,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:ER58"/>
+  <dimension ref="B1:ES58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -34432,15 +34625,15 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="148" width="10.875" style="1" customWidth="1"/>
-    <col min="149" max="16384" width="8.625" style="1"/>
+    <col min="106" max="149" width="10.875" style="1" customWidth="1"/>
+    <col min="150" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:148" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="BB1" s="78" t="s">
+    <row r="1" spans="2:149" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BB1" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="BC1" s="78"/>
+      <c r="BC1" s="79"/>
       <c r="BI1" s="18"/>
       <c r="CC1" s="29"/>
       <c r="CD1" s="29"/>
@@ -34511,919 +34704,926 @@
       <c r="EO1" s="19"/>
       <c r="EP1" s="19"/>
       <c r="EQ1" s="19"/>
-      <c r="ER1" s="19" t="s">
+      <c r="ER1" s="19"/>
+      <c r="ES1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:148" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="74" t="s">
+    <row r="2" spans="2:149" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="74"/>
-      <c r="AE2" s="74"/>
-      <c r="AF2" s="74"/>
-      <c r="AG2" s="74"/>
-      <c r="AH2" s="74"/>
-      <c r="AI2" s="74"/>
-      <c r="AJ2" s="74"/>
-      <c r="AK2" s="74"/>
-      <c r="AL2" s="74"/>
-      <c r="AM2" s="74"/>
-      <c r="AN2" s="74"/>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="74"/>
-      <c r="AT2" s="74"/>
-      <c r="AU2" s="74"/>
-      <c r="AV2" s="74"/>
-      <c r="AW2" s="74"/>
-      <c r="AX2" s="74"/>
-      <c r="AY2" s="74"/>
-      <c r="AZ2" s="74"/>
-      <c r="BA2" s="74"/>
-      <c r="BB2" s="74"/>
-      <c r="BC2" s="74"/>
-      <c r="BD2" s="74" t="s">
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
+      <c r="AB2" s="85"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="85"/>
+      <c r="AE2" s="85"/>
+      <c r="AF2" s="85"/>
+      <c r="AG2" s="85"/>
+      <c r="AH2" s="85"/>
+      <c r="AI2" s="85"/>
+      <c r="AJ2" s="85"/>
+      <c r="AK2" s="85"/>
+      <c r="AL2" s="85"/>
+      <c r="AM2" s="85"/>
+      <c r="AN2" s="85"/>
+      <c r="AO2" s="85"/>
+      <c r="AP2" s="85"/>
+      <c r="AQ2" s="85"/>
+      <c r="AR2" s="85"/>
+      <c r="AS2" s="85"/>
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="85"/>
+      <c r="AZ2" s="85"/>
+      <c r="BA2" s="85"/>
+      <c r="BB2" s="85"/>
+      <c r="BC2" s="85"/>
+      <c r="BD2" s="85" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="74"/>
-      <c r="BF2" s="74"/>
-      <c r="BG2" s="74"/>
-      <c r="BH2" s="74"/>
-      <c r="BI2" s="74"/>
-      <c r="BJ2" s="74"/>
-      <c r="BK2" s="74"/>
-      <c r="BL2" s="74"/>
-      <c r="BM2" s="74"/>
-      <c r="BN2" s="74"/>
-      <c r="BO2" s="74"/>
-      <c r="BP2" s="74"/>
-      <c r="BQ2" s="74"/>
-      <c r="BR2" s="74"/>
-      <c r="BS2" s="74"/>
-      <c r="BT2" s="74"/>
-      <c r="BU2" s="74"/>
-      <c r="BV2" s="74"/>
-      <c r="BW2" s="74"/>
-      <c r="BX2" s="74"/>
-      <c r="BY2" s="74"/>
-      <c r="BZ2" s="74"/>
-      <c r="CA2" s="74"/>
-      <c r="CB2" s="74"/>
-      <c r="CC2" s="74"/>
-      <c r="CD2" s="74"/>
-      <c r="CE2" s="74"/>
-      <c r="CF2" s="74"/>
-      <c r="CG2" s="74"/>
-      <c r="CH2" s="74"/>
-      <c r="CI2" s="74"/>
-      <c r="CJ2" s="74"/>
-      <c r="CK2" s="74"/>
-      <c r="CL2" s="74"/>
-      <c r="CM2" s="74"/>
-      <c r="CN2" s="74"/>
-      <c r="CO2" s="74"/>
-      <c r="CP2" s="74"/>
-      <c r="CQ2" s="74"/>
-      <c r="CR2" s="74"/>
-      <c r="CS2" s="74"/>
-      <c r="CT2" s="74"/>
-      <c r="CU2" s="74"/>
-      <c r="CV2" s="74"/>
-      <c r="CW2" s="74"/>
-      <c r="CX2" s="74"/>
-      <c r="CY2" s="74"/>
-      <c r="CZ2" s="74"/>
-      <c r="DA2" s="74"/>
-      <c r="DB2" s="74"/>
-      <c r="DC2" s="74"/>
-      <c r="DD2" s="74" t="s">
+      <c r="BE2" s="85"/>
+      <c r="BF2" s="85"/>
+      <c r="BG2" s="85"/>
+      <c r="BH2" s="85"/>
+      <c r="BI2" s="85"/>
+      <c r="BJ2" s="85"/>
+      <c r="BK2" s="85"/>
+      <c r="BL2" s="85"/>
+      <c r="BM2" s="85"/>
+      <c r="BN2" s="85"/>
+      <c r="BO2" s="85"/>
+      <c r="BP2" s="85"/>
+      <c r="BQ2" s="85"/>
+      <c r="BR2" s="85"/>
+      <c r="BS2" s="85"/>
+      <c r="BT2" s="85"/>
+      <c r="BU2" s="85"/>
+      <c r="BV2" s="85"/>
+      <c r="BW2" s="85"/>
+      <c r="BX2" s="85"/>
+      <c r="BY2" s="85"/>
+      <c r="BZ2" s="85"/>
+      <c r="CA2" s="85"/>
+      <c r="CB2" s="85"/>
+      <c r="CC2" s="85"/>
+      <c r="CD2" s="85"/>
+      <c r="CE2" s="85"/>
+      <c r="CF2" s="85"/>
+      <c r="CG2" s="85"/>
+      <c r="CH2" s="85"/>
+      <c r="CI2" s="85"/>
+      <c r="CJ2" s="85"/>
+      <c r="CK2" s="85"/>
+      <c r="CL2" s="85"/>
+      <c r="CM2" s="85"/>
+      <c r="CN2" s="85"/>
+      <c r="CO2" s="85"/>
+      <c r="CP2" s="85"/>
+      <c r="CQ2" s="85"/>
+      <c r="CR2" s="85"/>
+      <c r="CS2" s="85"/>
+      <c r="CT2" s="85"/>
+      <c r="CU2" s="85"/>
+      <c r="CV2" s="85"/>
+      <c r="CW2" s="85"/>
+      <c r="CX2" s="85"/>
+      <c r="CY2" s="85"/>
+      <c r="CZ2" s="85"/>
+      <c r="DA2" s="85"/>
+      <c r="DB2" s="85"/>
+      <c r="DC2" s="85"/>
+      <c r="DD2" s="85" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="74"/>
-      <c r="DF2" s="74"/>
-      <c r="DG2" s="74"/>
-      <c r="DH2" s="74"/>
-      <c r="DI2" s="74"/>
-      <c r="DJ2" s="74"/>
-      <c r="DK2" s="74"/>
-      <c r="DL2" s="74"/>
-      <c r="DM2" s="74"/>
-      <c r="DN2" s="74"/>
-      <c r="DO2" s="74"/>
-      <c r="DP2" s="74"/>
-      <c r="DQ2" s="74"/>
-      <c r="DR2" s="74"/>
-      <c r="DS2" s="74"/>
-      <c r="DT2" s="74"/>
-      <c r="DU2" s="74"/>
-      <c r="DV2" s="74"/>
-      <c r="DW2" s="74"/>
-      <c r="DX2" s="74"/>
-      <c r="DY2" s="74"/>
-      <c r="DZ2" s="74"/>
-      <c r="EA2" s="74"/>
-      <c r="EB2" s="74"/>
-      <c r="EC2" s="74"/>
-      <c r="ED2" s="74"/>
-      <c r="EE2" s="74"/>
-      <c r="EF2" s="74"/>
-      <c r="EG2" s="74"/>
-      <c r="EH2" s="74"/>
-      <c r="EI2" s="74"/>
-      <c r="EJ2" s="74"/>
-      <c r="EK2" s="74"/>
-      <c r="EL2" s="74"/>
-      <c r="EM2" s="74"/>
-      <c r="EN2" s="74"/>
-      <c r="EO2" s="74"/>
-      <c r="EP2" s="74"/>
-      <c r="EQ2" s="74"/>
-      <c r="ER2" s="74"/>
+      <c r="DE2" s="85"/>
+      <c r="DF2" s="85"/>
+      <c r="DG2" s="85"/>
+      <c r="DH2" s="85"/>
+      <c r="DI2" s="85"/>
+      <c r="DJ2" s="85"/>
+      <c r="DK2" s="85"/>
+      <c r="DL2" s="85"/>
+      <c r="DM2" s="85"/>
+      <c r="DN2" s="85"/>
+      <c r="DO2" s="85"/>
+      <c r="DP2" s="85"/>
+      <c r="DQ2" s="85"/>
+      <c r="DR2" s="85"/>
+      <c r="DS2" s="85"/>
+      <c r="DT2" s="85"/>
+      <c r="DU2" s="85"/>
+      <c r="DV2" s="85"/>
+      <c r="DW2" s="85"/>
+      <c r="DX2" s="85"/>
+      <c r="DY2" s="85"/>
+      <c r="DZ2" s="85"/>
+      <c r="EA2" s="85"/>
+      <c r="EB2" s="85"/>
+      <c r="EC2" s="85"/>
+      <c r="ED2" s="85"/>
+      <c r="EE2" s="85"/>
+      <c r="EF2" s="85"/>
+      <c r="EG2" s="85"/>
+      <c r="EH2" s="85"/>
+      <c r="EI2" s="85"/>
+      <c r="EJ2" s="85"/>
+      <c r="EK2" s="85"/>
+      <c r="EL2" s="85"/>
+      <c r="EM2" s="85"/>
+      <c r="EN2" s="85"/>
+      <c r="EO2" s="85"/>
+      <c r="EP2" s="85"/>
+      <c r="EQ2" s="85"/>
+      <c r="ER2" s="85"/>
+      <c r="ES2" s="85"/>
     </row>
-    <row r="3" spans="2:148" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="81" t="s">
+    <row r="3" spans="2:149" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="65" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
+      <c r="AO3" s="82"/>
+      <c r="AP3" s="82"/>
+      <c r="AQ3" s="82"/>
+      <c r="AR3" s="64" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="65"/>
-      <c r="AT3" s="65"/>
-      <c r="AU3" s="65"/>
-      <c r="AV3" s="65"/>
-      <c r="AW3" s="65"/>
-      <c r="AX3" s="65"/>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="65"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
-      <c r="BD3" s="66" t="s">
+      <c r="AS3" s="64"/>
+      <c r="AT3" s="64"/>
+      <c r="AU3" s="64"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="64"/>
+      <c r="AX3" s="64"/>
+      <c r="AY3" s="64"/>
+      <c r="AZ3" s="64"/>
+      <c r="BA3" s="64"/>
+      <c r="BB3" s="64"/>
+      <c r="BC3" s="64"/>
+      <c r="BD3" s="65" t="s">
         <v>322</v>
       </c>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="67"/>
-      <c r="BR3" s="67"/>
-      <c r="BS3" s="67"/>
-      <c r="BT3" s="67"/>
-      <c r="BU3" s="67"/>
-      <c r="BV3" s="67"/>
-      <c r="BW3" s="67"/>
-      <c r="BX3" s="67"/>
-      <c r="BY3" s="67"/>
-      <c r="BZ3" s="67"/>
-      <c r="CA3" s="67"/>
-      <c r="CB3" s="67"/>
-      <c r="CC3" s="67"/>
-      <c r="CD3" s="67"/>
-      <c r="CE3" s="67"/>
-      <c r="CF3" s="67"/>
-      <c r="CG3" s="67"/>
-      <c r="CH3" s="67"/>
-      <c r="CI3" s="67"/>
-      <c r="CJ3" s="67"/>
-      <c r="CK3" s="67"/>
-      <c r="CL3" s="67"/>
-      <c r="CM3" s="67"/>
-      <c r="CN3" s="67"/>
-      <c r="CO3" s="67"/>
-      <c r="CP3" s="67"/>
-      <c r="CQ3" s="71"/>
-      <c r="CR3" s="65" t="s">
+      <c r="BE3" s="66"/>
+      <c r="BF3" s="66"/>
+      <c r="BG3" s="66"/>
+      <c r="BH3" s="66"/>
+      <c r="BI3" s="66"/>
+      <c r="BJ3" s="66"/>
+      <c r="BK3" s="66"/>
+      <c r="BL3" s="66"/>
+      <c r="BM3" s="66"/>
+      <c r="BN3" s="66"/>
+      <c r="BO3" s="66"/>
+      <c r="BP3" s="66"/>
+      <c r="BQ3" s="66"/>
+      <c r="BR3" s="66"/>
+      <c r="BS3" s="66"/>
+      <c r="BT3" s="66"/>
+      <c r="BU3" s="66"/>
+      <c r="BV3" s="66"/>
+      <c r="BW3" s="66"/>
+      <c r="BX3" s="66"/>
+      <c r="BY3" s="66"/>
+      <c r="BZ3" s="66"/>
+      <c r="CA3" s="66"/>
+      <c r="CB3" s="66"/>
+      <c r="CC3" s="66"/>
+      <c r="CD3" s="66"/>
+      <c r="CE3" s="66"/>
+      <c r="CF3" s="66"/>
+      <c r="CG3" s="66"/>
+      <c r="CH3" s="66"/>
+      <c r="CI3" s="66"/>
+      <c r="CJ3" s="66"/>
+      <c r="CK3" s="66"/>
+      <c r="CL3" s="66"/>
+      <c r="CM3" s="66"/>
+      <c r="CN3" s="66"/>
+      <c r="CO3" s="66"/>
+      <c r="CP3" s="66"/>
+      <c r="CQ3" s="70"/>
+      <c r="CR3" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="65"/>
-      <c r="CT3" s="65"/>
-      <c r="CU3" s="65"/>
-      <c r="CV3" s="65"/>
-      <c r="CW3" s="65"/>
-      <c r="CX3" s="65"/>
-      <c r="CY3" s="65"/>
-      <c r="CZ3" s="65"/>
-      <c r="DA3" s="65"/>
-      <c r="DB3" s="65"/>
-      <c r="DC3" s="65"/>
-      <c r="DD3" s="66" t="s">
+      <c r="CS3" s="64"/>
+      <c r="CT3" s="64"/>
+      <c r="CU3" s="64"/>
+      <c r="CV3" s="64"/>
+      <c r="CW3" s="64"/>
+      <c r="CX3" s="64"/>
+      <c r="CY3" s="64"/>
+      <c r="CZ3" s="64"/>
+      <c r="DA3" s="64"/>
+      <c r="DB3" s="64"/>
+      <c r="DC3" s="64"/>
+      <c r="DD3" s="86" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="67"/>
-      <c r="DF3" s="67"/>
-      <c r="DG3" s="67"/>
-      <c r="DH3" s="67"/>
-      <c r="DI3" s="67"/>
-      <c r="DJ3" s="67"/>
-      <c r="DK3" s="67"/>
-      <c r="DL3" s="67"/>
-      <c r="DM3" s="67"/>
-      <c r="DN3" s="67"/>
-      <c r="DO3" s="67"/>
-      <c r="DP3" s="67"/>
-      <c r="DQ3" s="67"/>
-      <c r="DR3" s="67"/>
-      <c r="DS3" s="67"/>
-      <c r="DT3" s="67"/>
-      <c r="DU3" s="67"/>
-      <c r="DV3" s="67"/>
-      <c r="DW3" s="67"/>
-      <c r="DX3" s="67"/>
-      <c r="DY3" s="67"/>
-      <c r="DZ3" s="67"/>
-      <c r="EA3" s="67"/>
-      <c r="EB3" s="67"/>
-      <c r="EC3" s="67"/>
-      <c r="ED3" s="67"/>
-      <c r="EE3" s="67"/>
-      <c r="EF3" s="67"/>
-      <c r="EG3" s="67"/>
-      <c r="EH3" s="67"/>
-      <c r="EI3" s="67"/>
-      <c r="EJ3" s="67"/>
-      <c r="EK3" s="67"/>
-      <c r="EL3" s="67"/>
-      <c r="EM3" s="67"/>
-      <c r="EN3" s="67"/>
-      <c r="EO3" s="67"/>
-      <c r="EP3" s="67"/>
-      <c r="EQ3" s="71"/>
-      <c r="ER3" s="44" t="s">
+      <c r="DE3" s="87"/>
+      <c r="DF3" s="87"/>
+      <c r="DG3" s="87"/>
+      <c r="DH3" s="87"/>
+      <c r="DI3" s="87"/>
+      <c r="DJ3" s="87"/>
+      <c r="DK3" s="87"/>
+      <c r="DL3" s="87"/>
+      <c r="DM3" s="87"/>
+      <c r="DN3" s="87"/>
+      <c r="DO3" s="87"/>
+      <c r="DP3" s="87"/>
+      <c r="DQ3" s="87"/>
+      <c r="DR3" s="87"/>
+      <c r="DS3" s="87"/>
+      <c r="DT3" s="87"/>
+      <c r="DU3" s="87"/>
+      <c r="DV3" s="87"/>
+      <c r="DW3" s="87"/>
+      <c r="DX3" s="87"/>
+      <c r="DY3" s="87"/>
+      <c r="DZ3" s="87"/>
+      <c r="EA3" s="87"/>
+      <c r="EB3" s="87"/>
+      <c r="EC3" s="87"/>
+      <c r="ED3" s="87"/>
+      <c r="EE3" s="87"/>
+      <c r="EF3" s="87"/>
+      <c r="EG3" s="87"/>
+      <c r="EH3" s="87"/>
+      <c r="EI3" s="87"/>
+      <c r="EJ3" s="87"/>
+      <c r="EK3" s="87"/>
+      <c r="EL3" s="87"/>
+      <c r="EM3" s="87"/>
+      <c r="EN3" s="87"/>
+      <c r="EO3" s="87"/>
+      <c r="EP3" s="87"/>
+      <c r="EQ3" s="88"/>
+      <c r="ER3" s="65" t="s">
         <v>414</v>
       </c>
+      <c r="ES3" s="70"/>
     </row>
-    <row r="4" spans="2:148" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="75" t="s">
+    <row r="4" spans="2:149" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="76" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="75" t="s">
+      <c r="H4" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="75" t="s">
+      <c r="I4" s="76" t="s">
         <v>188</v>
       </c>
-      <c r="J4" s="75" t="s">
+      <c r="J4" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="K4" s="75" t="s">
+      <c r="K4" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="L4" s="75" t="s">
+      <c r="L4" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="75" t="s">
+      <c r="M4" s="76" t="s">
         <v>192</v>
       </c>
-      <c r="N4" s="75" t="s">
+      <c r="N4" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="O4" s="75" t="s">
+      <c r="O4" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="75" t="s">
+      <c r="P4" s="76" t="s">
         <v>195</v>
       </c>
-      <c r="Q4" s="75" t="s">
+      <c r="Q4" s="76" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="82" t="s">
+      <c r="R4" s="83" t="s">
         <v>196</v>
       </c>
-      <c r="S4" s="75" t="s">
+      <c r="S4" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="T4" s="75" t="s">
+      <c r="T4" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="U4" s="75" t="s">
+      <c r="U4" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="V4" s="75" t="s">
+      <c r="V4" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="W4" s="75" t="s">
+      <c r="W4" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="X4" s="75" t="s">
+      <c r="X4" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="79" t="s">
+      <c r="Y4" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="Z4" s="75" t="s">
+      <c r="Z4" s="76" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" s="75" t="s">
+      <c r="AA4" s="76" t="s">
         <v>163</v>
       </c>
-      <c r="AB4" s="75" t="s">
+      <c r="AB4" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="AC4" s="79" t="s">
+      <c r="AC4" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="AD4" s="75" t="s">
+      <c r="AD4" s="76" t="s">
         <v>166</v>
       </c>
-      <c r="AE4" s="75" t="s">
+      <c r="AE4" s="76" t="s">
         <v>199</v>
       </c>
-      <c r="AF4" s="75" t="s">
+      <c r="AF4" s="76" t="s">
         <v>200</v>
       </c>
-      <c r="AG4" s="75" t="s">
+      <c r="AG4" s="76" t="s">
         <v>201</v>
       </c>
-      <c r="AH4" s="75" t="s">
+      <c r="AH4" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="AI4" s="79" t="s">
+      <c r="AI4" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="AJ4" s="79" t="s">
+      <c r="AJ4" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="AK4" s="79" t="s">
+      <c r="AK4" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AL4" s="79" t="s">
+      <c r="AL4" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="AM4" s="79" t="s">
+      <c r="AM4" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="AN4" s="75" t="s">
+      <c r="AN4" s="76" t="s">
         <v>171</v>
       </c>
-      <c r="AO4" s="79" t="s">
+      <c r="AO4" s="80" t="s">
         <v>172</v>
       </c>
-      <c r="AP4" s="79" t="s">
+      <c r="AP4" s="80" t="s">
         <v>173</v>
       </c>
-      <c r="AQ4" s="75" t="s">
+      <c r="AQ4" s="76" t="s">
         <v>174</v>
       </c>
-      <c r="AR4" s="79" t="s">
+      <c r="AR4" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="AS4" s="75" t="s">
+      <c r="AS4" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="AT4" s="75" t="s">
+      <c r="AT4" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="AU4" s="75" t="s">
+      <c r="AU4" s="76" t="s">
         <v>178</v>
       </c>
-      <c r="AV4" s="75" t="s">
+      <c r="AV4" s="76" t="s">
         <v>179</v>
       </c>
-      <c r="AW4" s="75" t="s">
+      <c r="AW4" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="75" t="s">
+      <c r="AX4" s="76" t="s">
         <v>203</v>
       </c>
-      <c r="AY4" s="75" t="s">
+      <c r="AY4" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="AZ4" s="75" t="s">
+      <c r="AZ4" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="BA4" s="75" t="s">
+      <c r="BA4" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="BB4" s="75" t="s">
+      <c r="BB4" s="76" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="75" t="s">
+      <c r="BC4" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="BF4" s="46" t="s">
+      <c r="BF4" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="BG4" s="46" t="s">
+      <c r="BG4" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="BH4" s="46" t="s">
+      <c r="BH4" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="BI4" s="46" t="s">
+      <c r="BI4" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="BJ4" s="46" t="s">
+      <c r="BJ4" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="BK4" s="46" t="s">
+      <c r="BK4" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="BL4" s="46" t="s">
+      <c r="BL4" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="BM4" s="46" t="s">
+      <c r="BM4" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="BN4" s="46" t="s">
+      <c r="BN4" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="BO4" s="46" t="s">
+      <c r="BO4" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="BP4" s="46" t="s">
+      <c r="BP4" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="BQ4" s="46" t="s">
+      <c r="BQ4" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="BR4" s="46" t="s">
+      <c r="BR4" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="BS4" s="46" t="s">
+      <c r="BS4" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="BT4" s="46" t="s">
+      <c r="BT4" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="BU4" s="58" t="s">
+      <c r="BU4" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="BV4" s="58" t="s">
+      <c r="BV4" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="BW4" s="58" t="s">
+      <c r="BW4" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="BX4" s="58" t="s">
+      <c r="BX4" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="BY4" s="58" t="s">
+      <c r="BY4" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="BZ4" s="58" t="s">
+      <c r="BZ4" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="CA4" s="46" t="s">
+      <c r="CA4" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="CB4" s="46" t="s">
+      <c r="CB4" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="CC4" s="46" t="s">
+      <c r="CC4" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="CD4" s="46" t="s">
+      <c r="CD4" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="CE4" s="48" t="s">
+      <c r="CE4" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="CF4" s="48" t="s">
+      <c r="CF4" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="CG4" s="48" t="s">
+      <c r="CG4" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="CH4" s="48" t="s">
+      <c r="CH4" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="CI4" s="48" t="s">
+      <c r="CI4" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="CJ4" s="48" t="s">
+      <c r="CJ4" s="47" t="s">
         <v>263</v>
       </c>
-      <c r="CK4" s="48" t="s">
+      <c r="CK4" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="CL4" s="48" t="s">
+      <c r="CL4" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="CM4" s="48" t="s">
+      <c r="CM4" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="CN4" s="48" t="s">
+      <c r="CN4" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="CO4" s="48" t="s">
+      <c r="CO4" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="CP4" s="48" t="s">
+      <c r="CP4" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="CQ4" s="48" t="s">
+      <c r="CQ4" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="CR4" s="48" t="s">
+      <c r="CR4" s="47" t="s">
         <v>283</v>
       </c>
-      <c r="CS4" s="48" t="s">
+      <c r="CS4" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="CT4" s="48" t="s">
+      <c r="CT4" s="47" t="s">
         <v>287</v>
       </c>
-      <c r="CU4" s="48" t="s">
+      <c r="CU4" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="CV4" s="48" t="s">
+      <c r="CV4" s="47" t="s">
         <v>372</v>
       </c>
-      <c r="CW4" s="48" t="s">
+      <c r="CW4" s="47" t="s">
         <v>293</v>
       </c>
-      <c r="CX4" s="48" t="s">
+      <c r="CX4" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="CY4" s="48" t="s">
+      <c r="CY4" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="CZ4" s="48" t="s">
+      <c r="CZ4" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="DA4" s="48" t="s">
+      <c r="DA4" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="DB4" s="48" t="s">
+      <c r="DB4" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="DC4" s="48" t="s">
+      <c r="DC4" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="DD4" s="70" t="s">
+      <c r="DD4" s="69" t="s">
         <v>307</v>
       </c>
-      <c r="DE4" s="70" t="s">
+      <c r="DE4" s="69" t="s">
         <v>309</v>
       </c>
-      <c r="DF4" s="70" t="s">
+      <c r="DF4" s="69" t="s">
         <v>311</v>
       </c>
-      <c r="DG4" s="70" t="s">
+      <c r="DG4" s="69" t="s">
         <v>313</v>
       </c>
-      <c r="DH4" s="70" t="s">
+      <c r="DH4" s="69" t="s">
         <v>314</v>
       </c>
-      <c r="DI4" s="70" t="s">
+      <c r="DI4" s="69" t="s">
         <v>317</v>
       </c>
-      <c r="DJ4" s="70" t="s">
+      <c r="DJ4" s="69" t="s">
         <v>319</v>
       </c>
-      <c r="DK4" s="70" t="s">
+      <c r="DK4" s="69" t="s">
         <v>327</v>
       </c>
-      <c r="DL4" s="70" t="s">
+      <c r="DL4" s="69" t="s">
         <v>329</v>
       </c>
-      <c r="DM4" s="76" t="s">
+      <c r="DM4" s="77" t="s">
         <v>331</v>
       </c>
-      <c r="DN4" s="70" t="s">
+      <c r="DN4" s="69" t="s">
         <v>333</v>
       </c>
-      <c r="DO4" s="70" t="s">
+      <c r="DO4" s="69" t="s">
         <v>335</v>
       </c>
-      <c r="DP4" s="70" t="s">
+      <c r="DP4" s="69" t="s">
         <v>337</v>
       </c>
-      <c r="DQ4" s="70" t="s">
+      <c r="DQ4" s="69" t="s">
         <v>339</v>
       </c>
-      <c r="DR4" s="70" t="s">
+      <c r="DR4" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="DS4" s="70" t="s">
+      <c r="DS4" s="69" t="s">
         <v>346</v>
       </c>
-      <c r="DT4" s="70" t="s">
+      <c r="DT4" s="69" t="s">
         <v>350</v>
       </c>
-      <c r="DU4" s="76" t="s">
+      <c r="DU4" s="77" t="s">
         <v>366</v>
       </c>
-      <c r="DV4" s="76" t="s">
+      <c r="DV4" s="77" t="s">
         <v>367</v>
       </c>
-      <c r="DW4" s="76" t="s">
+      <c r="DW4" s="77" t="s">
         <v>368</v>
       </c>
-      <c r="DX4" s="76" t="s">
+      <c r="DX4" s="77" t="s">
         <v>369</v>
       </c>
-      <c r="DY4" s="76" t="s">
+      <c r="DY4" s="77" t="s">
         <v>370</v>
       </c>
-      <c r="DZ4" s="70" t="s">
+      <c r="DZ4" s="69" t="s">
         <v>364</v>
       </c>
-      <c r="EA4" s="70" t="s">
+      <c r="EA4" s="69" t="s">
         <v>373</v>
       </c>
-      <c r="EB4" s="70" t="s">
+      <c r="EB4" s="69" t="s">
         <v>376</v>
       </c>
-      <c r="EC4" s="70" t="s">
+      <c r="EC4" s="69" t="s">
         <v>380</v>
       </c>
-      <c r="ED4" s="70" t="s">
+      <c r="ED4" s="69" t="s">
         <v>383</v>
       </c>
-      <c r="EE4" s="70" t="s">
+      <c r="EE4" s="69" t="s">
         <v>385</v>
       </c>
-      <c r="EF4" s="70" t="s">
+      <c r="EF4" s="69" t="s">
         <v>387</v>
       </c>
-      <c r="EG4" s="70" t="s">
+      <c r="EG4" s="69" t="s">
         <v>388</v>
       </c>
-      <c r="EH4" s="70" t="s">
+      <c r="EH4" s="69" t="s">
         <v>390</v>
       </c>
-      <c r="EI4" s="70" t="s">
+      <c r="EI4" s="69" t="s">
         <v>392</v>
       </c>
-      <c r="EJ4" s="70" t="s">
+      <c r="EJ4" s="69" t="s">
         <v>396</v>
       </c>
-      <c r="EK4" s="70" t="s">
+      <c r="EK4" s="69" t="s">
         <v>397</v>
       </c>
-      <c r="EL4" s="70" t="s">
+      <c r="EL4" s="69" t="s">
         <v>399</v>
       </c>
-      <c r="EM4" s="70" t="s">
+      <c r="EM4" s="69" t="s">
         <v>401</v>
       </c>
-      <c r="EN4" s="70" t="s">
+      <c r="EN4" s="69" t="s">
         <v>403</v>
       </c>
-      <c r="EO4" s="70" t="s">
+      <c r="EO4" s="69" t="s">
         <v>406</v>
       </c>
-      <c r="EP4" s="70" t="s">
+      <c r="EP4" s="69" t="s">
         <v>408</v>
       </c>
-      <c r="EQ4" s="70" t="s">
+      <c r="EQ4" s="69" t="s">
         <v>410</v>
       </c>
-      <c r="ER4" s="70" t="s">
+      <c r="ER4" s="69" t="s">
         <v>413</v>
       </c>
+      <c r="ES4" s="69" t="s">
+        <v>417</v>
+      </c>
     </row>
-    <row r="5" spans="2:148" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="80"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="80"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="80"/>
-      <c r="AJ5" s="80"/>
-      <c r="AK5" s="80"/>
-      <c r="AL5" s="80"/>
-      <c r="AM5" s="80"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="80"/>
-      <c r="AP5" s="80"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="80"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="47"/>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="47"/>
-      <c r="BM5" s="47"/>
-      <c r="BN5" s="47"/>
-      <c r="BO5" s="47"/>
-      <c r="BP5" s="47"/>
-      <c r="BQ5" s="47"/>
-      <c r="BR5" s="47"/>
-      <c r="BS5" s="47"/>
-      <c r="BT5" s="47"/>
-      <c r="BU5" s="50"/>
-      <c r="BV5" s="50"/>
-      <c r="BW5" s="50"/>
-      <c r="BX5" s="50"/>
-      <c r="BY5" s="50"/>
-      <c r="BZ5" s="50"/>
-      <c r="CA5" s="47"/>
-      <c r="CB5" s="47"/>
-      <c r="CC5" s="47"/>
-      <c r="CD5" s="47"/>
-      <c r="CE5" s="49"/>
-      <c r="CF5" s="49"/>
-      <c r="CG5" s="49"/>
-      <c r="CH5" s="49"/>
-      <c r="CI5" s="49"/>
-      <c r="CJ5" s="49"/>
-      <c r="CK5" s="49"/>
-      <c r="CL5" s="49"/>
-      <c r="CM5" s="49"/>
-      <c r="CN5" s="49"/>
-      <c r="CO5" s="49"/>
-      <c r="CP5" s="49"/>
-      <c r="CQ5" s="49"/>
-      <c r="CR5" s="49"/>
-      <c r="CS5" s="49"/>
-      <c r="CT5" s="49"/>
-      <c r="CU5" s="49"/>
-      <c r="CV5" s="49"/>
-      <c r="CW5" s="49"/>
-      <c r="CX5" s="49"/>
-      <c r="CY5" s="49"/>
-      <c r="CZ5" s="49"/>
-      <c r="DA5" s="49"/>
-      <c r="DB5" s="49"/>
-      <c r="DC5" s="49"/>
-      <c r="DD5" s="49"/>
-      <c r="DE5" s="49"/>
-      <c r="DF5" s="49"/>
-      <c r="DG5" s="49"/>
-      <c r="DH5" s="49"/>
-      <c r="DI5" s="49"/>
-      <c r="DJ5" s="49"/>
-      <c r="DK5" s="49"/>
-      <c r="DL5" s="49"/>
-      <c r="DM5" s="77"/>
-      <c r="DN5" s="49"/>
-      <c r="DO5" s="49"/>
-      <c r="DP5" s="49"/>
-      <c r="DQ5" s="49"/>
-      <c r="DR5" s="49"/>
-      <c r="DS5" s="49"/>
-      <c r="DT5" s="49"/>
-      <c r="DU5" s="77"/>
-      <c r="DV5" s="77"/>
-      <c r="DW5" s="77"/>
-      <c r="DX5" s="77"/>
-      <c r="DY5" s="77"/>
-      <c r="DZ5" s="49"/>
-      <c r="EA5" s="49"/>
-      <c r="EB5" s="49"/>
-      <c r="EC5" s="49"/>
-      <c r="ED5" s="49"/>
-      <c r="EE5" s="70"/>
-      <c r="EF5" s="70"/>
-      <c r="EG5" s="70"/>
-      <c r="EH5" s="70"/>
-      <c r="EI5" s="70"/>
-      <c r="EJ5" s="70"/>
-      <c r="EK5" s="70"/>
-      <c r="EL5" s="70"/>
-      <c r="EM5" s="70"/>
-      <c r="EN5" s="70"/>
-      <c r="EO5" s="70"/>
-      <c r="EP5" s="70"/>
-      <c r="EQ5" s="70"/>
-      <c r="ER5" s="70"/>
+    <row r="5" spans="2:149" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="63"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="81"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="81"/>
+      <c r="AK5" s="81"/>
+      <c r="AL5" s="81"/>
+      <c r="AM5" s="81"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="81"/>
+      <c r="AP5" s="81"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="81"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="46"/>
+      <c r="BM5" s="46"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="49"/>
+      <c r="BV5" s="49"/>
+      <c r="BW5" s="49"/>
+      <c r="BX5" s="49"/>
+      <c r="BY5" s="49"/>
+      <c r="BZ5" s="49"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="48"/>
+      <c r="CF5" s="48"/>
+      <c r="CG5" s="48"/>
+      <c r="CH5" s="48"/>
+      <c r="CI5" s="48"/>
+      <c r="CJ5" s="48"/>
+      <c r="CK5" s="48"/>
+      <c r="CL5" s="48"/>
+      <c r="CM5" s="48"/>
+      <c r="CN5" s="48"/>
+      <c r="CO5" s="48"/>
+      <c r="CP5" s="48"/>
+      <c r="CQ5" s="48"/>
+      <c r="CR5" s="48"/>
+      <c r="CS5" s="48"/>
+      <c r="CT5" s="48"/>
+      <c r="CU5" s="48"/>
+      <c r="CV5" s="48"/>
+      <c r="CW5" s="48"/>
+      <c r="CX5" s="48"/>
+      <c r="CY5" s="48"/>
+      <c r="CZ5" s="48"/>
+      <c r="DA5" s="48"/>
+      <c r="DB5" s="48"/>
+      <c r="DC5" s="48"/>
+      <c r="DD5" s="48"/>
+      <c r="DE5" s="48"/>
+      <c r="DF5" s="48"/>
+      <c r="DG5" s="48"/>
+      <c r="DH5" s="48"/>
+      <c r="DI5" s="48"/>
+      <c r="DJ5" s="48"/>
+      <c r="DK5" s="48"/>
+      <c r="DL5" s="48"/>
+      <c r="DM5" s="78"/>
+      <c r="DN5" s="48"/>
+      <c r="DO5" s="48"/>
+      <c r="DP5" s="48"/>
+      <c r="DQ5" s="48"/>
+      <c r="DR5" s="48"/>
+      <c r="DS5" s="48"/>
+      <c r="DT5" s="48"/>
+      <c r="DU5" s="78"/>
+      <c r="DV5" s="78"/>
+      <c r="DW5" s="78"/>
+      <c r="DX5" s="78"/>
+      <c r="DY5" s="78"/>
+      <c r="DZ5" s="48"/>
+      <c r="EA5" s="48"/>
+      <c r="EB5" s="48"/>
+      <c r="EC5" s="48"/>
+      <c r="ED5" s="48"/>
+      <c r="EE5" s="69"/>
+      <c r="EF5" s="69"/>
+      <c r="EG5" s="69"/>
+      <c r="EH5" s="69"/>
+      <c r="EI5" s="69"/>
+      <c r="EJ5" s="69"/>
+      <c r="EK5" s="69"/>
+      <c r="EL5" s="69"/>
+      <c r="EM5" s="69"/>
+      <c r="EN5" s="69"/>
+      <c r="EO5" s="69"/>
+      <c r="EP5" s="69"/>
+      <c r="EQ5" s="69"/>
+      <c r="ER5" s="69"/>
+      <c r="ES5" s="69"/>
     </row>
-    <row r="6" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -35865,8 +36065,11 @@
       <c r="ER6" s="28">
         <v>112</v>
       </c>
+      <c r="ES6" s="28">
+        <v>145</v>
+      </c>
     </row>
-    <row r="7" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -36308,8 +36511,11 @@
       <c r="ER7" s="15">
         <v>0</v>
       </c>
+      <c r="ES7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -36751,8 +36957,11 @@
       <c r="ER8" s="28">
         <v>15</v>
       </c>
+      <c r="ES8" s="28">
+        <v>22</v>
+      </c>
     </row>
-    <row r="9" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -37194,8 +37403,11 @@
       <c r="ER9" s="15">
         <v>63</v>
       </c>
+      <c r="ES9" s="15">
+        <v>82</v>
+      </c>
     </row>
-    <row r="10" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -37637,8 +37849,11 @@
       <c r="ER10" s="15">
         <v>0</v>
       </c>
+      <c r="ES10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -38080,8 +38295,11 @@
       <c r="ER11" s="15">
         <v>19</v>
       </c>
+      <c r="ES11" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="12" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -38523,8 +38741,11 @@
       <c r="ER12" s="15">
         <v>14</v>
       </c>
+      <c r="ES12" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="13" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -38966,8 +39187,11 @@
       <c r="ER13" s="15">
         <v>11</v>
       </c>
+      <c r="ES13" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="14" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -39409,8 +39633,11 @@
       <c r="ER14" s="15">
         <v>24</v>
       </c>
+      <c r="ES14" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="15" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -39852,8 +40079,11 @@
       <c r="ER15" s="15">
         <v>1</v>
       </c>
+      <c r="ES15" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="16" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -40295,8 +40525,11 @@
       <c r="ER16" s="28">
         <v>114</v>
       </c>
+      <c r="ES16" s="28">
+        <v>158</v>
+      </c>
     </row>
-    <row r="17" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -40738,8 +40971,11 @@
       <c r="ER17" s="15">
         <v>154</v>
       </c>
+      <c r="ES17" s="15">
+        <v>224</v>
+      </c>
     </row>
-    <row r="18" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -41181,9 +41417,12 @@
       <c r="ER18" s="34">
         <v>1483</v>
       </c>
+      <c r="ES18" s="34">
+        <v>2149</v>
+      </c>
     </row>
-    <row r="19" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="54" t="s">
+    <row r="19" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="53" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -41624,9 +41863,12 @@
       <c r="ER19" s="15">
         <v>39</v>
       </c>
+      <c r="ES19" s="15">
+        <v>83</v>
+      </c>
     </row>
-    <row r="20" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="54"/>
+    <row r="20" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="53"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -42065,9 +42307,12 @@
       <c r="ER20" s="28">
         <v>125</v>
       </c>
+      <c r="ES20" s="28">
+        <v>217</v>
+      </c>
     </row>
-    <row r="21" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="54"/>
+    <row r="21" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="53"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -42506,8 +42751,11 @@
       <c r="ER21" s="15">
         <v>29</v>
       </c>
+      <c r="ES21" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="22" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -42949,8 +43197,11 @@
       <c r="ER22" s="15">
         <v>12</v>
       </c>
+      <c r="ES22" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -43392,8 +43643,11 @@
       <c r="ER23" s="15">
         <v>1</v>
       </c>
+      <c r="ES23" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -43835,8 +44089,11 @@
       <c r="ER24" s="15">
         <v>14</v>
       </c>
+      <c r="ES24" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="25" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -44278,8 +44535,11 @@
       <c r="ER25" s="15">
         <v>0</v>
       </c>
+      <c r="ES25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -44721,8 +44981,11 @@
       <c r="ER26" s="15">
         <v>13</v>
       </c>
+      <c r="ES26" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="27" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -45164,8 +45427,11 @@
       <c r="ER27" s="15">
         <v>0</v>
       </c>
+      <c r="ES27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -45607,9 +45873,12 @@
       <c r="ER28" s="15">
         <v>2</v>
       </c>
+      <c r="ES28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="55" t="s">
+    <row r="29" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="54" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -46050,9 +46319,12 @@
       <c r="ER29" s="15">
         <v>1</v>
       </c>
+      <c r="ES29" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="55"/>
+    <row r="30" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="54"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -46491,8 +46763,11 @@
       <c r="ER30" s="15">
         <v>5</v>
       </c>
+      <c r="ES30" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="31" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -46934,8 +47209,11 @@
       <c r="ER31" s="15">
         <v>24</v>
       </c>
+      <c r="ES31" s="15">
+        <v>56</v>
+      </c>
     </row>
-    <row r="32" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -47377,8 +47655,11 @@
       <c r="ER32" s="15">
         <v>2</v>
       </c>
+      <c r="ES32" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -47820,8 +48101,11 @@
       <c r="ER33" s="15">
         <v>0</v>
       </c>
+      <c r="ES33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -48263,9 +48547,12 @@
       <c r="ER34" s="15">
         <v>54</v>
       </c>
+      <c r="ES34" s="15">
+        <v>89</v>
+      </c>
     </row>
-    <row r="35" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="54" t="s">
+    <row r="35" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="53" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -48706,9 +48993,12 @@
       <c r="ER35" s="15">
         <v>281</v>
       </c>
+      <c r="ES35" s="15">
+        <v>399</v>
+      </c>
     </row>
-    <row r="36" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="54"/>
+    <row r="36" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="53"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -49147,8 +49437,11 @@
       <c r="ER36" s="28">
         <v>24</v>
       </c>
+      <c r="ES36" s="28">
+        <v>40</v>
+      </c>
     </row>
-    <row r="37" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -49590,8 +49883,11 @@
       <c r="ER37" s="15">
         <v>28</v>
       </c>
+      <c r="ES37" s="15">
+        <v>54</v>
+      </c>
     </row>
-    <row r="38" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -50033,8 +50329,11 @@
       <c r="ER38" s="15">
         <v>6</v>
       </c>
+      <c r="ES38" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="39" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -50476,8 +50775,11 @@
       <c r="ER39" s="15">
         <v>7</v>
       </c>
+      <c r="ES39" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="40" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -50919,8 +51221,11 @@
       <c r="ER40" s="15">
         <v>0</v>
       </c>
+      <c r="ES40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -51362,8 +51667,11 @@
       <c r="ER41" s="15">
         <v>0</v>
       </c>
+      <c r="ES41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -51805,8 +52113,11 @@
       <c r="ER42" s="15">
         <v>7</v>
       </c>
+      <c r="ES42" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -52248,8 +52559,11 @@
       <c r="ER43" s="28">
         <v>79</v>
       </c>
+      <c r="ES43" s="28">
+        <v>79</v>
+      </c>
     </row>
-    <row r="44" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -52691,8 +53005,11 @@
       <c r="ER44" s="15">
         <v>2</v>
       </c>
+      <c r="ES44" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -53134,8 +53451,11 @@
       <c r="ER45" s="15">
         <v>9</v>
       </c>
+      <c r="ES45" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -53577,8 +53897,11 @@
       <c r="ER46" s="15">
         <v>8</v>
       </c>
+      <c r="ES46" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="47" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -54020,8 +54343,11 @@
       <c r="ER47" s="15">
         <v>3</v>
       </c>
+      <c r="ES47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -54463,9 +54789,12 @@
       <c r="ER48" s="15">
         <v>1</v>
       </c>
+      <c r="ES48" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="49" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="54" t="s">
+    <row r="49" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="53" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -54906,9 +55235,12 @@
       <c r="ER49" s="15">
         <v>18</v>
       </c>
+      <c r="ES49" s="15">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="54"/>
+    <row r="50" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="53"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -55347,8 +55679,11 @@
       <c r="ER50" s="15">
         <v>4</v>
       </c>
+      <c r="ES50" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="51" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -55790,8 +56125,11 @@
       <c r="ER51" s="15">
         <v>2</v>
       </c>
+      <c r="ES51" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -56233,8 +56571,11 @@
       <c r="ER52" s="15">
         <v>17</v>
       </c>
+      <c r="ES52" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="53" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -56676,8 +57017,11 @@
       <c r="ER53" s="15">
         <v>24</v>
       </c>
+      <c r="ES53" s="15">
+        <v>37</v>
+      </c>
     </row>
-    <row r="54" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -57119,8 +57463,11 @@
       <c r="ER54" s="15">
         <v>8</v>
       </c>
+      <c r="ES54" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="55" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -57562,8 +57909,11 @@
       <c r="ER55" s="15">
         <v>24</v>
       </c>
+      <c r="ES55" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="56" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -58005,8 +58355,11 @@
       <c r="ER56" s="15">
         <v>0</v>
       </c>
+      <c r="ES56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -58448,8 +58801,11 @@
       <c r="ER57" s="15">
         <v>2</v>
       </c>
+      <c r="ES57" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="2:148" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -58918,7 +59274,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:ER58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:ES58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -59033,11 +59389,17 @@
         <f t="shared" si="8"/>
         <v>2885</v>
       </c>
+      <c r="ES58" s="14">
+        <f t="shared" si="8"/>
+        <v>4285</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="163">
+    <mergeCell ref="DD2:ES2"/>
+    <mergeCell ref="ER3:ES3"/>
+    <mergeCell ref="ES4:ES5"/>
     <mergeCell ref="DD3:EQ3"/>
-    <mergeCell ref="DD2:ER2"/>
     <mergeCell ref="ER4:ER5"/>
     <mergeCell ref="EP4:EP5"/>
     <mergeCell ref="EO4:EO5"/>
@@ -59209,7 +59571,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:ER57">
+  <conditionalFormatting sqref="EH6:ES57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -59249,7 +59611,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR61"/>
+  <dimension ref="A1:CS61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -59260,11 +59622,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="96" width="10.875" style="1" customWidth="1"/>
-    <col min="97" max="16384" width="8.625" style="1"/>
+    <col min="54" max="97" width="10.875" style="1" customWidth="1"/>
+    <col min="98" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:97" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -59335,601 +59697,608 @@
       <c r="CO1" s="19"/>
       <c r="CP1" s="19"/>
       <c r="CQ1" s="19"/>
-      <c r="CR1" s="19" t="s">
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:96" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="68" t="s">
+    <row r="2" spans="1:97" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="Z2" s="69"/>
-      <c r="AA2" s="69"/>
-      <c r="AB2" s="69"/>
-      <c r="AC2" s="69"/>
-      <c r="AD2" s="69"/>
-      <c r="AE2" s="69"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="69"/>
-      <c r="AH2" s="69"/>
-      <c r="AI2" s="69"/>
-      <c r="AJ2" s="69"/>
-      <c r="AK2" s="69"/>
-      <c r="AL2" s="69"/>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69"/>
-      <c r="AO2" s="69"/>
-      <c r="AP2" s="69"/>
-      <c r="AQ2" s="69"/>
-      <c r="AR2" s="69"/>
-      <c r="AS2" s="69"/>
-      <c r="AT2" s="69"/>
-      <c r="AU2" s="69"/>
-      <c r="AV2" s="69"/>
-      <c r="AW2" s="69"/>
-      <c r="AX2" s="69"/>
-      <c r="AY2" s="69"/>
-      <c r="AZ2" s="69"/>
-      <c r="BA2" s="69"/>
-      <c r="BB2" s="69"/>
-      <c r="BC2" s="84"/>
-      <c r="BD2" s="74" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="71"/>
+      <c r="BD2" s="85" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="74"/>
-      <c r="BF2" s="74"/>
-      <c r="BG2" s="74"/>
-      <c r="BH2" s="74"/>
-      <c r="BI2" s="74"/>
-      <c r="BJ2" s="74"/>
-      <c r="BK2" s="74"/>
-      <c r="BL2" s="74"/>
-      <c r="BM2" s="74"/>
-      <c r="BN2" s="74"/>
-      <c r="BO2" s="74"/>
-      <c r="BP2" s="74"/>
-      <c r="BQ2" s="74"/>
-      <c r="BR2" s="74"/>
-      <c r="BS2" s="74"/>
-      <c r="BT2" s="74"/>
-      <c r="BU2" s="74"/>
-      <c r="BV2" s="74"/>
-      <c r="BW2" s="74"/>
-      <c r="BX2" s="74"/>
-      <c r="BY2" s="74"/>
-      <c r="BZ2" s="74"/>
-      <c r="CA2" s="74"/>
-      <c r="CB2" s="74"/>
-      <c r="CC2" s="74"/>
-      <c r="CD2" s="74"/>
-      <c r="CE2" s="74"/>
-      <c r="CF2" s="74"/>
-      <c r="CG2" s="74"/>
-      <c r="CH2" s="74"/>
-      <c r="CI2" s="74"/>
-      <c r="CJ2" s="74"/>
-      <c r="CK2" s="74"/>
-      <c r="CL2" s="74"/>
-      <c r="CM2" s="74"/>
-      <c r="CN2" s="74"/>
-      <c r="CO2" s="74"/>
-      <c r="CP2" s="74"/>
-      <c r="CQ2" s="74"/>
-      <c r="CR2" s="74"/>
+      <c r="BE2" s="85"/>
+      <c r="BF2" s="85"/>
+      <c r="BG2" s="85"/>
+      <c r="BH2" s="85"/>
+      <c r="BI2" s="85"/>
+      <c r="BJ2" s="85"/>
+      <c r="BK2" s="85"/>
+      <c r="BL2" s="85"/>
+      <c r="BM2" s="85"/>
+      <c r="BN2" s="85"/>
+      <c r="BO2" s="85"/>
+      <c r="BP2" s="85"/>
+      <c r="BQ2" s="85"/>
+      <c r="BR2" s="85"/>
+      <c r="BS2" s="85"/>
+      <c r="BT2" s="85"/>
+      <c r="BU2" s="85"/>
+      <c r="BV2" s="85"/>
+      <c r="BW2" s="85"/>
+      <c r="BX2" s="85"/>
+      <c r="BY2" s="85"/>
+      <c r="BZ2" s="85"/>
+      <c r="CA2" s="85"/>
+      <c r="CB2" s="85"/>
+      <c r="CC2" s="85"/>
+      <c r="CD2" s="85"/>
+      <c r="CE2" s="85"/>
+      <c r="CF2" s="85"/>
+      <c r="CG2" s="85"/>
+      <c r="CH2" s="85"/>
+      <c r="CI2" s="85"/>
+      <c r="CJ2" s="85"/>
+      <c r="CK2" s="85"/>
+      <c r="CL2" s="85"/>
+      <c r="CM2" s="85"/>
+      <c r="CN2" s="85"/>
+      <c r="CO2" s="85"/>
+      <c r="CP2" s="85"/>
+      <c r="CQ2" s="85"/>
+      <c r="CR2" s="85"/>
+      <c r="CS2" s="85"/>
     </row>
-    <row r="3" spans="1:96" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="81" t="s">
+    <row r="3" spans="1:97" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="65" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
+      <c r="AO3" s="82"/>
+      <c r="AP3" s="82"/>
+      <c r="AQ3" s="82"/>
+      <c r="AR3" s="64" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="65"/>
-      <c r="AT3" s="65"/>
-      <c r="AU3" s="65"/>
-      <c r="AV3" s="65"/>
-      <c r="AW3" s="65"/>
-      <c r="AX3" s="65"/>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="65"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
-      <c r="BD3" s="66" t="s">
+      <c r="AS3" s="64"/>
+      <c r="AT3" s="64"/>
+      <c r="AU3" s="64"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="64"/>
+      <c r="AX3" s="64"/>
+      <c r="AY3" s="64"/>
+      <c r="AZ3" s="64"/>
+      <c r="BA3" s="64"/>
+      <c r="BB3" s="64"/>
+      <c r="BC3" s="64"/>
+      <c r="BD3" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="67"/>
-      <c r="BR3" s="67"/>
-      <c r="BS3" s="67"/>
-      <c r="BT3" s="67"/>
-      <c r="BU3" s="67"/>
-      <c r="BV3" s="67"/>
-      <c r="BW3" s="67"/>
-      <c r="BX3" s="67"/>
-      <c r="BY3" s="67"/>
-      <c r="BZ3" s="67"/>
-      <c r="CA3" s="67"/>
-      <c r="CB3" s="67"/>
-      <c r="CC3" s="67"/>
-      <c r="CD3" s="67"/>
-      <c r="CE3" s="67"/>
-      <c r="CF3" s="67"/>
-      <c r="CG3" s="67"/>
-      <c r="CH3" s="67"/>
-      <c r="CI3" s="67"/>
-      <c r="CJ3" s="67"/>
-      <c r="CK3" s="67"/>
-      <c r="CL3" s="67"/>
-      <c r="CM3" s="67"/>
-      <c r="CN3" s="67"/>
-      <c r="CO3" s="67"/>
-      <c r="CP3" s="67"/>
-      <c r="CQ3" s="71"/>
-      <c r="CR3" s="44" t="s">
+      <c r="BE3" s="87"/>
+      <c r="BF3" s="87"/>
+      <c r="BG3" s="87"/>
+      <c r="BH3" s="87"/>
+      <c r="BI3" s="87"/>
+      <c r="BJ3" s="87"/>
+      <c r="BK3" s="87"/>
+      <c r="BL3" s="87"/>
+      <c r="BM3" s="87"/>
+      <c r="BN3" s="87"/>
+      <c r="BO3" s="87"/>
+      <c r="BP3" s="87"/>
+      <c r="BQ3" s="87"/>
+      <c r="BR3" s="87"/>
+      <c r="BS3" s="87"/>
+      <c r="BT3" s="87"/>
+      <c r="BU3" s="87"/>
+      <c r="BV3" s="87"/>
+      <c r="BW3" s="87"/>
+      <c r="BX3" s="87"/>
+      <c r="BY3" s="87"/>
+      <c r="BZ3" s="87"/>
+      <c r="CA3" s="87"/>
+      <c r="CB3" s="87"/>
+      <c r="CC3" s="87"/>
+      <c r="CD3" s="87"/>
+      <c r="CE3" s="87"/>
+      <c r="CF3" s="87"/>
+      <c r="CG3" s="87"/>
+      <c r="CH3" s="87"/>
+      <c r="CI3" s="87"/>
+      <c r="CJ3" s="87"/>
+      <c r="CK3" s="87"/>
+      <c r="CL3" s="87"/>
+      <c r="CM3" s="87"/>
+      <c r="CN3" s="87"/>
+      <c r="CO3" s="87"/>
+      <c r="CP3" s="87"/>
+      <c r="CQ3" s="88"/>
+      <c r="CR3" s="64" t="s">
         <v>415</v>
       </c>
+      <c r="CS3" s="64"/>
     </row>
-    <row r="4" spans="1:96" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="46" t="s">
+    <row r="4" spans="1:97" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="J4" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="46" t="s">
+      <c r="L4" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="46" t="s">
+      <c r="M4" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="46" t="s">
+      <c r="N4" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="46" t="s">
+      <c r="O4" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="46" t="s">
+      <c r="P4" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="46" t="s">
+      <c r="Q4" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="46" t="s">
+      <c r="R4" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="46" t="s">
+      <c r="S4" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="46" t="s">
+      <c r="T4" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="46" t="s">
+      <c r="U4" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="46" t="s">
+      <c r="V4" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="46" t="s">
+      <c r="W4" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="46" t="s">
+      <c r="X4" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="46" t="s">
+      <c r="Y4" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="46" t="s">
+      <c r="Z4" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="46" t="s">
+      <c r="AA4" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="46" t="s">
+      <c r="AB4" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="46" t="s">
+      <c r="AC4" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="46" t="s">
+      <c r="AD4" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="48" t="s">
+      <c r="AE4" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="48" t="s">
+      <c r="AF4" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="48" t="s">
+      <c r="AG4" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="48" t="s">
+      <c r="AI4" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="48" t="s">
+      <c r="AJ4" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="48" t="s">
+      <c r="AL4" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="48" t="s">
+      <c r="AM4" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="48" t="s">
+      <c r="AO4" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="48" t="s">
+      <c r="AP4" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="48" t="s">
+      <c r="AR4" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="48" t="s">
+      <c r="AS4" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="48" t="s">
+      <c r="AT4" s="47" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="48" t="s">
+      <c r="AU4" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="48" t="s">
+      <c r="AV4" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="48" t="s">
+      <c r="AW4" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="48" t="s">
+      <c r="AX4" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="48" t="s">
+      <c r="AY4" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="48" t="s">
+      <c r="AZ4" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="48" t="s">
+      <c r="BA4" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="48" t="s">
+      <c r="BC4" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="70" t="s">
+      <c r="BD4" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="70" t="s">
+      <c r="BE4" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="70" t="s">
+      <c r="BF4" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="70" t="s">
+      <c r="BG4" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="70" t="s">
+      <c r="BH4" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="70" t="s">
+      <c r="BI4" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="70" t="s">
+      <c r="BJ4" s="69" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="70" t="s">
+      <c r="BK4" s="69" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="70" t="s">
+      <c r="BL4" s="69" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="70" t="s">
+      <c r="BM4" s="69" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="70" t="s">
+      <c r="BN4" s="69" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="70" t="s">
+      <c r="BO4" s="69" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="70" t="s">
+      <c r="BP4" s="69" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="70" t="s">
+      <c r="BQ4" s="69" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="70" t="s">
+      <c r="BR4" s="69" t="s">
         <v>343</v>
       </c>
-      <c r="BS4" s="70" t="s">
+      <c r="BS4" s="69" t="s">
         <v>347</v>
       </c>
-      <c r="BT4" s="70" t="s">
+      <c r="BT4" s="69" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="70" t="s">
+      <c r="BU4" s="69" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="70" t="s">
+      <c r="BV4" s="69" t="s">
         <v>355</v>
       </c>
-      <c r="BW4" s="70" t="s">
+      <c r="BW4" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="70" t="s">
+      <c r="BX4" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="70" t="s">
+      <c r="BY4" s="69" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="70" t="s">
+      <c r="BZ4" s="69" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="70" t="s">
+      <c r="CA4" s="69" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="70" t="s">
+      <c r="CB4" s="69" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="70" t="s">
+      <c r="CC4" s="69" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="70" t="s">
+      <c r="CD4" s="69" t="s">
         <v>382</v>
       </c>
-      <c r="CE4" s="70" t="s">
+      <c r="CE4" s="69" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="70" t="s">
+      <c r="CF4" s="69" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="70" t="s">
+      <c r="CG4" s="69" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="70" t="s">
+      <c r="CH4" s="69" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="70" t="s">
+      <c r="CI4" s="69" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="70" t="s">
+      <c r="CJ4" s="69" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="70" t="s">
+      <c r="CK4" s="69" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="70" t="s">
+      <c r="CL4" s="69" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="70" t="s">
+      <c r="CM4" s="69" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="70" t="s">
+      <c r="CN4" s="69" t="s">
         <v>404</v>
       </c>
-      <c r="CO4" s="70" t="s">
+      <c r="CO4" s="69" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="70" t="s">
+      <c r="CP4" s="69" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="70" t="s">
+      <c r="CQ4" s="69" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="70" t="s">
+      <c r="CR4" s="69" t="s">
         <v>412</v>
       </c>
+      <c r="CS4" s="69" t="s">
+        <v>416</v>
+      </c>
     </row>
-    <row r="5" spans="1:96" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="49"/>
-      <c r="AF5" s="49"/>
-      <c r="AG5" s="49"/>
-      <c r="AH5" s="49"/>
-      <c r="AI5" s="49"/>
-      <c r="AJ5" s="49"/>
-      <c r="AK5" s="49"/>
-      <c r="AL5" s="49"/>
-      <c r="AM5" s="49"/>
-      <c r="AN5" s="49"/>
-      <c r="AO5" s="49"/>
-      <c r="AP5" s="49"/>
-      <c r="AQ5" s="49"/>
-      <c r="AR5" s="49"/>
-      <c r="AS5" s="49"/>
-      <c r="AT5" s="49"/>
-      <c r="AU5" s="49"/>
-      <c r="AV5" s="49"/>
-      <c r="AW5" s="49"/>
-      <c r="AX5" s="49"/>
-      <c r="AY5" s="49"/>
-      <c r="AZ5" s="49"/>
-      <c r="BA5" s="49"/>
-      <c r="BB5" s="49"/>
-      <c r="BC5" s="49"/>
-      <c r="BD5" s="49"/>
-      <c r="BE5" s="49"/>
-      <c r="BF5" s="49"/>
-      <c r="BG5" s="49"/>
-      <c r="BH5" s="49"/>
-      <c r="BI5" s="49"/>
-      <c r="BJ5" s="49"/>
-      <c r="BK5" s="49"/>
-      <c r="BL5" s="49"/>
-      <c r="BM5" s="49"/>
-      <c r="BN5" s="49"/>
-      <c r="BO5" s="49"/>
-      <c r="BP5" s="49"/>
-      <c r="BQ5" s="49"/>
-      <c r="BR5" s="49"/>
-      <c r="BS5" s="49"/>
-      <c r="BT5" s="49"/>
-      <c r="BU5" s="49"/>
-      <c r="BV5" s="49"/>
-      <c r="BW5" s="49"/>
-      <c r="BX5" s="49"/>
-      <c r="BY5" s="49"/>
-      <c r="BZ5" s="70"/>
-      <c r="CA5" s="70"/>
-      <c r="CB5" s="70"/>
-      <c r="CC5" s="70"/>
-      <c r="CD5" s="70"/>
-      <c r="CE5" s="70"/>
-      <c r="CF5" s="70"/>
-      <c r="CG5" s="70"/>
-      <c r="CH5" s="70"/>
-      <c r="CI5" s="70"/>
-      <c r="CJ5" s="70"/>
-      <c r="CK5" s="70"/>
-      <c r="CL5" s="70"/>
-      <c r="CM5" s="70"/>
-      <c r="CN5" s="70"/>
-      <c r="CO5" s="70"/>
-      <c r="CP5" s="70"/>
-      <c r="CQ5" s="70"/>
-      <c r="CR5" s="70"/>
+    <row r="5" spans="1:97" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="63"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
+      <c r="AC5" s="46"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="48"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="48"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="48"/>
+      <c r="AU5" s="48"/>
+      <c r="AV5" s="48"/>
+      <c r="AW5" s="48"/>
+      <c r="AX5" s="48"/>
+      <c r="AY5" s="48"/>
+      <c r="AZ5" s="48"/>
+      <c r="BA5" s="48"/>
+      <c r="BB5" s="48"/>
+      <c r="BC5" s="48"/>
+      <c r="BD5" s="48"/>
+      <c r="BE5" s="48"/>
+      <c r="BF5" s="48"/>
+      <c r="BG5" s="48"/>
+      <c r="BH5" s="48"/>
+      <c r="BI5" s="48"/>
+      <c r="BJ5" s="48"/>
+      <c r="BK5" s="48"/>
+      <c r="BL5" s="48"/>
+      <c r="BM5" s="48"/>
+      <c r="BN5" s="48"/>
+      <c r="BO5" s="48"/>
+      <c r="BP5" s="48"/>
+      <c r="BQ5" s="48"/>
+      <c r="BR5" s="48"/>
+      <c r="BS5" s="48"/>
+      <c r="BT5" s="48"/>
+      <c r="BU5" s="48"/>
+      <c r="BV5" s="48"/>
+      <c r="BW5" s="48"/>
+      <c r="BX5" s="48"/>
+      <c r="BY5" s="48"/>
+      <c r="BZ5" s="69"/>
+      <c r="CA5" s="69"/>
+      <c r="CB5" s="69"/>
+      <c r="CC5" s="69"/>
+      <c r="CD5" s="69"/>
+      <c r="CE5" s="69"/>
+      <c r="CF5" s="69"/>
+      <c r="CG5" s="69"/>
+      <c r="CH5" s="69"/>
+      <c r="CI5" s="69"/>
+      <c r="CJ5" s="69"/>
+      <c r="CK5" s="69"/>
+      <c r="CL5" s="69"/>
+      <c r="CM5" s="69"/>
+      <c r="CN5" s="69"/>
+      <c r="CO5" s="69"/>
+      <c r="CP5" s="69"/>
+      <c r="CQ5" s="69"/>
+      <c r="CR5" s="69"/>
+      <c r="CS5" s="69"/>
     </row>
-    <row r="6" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -60216,8 +60585,11 @@
       <c r="CR6" s="28">
         <v>39</v>
       </c>
+      <c r="CS6" s="28">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -60503,8 +60875,11 @@
       <c r="CR7" s="15">
         <v>3</v>
       </c>
+      <c r="CS7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -60790,8 +61165,11 @@
       <c r="CR8" s="28">
         <v>2</v>
       </c>
+      <c r="CS8" s="28">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -61078,8 +61456,11 @@
       <c r="CR9" s="15">
         <v>32</v>
       </c>
+      <c r="CS9" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="10" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -61365,8 +61746,11 @@
       <c r="CR10" s="15">
         <v>2</v>
       </c>
+      <c r="CS10" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -61652,8 +62036,11 @@
       <c r="CR11" s="15">
         <v>9</v>
       </c>
+      <c r="CS11" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -61939,8 +62326,11 @@
       <c r="CR12" s="15">
         <v>3</v>
       </c>
+      <c r="CS12" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -62226,8 +62616,11 @@
       <c r="CR13" s="15">
         <v>35</v>
       </c>
+      <c r="CS13" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="14" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -62513,8 +62906,11 @@
       <c r="CR14" s="15">
         <v>15</v>
       </c>
+      <c r="CS14" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="15" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -62800,8 +63196,11 @@
       <c r="CR15" s="15">
         <v>5</v>
       </c>
+      <c r="CS15" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -63088,8 +63487,11 @@
       <c r="CR16" s="28">
         <v>26</v>
       </c>
+      <c r="CS16" s="28">
+        <v>27</v>
+      </c>
     </row>
-    <row r="17" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -63375,8 +63777,11 @@
       <c r="CR17" s="15">
         <v>81</v>
       </c>
+      <c r="CS17" s="15">
+        <v>70</v>
+      </c>
     </row>
-    <row r="18" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -63663,10 +64068,13 @@
       <c r="CR18" s="34">
         <v>871</v>
       </c>
+      <c r="CS18" s="34">
+        <v>777</v>
+      </c>
     </row>
-    <row r="19" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -63951,10 +64359,13 @@
       <c r="CR19" s="15">
         <v>68</v>
       </c>
+      <c r="CS19" s="15">
+        <v>90</v>
+      </c>
     </row>
-    <row r="20" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="89"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -64237,10 +64648,13 @@
       <c r="CR20" s="28">
         <v>251</v>
       </c>
+      <c r="CS20" s="28">
+        <v>242</v>
+      </c>
     </row>
-    <row r="21" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="86"/>
+      <c r="B21" s="90"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -64523,8 +64937,11 @@
       <c r="CR21" s="15">
         <v>8</v>
       </c>
+      <c r="CS21" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="22" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -64810,8 +65227,11 @@
       <c r="CR22" s="15">
         <v>5</v>
       </c>
+      <c r="CS22" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="23" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -65097,8 +65517,11 @@
       <c r="CR23" s="15">
         <v>0</v>
       </c>
+      <c r="CS23" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -65384,8 +65807,11 @@
       <c r="CR24" s="15">
         <v>4</v>
       </c>
+      <c r="CS24" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -65671,8 +66097,11 @@
       <c r="CR25" s="15">
         <v>2</v>
       </c>
+      <c r="CS25" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -65958,8 +66387,11 @@
       <c r="CR26" s="15">
         <v>11</v>
       </c>
+      <c r="CS26" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="27" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -66245,8 +66677,11 @@
       <c r="CR27" s="15">
         <v>0</v>
       </c>
+      <c r="CS27" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -66532,9 +66967,12 @@
       <c r="CR28" s="15">
         <v>0</v>
       </c>
+      <c r="CS28" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="87" t="s">
+    <row r="29" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="91" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -66819,9 +67257,12 @@
       <c r="CR29" s="15">
         <v>6</v>
       </c>
+      <c r="CS29" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="30" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="88"/>
+    <row r="30" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="92"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -67104,8 +67545,11 @@
       <c r="CR30" s="15">
         <v>40</v>
       </c>
+      <c r="CS30" s="15">
+        <v>40</v>
+      </c>
     </row>
-    <row r="31" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -67392,8 +67836,11 @@
       <c r="CR31" s="15">
         <v>182</v>
       </c>
+      <c r="CS31" s="15">
+        <v>133</v>
+      </c>
     </row>
-    <row r="32" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -67679,8 +68126,11 @@
       <c r="CR32" s="15">
         <v>6</v>
       </c>
+      <c r="CS32" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -67966,8 +68416,11 @@
       <c r="CR33" s="15">
         <v>0</v>
       </c>
+      <c r="CS33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -68254,10 +68707,13 @@
       <c r="CR34" s="15">
         <v>48</v>
       </c>
+      <c r="CS34" s="15">
+        <v>64</v>
+      </c>
     </row>
-    <row r="35" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="89" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -68542,9 +68998,12 @@
       <c r="CR35" s="15">
         <v>220</v>
       </c>
+      <c r="CS35" s="15">
+        <v>120</v>
+      </c>
     </row>
-    <row r="36" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="86"/>
+    <row r="36" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="90"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -68827,8 +69286,11 @@
       <c r="CR36" s="28">
         <v>68</v>
       </c>
+      <c r="CS36" s="28">
+        <v>78</v>
+      </c>
     </row>
-    <row r="37" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -69115,8 +69577,11 @@
       <c r="CR37" s="15">
         <v>36</v>
       </c>
+      <c r="CS37" s="15">
+        <v>55</v>
+      </c>
     </row>
-    <row r="38" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -69402,8 +69867,11 @@
       <c r="CR38" s="15">
         <v>20</v>
       </c>
+      <c r="CS38" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="39" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -69689,8 +70157,11 @@
       <c r="CR39" s="15">
         <v>15</v>
       </c>
+      <c r="CS39" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="40" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -69976,8 +70447,11 @@
       <c r="CR40" s="15">
         <v>0</v>
       </c>
+      <c r="CS40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -70263,8 +70737,11 @@
       <c r="CR41" s="15">
         <v>0</v>
       </c>
+      <c r="CS41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -70550,8 +71027,11 @@
       <c r="CR42" s="15">
         <v>37</v>
       </c>
+      <c r="CS42" s="15">
+        <v>50</v>
+      </c>
     </row>
-    <row r="43" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -70837,8 +71317,11 @@
       <c r="CR43" s="28">
         <v>73</v>
       </c>
+      <c r="CS43" s="28">
+        <v>70</v>
+      </c>
     </row>
-    <row r="44" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -71124,8 +71607,11 @@
       <c r="CR44" s="15">
         <v>4</v>
       </c>
+      <c r="CS44" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -71411,8 +71897,11 @@
       <c r="CR45" s="15">
         <v>17</v>
       </c>
+      <c r="CS45" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="46" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -71698,8 +72187,11 @@
       <c r="CR46" s="15">
         <v>27</v>
       </c>
+      <c r="CS46" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="47" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -71985,8 +72477,11 @@
       <c r="CR47" s="15">
         <v>2</v>
       </c>
+      <c r="CS47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -72272,10 +72767,13 @@
       <c r="CR48" s="15">
         <v>28</v>
       </c>
+      <c r="CS48" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="49" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="85" t="s">
+      <c r="B49" s="89" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -72560,9 +73058,12 @@
       <c r="CR49" s="15">
         <v>82</v>
       </c>
+      <c r="CS49" s="15">
+        <v>59</v>
+      </c>
     </row>
-    <row r="50" spans="1:96" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="86"/>
+    <row r="50" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="90"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -72845,8 +73346,11 @@
       <c r="CR50" s="15">
         <v>80</v>
       </c>
+      <c r="CS50" s="15">
+        <v>78</v>
+      </c>
     </row>
-    <row r="51" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -73132,8 +73636,11 @@
       <c r="CR51" s="15">
         <v>0</v>
       </c>
+      <c r="CS51" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -73419,8 +73926,11 @@
       <c r="CR52" s="15">
         <v>28</v>
       </c>
+      <c r="CS52" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="53" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -73706,8 +74216,11 @@
       <c r="CR53" s="15">
         <v>75</v>
       </c>
+      <c r="CS53" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="54" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -73993,8 +74506,11 @@
       <c r="CR54" s="15">
         <v>28</v>
       </c>
+      <c r="CS54" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="55" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -74280,8 +74796,11 @@
       <c r="CR55" s="15">
         <v>17</v>
       </c>
+      <c r="CS55" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="56" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -74567,8 +75086,11 @@
       <c r="CR56" s="15">
         <v>0</v>
       </c>
+      <c r="CS56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -74854,8 +75376,11 @@
       <c r="CR57" s="15">
         <v>1</v>
       </c>
+      <c r="CS57" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -75125,7 +75650,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CR58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CS58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -75232,8 +75757,12 @@
         <f t="shared" si="8"/>
         <v>2612</v>
       </c>
+      <c r="CS58" s="14">
+        <f t="shared" si="8"/>
+        <v>2340</v>
+      </c>
     </row>
-    <row r="59" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -75266,7 +75795,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -75299,7 +75828,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:96" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -75333,7 +75862,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="107">
+    <mergeCell ref="BD2:CS2"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="BL4:BL5"/>
@@ -75341,7 +75873,6 @@
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="BD2:CR2"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="CP4:CP5"/>
@@ -75366,6 +75897,7 @@
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="CC4:CC5"/>
     <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="AS4:AS5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="AV4:AV5"/>
@@ -75390,7 +75922,6 @@
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="P4:P5"/>
@@ -75441,7 +75972,7 @@
     <mergeCell ref="X4:X5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CR57">
+  <conditionalFormatting sqref="CH6:CS57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -75450,7 +75981,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="96" max="66" man="1"/>
+    <brk id="97" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -75467,7 +75998,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CR57</xm:sqref>
+          <xm:sqref>BP6:CS57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -75480,7 +76011,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CW61"/>
+  <dimension ref="A1:CX61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -75489,11 +76020,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="101" width="10.875" style="1" customWidth="1"/>
-    <col min="102" max="16384" width="8.625" style="1"/>
+    <col min="34" max="102" width="10.875" style="1" customWidth="1"/>
+    <col min="103" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:102" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -75564,621 +76095,628 @@
       <c r="CO1" s="19"/>
       <c r="CP1" s="19"/>
       <c r="CQ1" s="19"/>
-      <c r="CR1" s="19" t="s">
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:101" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="68" t="s">
+    <row r="2" spans="1:102" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
-      <c r="Z2" s="69"/>
-      <c r="AA2" s="69"/>
-      <c r="AB2" s="69"/>
-      <c r="AC2" s="69"/>
-      <c r="AD2" s="69"/>
-      <c r="AE2" s="69"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="69"/>
-      <c r="AH2" s="69"/>
-      <c r="AI2" s="69"/>
-      <c r="AJ2" s="69"/>
-      <c r="AK2" s="69"/>
-      <c r="AL2" s="69"/>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69"/>
-      <c r="AO2" s="69"/>
-      <c r="AP2" s="69"/>
-      <c r="AQ2" s="69"/>
-      <c r="AR2" s="69"/>
-      <c r="AS2" s="69"/>
-      <c r="AT2" s="69"/>
-      <c r="AU2" s="69"/>
-      <c r="AV2" s="69"/>
-      <c r="AW2" s="69"/>
-      <c r="AX2" s="69"/>
-      <c r="AY2" s="69"/>
-      <c r="AZ2" s="69"/>
-      <c r="BA2" s="69"/>
-      <c r="BB2" s="69"/>
-      <c r="BC2" s="84"/>
-      <c r="BD2" s="74" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="71"/>
+      <c r="BD2" s="85" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="74"/>
-      <c r="BF2" s="74"/>
-      <c r="BG2" s="74"/>
-      <c r="BH2" s="74"/>
-      <c r="BI2" s="74"/>
-      <c r="BJ2" s="74"/>
-      <c r="BK2" s="74"/>
-      <c r="BL2" s="74"/>
-      <c r="BM2" s="74"/>
-      <c r="BN2" s="74"/>
-      <c r="BO2" s="74"/>
-      <c r="BP2" s="74"/>
-      <c r="BQ2" s="74"/>
-      <c r="BR2" s="74"/>
-      <c r="BS2" s="74"/>
-      <c r="BT2" s="74"/>
-      <c r="BU2" s="74"/>
-      <c r="BV2" s="74"/>
-      <c r="BW2" s="74"/>
-      <c r="BX2" s="74"/>
-      <c r="BY2" s="74"/>
-      <c r="BZ2" s="74"/>
-      <c r="CA2" s="74"/>
-      <c r="CB2" s="74"/>
-      <c r="CC2" s="74"/>
-      <c r="CD2" s="74"/>
-      <c r="CE2" s="74"/>
-      <c r="CF2" s="74"/>
-      <c r="CG2" s="74"/>
-      <c r="CH2" s="74"/>
-      <c r="CI2" s="74"/>
-      <c r="CJ2" s="74"/>
-      <c r="CK2" s="74"/>
-      <c r="CL2" s="74"/>
-      <c r="CM2" s="74"/>
-      <c r="CN2" s="74"/>
-      <c r="CO2" s="74"/>
-      <c r="CP2" s="74"/>
-      <c r="CQ2" s="74"/>
-      <c r="CR2" s="74"/>
-      <c r="CS2" s="20"/>
+      <c r="BE2" s="85"/>
+      <c r="BF2" s="85"/>
+      <c r="BG2" s="85"/>
+      <c r="BH2" s="85"/>
+      <c r="BI2" s="85"/>
+      <c r="BJ2" s="85"/>
+      <c r="BK2" s="85"/>
+      <c r="BL2" s="85"/>
+      <c r="BM2" s="85"/>
+      <c r="BN2" s="85"/>
+      <c r="BO2" s="85"/>
+      <c r="BP2" s="85"/>
+      <c r="BQ2" s="85"/>
+      <c r="BR2" s="85"/>
+      <c r="BS2" s="85"/>
+      <c r="BT2" s="85"/>
+      <c r="BU2" s="85"/>
+      <c r="BV2" s="85"/>
+      <c r="BW2" s="85"/>
+      <c r="BX2" s="85"/>
+      <c r="BY2" s="85"/>
+      <c r="BZ2" s="85"/>
+      <c r="CA2" s="85"/>
+      <c r="CB2" s="85"/>
+      <c r="CC2" s="85"/>
+      <c r="CD2" s="85"/>
+      <c r="CE2" s="85"/>
+      <c r="CF2" s="85"/>
+      <c r="CG2" s="85"/>
+      <c r="CH2" s="85"/>
+      <c r="CI2" s="85"/>
+      <c r="CJ2" s="85"/>
+      <c r="CK2" s="85"/>
+      <c r="CL2" s="85"/>
+      <c r="CM2" s="85"/>
+      <c r="CN2" s="85"/>
+      <c r="CO2" s="85"/>
+      <c r="CP2" s="85"/>
+      <c r="CQ2" s="85"/>
+      <c r="CR2" s="85"/>
+      <c r="CS2" s="85"/>
       <c r="CT2" s="20"/>
       <c r="CU2" s="20"/>
       <c r="CV2" s="20"/>
       <c r="CW2" s="20"/>
+      <c r="CX2" s="20"/>
     </row>
-    <row r="3" spans="1:101" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="81" t="s">
+    <row r="3" spans="1:102" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="65" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
+      <c r="AO3" s="82"/>
+      <c r="AP3" s="82"/>
+      <c r="AQ3" s="82"/>
+      <c r="AR3" s="64" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="65"/>
-      <c r="AT3" s="65"/>
-      <c r="AU3" s="65"/>
-      <c r="AV3" s="65"/>
-      <c r="AW3" s="65"/>
-      <c r="AX3" s="65"/>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="65"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
-      <c r="BD3" s="66" t="s">
+      <c r="AS3" s="64"/>
+      <c r="AT3" s="64"/>
+      <c r="AU3" s="64"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="64"/>
+      <c r="AX3" s="64"/>
+      <c r="AY3" s="64"/>
+      <c r="AZ3" s="64"/>
+      <c r="BA3" s="64"/>
+      <c r="BB3" s="64"/>
+      <c r="BC3" s="64"/>
+      <c r="BD3" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="67"/>
-      <c r="BR3" s="67"/>
-      <c r="BS3" s="67"/>
-      <c r="BT3" s="67"/>
-      <c r="BU3" s="67"/>
-      <c r="BV3" s="67"/>
-      <c r="BW3" s="67"/>
-      <c r="BX3" s="67"/>
-      <c r="BY3" s="67"/>
-      <c r="BZ3" s="67"/>
-      <c r="CA3" s="67"/>
-      <c r="CB3" s="67"/>
-      <c r="CC3" s="67"/>
-      <c r="CD3" s="67"/>
-      <c r="CE3" s="67"/>
-      <c r="CF3" s="67"/>
-      <c r="CG3" s="67"/>
-      <c r="CH3" s="67"/>
-      <c r="CI3" s="67"/>
-      <c r="CJ3" s="67"/>
-      <c r="CK3" s="67"/>
-      <c r="CL3" s="67"/>
-      <c r="CM3" s="67"/>
-      <c r="CN3" s="67"/>
-      <c r="CO3" s="67"/>
-      <c r="CP3" s="67"/>
-      <c r="CQ3" s="71"/>
-      <c r="CR3" s="44" t="s">
+      <c r="BE3" s="87"/>
+      <c r="BF3" s="87"/>
+      <c r="BG3" s="87"/>
+      <c r="BH3" s="87"/>
+      <c r="BI3" s="87"/>
+      <c r="BJ3" s="87"/>
+      <c r="BK3" s="87"/>
+      <c r="BL3" s="87"/>
+      <c r="BM3" s="87"/>
+      <c r="BN3" s="87"/>
+      <c r="BO3" s="87"/>
+      <c r="BP3" s="87"/>
+      <c r="BQ3" s="87"/>
+      <c r="BR3" s="87"/>
+      <c r="BS3" s="87"/>
+      <c r="BT3" s="87"/>
+      <c r="BU3" s="87"/>
+      <c r="BV3" s="87"/>
+      <c r="BW3" s="87"/>
+      <c r="BX3" s="87"/>
+      <c r="BY3" s="87"/>
+      <c r="BZ3" s="87"/>
+      <c r="CA3" s="87"/>
+      <c r="CB3" s="87"/>
+      <c r="CC3" s="87"/>
+      <c r="CD3" s="87"/>
+      <c r="CE3" s="87"/>
+      <c r="CF3" s="87"/>
+      <c r="CG3" s="87"/>
+      <c r="CH3" s="87"/>
+      <c r="CI3" s="87"/>
+      <c r="CJ3" s="87"/>
+      <c r="CK3" s="87"/>
+      <c r="CL3" s="87"/>
+      <c r="CM3" s="87"/>
+      <c r="CN3" s="87"/>
+      <c r="CO3" s="87"/>
+      <c r="CP3" s="87"/>
+      <c r="CQ3" s="88"/>
+      <c r="CR3" s="65" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="21"/>
+      <c r="CS3" s="70"/>
       <c r="CT3" s="21"/>
       <c r="CU3" s="21"/>
       <c r="CV3" s="21"/>
       <c r="CW3" s="21"/>
+      <c r="CX3" s="21"/>
     </row>
-    <row r="4" spans="1:101" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="46" t="s">
+    <row r="4" spans="1:102" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="J4" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="46" t="s">
+      <c r="L4" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="46" t="s">
+      <c r="M4" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="46" t="s">
+      <c r="N4" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="46" t="s">
+      <c r="O4" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="46" t="s">
+      <c r="P4" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="46" t="s">
+      <c r="Q4" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="46" t="s">
+      <c r="R4" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="46" t="s">
+      <c r="S4" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="46" t="s">
+      <c r="T4" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="46" t="s">
+      <c r="U4" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="46" t="s">
+      <c r="V4" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="46" t="s">
+      <c r="W4" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="46" t="s">
+      <c r="X4" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="46" t="s">
+      <c r="Y4" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="46" t="s">
+      <c r="Z4" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="46" t="s">
+      <c r="AA4" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="46" t="s">
+      <c r="AB4" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="46" t="s">
+      <c r="AC4" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="46" t="s">
+      <c r="AD4" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="48" t="s">
+      <c r="AE4" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="48" t="s">
+      <c r="AF4" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="48" t="s">
+      <c r="AG4" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="48" t="s">
+      <c r="AI4" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="48" t="s">
+      <c r="AJ4" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="48" t="s">
+      <c r="AL4" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="48" t="s">
+      <c r="AM4" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="48" t="s">
+      <c r="AO4" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="48" t="s">
+      <c r="AP4" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="48" t="s">
+      <c r="AR4" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="48" t="s">
+      <c r="AS4" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="48" t="s">
+      <c r="AT4" s="47" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="48" t="s">
+      <c r="AU4" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="48" t="s">
+      <c r="AV4" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="48" t="s">
+      <c r="AW4" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="48" t="s">
+      <c r="AX4" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="48" t="s">
+      <c r="AY4" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="48" t="s">
+      <c r="AZ4" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="48" t="s">
+      <c r="BA4" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="48" t="s">
+      <c r="BC4" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="70" t="s">
+      <c r="BD4" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="70" t="s">
+      <c r="BE4" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="70" t="s">
+      <c r="BF4" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="70" t="s">
+      <c r="BG4" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="70" t="s">
+      <c r="BH4" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="70" t="s">
+      <c r="BI4" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="70" t="s">
+      <c r="BJ4" s="69" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="70" t="s">
+      <c r="BK4" s="69" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="70" t="s">
+      <c r="BL4" s="69" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="70" t="s">
+      <c r="BM4" s="69" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="70" t="s">
+      <c r="BN4" s="69" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="70" t="s">
+      <c r="BO4" s="69" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="70" t="s">
+      <c r="BP4" s="69" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="70" t="s">
+      <c r="BQ4" s="69" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="70" t="s">
+      <c r="BR4" s="69" t="s">
         <v>344</v>
       </c>
-      <c r="BS4" s="70" t="s">
+      <c r="BS4" s="69" t="s">
         <v>348</v>
       </c>
-      <c r="BT4" s="70" t="s">
+      <c r="BT4" s="69" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="70" t="s">
+      <c r="BU4" s="69" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="70" t="s">
+      <c r="BV4" s="69" t="s">
         <v>356</v>
       </c>
-      <c r="BW4" s="70" t="s">
+      <c r="BW4" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="70" t="s">
+      <c r="BX4" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="70" t="s">
+      <c r="BY4" s="69" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="70" t="s">
+      <c r="BZ4" s="69" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="70" t="s">
+      <c r="CA4" s="69" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="70" t="s">
+      <c r="CB4" s="69" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="70" t="s">
+      <c r="CC4" s="69" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="70" t="s">
+      <c r="CD4" s="69" t="s">
         <v>381</v>
       </c>
-      <c r="CE4" s="70" t="s">
+      <c r="CE4" s="69" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="70" t="s">
+      <c r="CF4" s="69" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="70" t="s">
+      <c r="CG4" s="69" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="70" t="s">
+      <c r="CH4" s="69" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="70" t="s">
+      <c r="CI4" s="69" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="70" t="s">
+      <c r="CJ4" s="69" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="70" t="s">
+      <c r="CK4" s="69" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="70" t="s">
+      <c r="CL4" s="69" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="70" t="s">
+      <c r="CM4" s="69" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="70" t="s">
+      <c r="CN4" s="69" t="s">
         <v>405</v>
       </c>
-      <c r="CO4" s="70" t="s">
+      <c r="CO4" s="69" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="70" t="s">
+      <c r="CP4" s="69" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="70" t="s">
+      <c r="CQ4" s="69" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="70" t="s">
+      <c r="CR4" s="69" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="90"/>
-      <c r="CT4" s="90"/>
-      <c r="CU4" s="90"/>
-      <c r="CV4" s="90"/>
-      <c r="CW4" s="90"/>
+      <c r="CS4" s="69" t="s">
+        <v>416</v>
+      </c>
+      <c r="CT4" s="94"/>
+      <c r="CU4" s="94"/>
+      <c r="CV4" s="94"/>
+      <c r="CW4" s="94"/>
+      <c r="CX4" s="94"/>
     </row>
-    <row r="5" spans="1:101" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="49"/>
-      <c r="AF5" s="49"/>
-      <c r="AG5" s="49"/>
-      <c r="AH5" s="49"/>
-      <c r="AI5" s="49"/>
-      <c r="AJ5" s="49"/>
-      <c r="AK5" s="49"/>
-      <c r="AL5" s="49"/>
-      <c r="AM5" s="49"/>
-      <c r="AN5" s="49"/>
-      <c r="AO5" s="49"/>
-      <c r="AP5" s="49"/>
-      <c r="AQ5" s="49"/>
-      <c r="AR5" s="49"/>
-      <c r="AS5" s="49"/>
-      <c r="AT5" s="49"/>
-      <c r="AU5" s="49"/>
-      <c r="AV5" s="49"/>
-      <c r="AW5" s="49"/>
-      <c r="AX5" s="49"/>
-      <c r="AY5" s="49"/>
-      <c r="AZ5" s="49"/>
-      <c r="BA5" s="49"/>
-      <c r="BB5" s="49"/>
-      <c r="BC5" s="49"/>
-      <c r="BD5" s="49"/>
-      <c r="BE5" s="49"/>
-      <c r="BF5" s="49"/>
-      <c r="BG5" s="49"/>
-      <c r="BH5" s="49"/>
-      <c r="BI5" s="49"/>
-      <c r="BJ5" s="49"/>
-      <c r="BK5" s="49"/>
-      <c r="BL5" s="49"/>
-      <c r="BM5" s="49"/>
-      <c r="BN5" s="49"/>
-      <c r="BO5" s="49"/>
-      <c r="BP5" s="49"/>
-      <c r="BQ5" s="70"/>
-      <c r="BR5" s="70"/>
-      <c r="BS5" s="70"/>
-      <c r="BT5" s="70"/>
-      <c r="BU5" s="70"/>
-      <c r="BV5" s="70"/>
-      <c r="BW5" s="70"/>
-      <c r="BX5" s="70"/>
-      <c r="BY5" s="70"/>
-      <c r="BZ5" s="70"/>
-      <c r="CA5" s="70"/>
-      <c r="CB5" s="70"/>
-      <c r="CC5" s="70"/>
-      <c r="CD5" s="70"/>
-      <c r="CE5" s="70"/>
-      <c r="CF5" s="70"/>
-      <c r="CG5" s="70"/>
-      <c r="CH5" s="70"/>
-      <c r="CI5" s="70"/>
-      <c r="CJ5" s="70"/>
-      <c r="CK5" s="70"/>
-      <c r="CL5" s="70"/>
-      <c r="CM5" s="70"/>
-      <c r="CN5" s="70"/>
-      <c r="CO5" s="70"/>
-      <c r="CP5" s="70"/>
-      <c r="CQ5" s="70"/>
-      <c r="CR5" s="70"/>
-      <c r="CS5" s="90"/>
-      <c r="CT5" s="90"/>
-      <c r="CU5" s="90"/>
-      <c r="CV5" s="90"/>
-      <c r="CW5" s="90"/>
+    <row r="5" spans="1:102" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="63"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
+      <c r="AC5" s="46"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="48"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="48"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="48"/>
+      <c r="AU5" s="48"/>
+      <c r="AV5" s="48"/>
+      <c r="AW5" s="48"/>
+      <c r="AX5" s="48"/>
+      <c r="AY5" s="48"/>
+      <c r="AZ5" s="48"/>
+      <c r="BA5" s="48"/>
+      <c r="BB5" s="48"/>
+      <c r="BC5" s="48"/>
+      <c r="BD5" s="48"/>
+      <c r="BE5" s="48"/>
+      <c r="BF5" s="48"/>
+      <c r="BG5" s="48"/>
+      <c r="BH5" s="48"/>
+      <c r="BI5" s="48"/>
+      <c r="BJ5" s="48"/>
+      <c r="BK5" s="48"/>
+      <c r="BL5" s="48"/>
+      <c r="BM5" s="48"/>
+      <c r="BN5" s="48"/>
+      <c r="BO5" s="48"/>
+      <c r="BP5" s="48"/>
+      <c r="BQ5" s="69"/>
+      <c r="BR5" s="69"/>
+      <c r="BS5" s="69"/>
+      <c r="BT5" s="69"/>
+      <c r="BU5" s="69"/>
+      <c r="BV5" s="69"/>
+      <c r="BW5" s="69"/>
+      <c r="BX5" s="69"/>
+      <c r="BY5" s="69"/>
+      <c r="BZ5" s="69"/>
+      <c r="CA5" s="69"/>
+      <c r="CB5" s="69"/>
+      <c r="CC5" s="69"/>
+      <c r="CD5" s="69"/>
+      <c r="CE5" s="69"/>
+      <c r="CF5" s="69"/>
+      <c r="CG5" s="69"/>
+      <c r="CH5" s="69"/>
+      <c r="CI5" s="69"/>
+      <c r="CJ5" s="69"/>
+      <c r="CK5" s="69"/>
+      <c r="CL5" s="69"/>
+      <c r="CM5" s="69"/>
+      <c r="CN5" s="69"/>
+      <c r="CO5" s="69"/>
+      <c r="CP5" s="69"/>
+      <c r="CQ5" s="69"/>
+      <c r="CR5" s="69"/>
+      <c r="CS5" s="69"/>
+      <c r="CT5" s="94"/>
+      <c r="CU5" s="94"/>
+      <c r="CV5" s="94"/>
+      <c r="CW5" s="94"/>
+      <c r="CX5" s="94"/>
     </row>
-    <row r="6" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -76465,13 +77003,16 @@
       <c r="CR6" s="28">
         <v>105</v>
       </c>
-      <c r="CS6" s="22"/>
+      <c r="CS6" s="28">
+        <v>153</v>
+      </c>
       <c r="CT6" s="22"/>
       <c r="CU6" s="22"/>
       <c r="CV6" s="22"/>
       <c r="CW6" s="22"/>
+      <c r="CX6" s="22"/>
     </row>
-    <row r="7" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -76757,13 +77298,16 @@
       <c r="CR7" s="15">
         <v>3</v>
       </c>
-      <c r="CS7" s="23"/>
+      <c r="CS7" s="15">
+        <v>2</v>
+      </c>
       <c r="CT7" s="23"/>
       <c r="CU7" s="23"/>
       <c r="CV7" s="23"/>
       <c r="CW7" s="23"/>
+      <c r="CX7" s="23"/>
     </row>
-    <row r="8" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -77049,13 +77593,16 @@
       <c r="CR8" s="28">
         <v>40</v>
       </c>
-      <c r="CS8" s="23"/>
+      <c r="CS8" s="28">
+        <v>50</v>
+      </c>
       <c r="CT8" s="23"/>
       <c r="CU8" s="23"/>
       <c r="CV8" s="23"/>
       <c r="CW8" s="23"/>
+      <c r="CX8" s="23"/>
     </row>
-    <row r="9" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -77342,13 +77889,16 @@
       <c r="CR9" s="15">
         <v>92</v>
       </c>
-      <c r="CS9" s="23"/>
+      <c r="CS9" s="15">
+        <v>104</v>
+      </c>
       <c r="CT9" s="23"/>
       <c r="CU9" s="23"/>
       <c r="CV9" s="23"/>
       <c r="CW9" s="23"/>
+      <c r="CX9" s="23"/>
     </row>
-    <row r="10" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -77634,13 +78184,16 @@
       <c r="CR10" s="15">
         <v>0</v>
       </c>
-      <c r="CS10" s="23"/>
+      <c r="CS10" s="15">
+        <v>0</v>
+      </c>
       <c r="CT10" s="23"/>
       <c r="CU10" s="23"/>
       <c r="CV10" s="23"/>
       <c r="CW10" s="23"/>
+      <c r="CX10" s="23"/>
     </row>
-    <row r="11" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -77926,13 +78479,16 @@
       <c r="CR11" s="15">
         <v>6</v>
       </c>
-      <c r="CS11" s="23"/>
+      <c r="CS11" s="15">
+        <v>10</v>
+      </c>
       <c r="CT11" s="23"/>
       <c r="CU11" s="23"/>
       <c r="CV11" s="23"/>
       <c r="CW11" s="23"/>
+      <c r="CX11" s="23"/>
     </row>
-    <row r="12" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -78218,13 +78774,16 @@
       <c r="CR12" s="15">
         <v>7</v>
       </c>
-      <c r="CS12" s="23"/>
+      <c r="CS12" s="15">
+        <v>7</v>
+      </c>
       <c r="CT12" s="23"/>
       <c r="CU12" s="23"/>
       <c r="CV12" s="23"/>
       <c r="CW12" s="23"/>
+      <c r="CX12" s="23"/>
     </row>
-    <row r="13" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -78510,13 +79069,16 @@
       <c r="CR13" s="15">
         <v>32</v>
       </c>
-      <c r="CS13" s="22"/>
+      <c r="CS13" s="15">
+        <v>20</v>
+      </c>
       <c r="CT13" s="22"/>
       <c r="CU13" s="22"/>
       <c r="CV13" s="22"/>
       <c r="CW13" s="22"/>
+      <c r="CX13" s="22"/>
     </row>
-    <row r="14" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -78802,13 +79364,16 @@
       <c r="CR14" s="15">
         <v>25</v>
       </c>
-      <c r="CS14" s="23"/>
+      <c r="CS14" s="15">
+        <v>28</v>
+      </c>
       <c r="CT14" s="23"/>
       <c r="CU14" s="23"/>
       <c r="CV14" s="23"/>
       <c r="CW14" s="23"/>
+      <c r="CX14" s="23"/>
     </row>
-    <row r="15" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -79094,13 +79659,16 @@
       <c r="CR15" s="15">
         <v>9</v>
       </c>
-      <c r="CS15" s="23"/>
+      <c r="CS15" s="15">
+        <v>9</v>
+      </c>
       <c r="CT15" s="23"/>
       <c r="CU15" s="23"/>
       <c r="CV15" s="23"/>
       <c r="CW15" s="23"/>
+      <c r="CX15" s="23"/>
     </row>
-    <row r="16" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -79387,13 +79955,16 @@
       <c r="CR16" s="28">
         <v>191</v>
       </c>
-      <c r="CS16" s="22"/>
+      <c r="CS16" s="28">
+        <v>229</v>
+      </c>
       <c r="CT16" s="22"/>
       <c r="CU16" s="22"/>
       <c r="CV16" s="22"/>
       <c r="CW16" s="22"/>
+      <c r="CX16" s="22"/>
     </row>
-    <row r="17" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -79679,13 +80250,16 @@
       <c r="CR17" s="15">
         <v>142</v>
       </c>
-      <c r="CS17" s="22"/>
+      <c r="CS17" s="15">
+        <v>175</v>
+      </c>
       <c r="CT17" s="22"/>
       <c r="CU17" s="22"/>
       <c r="CV17" s="22"/>
       <c r="CW17" s="22"/>
+      <c r="CX17" s="22"/>
     </row>
-    <row r="18" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -79972,15 +80546,18 @@
       <c r="CR18" s="34">
         <v>2377</v>
       </c>
-      <c r="CS18" s="22"/>
+      <c r="CS18" s="34">
+        <v>2626</v>
+      </c>
       <c r="CT18" s="22"/>
       <c r="CU18" s="22"/>
       <c r="CV18" s="22"/>
       <c r="CW18" s="22"/>
+      <c r="CX18" s="22"/>
     </row>
-    <row r="19" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -80265,15 +80842,18 @@
       <c r="CR19" s="15">
         <v>44</v>
       </c>
-      <c r="CS19" s="22"/>
+      <c r="CS19" s="15">
+        <v>80</v>
+      </c>
       <c r="CT19" s="22"/>
       <c r="CU19" s="22"/>
       <c r="CV19" s="22"/>
       <c r="CW19" s="22"/>
+      <c r="CX19" s="22"/>
     </row>
-    <row r="20" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="89"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -80556,15 +81136,18 @@
       <c r="CR20" s="28">
         <v>259</v>
       </c>
-      <c r="CS20" s="22"/>
+      <c r="CS20" s="28">
+        <v>299</v>
+      </c>
       <c r="CT20" s="22"/>
       <c r="CU20" s="22"/>
       <c r="CV20" s="22"/>
       <c r="CW20" s="22"/>
+      <c r="CX20" s="22"/>
     </row>
-    <row r="21" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="86"/>
+      <c r="B21" s="90"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -80847,13 +81430,16 @@
       <c r="CR21" s="15">
         <v>32</v>
       </c>
-      <c r="CS21" s="22"/>
+      <c r="CS21" s="15">
+        <v>35</v>
+      </c>
       <c r="CT21" s="22"/>
       <c r="CU21" s="22"/>
       <c r="CV21" s="22"/>
       <c r="CW21" s="22"/>
+      <c r="CX21" s="22"/>
     </row>
-    <row r="22" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -81139,13 +81725,16 @@
       <c r="CR22" s="15">
         <v>6</v>
       </c>
-      <c r="CS22" s="23"/>
+      <c r="CS22" s="15">
+        <v>5</v>
+      </c>
       <c r="CT22" s="23"/>
       <c r="CU22" s="23"/>
       <c r="CV22" s="23"/>
       <c r="CW22" s="23"/>
+      <c r="CX22" s="23"/>
     </row>
-    <row r="23" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -81431,13 +82020,16 @@
       <c r="CR23" s="15">
         <v>5</v>
       </c>
-      <c r="CS23" s="23"/>
+      <c r="CS23" s="15">
+        <v>6</v>
+      </c>
       <c r="CT23" s="23"/>
       <c r="CU23" s="23"/>
       <c r="CV23" s="23"/>
       <c r="CW23" s="23"/>
+      <c r="CX23" s="23"/>
     </row>
-    <row r="24" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -81723,13 +82315,16 @@
       <c r="CR24" s="15">
         <v>14</v>
       </c>
-      <c r="CS24" s="22"/>
+      <c r="CS24" s="15">
+        <v>24</v>
+      </c>
       <c r="CT24" s="22"/>
       <c r="CU24" s="22"/>
       <c r="CV24" s="22"/>
       <c r="CW24" s="22"/>
+      <c r="CX24" s="22"/>
     </row>
-    <row r="25" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -82015,13 +82610,16 @@
       <c r="CR25" s="15">
         <v>1</v>
       </c>
-      <c r="CS25" s="23"/>
+      <c r="CS25" s="15">
+        <v>5</v>
+      </c>
       <c r="CT25" s="23"/>
       <c r="CU25" s="23"/>
       <c r="CV25" s="23"/>
       <c r="CW25" s="23"/>
+      <c r="CX25" s="23"/>
     </row>
-    <row r="26" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -82307,13 +82905,16 @@
       <c r="CR26" s="15">
         <v>10</v>
       </c>
-      <c r="CS26" s="23"/>
+      <c r="CS26" s="15">
+        <v>15</v>
+      </c>
       <c r="CT26" s="23"/>
       <c r="CU26" s="23"/>
       <c r="CV26" s="23"/>
       <c r="CW26" s="23"/>
+      <c r="CX26" s="23"/>
     </row>
-    <row r="27" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -82599,13 +83200,16 @@
       <c r="CR27" s="15">
         <v>0</v>
       </c>
-      <c r="CS27" s="23"/>
+      <c r="CS27" s="15">
+        <v>0</v>
+      </c>
       <c r="CT27" s="23"/>
       <c r="CU27" s="23"/>
       <c r="CV27" s="23"/>
       <c r="CW27" s="23"/>
+      <c r="CX27" s="23"/>
     </row>
-    <row r="28" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -82891,14 +83495,17 @@
       <c r="CR28" s="15">
         <v>0</v>
       </c>
-      <c r="CS28" s="22"/>
+      <c r="CS28" s="15">
+        <v>10</v>
+      </c>
       <c r="CT28" s="22"/>
       <c r="CU28" s="22"/>
       <c r="CV28" s="22"/>
       <c r="CW28" s="22"/>
+      <c r="CX28" s="22"/>
     </row>
-    <row r="29" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="87" t="s">
+    <row r="29" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="91" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -83183,14 +83790,17 @@
       <c r="CR29" s="15">
         <v>5</v>
       </c>
-      <c r="CS29" s="23"/>
+      <c r="CS29" s="15">
+        <v>5</v>
+      </c>
       <c r="CT29" s="23"/>
       <c r="CU29" s="23"/>
       <c r="CV29" s="23"/>
       <c r="CW29" s="23"/>
+      <c r="CX29" s="23"/>
     </row>
-    <row r="30" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="88"/>
+    <row r="30" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="92"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -83473,13 +84083,16 @@
       <c r="CR30" s="15">
         <v>39</v>
       </c>
-      <c r="CS30" s="23"/>
+      <c r="CS30" s="15">
+        <v>48</v>
+      </c>
       <c r="CT30" s="23"/>
       <c r="CU30" s="23"/>
       <c r="CV30" s="23"/>
       <c r="CW30" s="23"/>
+      <c r="CX30" s="23"/>
     </row>
-    <row r="31" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -83766,13 +84379,16 @@
       <c r="CR31" s="15">
         <v>112</v>
       </c>
-      <c r="CS31" s="22"/>
+      <c r="CS31" s="15">
+        <v>183</v>
+      </c>
       <c r="CT31" s="22"/>
       <c r="CU31" s="22"/>
       <c r="CV31" s="22"/>
       <c r="CW31" s="22"/>
+      <c r="CX31" s="22"/>
     </row>
-    <row r="32" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -84058,13 +84674,16 @@
       <c r="CR32" s="15">
         <v>3</v>
       </c>
-      <c r="CS32" s="23"/>
+      <c r="CS32" s="15">
+        <v>13</v>
+      </c>
       <c r="CT32" s="23"/>
       <c r="CU32" s="23"/>
       <c r="CV32" s="23"/>
       <c r="CW32" s="23"/>
+      <c r="CX32" s="23"/>
     </row>
-    <row r="33" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -84350,13 +84969,16 @@
       <c r="CR33" s="15">
         <v>0</v>
       </c>
-      <c r="CS33" s="23"/>
+      <c r="CS33" s="15">
+        <v>1</v>
+      </c>
       <c r="CT33" s="23"/>
       <c r="CU33" s="23"/>
       <c r="CV33" s="23"/>
       <c r="CW33" s="23"/>
+      <c r="CX33" s="23"/>
     </row>
-    <row r="34" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -84643,15 +85265,18 @@
       <c r="CR34" s="15">
         <v>129</v>
       </c>
-      <c r="CS34" s="22"/>
+      <c r="CS34" s="15">
+        <v>176</v>
+      </c>
       <c r="CT34" s="22"/>
       <c r="CU34" s="22"/>
       <c r="CV34" s="22"/>
       <c r="CW34" s="22"/>
+      <c r="CX34" s="22"/>
     </row>
-    <row r="35" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="89" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -84936,14 +85561,17 @@
       <c r="CR35" s="15">
         <v>411</v>
       </c>
-      <c r="CS35" s="22"/>
+      <c r="CS35" s="15">
+        <v>556</v>
+      </c>
       <c r="CT35" s="22"/>
       <c r="CU35" s="22"/>
       <c r="CV35" s="22"/>
       <c r="CW35" s="22"/>
+      <c r="CX35" s="22"/>
     </row>
-    <row r="36" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="86"/>
+    <row r="36" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="90"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -85226,13 +85854,16 @@
       <c r="CR36" s="28">
         <v>62</v>
       </c>
-      <c r="CS36" s="22"/>
+      <c r="CS36" s="28">
+        <v>70</v>
+      </c>
       <c r="CT36" s="22"/>
       <c r="CU36" s="22"/>
       <c r="CV36" s="22"/>
       <c r="CW36" s="22"/>
+      <c r="CX36" s="22"/>
     </row>
-    <row r="37" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -85519,13 +86150,16 @@
       <c r="CR37" s="15">
         <v>90</v>
       </c>
-      <c r="CS37" s="22"/>
+      <c r="CS37" s="15">
+        <v>153</v>
+      </c>
       <c r="CT37" s="22"/>
       <c r="CU37" s="22"/>
       <c r="CV37" s="22"/>
       <c r="CW37" s="22"/>
+      <c r="CX37" s="22"/>
     </row>
-    <row r="38" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -85811,13 +86445,16 @@
       <c r="CR38" s="15">
         <v>26</v>
       </c>
-      <c r="CS38" s="23"/>
+      <c r="CS38" s="15">
+        <v>28</v>
+      </c>
       <c r="CT38" s="23"/>
       <c r="CU38" s="23"/>
       <c r="CV38" s="23"/>
       <c r="CW38" s="23"/>
+      <c r="CX38" s="23"/>
     </row>
-    <row r="39" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -86103,13 +86740,16 @@
       <c r="CR39" s="15">
         <v>16</v>
       </c>
-      <c r="CS39" s="23"/>
+      <c r="CS39" s="15">
+        <v>20</v>
+      </c>
       <c r="CT39" s="23"/>
       <c r="CU39" s="23"/>
       <c r="CV39" s="23"/>
       <c r="CW39" s="23"/>
+      <c r="CX39" s="23"/>
     </row>
-    <row r="40" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -86395,13 +87035,16 @@
       <c r="CR40" s="15">
         <v>0</v>
       </c>
-      <c r="CS40" s="23"/>
+      <c r="CS40" s="15">
+        <v>1</v>
+      </c>
       <c r="CT40" s="23"/>
       <c r="CU40" s="23"/>
       <c r="CV40" s="23"/>
       <c r="CW40" s="23"/>
+      <c r="CX40" s="23"/>
     </row>
-    <row r="41" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -86687,13 +87330,16 @@
       <c r="CR41" s="15">
         <v>1</v>
       </c>
-      <c r="CS41" s="23"/>
+      <c r="CS41" s="15">
+        <v>0</v>
+      </c>
       <c r="CT41" s="23"/>
       <c r="CU41" s="23"/>
       <c r="CV41" s="23"/>
       <c r="CW41" s="23"/>
+      <c r="CX41" s="23"/>
     </row>
-    <row r="42" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -86979,13 +87625,16 @@
       <c r="CR42" s="15">
         <v>21</v>
       </c>
-      <c r="CS42" s="23"/>
+      <c r="CS42" s="15">
+        <v>27</v>
+      </c>
       <c r="CT42" s="23"/>
       <c r="CU42" s="23"/>
       <c r="CV42" s="23"/>
       <c r="CW42" s="23"/>
+      <c r="CX42" s="23"/>
     </row>
-    <row r="43" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -87271,13 +87920,16 @@
       <c r="CR43" s="28">
         <v>56</v>
       </c>
-      <c r="CS43" s="23"/>
+      <c r="CS43" s="28">
+        <v>63</v>
+      </c>
       <c r="CT43" s="23"/>
       <c r="CU43" s="23"/>
       <c r="CV43" s="23"/>
       <c r="CW43" s="23"/>
+      <c r="CX43" s="23"/>
     </row>
-    <row r="44" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -87563,13 +88215,16 @@
       <c r="CR44" s="15">
         <v>4</v>
       </c>
-      <c r="CS44" s="23"/>
+      <c r="CS44" s="15">
+        <v>5</v>
+      </c>
       <c r="CT44" s="23"/>
       <c r="CU44" s="23"/>
       <c r="CV44" s="23"/>
       <c r="CW44" s="23"/>
+      <c r="CX44" s="23"/>
     </row>
-    <row r="45" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -87855,13 +88510,16 @@
       <c r="CR45" s="15">
         <v>37</v>
       </c>
-      <c r="CS45" s="22"/>
+      <c r="CS45" s="15">
+        <v>25</v>
+      </c>
       <c r="CT45" s="22"/>
       <c r="CU45" s="22"/>
       <c r="CV45" s="22"/>
       <c r="CW45" s="22"/>
+      <c r="CX45" s="22"/>
     </row>
-    <row r="46" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -88147,13 +88805,16 @@
       <c r="CR46" s="15">
         <v>45</v>
       </c>
-      <c r="CS46" s="23"/>
+      <c r="CS46" s="15">
+        <v>40</v>
+      </c>
       <c r="CT46" s="23"/>
       <c r="CU46" s="23"/>
       <c r="CV46" s="23"/>
       <c r="CW46" s="23"/>
+      <c r="CX46" s="23"/>
     </row>
-    <row r="47" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -88439,13 +89100,16 @@
       <c r="CR47" s="15">
         <v>5</v>
       </c>
-      <c r="CS47" s="23"/>
+      <c r="CS47" s="15">
+        <v>1</v>
+      </c>
       <c r="CT47" s="23"/>
       <c r="CU47" s="23"/>
       <c r="CV47" s="23"/>
       <c r="CW47" s="23"/>
+      <c r="CX47" s="23"/>
     </row>
-    <row r="48" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -88731,15 +89395,18 @@
       <c r="CR48" s="15">
         <v>32</v>
       </c>
-      <c r="CS48" s="23"/>
+      <c r="CS48" s="15">
+        <v>26</v>
+      </c>
       <c r="CT48" s="23"/>
       <c r="CU48" s="23"/>
       <c r="CV48" s="23"/>
       <c r="CW48" s="23"/>
+      <c r="CX48" s="23"/>
     </row>
-    <row r="49" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="85" t="s">
+      <c r="B49" s="89" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -89024,14 +89691,17 @@
       <c r="CR49" s="15">
         <v>196</v>
       </c>
-      <c r="CS49" s="22"/>
+      <c r="CS49" s="15">
+        <v>212</v>
+      </c>
       <c r="CT49" s="22"/>
       <c r="CU49" s="22"/>
       <c r="CV49" s="22"/>
       <c r="CW49" s="22"/>
+      <c r="CX49" s="22"/>
     </row>
-    <row r="50" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="86"/>
+    <row r="50" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="90"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -89314,13 +89984,16 @@
       <c r="CR50" s="15">
         <v>79</v>
       </c>
-      <c r="CS50" s="22"/>
+      <c r="CS50" s="15">
+        <v>82</v>
+      </c>
       <c r="CT50" s="22"/>
       <c r="CU50" s="22"/>
       <c r="CV50" s="22"/>
       <c r="CW50" s="22"/>
+      <c r="CX50" s="22"/>
     </row>
-    <row r="51" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -89606,13 +90279,16 @@
       <c r="CR51" s="15">
         <v>34</v>
       </c>
-      <c r="CS51" s="23"/>
+      <c r="CS51" s="15">
+        <v>33</v>
+      </c>
       <c r="CT51" s="23"/>
       <c r="CU51" s="23"/>
       <c r="CV51" s="23"/>
       <c r="CW51" s="23"/>
+      <c r="CX51" s="23"/>
     </row>
-    <row r="52" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -89898,13 +90574,16 @@
       <c r="CR52" s="15">
         <v>34</v>
       </c>
-      <c r="CS52" s="23"/>
+      <c r="CS52" s="15">
+        <v>42</v>
+      </c>
       <c r="CT52" s="23"/>
       <c r="CU52" s="23"/>
       <c r="CV52" s="23"/>
       <c r="CW52" s="23"/>
+      <c r="CX52" s="23"/>
     </row>
-    <row r="53" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -90190,13 +90869,16 @@
       <c r="CR53" s="15">
         <v>67</v>
       </c>
-      <c r="CS53" s="23"/>
+      <c r="CS53" s="15">
+        <v>57</v>
+      </c>
       <c r="CT53" s="23"/>
       <c r="CU53" s="23"/>
       <c r="CV53" s="23"/>
       <c r="CW53" s="23"/>
+      <c r="CX53" s="23"/>
     </row>
-    <row r="54" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -90482,13 +91164,16 @@
       <c r="CR54" s="15">
         <v>16</v>
       </c>
-      <c r="CS54" s="23"/>
+      <c r="CS54" s="15">
+        <v>12</v>
+      </c>
       <c r="CT54" s="23"/>
       <c r="CU54" s="23"/>
       <c r="CV54" s="23"/>
       <c r="CW54" s="23"/>
+      <c r="CX54" s="23"/>
     </row>
-    <row r="55" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -90774,13 +91459,16 @@
       <c r="CR55" s="15">
         <v>21</v>
       </c>
-      <c r="CS55" s="23"/>
+      <c r="CS55" s="15">
+        <v>26</v>
+      </c>
       <c r="CT55" s="23"/>
       <c r="CU55" s="23"/>
       <c r="CV55" s="23"/>
       <c r="CW55" s="23"/>
+      <c r="CX55" s="23"/>
     </row>
-    <row r="56" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -91066,13 +91754,16 @@
       <c r="CR56" s="15">
         <v>4</v>
       </c>
-      <c r="CS56" s="23"/>
+      <c r="CS56" s="15">
+        <v>21</v>
+      </c>
       <c r="CT56" s="23"/>
       <c r="CU56" s="23"/>
       <c r="CV56" s="23"/>
       <c r="CW56" s="23"/>
+      <c r="CX56" s="23"/>
     </row>
-    <row r="57" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -91358,13 +92049,16 @@
       <c r="CR57" s="15">
         <v>1</v>
       </c>
-      <c r="CS57" s="23"/>
+      <c r="CS57" s="15">
+        <v>3</v>
+      </c>
       <c r="CT57" s="23"/>
       <c r="CU57" s="23"/>
       <c r="CV57" s="23"/>
       <c r="CW57" s="23"/>
+      <c r="CX57" s="23"/>
     </row>
-    <row r="58" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -91634,7 +92328,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CR58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CS58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -91741,13 +92435,17 @@
         <f t="shared" si="4"/>
         <v>4946</v>
       </c>
-      <c r="CS58" s="24"/>
+      <c r="CS58" s="14">
+        <f t="shared" si="4"/>
+        <v>5821</v>
+      </c>
       <c r="CT58" s="24"/>
       <c r="CU58" s="24"/>
       <c r="CV58" s="24"/>
       <c r="CW58" s="24"/>
+      <c r="CX58" s="24"/>
     </row>
-    <row r="59" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -91780,7 +92478,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -91813,7 +92511,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -91847,8 +92545,23 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="BD2:CR2"/>
+  <mergeCells count="112">
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="CH4:CH5"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BD2:CS2"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="BK4:BK5"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CL4:CL5"/>
     <mergeCell ref="CK4:CK5"/>
@@ -91860,21 +92573,6 @@
     <mergeCell ref="BU4:BU5"/>
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="BK4:BK5"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="CC4:CC5"/>
     <mergeCell ref="AJ4:AJ5"/>
@@ -91916,6 +92614,8 @@
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="T4:T5"/>
@@ -91934,21 +92634,21 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="CF4:CF5"/>
@@ -91981,7 +92681,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CR57</xm:sqref>
+          <xm:sqref>BP6:CS57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050117-1\ＪＯＢ050117-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050124-2\ＪＯＢ050124-2\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11085"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CS$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CT$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CT$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$ES$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$ET$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$ET$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="420">
   <si>
     <t>都道府県</t>
   </si>
@@ -4526,6 +4526,18 @@
 【1月第3週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1/16(月)～
+1/22(日)分
+【1月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1/17(月)～
+1/23(日)分
+【1月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4889,7 +4901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5022,8 +5034,38 @@
     <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -5031,17 +5073,38 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5061,74 +5124,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5136,8 +5136,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5145,17 +5145,11 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5171,6 +5165,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -9341,7 +9338,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:ET61"/>
+  <dimension ref="A1:EU61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9355,11 +9352,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="149" width="10.875" style="1" customWidth="1"/>
-    <col min="150" max="16384" width="8.625" style="1"/>
+    <col min="106" max="150" width="10.875" style="1" customWidth="1"/>
+    <col min="151" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:150" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:151" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9435,925 +9432,932 @@
       <c r="EP1" s="19"/>
       <c r="EQ1" s="19"/>
       <c r="ER1" s="19"/>
-      <c r="ES1" s="19" t="s">
+      <c r="ES1" s="19"/>
+      <c r="ET1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:150" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="67" t="s">
+    <row r="2" spans="1:151" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="68"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-      <c r="AM2" s="68"/>
-      <c r="AN2" s="68"/>
-      <c r="AO2" s="68"/>
-      <c r="AP2" s="68"/>
-      <c r="AQ2" s="68"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="68"/>
-      <c r="AV2" s="68"/>
-      <c r="AW2" s="68"/>
-      <c r="AX2" s="68"/>
-      <c r="AY2" s="68"/>
-      <c r="AZ2" s="68"/>
-      <c r="BA2" s="68"/>
-      <c r="BB2" s="68"/>
-      <c r="BC2" s="68"/>
-      <c r="BD2" s="68" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="52"/>
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="52"/>
+      <c r="BD2" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="68"/>
-      <c r="BF2" s="68"/>
-      <c r="BG2" s="68"/>
-      <c r="BH2" s="68"/>
-      <c r="BI2" s="68"/>
-      <c r="BJ2" s="68"/>
-      <c r="BK2" s="68"/>
-      <c r="BL2" s="68"/>
-      <c r="BM2" s="68"/>
-      <c r="BN2" s="68"/>
-      <c r="BO2" s="68"/>
-      <c r="BP2" s="68"/>
-      <c r="BQ2" s="68"/>
-      <c r="BR2" s="68"/>
-      <c r="BS2" s="68"/>
-      <c r="BT2" s="68"/>
-      <c r="BU2" s="68"/>
-      <c r="BV2" s="68"/>
-      <c r="BW2" s="68"/>
-      <c r="BX2" s="68"/>
-      <c r="BY2" s="68"/>
-      <c r="BZ2" s="68"/>
-      <c r="CA2" s="68"/>
-      <c r="CB2" s="68"/>
-      <c r="CC2" s="68"/>
-      <c r="CD2" s="68"/>
-      <c r="CE2" s="68"/>
-      <c r="CF2" s="68"/>
-      <c r="CG2" s="68"/>
-      <c r="CH2" s="68"/>
-      <c r="CI2" s="68"/>
-      <c r="CJ2" s="68"/>
-      <c r="CK2" s="68"/>
-      <c r="CL2" s="68"/>
-      <c r="CM2" s="68"/>
-      <c r="CN2" s="68"/>
-      <c r="CO2" s="68"/>
-      <c r="CP2" s="68"/>
-      <c r="CQ2" s="68"/>
-      <c r="CR2" s="68"/>
-      <c r="CS2" s="68"/>
-      <c r="CT2" s="68"/>
-      <c r="CU2" s="68"/>
-      <c r="CV2" s="68"/>
-      <c r="CW2" s="68"/>
-      <c r="CX2" s="68"/>
-      <c r="CY2" s="68"/>
-      <c r="CZ2" s="68"/>
-      <c r="DA2" s="68"/>
-      <c r="DB2" s="68"/>
-      <c r="DC2" s="68"/>
-      <c r="DD2" s="68"/>
-      <c r="DE2" s="67" t="s">
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="52"/>
+      <c r="BO2" s="52"/>
+      <c r="BP2" s="52"/>
+      <c r="BQ2" s="52"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="52"/>
+      <c r="CC2" s="52"/>
+      <c r="CD2" s="52"/>
+      <c r="CE2" s="52"/>
+      <c r="CF2" s="52"/>
+      <c r="CG2" s="52"/>
+      <c r="CH2" s="52"/>
+      <c r="CI2" s="52"/>
+      <c r="CJ2" s="52"/>
+      <c r="CK2" s="52"/>
+      <c r="CL2" s="52"/>
+      <c r="CM2" s="52"/>
+      <c r="CN2" s="52"/>
+      <c r="CO2" s="52"/>
+      <c r="CP2" s="52"/>
+      <c r="CQ2" s="52"/>
+      <c r="CR2" s="52"/>
+      <c r="CS2" s="52"/>
+      <c r="CT2" s="52"/>
+      <c r="CU2" s="52"/>
+      <c r="CV2" s="52"/>
+      <c r="CW2" s="52"/>
+      <c r="CX2" s="52"/>
+      <c r="CY2" s="52"/>
+      <c r="CZ2" s="52"/>
+      <c r="DA2" s="52"/>
+      <c r="DB2" s="52"/>
+      <c r="DC2" s="52"/>
+      <c r="DD2" s="52"/>
+      <c r="DE2" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="68"/>
-      <c r="DG2" s="68"/>
-      <c r="DH2" s="68"/>
-      <c r="DI2" s="68"/>
-      <c r="DJ2" s="68"/>
-      <c r="DK2" s="68"/>
-      <c r="DL2" s="68"/>
-      <c r="DM2" s="68"/>
-      <c r="DN2" s="68"/>
-      <c r="DO2" s="68"/>
-      <c r="DP2" s="68"/>
-      <c r="DQ2" s="68"/>
-      <c r="DR2" s="68"/>
-      <c r="DS2" s="68"/>
-      <c r="DT2" s="68"/>
-      <c r="DU2" s="68"/>
-      <c r="DV2" s="68"/>
-      <c r="DW2" s="68"/>
-      <c r="DX2" s="68"/>
-      <c r="DY2" s="68"/>
-      <c r="DZ2" s="68"/>
-      <c r="EA2" s="68"/>
-      <c r="EB2" s="68"/>
-      <c r="EC2" s="68"/>
-      <c r="ED2" s="68"/>
-      <c r="EE2" s="68"/>
-      <c r="EF2" s="68"/>
-      <c r="EG2" s="68"/>
-      <c r="EH2" s="68"/>
-      <c r="EI2" s="68"/>
-      <c r="EJ2" s="68"/>
-      <c r="EK2" s="68"/>
-      <c r="EL2" s="68"/>
-      <c r="EM2" s="68"/>
-      <c r="EN2" s="68"/>
-      <c r="EO2" s="68"/>
-      <c r="EP2" s="68"/>
-      <c r="EQ2" s="68"/>
-      <c r="ER2" s="68"/>
-      <c r="ES2" s="71"/>
+      <c r="DF2" s="44"/>
+      <c r="DG2" s="44"/>
+      <c r="DH2" s="44"/>
+      <c r="DI2" s="44"/>
+      <c r="DJ2" s="44"/>
+      <c r="DK2" s="44"/>
+      <c r="DL2" s="44"/>
+      <c r="DM2" s="44"/>
+      <c r="DN2" s="44"/>
+      <c r="DO2" s="44"/>
+      <c r="DP2" s="44"/>
+      <c r="DQ2" s="44"/>
+      <c r="DR2" s="44"/>
+      <c r="DS2" s="44"/>
+      <c r="DT2" s="44"/>
+      <c r="DU2" s="44"/>
+      <c r="DV2" s="44"/>
+      <c r="DW2" s="44"/>
+      <c r="DX2" s="44"/>
+      <c r="DY2" s="44"/>
+      <c r="DZ2" s="44"/>
+      <c r="EA2" s="44"/>
+      <c r="EB2" s="44"/>
+      <c r="EC2" s="44"/>
+      <c r="ED2" s="44"/>
+      <c r="EE2" s="44"/>
+      <c r="EF2" s="44"/>
+      <c r="EG2" s="44"/>
+      <c r="EH2" s="44"/>
+      <c r="EI2" s="44"/>
+      <c r="EJ2" s="44"/>
+      <c r="EK2" s="44"/>
+      <c r="EL2" s="44"/>
+      <c r="EM2" s="44"/>
+      <c r="EN2" s="44"/>
+      <c r="EO2" s="44"/>
+      <c r="EP2" s="44"/>
+      <c r="EQ2" s="44"/>
+      <c r="ER2" s="44"/>
+      <c r="ES2" s="44"/>
+      <c r="ET2" s="44"/>
     </row>
-    <row r="3" spans="1:150" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="64" t="s">
+    <row r="3" spans="1:151" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64"/>
-      <c r="Z3" s="64"/>
-      <c r="AA3" s="64"/>
-      <c r="AB3" s="64"/>
-      <c r="AC3" s="64"/>
-      <c r="AD3" s="64"/>
-      <c r="AE3" s="64"/>
-      <c r="AF3" s="64"/>
-      <c r="AG3" s="64"/>
-      <c r="AH3" s="64"/>
-      <c r="AI3" s="64"/>
-      <c r="AJ3" s="64"/>
-      <c r="AK3" s="64"/>
-      <c r="AL3" s="64"/>
-      <c r="AM3" s="64"/>
-      <c r="AN3" s="64"/>
-      <c r="AO3" s="64"/>
-      <c r="AP3" s="64"/>
-      <c r="AQ3" s="64"/>
-      <c r="AR3" s="65" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
+      <c r="AR3" s="48" t="s">
         <v>216</v>
       </c>
-      <c r="AS3" s="66"/>
-      <c r="AT3" s="66"/>
-      <c r="AU3" s="66"/>
-      <c r="AV3" s="66"/>
-      <c r="AW3" s="66"/>
-      <c r="AX3" s="66"/>
-      <c r="AY3" s="66"/>
-      <c r="AZ3" s="66"/>
-      <c r="BA3" s="66"/>
-      <c r="BB3" s="66"/>
-      <c r="BC3" s="66"/>
-      <c r="BD3" s="66" t="s">
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="53"/>
+      <c r="AY3" s="53"/>
+      <c r="AZ3" s="53"/>
+      <c r="BA3" s="53"/>
+      <c r="BB3" s="53"/>
+      <c r="BC3" s="53"/>
+      <c r="BD3" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="BE3" s="66"/>
-      <c r="BF3" s="66"/>
-      <c r="BG3" s="66"/>
-      <c r="BH3" s="66"/>
-      <c r="BI3" s="66"/>
-      <c r="BJ3" s="66"/>
-      <c r="BK3" s="66"/>
-      <c r="BL3" s="66"/>
-      <c r="BM3" s="66"/>
-      <c r="BN3" s="66"/>
-      <c r="BO3" s="66"/>
-      <c r="BP3" s="66"/>
-      <c r="BQ3" s="66"/>
-      <c r="BR3" s="66"/>
-      <c r="BS3" s="66"/>
-      <c r="BT3" s="66"/>
-      <c r="BU3" s="66"/>
-      <c r="BV3" s="66"/>
-      <c r="BW3" s="66"/>
-      <c r="BX3" s="66"/>
-      <c r="BY3" s="66"/>
-      <c r="BZ3" s="66"/>
-      <c r="CA3" s="66"/>
-      <c r="CB3" s="66"/>
-      <c r="CC3" s="66"/>
-      <c r="CD3" s="66"/>
-      <c r="CE3" s="66"/>
-      <c r="CF3" s="66"/>
-      <c r="CG3" s="66"/>
-      <c r="CH3" s="66"/>
-      <c r="CI3" s="66"/>
-      <c r="CJ3" s="66"/>
-      <c r="CK3" s="66"/>
-      <c r="CL3" s="66"/>
-      <c r="CM3" s="66"/>
-      <c r="CN3" s="66"/>
-      <c r="CO3" s="66"/>
-      <c r="CP3" s="66"/>
-      <c r="CQ3" s="70"/>
-      <c r="CR3" s="64" t="s">
+      <c r="BE3" s="53"/>
+      <c r="BF3" s="53"/>
+      <c r="BG3" s="53"/>
+      <c r="BH3" s="53"/>
+      <c r="BI3" s="53"/>
+      <c r="BJ3" s="53"/>
+      <c r="BK3" s="53"/>
+      <c r="BL3" s="53"/>
+      <c r="BM3" s="53"/>
+      <c r="BN3" s="53"/>
+      <c r="BO3" s="53"/>
+      <c r="BP3" s="53"/>
+      <c r="BQ3" s="53"/>
+      <c r="BR3" s="53"/>
+      <c r="BS3" s="53"/>
+      <c r="BT3" s="53"/>
+      <c r="BU3" s="53"/>
+      <c r="BV3" s="53"/>
+      <c r="BW3" s="53"/>
+      <c r="BX3" s="53"/>
+      <c r="BY3" s="53"/>
+      <c r="BZ3" s="53"/>
+      <c r="CA3" s="53"/>
+      <c r="CB3" s="53"/>
+      <c r="CC3" s="53"/>
+      <c r="CD3" s="53"/>
+      <c r="CE3" s="53"/>
+      <c r="CF3" s="53"/>
+      <c r="CG3" s="53"/>
+      <c r="CH3" s="53"/>
+      <c r="CI3" s="53"/>
+      <c r="CJ3" s="53"/>
+      <c r="CK3" s="53"/>
+      <c r="CL3" s="53"/>
+      <c r="CM3" s="53"/>
+      <c r="CN3" s="53"/>
+      <c r="CO3" s="53"/>
+      <c r="CP3" s="53"/>
+      <c r="CQ3" s="54"/>
+      <c r="CR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="64"/>
-      <c r="CT3" s="64"/>
-      <c r="CU3" s="64"/>
-      <c r="CV3" s="64"/>
-      <c r="CW3" s="64"/>
-      <c r="CX3" s="64"/>
-      <c r="CY3" s="64"/>
-      <c r="CZ3" s="64"/>
-      <c r="DA3" s="64"/>
-      <c r="DB3" s="64"/>
-      <c r="DC3" s="64"/>
-      <c r="DD3" s="65"/>
-      <c r="DE3" s="65" t="s">
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="48"/>
+      <c r="DE3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="66"/>
-      <c r="DG3" s="66"/>
-      <c r="DH3" s="66"/>
-      <c r="DI3" s="66"/>
-      <c r="DJ3" s="66"/>
-      <c r="DK3" s="66"/>
-      <c r="DL3" s="66"/>
-      <c r="DM3" s="66"/>
-      <c r="DN3" s="66"/>
-      <c r="DO3" s="66"/>
-      <c r="DP3" s="66"/>
-      <c r="DQ3" s="66"/>
-      <c r="DR3" s="66"/>
-      <c r="DS3" s="66"/>
-      <c r="DT3" s="66"/>
-      <c r="DU3" s="66"/>
-      <c r="DV3" s="66"/>
-      <c r="DW3" s="66"/>
-      <c r="DX3" s="66"/>
-      <c r="DY3" s="66"/>
-      <c r="DZ3" s="66"/>
-      <c r="EA3" s="66"/>
-      <c r="EB3" s="66"/>
-      <c r="EC3" s="66"/>
-      <c r="ED3" s="66"/>
-      <c r="EE3" s="66"/>
-      <c r="EF3" s="66"/>
-      <c r="EG3" s="66"/>
-      <c r="EH3" s="66"/>
-      <c r="EI3" s="66"/>
-      <c r="EJ3" s="66"/>
-      <c r="EK3" s="66"/>
-      <c r="EL3" s="66"/>
-      <c r="EM3" s="66"/>
-      <c r="EN3" s="66"/>
-      <c r="EO3" s="66"/>
-      <c r="EP3" s="66"/>
-      <c r="EQ3" s="70"/>
-      <c r="ER3" s="72" t="s">
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="73"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
     </row>
-    <row r="4" spans="1:150" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="44" t="s">
+    <row r="4" spans="1:151" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="65" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="44" t="s">
+      <c r="J4" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="44" t="s">
+      <c r="K4" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="L4" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="44" t="s">
+      <c r="M4" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="N4" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="O4" s="44" t="s">
+      <c r="O4" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="44" t="s">
+      <c r="P4" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="Q4" s="44" t="s">
+      <c r="Q4" s="65" t="s">
         <v>147</v>
       </c>
-      <c r="R4" s="57" t="s">
+      <c r="R4" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="44" t="s">
+      <c r="T4" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="U4" s="57" t="s">
+      <c r="U4" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="57" t="s">
+      <c r="V4" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="W4" s="57" t="s">
+      <c r="W4" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="X4" s="57" t="s">
+      <c r="X4" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="Y4" s="57" t="s">
+      <c r="Y4" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="57" t="s">
+      <c r="Z4" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="AA4" s="44" t="s">
+      <c r="AA4" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="44" t="s">
+      <c r="AB4" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="44" t="s">
+      <c r="AC4" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="AD4" s="44" t="s">
+      <c r="AD4" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="AE4" s="44" t="s">
+      <c r="AE4" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="AF4" s="44" t="s">
+      <c r="AF4" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="AG4" s="44" t="s">
+      <c r="AG4" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="AH4" s="44" t="s">
+      <c r="AH4" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="AI4" s="44" t="s">
+      <c r="AI4" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="AJ4" s="44" t="s">
+      <c r="AJ4" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="AK4" s="44" t="s">
+      <c r="AK4" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="AL4" s="44" t="s">
+      <c r="AL4" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="AM4" s="44" t="s">
+      <c r="AM4" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="AN4" s="44" t="s">
+      <c r="AN4" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="AO4" s="44" t="s">
+      <c r="AO4" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="AP4" s="44" t="s">
+      <c r="AP4" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="AQ4" s="44" t="s">
+      <c r="AQ4" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" s="46" t="s">
+      <c r="AR4" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="AS4" s="46" t="s">
+      <c r="AS4" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="46" t="s">
+      <c r="AT4" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="46" t="s">
+      <c r="AU4" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="46" t="s">
+      <c r="AV4" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="46" t="s">
+      <c r="AW4" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="AX4" s="46" t="s">
+      <c r="AX4" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="AY4" s="46" t="s">
+      <c r="AY4" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="AZ4" s="46" t="s">
+      <c r="AZ4" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="BA4" s="46" t="s">
+      <c r="BA4" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="BB4" s="46" t="s">
+      <c r="BB4" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="BC4" s="46" t="s">
+      <c r="BC4" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="BD4" s="45" t="s">
+      <c r="BD4" s="55" t="s">
         <v>245</v>
       </c>
-      <c r="BE4" s="45" t="s">
+      <c r="BE4" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="45" t="s">
+      <c r="BF4" s="55" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="45" t="s">
+      <c r="BG4" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="BH4" s="45" t="s">
+      <c r="BH4" s="55" t="s">
         <v>244</v>
       </c>
-      <c r="BI4" s="45" t="s">
+      <c r="BI4" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="45" t="s">
+      <c r="BJ4" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="45" t="s">
+      <c r="BK4" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="49" t="s">
+      <c r="BL4" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="49" t="s">
+      <c r="BM4" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="BN4" s="45" t="s">
+      <c r="BN4" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="BO4" s="45" t="s">
+      <c r="BO4" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="BP4" s="45" t="s">
+      <c r="BP4" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="BQ4" s="45" t="s">
+      <c r="BQ4" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="BR4" s="45" t="s">
+      <c r="BR4" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="BS4" s="45" t="s">
+      <c r="BS4" s="55" t="s">
         <v>219</v>
       </c>
-      <c r="BT4" s="45" t="s">
+      <c r="BT4" s="55" t="s">
         <v>220</v>
       </c>
-      <c r="BU4" s="49" t="s">
+      <c r="BU4" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="BV4" s="49" t="s">
+      <c r="BV4" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="BW4" s="49" t="s">
+      <c r="BW4" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="BX4" s="49" t="s">
+      <c r="BX4" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="49" t="s">
+      <c r="BY4" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="BZ4" s="45" t="s">
+      <c r="BZ4" s="55" t="s">
         <v>226</v>
       </c>
-      <c r="CA4" s="45" t="s">
+      <c r="CA4" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="CB4" s="45" t="s">
+      <c r="CB4" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="CC4" s="45" t="s">
+      <c r="CC4" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="CD4" s="45" t="s">
+      <c r="CD4" s="55" t="s">
         <v>230</v>
       </c>
-      <c r="CE4" s="47" t="s">
+      <c r="CE4" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="CF4" s="47" t="s">
+      <c r="CF4" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="CG4" s="47" t="s">
+      <c r="CG4" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="CH4" s="47" t="s">
+      <c r="CH4" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="CI4" s="47" t="s">
+      <c r="CI4" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="CJ4" s="47" t="s">
+      <c r="CJ4" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="CK4" s="47" t="s">
+      <c r="CK4" s="49" t="s">
         <v>264</v>
       </c>
-      <c r="CL4" s="47" t="s">
+      <c r="CL4" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="CM4" s="47" t="s">
+      <c r="CM4" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="CN4" s="47" t="s">
+      <c r="CN4" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="CO4" s="47" t="s">
+      <c r="CO4" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="CP4" s="47" t="s">
+      <c r="CP4" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="CQ4" s="47" t="s">
+      <c r="CQ4" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="CR4" s="47" t="s">
+      <c r="CR4" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="CS4" s="47" t="s">
+      <c r="CS4" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="CT4" s="47" t="s">
+      <c r="CT4" s="49" t="s">
         <v>286</v>
       </c>
-      <c r="CU4" s="47" t="s">
+      <c r="CU4" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="CV4" s="47" t="s">
+      <c r="CV4" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="CW4" s="47" t="s">
+      <c r="CW4" s="49" t="s">
         <v>292</v>
       </c>
-      <c r="CX4" s="47" t="s">
+      <c r="CX4" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="CY4" s="47" t="s">
+      <c r="CY4" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="CZ4" s="47" t="s">
+      <c r="CZ4" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="DA4" s="47" t="s">
+      <c r="DA4" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="DB4" s="47" t="s">
+      <c r="DB4" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="DC4" s="47" t="s">
+      <c r="DC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="74" t="s">
+      <c r="DD4" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="DE4" s="69" t="s">
+      <c r="DE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="DF4" s="69" t="s">
+      <c r="DF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="DG4" s="69" t="s">
+      <c r="DG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="DH4" s="69" t="s">
+      <c r="DH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="DI4" s="69" t="s">
+      <c r="DI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="DJ4" s="69" t="s">
+      <c r="DJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="DK4" s="69" t="s">
+      <c r="DK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="DL4" s="69" t="s">
+      <c r="DL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="DM4" s="69" t="s">
+      <c r="DM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="DN4" s="69" t="s">
+      <c r="DN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="DO4" s="69" t="s">
+      <c r="DO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="DP4" s="69" t="s">
+      <c r="DP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="DQ4" s="69" t="s">
+      <c r="DQ4" s="46" t="s">
         <v>338</v>
       </c>
-      <c r="DR4" s="69" t="s">
+      <c r="DR4" s="46" t="s">
         <v>341</v>
       </c>
-      <c r="DS4" s="69" t="s">
+      <c r="DS4" s="46" t="s">
         <v>345</v>
       </c>
-      <c r="DT4" s="69" t="s">
+      <c r="DT4" s="46" t="s">
         <v>349</v>
       </c>
-      <c r="DU4" s="69" t="s">
+      <c r="DU4" s="46" t="s">
         <v>352</v>
       </c>
-      <c r="DV4" s="69" t="s">
+      <c r="DV4" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="DW4" s="69" t="s">
+      <c r="DW4" s="46" t="s">
         <v>357</v>
       </c>
-      <c r="DX4" s="69" t="s">
+      <c r="DX4" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="DY4" s="69" t="s">
+      <c r="DY4" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="DZ4" s="69" t="s">
+      <c r="DZ4" s="46" t="s">
         <v>363</v>
       </c>
-      <c r="EA4" s="69" t="s">
+      <c r="EA4" s="46" t="s">
         <v>371</v>
       </c>
-      <c r="EB4" s="69" t="s">
+      <c r="EB4" s="46" t="s">
         <v>375</v>
       </c>
-      <c r="EC4" s="69" t="s">
+      <c r="EC4" s="46" t="s">
         <v>379</v>
       </c>
-      <c r="ED4" s="69" t="s">
+      <c r="ED4" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="EE4" s="69" t="s">
+      <c r="EE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="EF4" s="69" t="s">
+      <c r="EF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="EG4" s="69" t="s">
+      <c r="EG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="EH4" s="69" t="s">
+      <c r="EH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="EI4" s="69" t="s">
+      <c r="EI4" s="46" t="s">
         <v>393</v>
       </c>
-      <c r="EJ4" s="69" t="s">
+      <c r="EJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="EK4" s="69" t="s">
+      <c r="EK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="EL4" s="69" t="s">
+      <c r="EL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="EM4" s="69" t="s">
+      <c r="EM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="EN4" s="69" t="s">
+      <c r="EN4" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="EO4" s="69" t="s">
+      <c r="EO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="EP4" s="69" t="s">
+      <c r="EP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="EQ4" s="69" t="s">
+      <c r="EQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="ER4" s="69" t="s">
+      <c r="ER4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="ES4" s="69" t="s">
+      <c r="ES4" s="46" t="s">
         <v>416</v>
       </c>
+      <c r="ET4" s="46" t="s">
+        <v>418</v>
+      </c>
     </row>
-    <row r="5" spans="1:150" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="63"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="45"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="45"/>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="50"/>
-      <c r="BM5" s="50"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
-      <c r="BQ5" s="46"/>
-      <c r="BR5" s="46"/>
-      <c r="BS5" s="46"/>
-      <c r="BT5" s="46"/>
-      <c r="BU5" s="50"/>
-      <c r="BV5" s="50"/>
-      <c r="BW5" s="50"/>
-      <c r="BX5" s="50"/>
-      <c r="BY5" s="50"/>
-      <c r="BZ5" s="46"/>
-      <c r="CA5" s="46"/>
-      <c r="CB5" s="46"/>
-      <c r="CC5" s="46"/>
-      <c r="CD5" s="46"/>
-      <c r="CE5" s="48"/>
-      <c r="CF5" s="48"/>
-      <c r="CG5" s="48"/>
-      <c r="CH5" s="48"/>
-      <c r="CI5" s="48"/>
-      <c r="CJ5" s="48"/>
-      <c r="CK5" s="48"/>
-      <c r="CL5" s="48"/>
-      <c r="CM5" s="48"/>
-      <c r="CN5" s="48"/>
-      <c r="CO5" s="48"/>
-      <c r="CP5" s="48"/>
-      <c r="CQ5" s="48"/>
-      <c r="CR5" s="48"/>
-      <c r="CS5" s="48"/>
-      <c r="CT5" s="48"/>
-      <c r="CU5" s="48"/>
-      <c r="CV5" s="48"/>
-      <c r="CW5" s="48"/>
-      <c r="CX5" s="48"/>
-      <c r="CY5" s="48"/>
-      <c r="CZ5" s="48"/>
-      <c r="DA5" s="48"/>
-      <c r="DB5" s="48"/>
-      <c r="DC5" s="48"/>
-      <c r="DD5" s="75"/>
-      <c r="DE5" s="48"/>
-      <c r="DF5" s="48"/>
-      <c r="DG5" s="48"/>
-      <c r="DH5" s="48"/>
-      <c r="DI5" s="48"/>
-      <c r="DJ5" s="48"/>
-      <c r="DK5" s="48"/>
-      <c r="DL5" s="48"/>
-      <c r="DM5" s="48"/>
-      <c r="DN5" s="48"/>
-      <c r="DO5" s="48"/>
-      <c r="DP5" s="48"/>
-      <c r="DQ5" s="48"/>
-      <c r="DR5" s="48"/>
-      <c r="DS5" s="48"/>
-      <c r="DT5" s="48"/>
-      <c r="DU5" s="48"/>
-      <c r="DV5" s="48"/>
-      <c r="DW5" s="48"/>
-      <c r="DX5" s="48"/>
-      <c r="DY5" s="48"/>
-      <c r="DZ5" s="48"/>
-      <c r="EA5" s="48"/>
-      <c r="EB5" s="48"/>
-      <c r="EC5" s="69"/>
-      <c r="ED5" s="69"/>
-      <c r="EE5" s="69"/>
-      <c r="EF5" s="69"/>
-      <c r="EG5" s="69"/>
-      <c r="EH5" s="69"/>
-      <c r="EI5" s="69"/>
-      <c r="EJ5" s="69"/>
-      <c r="EK5" s="69"/>
-      <c r="EL5" s="69"/>
-      <c r="EM5" s="69"/>
-      <c r="EN5" s="69"/>
-      <c r="EO5" s="69"/>
-      <c r="EP5" s="69"/>
-      <c r="EQ5" s="69"/>
-      <c r="ER5" s="69"/>
-      <c r="ES5" s="69"/>
+    <row r="5" spans="1:151" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="67"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="55"/>
+      <c r="AH5" s="55"/>
+      <c r="AI5" s="55"/>
+      <c r="AJ5" s="55"/>
+      <c r="AK5" s="55"/>
+      <c r="AL5" s="55"/>
+      <c r="AM5" s="55"/>
+      <c r="AN5" s="55"/>
+      <c r="AO5" s="55"/>
+      <c r="AP5" s="55"/>
+      <c r="AQ5" s="55"/>
+      <c r="AR5" s="56"/>
+      <c r="AS5" s="56"/>
+      <c r="AT5" s="56"/>
+      <c r="AU5" s="56"/>
+      <c r="AV5" s="56"/>
+      <c r="AW5" s="56"/>
+      <c r="AX5" s="56"/>
+      <c r="AY5" s="56"/>
+      <c r="AZ5" s="56"/>
+      <c r="BA5" s="56"/>
+      <c r="BB5" s="56"/>
+      <c r="BC5" s="56"/>
+      <c r="BD5" s="56"/>
+      <c r="BE5" s="56"/>
+      <c r="BF5" s="56"/>
+      <c r="BG5" s="56"/>
+      <c r="BH5" s="56"/>
+      <c r="BI5" s="56"/>
+      <c r="BJ5" s="56"/>
+      <c r="BK5" s="56"/>
+      <c r="BL5" s="58"/>
+      <c r="BM5" s="58"/>
+      <c r="BN5" s="56"/>
+      <c r="BO5" s="56"/>
+      <c r="BP5" s="56"/>
+      <c r="BQ5" s="56"/>
+      <c r="BR5" s="56"/>
+      <c r="BS5" s="56"/>
+      <c r="BT5" s="56"/>
+      <c r="BU5" s="58"/>
+      <c r="BV5" s="58"/>
+      <c r="BW5" s="58"/>
+      <c r="BX5" s="58"/>
+      <c r="BY5" s="58"/>
+      <c r="BZ5" s="56"/>
+      <c r="CA5" s="56"/>
+      <c r="CB5" s="56"/>
+      <c r="CC5" s="56"/>
+      <c r="CD5" s="56"/>
+      <c r="CE5" s="47"/>
+      <c r="CF5" s="47"/>
+      <c r="CG5" s="47"/>
+      <c r="CH5" s="47"/>
+      <c r="CI5" s="47"/>
+      <c r="CJ5" s="47"/>
+      <c r="CK5" s="47"/>
+      <c r="CL5" s="47"/>
+      <c r="CM5" s="47"/>
+      <c r="CN5" s="47"/>
+      <c r="CO5" s="47"/>
+      <c r="CP5" s="47"/>
+      <c r="CQ5" s="47"/>
+      <c r="CR5" s="47"/>
+      <c r="CS5" s="47"/>
+      <c r="CT5" s="47"/>
+      <c r="CU5" s="47"/>
+      <c r="CV5" s="47"/>
+      <c r="CW5" s="47"/>
+      <c r="CX5" s="47"/>
+      <c r="CY5" s="47"/>
+      <c r="CZ5" s="47"/>
+      <c r="DA5" s="47"/>
+      <c r="DB5" s="47"/>
+      <c r="DC5" s="47"/>
+      <c r="DD5" s="51"/>
+      <c r="DE5" s="47"/>
+      <c r="DF5" s="47"/>
+      <c r="DG5" s="47"/>
+      <c r="DH5" s="47"/>
+      <c r="DI5" s="47"/>
+      <c r="DJ5" s="47"/>
+      <c r="DK5" s="47"/>
+      <c r="DL5" s="47"/>
+      <c r="DM5" s="47"/>
+      <c r="DN5" s="47"/>
+      <c r="DO5" s="47"/>
+      <c r="DP5" s="47"/>
+      <c r="DQ5" s="47"/>
+      <c r="DR5" s="47"/>
+      <c r="DS5" s="47"/>
+      <c r="DT5" s="47"/>
+      <c r="DU5" s="47"/>
+      <c r="DV5" s="47"/>
+      <c r="DW5" s="47"/>
+      <c r="DX5" s="47"/>
+      <c r="DY5" s="47"/>
+      <c r="DZ5" s="47"/>
+      <c r="EA5" s="47"/>
+      <c r="EB5" s="47"/>
+      <c r="EC5" s="46"/>
+      <c r="ED5" s="46"/>
+      <c r="EE5" s="46"/>
+      <c r="EF5" s="46"/>
+      <c r="EG5" s="46"/>
+      <c r="EH5" s="46"/>
+      <c r="EI5" s="46"/>
+      <c r="EJ5" s="46"/>
+      <c r="EK5" s="46"/>
+      <c r="EL5" s="46"/>
+      <c r="EM5" s="46"/>
+      <c r="EN5" s="46"/>
+      <c r="EO5" s="46"/>
+      <c r="EP5" s="46"/>
+      <c r="EQ5" s="46"/>
+      <c r="ER5" s="46"/>
+      <c r="ES5" s="46"/>
+      <c r="ET5" s="46"/>
     </row>
-    <row r="6" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10799,9 +10803,12 @@
       <c r="ES6" s="28">
         <v>187</v>
       </c>
-      <c r="ET6" s="1"/>
+      <c r="ET6" s="28">
+        <v>149</v>
+      </c>
+      <c r="EU6" s="1"/>
     </row>
-    <row r="7" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11246,8 +11253,11 @@
       <c r="ES7" s="15">
         <v>3</v>
       </c>
+      <c r="ET7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11692,8 +11702,11 @@
       <c r="ES8" s="28">
         <v>51</v>
       </c>
+      <c r="ET8" s="28">
+        <v>30</v>
+      </c>
     </row>
-    <row r="9" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12139,8 +12152,11 @@
       <c r="ES9" s="15">
         <v>132</v>
       </c>
+      <c r="ET9" s="15">
+        <v>117</v>
+      </c>
     </row>
-    <row r="10" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12583,8 +12599,11 @@
       <c r="ES10" s="15">
         <v>3</v>
       </c>
+      <c r="ET10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13029,8 +13048,11 @@
       <c r="ES11" s="15">
         <v>15</v>
       </c>
+      <c r="ET11" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="12" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13475,8 +13497,11 @@
       <c r="ES12" s="15">
         <v>13</v>
       </c>
+      <c r="ET12" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="13" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -13921,9 +13946,12 @@
       <c r="ES13" s="15">
         <v>42</v>
       </c>
-      <c r="ET13" s="1"/>
+      <c r="ET13" s="15">
+        <v>51</v>
+      </c>
+      <c r="EU13" s="1"/>
     </row>
-    <row r="14" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14368,8 +14396,11 @@
       <c r="ES14" s="15">
         <v>52</v>
       </c>
+      <c r="ET14" s="15">
+        <v>48</v>
+      </c>
     </row>
-    <row r="15" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -14814,8 +14845,11 @@
       <c r="ES15" s="15">
         <v>18</v>
       </c>
+      <c r="ET15" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="16" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15261,9 +15295,12 @@
       <c r="ES16" s="28">
         <v>256</v>
       </c>
-      <c r="ET16" s="1"/>
+      <c r="ET16" s="28">
+        <v>216</v>
+      </c>
+      <c r="EU16" s="1"/>
     </row>
-    <row r="17" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15708,9 +15745,12 @@
       <c r="ES17" s="15">
         <v>245</v>
       </c>
-      <c r="ET17" s="1"/>
+      <c r="ET17" s="15">
+        <v>172</v>
+      </c>
+      <c r="EU17" s="1"/>
     </row>
-    <row r="18" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16156,11 +16196,14 @@
       <c r="ES18" s="34">
         <v>3403</v>
       </c>
-      <c r="ET18" s="1"/>
+      <c r="ET18" s="34">
+        <v>2637</v>
+      </c>
+      <c r="EU18" s="1"/>
     </row>
-    <row r="19" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="70" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -16604,11 +16647,14 @@
       <c r="ES19" s="15">
         <v>170</v>
       </c>
-      <c r="ET19" s="1"/>
+      <c r="ET19" s="15">
+        <v>129</v>
+      </c>
+      <c r="EU19" s="1"/>
     </row>
-    <row r="20" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="53"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -17050,11 +17096,14 @@
       <c r="ES20" s="28">
         <v>541</v>
       </c>
-      <c r="ET20" s="1"/>
+      <c r="ET20" s="28">
+        <v>308</v>
+      </c>
+      <c r="EU20" s="1"/>
     </row>
-    <row r="21" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="53"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -17496,9 +17545,12 @@
       <c r="ES21" s="15">
         <v>61</v>
       </c>
-      <c r="ET21" s="1"/>
+      <c r="ET21" s="15">
+        <v>85</v>
+      </c>
+      <c r="EU21" s="1"/>
     </row>
-    <row r="22" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -17943,8 +17995,11 @@
       <c r="ES22" s="15">
         <v>11</v>
       </c>
+      <c r="ET22" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18389,8 +18444,11 @@
       <c r="ES23" s="15">
         <v>8</v>
       </c>
+      <c r="ET23" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -18835,9 +18893,12 @@
       <c r="ES24" s="15">
         <v>33</v>
       </c>
-      <c r="ET24" s="1"/>
+      <c r="ET24" s="15">
+        <v>14</v>
+      </c>
+      <c r="EU24" s="1"/>
     </row>
-    <row r="25" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19282,8 +19343,11 @@
       <c r="ES25" s="15">
         <v>8</v>
       </c>
+      <c r="ET25" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -19728,8 +19792,11 @@
       <c r="ES26" s="15">
         <v>29</v>
       </c>
+      <c r="ET26" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="27" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20174,8 +20241,11 @@
       <c r="ES27" s="15">
         <v>3</v>
       </c>
+      <c r="ET27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -20620,10 +20690,13 @@
       <c r="ES28" s="15">
         <v>13</v>
       </c>
-      <c r="ET28" s="1"/>
+      <c r="ET28" s="15">
+        <v>2</v>
+      </c>
+      <c r="EU28" s="1"/>
     </row>
-    <row r="29" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="54" t="s">
+    <row r="29" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -21067,9 +21140,12 @@
       <c r="ES29" s="15">
         <v>11</v>
       </c>
+      <c r="ET29" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="54"/>
+    <row r="30" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -21511,8 +21587,11 @@
       <c r="ES30" s="15">
         <v>88</v>
       </c>
+      <c r="ET30" s="15">
+        <v>76</v>
+      </c>
     </row>
-    <row r="31" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -21958,9 +22037,12 @@
       <c r="ES31" s="15">
         <v>316</v>
       </c>
-      <c r="ET31" s="1"/>
+      <c r="ET31" s="15">
+        <v>221</v>
+      </c>
+      <c r="EU31" s="1"/>
     </row>
-    <row r="32" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22405,8 +22487,11 @@
       <c r="ES32" s="15">
         <v>16</v>
       </c>
+      <c r="ET32" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="33" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -22851,8 +22936,11 @@
       <c r="ES33" s="15">
         <v>1</v>
       </c>
+      <c r="ET33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23298,11 +23386,14 @@
       <c r="ES34" s="15">
         <v>240</v>
       </c>
-      <c r="ET34" s="1"/>
+      <c r="ET34" s="15">
+        <v>163</v>
+      </c>
+      <c r="EU34" s="1"/>
     </row>
-    <row r="35" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="70" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -23746,10 +23837,13 @@
       <c r="ES35" s="15">
         <v>676</v>
       </c>
-      <c r="ET35" s="1"/>
+      <c r="ET35" s="15">
+        <v>516</v>
+      </c>
+      <c r="EU35" s="1"/>
     </row>
-    <row r="36" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="53"/>
+    <row r="36" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -24191,9 +24285,12 @@
       <c r="ES36" s="28">
         <v>148</v>
       </c>
-      <c r="ET36" s="1"/>
+      <c r="ET36" s="28">
+        <v>78</v>
+      </c>
+      <c r="EU36" s="1"/>
     </row>
-    <row r="37" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -24639,9 +24736,12 @@
       <c r="ES37" s="15">
         <v>208</v>
       </c>
-      <c r="ET37" s="1"/>
+      <c r="ET37" s="15">
+        <v>117</v>
+      </c>
+      <c r="EU37" s="1"/>
     </row>
-    <row r="38" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -25086,8 +25186,11 @@
       <c r="ES38" s="15">
         <v>45</v>
       </c>
+      <c r="ET38" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="39" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -25532,8 +25635,11 @@
       <c r="ES39" s="15">
         <v>33</v>
       </c>
+      <c r="ET39" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="40" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -25978,8 +26084,11 @@
       <c r="ES40" s="15">
         <v>1</v>
       </c>
+      <c r="ET40" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -26424,8 +26533,11 @@
       <c r="ES41" s="15">
         <v>0</v>
       </c>
+      <c r="ET41" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -26870,8 +26982,11 @@
       <c r="ES42" s="15">
         <v>77</v>
       </c>
+      <c r="ET42" s="15">
+        <v>31</v>
+      </c>
     </row>
-    <row r="43" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27316,8 +27431,11 @@
       <c r="ES43" s="28">
         <v>133</v>
       </c>
+      <c r="ET43" s="28">
+        <v>132</v>
+      </c>
     </row>
-    <row r="44" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -27762,8 +27880,11 @@
       <c r="ES44" s="15">
         <v>8</v>
       </c>
+      <c r="ET44" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="45" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28208,9 +28329,12 @@
       <c r="ES45" s="15">
         <v>39</v>
       </c>
-      <c r="ET45" s="1"/>
+      <c r="ET45" s="15">
+        <v>27</v>
+      </c>
+      <c r="EU45" s="1"/>
     </row>
-    <row r="46" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -28655,8 +28779,11 @@
       <c r="ES46" s="15">
         <v>66</v>
       </c>
+      <c r="ET46" s="15">
+        <v>38</v>
+      </c>
     </row>
-    <row r="47" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -29101,8 +29228,11 @@
       <c r="ES47" s="15">
         <v>2</v>
       </c>
+      <c r="ET47" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="48" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -29547,10 +29677,13 @@
       <c r="ES48" s="15">
         <v>46</v>
       </c>
+      <c r="ET48" s="15">
+        <v>60</v>
+      </c>
     </row>
-    <row r="49" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="53" t="s">
+      <c r="B49" s="70" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -29994,10 +30127,13 @@
       <c r="ES49" s="15">
         <v>271</v>
       </c>
-      <c r="ET49" s="1"/>
+      <c r="ET49" s="15">
+        <v>159</v>
+      </c>
+      <c r="EU49" s="1"/>
     </row>
-    <row r="50" spans="1:150" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="53"/>
+    <row r="50" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -30439,9 +30575,12 @@
       <c r="ES50" s="15">
         <v>160</v>
       </c>
-      <c r="ET50" s="1"/>
+      <c r="ET50" s="15">
+        <v>63</v>
+      </c>
+      <c r="EU50" s="1"/>
     </row>
-    <row r="51" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -30886,8 +31025,11 @@
       <c r="ES51" s="15">
         <v>34</v>
       </c>
+      <c r="ET51" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="52" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -31332,8 +31474,11 @@
       <c r="ES52" s="15">
         <v>56</v>
       </c>
+      <c r="ET52" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="53" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -31778,8 +31923,11 @@
       <c r="ES53" s="15">
         <v>106</v>
       </c>
+      <c r="ET53" s="15">
+        <v>69</v>
+      </c>
     </row>
-    <row r="54" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -32224,8 +32372,11 @@
       <c r="ES54" s="15">
         <v>24</v>
       </c>
+      <c r="ET54" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="55" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -32670,8 +32821,11 @@
       <c r="ES55" s="15">
         <v>33</v>
       </c>
+      <c r="ET55" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="56" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -33116,8 +33270,11 @@
       <c r="ES56" s="15">
         <v>21</v>
       </c>
+      <c r="ET56" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="57" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -33562,8 +33719,11 @@
       <c r="ES57" s="15">
         <v>5</v>
       </c>
+      <c r="ET57" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -34041,7 +34201,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:ES58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:ET58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -34152,8 +34312,12 @@
         <f t="shared" si="10"/>
         <v>8161</v>
       </c>
+      <c r="ET58" s="14">
+        <f t="shared" si="10"/>
+        <v>5998</v>
+      </c>
     </row>
-    <row r="59" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -34237,7 +34401,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -34321,30 +34485,30 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:150" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="52"/>
-      <c r="H61" s="52"/>
-      <c r="I61" s="52"/>
-      <c r="J61" s="52"/>
-      <c r="K61" s="52"/>
-      <c r="L61" s="52"/>
-      <c r="M61" s="52"/>
-      <c r="N61" s="52"/>
-      <c r="O61" s="52"/>
-      <c r="P61" s="52"/>
-      <c r="Q61" s="52"/>
-      <c r="R61" s="52"/>
-      <c r="S61" s="52"/>
-      <c r="T61" s="52"/>
-      <c r="U61" s="52"/>
-      <c r="V61" s="52"/>
-      <c r="W61" s="52"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="69"/>
+      <c r="M61" s="69"/>
+      <c r="N61" s="69"/>
+      <c r="O61" s="69"/>
+      <c r="P61" s="69"/>
+      <c r="Q61" s="69"/>
+      <c r="R61" s="69"/>
+      <c r="S61" s="69"/>
+      <c r="T61" s="69"/>
+      <c r="U61" s="69"/>
+      <c r="V61" s="69"/>
+      <c r="W61" s="69"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -34406,66 +34570,84 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="163">
-    <mergeCell ref="EQ4:EQ5"/>
-    <mergeCell ref="EP4:EP5"/>
-    <mergeCell ref="EO4:EO5"/>
-    <mergeCell ref="EN4:EN5"/>
-    <mergeCell ref="EM4:EM5"/>
-    <mergeCell ref="EL4:EL5"/>
-    <mergeCell ref="EJ4:EJ5"/>
-    <mergeCell ref="ER4:ER5"/>
-    <mergeCell ref="DE3:EQ3"/>
-    <mergeCell ref="DT4:DT5"/>
-    <mergeCell ref="DP4:DP5"/>
-    <mergeCell ref="DE2:ES2"/>
-    <mergeCell ref="ER3:ES3"/>
-    <mergeCell ref="ES4:ES5"/>
-    <mergeCell ref="CR3:DD3"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="DD4:DD5"/>
-    <mergeCell ref="DA4:DA5"/>
-    <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="CW4:CW5"/>
-    <mergeCell ref="EI4:EI5"/>
-    <mergeCell ref="EH4:EH5"/>
-    <mergeCell ref="EC4:EC5"/>
-    <mergeCell ref="EB4:EB5"/>
-    <mergeCell ref="EA4:EA5"/>
-    <mergeCell ref="DF4:DF5"/>
-    <mergeCell ref="EG4:EG5"/>
-    <mergeCell ref="EF4:EF5"/>
-    <mergeCell ref="EE4:EE5"/>
-    <mergeCell ref="DZ4:DZ5"/>
-    <mergeCell ref="DJ4:DJ5"/>
-    <mergeCell ref="DI4:DI5"/>
-    <mergeCell ref="DG4:DG5"/>
-    <mergeCell ref="DE4:DE5"/>
-    <mergeCell ref="DC4:DC5"/>
-    <mergeCell ref="DB4:DB5"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="BD2:DD2"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="EK4:EK5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="DK4:DK5"/>
-    <mergeCell ref="DH4:DH5"/>
-    <mergeCell ref="DY4:DY5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="CE4:CE5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="DQ4:DQ5"/>
-    <mergeCell ref="DL4:DL5"/>
-    <mergeCell ref="DM4:DM5"/>
-    <mergeCell ref="ED4:ED5"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="CA4:CA5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="DX4:DX5"/>
-    <mergeCell ref="DW4:DW5"/>
-    <mergeCell ref="DV4:DV5"/>
-    <mergeCell ref="DU4:DU5"/>
+  <mergeCells count="164">
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AV4:AV5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="BR4:BR5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="D61:W61"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="D3:AQ3"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="D2:BC2"/>
     <mergeCell ref="DO4:DO5"/>
@@ -34490,86 +34672,69 @@
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="CG4:CG5"/>
     <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="D3:AQ3"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="D61:W61"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="BD2:DD2"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="EK4:EK5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="DK4:DK5"/>
+    <mergeCell ref="DH4:DH5"/>
+    <mergeCell ref="DY4:DY5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="DQ4:DQ5"/>
+    <mergeCell ref="DL4:DL5"/>
+    <mergeCell ref="DM4:DM5"/>
+    <mergeCell ref="ED4:ED5"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="DX4:DX5"/>
+    <mergeCell ref="DW4:DW5"/>
+    <mergeCell ref="DV4:DV5"/>
+    <mergeCell ref="DU4:DU5"/>
     <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="CR3:DD3"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="DD4:DD5"/>
+    <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="EI4:EI5"/>
+    <mergeCell ref="EH4:EH5"/>
+    <mergeCell ref="EC4:EC5"/>
+    <mergeCell ref="EB4:EB5"/>
+    <mergeCell ref="EA4:EA5"/>
+    <mergeCell ref="DF4:DF5"/>
+    <mergeCell ref="EG4:EG5"/>
+    <mergeCell ref="EF4:EF5"/>
+    <mergeCell ref="EE4:EE5"/>
+    <mergeCell ref="DZ4:DZ5"/>
+    <mergeCell ref="DJ4:DJ5"/>
+    <mergeCell ref="DI4:DI5"/>
+    <mergeCell ref="DG4:DG5"/>
+    <mergeCell ref="DE4:DE5"/>
+    <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="CZ4:CZ5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="DE2:ET2"/>
+    <mergeCell ref="ER3:ET3"/>
+    <mergeCell ref="ET4:ET5"/>
+    <mergeCell ref="EQ4:EQ5"/>
+    <mergeCell ref="EP4:EP5"/>
+    <mergeCell ref="EO4:EO5"/>
+    <mergeCell ref="EN4:EN5"/>
+    <mergeCell ref="EM4:EM5"/>
+    <mergeCell ref="EL4:EL5"/>
+    <mergeCell ref="EJ4:EJ5"/>
+    <mergeCell ref="ER4:ER5"/>
+    <mergeCell ref="DE3:EQ3"/>
+    <mergeCell ref="DT4:DT5"/>
+    <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="ES4:ES5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -34582,7 +34747,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:ES57">
+  <conditionalFormatting sqref="DP6:ET57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -34602,7 +34767,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:ES58"/>
+  <dimension ref="B1:ET58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -34625,15 +34790,15 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="149" width="10.875" style="1" customWidth="1"/>
-    <col min="150" max="16384" width="8.625" style="1"/>
+    <col min="106" max="150" width="10.875" style="1" customWidth="1"/>
+    <col min="151" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:149" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="BB1" s="79" t="s">
+    <row r="1" spans="2:150" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BB1" s="82" t="s">
         <v>323</v>
       </c>
-      <c r="BC1" s="79"/>
+      <c r="BC1" s="82"/>
       <c r="BI1" s="18"/>
       <c r="CC1" s="29"/>
       <c r="CD1" s="29"/>
@@ -34705,925 +34870,932 @@
       <c r="EP1" s="19"/>
       <c r="EQ1" s="19"/>
       <c r="ER1" s="19"/>
-      <c r="ES1" s="19" t="s">
+      <c r="ES1" s="19"/>
+      <c r="ET1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:149" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="85" t="s">
+    <row r="2" spans="2:150" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="85"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="85"/>
-      <c r="AF2" s="85"/>
-      <c r="AG2" s="85"/>
-      <c r="AH2" s="85"/>
-      <c r="AI2" s="85"/>
-      <c r="AJ2" s="85"/>
-      <c r="AK2" s="85"/>
-      <c r="AL2" s="85"/>
-      <c r="AM2" s="85"/>
-      <c r="AN2" s="85"/>
-      <c r="AO2" s="85"/>
-      <c r="AP2" s="85"/>
-      <c r="AQ2" s="85"/>
-      <c r="AR2" s="85"/>
-      <c r="AS2" s="85"/>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="85"/>
-      <c r="AZ2" s="85"/>
-      <c r="BA2" s="85"/>
-      <c r="BB2" s="85"/>
-      <c r="BC2" s="85"/>
-      <c r="BD2" s="85" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="44"/>
+      <c r="AV2" s="44"/>
+      <c r="AW2" s="44"/>
+      <c r="AX2" s="44"/>
+      <c r="AY2" s="44"/>
+      <c r="AZ2" s="44"/>
+      <c r="BA2" s="44"/>
+      <c r="BB2" s="44"/>
+      <c r="BC2" s="44"/>
+      <c r="BD2" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="85"/>
-      <c r="BF2" s="85"/>
-      <c r="BG2" s="85"/>
-      <c r="BH2" s="85"/>
-      <c r="BI2" s="85"/>
-      <c r="BJ2" s="85"/>
-      <c r="BK2" s="85"/>
-      <c r="BL2" s="85"/>
-      <c r="BM2" s="85"/>
-      <c r="BN2" s="85"/>
-      <c r="BO2" s="85"/>
-      <c r="BP2" s="85"/>
-      <c r="BQ2" s="85"/>
-      <c r="BR2" s="85"/>
-      <c r="BS2" s="85"/>
-      <c r="BT2" s="85"/>
-      <c r="BU2" s="85"/>
-      <c r="BV2" s="85"/>
-      <c r="BW2" s="85"/>
-      <c r="BX2" s="85"/>
-      <c r="BY2" s="85"/>
-      <c r="BZ2" s="85"/>
-      <c r="CA2" s="85"/>
-      <c r="CB2" s="85"/>
-      <c r="CC2" s="85"/>
-      <c r="CD2" s="85"/>
-      <c r="CE2" s="85"/>
-      <c r="CF2" s="85"/>
-      <c r="CG2" s="85"/>
-      <c r="CH2" s="85"/>
-      <c r="CI2" s="85"/>
-      <c r="CJ2" s="85"/>
-      <c r="CK2" s="85"/>
-      <c r="CL2" s="85"/>
-      <c r="CM2" s="85"/>
-      <c r="CN2" s="85"/>
-      <c r="CO2" s="85"/>
-      <c r="CP2" s="85"/>
-      <c r="CQ2" s="85"/>
-      <c r="CR2" s="85"/>
-      <c r="CS2" s="85"/>
-      <c r="CT2" s="85"/>
-      <c r="CU2" s="85"/>
-      <c r="CV2" s="85"/>
-      <c r="CW2" s="85"/>
-      <c r="CX2" s="85"/>
-      <c r="CY2" s="85"/>
-      <c r="CZ2" s="85"/>
-      <c r="DA2" s="85"/>
-      <c r="DB2" s="85"/>
-      <c r="DC2" s="85"/>
-      <c r="DD2" s="85" t="s">
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
+      <c r="CU2" s="44"/>
+      <c r="CV2" s="44"/>
+      <c r="CW2" s="44"/>
+      <c r="CX2" s="44"/>
+      <c r="CY2" s="44"/>
+      <c r="CZ2" s="44"/>
+      <c r="DA2" s="44"/>
+      <c r="DB2" s="44"/>
+      <c r="DC2" s="44"/>
+      <c r="DD2" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="85"/>
-      <c r="DF2" s="85"/>
-      <c r="DG2" s="85"/>
-      <c r="DH2" s="85"/>
-      <c r="DI2" s="85"/>
-      <c r="DJ2" s="85"/>
-      <c r="DK2" s="85"/>
-      <c r="DL2" s="85"/>
-      <c r="DM2" s="85"/>
-      <c r="DN2" s="85"/>
-      <c r="DO2" s="85"/>
-      <c r="DP2" s="85"/>
-      <c r="DQ2" s="85"/>
-      <c r="DR2" s="85"/>
-      <c r="DS2" s="85"/>
-      <c r="DT2" s="85"/>
-      <c r="DU2" s="85"/>
-      <c r="DV2" s="85"/>
-      <c r="DW2" s="85"/>
-      <c r="DX2" s="85"/>
-      <c r="DY2" s="85"/>
-      <c r="DZ2" s="85"/>
-      <c r="EA2" s="85"/>
-      <c r="EB2" s="85"/>
-      <c r="EC2" s="85"/>
-      <c r="ED2" s="85"/>
-      <c r="EE2" s="85"/>
-      <c r="EF2" s="85"/>
-      <c r="EG2" s="85"/>
-      <c r="EH2" s="85"/>
-      <c r="EI2" s="85"/>
-      <c r="EJ2" s="85"/>
-      <c r="EK2" s="85"/>
-      <c r="EL2" s="85"/>
-      <c r="EM2" s="85"/>
-      <c r="EN2" s="85"/>
-      <c r="EO2" s="85"/>
-      <c r="EP2" s="85"/>
-      <c r="EQ2" s="85"/>
-      <c r="ER2" s="85"/>
-      <c r="ES2" s="85"/>
+      <c r="DE2" s="44"/>
+      <c r="DF2" s="44"/>
+      <c r="DG2" s="44"/>
+      <c r="DH2" s="44"/>
+      <c r="DI2" s="44"/>
+      <c r="DJ2" s="44"/>
+      <c r="DK2" s="44"/>
+      <c r="DL2" s="44"/>
+      <c r="DM2" s="44"/>
+      <c r="DN2" s="44"/>
+      <c r="DO2" s="44"/>
+      <c r="DP2" s="44"/>
+      <c r="DQ2" s="44"/>
+      <c r="DR2" s="44"/>
+      <c r="DS2" s="44"/>
+      <c r="DT2" s="44"/>
+      <c r="DU2" s="44"/>
+      <c r="DV2" s="44"/>
+      <c r="DW2" s="44"/>
+      <c r="DX2" s="44"/>
+      <c r="DY2" s="44"/>
+      <c r="DZ2" s="44"/>
+      <c r="EA2" s="44"/>
+      <c r="EB2" s="44"/>
+      <c r="EC2" s="44"/>
+      <c r="ED2" s="44"/>
+      <c r="EE2" s="44"/>
+      <c r="EF2" s="44"/>
+      <c r="EG2" s="44"/>
+      <c r="EH2" s="44"/>
+      <c r="EI2" s="44"/>
+      <c r="EJ2" s="44"/>
+      <c r="EK2" s="44"/>
+      <c r="EL2" s="44"/>
+      <c r="EM2" s="44"/>
+      <c r="EN2" s="44"/>
+      <c r="EO2" s="44"/>
+      <c r="EP2" s="44"/>
+      <c r="EQ2" s="44"/>
+      <c r="ER2" s="44"/>
+      <c r="ES2" s="44"/>
+      <c r="ET2" s="44"/>
     </row>
-    <row r="3" spans="2:149" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82" t="s">
+    <row r="3" spans="2:150" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="82"/>
-      <c r="AL3" s="82"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="82"/>
-      <c r="AO3" s="82"/>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="64" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="81"/>
+      <c r="AH3" s="81"/>
+      <c r="AI3" s="81"/>
+      <c r="AJ3" s="81"/>
+      <c r="AK3" s="81"/>
+      <c r="AL3" s="81"/>
+      <c r="AM3" s="81"/>
+      <c r="AN3" s="81"/>
+      <c r="AO3" s="81"/>
+      <c r="AP3" s="81"/>
+      <c r="AQ3" s="81"/>
+      <c r="AR3" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="64"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="64"/>
-      <c r="AY3" s="64"/>
-      <c r="AZ3" s="64"/>
-      <c r="BA3" s="64"/>
-      <c r="BB3" s="64"/>
-      <c r="BC3" s="64"/>
-      <c r="BD3" s="65" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="BE3" s="66"/>
-      <c r="BF3" s="66"/>
-      <c r="BG3" s="66"/>
-      <c r="BH3" s="66"/>
-      <c r="BI3" s="66"/>
-      <c r="BJ3" s="66"/>
-      <c r="BK3" s="66"/>
-      <c r="BL3" s="66"/>
-      <c r="BM3" s="66"/>
-      <c r="BN3" s="66"/>
-      <c r="BO3" s="66"/>
-      <c r="BP3" s="66"/>
-      <c r="BQ3" s="66"/>
-      <c r="BR3" s="66"/>
-      <c r="BS3" s="66"/>
-      <c r="BT3" s="66"/>
-      <c r="BU3" s="66"/>
-      <c r="BV3" s="66"/>
-      <c r="BW3" s="66"/>
-      <c r="BX3" s="66"/>
-      <c r="BY3" s="66"/>
-      <c r="BZ3" s="66"/>
-      <c r="CA3" s="66"/>
-      <c r="CB3" s="66"/>
-      <c r="CC3" s="66"/>
-      <c r="CD3" s="66"/>
-      <c r="CE3" s="66"/>
-      <c r="CF3" s="66"/>
-      <c r="CG3" s="66"/>
-      <c r="CH3" s="66"/>
-      <c r="CI3" s="66"/>
-      <c r="CJ3" s="66"/>
-      <c r="CK3" s="66"/>
-      <c r="CL3" s="66"/>
-      <c r="CM3" s="66"/>
-      <c r="CN3" s="66"/>
-      <c r="CO3" s="66"/>
-      <c r="CP3" s="66"/>
-      <c r="CQ3" s="70"/>
-      <c r="CR3" s="64" t="s">
+      <c r="BE3" s="53"/>
+      <c r="BF3" s="53"/>
+      <c r="BG3" s="53"/>
+      <c r="BH3" s="53"/>
+      <c r="BI3" s="53"/>
+      <c r="BJ3" s="53"/>
+      <c r="BK3" s="53"/>
+      <c r="BL3" s="53"/>
+      <c r="BM3" s="53"/>
+      <c r="BN3" s="53"/>
+      <c r="BO3" s="53"/>
+      <c r="BP3" s="53"/>
+      <c r="BQ3" s="53"/>
+      <c r="BR3" s="53"/>
+      <c r="BS3" s="53"/>
+      <c r="BT3" s="53"/>
+      <c r="BU3" s="53"/>
+      <c r="BV3" s="53"/>
+      <c r="BW3" s="53"/>
+      <c r="BX3" s="53"/>
+      <c r="BY3" s="53"/>
+      <c r="BZ3" s="53"/>
+      <c r="CA3" s="53"/>
+      <c r="CB3" s="53"/>
+      <c r="CC3" s="53"/>
+      <c r="CD3" s="53"/>
+      <c r="CE3" s="53"/>
+      <c r="CF3" s="53"/>
+      <c r="CG3" s="53"/>
+      <c r="CH3" s="53"/>
+      <c r="CI3" s="53"/>
+      <c r="CJ3" s="53"/>
+      <c r="CK3" s="53"/>
+      <c r="CL3" s="53"/>
+      <c r="CM3" s="53"/>
+      <c r="CN3" s="53"/>
+      <c r="CO3" s="53"/>
+      <c r="CP3" s="53"/>
+      <c r="CQ3" s="54"/>
+      <c r="CR3" s="45" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="64"/>
-      <c r="CT3" s="64"/>
-      <c r="CU3" s="64"/>
-      <c r="CV3" s="64"/>
-      <c r="CW3" s="64"/>
-      <c r="CX3" s="64"/>
-      <c r="CY3" s="64"/>
-      <c r="CZ3" s="64"/>
-      <c r="DA3" s="64"/>
-      <c r="DB3" s="64"/>
-      <c r="DC3" s="64"/>
-      <c r="DD3" s="86" t="s">
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="87"/>
-      <c r="DF3" s="87"/>
-      <c r="DG3" s="87"/>
-      <c r="DH3" s="87"/>
-      <c r="DI3" s="87"/>
-      <c r="DJ3" s="87"/>
-      <c r="DK3" s="87"/>
-      <c r="DL3" s="87"/>
-      <c r="DM3" s="87"/>
-      <c r="DN3" s="87"/>
-      <c r="DO3" s="87"/>
-      <c r="DP3" s="87"/>
-      <c r="DQ3" s="87"/>
-      <c r="DR3" s="87"/>
-      <c r="DS3" s="87"/>
-      <c r="DT3" s="87"/>
-      <c r="DU3" s="87"/>
-      <c r="DV3" s="87"/>
-      <c r="DW3" s="87"/>
-      <c r="DX3" s="87"/>
-      <c r="DY3" s="87"/>
-      <c r="DZ3" s="87"/>
-      <c r="EA3" s="87"/>
-      <c r="EB3" s="87"/>
-      <c r="EC3" s="87"/>
-      <c r="ED3" s="87"/>
-      <c r="EE3" s="87"/>
-      <c r="EF3" s="87"/>
-      <c r="EG3" s="87"/>
-      <c r="EH3" s="87"/>
-      <c r="EI3" s="87"/>
-      <c r="EJ3" s="87"/>
-      <c r="EK3" s="87"/>
-      <c r="EL3" s="87"/>
-      <c r="EM3" s="87"/>
-      <c r="EN3" s="87"/>
-      <c r="EO3" s="87"/>
-      <c r="EP3" s="87"/>
-      <c r="EQ3" s="88"/>
-      <c r="ER3" s="65" t="s">
+      <c r="DE3" s="45"/>
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="70"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
     </row>
-    <row r="4" spans="2:149" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="76" t="s">
+    <row r="4" spans="2:150" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="78" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="78" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="J4" s="76" t="s">
+      <c r="J4" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="K4" s="76" t="s">
+      <c r="K4" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="L4" s="76" t="s">
+      <c r="L4" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="76" t="s">
+      <c r="M4" s="78" t="s">
         <v>192</v>
       </c>
-      <c r="N4" s="76" t="s">
+      <c r="N4" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="O4" s="76" t="s">
+      <c r="O4" s="78" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="76" t="s">
+      <c r="P4" s="78" t="s">
         <v>195</v>
       </c>
-      <c r="Q4" s="76" t="s">
+      <c r="Q4" s="78" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="83" t="s">
+      <c r="R4" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="S4" s="76" t="s">
+      <c r="S4" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="T4" s="76" t="s">
+      <c r="T4" s="78" t="s">
         <v>198</v>
       </c>
-      <c r="U4" s="76" t="s">
+      <c r="U4" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="V4" s="76" t="s">
+      <c r="V4" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="W4" s="76" t="s">
+      <c r="W4" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="X4" s="76" t="s">
+      <c r="X4" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="80" t="s">
+      <c r="Y4" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="Z4" s="76" t="s">
+      <c r="Z4" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" s="76" t="s">
+      <c r="AA4" s="78" t="s">
         <v>163</v>
       </c>
-      <c r="AB4" s="76" t="s">
+      <c r="AB4" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="AC4" s="80" t="s">
+      <c r="AC4" s="76" t="s">
         <v>165</v>
       </c>
-      <c r="AD4" s="76" t="s">
+      <c r="AD4" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="AE4" s="76" t="s">
+      <c r="AE4" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="AF4" s="76" t="s">
+      <c r="AF4" s="78" t="s">
         <v>200</v>
       </c>
-      <c r="AG4" s="76" t="s">
+      <c r="AG4" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="AH4" s="76" t="s">
+      <c r="AH4" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="AI4" s="80" t="s">
+      <c r="AI4" s="76" t="s">
         <v>167</v>
       </c>
-      <c r="AJ4" s="80" t="s">
+      <c r="AJ4" s="76" t="s">
         <v>168</v>
       </c>
-      <c r="AK4" s="80" t="s">
+      <c r="AK4" s="76" t="s">
         <v>169</v>
       </c>
-      <c r="AL4" s="80" t="s">
+      <c r="AL4" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="AM4" s="80" t="s">
+      <c r="AM4" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="AN4" s="76" t="s">
+      <c r="AN4" s="78" t="s">
         <v>171</v>
       </c>
-      <c r="AO4" s="80" t="s">
+      <c r="AO4" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="AP4" s="80" t="s">
+      <c r="AP4" s="76" t="s">
         <v>173</v>
       </c>
-      <c r="AQ4" s="76" t="s">
+      <c r="AQ4" s="78" t="s">
         <v>174</v>
       </c>
-      <c r="AR4" s="80" t="s">
+      <c r="AR4" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="AS4" s="76" t="s">
+      <c r="AS4" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="AT4" s="76" t="s">
+      <c r="AT4" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="AU4" s="76" t="s">
+      <c r="AU4" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="AV4" s="76" t="s">
+      <c r="AV4" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="AW4" s="76" t="s">
+      <c r="AW4" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="76" t="s">
+      <c r="AX4" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="AY4" s="76" t="s">
+      <c r="AY4" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="AZ4" s="76" t="s">
+      <c r="AZ4" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="BA4" s="76" t="s">
+      <c r="BA4" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="BB4" s="76" t="s">
+      <c r="BB4" s="78" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="76" t="s">
+      <c r="BC4" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="BD4" s="45" t="s">
+      <c r="BD4" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="BE4" s="45" t="s">
+      <c r="BE4" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="BF4" s="45" t="s">
+      <c r="BF4" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="BG4" s="45" t="s">
+      <c r="BG4" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="BH4" s="45" t="s">
+      <c r="BH4" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="BI4" s="45" t="s">
+      <c r="BI4" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="BJ4" s="45" t="s">
+      <c r="BJ4" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="BK4" s="45" t="s">
+      <c r="BK4" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="BL4" s="45" t="s">
+      <c r="BL4" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="BM4" s="45" t="s">
+      <c r="BM4" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="BN4" s="45" t="s">
+      <c r="BN4" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="BO4" s="45" t="s">
+      <c r="BO4" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="BP4" s="45" t="s">
+      <c r="BP4" s="55" t="s">
         <v>231</v>
       </c>
-      <c r="BQ4" s="45" t="s">
+      <c r="BQ4" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="BR4" s="45" t="s">
+      <c r="BR4" s="55" t="s">
         <v>233</v>
       </c>
-      <c r="BS4" s="45" t="s">
+      <c r="BS4" s="55" t="s">
         <v>234</v>
       </c>
-      <c r="BT4" s="45" t="s">
+      <c r="BT4" s="55" t="s">
         <v>235</v>
       </c>
-      <c r="BU4" s="57" t="s">
+      <c r="BU4" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="BV4" s="57" t="s">
+      <c r="BV4" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="BW4" s="57" t="s">
+      <c r="BW4" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="BX4" s="57" t="s">
+      <c r="BX4" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="BY4" s="57" t="s">
+      <c r="BY4" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="BZ4" s="57" t="s">
+      <c r="BZ4" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="CA4" s="45" t="s">
+      <c r="CA4" s="55" t="s">
         <v>236</v>
       </c>
-      <c r="CB4" s="45" t="s">
+      <c r="CB4" s="55" t="s">
         <v>237</v>
       </c>
-      <c r="CC4" s="45" t="s">
+      <c r="CC4" s="55" t="s">
         <v>238</v>
       </c>
-      <c r="CD4" s="45" t="s">
+      <c r="CD4" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="CE4" s="47" t="s">
+      <c r="CE4" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="CF4" s="47" t="s">
+      <c r="CF4" s="49" t="s">
         <v>255</v>
       </c>
-      <c r="CG4" s="47" t="s">
+      <c r="CG4" s="49" t="s">
         <v>257</v>
       </c>
-      <c r="CH4" s="47" t="s">
+      <c r="CH4" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="CI4" s="47" t="s">
+      <c r="CI4" s="49" t="s">
         <v>261</v>
       </c>
-      <c r="CJ4" s="47" t="s">
+      <c r="CJ4" s="49" t="s">
         <v>263</v>
       </c>
-      <c r="CK4" s="47" t="s">
+      <c r="CK4" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="CL4" s="47" t="s">
+      <c r="CL4" s="49" t="s">
         <v>267</v>
       </c>
-      <c r="CM4" s="47" t="s">
+      <c r="CM4" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="CN4" s="47" t="s">
+      <c r="CN4" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="CO4" s="47" t="s">
+      <c r="CO4" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="CP4" s="47" t="s">
+      <c r="CP4" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="CQ4" s="47" t="s">
+      <c r="CQ4" s="49" t="s">
         <v>277</v>
       </c>
-      <c r="CR4" s="47" t="s">
+      <c r="CR4" s="49" t="s">
         <v>283</v>
       </c>
-      <c r="CS4" s="47" t="s">
+      <c r="CS4" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="CT4" s="47" t="s">
+      <c r="CT4" s="49" t="s">
         <v>287</v>
       </c>
-      <c r="CU4" s="47" t="s">
+      <c r="CU4" s="49" t="s">
         <v>289</v>
       </c>
-      <c r="CV4" s="47" t="s">
+      <c r="CV4" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="CW4" s="47" t="s">
+      <c r="CW4" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="CX4" s="47" t="s">
+      <c r="CX4" s="49" t="s">
         <v>295</v>
       </c>
-      <c r="CY4" s="47" t="s">
+      <c r="CY4" s="49" t="s">
         <v>297</v>
       </c>
-      <c r="CZ4" s="47" t="s">
+      <c r="CZ4" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="DA4" s="47" t="s">
+      <c r="DA4" s="49" t="s">
         <v>300</v>
       </c>
-      <c r="DB4" s="47" t="s">
+      <c r="DB4" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="DC4" s="47" t="s">
+      <c r="DC4" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="DD4" s="69" t="s">
+      <c r="DD4" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="DE4" s="69" t="s">
+      <c r="DE4" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="DF4" s="69" t="s">
+      <c r="DF4" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="DG4" s="69" t="s">
+      <c r="DG4" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="DH4" s="69" t="s">
+      <c r="DH4" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="DI4" s="69" t="s">
+      <c r="DI4" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="DJ4" s="69" t="s">
+      <c r="DJ4" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="DK4" s="69" t="s">
+      <c r="DK4" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="DL4" s="69" t="s">
+      <c r="DL4" s="46" t="s">
         <v>329</v>
       </c>
-      <c r="DM4" s="77" t="s">
+      <c r="DM4" s="74" t="s">
         <v>331</v>
       </c>
-      <c r="DN4" s="69" t="s">
+      <c r="DN4" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="DO4" s="69" t="s">
+      <c r="DO4" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="DP4" s="69" t="s">
+      <c r="DP4" s="46" t="s">
         <v>337</v>
       </c>
-      <c r="DQ4" s="69" t="s">
+      <c r="DQ4" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="DR4" s="69" t="s">
+      <c r="DR4" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="DS4" s="69" t="s">
+      <c r="DS4" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="DT4" s="69" t="s">
+      <c r="DT4" s="46" t="s">
         <v>350</v>
       </c>
-      <c r="DU4" s="77" t="s">
+      <c r="DU4" s="74" t="s">
         <v>366</v>
       </c>
-      <c r="DV4" s="77" t="s">
+      <c r="DV4" s="74" t="s">
         <v>367</v>
       </c>
-      <c r="DW4" s="77" t="s">
+      <c r="DW4" s="74" t="s">
         <v>368</v>
       </c>
-      <c r="DX4" s="77" t="s">
+      <c r="DX4" s="74" t="s">
         <v>369</v>
       </c>
-      <c r="DY4" s="77" t="s">
+      <c r="DY4" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="DZ4" s="69" t="s">
+      <c r="DZ4" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="EA4" s="69" t="s">
+      <c r="EA4" s="46" t="s">
         <v>373</v>
       </c>
-      <c r="EB4" s="69" t="s">
+      <c r="EB4" s="46" t="s">
         <v>376</v>
       </c>
-      <c r="EC4" s="69" t="s">
+      <c r="EC4" s="46" t="s">
         <v>380</v>
       </c>
-      <c r="ED4" s="69" t="s">
+      <c r="ED4" s="46" t="s">
         <v>383</v>
       </c>
-      <c r="EE4" s="69" t="s">
+      <c r="EE4" s="46" t="s">
         <v>385</v>
       </c>
-      <c r="EF4" s="69" t="s">
+      <c r="EF4" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="EG4" s="69" t="s">
+      <c r="EG4" s="46" t="s">
         <v>388</v>
       </c>
-      <c r="EH4" s="69" t="s">
+      <c r="EH4" s="46" t="s">
         <v>390</v>
       </c>
-      <c r="EI4" s="69" t="s">
+      <c r="EI4" s="46" t="s">
         <v>392</v>
       </c>
-      <c r="EJ4" s="69" t="s">
+      <c r="EJ4" s="46" t="s">
         <v>396</v>
       </c>
-      <c r="EK4" s="69" t="s">
+      <c r="EK4" s="46" t="s">
         <v>397</v>
       </c>
-      <c r="EL4" s="69" t="s">
+      <c r="EL4" s="46" t="s">
         <v>399</v>
       </c>
-      <c r="EM4" s="69" t="s">
+      <c r="EM4" s="46" t="s">
         <v>401</v>
       </c>
-      <c r="EN4" s="69" t="s">
+      <c r="EN4" s="46" t="s">
         <v>403</v>
       </c>
-      <c r="EO4" s="69" t="s">
+      <c r="EO4" s="46" t="s">
         <v>406</v>
       </c>
-      <c r="EP4" s="69" t="s">
+      <c r="EP4" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="EQ4" s="69" t="s">
+      <c r="EQ4" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="ER4" s="69" t="s">
+      <c r="ER4" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="ES4" s="69" t="s">
+      <c r="ES4" s="46" t="s">
         <v>417</v>
       </c>
+      <c r="ET4" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
-    <row r="5" spans="2:149" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="63"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="81"/>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="81"/>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="81"/>
-      <c r="AP5" s="81"/>
-      <c r="AQ5" s="47"/>
-      <c r="AR5" s="81"/>
-      <c r="AS5" s="47"/>
-      <c r="AT5" s="47"/>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="47"/>
-      <c r="BA5" s="47"/>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="46"/>
-      <c r="BM5" s="46"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
-      <c r="BQ5" s="46"/>
-      <c r="BR5" s="46"/>
-      <c r="BS5" s="46"/>
-      <c r="BT5" s="46"/>
-      <c r="BU5" s="49"/>
-      <c r="BV5" s="49"/>
-      <c r="BW5" s="49"/>
-      <c r="BX5" s="49"/>
-      <c r="BY5" s="49"/>
-      <c r="BZ5" s="49"/>
-      <c r="CA5" s="46"/>
-      <c r="CB5" s="46"/>
-      <c r="CC5" s="46"/>
-      <c r="CD5" s="46"/>
-      <c r="CE5" s="48"/>
-      <c r="CF5" s="48"/>
-      <c r="CG5" s="48"/>
-      <c r="CH5" s="48"/>
-      <c r="CI5" s="48"/>
-      <c r="CJ5" s="48"/>
-      <c r="CK5" s="48"/>
-      <c r="CL5" s="48"/>
-      <c r="CM5" s="48"/>
-      <c r="CN5" s="48"/>
-      <c r="CO5" s="48"/>
-      <c r="CP5" s="48"/>
-      <c r="CQ5" s="48"/>
-      <c r="CR5" s="48"/>
-      <c r="CS5" s="48"/>
-      <c r="CT5" s="48"/>
-      <c r="CU5" s="48"/>
-      <c r="CV5" s="48"/>
-      <c r="CW5" s="48"/>
-      <c r="CX5" s="48"/>
-      <c r="CY5" s="48"/>
-      <c r="CZ5" s="48"/>
-      <c r="DA5" s="48"/>
-      <c r="DB5" s="48"/>
-      <c r="DC5" s="48"/>
-      <c r="DD5" s="48"/>
-      <c r="DE5" s="48"/>
-      <c r="DF5" s="48"/>
-      <c r="DG5" s="48"/>
-      <c r="DH5" s="48"/>
-      <c r="DI5" s="48"/>
-      <c r="DJ5" s="48"/>
-      <c r="DK5" s="48"/>
-      <c r="DL5" s="48"/>
-      <c r="DM5" s="78"/>
-      <c r="DN5" s="48"/>
-      <c r="DO5" s="48"/>
-      <c r="DP5" s="48"/>
-      <c r="DQ5" s="48"/>
-      <c r="DR5" s="48"/>
-      <c r="DS5" s="48"/>
-      <c r="DT5" s="48"/>
-      <c r="DU5" s="78"/>
-      <c r="DV5" s="78"/>
-      <c r="DW5" s="78"/>
-      <c r="DX5" s="78"/>
-      <c r="DY5" s="78"/>
-      <c r="DZ5" s="48"/>
-      <c r="EA5" s="48"/>
-      <c r="EB5" s="48"/>
-      <c r="EC5" s="48"/>
-      <c r="ED5" s="48"/>
-      <c r="EE5" s="69"/>
-      <c r="EF5" s="69"/>
-      <c r="EG5" s="69"/>
-      <c r="EH5" s="69"/>
-      <c r="EI5" s="69"/>
-      <c r="EJ5" s="69"/>
-      <c r="EK5" s="69"/>
-      <c r="EL5" s="69"/>
-      <c r="EM5" s="69"/>
-      <c r="EN5" s="69"/>
-      <c r="EO5" s="69"/>
-      <c r="EP5" s="69"/>
-      <c r="EQ5" s="69"/>
-      <c r="ER5" s="69"/>
-      <c r="ES5" s="69"/>
+    <row r="5" spans="2:150" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="67"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="77"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="49"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="77"/>
+      <c r="AJ5" s="77"/>
+      <c r="AK5" s="77"/>
+      <c r="AL5" s="77"/>
+      <c r="AM5" s="77"/>
+      <c r="AN5" s="49"/>
+      <c r="AO5" s="77"/>
+      <c r="AP5" s="77"/>
+      <c r="AQ5" s="49"/>
+      <c r="AR5" s="77"/>
+      <c r="AS5" s="49"/>
+      <c r="AT5" s="49"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
+      <c r="AW5" s="49"/>
+      <c r="AX5" s="49"/>
+      <c r="AY5" s="49"/>
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="49"/>
+      <c r="BC5" s="49"/>
+      <c r="BD5" s="56"/>
+      <c r="BE5" s="56"/>
+      <c r="BF5" s="56"/>
+      <c r="BG5" s="56"/>
+      <c r="BH5" s="56"/>
+      <c r="BI5" s="56"/>
+      <c r="BJ5" s="56"/>
+      <c r="BK5" s="56"/>
+      <c r="BL5" s="56"/>
+      <c r="BM5" s="56"/>
+      <c r="BN5" s="56"/>
+      <c r="BO5" s="56"/>
+      <c r="BP5" s="56"/>
+      <c r="BQ5" s="56"/>
+      <c r="BR5" s="56"/>
+      <c r="BS5" s="56"/>
+      <c r="BT5" s="56"/>
+      <c r="BU5" s="57"/>
+      <c r="BV5" s="57"/>
+      <c r="BW5" s="57"/>
+      <c r="BX5" s="57"/>
+      <c r="BY5" s="57"/>
+      <c r="BZ5" s="57"/>
+      <c r="CA5" s="56"/>
+      <c r="CB5" s="56"/>
+      <c r="CC5" s="56"/>
+      <c r="CD5" s="56"/>
+      <c r="CE5" s="47"/>
+      <c r="CF5" s="47"/>
+      <c r="CG5" s="47"/>
+      <c r="CH5" s="47"/>
+      <c r="CI5" s="47"/>
+      <c r="CJ5" s="47"/>
+      <c r="CK5" s="47"/>
+      <c r="CL5" s="47"/>
+      <c r="CM5" s="47"/>
+      <c r="CN5" s="47"/>
+      <c r="CO5" s="47"/>
+      <c r="CP5" s="47"/>
+      <c r="CQ5" s="47"/>
+      <c r="CR5" s="47"/>
+      <c r="CS5" s="47"/>
+      <c r="CT5" s="47"/>
+      <c r="CU5" s="47"/>
+      <c r="CV5" s="47"/>
+      <c r="CW5" s="47"/>
+      <c r="CX5" s="47"/>
+      <c r="CY5" s="47"/>
+      <c r="CZ5" s="47"/>
+      <c r="DA5" s="47"/>
+      <c r="DB5" s="47"/>
+      <c r="DC5" s="47"/>
+      <c r="DD5" s="47"/>
+      <c r="DE5" s="47"/>
+      <c r="DF5" s="47"/>
+      <c r="DG5" s="47"/>
+      <c r="DH5" s="47"/>
+      <c r="DI5" s="47"/>
+      <c r="DJ5" s="47"/>
+      <c r="DK5" s="47"/>
+      <c r="DL5" s="47"/>
+      <c r="DM5" s="75"/>
+      <c r="DN5" s="47"/>
+      <c r="DO5" s="47"/>
+      <c r="DP5" s="47"/>
+      <c r="DQ5" s="47"/>
+      <c r="DR5" s="47"/>
+      <c r="DS5" s="47"/>
+      <c r="DT5" s="47"/>
+      <c r="DU5" s="75"/>
+      <c r="DV5" s="75"/>
+      <c r="DW5" s="75"/>
+      <c r="DX5" s="75"/>
+      <c r="DY5" s="75"/>
+      <c r="DZ5" s="47"/>
+      <c r="EA5" s="47"/>
+      <c r="EB5" s="47"/>
+      <c r="EC5" s="47"/>
+      <c r="ED5" s="47"/>
+      <c r="EE5" s="46"/>
+      <c r="EF5" s="46"/>
+      <c r="EG5" s="46"/>
+      <c r="EH5" s="46"/>
+      <c r="EI5" s="46"/>
+      <c r="EJ5" s="46"/>
+      <c r="EK5" s="46"/>
+      <c r="EL5" s="46"/>
+      <c r="EM5" s="46"/>
+      <c r="EN5" s="46"/>
+      <c r="EO5" s="46"/>
+      <c r="EP5" s="46"/>
+      <c r="EQ5" s="46"/>
+      <c r="ER5" s="46"/>
+      <c r="ES5" s="46"/>
+      <c r="ET5" s="46"/>
     </row>
-    <row r="6" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -36068,8 +36240,11 @@
       <c r="ES6" s="28">
         <v>145</v>
       </c>
+      <c r="ET6" s="28">
+        <v>198</v>
+      </c>
     </row>
-    <row r="7" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -36514,8 +36689,11 @@
       <c r="ES7" s="15">
         <v>0</v>
       </c>
+      <c r="ET7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -36960,8 +37138,11 @@
       <c r="ES8" s="28">
         <v>22</v>
       </c>
+      <c r="ET8" s="28">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -37406,8 +37587,11 @@
       <c r="ES9" s="15">
         <v>82</v>
       </c>
+      <c r="ET9" s="15">
+        <v>63</v>
+      </c>
     </row>
-    <row r="10" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -37852,8 +38036,11 @@
       <c r="ES10" s="15">
         <v>0</v>
       </c>
+      <c r="ET10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -38298,8 +38485,11 @@
       <c r="ES11" s="15">
         <v>17</v>
       </c>
+      <c r="ET11" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="12" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -38744,8 +38934,11 @@
       <c r="ES12" s="15">
         <v>20</v>
       </c>
+      <c r="ET12" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="13" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -39190,8 +39383,11 @@
       <c r="ES13" s="15">
         <v>22</v>
       </c>
+      <c r="ET13" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="14" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -39636,8 +39832,11 @@
       <c r="ES14" s="15">
         <v>49</v>
       </c>
+      <c r="ET14" s="15">
+        <v>30</v>
+      </c>
     </row>
-    <row r="15" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -40082,8 +40281,11 @@
       <c r="ES15" s="15">
         <v>6</v>
       </c>
+      <c r="ET15" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -40528,8 +40730,11 @@
       <c r="ES16" s="28">
         <v>158</v>
       </c>
+      <c r="ET16" s="28">
+        <v>175</v>
+      </c>
     </row>
-    <row r="17" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -40974,8 +41179,11 @@
       <c r="ES17" s="15">
         <v>224</v>
       </c>
+      <c r="ET17" s="15">
+        <v>177</v>
+      </c>
     </row>
-    <row r="18" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -41420,9 +41628,12 @@
       <c r="ES18" s="34">
         <v>2149</v>
       </c>
+      <c r="ET18" s="34">
+        <v>2632</v>
+      </c>
     </row>
-    <row r="19" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="53" t="s">
+    <row r="19" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="70" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -41866,9 +42077,12 @@
       <c r="ES19" s="15">
         <v>83</v>
       </c>
+      <c r="ET19" s="15">
+        <v>133</v>
+      </c>
     </row>
-    <row r="20" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="53"/>
+    <row r="20" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -42310,9 +42524,12 @@
       <c r="ES20" s="28">
         <v>217</v>
       </c>
+      <c r="ET20" s="28">
+        <v>291</v>
+      </c>
     </row>
-    <row r="21" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="53"/>
+    <row r="21" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -42754,8 +42971,11 @@
       <c r="ES21" s="15">
         <v>49</v>
       </c>
+      <c r="ET21" s="15">
+        <v>45</v>
+      </c>
     </row>
-    <row r="22" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -43200,8 +43420,11 @@
       <c r="ES22" s="15">
         <v>8</v>
       </c>
+      <c r="ET22" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="23" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -43646,8 +43869,11 @@
       <c r="ES23" s="15">
         <v>2</v>
       </c>
+      <c r="ET23" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -44092,8 +44318,11 @@
       <c r="ES24" s="15">
         <v>22</v>
       </c>
+      <c r="ET24" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -44538,8 +44767,11 @@
       <c r="ES25" s="15">
         <v>0</v>
       </c>
+      <c r="ET25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -44984,8 +45216,11 @@
       <c r="ES26" s="15">
         <v>16</v>
       </c>
+      <c r="ET26" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="27" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -45430,8 +45665,11 @@
       <c r="ES27" s="15">
         <v>0</v>
       </c>
+      <c r="ET27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -45876,9 +46114,12 @@
       <c r="ES28" s="15">
         <v>0</v>
       </c>
+      <c r="ET28" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="29" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="54" t="s">
+    <row r="29" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -46322,9 +46563,12 @@
       <c r="ES29" s="15">
         <v>5</v>
       </c>
+      <c r="ET29" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="54"/>
+    <row r="30" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -46766,8 +47010,11 @@
       <c r="ES30" s="15">
         <v>17</v>
       </c>
+      <c r="ET30" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="31" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -47212,8 +47459,11 @@
       <c r="ES31" s="15">
         <v>56</v>
       </c>
+      <c r="ET31" s="15">
+        <v>44</v>
+      </c>
     </row>
-    <row r="32" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -47658,8 +47908,11 @@
       <c r="ES32" s="15">
         <v>4</v>
       </c>
+      <c r="ET32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -48104,8 +48357,11 @@
       <c r="ES33" s="15">
         <v>1</v>
       </c>
+      <c r="ET33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -48550,9 +48806,12 @@
       <c r="ES34" s="15">
         <v>89</v>
       </c>
+      <c r="ET34" s="15">
+        <v>108</v>
+      </c>
     </row>
-    <row r="35" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="53" t="s">
+    <row r="35" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="70" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -48996,9 +49255,12 @@
       <c r="ES35" s="15">
         <v>399</v>
       </c>
+      <c r="ET35" s="15">
+        <v>511</v>
+      </c>
     </row>
-    <row r="36" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="53"/>
+    <row r="36" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -49440,8 +49702,11 @@
       <c r="ES36" s="28">
         <v>40</v>
       </c>
+      <c r="ET36" s="28">
+        <v>55</v>
+      </c>
     </row>
-    <row r="37" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -49886,8 +50151,11 @@
       <c r="ES37" s="15">
         <v>54</v>
       </c>
+      <c r="ET37" s="15">
+        <v>88</v>
+      </c>
     </row>
-    <row r="38" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -50332,8 +50600,11 @@
       <c r="ES38" s="15">
         <v>13</v>
       </c>
+      <c r="ET38" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="39" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -50778,8 +51049,11 @@
       <c r="ES39" s="15">
         <v>23</v>
       </c>
+      <c r="ET39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -51224,8 +51498,11 @@
       <c r="ES40" s="15">
         <v>0</v>
       </c>
+      <c r="ET40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -51670,8 +51947,11 @@
       <c r="ES41" s="15">
         <v>0</v>
       </c>
+      <c r="ET41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -52116,8 +52396,11 @@
       <c r="ES42" s="15">
         <v>16</v>
       </c>
+      <c r="ET42" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -52562,8 +52845,11 @@
       <c r="ES43" s="28">
         <v>79</v>
       </c>
+      <c r="ET43" s="28">
+        <v>73</v>
+      </c>
     </row>
-    <row r="44" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -53008,8 +53294,11 @@
       <c r="ES44" s="15">
         <v>0</v>
       </c>
+      <c r="ET44" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="45" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -53454,8 +53743,11 @@
       <c r="ES45" s="15">
         <v>8</v>
       </c>
+      <c r="ET45" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -53900,8 +54192,11 @@
       <c r="ES46" s="15">
         <v>13</v>
       </c>
+      <c r="ET46" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="47" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -54346,8 +54641,11 @@
       <c r="ES47" s="15">
         <v>2</v>
       </c>
+      <c r="ET47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -54792,9 +55090,12 @@
       <c r="ES48" s="15">
         <v>13</v>
       </c>
+      <c r="ET48" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="49" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="53" t="s">
+    <row r="49" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="70" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -55238,9 +55539,12 @@
       <c r="ES49" s="15">
         <v>50</v>
       </c>
+      <c r="ET49" s="15">
+        <v>92</v>
+      </c>
     </row>
-    <row r="50" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="53"/>
+    <row r="50" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -55682,8 +55986,11 @@
       <c r="ES50" s="15">
         <v>10</v>
       </c>
+      <c r="ET50" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="51" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -56128,8 +56435,11 @@
       <c r="ES51" s="15">
         <v>2</v>
       </c>
+      <c r="ET51" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -56574,8 +56884,11 @@
       <c r="ES52" s="15">
         <v>24</v>
       </c>
+      <c r="ET52" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="53" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -57020,8 +57333,11 @@
       <c r="ES53" s="15">
         <v>37</v>
       </c>
+      <c r="ET53" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="54" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -57466,8 +57782,11 @@
       <c r="ES54" s="15">
         <v>15</v>
       </c>
+      <c r="ET54" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="55" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -57912,8 +58231,11 @@
       <c r="ES55" s="15">
         <v>19</v>
       </c>
+      <c r="ET55" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="56" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -58358,8 +58680,11 @@
       <c r="ES56" s="15">
         <v>0</v>
       </c>
+      <c r="ET56" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="57" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -58804,8 +59129,11 @@
       <c r="ES57" s="15">
         <v>5</v>
       </c>
+      <c r="ET57" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="2:149" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -59274,7 +59602,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:ES58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:ET58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -59393,100 +59721,61 @@
         <f t="shared" si="8"/>
         <v>4285</v>
       </c>
+      <c r="ET58" s="14">
+        <f t="shared" si="8"/>
+        <v>5065</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="163">
-    <mergeCell ref="DD2:ES2"/>
-    <mergeCell ref="ER3:ES3"/>
-    <mergeCell ref="ES4:ES5"/>
-    <mergeCell ref="DD3:EQ3"/>
-    <mergeCell ref="ER4:ER5"/>
-    <mergeCell ref="EP4:EP5"/>
-    <mergeCell ref="EO4:EO5"/>
-    <mergeCell ref="EF4:EF5"/>
-    <mergeCell ref="DK4:DK5"/>
-    <mergeCell ref="DH4:DH5"/>
-    <mergeCell ref="ED4:ED5"/>
-    <mergeCell ref="EN4:EN5"/>
-    <mergeCell ref="DN4:DN5"/>
-    <mergeCell ref="DT4:DT5"/>
-    <mergeCell ref="EC4:EC5"/>
-    <mergeCell ref="EI4:EI5"/>
-    <mergeCell ref="EH4:EH5"/>
-    <mergeCell ref="EQ4:EQ5"/>
-    <mergeCell ref="DJ4:DJ5"/>
+  <mergeCells count="164">
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="DY4:DY5"/>
+    <mergeCell ref="DW4:DW5"/>
+    <mergeCell ref="DU4:DU5"/>
+    <mergeCell ref="DE4:DE5"/>
+    <mergeCell ref="DF4:DF5"/>
+    <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="DD4:DD5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="DI4:DI5"/>
     <mergeCell ref="DR4:DR5"/>
     <mergeCell ref="DQ4:DQ5"/>
-    <mergeCell ref="EG4:EG5"/>
-    <mergeCell ref="DM4:DM5"/>
-    <mergeCell ref="DL4:DL5"/>
-    <mergeCell ref="DG4:DG5"/>
-    <mergeCell ref="EM4:EM5"/>
-    <mergeCell ref="EL4:EL5"/>
-    <mergeCell ref="EK4:EK5"/>
-    <mergeCell ref="EJ4:EJ5"/>
-    <mergeCell ref="CY4:CY5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="DC4:DC5"/>
-    <mergeCell ref="DX4:DX5"/>
-    <mergeCell ref="DZ4:DZ5"/>
-    <mergeCell ref="DP4:DP5"/>
-    <mergeCell ref="DO4:DO5"/>
-    <mergeCell ref="EE4:EE5"/>
-    <mergeCell ref="DS4:DS5"/>
-    <mergeCell ref="DV4:DV5"/>
-    <mergeCell ref="EB4:EB5"/>
-    <mergeCell ref="EA4:EA5"/>
-    <mergeCell ref="CR3:DC3"/>
-    <mergeCell ref="BD2:DC2"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="BF4:BF5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="D2:BC2"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BR4:BR5"/>
+    <mergeCell ref="BI4:BI5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BK4:BK5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="BT4:BT5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="AR3:BC3"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D3:AQ3"/>
     <mergeCell ref="X4:X5"/>
@@ -59511,54 +59800,98 @@
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="CA4:CA5"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="BI4:BI5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="BK4:BK5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="BJ4:BJ5"/>
-    <mergeCell ref="BT4:BT5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="BY4:BY5"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="DO4:DO5"/>
     <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="DY4:DY5"/>
-    <mergeCell ref="DW4:DW5"/>
-    <mergeCell ref="DU4:DU5"/>
-    <mergeCell ref="DE4:DE5"/>
-    <mergeCell ref="DF4:DF5"/>
-    <mergeCell ref="CX4:CX5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="DA4:DA5"/>
-    <mergeCell ref="CW4:CW5"/>
-    <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="DD4:DD5"/>
-    <mergeCell ref="CZ4:CZ5"/>
-    <mergeCell ref="DB4:DB5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CP4:CP5"/>
     <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="CL4:CL5"/>
     <mergeCell ref="CE4:CE5"/>
-    <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="EA4:EA5"/>
+    <mergeCell ref="CR3:DC3"/>
+    <mergeCell ref="BD2:DC2"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AV4:AV5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="BF4:BF5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="D2:BC2"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="DJ4:DJ5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="DM4:DM5"/>
+    <mergeCell ref="DL4:DL5"/>
+    <mergeCell ref="DG4:DG5"/>
+    <mergeCell ref="EM4:EM5"/>
+    <mergeCell ref="EL4:EL5"/>
+    <mergeCell ref="EK4:EK5"/>
+    <mergeCell ref="EJ4:EJ5"/>
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CF4:CF5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="DX4:DX5"/>
+    <mergeCell ref="DZ4:DZ5"/>
+    <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="EG4:EG5"/>
+    <mergeCell ref="EE4:EE5"/>
+    <mergeCell ref="DS4:DS5"/>
+    <mergeCell ref="DV4:DV5"/>
+    <mergeCell ref="EB4:EB5"/>
+    <mergeCell ref="DD2:ET2"/>
+    <mergeCell ref="ER3:ET3"/>
+    <mergeCell ref="ET4:ET5"/>
+    <mergeCell ref="ES4:ES5"/>
+    <mergeCell ref="DD3:EQ3"/>
+    <mergeCell ref="ER4:ER5"/>
+    <mergeCell ref="EP4:EP5"/>
+    <mergeCell ref="EO4:EO5"/>
+    <mergeCell ref="EF4:EF5"/>
+    <mergeCell ref="DK4:DK5"/>
+    <mergeCell ref="DH4:DH5"/>
+    <mergeCell ref="ED4:ED5"/>
+    <mergeCell ref="EN4:EN5"/>
+    <mergeCell ref="DN4:DN5"/>
+    <mergeCell ref="DT4:DT5"/>
+    <mergeCell ref="EC4:EC5"/>
+    <mergeCell ref="EI4:EI5"/>
+    <mergeCell ref="EH4:EH5"/>
+    <mergeCell ref="EQ4:EQ5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -59571,7 +59904,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:ES57">
+  <conditionalFormatting sqref="EH6:ET57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -59611,7 +59944,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS61"/>
+  <dimension ref="A1:CT61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -59622,11 +59955,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="97" width="10.875" style="1" customWidth="1"/>
-    <col min="98" max="16384" width="8.625" style="1"/>
+    <col min="54" max="98" width="10.875" style="1" customWidth="1"/>
+    <col min="99" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:97" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:98" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -59698,607 +60031,614 @@
       <c r="CP1" s="19"/>
       <c r="CQ1" s="19"/>
       <c r="CR1" s="19"/>
-      <c r="CS1" s="19" t="s">
+      <c r="CS1" s="19"/>
+      <c r="CT1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:97" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="67" t="s">
+    <row r="2" spans="1:98" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="59" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="68"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-      <c r="AM2" s="68"/>
-      <c r="AN2" s="68"/>
-      <c r="AO2" s="68"/>
-      <c r="AP2" s="68"/>
-      <c r="AQ2" s="68"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="68"/>
-      <c r="AV2" s="68"/>
-      <c r="AW2" s="68"/>
-      <c r="AX2" s="68"/>
-      <c r="AY2" s="68"/>
-      <c r="AZ2" s="68"/>
-      <c r="BA2" s="68"/>
-      <c r="BB2" s="68"/>
-      <c r="BC2" s="71"/>
-      <c r="BD2" s="85" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="52"/>
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="88"/>
+      <c r="BD2" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="85"/>
-      <c r="BF2" s="85"/>
-      <c r="BG2" s="85"/>
-      <c r="BH2" s="85"/>
-      <c r="BI2" s="85"/>
-      <c r="BJ2" s="85"/>
-      <c r="BK2" s="85"/>
-      <c r="BL2" s="85"/>
-      <c r="BM2" s="85"/>
-      <c r="BN2" s="85"/>
-      <c r="BO2" s="85"/>
-      <c r="BP2" s="85"/>
-      <c r="BQ2" s="85"/>
-      <c r="BR2" s="85"/>
-      <c r="BS2" s="85"/>
-      <c r="BT2" s="85"/>
-      <c r="BU2" s="85"/>
-      <c r="BV2" s="85"/>
-      <c r="BW2" s="85"/>
-      <c r="BX2" s="85"/>
-      <c r="BY2" s="85"/>
-      <c r="BZ2" s="85"/>
-      <c r="CA2" s="85"/>
-      <c r="CB2" s="85"/>
-      <c r="CC2" s="85"/>
-      <c r="CD2" s="85"/>
-      <c r="CE2" s="85"/>
-      <c r="CF2" s="85"/>
-      <c r="CG2" s="85"/>
-      <c r="CH2" s="85"/>
-      <c r="CI2" s="85"/>
-      <c r="CJ2" s="85"/>
-      <c r="CK2" s="85"/>
-      <c r="CL2" s="85"/>
-      <c r="CM2" s="85"/>
-      <c r="CN2" s="85"/>
-      <c r="CO2" s="85"/>
-      <c r="CP2" s="85"/>
-      <c r="CQ2" s="85"/>
-      <c r="CR2" s="85"/>
-      <c r="CS2" s="85"/>
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
     </row>
-    <row r="3" spans="1:97" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82" t="s">
+    <row r="3" spans="1:98" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="82"/>
-      <c r="AL3" s="82"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="82"/>
-      <c r="AO3" s="82"/>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="64" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="81"/>
+      <c r="AH3" s="81"/>
+      <c r="AI3" s="81"/>
+      <c r="AJ3" s="81"/>
+      <c r="AK3" s="81"/>
+      <c r="AL3" s="81"/>
+      <c r="AM3" s="81"/>
+      <c r="AN3" s="81"/>
+      <c r="AO3" s="81"/>
+      <c r="AP3" s="81"/>
+      <c r="AQ3" s="81"/>
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="64"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="64"/>
-      <c r="AY3" s="64"/>
-      <c r="AZ3" s="64"/>
-      <c r="BA3" s="64"/>
-      <c r="BB3" s="64"/>
-      <c r="BC3" s="64"/>
-      <c r="BD3" s="86" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="87"/>
-      <c r="BF3" s="87"/>
-      <c r="BG3" s="87"/>
-      <c r="BH3" s="87"/>
-      <c r="BI3" s="87"/>
-      <c r="BJ3" s="87"/>
-      <c r="BK3" s="87"/>
-      <c r="BL3" s="87"/>
-      <c r="BM3" s="87"/>
-      <c r="BN3" s="87"/>
-      <c r="BO3" s="87"/>
-      <c r="BP3" s="87"/>
-      <c r="BQ3" s="87"/>
-      <c r="BR3" s="87"/>
-      <c r="BS3" s="87"/>
-      <c r="BT3" s="87"/>
-      <c r="BU3" s="87"/>
-      <c r="BV3" s="87"/>
-      <c r="BW3" s="87"/>
-      <c r="BX3" s="87"/>
-      <c r="BY3" s="87"/>
-      <c r="BZ3" s="87"/>
-      <c r="CA3" s="87"/>
-      <c r="CB3" s="87"/>
-      <c r="CC3" s="87"/>
-      <c r="CD3" s="87"/>
-      <c r="CE3" s="87"/>
-      <c r="CF3" s="87"/>
-      <c r="CG3" s="87"/>
-      <c r="CH3" s="87"/>
-      <c r="CI3" s="87"/>
-      <c r="CJ3" s="87"/>
-      <c r="CK3" s="87"/>
-      <c r="CL3" s="87"/>
-      <c r="CM3" s="87"/>
-      <c r="CN3" s="87"/>
-      <c r="CO3" s="87"/>
-      <c r="CP3" s="87"/>
-      <c r="CQ3" s="88"/>
-      <c r="CR3" s="64" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="64"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
     </row>
-    <row r="4" spans="1:97" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="45" t="s">
+    <row r="4" spans="1:98" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="55" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="55" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="45" t="s">
+      <c r="K4" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="L4" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="55" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="N4" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="45" t="s">
+      <c r="P4" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="45" t="s">
+      <c r="Q4" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="45" t="s">
+      <c r="R4" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="55" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="45" t="s">
+      <c r="T4" s="55" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="45" t="s">
+      <c r="U4" s="55" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="45" t="s">
+      <c r="W4" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="45" t="s">
+      <c r="X4" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="45" t="s">
+      <c r="Y4" s="55" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="45" t="s">
+      <c r="Z4" s="55" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="45" t="s">
+      <c r="AA4" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="45" t="s">
+      <c r="AC4" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="45" t="s">
+      <c r="AD4" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="47" t="s">
+      <c r="AE4" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="47" t="s">
+      <c r="AF4" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="47" t="s">
+      <c r="AG4" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="47" t="s">
+      <c r="AH4" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="47" t="s">
+      <c r="AI4" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="47" t="s">
+      <c r="AJ4" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="47" t="s">
+      <c r="AK4" s="49" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="47" t="s">
+      <c r="AL4" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="47" t="s">
+      <c r="AM4" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="47" t="s">
+      <c r="AN4" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="47" t="s">
+      <c r="AO4" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="47" t="s">
+      <c r="AP4" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="47" t="s">
+      <c r="AQ4" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="47" t="s">
+      <c r="AR4" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="47" t="s">
+      <c r="AS4" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="47" t="s">
+      <c r="AT4" s="49" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="47" t="s">
+      <c r="AU4" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="47" t="s">
+      <c r="AV4" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="47" t="s">
+      <c r="AW4" s="49" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="47" t="s">
+      <c r="AX4" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="47" t="s">
+      <c r="AY4" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="47" t="s">
+      <c r="AZ4" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="47" t="s">
+      <c r="BA4" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="47" t="s">
+      <c r="BB4" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="47" t="s">
+      <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="69" t="s">
+      <c r="BD4" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="69" t="s">
+      <c r="BE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="69" t="s">
+      <c r="BF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="69" t="s">
+      <c r="BG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="69" t="s">
+      <c r="BH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="69" t="s">
+      <c r="BI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="69" t="s">
+      <c r="BJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="69" t="s">
+      <c r="BK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="69" t="s">
+      <c r="BL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="69" t="s">
+      <c r="BM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="69" t="s">
+      <c r="BN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="69" t="s">
+      <c r="BO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="69" t="s">
+      <c r="BP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="69" t="s">
+      <c r="BQ4" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="69" t="s">
+      <c r="BR4" s="46" t="s">
         <v>343</v>
       </c>
-      <c r="BS4" s="69" t="s">
+      <c r="BS4" s="46" t="s">
         <v>347</v>
       </c>
-      <c r="BT4" s="69" t="s">
+      <c r="BT4" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="69" t="s">
+      <c r="BU4" s="46" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="69" t="s">
+      <c r="BV4" s="46" t="s">
         <v>355</v>
       </c>
-      <c r="BW4" s="69" t="s">
+      <c r="BW4" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="69" t="s">
+      <c r="BX4" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="69" t="s">
+      <c r="BY4" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="69" t="s">
+      <c r="BZ4" s="46" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="69" t="s">
+      <c r="CA4" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="69" t="s">
+      <c r="CB4" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="69" t="s">
+      <c r="CC4" s="46" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="69" t="s">
+      <c r="CD4" s="46" t="s">
         <v>382</v>
       </c>
-      <c r="CE4" s="69" t="s">
+      <c r="CE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="69" t="s">
+      <c r="CF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="69" t="s">
+      <c r="CG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="69" t="s">
+      <c r="CH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="69" t="s">
+      <c r="CI4" s="46" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="69" t="s">
+      <c r="CJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="69" t="s">
+      <c r="CK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="69" t="s">
+      <c r="CL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="69" t="s">
+      <c r="CM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="69" t="s">
+      <c r="CN4" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="CO4" s="69" t="s">
+      <c r="CO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="69" t="s">
+      <c r="CP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="69" t="s">
+      <c r="CQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="69" t="s">
+      <c r="CR4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="69" t="s">
+      <c r="CS4" s="46" t="s">
         <v>416</v>
       </c>
+      <c r="CT4" s="46" t="s">
+        <v>418</v>
+      </c>
     </row>
-    <row r="5" spans="1:97" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="63"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-      <c r="Y5" s="46"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
-      <c r="BD5" s="48"/>
-      <c r="BE5" s="48"/>
-      <c r="BF5" s="48"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
-      <c r="BJ5" s="48"/>
-      <c r="BK5" s="48"/>
-      <c r="BL5" s="48"/>
-      <c r="BM5" s="48"/>
-      <c r="BN5" s="48"/>
-      <c r="BO5" s="48"/>
-      <c r="BP5" s="48"/>
-      <c r="BQ5" s="48"/>
-      <c r="BR5" s="48"/>
-      <c r="BS5" s="48"/>
-      <c r="BT5" s="48"/>
-      <c r="BU5" s="48"/>
-      <c r="BV5" s="48"/>
-      <c r="BW5" s="48"/>
-      <c r="BX5" s="48"/>
-      <c r="BY5" s="48"/>
-      <c r="BZ5" s="69"/>
-      <c r="CA5" s="69"/>
-      <c r="CB5" s="69"/>
-      <c r="CC5" s="69"/>
-      <c r="CD5" s="69"/>
-      <c r="CE5" s="69"/>
-      <c r="CF5" s="69"/>
-      <c r="CG5" s="69"/>
-      <c r="CH5" s="69"/>
-      <c r="CI5" s="69"/>
-      <c r="CJ5" s="69"/>
-      <c r="CK5" s="69"/>
-      <c r="CL5" s="69"/>
-      <c r="CM5" s="69"/>
-      <c r="CN5" s="69"/>
-      <c r="CO5" s="69"/>
-      <c r="CP5" s="69"/>
-      <c r="CQ5" s="69"/>
-      <c r="CR5" s="69"/>
-      <c r="CS5" s="69"/>
+    <row r="5" spans="1:98" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="67"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="47"/>
+      <c r="BO5" s="47"/>
+      <c r="BP5" s="47"/>
+      <c r="BQ5" s="47"/>
+      <c r="BR5" s="47"/>
+      <c r="BS5" s="47"/>
+      <c r="BT5" s="47"/>
+      <c r="BU5" s="47"/>
+      <c r="BV5" s="47"/>
+      <c r="BW5" s="47"/>
+      <c r="BX5" s="47"/>
+      <c r="BY5" s="47"/>
+      <c r="BZ5" s="46"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
     </row>
-    <row r="6" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -60588,8 +60928,11 @@
       <c r="CS6" s="28">
         <v>34</v>
       </c>
+      <c r="CT6" s="28">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -60878,8 +61221,11 @@
       <c r="CS7" s="15">
         <v>1</v>
       </c>
+      <c r="CT7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -61168,8 +61514,11 @@
       <c r="CS8" s="28">
         <v>1</v>
       </c>
+      <c r="CT8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -61459,8 +61808,11 @@
       <c r="CS9" s="15">
         <v>28</v>
       </c>
+      <c r="CT9" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="10" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -61749,8 +62101,11 @@
       <c r="CS10" s="15">
         <v>3</v>
       </c>
+      <c r="CT10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -62039,8 +62394,11 @@
       <c r="CS11" s="15">
         <v>5</v>
       </c>
+      <c r="CT11" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="12" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -62329,8 +62687,11 @@
       <c r="CS12" s="15">
         <v>6</v>
       </c>
+      <c r="CT12" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -62619,8 +62980,11 @@
       <c r="CS13" s="15">
         <v>22</v>
       </c>
+      <c r="CT13" s="15">
+        <v>31</v>
+      </c>
     </row>
-    <row r="14" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -62909,8 +63273,11 @@
       <c r="CS14" s="15">
         <v>24</v>
       </c>
+      <c r="CT14" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="15" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -63199,8 +63566,11 @@
       <c r="CS15" s="15">
         <v>9</v>
       </c>
+      <c r="CT15" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -63490,8 +63860,11 @@
       <c r="CS16" s="28">
         <v>27</v>
       </c>
+      <c r="CT16" s="28">
+        <v>12</v>
+      </c>
     </row>
-    <row r="17" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -63780,8 +64153,11 @@
       <c r="CS17" s="15">
         <v>70</v>
       </c>
+      <c r="CT17" s="15">
+        <v>56</v>
+      </c>
     </row>
-    <row r="18" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -64071,10 +64447,13 @@
       <c r="CS18" s="34">
         <v>777</v>
       </c>
+      <c r="CT18" s="34">
+        <v>502</v>
+      </c>
     </row>
-    <row r="19" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="83" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -64362,10 +64741,13 @@
       <c r="CS19" s="15">
         <v>90</v>
       </c>
+      <c r="CT19" s="15">
+        <v>75</v>
+      </c>
     </row>
-    <row r="20" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -64651,10 +65033,13 @@
       <c r="CS20" s="28">
         <v>242</v>
       </c>
+      <c r="CT20" s="28">
+        <v>148</v>
+      </c>
     </row>
-    <row r="21" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="90"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -64940,8 +65325,11 @@
       <c r="CS21" s="15">
         <v>26</v>
       </c>
+      <c r="CT21" s="15">
+        <v>34</v>
+      </c>
     </row>
-    <row r="22" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -65230,8 +65618,11 @@
       <c r="CS22" s="15">
         <v>6</v>
       </c>
+      <c r="CT22" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -65520,8 +65911,11 @@
       <c r="CS23" s="15">
         <v>2</v>
       </c>
+      <c r="CT23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -65810,8 +66204,11 @@
       <c r="CS24" s="15">
         <v>9</v>
       </c>
+      <c r="CT24" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -66100,8 +66497,11 @@
       <c r="CS25" s="15">
         <v>3</v>
       </c>
+      <c r="CT25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -66390,8 +66790,11 @@
       <c r="CS26" s="15">
         <v>14</v>
       </c>
+      <c r="CT26" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="27" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -66680,8 +67083,11 @@
       <c r="CS27" s="15">
         <v>3</v>
       </c>
+      <c r="CT27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -66970,9 +67376,12 @@
       <c r="CS28" s="15">
         <v>3</v>
       </c>
+      <c r="CT28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="91" t="s">
+    <row r="29" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -67260,9 +67669,12 @@
       <c r="CS29" s="15">
         <v>6</v>
       </c>
+      <c r="CT29" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="92"/>
+    <row r="30" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -67548,8 +67960,11 @@
       <c r="CS30" s="15">
         <v>40</v>
       </c>
+      <c r="CT30" s="15">
+        <v>34</v>
+      </c>
     </row>
-    <row r="31" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -67839,8 +68254,11 @@
       <c r="CS31" s="15">
         <v>133</v>
       </c>
+      <c r="CT31" s="15">
+        <v>94</v>
+      </c>
     </row>
-    <row r="32" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -68129,8 +68547,11 @@
       <c r="CS32" s="15">
         <v>3</v>
       </c>
+      <c r="CT32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -68419,8 +68840,11 @@
       <c r="CS33" s="15">
         <v>0</v>
       </c>
+      <c r="CT33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -68710,10 +69134,13 @@
       <c r="CS34" s="15">
         <v>64</v>
       </c>
+      <c r="CT34" s="15">
+        <v>56</v>
+      </c>
     </row>
-    <row r="35" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="89" t="s">
+      <c r="B35" s="83" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -69001,9 +69428,12 @@
       <c r="CS35" s="15">
         <v>120</v>
       </c>
+      <c r="CT35" s="15">
+        <v>147</v>
+      </c>
     </row>
-    <row r="36" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="90"/>
+    <row r="36" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -69289,8 +69719,11 @@
       <c r="CS36" s="28">
         <v>78</v>
       </c>
+      <c r="CT36" s="28">
+        <v>39</v>
+      </c>
     </row>
-    <row r="37" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -69580,8 +70013,11 @@
       <c r="CS37" s="15">
         <v>55</v>
       </c>
+      <c r="CT37" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="38" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -69870,8 +70306,11 @@
       <c r="CS38" s="15">
         <v>17</v>
       </c>
+      <c r="CT38" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="39" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -70160,8 +70599,11 @@
       <c r="CS39" s="15">
         <v>13</v>
       </c>
+      <c r="CT39" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="40" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -70450,8 +70892,11 @@
       <c r="CS40" s="15">
         <v>0</v>
       </c>
+      <c r="CT40" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -70740,8 +71185,11 @@
       <c r="CS41" s="15">
         <v>0</v>
       </c>
+      <c r="CT41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -71030,8 +71478,11 @@
       <c r="CS42" s="15">
         <v>50</v>
       </c>
+      <c r="CT42" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="43" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -71320,8 +71771,11 @@
       <c r="CS43" s="28">
         <v>70</v>
       </c>
+      <c r="CT43" s="28">
+        <v>54</v>
+      </c>
     </row>
-    <row r="44" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -71610,8 +72064,11 @@
       <c r="CS44" s="15">
         <v>3</v>
       </c>
+      <c r="CT44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -71900,8 +72357,11 @@
       <c r="CS45" s="15">
         <v>14</v>
       </c>
+      <c r="CT45" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="46" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -72190,8 +72650,11 @@
       <c r="CS46" s="15">
         <v>26</v>
       </c>
+      <c r="CT46" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="47" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -72480,8 +72943,11 @@
       <c r="CS47" s="15">
         <v>1</v>
       </c>
+      <c r="CT47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -72770,10 +73236,13 @@
       <c r="CS48" s="15">
         <v>20</v>
       </c>
+      <c r="CT48" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="49" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="89" t="s">
+      <c r="B49" s="83" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -73061,9 +73530,12 @@
       <c r="CS49" s="15">
         <v>59</v>
       </c>
+      <c r="CT49" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="50" spans="1:97" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="90"/>
+    <row r="50" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -73349,8 +73821,11 @@
       <c r="CS50" s="15">
         <v>78</v>
       </c>
+      <c r="CT50" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="51" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -73639,8 +74114,11 @@
       <c r="CS51" s="15">
         <v>1</v>
       </c>
+      <c r="CT51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -73929,8 +74407,11 @@
       <c r="CS52" s="15">
         <v>14</v>
       </c>
+      <c r="CT52" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -74219,8 +74700,11 @@
       <c r="CS53" s="15">
         <v>49</v>
       </c>
+      <c r="CT53" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="54" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -74509,8 +74993,11 @@
       <c r="CS54" s="15">
         <v>12</v>
       </c>
+      <c r="CT54" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -74799,8 +75286,11 @@
       <c r="CS55" s="15">
         <v>7</v>
       </c>
+      <c r="CT55" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="56" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -75089,8 +75579,11 @@
       <c r="CS56" s="15">
         <v>0</v>
       </c>
+      <c r="CT56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -75379,8 +75872,11 @@
       <c r="CS57" s="15">
         <v>2</v>
       </c>
+      <c r="CT57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -75650,7 +76146,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CS58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CT58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -75761,8 +76257,12 @@
         <f t="shared" si="8"/>
         <v>2340</v>
       </c>
+      <c r="CT58" s="14">
+        <f t="shared" si="8"/>
+        <v>1591</v>
+      </c>
     </row>
-    <row r="59" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -75795,7 +76295,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -75828,7 +76328,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:97" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -75862,42 +76362,55 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="107">
-    <mergeCell ref="BD2:CS2"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BF4:BF5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CP4:CP5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="CA4:CA5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="BX4:BX5"/>
+  <mergeCells count="108">
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D2:BC2"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="D3:AQ3"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AR3:BC3"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="AS4:AS5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="AV4:AV5"/>
@@ -75922,57 +76435,45 @@
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D2:BC2"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="D3:AQ3"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="CH4:CH5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="BD2:CT2"/>
+    <mergeCell ref="CR3:CT3"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BF4:BF5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="CF4:CF5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AL4:AL5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CS57">
+  <conditionalFormatting sqref="CH6:CT57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -75981,7 +76482,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="97" max="66" man="1"/>
+    <brk id="98" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -75998,7 +76499,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CS57</xm:sqref>
+          <xm:sqref>BP6:CT57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -76011,7 +76512,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CX61"/>
+  <dimension ref="A1:CY61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -76020,11 +76521,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="102" width="10.875" style="1" customWidth="1"/>
-    <col min="103" max="16384" width="8.625" style="1"/>
+    <col min="34" max="103" width="10.875" style="1" customWidth="1"/>
+    <col min="104" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:103" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -76096,627 +76597,635 @@
       <c r="CP1" s="19"/>
       <c r="CQ1" s="19"/>
       <c r="CR1" s="19"/>
-      <c r="CS1" s="19" t="s">
+      <c r="CS1" s="19"/>
+      <c r="CT1" s="19" t="s">
         <v>290</v>
       </c>
+      <c r="CU1" s="19"/>
     </row>
-    <row r="2" spans="1:102" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="67" t="s">
+    <row r="2" spans="1:103" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="59" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="68"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-      <c r="AM2" s="68"/>
-      <c r="AN2" s="68"/>
-      <c r="AO2" s="68"/>
-      <c r="AP2" s="68"/>
-      <c r="AQ2" s="68"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="68"/>
-      <c r="AV2" s="68"/>
-      <c r="AW2" s="68"/>
-      <c r="AX2" s="68"/>
-      <c r="AY2" s="68"/>
-      <c r="AZ2" s="68"/>
-      <c r="BA2" s="68"/>
-      <c r="BB2" s="68"/>
-      <c r="BC2" s="71"/>
-      <c r="BD2" s="85" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="52"/>
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="88"/>
+      <c r="BD2" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="85"/>
-      <c r="BF2" s="85"/>
-      <c r="BG2" s="85"/>
-      <c r="BH2" s="85"/>
-      <c r="BI2" s="85"/>
-      <c r="BJ2" s="85"/>
-      <c r="BK2" s="85"/>
-      <c r="BL2" s="85"/>
-      <c r="BM2" s="85"/>
-      <c r="BN2" s="85"/>
-      <c r="BO2" s="85"/>
-      <c r="BP2" s="85"/>
-      <c r="BQ2" s="85"/>
-      <c r="BR2" s="85"/>
-      <c r="BS2" s="85"/>
-      <c r="BT2" s="85"/>
-      <c r="BU2" s="85"/>
-      <c r="BV2" s="85"/>
-      <c r="BW2" s="85"/>
-      <c r="BX2" s="85"/>
-      <c r="BY2" s="85"/>
-      <c r="BZ2" s="85"/>
-      <c r="CA2" s="85"/>
-      <c r="CB2" s="85"/>
-      <c r="CC2" s="85"/>
-      <c r="CD2" s="85"/>
-      <c r="CE2" s="85"/>
-      <c r="CF2" s="85"/>
-      <c r="CG2" s="85"/>
-      <c r="CH2" s="85"/>
-      <c r="CI2" s="85"/>
-      <c r="CJ2" s="85"/>
-      <c r="CK2" s="85"/>
-      <c r="CL2" s="85"/>
-      <c r="CM2" s="85"/>
-      <c r="CN2" s="85"/>
-      <c r="CO2" s="85"/>
-      <c r="CP2" s="85"/>
-      <c r="CQ2" s="85"/>
-      <c r="CR2" s="85"/>
-      <c r="CS2" s="85"/>
-      <c r="CT2" s="20"/>
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
       <c r="CU2" s="20"/>
       <c r="CV2" s="20"/>
       <c r="CW2" s="20"/>
       <c r="CX2" s="20"/>
+      <c r="CY2" s="20"/>
     </row>
-    <row r="3" spans="1:102" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82" t="s">
+    <row r="3" spans="1:103" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AI3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="82"/>
-      <c r="AL3" s="82"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="82"/>
-      <c r="AO3" s="82"/>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="64" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="81"/>
+      <c r="AH3" s="81"/>
+      <c r="AI3" s="81"/>
+      <c r="AJ3" s="81"/>
+      <c r="AK3" s="81"/>
+      <c r="AL3" s="81"/>
+      <c r="AM3" s="81"/>
+      <c r="AN3" s="81"/>
+      <c r="AO3" s="81"/>
+      <c r="AP3" s="81"/>
+      <c r="AQ3" s="81"/>
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="64"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="64"/>
-      <c r="AY3" s="64"/>
-      <c r="AZ3" s="64"/>
-      <c r="BA3" s="64"/>
-      <c r="BB3" s="64"/>
-      <c r="BC3" s="64"/>
-      <c r="BD3" s="86" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="87"/>
-      <c r="BF3" s="87"/>
-      <c r="BG3" s="87"/>
-      <c r="BH3" s="87"/>
-      <c r="BI3" s="87"/>
-      <c r="BJ3" s="87"/>
-      <c r="BK3" s="87"/>
-      <c r="BL3" s="87"/>
-      <c r="BM3" s="87"/>
-      <c r="BN3" s="87"/>
-      <c r="BO3" s="87"/>
-      <c r="BP3" s="87"/>
-      <c r="BQ3" s="87"/>
-      <c r="BR3" s="87"/>
-      <c r="BS3" s="87"/>
-      <c r="BT3" s="87"/>
-      <c r="BU3" s="87"/>
-      <c r="BV3" s="87"/>
-      <c r="BW3" s="87"/>
-      <c r="BX3" s="87"/>
-      <c r="BY3" s="87"/>
-      <c r="BZ3" s="87"/>
-      <c r="CA3" s="87"/>
-      <c r="CB3" s="87"/>
-      <c r="CC3" s="87"/>
-      <c r="CD3" s="87"/>
-      <c r="CE3" s="87"/>
-      <c r="CF3" s="87"/>
-      <c r="CG3" s="87"/>
-      <c r="CH3" s="87"/>
-      <c r="CI3" s="87"/>
-      <c r="CJ3" s="87"/>
-      <c r="CK3" s="87"/>
-      <c r="CL3" s="87"/>
-      <c r="CM3" s="87"/>
-      <c r="CN3" s="87"/>
-      <c r="CO3" s="87"/>
-      <c r="CP3" s="87"/>
-      <c r="CQ3" s="88"/>
-      <c r="CR3" s="65" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="70"/>
-      <c r="CT3" s="21"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
       <c r="CU3" s="21"/>
       <c r="CV3" s="21"/>
       <c r="CW3" s="21"/>
       <c r="CX3" s="21"/>
+      <c r="CY3" s="21"/>
     </row>
-    <row r="4" spans="1:102" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="45" t="s">
+    <row r="4" spans="1:103" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="55" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="55" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="45" t="s">
+      <c r="K4" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="L4" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="55" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="N4" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="45" t="s">
+      <c r="P4" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="45" t="s">
+      <c r="Q4" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="45" t="s">
+      <c r="R4" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="55" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="45" t="s">
+      <c r="T4" s="55" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="45" t="s">
+      <c r="U4" s="55" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="45" t="s">
+      <c r="W4" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="45" t="s">
+      <c r="X4" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="45" t="s">
+      <c r="Y4" s="55" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="45" t="s">
+      <c r="Z4" s="55" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="45" t="s">
+      <c r="AA4" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="45" t="s">
+      <c r="AC4" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="45" t="s">
+      <c r="AD4" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="47" t="s">
+      <c r="AE4" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="47" t="s">
+      <c r="AF4" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="47" t="s">
+      <c r="AG4" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="47" t="s">
+      <c r="AH4" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="47" t="s">
+      <c r="AI4" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="47" t="s">
+      <c r="AJ4" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="47" t="s">
+      <c r="AK4" s="49" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="47" t="s">
+      <c r="AL4" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="47" t="s">
+      <c r="AM4" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="47" t="s">
+      <c r="AN4" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="47" t="s">
+      <c r="AO4" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="47" t="s">
+      <c r="AP4" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="47" t="s">
+      <c r="AQ4" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="47" t="s">
+      <c r="AR4" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="47" t="s">
+      <c r="AS4" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="47" t="s">
+      <c r="AT4" s="49" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="47" t="s">
+      <c r="AU4" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="47" t="s">
+      <c r="AV4" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="47" t="s">
+      <c r="AW4" s="49" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="47" t="s">
+      <c r="AX4" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="47" t="s">
+      <c r="AY4" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="47" t="s">
+      <c r="AZ4" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="47" t="s">
+      <c r="BA4" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="47" t="s">
+      <c r="BB4" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="47" t="s">
+      <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="69" t="s">
+      <c r="BD4" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="69" t="s">
+      <c r="BE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="69" t="s">
+      <c r="BF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="69" t="s">
+      <c r="BG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="69" t="s">
+      <c r="BH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="69" t="s">
+      <c r="BI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="69" t="s">
+      <c r="BJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="69" t="s">
+      <c r="BK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="69" t="s">
+      <c r="BL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="69" t="s">
+      <c r="BM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="69" t="s">
+      <c r="BN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="69" t="s">
+      <c r="BO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="69" t="s">
+      <c r="BP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="69" t="s">
+      <c r="BQ4" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="69" t="s">
+      <c r="BR4" s="46" t="s">
         <v>344</v>
       </c>
-      <c r="BS4" s="69" t="s">
+      <c r="BS4" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="BT4" s="69" t="s">
+      <c r="BT4" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="69" t="s">
+      <c r="BU4" s="46" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="69" t="s">
+      <c r="BV4" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="BW4" s="69" t="s">
+      <c r="BW4" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="69" t="s">
+      <c r="BX4" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="69" t="s">
+      <c r="BY4" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="69" t="s">
+      <c r="BZ4" s="46" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="69" t="s">
+      <c r="CA4" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="69" t="s">
+      <c r="CB4" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="69" t="s">
+      <c r="CC4" s="46" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="69" t="s">
+      <c r="CD4" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="CE4" s="69" t="s">
+      <c r="CE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="69" t="s">
+      <c r="CF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="69" t="s">
+      <c r="CG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="69" t="s">
+      <c r="CH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="69" t="s">
+      <c r="CI4" s="46" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="69" t="s">
+      <c r="CJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="69" t="s">
+      <c r="CK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="69" t="s">
+      <c r="CL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="69" t="s">
+      <c r="CM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="69" t="s">
+      <c r="CN4" s="46" t="s">
         <v>405</v>
       </c>
-      <c r="CO4" s="69" t="s">
+      <c r="CO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="69" t="s">
+      <c r="CP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="69" t="s">
+      <c r="CQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="69" t="s">
+      <c r="CR4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="69" t="s">
+      <c r="CS4" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="CT4" s="94"/>
-      <c r="CU4" s="94"/>
-      <c r="CV4" s="94"/>
-      <c r="CW4" s="94"/>
-      <c r="CX4" s="94"/>
+      <c r="CT4" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="CU4" s="89"/>
+      <c r="CV4" s="89"/>
+      <c r="CW4" s="89"/>
+      <c r="CX4" s="89"/>
+      <c r="CY4" s="89"/>
     </row>
-    <row r="5" spans="1:102" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="63"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-      <c r="Y5" s="46"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
-      <c r="BD5" s="48"/>
-      <c r="BE5" s="48"/>
-      <c r="BF5" s="48"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
-      <c r="BJ5" s="48"/>
-      <c r="BK5" s="48"/>
-      <c r="BL5" s="48"/>
-      <c r="BM5" s="48"/>
-      <c r="BN5" s="48"/>
-      <c r="BO5" s="48"/>
-      <c r="BP5" s="48"/>
-      <c r="BQ5" s="69"/>
-      <c r="BR5" s="69"/>
-      <c r="BS5" s="69"/>
-      <c r="BT5" s="69"/>
-      <c r="BU5" s="69"/>
-      <c r="BV5" s="69"/>
-      <c r="BW5" s="69"/>
-      <c r="BX5" s="69"/>
-      <c r="BY5" s="69"/>
-      <c r="BZ5" s="69"/>
-      <c r="CA5" s="69"/>
-      <c r="CB5" s="69"/>
-      <c r="CC5" s="69"/>
-      <c r="CD5" s="69"/>
-      <c r="CE5" s="69"/>
-      <c r="CF5" s="69"/>
-      <c r="CG5" s="69"/>
-      <c r="CH5" s="69"/>
-      <c r="CI5" s="69"/>
-      <c r="CJ5" s="69"/>
-      <c r="CK5" s="69"/>
-      <c r="CL5" s="69"/>
-      <c r="CM5" s="69"/>
-      <c r="CN5" s="69"/>
-      <c r="CO5" s="69"/>
-      <c r="CP5" s="69"/>
-      <c r="CQ5" s="69"/>
-      <c r="CR5" s="69"/>
-      <c r="CS5" s="69"/>
-      <c r="CT5" s="94"/>
-      <c r="CU5" s="94"/>
-      <c r="CV5" s="94"/>
-      <c r="CW5" s="94"/>
-      <c r="CX5" s="94"/>
+    <row r="5" spans="1:103" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="67"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="47"/>
+      <c r="BO5" s="47"/>
+      <c r="BP5" s="47"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="46"/>
+      <c r="BV5" s="46"/>
+      <c r="BW5" s="46"/>
+      <c r="BX5" s="46"/>
+      <c r="BY5" s="46"/>
+      <c r="BZ5" s="46"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="89"/>
+      <c r="CV5" s="89"/>
+      <c r="CW5" s="89"/>
+      <c r="CX5" s="89"/>
+      <c r="CY5" s="89"/>
     </row>
-    <row r="6" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -77006,13 +77515,16 @@
       <c r="CS6" s="28">
         <v>153</v>
       </c>
-      <c r="CT6" s="22"/>
+      <c r="CT6" s="28">
+        <v>122</v>
+      </c>
       <c r="CU6" s="22"/>
       <c r="CV6" s="22"/>
       <c r="CW6" s="22"/>
       <c r="CX6" s="22"/>
+      <c r="CY6" s="22"/>
     </row>
-    <row r="7" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -77301,13 +77813,16 @@
       <c r="CS7" s="15">
         <v>2</v>
       </c>
-      <c r="CT7" s="23"/>
+      <c r="CT7" s="15">
+        <v>1</v>
+      </c>
       <c r="CU7" s="23"/>
       <c r="CV7" s="23"/>
       <c r="CW7" s="23"/>
       <c r="CX7" s="23"/>
+      <c r="CY7" s="23"/>
     </row>
-    <row r="8" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -77596,13 +78111,16 @@
       <c r="CS8" s="28">
         <v>50</v>
       </c>
-      <c r="CT8" s="23"/>
+      <c r="CT8" s="28">
+        <v>30</v>
+      </c>
       <c r="CU8" s="23"/>
       <c r="CV8" s="23"/>
       <c r="CW8" s="23"/>
       <c r="CX8" s="23"/>
+      <c r="CY8" s="23"/>
     </row>
-    <row r="9" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -77892,13 +78410,16 @@
       <c r="CS9" s="15">
         <v>104</v>
       </c>
-      <c r="CT9" s="23"/>
+      <c r="CT9" s="15">
+        <v>101</v>
+      </c>
       <c r="CU9" s="23"/>
       <c r="CV9" s="23"/>
       <c r="CW9" s="23"/>
       <c r="CX9" s="23"/>
+      <c r="CY9" s="23"/>
     </row>
-    <row r="10" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -78187,13 +78708,16 @@
       <c r="CS10" s="15">
         <v>0</v>
       </c>
-      <c r="CT10" s="23"/>
+      <c r="CT10" s="15">
+        <v>1</v>
+      </c>
       <c r="CU10" s="23"/>
       <c r="CV10" s="23"/>
       <c r="CW10" s="23"/>
       <c r="CX10" s="23"/>
+      <c r="CY10" s="23"/>
     </row>
-    <row r="11" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -78482,13 +79006,16 @@
       <c r="CS11" s="15">
         <v>10</v>
       </c>
-      <c r="CT11" s="23"/>
+      <c r="CT11" s="15">
+        <v>7</v>
+      </c>
       <c r="CU11" s="23"/>
       <c r="CV11" s="23"/>
       <c r="CW11" s="23"/>
       <c r="CX11" s="23"/>
+      <c r="CY11" s="23"/>
     </row>
-    <row r="12" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -78777,13 +79304,16 @@
       <c r="CS12" s="15">
         <v>7</v>
       </c>
-      <c r="CT12" s="23"/>
+      <c r="CT12" s="15">
+        <v>11</v>
+      </c>
       <c r="CU12" s="23"/>
       <c r="CV12" s="23"/>
       <c r="CW12" s="23"/>
       <c r="CX12" s="23"/>
+      <c r="CY12" s="23"/>
     </row>
-    <row r="13" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -79072,13 +79602,16 @@
       <c r="CS13" s="15">
         <v>20</v>
       </c>
-      <c r="CT13" s="22"/>
+      <c r="CT13" s="15">
+        <v>20</v>
+      </c>
       <c r="CU13" s="22"/>
       <c r="CV13" s="22"/>
       <c r="CW13" s="22"/>
       <c r="CX13" s="22"/>
+      <c r="CY13" s="22"/>
     </row>
-    <row r="14" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -79367,13 +79900,16 @@
       <c r="CS14" s="15">
         <v>28</v>
       </c>
-      <c r="CT14" s="23"/>
+      <c r="CT14" s="15">
+        <v>26</v>
+      </c>
       <c r="CU14" s="23"/>
       <c r="CV14" s="23"/>
       <c r="CW14" s="23"/>
       <c r="CX14" s="23"/>
+      <c r="CY14" s="23"/>
     </row>
-    <row r="15" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -79662,13 +80198,16 @@
       <c r="CS15" s="15">
         <v>9</v>
       </c>
-      <c r="CT15" s="23"/>
+      <c r="CT15" s="15">
+        <v>6</v>
+      </c>
       <c r="CU15" s="23"/>
       <c r="CV15" s="23"/>
       <c r="CW15" s="23"/>
       <c r="CX15" s="23"/>
+      <c r="CY15" s="23"/>
     </row>
-    <row r="16" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -79958,13 +80497,16 @@
       <c r="CS16" s="28">
         <v>229</v>
       </c>
-      <c r="CT16" s="22"/>
+      <c r="CT16" s="28">
+        <v>204</v>
+      </c>
       <c r="CU16" s="22"/>
       <c r="CV16" s="22"/>
       <c r="CW16" s="22"/>
       <c r="CX16" s="22"/>
+      <c r="CY16" s="22"/>
     </row>
-    <row r="17" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -80253,13 +80795,16 @@
       <c r="CS17" s="15">
         <v>175</v>
       </c>
-      <c r="CT17" s="22"/>
+      <c r="CT17" s="15">
+        <v>116</v>
+      </c>
       <c r="CU17" s="22"/>
       <c r="CV17" s="22"/>
       <c r="CW17" s="22"/>
       <c r="CX17" s="22"/>
+      <c r="CY17" s="22"/>
     </row>
-    <row r="18" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -80549,15 +81094,18 @@
       <c r="CS18" s="34">
         <v>2626</v>
       </c>
-      <c r="CT18" s="22"/>
+      <c r="CT18" s="34">
+        <v>2135</v>
+      </c>
       <c r="CU18" s="22"/>
       <c r="CV18" s="22"/>
       <c r="CW18" s="22"/>
       <c r="CX18" s="22"/>
+      <c r="CY18" s="22"/>
     </row>
-    <row r="19" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="83" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -80845,15 +81393,18 @@
       <c r="CS19" s="15">
         <v>80</v>
       </c>
-      <c r="CT19" s="22"/>
+      <c r="CT19" s="15">
+        <v>54</v>
+      </c>
       <c r="CU19" s="22"/>
       <c r="CV19" s="22"/>
       <c r="CW19" s="22"/>
       <c r="CX19" s="22"/>
+      <c r="CY19" s="22"/>
     </row>
-    <row r="20" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -81139,15 +81690,18 @@
       <c r="CS20" s="28">
         <v>299</v>
       </c>
-      <c r="CT20" s="22"/>
+      <c r="CT20" s="28">
+        <v>160</v>
+      </c>
       <c r="CU20" s="22"/>
       <c r="CV20" s="22"/>
       <c r="CW20" s="22"/>
       <c r="CX20" s="22"/>
+      <c r="CY20" s="22"/>
     </row>
-    <row r="21" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="90"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -81433,13 +81987,16 @@
       <c r="CS21" s="15">
         <v>35</v>
       </c>
-      <c r="CT21" s="22"/>
+      <c r="CT21" s="15">
+        <v>51</v>
+      </c>
       <c r="CU21" s="22"/>
       <c r="CV21" s="22"/>
       <c r="CW21" s="22"/>
       <c r="CX21" s="22"/>
+      <c r="CY21" s="22"/>
     </row>
-    <row r="22" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -81728,13 +82285,16 @@
       <c r="CS22" s="15">
         <v>5</v>
       </c>
-      <c r="CT22" s="23"/>
+      <c r="CT22" s="15">
+        <v>3</v>
+      </c>
       <c r="CU22" s="23"/>
       <c r="CV22" s="23"/>
       <c r="CW22" s="23"/>
       <c r="CX22" s="23"/>
+      <c r="CY22" s="23"/>
     </row>
-    <row r="23" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -82023,13 +82583,16 @@
       <c r="CS23" s="15">
         <v>6</v>
       </c>
-      <c r="CT23" s="23"/>
+      <c r="CT23" s="15">
+        <v>3</v>
+      </c>
       <c r="CU23" s="23"/>
       <c r="CV23" s="23"/>
       <c r="CW23" s="23"/>
       <c r="CX23" s="23"/>
+      <c r="CY23" s="23"/>
     </row>
-    <row r="24" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -82318,13 +82881,16 @@
       <c r="CS24" s="15">
         <v>24</v>
       </c>
-      <c r="CT24" s="22"/>
+      <c r="CT24" s="15">
+        <v>11</v>
+      </c>
       <c r="CU24" s="22"/>
       <c r="CV24" s="22"/>
       <c r="CW24" s="22"/>
       <c r="CX24" s="22"/>
+      <c r="CY24" s="22"/>
     </row>
-    <row r="25" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -82613,13 +83179,16 @@
       <c r="CS25" s="15">
         <v>5</v>
       </c>
-      <c r="CT25" s="23"/>
+      <c r="CT25" s="15">
+        <v>2</v>
+      </c>
       <c r="CU25" s="23"/>
       <c r="CV25" s="23"/>
       <c r="CW25" s="23"/>
       <c r="CX25" s="23"/>
+      <c r="CY25" s="23"/>
     </row>
-    <row r="26" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -82908,13 +83477,16 @@
       <c r="CS26" s="15">
         <v>15</v>
       </c>
-      <c r="CT26" s="23"/>
+      <c r="CT26" s="15">
+        <v>31</v>
+      </c>
       <c r="CU26" s="23"/>
       <c r="CV26" s="23"/>
       <c r="CW26" s="23"/>
       <c r="CX26" s="23"/>
+      <c r="CY26" s="23"/>
     </row>
-    <row r="27" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -83203,13 +83775,16 @@
       <c r="CS27" s="15">
         <v>0</v>
       </c>
-      <c r="CT27" s="23"/>
+      <c r="CT27" s="15">
+        <v>0</v>
+      </c>
       <c r="CU27" s="23"/>
       <c r="CV27" s="23"/>
       <c r="CW27" s="23"/>
       <c r="CX27" s="23"/>
+      <c r="CY27" s="23"/>
     </row>
-    <row r="28" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -83498,14 +84073,17 @@
       <c r="CS28" s="15">
         <v>10</v>
       </c>
-      <c r="CT28" s="22"/>
+      <c r="CT28" s="15">
+        <v>2</v>
+      </c>
       <c r="CU28" s="22"/>
       <c r="CV28" s="22"/>
       <c r="CW28" s="22"/>
       <c r="CX28" s="22"/>
+      <c r="CY28" s="22"/>
     </row>
-    <row r="29" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="91" t="s">
+    <row r="29" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -83793,14 +84371,17 @@
       <c r="CS29" s="15">
         <v>5</v>
       </c>
-      <c r="CT29" s="23"/>
+      <c r="CT29" s="15">
+        <v>3</v>
+      </c>
       <c r="CU29" s="23"/>
       <c r="CV29" s="23"/>
       <c r="CW29" s="23"/>
       <c r="CX29" s="23"/>
+      <c r="CY29" s="23"/>
     </row>
-    <row r="30" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="92"/>
+    <row r="30" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -84086,13 +84667,16 @@
       <c r="CS30" s="15">
         <v>48</v>
       </c>
-      <c r="CT30" s="23"/>
+      <c r="CT30" s="15">
+        <v>42</v>
+      </c>
       <c r="CU30" s="23"/>
       <c r="CV30" s="23"/>
       <c r="CW30" s="23"/>
       <c r="CX30" s="23"/>
+      <c r="CY30" s="23"/>
     </row>
-    <row r="31" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -84382,13 +84966,16 @@
       <c r="CS31" s="15">
         <v>183</v>
       </c>
-      <c r="CT31" s="22"/>
+      <c r="CT31" s="15">
+        <v>127</v>
+      </c>
       <c r="CU31" s="22"/>
       <c r="CV31" s="22"/>
       <c r="CW31" s="22"/>
       <c r="CX31" s="22"/>
+      <c r="CY31" s="22"/>
     </row>
-    <row r="32" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -84677,13 +85264,16 @@
       <c r="CS32" s="15">
         <v>13</v>
       </c>
-      <c r="CT32" s="23"/>
+      <c r="CT32" s="15">
+        <v>6</v>
+      </c>
       <c r="CU32" s="23"/>
       <c r="CV32" s="23"/>
       <c r="CW32" s="23"/>
       <c r="CX32" s="23"/>
+      <c r="CY32" s="23"/>
     </row>
-    <row r="33" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -84972,13 +85562,16 @@
       <c r="CS33" s="15">
         <v>1</v>
       </c>
-      <c r="CT33" s="23"/>
+      <c r="CT33" s="15">
+        <v>0</v>
+      </c>
       <c r="CU33" s="23"/>
       <c r="CV33" s="23"/>
       <c r="CW33" s="23"/>
       <c r="CX33" s="23"/>
+      <c r="CY33" s="23"/>
     </row>
-    <row r="34" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -85268,15 +85861,18 @@
       <c r="CS34" s="15">
         <v>176</v>
       </c>
-      <c r="CT34" s="22"/>
+      <c r="CT34" s="15">
+        <v>107</v>
+      </c>
       <c r="CU34" s="22"/>
       <c r="CV34" s="22"/>
       <c r="CW34" s="22"/>
       <c r="CX34" s="22"/>
+      <c r="CY34" s="22"/>
     </row>
-    <row r="35" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="89" t="s">
+      <c r="B35" s="83" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -85564,14 +86160,17 @@
       <c r="CS35" s="15">
         <v>556</v>
       </c>
-      <c r="CT35" s="22"/>
+      <c r="CT35" s="15">
+        <v>369</v>
+      </c>
       <c r="CU35" s="22"/>
       <c r="CV35" s="22"/>
       <c r="CW35" s="22"/>
       <c r="CX35" s="22"/>
+      <c r="CY35" s="22"/>
     </row>
-    <row r="36" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="90"/>
+    <row r="36" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -85857,13 +86456,16 @@
       <c r="CS36" s="28">
         <v>70</v>
       </c>
-      <c r="CT36" s="22"/>
+      <c r="CT36" s="28">
+        <v>39</v>
+      </c>
       <c r="CU36" s="22"/>
       <c r="CV36" s="22"/>
       <c r="CW36" s="22"/>
       <c r="CX36" s="22"/>
+      <c r="CY36" s="22"/>
     </row>
-    <row r="37" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -86153,13 +86755,16 @@
       <c r="CS37" s="15">
         <v>153</v>
       </c>
-      <c r="CT37" s="22"/>
+      <c r="CT37" s="15">
+        <v>94</v>
+      </c>
       <c r="CU37" s="22"/>
       <c r="CV37" s="22"/>
       <c r="CW37" s="22"/>
       <c r="CX37" s="22"/>
+      <c r="CY37" s="22"/>
     </row>
-    <row r="38" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -86448,13 +87053,16 @@
       <c r="CS38" s="15">
         <v>28</v>
       </c>
-      <c r="CT38" s="23"/>
+      <c r="CT38" s="15">
+        <v>23</v>
+      </c>
       <c r="CU38" s="23"/>
       <c r="CV38" s="23"/>
       <c r="CW38" s="23"/>
       <c r="CX38" s="23"/>
+      <c r="CY38" s="23"/>
     </row>
-    <row r="39" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -86743,13 +87351,16 @@
       <c r="CS39" s="15">
         <v>20</v>
       </c>
-      <c r="CT39" s="23"/>
+      <c r="CT39" s="15">
+        <v>14</v>
+      </c>
       <c r="CU39" s="23"/>
       <c r="CV39" s="23"/>
       <c r="CW39" s="23"/>
       <c r="CX39" s="23"/>
+      <c r="CY39" s="23"/>
     </row>
-    <row r="40" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -87038,13 +87649,16 @@
       <c r="CS40" s="15">
         <v>1</v>
       </c>
-      <c r="CT40" s="23"/>
+      <c r="CT40" s="15">
+        <v>0</v>
+      </c>
       <c r="CU40" s="23"/>
       <c r="CV40" s="23"/>
       <c r="CW40" s="23"/>
       <c r="CX40" s="23"/>
+      <c r="CY40" s="23"/>
     </row>
-    <row r="41" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -87333,13 +87947,16 @@
       <c r="CS41" s="15">
         <v>0</v>
       </c>
-      <c r="CT41" s="23"/>
+      <c r="CT41" s="15">
+        <v>1</v>
+      </c>
       <c r="CU41" s="23"/>
       <c r="CV41" s="23"/>
       <c r="CW41" s="23"/>
       <c r="CX41" s="23"/>
+      <c r="CY41" s="23"/>
     </row>
-    <row r="42" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -87628,13 +88245,16 @@
       <c r="CS42" s="15">
         <v>27</v>
       </c>
-      <c r="CT42" s="23"/>
+      <c r="CT42" s="15">
+        <v>16</v>
+      </c>
       <c r="CU42" s="23"/>
       <c r="CV42" s="23"/>
       <c r="CW42" s="23"/>
       <c r="CX42" s="23"/>
+      <c r="CY42" s="23"/>
     </row>
-    <row r="43" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -87923,13 +88543,16 @@
       <c r="CS43" s="28">
         <v>63</v>
       </c>
-      <c r="CT43" s="23"/>
+      <c r="CT43" s="28">
+        <v>78</v>
+      </c>
       <c r="CU43" s="23"/>
       <c r="CV43" s="23"/>
       <c r="CW43" s="23"/>
       <c r="CX43" s="23"/>
+      <c r="CY43" s="23"/>
     </row>
-    <row r="44" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -88218,13 +88841,16 @@
       <c r="CS44" s="15">
         <v>5</v>
       </c>
-      <c r="CT44" s="23"/>
+      <c r="CT44" s="15">
+        <v>3</v>
+      </c>
       <c r="CU44" s="23"/>
       <c r="CV44" s="23"/>
       <c r="CW44" s="23"/>
       <c r="CX44" s="23"/>
+      <c r="CY44" s="23"/>
     </row>
-    <row r="45" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -88513,13 +89139,16 @@
       <c r="CS45" s="15">
         <v>25</v>
       </c>
-      <c r="CT45" s="22"/>
+      <c r="CT45" s="15">
+        <v>16</v>
+      </c>
       <c r="CU45" s="22"/>
       <c r="CV45" s="22"/>
       <c r="CW45" s="22"/>
       <c r="CX45" s="22"/>
+      <c r="CY45" s="22"/>
     </row>
-    <row r="46" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -88808,13 +89437,16 @@
       <c r="CS46" s="15">
         <v>40</v>
       </c>
-      <c r="CT46" s="23"/>
+      <c r="CT46" s="15">
+        <v>26</v>
+      </c>
       <c r="CU46" s="23"/>
       <c r="CV46" s="23"/>
       <c r="CW46" s="23"/>
       <c r="CX46" s="23"/>
+      <c r="CY46" s="23"/>
     </row>
-    <row r="47" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -89103,13 +89735,16 @@
       <c r="CS47" s="15">
         <v>1</v>
       </c>
-      <c r="CT47" s="23"/>
+      <c r="CT47" s="15">
+        <v>4</v>
+      </c>
       <c r="CU47" s="23"/>
       <c r="CV47" s="23"/>
       <c r="CW47" s="23"/>
       <c r="CX47" s="23"/>
+      <c r="CY47" s="23"/>
     </row>
-    <row r="48" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -89398,15 +90033,18 @@
       <c r="CS48" s="15">
         <v>26</v>
       </c>
-      <c r="CT48" s="23"/>
+      <c r="CT48" s="15">
+        <v>31</v>
+      </c>
       <c r="CU48" s="23"/>
       <c r="CV48" s="23"/>
       <c r="CW48" s="23"/>
       <c r="CX48" s="23"/>
+      <c r="CY48" s="23"/>
     </row>
-    <row r="49" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="89" t="s">
+      <c r="B49" s="83" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -89694,14 +90332,17 @@
       <c r="CS49" s="15">
         <v>212</v>
       </c>
-      <c r="CT49" s="22"/>
+      <c r="CT49" s="15">
+        <v>146</v>
+      </c>
       <c r="CU49" s="22"/>
       <c r="CV49" s="22"/>
       <c r="CW49" s="22"/>
       <c r="CX49" s="22"/>
+      <c r="CY49" s="22"/>
     </row>
-    <row r="50" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="90"/>
+    <row r="50" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -89987,13 +90628,16 @@
       <c r="CS50" s="15">
         <v>82</v>
       </c>
-      <c r="CT50" s="22"/>
+      <c r="CT50" s="15">
+        <v>37</v>
+      </c>
       <c r="CU50" s="22"/>
       <c r="CV50" s="22"/>
       <c r="CW50" s="22"/>
       <c r="CX50" s="22"/>
+      <c r="CY50" s="22"/>
     </row>
-    <row r="51" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -90282,13 +90926,16 @@
       <c r="CS51" s="15">
         <v>33</v>
       </c>
-      <c r="CT51" s="23"/>
+      <c r="CT51" s="15">
+        <v>16</v>
+      </c>
       <c r="CU51" s="23"/>
       <c r="CV51" s="23"/>
       <c r="CW51" s="23"/>
       <c r="CX51" s="23"/>
+      <c r="CY51" s="23"/>
     </row>
-    <row r="52" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -90577,13 +91224,16 @@
       <c r="CS52" s="15">
         <v>42</v>
       </c>
-      <c r="CT52" s="23"/>
+      <c r="CT52" s="15">
+        <v>20</v>
+      </c>
       <c r="CU52" s="23"/>
       <c r="CV52" s="23"/>
       <c r="CW52" s="23"/>
       <c r="CX52" s="23"/>
+      <c r="CY52" s="23"/>
     </row>
-    <row r="53" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -90872,13 +91522,16 @@
       <c r="CS53" s="15">
         <v>57</v>
       </c>
-      <c r="CT53" s="23"/>
+      <c r="CT53" s="15">
+        <v>49</v>
+      </c>
       <c r="CU53" s="23"/>
       <c r="CV53" s="23"/>
       <c r="CW53" s="23"/>
       <c r="CX53" s="23"/>
+      <c r="CY53" s="23"/>
     </row>
-    <row r="54" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -91167,13 +91820,16 @@
       <c r="CS54" s="15">
         <v>12</v>
       </c>
-      <c r="CT54" s="23"/>
+      <c r="CT54" s="15">
+        <v>8</v>
+      </c>
       <c r="CU54" s="23"/>
       <c r="CV54" s="23"/>
       <c r="CW54" s="23"/>
       <c r="CX54" s="23"/>
+      <c r="CY54" s="23"/>
     </row>
-    <row r="55" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -91462,13 +92118,16 @@
       <c r="CS55" s="15">
         <v>26</v>
       </c>
-      <c r="CT55" s="23"/>
+      <c r="CT55" s="15">
+        <v>20</v>
+      </c>
       <c r="CU55" s="23"/>
       <c r="CV55" s="23"/>
       <c r="CW55" s="23"/>
       <c r="CX55" s="23"/>
+      <c r="CY55" s="23"/>
     </row>
-    <row r="56" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -91757,13 +92416,16 @@
       <c r="CS56" s="15">
         <v>21</v>
       </c>
-      <c r="CT56" s="23"/>
+      <c r="CT56" s="15">
+        <v>11</v>
+      </c>
       <c r="CU56" s="23"/>
       <c r="CV56" s="23"/>
       <c r="CW56" s="23"/>
       <c r="CX56" s="23"/>
+      <c r="CY56" s="23"/>
     </row>
-    <row r="57" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -92052,13 +92714,16 @@
       <c r="CS57" s="15">
         <v>3</v>
       </c>
-      <c r="CT57" s="23"/>
+      <c r="CT57" s="15">
+        <v>4</v>
+      </c>
       <c r="CU57" s="23"/>
       <c r="CV57" s="23"/>
       <c r="CW57" s="23"/>
       <c r="CX57" s="23"/>
+      <c r="CY57" s="23"/>
     </row>
-    <row r="58" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -92328,7 +92993,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CS58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CT58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -92439,13 +93104,17 @@
         <f t="shared" si="4"/>
         <v>5821</v>
       </c>
-      <c r="CT58" s="24"/>
+      <c r="CT58" s="14">
+        <f t="shared" si="4"/>
+        <v>4407</v>
+      </c>
       <c r="CU58" s="24"/>
       <c r="CV58" s="24"/>
       <c r="CW58" s="24"/>
       <c r="CX58" s="24"/>
+      <c r="CY58" s="24"/>
     </row>
-    <row r="59" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -92478,7 +93147,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -92511,7 +93180,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -92545,56 +93214,49 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="BD2:CS2"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="BK4:BK5"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BT4:BT5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="CA4:CA5"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="BJ4:BJ5"/>
-    <mergeCell ref="BI4:BI5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="BF4:BF5"/>
-    <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AQ4:AQ5"/>
+  <mergeCells count="113">
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="AV4:AV5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="CF4:CF5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -92616,48 +93278,56 @@
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="CX4:CX5"/>
-    <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="BY4:BY5"/>
+    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="BI4:BI5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="BF4:BF5"/>
+    <mergeCell ref="BK4:BK5"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="AR3:BC3"/>
+    <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BT4:BT5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="BR4:BR5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="CH4:CH5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="BD2:CT2"/>
+    <mergeCell ref="CR3:CT3"/>
     <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="CW4:CW5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="CP4:CP5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="BD4:BD5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -92681,7 +93351,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CS57</xm:sqref>
+          <xm:sqref>BP6:CT57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050124-2\ＪＯＢ050124-2\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050131-1\ＪＯＢ050131-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11085"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CT$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CT$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$ET$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$ET$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CU$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CU$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EU$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EU$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="422">
   <si>
     <t>都道府県</t>
   </si>
@@ -4538,6 +4538,18 @@
 【1月第4週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1/23(月)～
+1/29(日)分
+【1月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1/24(月)～
+1/30(日)分
+【1月第5週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5034,9 +5046,6 @@
     <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5044,6 +5053,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9338,7 +9350,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EU61"/>
+  <dimension ref="A1:EV61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9352,11 +9364,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="150" width="10.875" style="1" customWidth="1"/>
-    <col min="151" max="16384" width="8.625" style="1"/>
+    <col min="106" max="151" width="10.875" style="1" customWidth="1"/>
+    <col min="152" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:151" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:152" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9433,11 +9445,12 @@
       <c r="EQ1" s="19"/>
       <c r="ER1" s="19"/>
       <c r="ES1" s="19"/>
-      <c r="ET1" s="19" t="s">
+      <c r="ET1" s="19"/>
+      <c r="EU1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:151" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:152" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -9549,96 +9562,97 @@
       <c r="DB2" s="52"/>
       <c r="DC2" s="52"/>
       <c r="DD2" s="52"/>
-      <c r="DE2" s="44" t="s">
+      <c r="DE2" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="44"/>
-      <c r="DG2" s="44"/>
-      <c r="DH2" s="44"/>
-      <c r="DI2" s="44"/>
-      <c r="DJ2" s="44"/>
-      <c r="DK2" s="44"/>
-      <c r="DL2" s="44"/>
-      <c r="DM2" s="44"/>
-      <c r="DN2" s="44"/>
-      <c r="DO2" s="44"/>
-      <c r="DP2" s="44"/>
-      <c r="DQ2" s="44"/>
-      <c r="DR2" s="44"/>
-      <c r="DS2" s="44"/>
-      <c r="DT2" s="44"/>
-      <c r="DU2" s="44"/>
-      <c r="DV2" s="44"/>
-      <c r="DW2" s="44"/>
-      <c r="DX2" s="44"/>
-      <c r="DY2" s="44"/>
-      <c r="DZ2" s="44"/>
-      <c r="EA2" s="44"/>
-      <c r="EB2" s="44"/>
-      <c r="EC2" s="44"/>
-      <c r="ED2" s="44"/>
-      <c r="EE2" s="44"/>
-      <c r="EF2" s="44"/>
-      <c r="EG2" s="44"/>
-      <c r="EH2" s="44"/>
-      <c r="EI2" s="44"/>
-      <c r="EJ2" s="44"/>
-      <c r="EK2" s="44"/>
-      <c r="EL2" s="44"/>
-      <c r="EM2" s="44"/>
-      <c r="EN2" s="44"/>
-      <c r="EO2" s="44"/>
-      <c r="EP2" s="44"/>
-      <c r="EQ2" s="44"/>
-      <c r="ER2" s="44"/>
-      <c r="ES2" s="44"/>
-      <c r="ET2" s="44"/>
+      <c r="DF2" s="47"/>
+      <c r="DG2" s="47"/>
+      <c r="DH2" s="47"/>
+      <c r="DI2" s="47"/>
+      <c r="DJ2" s="47"/>
+      <c r="DK2" s="47"/>
+      <c r="DL2" s="47"/>
+      <c r="DM2" s="47"/>
+      <c r="DN2" s="47"/>
+      <c r="DO2" s="47"/>
+      <c r="DP2" s="47"/>
+      <c r="DQ2" s="47"/>
+      <c r="DR2" s="47"/>
+      <c r="DS2" s="47"/>
+      <c r="DT2" s="47"/>
+      <c r="DU2" s="47"/>
+      <c r="DV2" s="47"/>
+      <c r="DW2" s="47"/>
+      <c r="DX2" s="47"/>
+      <c r="DY2" s="47"/>
+      <c r="DZ2" s="47"/>
+      <c r="EA2" s="47"/>
+      <c r="EB2" s="47"/>
+      <c r="EC2" s="47"/>
+      <c r="ED2" s="47"/>
+      <c r="EE2" s="47"/>
+      <c r="EF2" s="47"/>
+      <c r="EG2" s="47"/>
+      <c r="EH2" s="47"/>
+      <c r="EI2" s="47"/>
+      <c r="EJ2" s="47"/>
+      <c r="EK2" s="47"/>
+      <c r="EL2" s="47"/>
+      <c r="EM2" s="47"/>
+      <c r="EN2" s="47"/>
+      <c r="EO2" s="47"/>
+      <c r="EP2" s="47"/>
+      <c r="EQ2" s="47"/>
+      <c r="ER2" s="47"/>
+      <c r="ES2" s="47"/>
+      <c r="ET2" s="47"/>
+      <c r="EU2" s="47"/>
     </row>
-    <row r="3" spans="1:151" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:152" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="45"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="44"/>
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="44"/>
+      <c r="AK3" s="44"/>
+      <c r="AL3" s="44"/>
+      <c r="AM3" s="44"/>
+      <c r="AN3" s="44"/>
+      <c r="AO3" s="44"/>
+      <c r="AP3" s="44"/>
+      <c r="AQ3" s="44"/>
       <c r="AR3" s="48" t="s">
         <v>216</v>
       </c>
@@ -9695,69 +9709,70 @@
       <c r="CO3" s="53"/>
       <c r="CP3" s="53"/>
       <c r="CQ3" s="54"/>
-      <c r="CR3" s="45" t="s">
+      <c r="CR3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
+      <c r="CS3" s="44"/>
+      <c r="CT3" s="44"/>
+      <c r="CU3" s="44"/>
+      <c r="CV3" s="44"/>
+      <c r="CW3" s="44"/>
+      <c r="CX3" s="44"/>
+      <c r="CY3" s="44"/>
+      <c r="CZ3" s="44"/>
+      <c r="DA3" s="44"/>
+      <c r="DB3" s="44"/>
+      <c r="DC3" s="44"/>
       <c r="DD3" s="48"/>
-      <c r="DE3" s="45" t="s">
+      <c r="DE3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DF3" s="44"/>
+      <c r="DG3" s="44"/>
+      <c r="DH3" s="44"/>
+      <c r="DI3" s="44"/>
+      <c r="DJ3" s="44"/>
+      <c r="DK3" s="44"/>
+      <c r="DL3" s="44"/>
+      <c r="DM3" s="44"/>
+      <c r="DN3" s="44"/>
+      <c r="DO3" s="44"/>
+      <c r="DP3" s="44"/>
+      <c r="DQ3" s="44"/>
+      <c r="DR3" s="44"/>
+      <c r="DS3" s="44"/>
+      <c r="DT3" s="44"/>
+      <c r="DU3" s="44"/>
+      <c r="DV3" s="44"/>
+      <c r="DW3" s="44"/>
+      <c r="DX3" s="44"/>
+      <c r="DY3" s="44"/>
+      <c r="DZ3" s="44"/>
+      <c r="EA3" s="44"/>
+      <c r="EB3" s="44"/>
+      <c r="EC3" s="44"/>
+      <c r="ED3" s="44"/>
+      <c r="EE3" s="44"/>
+      <c r="EF3" s="44"/>
+      <c r="EG3" s="44"/>
+      <c r="EH3" s="44"/>
+      <c r="EI3" s="44"/>
+      <c r="EJ3" s="44"/>
+      <c r="EK3" s="44"/>
+      <c r="EL3" s="44"/>
+      <c r="EM3" s="44"/>
+      <c r="EN3" s="44"/>
+      <c r="EO3" s="44"/>
+      <c r="EP3" s="44"/>
+      <c r="EQ3" s="44"/>
+      <c r="ER3" s="44" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
+      <c r="ES3" s="44"/>
+      <c r="ET3" s="44"/>
+      <c r="EU3" s="44"/>
     </row>
-    <row r="4" spans="1:151" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:152" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -10079,134 +10094,137 @@
       <c r="DD4" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="DE4" s="46" t="s">
+      <c r="DE4" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="DF4" s="46" t="s">
+      <c r="DF4" s="45" t="s">
         <v>310</v>
       </c>
-      <c r="DG4" s="46" t="s">
+      <c r="DG4" s="45" t="s">
         <v>312</v>
       </c>
-      <c r="DH4" s="46" t="s">
+      <c r="DH4" s="45" t="s">
         <v>315</v>
       </c>
-      <c r="DI4" s="46" t="s">
+      <c r="DI4" s="45" t="s">
         <v>316</v>
       </c>
-      <c r="DJ4" s="46" t="s">
+      <c r="DJ4" s="45" t="s">
         <v>318</v>
       </c>
-      <c r="DK4" s="46" t="s">
+      <c r="DK4" s="45" t="s">
         <v>326</v>
       </c>
-      <c r="DL4" s="46" t="s">
+      <c r="DL4" s="45" t="s">
         <v>328</v>
       </c>
-      <c r="DM4" s="46" t="s">
+      <c r="DM4" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="DN4" s="46" t="s">
+      <c r="DN4" s="45" t="s">
         <v>332</v>
       </c>
-      <c r="DO4" s="46" t="s">
+      <c r="DO4" s="45" t="s">
         <v>334</v>
       </c>
-      <c r="DP4" s="46" t="s">
+      <c r="DP4" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="DQ4" s="46" t="s">
+      <c r="DQ4" s="45" t="s">
         <v>338</v>
       </c>
-      <c r="DR4" s="46" t="s">
+      <c r="DR4" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="DS4" s="46" t="s">
+      <c r="DS4" s="45" t="s">
         <v>345</v>
       </c>
-      <c r="DT4" s="46" t="s">
+      <c r="DT4" s="45" t="s">
         <v>349</v>
       </c>
-      <c r="DU4" s="46" t="s">
+      <c r="DU4" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="DV4" s="46" t="s">
+      <c r="DV4" s="45" t="s">
         <v>354</v>
       </c>
-      <c r="DW4" s="46" t="s">
+      <c r="DW4" s="45" t="s">
         <v>357</v>
       </c>
-      <c r="DX4" s="46" t="s">
+      <c r="DX4" s="45" t="s">
         <v>359</v>
       </c>
-      <c r="DY4" s="46" t="s">
+      <c r="DY4" s="45" t="s">
         <v>361</v>
       </c>
-      <c r="DZ4" s="46" t="s">
+      <c r="DZ4" s="45" t="s">
         <v>363</v>
       </c>
-      <c r="EA4" s="46" t="s">
+      <c r="EA4" s="45" t="s">
         <v>371</v>
       </c>
-      <c r="EB4" s="46" t="s">
+      <c r="EB4" s="45" t="s">
         <v>375</v>
       </c>
-      <c r="EC4" s="46" t="s">
+      <c r="EC4" s="45" t="s">
         <v>379</v>
       </c>
-      <c r="ED4" s="46" t="s">
+      <c r="ED4" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="EE4" s="46" t="s">
+      <c r="EE4" s="45" t="s">
         <v>384</v>
       </c>
-      <c r="EF4" s="46" t="s">
+      <c r="EF4" s="45" t="s">
         <v>386</v>
       </c>
-      <c r="EG4" s="46" t="s">
+      <c r="EG4" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="EH4" s="46" t="s">
+      <c r="EH4" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="EI4" s="46" t="s">
+      <c r="EI4" s="45" t="s">
         <v>393</v>
       </c>
-      <c r="EJ4" s="46" t="s">
+      <c r="EJ4" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="EK4" s="46" t="s">
+      <c r="EK4" s="45" t="s">
         <v>398</v>
       </c>
-      <c r="EL4" s="46" t="s">
+      <c r="EL4" s="45" t="s">
         <v>400</v>
       </c>
-      <c r="EM4" s="46" t="s">
+      <c r="EM4" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="EN4" s="46" t="s">
+      <c r="EN4" s="45" t="s">
         <v>404</v>
       </c>
-      <c r="EO4" s="46" t="s">
+      <c r="EO4" s="45" t="s">
         <v>407</v>
       </c>
-      <c r="EP4" s="46" t="s">
+      <c r="EP4" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="EQ4" s="46" t="s">
+      <c r="EQ4" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="ER4" s="46" t="s">
+      <c r="ER4" s="45" t="s">
         <v>412</v>
       </c>
-      <c r="ES4" s="46" t="s">
+      <c r="ES4" s="45" t="s">
         <v>416</v>
       </c>
-      <c r="ET4" s="46" t="s">
+      <c r="ET4" s="45" t="s">
         <v>418</v>
       </c>
+      <c r="EU4" s="45" t="s">
+        <v>420</v>
+      </c>
     </row>
-    <row r="5" spans="1:151" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:152" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="55"/>
@@ -10288,76 +10306,77 @@
       <c r="CB5" s="56"/>
       <c r="CC5" s="56"/>
       <c r="CD5" s="56"/>
-      <c r="CE5" s="47"/>
-      <c r="CF5" s="47"/>
-      <c r="CG5" s="47"/>
-      <c r="CH5" s="47"/>
-      <c r="CI5" s="47"/>
-      <c r="CJ5" s="47"/>
-      <c r="CK5" s="47"/>
-      <c r="CL5" s="47"/>
-      <c r="CM5" s="47"/>
-      <c r="CN5" s="47"/>
-      <c r="CO5" s="47"/>
-      <c r="CP5" s="47"/>
-      <c r="CQ5" s="47"/>
-      <c r="CR5" s="47"/>
-      <c r="CS5" s="47"/>
-      <c r="CT5" s="47"/>
-      <c r="CU5" s="47"/>
-      <c r="CV5" s="47"/>
-      <c r="CW5" s="47"/>
-      <c r="CX5" s="47"/>
-      <c r="CY5" s="47"/>
-      <c r="CZ5" s="47"/>
-      <c r="DA5" s="47"/>
-      <c r="DB5" s="47"/>
-      <c r="DC5" s="47"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
+      <c r="CW5" s="46"/>
+      <c r="CX5" s="46"/>
+      <c r="CY5" s="46"/>
+      <c r="CZ5" s="46"/>
+      <c r="DA5" s="46"/>
+      <c r="DB5" s="46"/>
+      <c r="DC5" s="46"/>
       <c r="DD5" s="51"/>
-      <c r="DE5" s="47"/>
-      <c r="DF5" s="47"/>
-      <c r="DG5" s="47"/>
-      <c r="DH5" s="47"/>
-      <c r="DI5" s="47"/>
-      <c r="DJ5" s="47"/>
-      <c r="DK5" s="47"/>
-      <c r="DL5" s="47"/>
-      <c r="DM5" s="47"/>
-      <c r="DN5" s="47"/>
-      <c r="DO5" s="47"/>
-      <c r="DP5" s="47"/>
-      <c r="DQ5" s="47"/>
-      <c r="DR5" s="47"/>
-      <c r="DS5" s="47"/>
-      <c r="DT5" s="47"/>
-      <c r="DU5" s="47"/>
-      <c r="DV5" s="47"/>
-      <c r="DW5" s="47"/>
-      <c r="DX5" s="47"/>
-      <c r="DY5" s="47"/>
-      <c r="DZ5" s="47"/>
-      <c r="EA5" s="47"/>
-      <c r="EB5" s="47"/>
-      <c r="EC5" s="46"/>
-      <c r="ED5" s="46"/>
-      <c r="EE5" s="46"/>
-      <c r="EF5" s="46"/>
-      <c r="EG5" s="46"/>
-      <c r="EH5" s="46"/>
-      <c r="EI5" s="46"/>
-      <c r="EJ5" s="46"/>
-      <c r="EK5" s="46"/>
-      <c r="EL5" s="46"/>
-      <c r="EM5" s="46"/>
-      <c r="EN5" s="46"/>
-      <c r="EO5" s="46"/>
-      <c r="EP5" s="46"/>
-      <c r="EQ5" s="46"/>
-      <c r="ER5" s="46"/>
-      <c r="ES5" s="46"/>
-      <c r="ET5" s="46"/>
+      <c r="DE5" s="46"/>
+      <c r="DF5" s="46"/>
+      <c r="DG5" s="46"/>
+      <c r="DH5" s="46"/>
+      <c r="DI5" s="46"/>
+      <c r="DJ5" s="46"/>
+      <c r="DK5" s="46"/>
+      <c r="DL5" s="46"/>
+      <c r="DM5" s="46"/>
+      <c r="DN5" s="46"/>
+      <c r="DO5" s="46"/>
+      <c r="DP5" s="46"/>
+      <c r="DQ5" s="46"/>
+      <c r="DR5" s="46"/>
+      <c r="DS5" s="46"/>
+      <c r="DT5" s="46"/>
+      <c r="DU5" s="46"/>
+      <c r="DV5" s="46"/>
+      <c r="DW5" s="46"/>
+      <c r="DX5" s="46"/>
+      <c r="DY5" s="46"/>
+      <c r="DZ5" s="46"/>
+      <c r="EA5" s="46"/>
+      <c r="EB5" s="46"/>
+      <c r="EC5" s="45"/>
+      <c r="ED5" s="45"/>
+      <c r="EE5" s="45"/>
+      <c r="EF5" s="45"/>
+      <c r="EG5" s="45"/>
+      <c r="EH5" s="45"/>
+      <c r="EI5" s="45"/>
+      <c r="EJ5" s="45"/>
+      <c r="EK5" s="45"/>
+      <c r="EL5" s="45"/>
+      <c r="EM5" s="45"/>
+      <c r="EN5" s="45"/>
+      <c r="EO5" s="45"/>
+      <c r="EP5" s="45"/>
+      <c r="EQ5" s="45"/>
+      <c r="ER5" s="45"/>
+      <c r="ES5" s="45"/>
+      <c r="ET5" s="45"/>
+      <c r="EU5" s="45"/>
     </row>
-    <row r="6" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10806,9 +10825,12 @@
       <c r="ET6" s="28">
         <v>149</v>
       </c>
-      <c r="EU6" s="1"/>
+      <c r="EU6" s="28">
+        <v>147</v>
+      </c>
+      <c r="EV6" s="1"/>
     </row>
-    <row r="7" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11256,8 +11278,11 @@
       <c r="ET7" s="15">
         <v>2</v>
       </c>
+      <c r="EU7" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11705,8 +11730,11 @@
       <c r="ET8" s="28">
         <v>30</v>
       </c>
+      <c r="EU8" s="28">
+        <v>39</v>
+      </c>
     </row>
-    <row r="9" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12155,8 +12183,11 @@
       <c r="ET9" s="15">
         <v>117</v>
       </c>
+      <c r="EU9" s="15">
+        <v>133</v>
+      </c>
     </row>
-    <row r="10" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12602,8 +12633,11 @@
       <c r="ET10" s="15">
         <v>1</v>
       </c>
+      <c r="EU10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13051,8 +13085,11 @@
       <c r="ET11" s="15">
         <v>13</v>
       </c>
+      <c r="EU11" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13500,8 +13537,11 @@
       <c r="ET12" s="15">
         <v>13</v>
       </c>
+      <c r="EU12" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -13949,9 +13989,12 @@
       <c r="ET13" s="15">
         <v>51</v>
       </c>
-      <c r="EU13" s="1"/>
+      <c r="EU13" s="15">
+        <v>44</v>
+      </c>
+      <c r="EV13" s="1"/>
     </row>
-    <row r="14" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14399,8 +14442,11 @@
       <c r="ET14" s="15">
         <v>48</v>
       </c>
+      <c r="EU14" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="15" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -14848,8 +14894,11 @@
       <c r="ET15" s="15">
         <v>17</v>
       </c>
+      <c r="EU15" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15298,9 +15347,12 @@
       <c r="ET16" s="28">
         <v>216</v>
       </c>
-      <c r="EU16" s="1"/>
+      <c r="EU16" s="28">
+        <v>171</v>
+      </c>
+      <c r="EV16" s="1"/>
     </row>
-    <row r="17" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15748,9 +15800,12 @@
       <c r="ET17" s="15">
         <v>172</v>
       </c>
-      <c r="EU17" s="1"/>
+      <c r="EU17" s="15">
+        <v>217</v>
+      </c>
+      <c r="EV17" s="1"/>
     </row>
-    <row r="18" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16199,9 +16254,12 @@
       <c r="ET18" s="34">
         <v>2637</v>
       </c>
-      <c r="EU18" s="1"/>
+      <c r="EU18" s="34">
+        <v>2469</v>
+      </c>
+      <c r="EV18" s="1"/>
     </row>
-    <row r="19" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="70" t="s">
         <v>27</v>
@@ -16650,9 +16708,12 @@
       <c r="ET19" s="15">
         <v>129</v>
       </c>
-      <c r="EU19" s="1"/>
+      <c r="EU19" s="15">
+        <v>99</v>
+      </c>
+      <c r="EV19" s="1"/>
     </row>
-    <row r="20" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
@@ -17099,9 +17160,12 @@
       <c r="ET20" s="28">
         <v>308</v>
       </c>
-      <c r="EU20" s="1"/>
+      <c r="EU20" s="28">
+        <v>283</v>
+      </c>
+      <c r="EV20" s="1"/>
     </row>
-    <row r="21" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
@@ -17548,9 +17612,12 @@
       <c r="ET21" s="15">
         <v>85</v>
       </c>
-      <c r="EU21" s="1"/>
+      <c r="EU21" s="15">
+        <v>69</v>
+      </c>
+      <c r="EV21" s="1"/>
     </row>
-    <row r="22" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -17998,8 +18065,11 @@
       <c r="ET22" s="15">
         <v>5</v>
       </c>
+      <c r="EU22" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18447,8 +18517,11 @@
       <c r="ET23" s="15">
         <v>3</v>
       </c>
+      <c r="EU23" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="24" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -18896,9 +18969,12 @@
       <c r="ET24" s="15">
         <v>14</v>
       </c>
-      <c r="EU24" s="1"/>
+      <c r="EU24" s="15">
+        <v>22</v>
+      </c>
+      <c r="EV24" s="1"/>
     </row>
-    <row r="25" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19346,8 +19422,11 @@
       <c r="ET25" s="15">
         <v>3</v>
       </c>
+      <c r="EU25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -19795,8 +19874,11 @@
       <c r="ET26" s="15">
         <v>51</v>
       </c>
+      <c r="EU26" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="27" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20244,8 +20326,11 @@
       <c r="ET27" s="15">
         <v>1</v>
       </c>
+      <c r="EU27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -20693,9 +20778,12 @@
       <c r="ET28" s="15">
         <v>2</v>
       </c>
-      <c r="EU28" s="1"/>
+      <c r="EU28" s="15">
+        <v>9</v>
+      </c>
+      <c r="EV28" s="1"/>
     </row>
-    <row r="29" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -21143,8 +21231,11 @@
       <c r="ET29" s="15">
         <v>7</v>
       </c>
+      <c r="EU29" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -21590,8 +21681,11 @@
       <c r="ET30" s="15">
         <v>76</v>
       </c>
+      <c r="EU30" s="15">
+        <v>66</v>
+      </c>
     </row>
-    <row r="31" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -22040,9 +22134,12 @@
       <c r="ET31" s="15">
         <v>221</v>
       </c>
-      <c r="EU31" s="1"/>
+      <c r="EU31" s="15">
+        <v>215</v>
+      </c>
+      <c r="EV31" s="1"/>
     </row>
-    <row r="32" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22490,8 +22587,11 @@
       <c r="ET32" s="15">
         <v>6</v>
       </c>
+      <c r="EU32" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -22939,8 +23039,11 @@
       <c r="ET33" s="15">
         <v>1</v>
       </c>
+      <c r="EU33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23389,9 +23492,12 @@
       <c r="ET34" s="15">
         <v>163</v>
       </c>
-      <c r="EU34" s="1"/>
+      <c r="EU34" s="15">
+        <v>187</v>
+      </c>
+      <c r="EV34" s="1"/>
     </row>
-    <row r="35" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="70" t="s">
         <v>56</v>
@@ -23840,9 +23946,12 @@
       <c r="ET35" s="15">
         <v>516</v>
       </c>
-      <c r="EU35" s="1"/>
+      <c r="EU35" s="15">
+        <v>405</v>
+      </c>
+      <c r="EV35" s="1"/>
     </row>
-    <row r="36" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -24288,9 +24397,12 @@
       <c r="ET36" s="28">
         <v>78</v>
       </c>
-      <c r="EU36" s="1"/>
+      <c r="EU36" s="28">
+        <v>68</v>
+      </c>
+      <c r="EV36" s="1"/>
     </row>
-    <row r="37" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -24739,9 +24851,12 @@
       <c r="ET37" s="15">
         <v>117</v>
       </c>
-      <c r="EU37" s="1"/>
+      <c r="EU37" s="15">
+        <v>153</v>
+      </c>
+      <c r="EV37" s="1"/>
     </row>
-    <row r="38" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -25189,8 +25304,11 @@
       <c r="ET38" s="15">
         <v>43</v>
       </c>
+      <c r="EU38" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="39" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -25638,8 +25756,11 @@
       <c r="ET39" s="15">
         <v>19</v>
       </c>
+      <c r="EU39" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="40" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -26087,8 +26208,11 @@
       <c r="ET40" s="15">
         <v>2</v>
       </c>
+      <c r="EU40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -26536,8 +26660,11 @@
       <c r="ET41" s="15">
         <v>1</v>
       </c>
+      <c r="EU41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -26985,8 +27112,11 @@
       <c r="ET42" s="15">
         <v>31</v>
       </c>
+      <c r="EU42" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="43" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27434,8 +27564,11 @@
       <c r="ET43" s="28">
         <v>132</v>
       </c>
+      <c r="EU43" s="28">
+        <v>128</v>
+      </c>
     </row>
-    <row r="44" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -27883,8 +28016,11 @@
       <c r="ET44" s="15">
         <v>4</v>
       </c>
+      <c r="EU44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28332,9 +28468,12 @@
       <c r="ET45" s="15">
         <v>27</v>
       </c>
-      <c r="EU45" s="1"/>
+      <c r="EU45" s="15">
+        <v>26</v>
+      </c>
+      <c r="EV45" s="1"/>
     </row>
-    <row r="46" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -28782,8 +28921,11 @@
       <c r="ET46" s="15">
         <v>38</v>
       </c>
+      <c r="EU46" s="15">
+        <v>30</v>
+      </c>
     </row>
-    <row r="47" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -29231,8 +29373,11 @@
       <c r="ET47" s="15">
         <v>6</v>
       </c>
+      <c r="EU47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -29680,8 +29825,11 @@
       <c r="ET48" s="15">
         <v>60</v>
       </c>
+      <c r="EU48" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="49" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="70" t="s">
         <v>83</v>
@@ -30130,9 +30278,12 @@
       <c r="ET49" s="15">
         <v>159</v>
       </c>
-      <c r="EU49" s="1"/>
+      <c r="EU49" s="15">
+        <v>115</v>
+      </c>
+      <c r="EV49" s="1"/>
     </row>
-    <row r="50" spans="1:151" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -30578,9 +30729,12 @@
       <c r="ET50" s="15">
         <v>63</v>
       </c>
-      <c r="EU50" s="1"/>
+      <c r="EU50" s="15">
+        <v>62</v>
+      </c>
+      <c r="EV50" s="1"/>
     </row>
-    <row r="51" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -31028,8 +31182,11 @@
       <c r="ET51" s="15">
         <v>16</v>
       </c>
+      <c r="EU51" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="52" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -31477,8 +31634,11 @@
       <c r="ET52" s="15">
         <v>24</v>
       </c>
+      <c r="EU52" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="53" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -31926,8 +32086,11 @@
       <c r="ET53" s="15">
         <v>69</v>
       </c>
+      <c r="EU53" s="15">
+        <v>64</v>
+      </c>
     </row>
-    <row r="54" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -32375,8 +32538,11 @@
       <c r="ET54" s="15">
         <v>11</v>
       </c>
+      <c r="EU54" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -32824,8 +32990,11 @@
       <c r="ET55" s="15">
         <v>25</v>
       </c>
+      <c r="EU55" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="56" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -33273,8 +33442,11 @@
       <c r="ET56" s="15">
         <v>12</v>
       </c>
+      <c r="EU56" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="57" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -33722,8 +33894,11 @@
       <c r="ET57" s="15">
         <v>4</v>
       </c>
+      <c r="EU57" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -34201,7 +34376,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:ET58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:EU58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -34316,8 +34491,12 @@
         <f t="shared" si="10"/>
         <v>5998</v>
       </c>
+      <c r="EU58" s="14">
+        <f t="shared" si="10"/>
+        <v>5519</v>
+      </c>
     </row>
-    <row r="59" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -34401,7 +34580,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -34485,7 +34664,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:151" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -34570,7 +34749,7 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="165">
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -34720,8 +34899,13 @@
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="DE2:ET2"/>
-    <mergeCell ref="ER3:ET3"/>
+    <mergeCell ref="DE3:EQ3"/>
+    <mergeCell ref="DT4:DT5"/>
+    <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="ES4:ES5"/>
+    <mergeCell ref="DE2:EU2"/>
+    <mergeCell ref="ER3:EU3"/>
+    <mergeCell ref="EU4:EU5"/>
     <mergeCell ref="ET4:ET5"/>
     <mergeCell ref="EQ4:EQ5"/>
     <mergeCell ref="EP4:EP5"/>
@@ -34731,10 +34915,6 @@
     <mergeCell ref="EL4:EL5"/>
     <mergeCell ref="EJ4:EJ5"/>
     <mergeCell ref="ER4:ER5"/>
-    <mergeCell ref="DE3:EQ3"/>
-    <mergeCell ref="DT4:DT5"/>
-    <mergeCell ref="DP4:DP5"/>
-    <mergeCell ref="ES4:ES5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -34747,7 +34927,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:ET57">
+  <conditionalFormatting sqref="DP6:EU57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -34767,7 +34947,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:ET58"/>
+  <dimension ref="B1:EU58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -34790,11 +34970,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="150" width="10.875" style="1" customWidth="1"/>
-    <col min="151" max="16384" width="8.625" style="1"/>
+    <col min="106" max="151" width="10.875" style="1" customWidth="1"/>
+    <col min="152" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:150" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:151" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="82" t="s">
         <v>323</v>
       </c>
@@ -34871,168 +35051,170 @@
       <c r="EQ1" s="19"/>
       <c r="ER1" s="19"/>
       <c r="ES1" s="19"/>
-      <c r="ET1" s="19" t="s">
+      <c r="ET1" s="19"/>
+      <c r="EU1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:150" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:151" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="44"/>
-      <c r="AM2" s="44"/>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="44"/>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="44"/>
-      <c r="AU2" s="44"/>
-      <c r="AV2" s="44"/>
-      <c r="AW2" s="44"/>
-      <c r="AX2" s="44"/>
-      <c r="AY2" s="44"/>
-      <c r="AZ2" s="44"/>
-      <c r="BA2" s="44"/>
-      <c r="BB2" s="44"/>
-      <c r="BC2" s="44"/>
-      <c r="BD2" s="44" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="47"/>
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="47"/>
+      <c r="AG2" s="47"/>
+      <c r="AH2" s="47"/>
+      <c r="AI2" s="47"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="47"/>
+      <c r="AP2" s="47"/>
+      <c r="AQ2" s="47"/>
+      <c r="AR2" s="47"/>
+      <c r="AS2" s="47"/>
+      <c r="AT2" s="47"/>
+      <c r="AU2" s="47"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="47"/>
+      <c r="BB2" s="47"/>
+      <c r="BC2" s="47"/>
+      <c r="BD2" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="44"/>
-      <c r="BF2" s="44"/>
-      <c r="BG2" s="44"/>
-      <c r="BH2" s="44"/>
-      <c r="BI2" s="44"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="44"/>
-      <c r="BL2" s="44"/>
-      <c r="BM2" s="44"/>
-      <c r="BN2" s="44"/>
-      <c r="BO2" s="44"/>
-      <c r="BP2" s="44"/>
-      <c r="BQ2" s="44"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="44"/>
-      <c r="BT2" s="44"/>
-      <c r="BU2" s="44"/>
-      <c r="BV2" s="44"/>
-      <c r="BW2" s="44"/>
-      <c r="BX2" s="44"/>
-      <c r="BY2" s="44"/>
-      <c r="BZ2" s="44"/>
-      <c r="CA2" s="44"/>
-      <c r="CB2" s="44"/>
-      <c r="CC2" s="44"/>
-      <c r="CD2" s="44"/>
-      <c r="CE2" s="44"/>
-      <c r="CF2" s="44"/>
-      <c r="CG2" s="44"/>
-      <c r="CH2" s="44"/>
-      <c r="CI2" s="44"/>
-      <c r="CJ2" s="44"/>
-      <c r="CK2" s="44"/>
-      <c r="CL2" s="44"/>
-      <c r="CM2" s="44"/>
-      <c r="CN2" s="44"/>
-      <c r="CO2" s="44"/>
-      <c r="CP2" s="44"/>
-      <c r="CQ2" s="44"/>
-      <c r="CR2" s="44"/>
-      <c r="CS2" s="44"/>
-      <c r="CT2" s="44"/>
-      <c r="CU2" s="44"/>
-      <c r="CV2" s="44"/>
-      <c r="CW2" s="44"/>
-      <c r="CX2" s="44"/>
-      <c r="CY2" s="44"/>
-      <c r="CZ2" s="44"/>
-      <c r="DA2" s="44"/>
-      <c r="DB2" s="44"/>
-      <c r="DC2" s="44"/>
-      <c r="DD2" s="44" t="s">
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="47"/>
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
+      <c r="BJ2" s="47"/>
+      <c r="BK2" s="47"/>
+      <c r="BL2" s="47"/>
+      <c r="BM2" s="47"/>
+      <c r="BN2" s="47"/>
+      <c r="BO2" s="47"/>
+      <c r="BP2" s="47"/>
+      <c r="BQ2" s="47"/>
+      <c r="BR2" s="47"/>
+      <c r="BS2" s="47"/>
+      <c r="BT2" s="47"/>
+      <c r="BU2" s="47"/>
+      <c r="BV2" s="47"/>
+      <c r="BW2" s="47"/>
+      <c r="BX2" s="47"/>
+      <c r="BY2" s="47"/>
+      <c r="BZ2" s="47"/>
+      <c r="CA2" s="47"/>
+      <c r="CB2" s="47"/>
+      <c r="CC2" s="47"/>
+      <c r="CD2" s="47"/>
+      <c r="CE2" s="47"/>
+      <c r="CF2" s="47"/>
+      <c r="CG2" s="47"/>
+      <c r="CH2" s="47"/>
+      <c r="CI2" s="47"/>
+      <c r="CJ2" s="47"/>
+      <c r="CK2" s="47"/>
+      <c r="CL2" s="47"/>
+      <c r="CM2" s="47"/>
+      <c r="CN2" s="47"/>
+      <c r="CO2" s="47"/>
+      <c r="CP2" s="47"/>
+      <c r="CQ2" s="47"/>
+      <c r="CR2" s="47"/>
+      <c r="CS2" s="47"/>
+      <c r="CT2" s="47"/>
+      <c r="CU2" s="47"/>
+      <c r="CV2" s="47"/>
+      <c r="CW2" s="47"/>
+      <c r="CX2" s="47"/>
+      <c r="CY2" s="47"/>
+      <c r="CZ2" s="47"/>
+      <c r="DA2" s="47"/>
+      <c r="DB2" s="47"/>
+      <c r="DC2" s="47"/>
+      <c r="DD2" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="44"/>
-      <c r="DF2" s="44"/>
-      <c r="DG2" s="44"/>
-      <c r="DH2" s="44"/>
-      <c r="DI2" s="44"/>
-      <c r="DJ2" s="44"/>
-      <c r="DK2" s="44"/>
-      <c r="DL2" s="44"/>
-      <c r="DM2" s="44"/>
-      <c r="DN2" s="44"/>
-      <c r="DO2" s="44"/>
-      <c r="DP2" s="44"/>
-      <c r="DQ2" s="44"/>
-      <c r="DR2" s="44"/>
-      <c r="DS2" s="44"/>
-      <c r="DT2" s="44"/>
-      <c r="DU2" s="44"/>
-      <c r="DV2" s="44"/>
-      <c r="DW2" s="44"/>
-      <c r="DX2" s="44"/>
-      <c r="DY2" s="44"/>
-      <c r="DZ2" s="44"/>
-      <c r="EA2" s="44"/>
-      <c r="EB2" s="44"/>
-      <c r="EC2" s="44"/>
-      <c r="ED2" s="44"/>
-      <c r="EE2" s="44"/>
-      <c r="EF2" s="44"/>
-      <c r="EG2" s="44"/>
-      <c r="EH2" s="44"/>
-      <c r="EI2" s="44"/>
-      <c r="EJ2" s="44"/>
-      <c r="EK2" s="44"/>
-      <c r="EL2" s="44"/>
-      <c r="EM2" s="44"/>
-      <c r="EN2" s="44"/>
-      <c r="EO2" s="44"/>
-      <c r="EP2" s="44"/>
-      <c r="EQ2" s="44"/>
-      <c r="ER2" s="44"/>
-      <c r="ES2" s="44"/>
-      <c r="ET2" s="44"/>
+      <c r="DE2" s="47"/>
+      <c r="DF2" s="47"/>
+      <c r="DG2" s="47"/>
+      <c r="DH2" s="47"/>
+      <c r="DI2" s="47"/>
+      <c r="DJ2" s="47"/>
+      <c r="DK2" s="47"/>
+      <c r="DL2" s="47"/>
+      <c r="DM2" s="47"/>
+      <c r="DN2" s="47"/>
+      <c r="DO2" s="47"/>
+      <c r="DP2" s="47"/>
+      <c r="DQ2" s="47"/>
+      <c r="DR2" s="47"/>
+      <c r="DS2" s="47"/>
+      <c r="DT2" s="47"/>
+      <c r="DU2" s="47"/>
+      <c r="DV2" s="47"/>
+      <c r="DW2" s="47"/>
+      <c r="DX2" s="47"/>
+      <c r="DY2" s="47"/>
+      <c r="DZ2" s="47"/>
+      <c r="EA2" s="47"/>
+      <c r="EB2" s="47"/>
+      <c r="EC2" s="47"/>
+      <c r="ED2" s="47"/>
+      <c r="EE2" s="47"/>
+      <c r="EF2" s="47"/>
+      <c r="EG2" s="47"/>
+      <c r="EH2" s="47"/>
+      <c r="EI2" s="47"/>
+      <c r="EJ2" s="47"/>
+      <c r="EK2" s="47"/>
+      <c r="EL2" s="47"/>
+      <c r="EM2" s="47"/>
+      <c r="EN2" s="47"/>
+      <c r="EO2" s="47"/>
+      <c r="EP2" s="47"/>
+      <c r="EQ2" s="47"/>
+      <c r="ER2" s="47"/>
+      <c r="ES2" s="47"/>
+      <c r="ET2" s="47"/>
+      <c r="EU2" s="47"/>
     </row>
-    <row r="3" spans="2:150" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:151" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -35077,20 +35259,20 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="45" t="s">
+      <c r="AR3" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
+      <c r="AS3" s="44"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="44"/>
+      <c r="AW3" s="44"/>
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
       <c r="BD3" s="48" t="s">
         <v>322</v>
       </c>
@@ -35133,69 +35315,70 @@
       <c r="CO3" s="53"/>
       <c r="CP3" s="53"/>
       <c r="CQ3" s="54"/>
-      <c r="CR3" s="45" t="s">
+      <c r="CR3" s="44" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
-      <c r="DD3" s="45" t="s">
+      <c r="CS3" s="44"/>
+      <c r="CT3" s="44"/>
+      <c r="CU3" s="44"/>
+      <c r="CV3" s="44"/>
+      <c r="CW3" s="44"/>
+      <c r="CX3" s="44"/>
+      <c r="CY3" s="44"/>
+      <c r="CZ3" s="44"/>
+      <c r="DA3" s="44"/>
+      <c r="DB3" s="44"/>
+      <c r="DC3" s="44"/>
+      <c r="DD3" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="45"/>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DE3" s="44"/>
+      <c r="DF3" s="44"/>
+      <c r="DG3" s="44"/>
+      <c r="DH3" s="44"/>
+      <c r="DI3" s="44"/>
+      <c r="DJ3" s="44"/>
+      <c r="DK3" s="44"/>
+      <c r="DL3" s="44"/>
+      <c r="DM3" s="44"/>
+      <c r="DN3" s="44"/>
+      <c r="DO3" s="44"/>
+      <c r="DP3" s="44"/>
+      <c r="DQ3" s="44"/>
+      <c r="DR3" s="44"/>
+      <c r="DS3" s="44"/>
+      <c r="DT3" s="44"/>
+      <c r="DU3" s="44"/>
+      <c r="DV3" s="44"/>
+      <c r="DW3" s="44"/>
+      <c r="DX3" s="44"/>
+      <c r="DY3" s="44"/>
+      <c r="DZ3" s="44"/>
+      <c r="EA3" s="44"/>
+      <c r="EB3" s="44"/>
+      <c r="EC3" s="44"/>
+      <c r="ED3" s="44"/>
+      <c r="EE3" s="44"/>
+      <c r="EF3" s="44"/>
+      <c r="EG3" s="44"/>
+      <c r="EH3" s="44"/>
+      <c r="EI3" s="44"/>
+      <c r="EJ3" s="44"/>
+      <c r="EK3" s="44"/>
+      <c r="EL3" s="44"/>
+      <c r="EM3" s="44"/>
+      <c r="EN3" s="44"/>
+      <c r="EO3" s="44"/>
+      <c r="EP3" s="44"/>
+      <c r="EQ3" s="44"/>
+      <c r="ER3" s="44" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
+      <c r="ES3" s="44"/>
+      <c r="ET3" s="44"/>
+      <c r="EU3" s="44"/>
     </row>
-    <row r="4" spans="2:150" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:151" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -35514,55 +35697,55 @@
       <c r="DC4" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="DD4" s="46" t="s">
+      <c r="DD4" s="45" t="s">
         <v>307</v>
       </c>
-      <c r="DE4" s="46" t="s">
+      <c r="DE4" s="45" t="s">
         <v>309</v>
       </c>
-      <c r="DF4" s="46" t="s">
+      <c r="DF4" s="45" t="s">
         <v>311</v>
       </c>
-      <c r="DG4" s="46" t="s">
+      <c r="DG4" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="DH4" s="46" t="s">
+      <c r="DH4" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="DI4" s="46" t="s">
+      <c r="DI4" s="45" t="s">
         <v>317</v>
       </c>
-      <c r="DJ4" s="46" t="s">
+      <c r="DJ4" s="45" t="s">
         <v>319</v>
       </c>
-      <c r="DK4" s="46" t="s">
+      <c r="DK4" s="45" t="s">
         <v>327</v>
       </c>
-      <c r="DL4" s="46" t="s">
+      <c r="DL4" s="45" t="s">
         <v>329</v>
       </c>
       <c r="DM4" s="74" t="s">
         <v>331</v>
       </c>
-      <c r="DN4" s="46" t="s">
+      <c r="DN4" s="45" t="s">
         <v>333</v>
       </c>
-      <c r="DO4" s="46" t="s">
+      <c r="DO4" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="DP4" s="46" t="s">
+      <c r="DP4" s="45" t="s">
         <v>337</v>
       </c>
-      <c r="DQ4" s="46" t="s">
+      <c r="DQ4" s="45" t="s">
         <v>339</v>
       </c>
-      <c r="DR4" s="46" t="s">
+      <c r="DR4" s="45" t="s">
         <v>342</v>
       </c>
-      <c r="DS4" s="46" t="s">
+      <c r="DS4" s="45" t="s">
         <v>346</v>
       </c>
-      <c r="DT4" s="46" t="s">
+      <c r="DT4" s="45" t="s">
         <v>350</v>
       </c>
       <c r="DU4" s="74" t="s">
@@ -35580,71 +35763,74 @@
       <c r="DY4" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="DZ4" s="46" t="s">
+      <c r="DZ4" s="45" t="s">
         <v>364</v>
       </c>
-      <c r="EA4" s="46" t="s">
+      <c r="EA4" s="45" t="s">
         <v>373</v>
       </c>
-      <c r="EB4" s="46" t="s">
+      <c r="EB4" s="45" t="s">
         <v>376</v>
       </c>
-      <c r="EC4" s="46" t="s">
+      <c r="EC4" s="45" t="s">
         <v>380</v>
       </c>
-      <c r="ED4" s="46" t="s">
+      <c r="ED4" s="45" t="s">
         <v>383</v>
       </c>
-      <c r="EE4" s="46" t="s">
+      <c r="EE4" s="45" t="s">
         <v>385</v>
       </c>
-      <c r="EF4" s="46" t="s">
+      <c r="EF4" s="45" t="s">
         <v>387</v>
       </c>
-      <c r="EG4" s="46" t="s">
+      <c r="EG4" s="45" t="s">
         <v>388</v>
       </c>
-      <c r="EH4" s="46" t="s">
+      <c r="EH4" s="45" t="s">
         <v>390</v>
       </c>
-      <c r="EI4" s="46" t="s">
+      <c r="EI4" s="45" t="s">
         <v>392</v>
       </c>
-      <c r="EJ4" s="46" t="s">
+      <c r="EJ4" s="45" t="s">
         <v>396</v>
       </c>
-      <c r="EK4" s="46" t="s">
+      <c r="EK4" s="45" t="s">
         <v>397</v>
       </c>
-      <c r="EL4" s="46" t="s">
+      <c r="EL4" s="45" t="s">
         <v>399</v>
       </c>
-      <c r="EM4" s="46" t="s">
+      <c r="EM4" s="45" t="s">
         <v>401</v>
       </c>
-      <c r="EN4" s="46" t="s">
+      <c r="EN4" s="45" t="s">
         <v>403</v>
       </c>
-      <c r="EO4" s="46" t="s">
+      <c r="EO4" s="45" t="s">
         <v>406</v>
       </c>
-      <c r="EP4" s="46" t="s">
+      <c r="EP4" s="45" t="s">
         <v>408</v>
       </c>
-      <c r="EQ4" s="46" t="s">
+      <c r="EQ4" s="45" t="s">
         <v>410</v>
       </c>
-      <c r="ER4" s="46" t="s">
+      <c r="ER4" s="45" t="s">
         <v>413</v>
       </c>
-      <c r="ES4" s="46" t="s">
+      <c r="ES4" s="45" t="s">
         <v>417</v>
       </c>
-      <c r="ET4" s="46" t="s">
+      <c r="ET4" s="45" t="s">
         <v>419</v>
       </c>
+      <c r="EU4" s="45" t="s">
+        <v>421</v>
+      </c>
     </row>
-    <row r="5" spans="2:150" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:151" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="49"/>
@@ -35726,76 +35912,77 @@
       <c r="CB5" s="56"/>
       <c r="CC5" s="56"/>
       <c r="CD5" s="56"/>
-      <c r="CE5" s="47"/>
-      <c r="CF5" s="47"/>
-      <c r="CG5" s="47"/>
-      <c r="CH5" s="47"/>
-      <c r="CI5" s="47"/>
-      <c r="CJ5" s="47"/>
-      <c r="CK5" s="47"/>
-      <c r="CL5" s="47"/>
-      <c r="CM5" s="47"/>
-      <c r="CN5" s="47"/>
-      <c r="CO5" s="47"/>
-      <c r="CP5" s="47"/>
-      <c r="CQ5" s="47"/>
-      <c r="CR5" s="47"/>
-      <c r="CS5" s="47"/>
-      <c r="CT5" s="47"/>
-      <c r="CU5" s="47"/>
-      <c r="CV5" s="47"/>
-      <c r="CW5" s="47"/>
-      <c r="CX5" s="47"/>
-      <c r="CY5" s="47"/>
-      <c r="CZ5" s="47"/>
-      <c r="DA5" s="47"/>
-      <c r="DB5" s="47"/>
-      <c r="DC5" s="47"/>
-      <c r="DD5" s="47"/>
-      <c r="DE5" s="47"/>
-      <c r="DF5" s="47"/>
-      <c r="DG5" s="47"/>
-      <c r="DH5" s="47"/>
-      <c r="DI5" s="47"/>
-      <c r="DJ5" s="47"/>
-      <c r="DK5" s="47"/>
-      <c r="DL5" s="47"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
+      <c r="CW5" s="46"/>
+      <c r="CX5" s="46"/>
+      <c r="CY5" s="46"/>
+      <c r="CZ5" s="46"/>
+      <c r="DA5" s="46"/>
+      <c r="DB5" s="46"/>
+      <c r="DC5" s="46"/>
+      <c r="DD5" s="46"/>
+      <c r="DE5" s="46"/>
+      <c r="DF5" s="46"/>
+      <c r="DG5" s="46"/>
+      <c r="DH5" s="46"/>
+      <c r="DI5" s="46"/>
+      <c r="DJ5" s="46"/>
+      <c r="DK5" s="46"/>
+      <c r="DL5" s="46"/>
       <c r="DM5" s="75"/>
-      <c r="DN5" s="47"/>
-      <c r="DO5" s="47"/>
-      <c r="DP5" s="47"/>
-      <c r="DQ5" s="47"/>
-      <c r="DR5" s="47"/>
-      <c r="DS5" s="47"/>
-      <c r="DT5" s="47"/>
+      <c r="DN5" s="46"/>
+      <c r="DO5" s="46"/>
+      <c r="DP5" s="46"/>
+      <c r="DQ5" s="46"/>
+      <c r="DR5" s="46"/>
+      <c r="DS5" s="46"/>
+      <c r="DT5" s="46"/>
       <c r="DU5" s="75"/>
       <c r="DV5" s="75"/>
       <c r="DW5" s="75"/>
       <c r="DX5" s="75"/>
       <c r="DY5" s="75"/>
-      <c r="DZ5" s="47"/>
-      <c r="EA5" s="47"/>
-      <c r="EB5" s="47"/>
-      <c r="EC5" s="47"/>
-      <c r="ED5" s="47"/>
-      <c r="EE5" s="46"/>
-      <c r="EF5" s="46"/>
-      <c r="EG5" s="46"/>
-      <c r="EH5" s="46"/>
-      <c r="EI5" s="46"/>
-      <c r="EJ5" s="46"/>
-      <c r="EK5" s="46"/>
-      <c r="EL5" s="46"/>
-      <c r="EM5" s="46"/>
-      <c r="EN5" s="46"/>
-      <c r="EO5" s="46"/>
-      <c r="EP5" s="46"/>
-      <c r="EQ5" s="46"/>
-      <c r="ER5" s="46"/>
-      <c r="ES5" s="46"/>
-      <c r="ET5" s="46"/>
+      <c r="DZ5" s="46"/>
+      <c r="EA5" s="46"/>
+      <c r="EB5" s="46"/>
+      <c r="EC5" s="46"/>
+      <c r="ED5" s="46"/>
+      <c r="EE5" s="45"/>
+      <c r="EF5" s="45"/>
+      <c r="EG5" s="45"/>
+      <c r="EH5" s="45"/>
+      <c r="EI5" s="45"/>
+      <c r="EJ5" s="45"/>
+      <c r="EK5" s="45"/>
+      <c r="EL5" s="45"/>
+      <c r="EM5" s="45"/>
+      <c r="EN5" s="45"/>
+      <c r="EO5" s="45"/>
+      <c r="EP5" s="45"/>
+      <c r="EQ5" s="45"/>
+      <c r="ER5" s="45"/>
+      <c r="ES5" s="45"/>
+      <c r="ET5" s="45"/>
+      <c r="EU5" s="45"/>
     </row>
-    <row r="6" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -36243,8 +36430,11 @@
       <c r="ET6" s="28">
         <v>198</v>
       </c>
+      <c r="EU6" s="28">
+        <v>187</v>
+      </c>
     </row>
-    <row r="7" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -36692,8 +36882,11 @@
       <c r="ET7" s="15">
         <v>2</v>
       </c>
+      <c r="EU7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -37141,8 +37334,11 @@
       <c r="ET8" s="28">
         <v>9</v>
       </c>
+      <c r="EU8" s="28">
+        <v>8</v>
+      </c>
     </row>
-    <row r="9" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -37590,8 +37786,11 @@
       <c r="ET9" s="15">
         <v>63</v>
       </c>
+      <c r="EU9" s="15">
+        <v>81</v>
+      </c>
     </row>
-    <row r="10" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -38039,8 +38238,11 @@
       <c r="ET10" s="15">
         <v>0</v>
       </c>
+      <c r="EU10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -38488,8 +38690,11 @@
       <c r="ET11" s="15">
         <v>11</v>
       </c>
+      <c r="EU11" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -38937,8 +39142,11 @@
       <c r="ET12" s="15">
         <v>13</v>
       </c>
+      <c r="EU12" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -39386,8 +39594,11 @@
       <c r="ET13" s="15">
         <v>26</v>
       </c>
+      <c r="EU13" s="15">
+        <v>34</v>
+      </c>
     </row>
-    <row r="14" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -39835,8 +40046,11 @@
       <c r="ET14" s="15">
         <v>30</v>
       </c>
+      <c r="EU14" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="15" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -40284,8 +40498,11 @@
       <c r="ET15" s="15">
         <v>7</v>
       </c>
+      <c r="EU15" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="16" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -40733,8 +40950,11 @@
       <c r="ET16" s="28">
         <v>175</v>
       </c>
+      <c r="EU16" s="28">
+        <v>206</v>
+      </c>
     </row>
-    <row r="17" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -41182,8 +41402,11 @@
       <c r="ET17" s="15">
         <v>177</v>
       </c>
+      <c r="EU17" s="15">
+        <v>189</v>
+      </c>
     </row>
-    <row r="18" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -41631,8 +41854,11 @@
       <c r="ET18" s="34">
         <v>2632</v>
       </c>
+      <c r="EU18" s="34">
+        <v>2668</v>
+      </c>
     </row>
-    <row r="19" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="70" t="s">
         <v>27</v>
       </c>
@@ -42080,8 +42306,11 @@
       <c r="ET19" s="15">
         <v>133</v>
       </c>
+      <c r="EU19" s="15">
+        <v>119</v>
+      </c>
     </row>
-    <row r="20" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -42527,8 +42756,11 @@
       <c r="ET20" s="28">
         <v>291</v>
       </c>
+      <c r="EU20" s="28">
+        <v>310</v>
+      </c>
     </row>
-    <row r="21" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -42974,8 +43206,11 @@
       <c r="ET21" s="15">
         <v>45</v>
       </c>
+      <c r="EU21" s="15">
+        <v>66</v>
+      </c>
     </row>
-    <row r="22" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -43423,8 +43658,11 @@
       <c r="ET22" s="15">
         <v>12</v>
       </c>
+      <c r="EU22" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="23" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -43872,8 +44110,11 @@
       <c r="ET23" s="15">
         <v>3</v>
       </c>
+      <c r="EU23" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="24" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -44321,8 +44562,11 @@
       <c r="ET24" s="15">
         <v>7</v>
       </c>
+      <c r="EU24" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="25" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -44770,8 +45014,11 @@
       <c r="ET25" s="15">
         <v>0</v>
       </c>
+      <c r="EU25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -45219,8 +45466,11 @@
       <c r="ET26" s="15">
         <v>10</v>
       </c>
+      <c r="EU26" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="27" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -45668,8 +45918,11 @@
       <c r="ET27" s="15">
         <v>0</v>
       </c>
+      <c r="EU27" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -46117,8 +46370,11 @@
       <c r="ET28" s="15">
         <v>6</v>
       </c>
+      <c r="EU28" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -46566,8 +46822,11 @@
       <c r="ET29" s="15">
         <v>4</v>
       </c>
+      <c r="EU29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -47013,8 +47272,11 @@
       <c r="ET30" s="15">
         <v>21</v>
       </c>
+      <c r="EU30" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="31" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -47462,8 +47724,11 @@
       <c r="ET31" s="15">
         <v>44</v>
       </c>
+      <c r="EU31" s="15">
+        <v>73</v>
+      </c>
     </row>
-    <row r="32" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -47911,8 +48176,11 @@
       <c r="ET32" s="15">
         <v>1</v>
       </c>
+      <c r="EU32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -48360,8 +48628,11 @@
       <c r="ET33" s="15">
         <v>1</v>
       </c>
+      <c r="EU33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -48809,8 +49080,11 @@
       <c r="ET34" s="15">
         <v>108</v>
       </c>
+      <c r="EU34" s="15">
+        <v>116</v>
+      </c>
     </row>
-    <row r="35" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="70" t="s">
         <v>56</v>
       </c>
@@ -49258,8 +49532,11 @@
       <c r="ET35" s="15">
         <v>511</v>
       </c>
+      <c r="EU35" s="15">
+        <v>641</v>
+      </c>
     </row>
-    <row r="36" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -49705,8 +49982,11 @@
       <c r="ET36" s="28">
         <v>55</v>
       </c>
+      <c r="EU36" s="28">
+        <v>94</v>
+      </c>
     </row>
-    <row r="37" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -50154,8 +50434,11 @@
       <c r="ET37" s="15">
         <v>88</v>
       </c>
+      <c r="EU37" s="15">
+        <v>109</v>
+      </c>
     </row>
-    <row r="38" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -50603,8 +50886,11 @@
       <c r="ET38" s="15">
         <v>25</v>
       </c>
+      <c r="EU38" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="39" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -51052,8 +51338,11 @@
       <c r="ET39" s="15">
         <v>8</v>
       </c>
+      <c r="EU39" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="40" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -51501,8 +51790,11 @@
       <c r="ET40" s="15">
         <v>0</v>
       </c>
+      <c r="EU40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -51950,8 +52242,11 @@
       <c r="ET41" s="15">
         <v>0</v>
       </c>
+      <c r="EU41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -52399,8 +52694,11 @@
       <c r="ET42" s="15">
         <v>4</v>
       </c>
+      <c r="EU42" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="43" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -52848,8 +53146,11 @@
       <c r="ET43" s="28">
         <v>73</v>
       </c>
+      <c r="EU43" s="28">
+        <v>85</v>
+      </c>
     </row>
-    <row r="44" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -53297,8 +53598,11 @@
       <c r="ET44" s="15">
         <v>7</v>
       </c>
+      <c r="EU44" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="45" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -53746,8 +54050,11 @@
       <c r="ET45" s="15">
         <v>9</v>
       </c>
+      <c r="EU45" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -54195,8 +54502,11 @@
       <c r="ET46" s="15">
         <v>29</v>
       </c>
+      <c r="EU46" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -54644,8 +54954,11 @@
       <c r="ET47" s="15">
         <v>1</v>
       </c>
+      <c r="EU47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -55093,8 +55406,11 @@
       <c r="ET48" s="15">
         <v>15</v>
       </c>
+      <c r="EU48" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="70" t="s">
         <v>83</v>
       </c>
@@ -55542,8 +55858,11 @@
       <c r="ET49" s="15">
         <v>92</v>
       </c>
+      <c r="EU49" s="15">
+        <v>111</v>
+      </c>
     </row>
-    <row r="50" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -55989,8 +56308,11 @@
       <c r="ET50" s="15">
         <v>28</v>
       </c>
+      <c r="EU50" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="51" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -56438,8 +56760,11 @@
       <c r="ET51" s="15">
         <v>2</v>
       </c>
+      <c r="EU51" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -56887,8 +57212,11 @@
       <c r="ET52" s="15">
         <v>25</v>
       </c>
+      <c r="EU52" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -57336,8 +57664,11 @@
       <c r="ET53" s="15">
         <v>29</v>
       </c>
+      <c r="EU53" s="15">
+        <v>40</v>
+      </c>
     </row>
-    <row r="54" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -57785,8 +58116,11 @@
       <c r="ET54" s="15">
         <v>19</v>
       </c>
+      <c r="EU54" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="55" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -58234,8 +58568,11 @@
       <c r="ET55" s="15">
         <v>10</v>
       </c>
+      <c r="EU55" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="56" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -58683,8 +59020,11 @@
       <c r="ET56" s="15">
         <v>3</v>
       </c>
+      <c r="EU56" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -59132,8 +59472,11 @@
       <c r="ET57" s="15">
         <v>3</v>
       </c>
+      <c r="EU57" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="2:150" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -59602,7 +59945,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:ET58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:EU58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -59725,9 +60068,15 @@
         <f t="shared" si="8"/>
         <v>5065</v>
       </c>
+      <c r="EU58" s="14">
+        <f t="shared" si="8"/>
+        <v>5448</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="165">
+    <mergeCell ref="ER3:EU3"/>
+    <mergeCell ref="EU4:EU5"/>
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="CU4:CU5"/>
@@ -59749,7 +60098,6 @@
     <mergeCell ref="CL4:CL5"/>
     <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="DI4:DI5"/>
     <mergeCell ref="DR4:DR5"/>
     <mergeCell ref="DQ4:DQ5"/>
     <mergeCell ref="BB1:BC1"/>
@@ -59773,8 +60121,7 @@
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="DD2:EU2"/>
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D3:AQ3"/>
@@ -59797,7 +60144,6 @@
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="BY4:BY5"/>
@@ -59820,7 +60166,8 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="DO4:DO5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="CC4:CC5"/>
     <mergeCell ref="CE4:CE5"/>
@@ -59844,7 +60191,7 @@
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
     <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="DJ4:DJ5"/>
+    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AM4:AM5"/>
     <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AP4:AP5"/>
@@ -59868,13 +60215,12 @@
     <mergeCell ref="DX4:DX5"/>
     <mergeCell ref="DZ4:DZ5"/>
     <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="DO4:DO5"/>
     <mergeCell ref="EG4:EG5"/>
     <mergeCell ref="EE4:EE5"/>
     <mergeCell ref="DS4:DS5"/>
     <mergeCell ref="DV4:DV5"/>
     <mergeCell ref="EB4:EB5"/>
-    <mergeCell ref="DD2:ET2"/>
-    <mergeCell ref="ER3:ET3"/>
     <mergeCell ref="ET4:ET5"/>
     <mergeCell ref="ES4:ES5"/>
     <mergeCell ref="DD3:EQ3"/>
@@ -59892,6 +60238,8 @@
     <mergeCell ref="EI4:EI5"/>
     <mergeCell ref="EH4:EH5"/>
     <mergeCell ref="EQ4:EQ5"/>
+    <mergeCell ref="DJ4:DJ5"/>
+    <mergeCell ref="DI4:DI5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -59904,7 +60252,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:ET57">
+  <conditionalFormatting sqref="EH6:EU57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -59944,7 +60292,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CT61"/>
+  <dimension ref="A1:CU61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -59955,11 +60303,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="98" width="10.875" style="1" customWidth="1"/>
-    <col min="99" max="16384" width="8.625" style="1"/>
+    <col min="54" max="99" width="10.875" style="1" customWidth="1"/>
+    <col min="100" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:99" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -60032,11 +60380,12 @@
       <c r="CQ1" s="19"/>
       <c r="CR1" s="19"/>
       <c r="CS1" s="19"/>
-      <c r="CT1" s="19" t="s">
+      <c r="CT1" s="19"/>
+      <c r="CU1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:98" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:99" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -60093,53 +60442,54 @@
       <c r="BA2" s="52"/>
       <c r="BB2" s="52"/>
       <c r="BC2" s="88"/>
-      <c r="BD2" s="44" t="s">
+      <c r="BD2" s="47" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="44"/>
-      <c r="BF2" s="44"/>
-      <c r="BG2" s="44"/>
-      <c r="BH2" s="44"/>
-      <c r="BI2" s="44"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="44"/>
-      <c r="BL2" s="44"/>
-      <c r="BM2" s="44"/>
-      <c r="BN2" s="44"/>
-      <c r="BO2" s="44"/>
-      <c r="BP2" s="44"/>
-      <c r="BQ2" s="44"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="44"/>
-      <c r="BT2" s="44"/>
-      <c r="BU2" s="44"/>
-      <c r="BV2" s="44"/>
-      <c r="BW2" s="44"/>
-      <c r="BX2" s="44"/>
-      <c r="BY2" s="44"/>
-      <c r="BZ2" s="44"/>
-      <c r="CA2" s="44"/>
-      <c r="CB2" s="44"/>
-      <c r="CC2" s="44"/>
-      <c r="CD2" s="44"/>
-      <c r="CE2" s="44"/>
-      <c r="CF2" s="44"/>
-      <c r="CG2" s="44"/>
-      <c r="CH2" s="44"/>
-      <c r="CI2" s="44"/>
-      <c r="CJ2" s="44"/>
-      <c r="CK2" s="44"/>
-      <c r="CL2" s="44"/>
-      <c r="CM2" s="44"/>
-      <c r="CN2" s="44"/>
-      <c r="CO2" s="44"/>
-      <c r="CP2" s="44"/>
-      <c r="CQ2" s="44"/>
-      <c r="CR2" s="44"/>
-      <c r="CS2" s="44"/>
-      <c r="CT2" s="44"/>
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="47"/>
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
+      <c r="BJ2" s="47"/>
+      <c r="BK2" s="47"/>
+      <c r="BL2" s="47"/>
+      <c r="BM2" s="47"/>
+      <c r="BN2" s="47"/>
+      <c r="BO2" s="47"/>
+      <c r="BP2" s="47"/>
+      <c r="BQ2" s="47"/>
+      <c r="BR2" s="47"/>
+      <c r="BS2" s="47"/>
+      <c r="BT2" s="47"/>
+      <c r="BU2" s="47"/>
+      <c r="BV2" s="47"/>
+      <c r="BW2" s="47"/>
+      <c r="BX2" s="47"/>
+      <c r="BY2" s="47"/>
+      <c r="BZ2" s="47"/>
+      <c r="CA2" s="47"/>
+      <c r="CB2" s="47"/>
+      <c r="CC2" s="47"/>
+      <c r="CD2" s="47"/>
+      <c r="CE2" s="47"/>
+      <c r="CF2" s="47"/>
+      <c r="CG2" s="47"/>
+      <c r="CH2" s="47"/>
+      <c r="CI2" s="47"/>
+      <c r="CJ2" s="47"/>
+      <c r="CK2" s="47"/>
+      <c r="CL2" s="47"/>
+      <c r="CM2" s="47"/>
+      <c r="CN2" s="47"/>
+      <c r="CO2" s="47"/>
+      <c r="CP2" s="47"/>
+      <c r="CQ2" s="47"/>
+      <c r="CR2" s="47"/>
+      <c r="CS2" s="47"/>
+      <c r="CT2" s="47"/>
+      <c r="CU2" s="47"/>
     </row>
-    <row r="3" spans="1:98" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:99" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -60184,69 +60534,70 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="45" t="s">
+      <c r="AR3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="45" t="s">
+      <c r="AS3" s="44"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="44"/>
+      <c r="AW3" s="44"/>
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
+      <c r="BD3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="45"/>
-      <c r="BF3" s="45"/>
-      <c r="BG3" s="45"/>
-      <c r="BH3" s="45"/>
-      <c r="BI3" s="45"/>
-      <c r="BJ3" s="45"/>
-      <c r="BK3" s="45"/>
-      <c r="BL3" s="45"/>
-      <c r="BM3" s="45"/>
-      <c r="BN3" s="45"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="45"/>
-      <c r="BQ3" s="45"/>
-      <c r="BR3" s="45"/>
-      <c r="BS3" s="45"/>
-      <c r="BT3" s="45"/>
-      <c r="BU3" s="45"/>
-      <c r="BV3" s="45"/>
-      <c r="BW3" s="45"/>
-      <c r="BX3" s="45"/>
-      <c r="BY3" s="45"/>
-      <c r="BZ3" s="45"/>
-      <c r="CA3" s="45"/>
-      <c r="CB3" s="45"/>
-      <c r="CC3" s="45"/>
-      <c r="CD3" s="45"/>
-      <c r="CE3" s="45"/>
-      <c r="CF3" s="45"/>
-      <c r="CG3" s="45"/>
-      <c r="CH3" s="45"/>
-      <c r="CI3" s="45"/>
-      <c r="CJ3" s="45"/>
-      <c r="CK3" s="45"/>
-      <c r="CL3" s="45"/>
-      <c r="CM3" s="45"/>
-      <c r="CN3" s="45"/>
-      <c r="CO3" s="45"/>
-      <c r="CP3" s="45"/>
-      <c r="CQ3" s="45"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="44"/>
+      <c r="BJ3" s="44"/>
+      <c r="BK3" s="44"/>
+      <c r="BL3" s="44"/>
+      <c r="BM3" s="44"/>
+      <c r="BN3" s="44"/>
+      <c r="BO3" s="44"/>
+      <c r="BP3" s="44"/>
+      <c r="BQ3" s="44"/>
+      <c r="BR3" s="44"/>
+      <c r="BS3" s="44"/>
+      <c r="BT3" s="44"/>
+      <c r="BU3" s="44"/>
+      <c r="BV3" s="44"/>
+      <c r="BW3" s="44"/>
+      <c r="BX3" s="44"/>
+      <c r="BY3" s="44"/>
+      <c r="BZ3" s="44"/>
+      <c r="CA3" s="44"/>
+      <c r="CB3" s="44"/>
+      <c r="CC3" s="44"/>
+      <c r="CD3" s="44"/>
+      <c r="CE3" s="44"/>
+      <c r="CF3" s="44"/>
+      <c r="CG3" s="44"/>
+      <c r="CH3" s="44"/>
+      <c r="CI3" s="44"/>
+      <c r="CJ3" s="44"/>
+      <c r="CK3" s="44"/>
+      <c r="CL3" s="44"/>
+      <c r="CM3" s="44"/>
+      <c r="CN3" s="44"/>
+      <c r="CO3" s="44"/>
+      <c r="CP3" s="44"/>
+      <c r="CQ3" s="44"/>
+      <c r="CR3" s="44" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
+      <c r="CS3" s="44"/>
+      <c r="CT3" s="44"/>
+      <c r="CU3" s="44"/>
     </row>
-    <row r="4" spans="1:98" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:99" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -60409,137 +60760,140 @@
       <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="46" t="s">
+      <c r="BF4" s="45" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="46" t="s">
+      <c r="BG4" s="45" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="46" t="s">
+      <c r="BH4" s="45" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="46" t="s">
+      <c r="BI4" s="45" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="46" t="s">
+      <c r="BJ4" s="45" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="46" t="s">
+      <c r="BK4" s="45" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="46" t="s">
+      <c r="BL4" s="45" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="46" t="s">
+      <c r="BM4" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="46" t="s">
+      <c r="BN4" s="45" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="46" t="s">
+      <c r="BO4" s="45" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="46" t="s">
+      <c r="BP4" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="46" t="s">
+      <c r="BQ4" s="45" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="46" t="s">
+      <c r="BR4" s="45" t="s">
         <v>343</v>
       </c>
-      <c r="BS4" s="46" t="s">
+      <c r="BS4" s="45" t="s">
         <v>347</v>
       </c>
-      <c r="BT4" s="46" t="s">
+      <c r="BT4" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="46" t="s">
+      <c r="BU4" s="45" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="46" t="s">
+      <c r="BV4" s="45" t="s">
         <v>355</v>
       </c>
-      <c r="BW4" s="46" t="s">
+      <c r="BW4" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="46" t="s">
+      <c r="BX4" s="45" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="46" t="s">
+      <c r="BY4" s="45" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="46" t="s">
+      <c r="BZ4" s="45" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="46" t="s">
+      <c r="CA4" s="45" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="46" t="s">
+      <c r="CB4" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="46" t="s">
+      <c r="CC4" s="45" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="46" t="s">
+      <c r="CD4" s="45" t="s">
         <v>382</v>
       </c>
-      <c r="CE4" s="46" t="s">
+      <c r="CE4" s="45" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="46" t="s">
+      <c r="CF4" s="45" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="46" t="s">
+      <c r="CG4" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="46" t="s">
+      <c r="CH4" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="46" t="s">
+      <c r="CI4" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="46" t="s">
+      <c r="CJ4" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="46" t="s">
+      <c r="CK4" s="45" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="46" t="s">
+      <c r="CL4" s="45" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="46" t="s">
+      <c r="CM4" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="46" t="s">
+      <c r="CN4" s="45" t="s">
         <v>404</v>
       </c>
-      <c r="CO4" s="46" t="s">
+      <c r="CO4" s="45" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="46" t="s">
+      <c r="CP4" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="46" t="s">
+      <c r="CQ4" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="46" t="s">
+      <c r="CR4" s="45" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="46" t="s">
+      <c r="CS4" s="45" t="s">
         <v>416</v>
       </c>
-      <c r="CT4" s="46" t="s">
+      <c r="CT4" s="45" t="s">
         <v>418</v>
       </c>
+      <c r="CU4" s="45" t="s">
+        <v>420</v>
+      </c>
     </row>
-    <row r="5" spans="1:98" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:99" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -60569,76 +60923,77 @@
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
       <c r="AD5" s="56"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="47"/>
-      <c r="AR5" s="47"/>
-      <c r="AS5" s="47"/>
-      <c r="AT5" s="47"/>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="47"/>
-      <c r="BA5" s="47"/>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="47"/>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="47"/>
-      <c r="BM5" s="47"/>
-      <c r="BN5" s="47"/>
-      <c r="BO5" s="47"/>
-      <c r="BP5" s="47"/>
-      <c r="BQ5" s="47"/>
-      <c r="BR5" s="47"/>
-      <c r="BS5" s="47"/>
-      <c r="BT5" s="47"/>
-      <c r="BU5" s="47"/>
-      <c r="BV5" s="47"/>
-      <c r="BW5" s="47"/>
-      <c r="BX5" s="47"/>
-      <c r="BY5" s="47"/>
-      <c r="BZ5" s="46"/>
-      <c r="CA5" s="46"/>
-      <c r="CB5" s="46"/>
-      <c r="CC5" s="46"/>
-      <c r="CD5" s="46"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="46"/>
+      <c r="BM5" s="46"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="46"/>
+      <c r="BV5" s="46"/>
+      <c r="BW5" s="46"/>
+      <c r="BX5" s="46"/>
+      <c r="BY5" s="46"/>
+      <c r="BZ5" s="45"/>
+      <c r="CA5" s="45"/>
+      <c r="CB5" s="45"/>
+      <c r="CC5" s="45"/>
+      <c r="CD5" s="45"/>
+      <c r="CE5" s="45"/>
+      <c r="CF5" s="45"/>
+      <c r="CG5" s="45"/>
+      <c r="CH5" s="45"/>
+      <c r="CI5" s="45"/>
+      <c r="CJ5" s="45"/>
+      <c r="CK5" s="45"/>
+      <c r="CL5" s="45"/>
+      <c r="CM5" s="45"/>
+      <c r="CN5" s="45"/>
+      <c r="CO5" s="45"/>
+      <c r="CP5" s="45"/>
+      <c r="CQ5" s="45"/>
+      <c r="CR5" s="45"/>
+      <c r="CS5" s="45"/>
+      <c r="CT5" s="45"/>
+      <c r="CU5" s="45"/>
     </row>
-    <row r="6" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -60931,8 +61286,11 @@
       <c r="CT6" s="28">
         <v>27</v>
       </c>
+      <c r="CU6" s="28">
+        <v>28</v>
+      </c>
     </row>
-    <row r="7" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -61224,8 +61582,11 @@
       <c r="CT7" s="15">
         <v>1</v>
       </c>
+      <c r="CU7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -61517,8 +61878,11 @@
       <c r="CT8" s="28">
         <v>0</v>
       </c>
+      <c r="CU8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -61811,8 +62175,11 @@
       <c r="CT9" s="15">
         <v>16</v>
       </c>
+      <c r="CU9" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="10" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -62104,8 +62471,11 @@
       <c r="CT10" s="15">
         <v>0</v>
       </c>
+      <c r="CU10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -62397,8 +62767,11 @@
       <c r="CT11" s="15">
         <v>6</v>
       </c>
+      <c r="CU11" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -62690,8 +63063,11 @@
       <c r="CT12" s="15">
         <v>2</v>
       </c>
+      <c r="CU12" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -62983,8 +63359,11 @@
       <c r="CT13" s="15">
         <v>31</v>
       </c>
+      <c r="CU13" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="14" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -63276,8 +63655,11 @@
       <c r="CT14" s="15">
         <v>22</v>
       </c>
+      <c r="CU14" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -63569,8 +63951,11 @@
       <c r="CT15" s="15">
         <v>11</v>
       </c>
+      <c r="CU15" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -63863,8 +64248,11 @@
       <c r="CT16" s="28">
         <v>12</v>
       </c>
+      <c r="CU16" s="28">
+        <v>11</v>
+      </c>
     </row>
-    <row r="17" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -64156,8 +64544,11 @@
       <c r="CT17" s="15">
         <v>56</v>
       </c>
+      <c r="CU17" s="15">
+        <v>52</v>
+      </c>
     </row>
-    <row r="18" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -64450,8 +64841,11 @@
       <c r="CT18" s="34">
         <v>502</v>
       </c>
+      <c r="CU18" s="34">
+        <v>388</v>
+      </c>
     </row>
-    <row r="19" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -64744,8 +65138,11 @@
       <c r="CT19" s="15">
         <v>75</v>
       </c>
+      <c r="CU19" s="15">
+        <v>54</v>
+      </c>
     </row>
-    <row r="20" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -65036,8 +65433,11 @@
       <c r="CT20" s="28">
         <v>148</v>
       </c>
+      <c r="CU20" s="28">
+        <v>121</v>
+      </c>
     </row>
-    <row r="21" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -65328,8 +65728,11 @@
       <c r="CT21" s="15">
         <v>34</v>
       </c>
+      <c r="CU21" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="22" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -65621,8 +66024,11 @@
       <c r="CT22" s="15">
         <v>2</v>
       </c>
+      <c r="CU22" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -65914,8 +66320,11 @@
       <c r="CT23" s="15">
         <v>0</v>
       </c>
+      <c r="CU23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -66207,8 +66616,11 @@
       <c r="CT24" s="15">
         <v>3</v>
       </c>
+      <c r="CU24" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -66500,8 +66912,11 @@
       <c r="CT25" s="15">
         <v>1</v>
       </c>
+      <c r="CU25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -66793,8 +67208,11 @@
       <c r="CT26" s="15">
         <v>20</v>
       </c>
+      <c r="CU26" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -67086,8 +67504,11 @@
       <c r="CT27" s="15">
         <v>1</v>
       </c>
+      <c r="CU27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -67379,8 +67800,11 @@
       <c r="CT28" s="15">
         <v>0</v>
       </c>
+      <c r="CU28" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -67672,8 +68096,11 @@
       <c r="CT29" s="15">
         <v>4</v>
       </c>
+      <c r="CU29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -67963,8 +68390,11 @@
       <c r="CT30" s="15">
         <v>34</v>
       </c>
+      <c r="CU30" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -68257,8 +68687,11 @@
       <c r="CT31" s="15">
         <v>94</v>
       </c>
+      <c r="CU31" s="15">
+        <v>83</v>
+      </c>
     </row>
-    <row r="32" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -68550,8 +68983,11 @@
       <c r="CT32" s="15">
         <v>0</v>
       </c>
+      <c r="CU32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -68843,8 +69279,11 @@
       <c r="CT33" s="15">
         <v>1</v>
       </c>
+      <c r="CU33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -69137,8 +69576,11 @@
       <c r="CT34" s="15">
         <v>56</v>
       </c>
+      <c r="CU34" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="35" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -69431,8 +69873,11 @@
       <c r="CT35" s="15">
         <v>147</v>
       </c>
+      <c r="CU35" s="15">
+        <v>91</v>
+      </c>
     </row>
-    <row r="36" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -69722,8 +70167,11 @@
       <c r="CT36" s="28">
         <v>39</v>
       </c>
+      <c r="CU36" s="28">
+        <v>33</v>
+      </c>
     </row>
-    <row r="37" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -70016,8 +70464,11 @@
       <c r="CT37" s="15">
         <v>23</v>
       </c>
+      <c r="CU37" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="38" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -70309,8 +70760,11 @@
       <c r="CT38" s="15">
         <v>20</v>
       </c>
+      <c r="CU38" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="39" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -70602,8 +71056,11 @@
       <c r="CT39" s="15">
         <v>5</v>
       </c>
+      <c r="CU39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -70895,8 +71352,11 @@
       <c r="CT40" s="15">
         <v>2</v>
       </c>
+      <c r="CU40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -71188,8 +71648,11 @@
       <c r="CT41" s="15">
         <v>0</v>
       </c>
+      <c r="CU41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -71481,8 +71944,11 @@
       <c r="CT42" s="15">
         <v>15</v>
       </c>
+      <c r="CU42" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -71774,8 +72240,11 @@
       <c r="CT43" s="28">
         <v>54</v>
       </c>
+      <c r="CU43" s="28">
+        <v>50</v>
+      </c>
     </row>
-    <row r="44" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -72067,8 +72536,11 @@
       <c r="CT44" s="15">
         <v>1</v>
       </c>
+      <c r="CU44" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -72360,8 +72832,11 @@
       <c r="CT45" s="15">
         <v>11</v>
       </c>
+      <c r="CU45" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -72653,8 +73128,11 @@
       <c r="CT46" s="15">
         <v>12</v>
       </c>
+      <c r="CU46" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="47" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -72946,8 +73424,11 @@
       <c r="CT47" s="15">
         <v>2</v>
       </c>
+      <c r="CU47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -73239,8 +73720,11 @@
       <c r="CT48" s="15">
         <v>29</v>
       </c>
+      <c r="CU48" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="49" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -73533,8 +74017,11 @@
       <c r="CT49" s="15">
         <v>13</v>
       </c>
+      <c r="CU49" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="1:98" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -73824,8 +74311,11 @@
       <c r="CT50" s="15">
         <v>26</v>
       </c>
+      <c r="CU50" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="51" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -74117,8 +74607,11 @@
       <c r="CT51" s="15">
         <v>0</v>
       </c>
+      <c r="CU51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -74410,8 +74903,11 @@
       <c r="CT52" s="15">
         <v>4</v>
       </c>
+      <c r="CU52" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -74703,8 +75199,11 @@
       <c r="CT53" s="15">
         <v>20</v>
       </c>
+      <c r="CU53" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="54" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -74996,8 +75495,11 @@
       <c r="CT54" s="15">
         <v>3</v>
       </c>
+      <c r="CU54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -75289,8 +75791,11 @@
       <c r="CT55" s="15">
         <v>5</v>
       </c>
+      <c r="CU55" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -75582,8 +76087,11 @@
       <c r="CT56" s="15">
         <v>1</v>
       </c>
+      <c r="CU56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -75875,8 +76383,11 @@
       <c r="CT57" s="15">
         <v>0</v>
       </c>
+      <c r="CU57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -76146,7 +76657,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CT58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CU58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -76261,8 +76772,12 @@
         <f t="shared" si="8"/>
         <v>1591</v>
       </c>
+      <c r="CU58" s="14">
+        <f t="shared" si="8"/>
+        <v>1203</v>
+      </c>
     </row>
-    <row r="59" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -76295,7 +76810,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -76328,7 +76843,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:98" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -76362,7 +76877,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="109">
+    <mergeCell ref="BD2:CU2"/>
+    <mergeCell ref="CR3:CU3"/>
+    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F4:F5"/>
@@ -76384,9 +76902,6 @@
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="X4:X5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="P4:P5"/>
@@ -76408,6 +76923,10 @@
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B19:B21"/>
+    <mergeCell ref="BR4:BR5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="BY4:BY5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="N4:N5"/>
@@ -76417,6 +76936,19 @@
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="CH4:CH5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="CE4:CE5"/>
     <mergeCell ref="BE4:BE5"/>
     <mergeCell ref="BS4:BS5"/>
@@ -76431,24 +76963,11 @@
     <mergeCell ref="BU4:BU5"/>
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="BD2:CT2"/>
-    <mergeCell ref="CR3:CT3"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AL4:AL5"/>
     <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="AK4:AK5"/>
@@ -76466,14 +76985,11 @@
     <mergeCell ref="CA4:CA5"/>
     <mergeCell ref="CO4:CO5"/>
     <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CT57">
+  <conditionalFormatting sqref="CH6:CU57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -76482,7 +76998,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="98" max="66" man="1"/>
+    <brk id="99" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -76499,7 +77015,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CT57</xm:sqref>
+          <xm:sqref>BP6:CU57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -76512,7 +77028,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CY61"/>
+  <dimension ref="A1:CZ61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -76521,11 +77037,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="103" width="10.875" style="1" customWidth="1"/>
-    <col min="104" max="16384" width="8.625" style="1"/>
+    <col min="34" max="104" width="10.875" style="1" customWidth="1"/>
+    <col min="105" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:103" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:104" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -76598,12 +77114,13 @@
       <c r="CQ1" s="19"/>
       <c r="CR1" s="19"/>
       <c r="CS1" s="19"/>
-      <c r="CT1" s="19" t="s">
+      <c r="CT1" s="19"/>
+      <c r="CU1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="CU1" s="19"/>
+      <c r="CV1" s="19"/>
     </row>
-    <row r="2" spans="1:103" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:104" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -76660,58 +77177,59 @@
       <c r="BA2" s="52"/>
       <c r="BB2" s="52"/>
       <c r="BC2" s="88"/>
-      <c r="BD2" s="44" t="s">
+      <c r="BD2" s="47" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="44"/>
-      <c r="BF2" s="44"/>
-      <c r="BG2" s="44"/>
-      <c r="BH2" s="44"/>
-      <c r="BI2" s="44"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="44"/>
-      <c r="BL2" s="44"/>
-      <c r="BM2" s="44"/>
-      <c r="BN2" s="44"/>
-      <c r="BO2" s="44"/>
-      <c r="BP2" s="44"/>
-      <c r="BQ2" s="44"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="44"/>
-      <c r="BT2" s="44"/>
-      <c r="BU2" s="44"/>
-      <c r="BV2" s="44"/>
-      <c r="BW2" s="44"/>
-      <c r="BX2" s="44"/>
-      <c r="BY2" s="44"/>
-      <c r="BZ2" s="44"/>
-      <c r="CA2" s="44"/>
-      <c r="CB2" s="44"/>
-      <c r="CC2" s="44"/>
-      <c r="CD2" s="44"/>
-      <c r="CE2" s="44"/>
-      <c r="CF2" s="44"/>
-      <c r="CG2" s="44"/>
-      <c r="CH2" s="44"/>
-      <c r="CI2" s="44"/>
-      <c r="CJ2" s="44"/>
-      <c r="CK2" s="44"/>
-      <c r="CL2" s="44"/>
-      <c r="CM2" s="44"/>
-      <c r="CN2" s="44"/>
-      <c r="CO2" s="44"/>
-      <c r="CP2" s="44"/>
-      <c r="CQ2" s="44"/>
-      <c r="CR2" s="44"/>
-      <c r="CS2" s="44"/>
-      <c r="CT2" s="44"/>
-      <c r="CU2" s="20"/>
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="47"/>
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
+      <c r="BJ2" s="47"/>
+      <c r="BK2" s="47"/>
+      <c r="BL2" s="47"/>
+      <c r="BM2" s="47"/>
+      <c r="BN2" s="47"/>
+      <c r="BO2" s="47"/>
+      <c r="BP2" s="47"/>
+      <c r="BQ2" s="47"/>
+      <c r="BR2" s="47"/>
+      <c r="BS2" s="47"/>
+      <c r="BT2" s="47"/>
+      <c r="BU2" s="47"/>
+      <c r="BV2" s="47"/>
+      <c r="BW2" s="47"/>
+      <c r="BX2" s="47"/>
+      <c r="BY2" s="47"/>
+      <c r="BZ2" s="47"/>
+      <c r="CA2" s="47"/>
+      <c r="CB2" s="47"/>
+      <c r="CC2" s="47"/>
+      <c r="CD2" s="47"/>
+      <c r="CE2" s="47"/>
+      <c r="CF2" s="47"/>
+      <c r="CG2" s="47"/>
+      <c r="CH2" s="47"/>
+      <c r="CI2" s="47"/>
+      <c r="CJ2" s="47"/>
+      <c r="CK2" s="47"/>
+      <c r="CL2" s="47"/>
+      <c r="CM2" s="47"/>
+      <c r="CN2" s="47"/>
+      <c r="CO2" s="47"/>
+      <c r="CP2" s="47"/>
+      <c r="CQ2" s="47"/>
+      <c r="CR2" s="47"/>
+      <c r="CS2" s="47"/>
+      <c r="CT2" s="47"/>
+      <c r="CU2" s="47"/>
       <c r="CV2" s="20"/>
       <c r="CW2" s="20"/>
       <c r="CX2" s="20"/>
       <c r="CY2" s="20"/>
+      <c r="CZ2" s="20"/>
     </row>
-    <row r="3" spans="1:103" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:104" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -76756,74 +77274,75 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="45" t="s">
+      <c r="AR3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="45" t="s">
+      <c r="AS3" s="44"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="44"/>
+      <c r="AW3" s="44"/>
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
+      <c r="BD3" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="45"/>
-      <c r="BF3" s="45"/>
-      <c r="BG3" s="45"/>
-      <c r="BH3" s="45"/>
-      <c r="BI3" s="45"/>
-      <c r="BJ3" s="45"/>
-      <c r="BK3" s="45"/>
-      <c r="BL3" s="45"/>
-      <c r="BM3" s="45"/>
-      <c r="BN3" s="45"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="45"/>
-      <c r="BQ3" s="45"/>
-      <c r="BR3" s="45"/>
-      <c r="BS3" s="45"/>
-      <c r="BT3" s="45"/>
-      <c r="BU3" s="45"/>
-      <c r="BV3" s="45"/>
-      <c r="BW3" s="45"/>
-      <c r="BX3" s="45"/>
-      <c r="BY3" s="45"/>
-      <c r="BZ3" s="45"/>
-      <c r="CA3" s="45"/>
-      <c r="CB3" s="45"/>
-      <c r="CC3" s="45"/>
-      <c r="CD3" s="45"/>
-      <c r="CE3" s="45"/>
-      <c r="CF3" s="45"/>
-      <c r="CG3" s="45"/>
-      <c r="CH3" s="45"/>
-      <c r="CI3" s="45"/>
-      <c r="CJ3" s="45"/>
-      <c r="CK3" s="45"/>
-      <c r="CL3" s="45"/>
-      <c r="CM3" s="45"/>
-      <c r="CN3" s="45"/>
-      <c r="CO3" s="45"/>
-      <c r="CP3" s="45"/>
-      <c r="CQ3" s="45"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="44"/>
+      <c r="BJ3" s="44"/>
+      <c r="BK3" s="44"/>
+      <c r="BL3" s="44"/>
+      <c r="BM3" s="44"/>
+      <c r="BN3" s="44"/>
+      <c r="BO3" s="44"/>
+      <c r="BP3" s="44"/>
+      <c r="BQ3" s="44"/>
+      <c r="BR3" s="44"/>
+      <c r="BS3" s="44"/>
+      <c r="BT3" s="44"/>
+      <c r="BU3" s="44"/>
+      <c r="BV3" s="44"/>
+      <c r="BW3" s="44"/>
+      <c r="BX3" s="44"/>
+      <c r="BY3" s="44"/>
+      <c r="BZ3" s="44"/>
+      <c r="CA3" s="44"/>
+      <c r="CB3" s="44"/>
+      <c r="CC3" s="44"/>
+      <c r="CD3" s="44"/>
+      <c r="CE3" s="44"/>
+      <c r="CF3" s="44"/>
+      <c r="CG3" s="44"/>
+      <c r="CH3" s="44"/>
+      <c r="CI3" s="44"/>
+      <c r="CJ3" s="44"/>
+      <c r="CK3" s="44"/>
+      <c r="CL3" s="44"/>
+      <c r="CM3" s="44"/>
+      <c r="CN3" s="44"/>
+      <c r="CO3" s="44"/>
+      <c r="CP3" s="44"/>
+      <c r="CQ3" s="44"/>
+      <c r="CR3" s="44" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="21"/>
+      <c r="CS3" s="44"/>
+      <c r="CT3" s="44"/>
+      <c r="CU3" s="44"/>
       <c r="CV3" s="21"/>
       <c r="CW3" s="21"/>
       <c r="CX3" s="21"/>
       <c r="CY3" s="21"/>
+      <c r="CZ3" s="21"/>
     </row>
-    <row r="4" spans="1:103" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:104" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -76986,142 +77505,145 @@
       <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="46" t="s">
+      <c r="BF4" s="45" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="46" t="s">
+      <c r="BG4" s="45" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="46" t="s">
+      <c r="BH4" s="45" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="46" t="s">
+      <c r="BI4" s="45" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="46" t="s">
+      <c r="BJ4" s="45" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="46" t="s">
+      <c r="BK4" s="45" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="46" t="s">
+      <c r="BL4" s="45" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="46" t="s">
+      <c r="BM4" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="46" t="s">
+      <c r="BN4" s="45" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="46" t="s">
+      <c r="BO4" s="45" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="46" t="s">
+      <c r="BP4" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="46" t="s">
+      <c r="BQ4" s="45" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="46" t="s">
+      <c r="BR4" s="45" t="s">
         <v>344</v>
       </c>
-      <c r="BS4" s="46" t="s">
+      <c r="BS4" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="BT4" s="46" t="s">
+      <c r="BT4" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="46" t="s">
+      <c r="BU4" s="45" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="46" t="s">
+      <c r="BV4" s="45" t="s">
         <v>356</v>
       </c>
-      <c r="BW4" s="46" t="s">
+      <c r="BW4" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="46" t="s">
+      <c r="BX4" s="45" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="46" t="s">
+      <c r="BY4" s="45" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="46" t="s">
+      <c r="BZ4" s="45" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="46" t="s">
+      <c r="CA4" s="45" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="46" t="s">
+      <c r="CB4" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="46" t="s">
+      <c r="CC4" s="45" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="46" t="s">
+      <c r="CD4" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="CE4" s="46" t="s">
+      <c r="CE4" s="45" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="46" t="s">
+      <c r="CF4" s="45" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="46" t="s">
+      <c r="CG4" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="46" t="s">
+      <c r="CH4" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="46" t="s">
+      <c r="CI4" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="46" t="s">
+      <c r="CJ4" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="46" t="s">
+      <c r="CK4" s="45" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="46" t="s">
+      <c r="CL4" s="45" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="46" t="s">
+      <c r="CM4" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="46" t="s">
+      <c r="CN4" s="45" t="s">
         <v>405</v>
       </c>
-      <c r="CO4" s="46" t="s">
+      <c r="CO4" s="45" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="46" t="s">
+      <c r="CP4" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="46" t="s">
+      <c r="CQ4" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="46" t="s">
+      <c r="CR4" s="45" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="46" t="s">
+      <c r="CS4" s="45" t="s">
         <v>416</v>
       </c>
-      <c r="CT4" s="46" t="s">
+      <c r="CT4" s="45" t="s">
         <v>418</v>
       </c>
-      <c r="CU4" s="89"/>
+      <c r="CU4" s="45" t="s">
+        <v>420</v>
+      </c>
       <c r="CV4" s="89"/>
       <c r="CW4" s="89"/>
       <c r="CX4" s="89"/>
       <c r="CY4" s="89"/>
+      <c r="CZ4" s="89"/>
     </row>
-    <row r="5" spans="1:103" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:104" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -77151,81 +77673,82 @@
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
       <c r="AD5" s="56"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="47"/>
-      <c r="AR5" s="47"/>
-      <c r="AS5" s="47"/>
-      <c r="AT5" s="47"/>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="47"/>
-      <c r="BA5" s="47"/>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="47"/>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="47"/>
-      <c r="BM5" s="47"/>
-      <c r="BN5" s="47"/>
-      <c r="BO5" s="47"/>
-      <c r="BP5" s="47"/>
-      <c r="BQ5" s="46"/>
-      <c r="BR5" s="46"/>
-      <c r="BS5" s="46"/>
-      <c r="BT5" s="46"/>
-      <c r="BU5" s="46"/>
-      <c r="BV5" s="46"/>
-      <c r="BW5" s="46"/>
-      <c r="BX5" s="46"/>
-      <c r="BY5" s="46"/>
-      <c r="BZ5" s="46"/>
-      <c r="CA5" s="46"/>
-      <c r="CB5" s="46"/>
-      <c r="CC5" s="46"/>
-      <c r="CD5" s="46"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="89"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="46"/>
+      <c r="BM5" s="46"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
+      <c r="BQ5" s="45"/>
+      <c r="BR5" s="45"/>
+      <c r="BS5" s="45"/>
+      <c r="BT5" s="45"/>
+      <c r="BU5" s="45"/>
+      <c r="BV5" s="45"/>
+      <c r="BW5" s="45"/>
+      <c r="BX5" s="45"/>
+      <c r="BY5" s="45"/>
+      <c r="BZ5" s="45"/>
+      <c r="CA5" s="45"/>
+      <c r="CB5" s="45"/>
+      <c r="CC5" s="45"/>
+      <c r="CD5" s="45"/>
+      <c r="CE5" s="45"/>
+      <c r="CF5" s="45"/>
+      <c r="CG5" s="45"/>
+      <c r="CH5" s="45"/>
+      <c r="CI5" s="45"/>
+      <c r="CJ5" s="45"/>
+      <c r="CK5" s="45"/>
+      <c r="CL5" s="45"/>
+      <c r="CM5" s="45"/>
+      <c r="CN5" s="45"/>
+      <c r="CO5" s="45"/>
+      <c r="CP5" s="45"/>
+      <c r="CQ5" s="45"/>
+      <c r="CR5" s="45"/>
+      <c r="CS5" s="45"/>
+      <c r="CT5" s="45"/>
+      <c r="CU5" s="45"/>
       <c r="CV5" s="89"/>
       <c r="CW5" s="89"/>
       <c r="CX5" s="89"/>
       <c r="CY5" s="89"/>
+      <c r="CZ5" s="89"/>
     </row>
-    <row r="6" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -77518,13 +78041,16 @@
       <c r="CT6" s="28">
         <v>122</v>
       </c>
-      <c r="CU6" s="22"/>
+      <c r="CU6" s="28">
+        <v>119</v>
+      </c>
       <c r="CV6" s="22"/>
       <c r="CW6" s="22"/>
       <c r="CX6" s="22"/>
       <c r="CY6" s="22"/>
+      <c r="CZ6" s="22"/>
     </row>
-    <row r="7" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -77816,13 +78342,16 @@
       <c r="CT7" s="15">
         <v>1</v>
       </c>
-      <c r="CU7" s="23"/>
+      <c r="CU7" s="15">
+        <v>2</v>
+      </c>
       <c r="CV7" s="23"/>
       <c r="CW7" s="23"/>
       <c r="CX7" s="23"/>
       <c r="CY7" s="23"/>
+      <c r="CZ7" s="23"/>
     </row>
-    <row r="8" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -78114,13 +78643,16 @@
       <c r="CT8" s="28">
         <v>30</v>
       </c>
-      <c r="CU8" s="23"/>
+      <c r="CU8" s="28">
+        <v>39</v>
+      </c>
       <c r="CV8" s="23"/>
       <c r="CW8" s="23"/>
       <c r="CX8" s="23"/>
       <c r="CY8" s="23"/>
+      <c r="CZ8" s="23"/>
     </row>
-    <row r="9" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -78413,13 +78945,16 @@
       <c r="CT9" s="15">
         <v>101</v>
       </c>
-      <c r="CU9" s="23"/>
+      <c r="CU9" s="15">
+        <v>115</v>
+      </c>
       <c r="CV9" s="23"/>
       <c r="CW9" s="23"/>
       <c r="CX9" s="23"/>
       <c r="CY9" s="23"/>
+      <c r="CZ9" s="23"/>
     </row>
-    <row r="10" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -78711,13 +79246,16 @@
       <c r="CT10" s="15">
         <v>1</v>
       </c>
-      <c r="CU10" s="23"/>
+      <c r="CU10" s="15">
+        <v>1</v>
+      </c>
       <c r="CV10" s="23"/>
       <c r="CW10" s="23"/>
       <c r="CX10" s="23"/>
       <c r="CY10" s="23"/>
+      <c r="CZ10" s="23"/>
     </row>
-    <row r="11" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -79009,13 +79547,16 @@
       <c r="CT11" s="15">
         <v>7</v>
       </c>
-      <c r="CU11" s="23"/>
+      <c r="CU11" s="15">
+        <v>10</v>
+      </c>
       <c r="CV11" s="23"/>
       <c r="CW11" s="23"/>
       <c r="CX11" s="23"/>
       <c r="CY11" s="23"/>
+      <c r="CZ11" s="23"/>
     </row>
-    <row r="12" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -79307,13 +79848,16 @@
       <c r="CT12" s="15">
         <v>11</v>
       </c>
-      <c r="CU12" s="23"/>
+      <c r="CU12" s="15">
+        <v>6</v>
+      </c>
       <c r="CV12" s="23"/>
       <c r="CW12" s="23"/>
       <c r="CX12" s="23"/>
       <c r="CY12" s="23"/>
+      <c r="CZ12" s="23"/>
     </row>
-    <row r="13" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -79605,13 +80149,16 @@
       <c r="CT13" s="15">
         <v>20</v>
       </c>
-      <c r="CU13" s="22"/>
+      <c r="CU13" s="15">
+        <v>29</v>
+      </c>
       <c r="CV13" s="22"/>
       <c r="CW13" s="22"/>
       <c r="CX13" s="22"/>
       <c r="CY13" s="22"/>
+      <c r="CZ13" s="22"/>
     </row>
-    <row r="14" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -79903,13 +80450,16 @@
       <c r="CT14" s="15">
         <v>26</v>
       </c>
-      <c r="CU14" s="23"/>
+      <c r="CU14" s="15">
+        <v>19</v>
+      </c>
       <c r="CV14" s="23"/>
       <c r="CW14" s="23"/>
       <c r="CX14" s="23"/>
       <c r="CY14" s="23"/>
+      <c r="CZ14" s="23"/>
     </row>
-    <row r="15" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -80201,13 +80751,16 @@
       <c r="CT15" s="15">
         <v>6</v>
       </c>
-      <c r="CU15" s="23"/>
+      <c r="CU15" s="15">
+        <v>6</v>
+      </c>
       <c r="CV15" s="23"/>
       <c r="CW15" s="23"/>
       <c r="CX15" s="23"/>
       <c r="CY15" s="23"/>
+      <c r="CZ15" s="23"/>
     </row>
-    <row r="16" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -80500,13 +81053,16 @@
       <c r="CT16" s="28">
         <v>204</v>
       </c>
-      <c r="CU16" s="22"/>
+      <c r="CU16" s="28">
+        <v>160</v>
+      </c>
       <c r="CV16" s="22"/>
       <c r="CW16" s="22"/>
       <c r="CX16" s="22"/>
       <c r="CY16" s="22"/>
+      <c r="CZ16" s="22"/>
     </row>
-    <row r="17" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -80798,13 +81354,16 @@
       <c r="CT17" s="15">
         <v>116</v>
       </c>
-      <c r="CU17" s="22"/>
+      <c r="CU17" s="15">
+        <v>165</v>
+      </c>
       <c r="CV17" s="22"/>
       <c r="CW17" s="22"/>
       <c r="CX17" s="22"/>
       <c r="CY17" s="22"/>
+      <c r="CZ17" s="22"/>
     </row>
-    <row r="18" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -81097,13 +81656,16 @@
       <c r="CT18" s="34">
         <v>2135</v>
       </c>
-      <c r="CU18" s="22"/>
+      <c r="CU18" s="34">
+        <v>2081</v>
+      </c>
       <c r="CV18" s="22"/>
       <c r="CW18" s="22"/>
       <c r="CX18" s="22"/>
       <c r="CY18" s="22"/>
+      <c r="CZ18" s="22"/>
     </row>
-    <row r="19" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -81396,13 +81958,16 @@
       <c r="CT19" s="15">
         <v>54</v>
       </c>
-      <c r="CU19" s="22"/>
+      <c r="CU19" s="15">
+        <v>45</v>
+      </c>
       <c r="CV19" s="22"/>
       <c r="CW19" s="22"/>
       <c r="CX19" s="22"/>
       <c r="CY19" s="22"/>
+      <c r="CZ19" s="22"/>
     </row>
-    <row r="20" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -81693,13 +82258,16 @@
       <c r="CT20" s="28">
         <v>160</v>
       </c>
-      <c r="CU20" s="22"/>
+      <c r="CU20" s="28">
+        <v>162</v>
+      </c>
       <c r="CV20" s="22"/>
       <c r="CW20" s="22"/>
       <c r="CX20" s="22"/>
       <c r="CY20" s="22"/>
+      <c r="CZ20" s="22"/>
     </row>
-    <row r="21" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -81990,13 +82558,16 @@
       <c r="CT21" s="15">
         <v>51</v>
       </c>
-      <c r="CU21" s="22"/>
+      <c r="CU21" s="15">
+        <v>47</v>
+      </c>
       <c r="CV21" s="22"/>
       <c r="CW21" s="22"/>
       <c r="CX21" s="22"/>
       <c r="CY21" s="22"/>
+      <c r="CZ21" s="22"/>
     </row>
-    <row r="22" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -82288,13 +82859,16 @@
       <c r="CT22" s="15">
         <v>3</v>
       </c>
-      <c r="CU22" s="23"/>
+      <c r="CU22" s="15">
+        <v>3</v>
+      </c>
       <c r="CV22" s="23"/>
       <c r="CW22" s="23"/>
       <c r="CX22" s="23"/>
       <c r="CY22" s="23"/>
+      <c r="CZ22" s="23"/>
     </row>
-    <row r="23" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -82586,13 +83160,16 @@
       <c r="CT23" s="15">
         <v>3</v>
       </c>
-      <c r="CU23" s="23"/>
+      <c r="CU23" s="15">
+        <v>10</v>
+      </c>
       <c r="CV23" s="23"/>
       <c r="CW23" s="23"/>
       <c r="CX23" s="23"/>
       <c r="CY23" s="23"/>
+      <c r="CZ23" s="23"/>
     </row>
-    <row r="24" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -82884,13 +83461,16 @@
       <c r="CT24" s="15">
         <v>11</v>
       </c>
-      <c r="CU24" s="22"/>
+      <c r="CU24" s="15">
+        <v>20</v>
+      </c>
       <c r="CV24" s="22"/>
       <c r="CW24" s="22"/>
       <c r="CX24" s="22"/>
       <c r="CY24" s="22"/>
+      <c r="CZ24" s="22"/>
     </row>
-    <row r="25" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -83182,13 +83762,16 @@
       <c r="CT25" s="15">
         <v>2</v>
       </c>
-      <c r="CU25" s="23"/>
+      <c r="CU25" s="15">
+        <v>0</v>
+      </c>
       <c r="CV25" s="23"/>
       <c r="CW25" s="23"/>
       <c r="CX25" s="23"/>
       <c r="CY25" s="23"/>
+      <c r="CZ25" s="23"/>
     </row>
-    <row r="26" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -83480,13 +84063,16 @@
       <c r="CT26" s="15">
         <v>31</v>
       </c>
-      <c r="CU26" s="23"/>
+      <c r="CU26" s="15">
+        <v>18</v>
+      </c>
       <c r="CV26" s="23"/>
       <c r="CW26" s="23"/>
       <c r="CX26" s="23"/>
       <c r="CY26" s="23"/>
+      <c r="CZ26" s="23"/>
     </row>
-    <row r="27" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -83778,13 +84364,16 @@
       <c r="CT27" s="15">
         <v>0</v>
       </c>
-      <c r="CU27" s="23"/>
+      <c r="CU27" s="15">
+        <v>0</v>
+      </c>
       <c r="CV27" s="23"/>
       <c r="CW27" s="23"/>
       <c r="CX27" s="23"/>
       <c r="CY27" s="23"/>
+      <c r="CZ27" s="23"/>
     </row>
-    <row r="28" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -84076,13 +84665,16 @@
       <c r="CT28" s="15">
         <v>2</v>
       </c>
-      <c r="CU28" s="22"/>
+      <c r="CU28" s="15">
+        <v>7</v>
+      </c>
       <c r="CV28" s="22"/>
       <c r="CW28" s="22"/>
       <c r="CX28" s="22"/>
       <c r="CY28" s="22"/>
+      <c r="CZ28" s="22"/>
     </row>
-    <row r="29" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -84374,13 +84966,16 @@
       <c r="CT29" s="15">
         <v>3</v>
       </c>
-      <c r="CU29" s="23"/>
+      <c r="CU29" s="15">
+        <v>2</v>
+      </c>
       <c r="CV29" s="23"/>
       <c r="CW29" s="23"/>
       <c r="CX29" s="23"/>
       <c r="CY29" s="23"/>
+      <c r="CZ29" s="23"/>
     </row>
-    <row r="30" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -84670,13 +85265,16 @@
       <c r="CT30" s="15">
         <v>42</v>
       </c>
-      <c r="CU30" s="23"/>
+      <c r="CU30" s="15">
+        <v>46</v>
+      </c>
       <c r="CV30" s="23"/>
       <c r="CW30" s="23"/>
       <c r="CX30" s="23"/>
       <c r="CY30" s="23"/>
+      <c r="CZ30" s="23"/>
     </row>
-    <row r="31" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -84969,13 +85567,16 @@
       <c r="CT31" s="15">
         <v>127</v>
       </c>
-      <c r="CU31" s="22"/>
+      <c r="CU31" s="15">
+        <v>132</v>
+      </c>
       <c r="CV31" s="22"/>
       <c r="CW31" s="22"/>
       <c r="CX31" s="22"/>
       <c r="CY31" s="22"/>
+      <c r="CZ31" s="22"/>
     </row>
-    <row r="32" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -85267,13 +85868,16 @@
       <c r="CT32" s="15">
         <v>6</v>
       </c>
-      <c r="CU32" s="23"/>
+      <c r="CU32" s="15">
+        <v>2</v>
+      </c>
       <c r="CV32" s="23"/>
       <c r="CW32" s="23"/>
       <c r="CX32" s="23"/>
       <c r="CY32" s="23"/>
+      <c r="CZ32" s="23"/>
     </row>
-    <row r="33" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -85565,13 +86169,16 @@
       <c r="CT33" s="15">
         <v>0</v>
       </c>
-      <c r="CU33" s="23"/>
+      <c r="CU33" s="15">
+        <v>0</v>
+      </c>
       <c r="CV33" s="23"/>
       <c r="CW33" s="23"/>
       <c r="CX33" s="23"/>
       <c r="CY33" s="23"/>
+      <c r="CZ33" s="23"/>
     </row>
-    <row r="34" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -85864,13 +86471,16 @@
       <c r="CT34" s="15">
         <v>107</v>
       </c>
-      <c r="CU34" s="22"/>
+      <c r="CU34" s="15">
+        <v>160</v>
+      </c>
       <c r="CV34" s="22"/>
       <c r="CW34" s="22"/>
       <c r="CX34" s="22"/>
       <c r="CY34" s="22"/>
+      <c r="CZ34" s="22"/>
     </row>
-    <row r="35" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -86163,13 +86773,16 @@
       <c r="CT35" s="15">
         <v>369</v>
       </c>
-      <c r="CU35" s="22"/>
+      <c r="CU35" s="15">
+        <v>314</v>
+      </c>
       <c r="CV35" s="22"/>
       <c r="CW35" s="22"/>
       <c r="CX35" s="22"/>
       <c r="CY35" s="22"/>
+      <c r="CZ35" s="22"/>
     </row>
-    <row r="36" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -86459,13 +87072,16 @@
       <c r="CT36" s="28">
         <v>39</v>
       </c>
-      <c r="CU36" s="22"/>
+      <c r="CU36" s="28">
+        <v>35</v>
+      </c>
       <c r="CV36" s="22"/>
       <c r="CW36" s="22"/>
       <c r="CX36" s="22"/>
       <c r="CY36" s="22"/>
+      <c r="CZ36" s="22"/>
     </row>
-    <row r="37" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -86758,13 +87374,16 @@
       <c r="CT37" s="15">
         <v>94</v>
       </c>
-      <c r="CU37" s="22"/>
+      <c r="CU37" s="15">
+        <v>127</v>
+      </c>
       <c r="CV37" s="22"/>
       <c r="CW37" s="22"/>
       <c r="CX37" s="22"/>
       <c r="CY37" s="22"/>
+      <c r="CZ37" s="22"/>
     </row>
-    <row r="38" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -87056,13 +87675,16 @@
       <c r="CT38" s="15">
         <v>23</v>
       </c>
-      <c r="CU38" s="23"/>
+      <c r="CU38" s="15">
+        <v>25</v>
+      </c>
       <c r="CV38" s="23"/>
       <c r="CW38" s="23"/>
       <c r="CX38" s="23"/>
       <c r="CY38" s="23"/>
+      <c r="CZ38" s="23"/>
     </row>
-    <row r="39" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -87354,13 +87976,16 @@
       <c r="CT39" s="15">
         <v>14</v>
       </c>
-      <c r="CU39" s="23"/>
+      <c r="CU39" s="15">
+        <v>14</v>
+      </c>
       <c r="CV39" s="23"/>
       <c r="CW39" s="23"/>
       <c r="CX39" s="23"/>
       <c r="CY39" s="23"/>
+      <c r="CZ39" s="23"/>
     </row>
-    <row r="40" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -87652,13 +88277,16 @@
       <c r="CT40" s="15">
         <v>0</v>
       </c>
-      <c r="CU40" s="23"/>
+      <c r="CU40" s="15">
+        <v>0</v>
+      </c>
       <c r="CV40" s="23"/>
       <c r="CW40" s="23"/>
       <c r="CX40" s="23"/>
       <c r="CY40" s="23"/>
+      <c r="CZ40" s="23"/>
     </row>
-    <row r="41" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -87950,13 +88578,16 @@
       <c r="CT41" s="15">
         <v>1</v>
       </c>
-      <c r="CU41" s="23"/>
+      <c r="CU41" s="15">
+        <v>0</v>
+      </c>
       <c r="CV41" s="23"/>
       <c r="CW41" s="23"/>
       <c r="CX41" s="23"/>
       <c r="CY41" s="23"/>
+      <c r="CZ41" s="23"/>
     </row>
-    <row r="42" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -88248,13 +88879,16 @@
       <c r="CT42" s="15">
         <v>16</v>
       </c>
-      <c r="CU42" s="23"/>
+      <c r="CU42" s="15">
+        <v>16</v>
+      </c>
       <c r="CV42" s="23"/>
       <c r="CW42" s="23"/>
       <c r="CX42" s="23"/>
       <c r="CY42" s="23"/>
+      <c r="CZ42" s="23"/>
     </row>
-    <row r="43" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -88546,13 +89180,16 @@
       <c r="CT43" s="28">
         <v>78</v>
       </c>
-      <c r="CU43" s="23"/>
+      <c r="CU43" s="28">
+        <v>78</v>
+      </c>
       <c r="CV43" s="23"/>
       <c r="CW43" s="23"/>
       <c r="CX43" s="23"/>
       <c r="CY43" s="23"/>
+      <c r="CZ43" s="23"/>
     </row>
-    <row r="44" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -88844,13 +89481,16 @@
       <c r="CT44" s="15">
         <v>3</v>
       </c>
-      <c r="CU44" s="23"/>
+      <c r="CU44" s="15">
+        <v>1</v>
+      </c>
       <c r="CV44" s="23"/>
       <c r="CW44" s="23"/>
       <c r="CX44" s="23"/>
       <c r="CY44" s="23"/>
+      <c r="CZ44" s="23"/>
     </row>
-    <row r="45" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -89142,13 +89782,16 @@
       <c r="CT45" s="15">
         <v>16</v>
       </c>
-      <c r="CU45" s="22"/>
+      <c r="CU45" s="15">
+        <v>18</v>
+      </c>
       <c r="CV45" s="22"/>
       <c r="CW45" s="22"/>
       <c r="CX45" s="22"/>
       <c r="CY45" s="22"/>
+      <c r="CZ45" s="22"/>
     </row>
-    <row r="46" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -89440,13 +90083,16 @@
       <c r="CT46" s="15">
         <v>26</v>
       </c>
-      <c r="CU46" s="23"/>
+      <c r="CU46" s="15">
+        <v>11</v>
+      </c>
       <c r="CV46" s="23"/>
       <c r="CW46" s="23"/>
       <c r="CX46" s="23"/>
       <c r="CY46" s="23"/>
+      <c r="CZ46" s="23"/>
     </row>
-    <row r="47" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -89738,13 +90384,16 @@
       <c r="CT47" s="15">
         <v>4</v>
       </c>
-      <c r="CU47" s="23"/>
+      <c r="CU47" s="15">
+        <v>1</v>
+      </c>
       <c r="CV47" s="23"/>
       <c r="CW47" s="23"/>
       <c r="CX47" s="23"/>
       <c r="CY47" s="23"/>
+      <c r="CZ47" s="23"/>
     </row>
-    <row r="48" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -90036,13 +90685,16 @@
       <c r="CT48" s="15">
         <v>31</v>
       </c>
-      <c r="CU48" s="23"/>
+      <c r="CU48" s="15">
+        <v>10</v>
+      </c>
       <c r="CV48" s="23"/>
       <c r="CW48" s="23"/>
       <c r="CX48" s="23"/>
       <c r="CY48" s="23"/>
+      <c r="CZ48" s="23"/>
     </row>
-    <row r="49" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -90335,13 +90987,16 @@
       <c r="CT49" s="15">
         <v>146</v>
       </c>
-      <c r="CU49" s="22"/>
+      <c r="CU49" s="15">
+        <v>110</v>
+      </c>
       <c r="CV49" s="22"/>
       <c r="CW49" s="22"/>
       <c r="CX49" s="22"/>
       <c r="CY49" s="22"/>
+      <c r="CZ49" s="22"/>
     </row>
-    <row r="50" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -90631,13 +91286,16 @@
       <c r="CT50" s="15">
         <v>37</v>
       </c>
-      <c r="CU50" s="22"/>
+      <c r="CU50" s="15">
+        <v>33</v>
+      </c>
       <c r="CV50" s="22"/>
       <c r="CW50" s="22"/>
       <c r="CX50" s="22"/>
       <c r="CY50" s="22"/>
+      <c r="CZ50" s="22"/>
     </row>
-    <row r="51" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -90929,13 +91587,16 @@
       <c r="CT51" s="15">
         <v>16</v>
       </c>
-      <c r="CU51" s="23"/>
+      <c r="CU51" s="15">
+        <v>20</v>
+      </c>
       <c r="CV51" s="23"/>
       <c r="CW51" s="23"/>
       <c r="CX51" s="23"/>
       <c r="CY51" s="23"/>
+      <c r="CZ51" s="23"/>
     </row>
-    <row r="52" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -91227,13 +91888,16 @@
       <c r="CT52" s="15">
         <v>20</v>
       </c>
-      <c r="CU52" s="23"/>
+      <c r="CU52" s="15">
+        <v>20</v>
+      </c>
       <c r="CV52" s="23"/>
       <c r="CW52" s="23"/>
       <c r="CX52" s="23"/>
       <c r="CY52" s="23"/>
+      <c r="CZ52" s="23"/>
     </row>
-    <row r="53" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -91525,13 +92189,16 @@
       <c r="CT53" s="15">
         <v>49</v>
       </c>
-      <c r="CU53" s="23"/>
+      <c r="CU53" s="15">
+        <v>47</v>
+      </c>
       <c r="CV53" s="23"/>
       <c r="CW53" s="23"/>
       <c r="CX53" s="23"/>
       <c r="CY53" s="23"/>
+      <c r="CZ53" s="23"/>
     </row>
-    <row r="54" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -91823,13 +92490,16 @@
       <c r="CT54" s="15">
         <v>8</v>
       </c>
-      <c r="CU54" s="23"/>
+      <c r="CU54" s="15">
+        <v>5</v>
+      </c>
       <c r="CV54" s="23"/>
       <c r="CW54" s="23"/>
       <c r="CX54" s="23"/>
       <c r="CY54" s="23"/>
+      <c r="CZ54" s="23"/>
     </row>
-    <row r="55" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -92121,13 +92791,16 @@
       <c r="CT55" s="15">
         <v>20</v>
       </c>
-      <c r="CU55" s="23"/>
+      <c r="CU55" s="15">
+        <v>18</v>
+      </c>
       <c r="CV55" s="23"/>
       <c r="CW55" s="23"/>
       <c r="CX55" s="23"/>
       <c r="CY55" s="23"/>
+      <c r="CZ55" s="23"/>
     </row>
-    <row r="56" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -92419,13 +93092,16 @@
       <c r="CT56" s="15">
         <v>11</v>
       </c>
-      <c r="CU56" s="23"/>
+      <c r="CU56" s="15">
+        <v>3</v>
+      </c>
       <c r="CV56" s="23"/>
       <c r="CW56" s="23"/>
       <c r="CX56" s="23"/>
       <c r="CY56" s="23"/>
+      <c r="CZ56" s="23"/>
     </row>
-    <row r="57" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -92717,13 +93393,16 @@
       <c r="CT57" s="15">
         <v>4</v>
       </c>
-      <c r="CU57" s="23"/>
+      <c r="CU57" s="15">
+        <v>4</v>
+      </c>
       <c r="CV57" s="23"/>
       <c r="CW57" s="23"/>
       <c r="CX57" s="23"/>
       <c r="CY57" s="23"/>
+      <c r="CZ57" s="23"/>
     </row>
-    <row r="58" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -92993,7 +93672,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CT58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CU58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -93108,13 +93787,17 @@
         <f t="shared" si="4"/>
         <v>4407</v>
       </c>
-      <c r="CU58" s="24"/>
+      <c r="CU58" s="14">
+        <f t="shared" si="4"/>
+        <v>4316</v>
+      </c>
       <c r="CV58" s="24"/>
       <c r="CW58" s="24"/>
       <c r="CX58" s="24"/>
       <c r="CY58" s="24"/>
+      <c r="CZ58" s="24"/>
     </row>
-    <row r="59" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -93147,7 +93830,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -93180,7 +93863,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -93214,22 +93897,22 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="CY4:CY5"/>
+  <mergeCells count="114">
+    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="CF4:CF5"/>
@@ -93281,6 +93964,9 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="BL4:BL5"/>
     <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AG4:AG5"/>
@@ -93300,6 +93986,11 @@
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="BK4:BK5"/>
     <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="BD2:CU2"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CL4:CL5"/>
@@ -93318,16 +94009,9 @@
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="BD2:CT2"/>
-    <mergeCell ref="CR3:CT3"/>
+    <mergeCell ref="CR3:CU3"/>
+    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="BD4:BD5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -93351,7 +94035,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CT57</xm:sqref>
+          <xm:sqref>BP6:CU57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050131-1\ＪＯＢ050131-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050207-2\ＪＯＢ050207-2\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CU$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CU$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EU$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EU$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CV$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CV$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EV$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EV$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="424">
   <si>
     <t>都道府県</t>
   </si>
@@ -4550,6 +4550,20 @@
 【1月第5週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1/30(月)～
+2/5(日)分
+【1月第5週
+2月第1週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1/31(月)～
+2/6(日)分
+【1月第6週
+2月第1週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5046,6 +5060,9 @@
     <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5053,9 +5070,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9350,7 +9364,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EV61"/>
+  <dimension ref="A1:EW61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9364,11 +9378,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="151" width="10.875" style="1" customWidth="1"/>
-    <col min="152" max="16384" width="8.625" style="1"/>
+    <col min="106" max="152" width="10.875" style="1" customWidth="1"/>
+    <col min="153" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:152" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:153" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9446,11 +9460,12 @@
       <c r="ER1" s="19"/>
       <c r="ES1" s="19"/>
       <c r="ET1" s="19"/>
-      <c r="EU1" s="19" t="s">
+      <c r="EU1" s="19"/>
+      <c r="EV1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:152" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:153" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -9562,97 +9577,98 @@
       <c r="DB2" s="52"/>
       <c r="DC2" s="52"/>
       <c r="DD2" s="52"/>
-      <c r="DE2" s="47" t="s">
+      <c r="DE2" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="47"/>
-      <c r="DG2" s="47"/>
-      <c r="DH2" s="47"/>
-      <c r="DI2" s="47"/>
-      <c r="DJ2" s="47"/>
-      <c r="DK2" s="47"/>
-      <c r="DL2" s="47"/>
-      <c r="DM2" s="47"/>
-      <c r="DN2" s="47"/>
-      <c r="DO2" s="47"/>
-      <c r="DP2" s="47"/>
-      <c r="DQ2" s="47"/>
-      <c r="DR2" s="47"/>
-      <c r="DS2" s="47"/>
-      <c r="DT2" s="47"/>
-      <c r="DU2" s="47"/>
-      <c r="DV2" s="47"/>
-      <c r="DW2" s="47"/>
-      <c r="DX2" s="47"/>
-      <c r="DY2" s="47"/>
-      <c r="DZ2" s="47"/>
-      <c r="EA2" s="47"/>
-      <c r="EB2" s="47"/>
-      <c r="EC2" s="47"/>
-      <c r="ED2" s="47"/>
-      <c r="EE2" s="47"/>
-      <c r="EF2" s="47"/>
-      <c r="EG2" s="47"/>
-      <c r="EH2" s="47"/>
-      <c r="EI2" s="47"/>
-      <c r="EJ2" s="47"/>
-      <c r="EK2" s="47"/>
-      <c r="EL2" s="47"/>
-      <c r="EM2" s="47"/>
-      <c r="EN2" s="47"/>
-      <c r="EO2" s="47"/>
-      <c r="EP2" s="47"/>
-      <c r="EQ2" s="47"/>
-      <c r="ER2" s="47"/>
-      <c r="ES2" s="47"/>
-      <c r="ET2" s="47"/>
-      <c r="EU2" s="47"/>
+      <c r="DF2" s="44"/>
+      <c r="DG2" s="44"/>
+      <c r="DH2" s="44"/>
+      <c r="DI2" s="44"/>
+      <c r="DJ2" s="44"/>
+      <c r="DK2" s="44"/>
+      <c r="DL2" s="44"/>
+      <c r="DM2" s="44"/>
+      <c r="DN2" s="44"/>
+      <c r="DO2" s="44"/>
+      <c r="DP2" s="44"/>
+      <c r="DQ2" s="44"/>
+      <c r="DR2" s="44"/>
+      <c r="DS2" s="44"/>
+      <c r="DT2" s="44"/>
+      <c r="DU2" s="44"/>
+      <c r="DV2" s="44"/>
+      <c r="DW2" s="44"/>
+      <c r="DX2" s="44"/>
+      <c r="DY2" s="44"/>
+      <c r="DZ2" s="44"/>
+      <c r="EA2" s="44"/>
+      <c r="EB2" s="44"/>
+      <c r="EC2" s="44"/>
+      <c r="ED2" s="44"/>
+      <c r="EE2" s="44"/>
+      <c r="EF2" s="44"/>
+      <c r="EG2" s="44"/>
+      <c r="EH2" s="44"/>
+      <c r="EI2" s="44"/>
+      <c r="EJ2" s="44"/>
+      <c r="EK2" s="44"/>
+      <c r="EL2" s="44"/>
+      <c r="EM2" s="44"/>
+      <c r="EN2" s="44"/>
+      <c r="EO2" s="44"/>
+      <c r="EP2" s="44"/>
+      <c r="EQ2" s="44"/>
+      <c r="ER2" s="44"/>
+      <c r="ES2" s="44"/>
+      <c r="ET2" s="44"/>
+      <c r="EU2" s="44"/>
+      <c r="EV2" s="44"/>
     </row>
-    <row r="3" spans="1:152" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:153" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="44"/>
-      <c r="AM3" s="44"/>
-      <c r="AN3" s="44"/>
-      <c r="AO3" s="44"/>
-      <c r="AP3" s="44"/>
-      <c r="AQ3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
       <c r="AR3" s="48" t="s">
         <v>216</v>
       </c>
@@ -9709,70 +9725,71 @@
       <c r="CO3" s="53"/>
       <c r="CP3" s="53"/>
       <c r="CQ3" s="54"/>
-      <c r="CR3" s="44" t="s">
+      <c r="CR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="44"/>
-      <c r="CT3" s="44"/>
-      <c r="CU3" s="44"/>
-      <c r="CV3" s="44"/>
-      <c r="CW3" s="44"/>
-      <c r="CX3" s="44"/>
-      <c r="CY3" s="44"/>
-      <c r="CZ3" s="44"/>
-      <c r="DA3" s="44"/>
-      <c r="DB3" s="44"/>
-      <c r="DC3" s="44"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
       <c r="DD3" s="48"/>
-      <c r="DE3" s="44" t="s">
+      <c r="DE3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="44"/>
-      <c r="DG3" s="44"/>
-      <c r="DH3" s="44"/>
-      <c r="DI3" s="44"/>
-      <c r="DJ3" s="44"/>
-      <c r="DK3" s="44"/>
-      <c r="DL3" s="44"/>
-      <c r="DM3" s="44"/>
-      <c r="DN3" s="44"/>
-      <c r="DO3" s="44"/>
-      <c r="DP3" s="44"/>
-      <c r="DQ3" s="44"/>
-      <c r="DR3" s="44"/>
-      <c r="DS3" s="44"/>
-      <c r="DT3" s="44"/>
-      <c r="DU3" s="44"/>
-      <c r="DV3" s="44"/>
-      <c r="DW3" s="44"/>
-      <c r="DX3" s="44"/>
-      <c r="DY3" s="44"/>
-      <c r="DZ3" s="44"/>
-      <c r="EA3" s="44"/>
-      <c r="EB3" s="44"/>
-      <c r="EC3" s="44"/>
-      <c r="ED3" s="44"/>
-      <c r="EE3" s="44"/>
-      <c r="EF3" s="44"/>
-      <c r="EG3" s="44"/>
-      <c r="EH3" s="44"/>
-      <c r="EI3" s="44"/>
-      <c r="EJ3" s="44"/>
-      <c r="EK3" s="44"/>
-      <c r="EL3" s="44"/>
-      <c r="EM3" s="44"/>
-      <c r="EN3" s="44"/>
-      <c r="EO3" s="44"/>
-      <c r="EP3" s="44"/>
-      <c r="EQ3" s="44"/>
-      <c r="ER3" s="44" t="s">
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="44"/>
-      <c r="ET3" s="44"/>
-      <c r="EU3" s="44"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
+      <c r="EU3" s="45"/>
+      <c r="EV3" s="45"/>
     </row>
-    <row r="4" spans="1:152" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:153" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -10094,137 +10111,140 @@
       <c r="DD4" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="DE4" s="45" t="s">
+      <c r="DE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="DF4" s="45" t="s">
+      <c r="DF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="DG4" s="45" t="s">
+      <c r="DG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="DH4" s="45" t="s">
+      <c r="DH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="DI4" s="45" t="s">
+      <c r="DI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="DJ4" s="45" t="s">
+      <c r="DJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="DK4" s="45" t="s">
+      <c r="DK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="DL4" s="45" t="s">
+      <c r="DL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="DM4" s="45" t="s">
+      <c r="DM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="DN4" s="45" t="s">
+      <c r="DN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="DO4" s="45" t="s">
+      <c r="DO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="DP4" s="45" t="s">
+      <c r="DP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="DQ4" s="45" t="s">
+      <c r="DQ4" s="46" t="s">
         <v>338</v>
       </c>
-      <c r="DR4" s="45" t="s">
+      <c r="DR4" s="46" t="s">
         <v>341</v>
       </c>
-      <c r="DS4" s="45" t="s">
+      <c r="DS4" s="46" t="s">
         <v>345</v>
       </c>
-      <c r="DT4" s="45" t="s">
+      <c r="DT4" s="46" t="s">
         <v>349</v>
       </c>
-      <c r="DU4" s="45" t="s">
+      <c r="DU4" s="46" t="s">
         <v>352</v>
       </c>
-      <c r="DV4" s="45" t="s">
+      <c r="DV4" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="DW4" s="45" t="s">
+      <c r="DW4" s="46" t="s">
         <v>357</v>
       </c>
-      <c r="DX4" s="45" t="s">
+      <c r="DX4" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="DY4" s="45" t="s">
+      <c r="DY4" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="DZ4" s="45" t="s">
+      <c r="DZ4" s="46" t="s">
         <v>363</v>
       </c>
-      <c r="EA4" s="45" t="s">
+      <c r="EA4" s="46" t="s">
         <v>371</v>
       </c>
-      <c r="EB4" s="45" t="s">
+      <c r="EB4" s="46" t="s">
         <v>375</v>
       </c>
-      <c r="EC4" s="45" t="s">
+      <c r="EC4" s="46" t="s">
         <v>379</v>
       </c>
-      <c r="ED4" s="45" t="s">
+      <c r="ED4" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="EE4" s="45" t="s">
+      <c r="EE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="EF4" s="45" t="s">
+      <c r="EF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="EG4" s="45" t="s">
+      <c r="EG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="EH4" s="45" t="s">
+      <c r="EH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="EI4" s="45" t="s">
+      <c r="EI4" s="46" t="s">
         <v>393</v>
       </c>
-      <c r="EJ4" s="45" t="s">
+      <c r="EJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="EK4" s="45" t="s">
+      <c r="EK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="EL4" s="45" t="s">
+      <c r="EL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="EM4" s="45" t="s">
+      <c r="EM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="EN4" s="45" t="s">
+      <c r="EN4" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="EO4" s="45" t="s">
+      <c r="EO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="EP4" s="45" t="s">
+      <c r="EP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="EQ4" s="45" t="s">
+      <c r="EQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="ER4" s="45" t="s">
+      <c r="ER4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="ES4" s="45" t="s">
+      <c r="ES4" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="ET4" s="45" t="s">
+      <c r="ET4" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="EU4" s="45" t="s">
+      <c r="EU4" s="46" t="s">
         <v>420</v>
       </c>
+      <c r="EV4" s="46" t="s">
+        <v>422</v>
+      </c>
     </row>
-    <row r="5" spans="1:152" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:153" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="55"/>
@@ -10306,77 +10326,78 @@
       <c r="CB5" s="56"/>
       <c r="CC5" s="56"/>
       <c r="CD5" s="56"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="46"/>
-      <c r="CV5" s="46"/>
-      <c r="CW5" s="46"/>
-      <c r="CX5" s="46"/>
-      <c r="CY5" s="46"/>
-      <c r="CZ5" s="46"/>
-      <c r="DA5" s="46"/>
-      <c r="DB5" s="46"/>
-      <c r="DC5" s="46"/>
+      <c r="CE5" s="47"/>
+      <c r="CF5" s="47"/>
+      <c r="CG5" s="47"/>
+      <c r="CH5" s="47"/>
+      <c r="CI5" s="47"/>
+      <c r="CJ5" s="47"/>
+      <c r="CK5" s="47"/>
+      <c r="CL5" s="47"/>
+      <c r="CM5" s="47"/>
+      <c r="CN5" s="47"/>
+      <c r="CO5" s="47"/>
+      <c r="CP5" s="47"/>
+      <c r="CQ5" s="47"/>
+      <c r="CR5" s="47"/>
+      <c r="CS5" s="47"/>
+      <c r="CT5" s="47"/>
+      <c r="CU5" s="47"/>
+      <c r="CV5" s="47"/>
+      <c r="CW5" s="47"/>
+      <c r="CX5" s="47"/>
+      <c r="CY5" s="47"/>
+      <c r="CZ5" s="47"/>
+      <c r="DA5" s="47"/>
+      <c r="DB5" s="47"/>
+      <c r="DC5" s="47"/>
       <c r="DD5" s="51"/>
-      <c r="DE5" s="46"/>
-      <c r="DF5" s="46"/>
-      <c r="DG5" s="46"/>
-      <c r="DH5" s="46"/>
-      <c r="DI5" s="46"/>
-      <c r="DJ5" s="46"/>
-      <c r="DK5" s="46"/>
-      <c r="DL5" s="46"/>
-      <c r="DM5" s="46"/>
-      <c r="DN5" s="46"/>
-      <c r="DO5" s="46"/>
-      <c r="DP5" s="46"/>
-      <c r="DQ5" s="46"/>
-      <c r="DR5" s="46"/>
-      <c r="DS5" s="46"/>
-      <c r="DT5" s="46"/>
-      <c r="DU5" s="46"/>
-      <c r="DV5" s="46"/>
-      <c r="DW5" s="46"/>
-      <c r="DX5" s="46"/>
-      <c r="DY5" s="46"/>
-      <c r="DZ5" s="46"/>
-      <c r="EA5" s="46"/>
-      <c r="EB5" s="46"/>
-      <c r="EC5" s="45"/>
-      <c r="ED5" s="45"/>
-      <c r="EE5" s="45"/>
-      <c r="EF5" s="45"/>
-      <c r="EG5" s="45"/>
-      <c r="EH5" s="45"/>
-      <c r="EI5" s="45"/>
-      <c r="EJ5" s="45"/>
-      <c r="EK5" s="45"/>
-      <c r="EL5" s="45"/>
-      <c r="EM5" s="45"/>
-      <c r="EN5" s="45"/>
-      <c r="EO5" s="45"/>
-      <c r="EP5" s="45"/>
-      <c r="EQ5" s="45"/>
-      <c r="ER5" s="45"/>
-      <c r="ES5" s="45"/>
-      <c r="ET5" s="45"/>
-      <c r="EU5" s="45"/>
+      <c r="DE5" s="47"/>
+      <c r="DF5" s="47"/>
+      <c r="DG5" s="47"/>
+      <c r="DH5" s="47"/>
+      <c r="DI5" s="47"/>
+      <c r="DJ5" s="47"/>
+      <c r="DK5" s="47"/>
+      <c r="DL5" s="47"/>
+      <c r="DM5" s="47"/>
+      <c r="DN5" s="47"/>
+      <c r="DO5" s="47"/>
+      <c r="DP5" s="47"/>
+      <c r="DQ5" s="47"/>
+      <c r="DR5" s="47"/>
+      <c r="DS5" s="47"/>
+      <c r="DT5" s="47"/>
+      <c r="DU5" s="47"/>
+      <c r="DV5" s="47"/>
+      <c r="DW5" s="47"/>
+      <c r="DX5" s="47"/>
+      <c r="DY5" s="47"/>
+      <c r="DZ5" s="47"/>
+      <c r="EA5" s="47"/>
+      <c r="EB5" s="47"/>
+      <c r="EC5" s="46"/>
+      <c r="ED5" s="46"/>
+      <c r="EE5" s="46"/>
+      <c r="EF5" s="46"/>
+      <c r="EG5" s="46"/>
+      <c r="EH5" s="46"/>
+      <c r="EI5" s="46"/>
+      <c r="EJ5" s="46"/>
+      <c r="EK5" s="46"/>
+      <c r="EL5" s="46"/>
+      <c r="EM5" s="46"/>
+      <c r="EN5" s="46"/>
+      <c r="EO5" s="46"/>
+      <c r="EP5" s="46"/>
+      <c r="EQ5" s="46"/>
+      <c r="ER5" s="46"/>
+      <c r="ES5" s="46"/>
+      <c r="ET5" s="46"/>
+      <c r="EU5" s="46"/>
+      <c r="EV5" s="46"/>
     </row>
-    <row r="6" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10828,9 +10849,12 @@
       <c r="EU6" s="28">
         <v>147</v>
       </c>
-      <c r="EV6" s="1"/>
+      <c r="EV6" s="28">
+        <v>114</v>
+      </c>
+      <c r="EW6" s="1"/>
     </row>
-    <row r="7" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11281,8 +11305,11 @@
       <c r="EU7" s="15">
         <v>3</v>
       </c>
+      <c r="EV7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11733,8 +11760,11 @@
       <c r="EU8" s="28">
         <v>39</v>
       </c>
+      <c r="EV8" s="28">
+        <v>33</v>
+      </c>
     </row>
-    <row r="9" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12186,8 +12216,11 @@
       <c r="EU9" s="15">
         <v>133</v>
       </c>
+      <c r="EV9" s="15">
+        <v>130</v>
+      </c>
     </row>
-    <row r="10" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12636,8 +12669,11 @@
       <c r="EU10" s="15">
         <v>1</v>
       </c>
+      <c r="EV10" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13088,8 +13124,11 @@
       <c r="EU11" s="15">
         <v>15</v>
       </c>
+      <c r="EV11" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="12" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13540,8 +13579,11 @@
       <c r="EU12" s="15">
         <v>7</v>
       </c>
+      <c r="EV12" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -13992,9 +14034,12 @@
       <c r="EU13" s="15">
         <v>44</v>
       </c>
-      <c r="EV13" s="1"/>
+      <c r="EV13" s="15">
+        <v>45</v>
+      </c>
+      <c r="EW13" s="1"/>
     </row>
-    <row r="14" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14445,8 +14490,11 @@
       <c r="EU14" s="15">
         <v>28</v>
       </c>
+      <c r="EV14" s="15">
+        <v>37</v>
+      </c>
     </row>
-    <row r="15" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -14897,8 +14945,11 @@
       <c r="EU15" s="15">
         <v>11</v>
       </c>
+      <c r="EV15" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="16" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15350,9 +15401,12 @@
       <c r="EU16" s="28">
         <v>171</v>
       </c>
-      <c r="EV16" s="1"/>
+      <c r="EV16" s="28">
+        <v>171</v>
+      </c>
+      <c r="EW16" s="1"/>
     </row>
-    <row r="17" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15803,9 +15857,12 @@
       <c r="EU17" s="15">
         <v>217</v>
       </c>
-      <c r="EV17" s="1"/>
+      <c r="EV17" s="15">
+        <v>181</v>
+      </c>
+      <c r="EW17" s="1"/>
     </row>
-    <row r="18" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16257,9 +16314,12 @@
       <c r="EU18" s="34">
         <v>2469</v>
       </c>
-      <c r="EV18" s="1"/>
+      <c r="EV18" s="34">
+        <v>2199</v>
+      </c>
+      <c r="EW18" s="1"/>
     </row>
-    <row r="19" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="70" t="s">
         <v>27</v>
@@ -16711,9 +16771,12 @@
       <c r="EU19" s="15">
         <v>99</v>
       </c>
-      <c r="EV19" s="1"/>
+      <c r="EV19" s="15">
+        <v>72</v>
+      </c>
+      <c r="EW19" s="1"/>
     </row>
-    <row r="20" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
@@ -17163,9 +17226,12 @@
       <c r="EU20" s="28">
         <v>283</v>
       </c>
-      <c r="EV20" s="1"/>
+      <c r="EV20" s="28">
+        <v>269</v>
+      </c>
+      <c r="EW20" s="1"/>
     </row>
-    <row r="21" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
@@ -17615,9 +17681,12 @@
       <c r="EU21" s="15">
         <v>69</v>
       </c>
-      <c r="EV21" s="1"/>
+      <c r="EV21" s="15">
+        <v>38</v>
+      </c>
+      <c r="EW21" s="1"/>
     </row>
-    <row r="22" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18068,8 +18137,11 @@
       <c r="EU22" s="15">
         <v>5</v>
       </c>
+      <c r="EV22" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18520,8 +18592,11 @@
       <c r="EU23" s="15">
         <v>10</v>
       </c>
+      <c r="EV23" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="24" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -18972,9 +19047,12 @@
       <c r="EU24" s="15">
         <v>22</v>
       </c>
-      <c r="EV24" s="1"/>
+      <c r="EV24" s="15">
+        <v>18</v>
+      </c>
+      <c r="EW24" s="1"/>
     </row>
-    <row r="25" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19425,8 +19503,11 @@
       <c r="EU25" s="15">
         <v>0</v>
       </c>
+      <c r="EV25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -19877,8 +19958,11 @@
       <c r="EU26" s="15">
         <v>27</v>
       </c>
+      <c r="EV26" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="27" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20329,8 +20413,11 @@
       <c r="EU27" s="15">
         <v>1</v>
       </c>
+      <c r="EV27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -20781,9 +20868,12 @@
       <c r="EU28" s="15">
         <v>9</v>
       </c>
-      <c r="EV28" s="1"/>
+      <c r="EV28" s="15">
+        <v>2</v>
+      </c>
+      <c r="EW28" s="1"/>
     </row>
-    <row r="29" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -21234,8 +21324,11 @@
       <c r="EU29" s="15">
         <v>3</v>
       </c>
+      <c r="EV29" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -21684,8 +21777,11 @@
       <c r="EU30" s="15">
         <v>66</v>
       </c>
+      <c r="EV30" s="15">
+        <v>46</v>
+      </c>
     </row>
-    <row r="31" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -22137,9 +22233,12 @@
       <c r="EU31" s="15">
         <v>215</v>
       </c>
-      <c r="EV31" s="1"/>
+      <c r="EV31" s="15">
+        <v>133</v>
+      </c>
+      <c r="EW31" s="1"/>
     </row>
-    <row r="32" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22590,8 +22689,11 @@
       <c r="EU32" s="15">
         <v>2</v>
       </c>
+      <c r="EV32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -23042,8 +23144,11 @@
       <c r="EU33" s="15">
         <v>0</v>
       </c>
+      <c r="EV33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23495,9 +23600,12 @@
       <c r="EU34" s="15">
         <v>187</v>
       </c>
-      <c r="EV34" s="1"/>
+      <c r="EV34" s="15">
+        <v>163</v>
+      </c>
+      <c r="EW34" s="1"/>
     </row>
-    <row r="35" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="70" t="s">
         <v>56</v>
@@ -23949,9 +24057,12 @@
       <c r="EU35" s="15">
         <v>405</v>
       </c>
-      <c r="EV35" s="1"/>
+      <c r="EV35" s="15">
+        <v>385</v>
+      </c>
+      <c r="EW35" s="1"/>
     </row>
-    <row r="36" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -24400,9 +24511,12 @@
       <c r="EU36" s="28">
         <v>68</v>
       </c>
-      <c r="EV36" s="1"/>
+      <c r="EV36" s="28">
+        <v>45</v>
+      </c>
+      <c r="EW36" s="1"/>
     </row>
-    <row r="37" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -24854,9 +24968,12 @@
       <c r="EU37" s="15">
         <v>153</v>
       </c>
-      <c r="EV37" s="1"/>
+      <c r="EV37" s="15">
+        <v>97</v>
+      </c>
+      <c r="EW37" s="1"/>
     </row>
-    <row r="38" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -25307,8 +25424,11 @@
       <c r="EU38" s="15">
         <v>36</v>
       </c>
+      <c r="EV38" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="39" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -25759,8 +25879,11 @@
       <c r="EU39" s="15">
         <v>22</v>
       </c>
+      <c r="EV39" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="40" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -26211,8 +26334,11 @@
       <c r="EU40" s="15">
         <v>0</v>
       </c>
+      <c r="EV40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -26663,8 +26789,11 @@
       <c r="EU41" s="15">
         <v>0</v>
       </c>
+      <c r="EV41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -27115,8 +27244,11 @@
       <c r="EU42" s="15">
         <v>20</v>
       </c>
+      <c r="EV42" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="43" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27567,8 +27699,11 @@
       <c r="EU43" s="28">
         <v>128</v>
       </c>
+      <c r="EV43" s="28">
+        <v>91</v>
+      </c>
     </row>
-    <row r="44" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -28019,8 +28154,11 @@
       <c r="EU44" s="15">
         <v>1</v>
       </c>
+      <c r="EV44" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28471,9 +28609,12 @@
       <c r="EU45" s="15">
         <v>26</v>
       </c>
-      <c r="EV45" s="1"/>
+      <c r="EV45" s="15">
+        <v>32</v>
+      </c>
+      <c r="EW45" s="1"/>
     </row>
-    <row r="46" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -28924,8 +29065,11 @@
       <c r="EU46" s="15">
         <v>30</v>
       </c>
+      <c r="EV46" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="47" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -29376,8 +29520,11 @@
       <c r="EU47" s="15">
         <v>1</v>
       </c>
+      <c r="EV47" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -29828,8 +29975,11 @@
       <c r="EU48" s="15">
         <v>22</v>
       </c>
+      <c r="EV48" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="49" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="70" t="s">
         <v>83</v>
@@ -30281,9 +30431,12 @@
       <c r="EU49" s="15">
         <v>115</v>
       </c>
-      <c r="EV49" s="1"/>
+      <c r="EV49" s="15">
+        <v>61</v>
+      </c>
+      <c r="EW49" s="1"/>
     </row>
-    <row r="50" spans="1:152" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -30732,9 +30885,12 @@
       <c r="EU50" s="15">
         <v>62</v>
       </c>
-      <c r="EV50" s="1"/>
+      <c r="EV50" s="15">
+        <v>30</v>
+      </c>
+      <c r="EW50" s="1"/>
     </row>
-    <row r="51" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -31185,8 +31341,11 @@
       <c r="EU51" s="15">
         <v>20</v>
       </c>
+      <c r="EV51" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="52" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -31637,8 +31796,11 @@
       <c r="EU52" s="15">
         <v>28</v>
       </c>
+      <c r="EV52" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="53" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -32089,8 +32251,11 @@
       <c r="EU53" s="15">
         <v>64</v>
       </c>
+      <c r="EV53" s="15">
+        <v>75</v>
+      </c>
     </row>
-    <row r="54" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -32541,8 +32706,11 @@
       <c r="EU54" s="15">
         <v>9</v>
       </c>
+      <c r="EV54" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="55" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -32993,8 +33161,11 @@
       <c r="EU55" s="15">
         <v>19</v>
       </c>
+      <c r="EV55" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="56" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -33445,8 +33616,11 @@
       <c r="EU56" s="15">
         <v>3</v>
       </c>
+      <c r="EV56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -33897,8 +34071,11 @@
       <c r="EU57" s="15">
         <v>4</v>
       </c>
+      <c r="EV57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -34376,7 +34553,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:EU58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:EV58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -34495,8 +34672,12 @@
         <f t="shared" si="10"/>
         <v>5519</v>
       </c>
+      <c r="EV58" s="14">
+        <f t="shared" si="10"/>
+        <v>4724</v>
+      </c>
     </row>
-    <row r="59" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -34580,7 +34761,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -34664,7 +34845,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:152" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -34749,7 +34930,7 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -34899,12 +35080,13 @@
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="DE2:EV2"/>
+    <mergeCell ref="ER3:EV3"/>
+    <mergeCell ref="EV4:EV5"/>
     <mergeCell ref="DE3:EQ3"/>
     <mergeCell ref="DT4:DT5"/>
     <mergeCell ref="DP4:DP5"/>
     <mergeCell ref="ES4:ES5"/>
-    <mergeCell ref="DE2:EU2"/>
-    <mergeCell ref="ER3:EU3"/>
     <mergeCell ref="EU4:EU5"/>
     <mergeCell ref="ET4:ET5"/>
     <mergeCell ref="EQ4:EQ5"/>
@@ -34927,7 +35109,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:EU57">
+  <conditionalFormatting sqref="DP6:EV57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -34947,7 +35129,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:EU58"/>
+  <dimension ref="B1:EV58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -34970,11 +35152,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="151" width="10.875" style="1" customWidth="1"/>
-    <col min="152" max="16384" width="8.625" style="1"/>
+    <col min="106" max="152" width="10.875" style="1" customWidth="1"/>
+    <col min="153" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:151" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:152" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="82" t="s">
         <v>323</v>
       </c>
@@ -35052,169 +35234,171 @@
       <c r="ER1" s="19"/>
       <c r="ES1" s="19"/>
       <c r="ET1" s="19"/>
-      <c r="EU1" s="19" t="s">
+      <c r="EU1" s="19"/>
+      <c r="EV1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:151" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:152" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="47"/>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="47"/>
-      <c r="AD2" s="47"/>
-      <c r="AE2" s="47"/>
-      <c r="AF2" s="47"/>
-      <c r="AG2" s="47"/>
-      <c r="AH2" s="47"/>
-      <c r="AI2" s="47"/>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="47"/>
-      <c r="AP2" s="47"/>
-      <c r="AQ2" s="47"/>
-      <c r="AR2" s="47"/>
-      <c r="AS2" s="47"/>
-      <c r="AT2" s="47"/>
-      <c r="AU2" s="47"/>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="47"/>
-      <c r="BB2" s="47"/>
-      <c r="BC2" s="47"/>
-      <c r="BD2" s="47" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="44"/>
+      <c r="AV2" s="44"/>
+      <c r="AW2" s="44"/>
+      <c r="AX2" s="44"/>
+      <c r="AY2" s="44"/>
+      <c r="AZ2" s="44"/>
+      <c r="BA2" s="44"/>
+      <c r="BB2" s="44"/>
+      <c r="BC2" s="44"/>
+      <c r="BD2" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="47"/>
-      <c r="BF2" s="47"/>
-      <c r="BG2" s="47"/>
-      <c r="BH2" s="47"/>
-      <c r="BI2" s="47"/>
-      <c r="BJ2" s="47"/>
-      <c r="BK2" s="47"/>
-      <c r="BL2" s="47"/>
-      <c r="BM2" s="47"/>
-      <c r="BN2" s="47"/>
-      <c r="BO2" s="47"/>
-      <c r="BP2" s="47"/>
-      <c r="BQ2" s="47"/>
-      <c r="BR2" s="47"/>
-      <c r="BS2" s="47"/>
-      <c r="BT2" s="47"/>
-      <c r="BU2" s="47"/>
-      <c r="BV2" s="47"/>
-      <c r="BW2" s="47"/>
-      <c r="BX2" s="47"/>
-      <c r="BY2" s="47"/>
-      <c r="BZ2" s="47"/>
-      <c r="CA2" s="47"/>
-      <c r="CB2" s="47"/>
-      <c r="CC2" s="47"/>
-      <c r="CD2" s="47"/>
-      <c r="CE2" s="47"/>
-      <c r="CF2" s="47"/>
-      <c r="CG2" s="47"/>
-      <c r="CH2" s="47"/>
-      <c r="CI2" s="47"/>
-      <c r="CJ2" s="47"/>
-      <c r="CK2" s="47"/>
-      <c r="CL2" s="47"/>
-      <c r="CM2" s="47"/>
-      <c r="CN2" s="47"/>
-      <c r="CO2" s="47"/>
-      <c r="CP2" s="47"/>
-      <c r="CQ2" s="47"/>
-      <c r="CR2" s="47"/>
-      <c r="CS2" s="47"/>
-      <c r="CT2" s="47"/>
-      <c r="CU2" s="47"/>
-      <c r="CV2" s="47"/>
-      <c r="CW2" s="47"/>
-      <c r="CX2" s="47"/>
-      <c r="CY2" s="47"/>
-      <c r="CZ2" s="47"/>
-      <c r="DA2" s="47"/>
-      <c r="DB2" s="47"/>
-      <c r="DC2" s="47"/>
-      <c r="DD2" s="47" t="s">
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
+      <c r="CU2" s="44"/>
+      <c r="CV2" s="44"/>
+      <c r="CW2" s="44"/>
+      <c r="CX2" s="44"/>
+      <c r="CY2" s="44"/>
+      <c r="CZ2" s="44"/>
+      <c r="DA2" s="44"/>
+      <c r="DB2" s="44"/>
+      <c r="DC2" s="44"/>
+      <c r="DD2" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="47"/>
-      <c r="DF2" s="47"/>
-      <c r="DG2" s="47"/>
-      <c r="DH2" s="47"/>
-      <c r="DI2" s="47"/>
-      <c r="DJ2" s="47"/>
-      <c r="DK2" s="47"/>
-      <c r="DL2" s="47"/>
-      <c r="DM2" s="47"/>
-      <c r="DN2" s="47"/>
-      <c r="DO2" s="47"/>
-      <c r="DP2" s="47"/>
-      <c r="DQ2" s="47"/>
-      <c r="DR2" s="47"/>
-      <c r="DS2" s="47"/>
-      <c r="DT2" s="47"/>
-      <c r="DU2" s="47"/>
-      <c r="DV2" s="47"/>
-      <c r="DW2" s="47"/>
-      <c r="DX2" s="47"/>
-      <c r="DY2" s="47"/>
-      <c r="DZ2" s="47"/>
-      <c r="EA2" s="47"/>
-      <c r="EB2" s="47"/>
-      <c r="EC2" s="47"/>
-      <c r="ED2" s="47"/>
-      <c r="EE2" s="47"/>
-      <c r="EF2" s="47"/>
-      <c r="EG2" s="47"/>
-      <c r="EH2" s="47"/>
-      <c r="EI2" s="47"/>
-      <c r="EJ2" s="47"/>
-      <c r="EK2" s="47"/>
-      <c r="EL2" s="47"/>
-      <c r="EM2" s="47"/>
-      <c r="EN2" s="47"/>
-      <c r="EO2" s="47"/>
-      <c r="EP2" s="47"/>
-      <c r="EQ2" s="47"/>
-      <c r="ER2" s="47"/>
-      <c r="ES2" s="47"/>
-      <c r="ET2" s="47"/>
-      <c r="EU2" s="47"/>
+      <c r="DE2" s="44"/>
+      <c r="DF2" s="44"/>
+      <c r="DG2" s="44"/>
+      <c r="DH2" s="44"/>
+      <c r="DI2" s="44"/>
+      <c r="DJ2" s="44"/>
+      <c r="DK2" s="44"/>
+      <c r="DL2" s="44"/>
+      <c r="DM2" s="44"/>
+      <c r="DN2" s="44"/>
+      <c r="DO2" s="44"/>
+      <c r="DP2" s="44"/>
+      <c r="DQ2" s="44"/>
+      <c r="DR2" s="44"/>
+      <c r="DS2" s="44"/>
+      <c r="DT2" s="44"/>
+      <c r="DU2" s="44"/>
+      <c r="DV2" s="44"/>
+      <c r="DW2" s="44"/>
+      <c r="DX2" s="44"/>
+      <c r="DY2" s="44"/>
+      <c r="DZ2" s="44"/>
+      <c r="EA2" s="44"/>
+      <c r="EB2" s="44"/>
+      <c r="EC2" s="44"/>
+      <c r="ED2" s="44"/>
+      <c r="EE2" s="44"/>
+      <c r="EF2" s="44"/>
+      <c r="EG2" s="44"/>
+      <c r="EH2" s="44"/>
+      <c r="EI2" s="44"/>
+      <c r="EJ2" s="44"/>
+      <c r="EK2" s="44"/>
+      <c r="EL2" s="44"/>
+      <c r="EM2" s="44"/>
+      <c r="EN2" s="44"/>
+      <c r="EO2" s="44"/>
+      <c r="EP2" s="44"/>
+      <c r="EQ2" s="44"/>
+      <c r="ER2" s="44"/>
+      <c r="ES2" s="44"/>
+      <c r="ET2" s="44"/>
+      <c r="EU2" s="44"/>
+      <c r="EV2" s="44"/>
     </row>
-    <row r="3" spans="2:151" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:152" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -35259,20 +35443,20 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="44" t="s">
+      <c r="AR3" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="44"/>
-      <c r="AW3" s="44"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
       <c r="BD3" s="48" t="s">
         <v>322</v>
       </c>
@@ -35315,70 +35499,71 @@
       <c r="CO3" s="53"/>
       <c r="CP3" s="53"/>
       <c r="CQ3" s="54"/>
-      <c r="CR3" s="44" t="s">
+      <c r="CR3" s="45" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="44"/>
-      <c r="CT3" s="44"/>
-      <c r="CU3" s="44"/>
-      <c r="CV3" s="44"/>
-      <c r="CW3" s="44"/>
-      <c r="CX3" s="44"/>
-      <c r="CY3" s="44"/>
-      <c r="CZ3" s="44"/>
-      <c r="DA3" s="44"/>
-      <c r="DB3" s="44"/>
-      <c r="DC3" s="44"/>
-      <c r="DD3" s="44" t="s">
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="44"/>
-      <c r="DF3" s="44"/>
-      <c r="DG3" s="44"/>
-      <c r="DH3" s="44"/>
-      <c r="DI3" s="44"/>
-      <c r="DJ3" s="44"/>
-      <c r="DK3" s="44"/>
-      <c r="DL3" s="44"/>
-      <c r="DM3" s="44"/>
-      <c r="DN3" s="44"/>
-      <c r="DO3" s="44"/>
-      <c r="DP3" s="44"/>
-      <c r="DQ3" s="44"/>
-      <c r="DR3" s="44"/>
-      <c r="DS3" s="44"/>
-      <c r="DT3" s="44"/>
-      <c r="DU3" s="44"/>
-      <c r="DV3" s="44"/>
-      <c r="DW3" s="44"/>
-      <c r="DX3" s="44"/>
-      <c r="DY3" s="44"/>
-      <c r="DZ3" s="44"/>
-      <c r="EA3" s="44"/>
-      <c r="EB3" s="44"/>
-      <c r="EC3" s="44"/>
-      <c r="ED3" s="44"/>
-      <c r="EE3" s="44"/>
-      <c r="EF3" s="44"/>
-      <c r="EG3" s="44"/>
-      <c r="EH3" s="44"/>
-      <c r="EI3" s="44"/>
-      <c r="EJ3" s="44"/>
-      <c r="EK3" s="44"/>
-      <c r="EL3" s="44"/>
-      <c r="EM3" s="44"/>
-      <c r="EN3" s="44"/>
-      <c r="EO3" s="44"/>
-      <c r="EP3" s="44"/>
-      <c r="EQ3" s="44"/>
-      <c r="ER3" s="44" t="s">
+      <c r="DE3" s="45"/>
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="44"/>
-      <c r="ET3" s="44"/>
-      <c r="EU3" s="44"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
+      <c r="EU3" s="45"/>
+      <c r="EV3" s="45"/>
     </row>
-    <row r="4" spans="2:151" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:152" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -35697,55 +35882,55 @@
       <c r="DC4" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="DD4" s="45" t="s">
+      <c r="DD4" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="DE4" s="45" t="s">
+      <c r="DE4" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="DF4" s="45" t="s">
+      <c r="DF4" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="DG4" s="45" t="s">
+      <c r="DG4" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="DH4" s="45" t="s">
+      <c r="DH4" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="DI4" s="45" t="s">
+      <c r="DI4" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="DJ4" s="45" t="s">
+      <c r="DJ4" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="DK4" s="45" t="s">
+      <c r="DK4" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="DL4" s="45" t="s">
+      <c r="DL4" s="46" t="s">
         <v>329</v>
       </c>
       <c r="DM4" s="74" t="s">
         <v>331</v>
       </c>
-      <c r="DN4" s="45" t="s">
+      <c r="DN4" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="DO4" s="45" t="s">
+      <c r="DO4" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="DP4" s="45" t="s">
+      <c r="DP4" s="46" t="s">
         <v>337</v>
       </c>
-      <c r="DQ4" s="45" t="s">
+      <c r="DQ4" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="DR4" s="45" t="s">
+      <c r="DR4" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="DS4" s="45" t="s">
+      <c r="DS4" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="DT4" s="45" t="s">
+      <c r="DT4" s="46" t="s">
         <v>350</v>
       </c>
       <c r="DU4" s="74" t="s">
@@ -35763,74 +35948,77 @@
       <c r="DY4" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="DZ4" s="45" t="s">
+      <c r="DZ4" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="EA4" s="45" t="s">
+      <c r="EA4" s="46" t="s">
         <v>373</v>
       </c>
-      <c r="EB4" s="45" t="s">
+      <c r="EB4" s="46" t="s">
         <v>376</v>
       </c>
-      <c r="EC4" s="45" t="s">
+      <c r="EC4" s="46" t="s">
         <v>380</v>
       </c>
-      <c r="ED4" s="45" t="s">
+      <c r="ED4" s="46" t="s">
         <v>383</v>
       </c>
-      <c r="EE4" s="45" t="s">
+      <c r="EE4" s="46" t="s">
         <v>385</v>
       </c>
-      <c r="EF4" s="45" t="s">
+      <c r="EF4" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="EG4" s="45" t="s">
+      <c r="EG4" s="46" t="s">
         <v>388</v>
       </c>
-      <c r="EH4" s="45" t="s">
+      <c r="EH4" s="46" t="s">
         <v>390</v>
       </c>
-      <c r="EI4" s="45" t="s">
+      <c r="EI4" s="46" t="s">
         <v>392</v>
       </c>
-      <c r="EJ4" s="45" t="s">
+      <c r="EJ4" s="46" t="s">
         <v>396</v>
       </c>
-      <c r="EK4" s="45" t="s">
+      <c r="EK4" s="46" t="s">
         <v>397</v>
       </c>
-      <c r="EL4" s="45" t="s">
+      <c r="EL4" s="46" t="s">
         <v>399</v>
       </c>
-      <c r="EM4" s="45" t="s">
+      <c r="EM4" s="46" t="s">
         <v>401</v>
       </c>
-      <c r="EN4" s="45" t="s">
+      <c r="EN4" s="46" t="s">
         <v>403</v>
       </c>
-      <c r="EO4" s="45" t="s">
+      <c r="EO4" s="46" t="s">
         <v>406</v>
       </c>
-      <c r="EP4" s="45" t="s">
+      <c r="EP4" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="EQ4" s="45" t="s">
+      <c r="EQ4" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="ER4" s="45" t="s">
+      <c r="ER4" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="ES4" s="45" t="s">
+      <c r="ES4" s="46" t="s">
         <v>417</v>
       </c>
-      <c r="ET4" s="45" t="s">
+      <c r="ET4" s="46" t="s">
         <v>419</v>
       </c>
-      <c r="EU4" s="45" t="s">
+      <c r="EU4" s="46" t="s">
         <v>421</v>
       </c>
+      <c r="EV4" s="46" t="s">
+        <v>423</v>
+      </c>
     </row>
-    <row r="5" spans="2:151" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:152" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="49"/>
@@ -35912,77 +36100,78 @@
       <c r="CB5" s="56"/>
       <c r="CC5" s="56"/>
       <c r="CD5" s="56"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="46"/>
-      <c r="CV5" s="46"/>
-      <c r="CW5" s="46"/>
-      <c r="CX5" s="46"/>
-      <c r="CY5" s="46"/>
-      <c r="CZ5" s="46"/>
-      <c r="DA5" s="46"/>
-      <c r="DB5" s="46"/>
-      <c r="DC5" s="46"/>
-      <c r="DD5" s="46"/>
-      <c r="DE5" s="46"/>
-      <c r="DF5" s="46"/>
-      <c r="DG5" s="46"/>
-      <c r="DH5" s="46"/>
-      <c r="DI5" s="46"/>
-      <c r="DJ5" s="46"/>
-      <c r="DK5" s="46"/>
-      <c r="DL5" s="46"/>
+      <c r="CE5" s="47"/>
+      <c r="CF5" s="47"/>
+      <c r="CG5" s="47"/>
+      <c r="CH5" s="47"/>
+      <c r="CI5" s="47"/>
+      <c r="CJ5" s="47"/>
+      <c r="CK5" s="47"/>
+      <c r="CL5" s="47"/>
+      <c r="CM5" s="47"/>
+      <c r="CN5" s="47"/>
+      <c r="CO5" s="47"/>
+      <c r="CP5" s="47"/>
+      <c r="CQ5" s="47"/>
+      <c r="CR5" s="47"/>
+      <c r="CS5" s="47"/>
+      <c r="CT5" s="47"/>
+      <c r="CU5" s="47"/>
+      <c r="CV5" s="47"/>
+      <c r="CW5" s="47"/>
+      <c r="CX5" s="47"/>
+      <c r="CY5" s="47"/>
+      <c r="CZ5" s="47"/>
+      <c r="DA5" s="47"/>
+      <c r="DB5" s="47"/>
+      <c r="DC5" s="47"/>
+      <c r="DD5" s="47"/>
+      <c r="DE5" s="47"/>
+      <c r="DF5" s="47"/>
+      <c r="DG5" s="47"/>
+      <c r="DH5" s="47"/>
+      <c r="DI5" s="47"/>
+      <c r="DJ5" s="47"/>
+      <c r="DK5" s="47"/>
+      <c r="DL5" s="47"/>
       <c r="DM5" s="75"/>
-      <c r="DN5" s="46"/>
-      <c r="DO5" s="46"/>
-      <c r="DP5" s="46"/>
-      <c r="DQ5" s="46"/>
-      <c r="DR5" s="46"/>
-      <c r="DS5" s="46"/>
-      <c r="DT5" s="46"/>
+      <c r="DN5" s="47"/>
+      <c r="DO5" s="47"/>
+      <c r="DP5" s="47"/>
+      <c r="DQ5" s="47"/>
+      <c r="DR5" s="47"/>
+      <c r="DS5" s="47"/>
+      <c r="DT5" s="47"/>
       <c r="DU5" s="75"/>
       <c r="DV5" s="75"/>
       <c r="DW5" s="75"/>
       <c r="DX5" s="75"/>
       <c r="DY5" s="75"/>
-      <c r="DZ5" s="46"/>
-      <c r="EA5" s="46"/>
-      <c r="EB5" s="46"/>
-      <c r="EC5" s="46"/>
-      <c r="ED5" s="46"/>
-      <c r="EE5" s="45"/>
-      <c r="EF5" s="45"/>
-      <c r="EG5" s="45"/>
-      <c r="EH5" s="45"/>
-      <c r="EI5" s="45"/>
-      <c r="EJ5" s="45"/>
-      <c r="EK5" s="45"/>
-      <c r="EL5" s="45"/>
-      <c r="EM5" s="45"/>
-      <c r="EN5" s="45"/>
-      <c r="EO5" s="45"/>
-      <c r="EP5" s="45"/>
-      <c r="EQ5" s="45"/>
-      <c r="ER5" s="45"/>
-      <c r="ES5" s="45"/>
-      <c r="ET5" s="45"/>
-      <c r="EU5" s="45"/>
+      <c r="DZ5" s="47"/>
+      <c r="EA5" s="47"/>
+      <c r="EB5" s="47"/>
+      <c r="EC5" s="47"/>
+      <c r="ED5" s="47"/>
+      <c r="EE5" s="46"/>
+      <c r="EF5" s="46"/>
+      <c r="EG5" s="46"/>
+      <c r="EH5" s="46"/>
+      <c r="EI5" s="46"/>
+      <c r="EJ5" s="46"/>
+      <c r="EK5" s="46"/>
+      <c r="EL5" s="46"/>
+      <c r="EM5" s="46"/>
+      <c r="EN5" s="46"/>
+      <c r="EO5" s="46"/>
+      <c r="EP5" s="46"/>
+      <c r="EQ5" s="46"/>
+      <c r="ER5" s="46"/>
+      <c r="ES5" s="46"/>
+      <c r="ET5" s="46"/>
+      <c r="EU5" s="46"/>
+      <c r="EV5" s="46"/>
     </row>
-    <row r="6" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -36433,8 +36622,11 @@
       <c r="EU6" s="28">
         <v>187</v>
       </c>
+      <c r="EV6" s="28">
+        <v>161</v>
+      </c>
     </row>
-    <row r="7" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -36885,8 +37077,11 @@
       <c r="EU7" s="15">
         <v>2</v>
       </c>
+      <c r="EV7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -37337,8 +37532,11 @@
       <c r="EU8" s="28">
         <v>8</v>
       </c>
+      <c r="EV8" s="28">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -37789,8 +37987,11 @@
       <c r="EU9" s="15">
         <v>81</v>
       </c>
+      <c r="EV9" s="15">
+        <v>77</v>
+      </c>
     </row>
-    <row r="10" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -38241,8 +38442,11 @@
       <c r="EU10" s="15">
         <v>0</v>
       </c>
+      <c r="EV10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -38693,8 +38897,11 @@
       <c r="EU11" s="15">
         <v>9</v>
       </c>
+      <c r="EV11" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="12" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -39145,8 +39352,11 @@
       <c r="EU12" s="15">
         <v>18</v>
       </c>
+      <c r="EV12" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -39597,8 +39807,11 @@
       <c r="EU13" s="15">
         <v>34</v>
       </c>
+      <c r="EV13" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="14" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -40049,8 +40262,11 @@
       <c r="EU14" s="15">
         <v>43</v>
       </c>
+      <c r="EV14" s="15">
+        <v>52</v>
+      </c>
     </row>
-    <row r="15" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -40501,8 +40717,11 @@
       <c r="EU15" s="15">
         <v>6</v>
       </c>
+      <c r="EV15" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="16" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -40953,8 +41172,11 @@
       <c r="EU16" s="28">
         <v>206</v>
       </c>
+      <c r="EV16" s="28">
+        <v>185</v>
+      </c>
     </row>
-    <row r="17" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -41405,8 +41627,11 @@
       <c r="EU17" s="15">
         <v>189</v>
       </c>
+      <c r="EV17" s="15">
+        <v>227</v>
+      </c>
     </row>
-    <row r="18" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -41857,8 +42082,11 @@
       <c r="EU18" s="34">
         <v>2668</v>
       </c>
+      <c r="EV18" s="34">
+        <v>2666</v>
+      </c>
     </row>
-    <row r="19" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="70" t="s">
         <v>27</v>
       </c>
@@ -42309,8 +42537,11 @@
       <c r="EU19" s="15">
         <v>119</v>
       </c>
+      <c r="EV19" s="15">
+        <v>102</v>
+      </c>
     </row>
-    <row r="20" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -42759,8 +42990,11 @@
       <c r="EU20" s="28">
         <v>310</v>
       </c>
+      <c r="EV20" s="28">
+        <v>369</v>
+      </c>
     </row>
-    <row r="21" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -43209,8 +43443,11 @@
       <c r="EU21" s="15">
         <v>66</v>
       </c>
+      <c r="EV21" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -43661,8 +43898,11 @@
       <c r="EU22" s="15">
         <v>12</v>
       </c>
+      <c r="EV22" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="23" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -44113,8 +44353,11 @@
       <c r="EU23" s="15">
         <v>5</v>
       </c>
+      <c r="EV23" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -44565,8 +44808,11 @@
       <c r="EU24" s="15">
         <v>12</v>
       </c>
+      <c r="EV24" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -45017,8 +45263,11 @@
       <c r="EU25" s="15">
         <v>0</v>
       </c>
+      <c r="EV25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -45469,8 +45718,11 @@
       <c r="EU26" s="15">
         <v>13</v>
       </c>
+      <c r="EV26" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="27" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -45921,8 +46173,11 @@
       <c r="EU27" s="15">
         <v>2</v>
       </c>
+      <c r="EV27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -46373,8 +46628,11 @@
       <c r="EU28" s="15">
         <v>5</v>
       </c>
+      <c r="EV28" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -46825,8 +47083,11 @@
       <c r="EU29" s="15">
         <v>1</v>
       </c>
+      <c r="EV29" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -47275,8 +47536,11 @@
       <c r="EU30" s="15">
         <v>17</v>
       </c>
+      <c r="EV30" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="31" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -47727,8 +47991,11 @@
       <c r="EU31" s="15">
         <v>73</v>
       </c>
+      <c r="EV31" s="15">
+        <v>143</v>
+      </c>
     </row>
-    <row r="32" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -48179,8 +48446,11 @@
       <c r="EU32" s="15">
         <v>1</v>
       </c>
+      <c r="EV32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -48631,8 +48901,11 @@
       <c r="EU33" s="15">
         <v>0</v>
       </c>
+      <c r="EV33" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -49083,8 +49356,11 @@
       <c r="EU34" s="15">
         <v>116</v>
       </c>
+      <c r="EV34" s="15">
+        <v>136</v>
+      </c>
     </row>
-    <row r="35" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="70" t="s">
         <v>56</v>
       </c>
@@ -49535,8 +49811,11 @@
       <c r="EU35" s="15">
         <v>641</v>
       </c>
+      <c r="EV35" s="15">
+        <v>730</v>
+      </c>
     </row>
-    <row r="36" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -49985,8 +50264,11 @@
       <c r="EU36" s="28">
         <v>94</v>
       </c>
+      <c r="EV36" s="28">
+        <v>131</v>
+      </c>
     </row>
-    <row r="37" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -50437,8 +50719,11 @@
       <c r="EU37" s="15">
         <v>109</v>
       </c>
+      <c r="EV37" s="15">
+        <v>163</v>
+      </c>
     </row>
-    <row r="38" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -50889,8 +51174,11 @@
       <c r="EU38" s="15">
         <v>28</v>
       </c>
+      <c r="EV38" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="39" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -51341,8 +51629,11 @@
       <c r="EU39" s="15">
         <v>7</v>
       </c>
+      <c r="EV39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -51793,8 +52084,11 @@
       <c r="EU40" s="15">
         <v>0</v>
       </c>
+      <c r="EV40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -52245,8 +52539,11 @@
       <c r="EU41" s="15">
         <v>0</v>
       </c>
+      <c r="EV41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -52697,8 +52994,11 @@
       <c r="EU42" s="15">
         <v>22</v>
       </c>
+      <c r="EV42" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="43" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -53149,8 +53449,11 @@
       <c r="EU43" s="28">
         <v>85</v>
       </c>
+      <c r="EV43" s="28">
+        <v>65</v>
+      </c>
     </row>
-    <row r="44" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -53601,8 +53904,11 @@
       <c r="EU44" s="15">
         <v>7</v>
       </c>
+      <c r="EV44" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -54053,8 +54359,11 @@
       <c r="EU45" s="15">
         <v>5</v>
       </c>
+      <c r="EV45" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="46" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -54505,8 +54814,11 @@
       <c r="EU46" s="15">
         <v>16</v>
       </c>
+      <c r="EV46" s="15">
+        <v>30</v>
+      </c>
     </row>
-    <row r="47" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -54957,8 +55269,11 @@
       <c r="EU47" s="15">
         <v>1</v>
       </c>
+      <c r="EV47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -55409,8 +55724,11 @@
       <c r="EU48" s="15">
         <v>8</v>
       </c>
+      <c r="EV48" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="49" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="70" t="s">
         <v>83</v>
       </c>
@@ -55861,8 +56179,11 @@
       <c r="EU49" s="15">
         <v>111</v>
       </c>
+      <c r="EV49" s="15">
+        <v>86</v>
+      </c>
     </row>
-    <row r="50" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -56311,8 +56632,11 @@
       <c r="EU50" s="15">
         <v>29</v>
       </c>
+      <c r="EV50" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="51" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -56763,8 +57087,11 @@
       <c r="EU51" s="15">
         <v>2</v>
       </c>
+      <c r="EV51" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -57215,8 +57542,11 @@
       <c r="EU52" s="15">
         <v>9</v>
       </c>
+      <c r="EV52" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="53" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -57667,8 +57997,11 @@
       <c r="EU53" s="15">
         <v>40</v>
       </c>
+      <c r="EV53" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="54" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -58119,8 +58452,11 @@
       <c r="EU54" s="15">
         <v>19</v>
       </c>
+      <c r="EV54" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -58571,8 +58907,11 @@
       <c r="EU55" s="15">
         <v>7</v>
       </c>
+      <c r="EV55" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="56" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -59023,8 +59362,11 @@
       <c r="EU56" s="15">
         <v>2</v>
       </c>
+      <c r="EV56" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -59475,8 +59817,11 @@
       <c r="EU57" s="15">
         <v>3</v>
       </c>
+      <c r="EV57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="2:151" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -59945,7 +60290,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:EU58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:EV58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -60072,10 +60417,16 @@
         <f t="shared" si="8"/>
         <v>5448</v>
       </c>
+      <c r="EV58" s="14">
+        <f t="shared" si="8"/>
+        <v>5705</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="165">
-    <mergeCell ref="ER3:EU3"/>
+  <mergeCells count="166">
+    <mergeCell ref="DD2:EV2"/>
+    <mergeCell ref="ER3:EV3"/>
+    <mergeCell ref="EV4:EV5"/>
     <mergeCell ref="EU4:EU5"/>
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="CS4:CS5"/>
@@ -60121,7 +60472,6 @@
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="DD2:EU2"/>
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D3:AQ3"/>
@@ -60169,6 +60519,7 @@
     <mergeCell ref="BV4:BV5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="CC4:CC5"/>
     <mergeCell ref="CE4:CE5"/>
     <mergeCell ref="CH4:CH5"/>
@@ -60193,7 +60544,6 @@
     <mergeCell ref="AL4:AL5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AS4:AS5"/>
     <mergeCell ref="DM4:DM5"/>
@@ -60252,7 +60602,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:EU57">
+  <conditionalFormatting sqref="EH6:EV57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -60292,7 +60642,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU61"/>
+  <dimension ref="A1:CV61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -60303,11 +60653,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="99" width="10.875" style="1" customWidth="1"/>
-    <col min="100" max="16384" width="8.625" style="1"/>
+    <col min="54" max="100" width="10.875" style="1" customWidth="1"/>
+    <col min="101" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:99" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:100" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -60381,11 +60731,12 @@
       <c r="CR1" s="19"/>
       <c r="CS1" s="19"/>
       <c r="CT1" s="19"/>
-      <c r="CU1" s="19" t="s">
+      <c r="CU1" s="19"/>
+      <c r="CV1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:99" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:100" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -60442,54 +60793,55 @@
       <c r="BA2" s="52"/>
       <c r="BB2" s="52"/>
       <c r="BC2" s="88"/>
-      <c r="BD2" s="47" t="s">
+      <c r="BD2" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="47"/>
-      <c r="BF2" s="47"/>
-      <c r="BG2" s="47"/>
-      <c r="BH2" s="47"/>
-      <c r="BI2" s="47"/>
-      <c r="BJ2" s="47"/>
-      <c r="BK2" s="47"/>
-      <c r="BL2" s="47"/>
-      <c r="BM2" s="47"/>
-      <c r="BN2" s="47"/>
-      <c r="BO2" s="47"/>
-      <c r="BP2" s="47"/>
-      <c r="BQ2" s="47"/>
-      <c r="BR2" s="47"/>
-      <c r="BS2" s="47"/>
-      <c r="BT2" s="47"/>
-      <c r="BU2" s="47"/>
-      <c r="BV2" s="47"/>
-      <c r="BW2" s="47"/>
-      <c r="BX2" s="47"/>
-      <c r="BY2" s="47"/>
-      <c r="BZ2" s="47"/>
-      <c r="CA2" s="47"/>
-      <c r="CB2" s="47"/>
-      <c r="CC2" s="47"/>
-      <c r="CD2" s="47"/>
-      <c r="CE2" s="47"/>
-      <c r="CF2" s="47"/>
-      <c r="CG2" s="47"/>
-      <c r="CH2" s="47"/>
-      <c r="CI2" s="47"/>
-      <c r="CJ2" s="47"/>
-      <c r="CK2" s="47"/>
-      <c r="CL2" s="47"/>
-      <c r="CM2" s="47"/>
-      <c r="CN2" s="47"/>
-      <c r="CO2" s="47"/>
-      <c r="CP2" s="47"/>
-      <c r="CQ2" s="47"/>
-      <c r="CR2" s="47"/>
-      <c r="CS2" s="47"/>
-      <c r="CT2" s="47"/>
-      <c r="CU2" s="47"/>
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
+      <c r="CU2" s="44"/>
+      <c r="CV2" s="44"/>
     </row>
-    <row r="3" spans="1:99" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:100" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -60534,70 +60886,71 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="44" t="s">
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="44"/>
-      <c r="AW3" s="44"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="44"/>
-      <c r="BK3" s="44"/>
-      <c r="BL3" s="44"/>
-      <c r="BM3" s="44"/>
-      <c r="BN3" s="44"/>
-      <c r="BO3" s="44"/>
-      <c r="BP3" s="44"/>
-      <c r="BQ3" s="44"/>
-      <c r="BR3" s="44"/>
-      <c r="BS3" s="44"/>
-      <c r="BT3" s="44"/>
-      <c r="BU3" s="44"/>
-      <c r="BV3" s="44"/>
-      <c r="BW3" s="44"/>
-      <c r="BX3" s="44"/>
-      <c r="BY3" s="44"/>
-      <c r="BZ3" s="44"/>
-      <c r="CA3" s="44"/>
-      <c r="CB3" s="44"/>
-      <c r="CC3" s="44"/>
-      <c r="CD3" s="44"/>
-      <c r="CE3" s="44"/>
-      <c r="CF3" s="44"/>
-      <c r="CG3" s="44"/>
-      <c r="CH3" s="44"/>
-      <c r="CI3" s="44"/>
-      <c r="CJ3" s="44"/>
-      <c r="CK3" s="44"/>
-      <c r="CL3" s="44"/>
-      <c r="CM3" s="44"/>
-      <c r="CN3" s="44"/>
-      <c r="CO3" s="44"/>
-      <c r="CP3" s="44"/>
-      <c r="CQ3" s="44"/>
-      <c r="CR3" s="44" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="44"/>
-      <c r="CT3" s="44"/>
-      <c r="CU3" s="44"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
     </row>
-    <row r="4" spans="1:99" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:100" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -60760,140 +61113,143 @@
       <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="45" t="s">
+      <c r="BD4" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="45" t="s">
+      <c r="BE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="45" t="s">
+      <c r="BF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="45" t="s">
+      <c r="BG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="45" t="s">
+      <c r="BH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="45" t="s">
+      <c r="BI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="45" t="s">
+      <c r="BJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="45" t="s">
+      <c r="BK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="45" t="s">
+      <c r="BL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="45" t="s">
+      <c r="BM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="45" t="s">
+      <c r="BN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="45" t="s">
+      <c r="BO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="45" t="s">
+      <c r="BP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="45" t="s">
+      <c r="BQ4" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="45" t="s">
+      <c r="BR4" s="46" t="s">
         <v>343</v>
       </c>
-      <c r="BS4" s="45" t="s">
+      <c r="BS4" s="46" t="s">
         <v>347</v>
       </c>
-      <c r="BT4" s="45" t="s">
+      <c r="BT4" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="45" t="s">
+      <c r="BU4" s="46" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="45" t="s">
+      <c r="BV4" s="46" t="s">
         <v>355</v>
       </c>
-      <c r="BW4" s="45" t="s">
+      <c r="BW4" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="45" t="s">
+      <c r="BX4" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="45" t="s">
+      <c r="BY4" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="45" t="s">
+      <c r="BZ4" s="46" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="45" t="s">
+      <c r="CA4" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="45" t="s">
+      <c r="CB4" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="45" t="s">
+      <c r="CC4" s="46" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="45" t="s">
+      <c r="CD4" s="46" t="s">
         <v>382</v>
       </c>
-      <c r="CE4" s="45" t="s">
+      <c r="CE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="45" t="s">
+      <c r="CF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="45" t="s">
+      <c r="CG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="45" t="s">
+      <c r="CH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="45" t="s">
+      <c r="CI4" s="46" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="45" t="s">
+      <c r="CJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="45" t="s">
+      <c r="CK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="45" t="s">
+      <c r="CL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="45" t="s">
+      <c r="CM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="45" t="s">
+      <c r="CN4" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="CO4" s="45" t="s">
+      <c r="CO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="45" t="s">
+      <c r="CP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="45" t="s">
+      <c r="CQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="45" t="s">
+      <c r="CR4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="45" t="s">
+      <c r="CS4" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="CT4" s="45" t="s">
+      <c r="CT4" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="CU4" s="45" t="s">
+      <c r="CU4" s="46" t="s">
         <v>420</v>
       </c>
+      <c r="CV4" s="46" t="s">
+        <v>422</v>
+      </c>
     </row>
-    <row r="5" spans="1:99" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:100" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -60923,77 +61279,78 @@
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
       <c r="AD5" s="56"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="46"/>
-      <c r="BM5" s="46"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
-      <c r="BQ5" s="46"/>
-      <c r="BR5" s="46"/>
-      <c r="BS5" s="46"/>
-      <c r="BT5" s="46"/>
-      <c r="BU5" s="46"/>
-      <c r="BV5" s="46"/>
-      <c r="BW5" s="46"/>
-      <c r="BX5" s="46"/>
-      <c r="BY5" s="46"/>
-      <c r="BZ5" s="45"/>
-      <c r="CA5" s="45"/>
-      <c r="CB5" s="45"/>
-      <c r="CC5" s="45"/>
-      <c r="CD5" s="45"/>
-      <c r="CE5" s="45"/>
-      <c r="CF5" s="45"/>
-      <c r="CG5" s="45"/>
-      <c r="CH5" s="45"/>
-      <c r="CI5" s="45"/>
-      <c r="CJ5" s="45"/>
-      <c r="CK5" s="45"/>
-      <c r="CL5" s="45"/>
-      <c r="CM5" s="45"/>
-      <c r="CN5" s="45"/>
-      <c r="CO5" s="45"/>
-      <c r="CP5" s="45"/>
-      <c r="CQ5" s="45"/>
-      <c r="CR5" s="45"/>
-      <c r="CS5" s="45"/>
-      <c r="CT5" s="45"/>
-      <c r="CU5" s="45"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="47"/>
+      <c r="BO5" s="47"/>
+      <c r="BP5" s="47"/>
+      <c r="BQ5" s="47"/>
+      <c r="BR5" s="47"/>
+      <c r="BS5" s="47"/>
+      <c r="BT5" s="47"/>
+      <c r="BU5" s="47"/>
+      <c r="BV5" s="47"/>
+      <c r="BW5" s="47"/>
+      <c r="BX5" s="47"/>
+      <c r="BY5" s="47"/>
+      <c r="BZ5" s="46"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
     </row>
-    <row r="6" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -61289,8 +61646,11 @@
       <c r="CU6" s="28">
         <v>28</v>
       </c>
+      <c r="CV6" s="28">
+        <v>21</v>
+      </c>
     </row>
-    <row r="7" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -61585,8 +61945,11 @@
       <c r="CU7" s="15">
         <v>1</v>
       </c>
+      <c r="CV7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -61881,8 +62244,11 @@
       <c r="CU8" s="28">
         <v>0</v>
       </c>
+      <c r="CV8" s="28">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -62178,8 +62544,11 @@
       <c r="CU9" s="15">
         <v>18</v>
       </c>
+      <c r="CV9" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -62474,8 +62843,11 @@
       <c r="CU10" s="15">
         <v>0</v>
       </c>
+      <c r="CV10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -62770,8 +63142,11 @@
       <c r="CU11" s="15">
         <v>5</v>
       </c>
+      <c r="CV11" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="12" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -63066,8 +63441,11 @@
       <c r="CU12" s="15">
         <v>1</v>
       </c>
+      <c r="CV12" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -63362,8 +63740,11 @@
       <c r="CU13" s="15">
         <v>15</v>
       </c>
+      <c r="CV13" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="14" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -63658,8 +64039,11 @@
       <c r="CU14" s="15">
         <v>9</v>
       </c>
+      <c r="CV14" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -63954,8 +64338,11 @@
       <c r="CU15" s="15">
         <v>5</v>
       </c>
+      <c r="CV15" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="16" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -64251,8 +64638,11 @@
       <c r="CU16" s="28">
         <v>11</v>
       </c>
+      <c r="CV16" s="28">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -64547,8 +64937,11 @@
       <c r="CU17" s="15">
         <v>52</v>
       </c>
+      <c r="CV17" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="18" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -64844,8 +65237,11 @@
       <c r="CU18" s="34">
         <v>388</v>
       </c>
+      <c r="CV18" s="34">
+        <v>346</v>
+      </c>
     </row>
-    <row r="19" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -65141,8 +65537,11 @@
       <c r="CU19" s="15">
         <v>54</v>
       </c>
+      <c r="CV19" s="15">
+        <v>35</v>
+      </c>
     </row>
-    <row r="20" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -65436,8 +65835,11 @@
       <c r="CU20" s="28">
         <v>121</v>
       </c>
+      <c r="CV20" s="28">
+        <v>105</v>
+      </c>
     </row>
-    <row r="21" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -65731,8 +66133,11 @@
       <c r="CU21" s="15">
         <v>22</v>
       </c>
+      <c r="CV21" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -66027,8 +66432,11 @@
       <c r="CU22" s="15">
         <v>2</v>
       </c>
+      <c r="CV22" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -66323,8 +66731,11 @@
       <c r="CU23" s="15">
         <v>0</v>
       </c>
+      <c r="CV23" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -66619,8 +67030,11 @@
       <c r="CU24" s="15">
         <v>2</v>
       </c>
+      <c r="CV24" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -66915,8 +67329,11 @@
       <c r="CU25" s="15">
         <v>0</v>
       </c>
+      <c r="CV25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -67211,8 +67628,11 @@
       <c r="CU26" s="15">
         <v>9</v>
       </c>
+      <c r="CV26" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="27" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -67507,8 +67927,11 @@
       <c r="CU27" s="15">
         <v>1</v>
       </c>
+      <c r="CV27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -67803,8 +68226,11 @@
       <c r="CU28" s="15">
         <v>2</v>
       </c>
+      <c r="CV28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -68099,8 +68525,11 @@
       <c r="CU29" s="15">
         <v>1</v>
       </c>
+      <c r="CV29" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -68393,8 +68822,11 @@
       <c r="CU30" s="15">
         <v>20</v>
       </c>
+      <c r="CV30" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="31" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -68690,8 +69122,11 @@
       <c r="CU31" s="15">
         <v>83</v>
       </c>
+      <c r="CV31" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="32" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -68986,8 +69421,11 @@
       <c r="CU32" s="15">
         <v>0</v>
       </c>
+      <c r="CV32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -69282,8 +69720,11 @@
       <c r="CU33" s="15">
         <v>0</v>
       </c>
+      <c r="CV33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -69579,8 +70020,11 @@
       <c r="CU34" s="15">
         <v>27</v>
       </c>
+      <c r="CV34" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="35" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -69876,8 +70320,11 @@
       <c r="CU35" s="15">
         <v>91</v>
       </c>
+      <c r="CV35" s="15">
+        <v>99</v>
+      </c>
     </row>
-    <row r="36" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -70170,8 +70617,11 @@
       <c r="CU36" s="28">
         <v>33</v>
       </c>
+      <c r="CV36" s="28">
+        <v>22</v>
+      </c>
     </row>
-    <row r="37" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -70467,8 +70917,11 @@
       <c r="CU37" s="15">
         <v>26</v>
       </c>
+      <c r="CV37" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="38" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -70763,8 +71216,11 @@
       <c r="CU38" s="15">
         <v>11</v>
       </c>
+      <c r="CV38" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="39" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -71059,8 +71515,11 @@
       <c r="CU39" s="15">
         <v>8</v>
       </c>
+      <c r="CV39" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="40" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -71355,8 +71814,11 @@
       <c r="CU40" s="15">
         <v>0</v>
       </c>
+      <c r="CV40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -71651,8 +72113,11 @@
       <c r="CU41" s="15">
         <v>0</v>
       </c>
+      <c r="CV41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -71947,8 +72412,11 @@
       <c r="CU42" s="15">
         <v>4</v>
       </c>
+      <c r="CV42" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="43" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -72243,8 +72711,11 @@
       <c r="CU43" s="28">
         <v>50</v>
       </c>
+      <c r="CV43" s="28">
+        <v>40</v>
+      </c>
     </row>
-    <row r="44" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -72539,8 +73010,11 @@
       <c r="CU44" s="15">
         <v>0</v>
       </c>
+      <c r="CV44" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -72835,8 +73309,11 @@
       <c r="CU45" s="15">
         <v>8</v>
       </c>
+      <c r="CV45" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -73131,8 +73608,11 @@
       <c r="CU46" s="15">
         <v>19</v>
       </c>
+      <c r="CV46" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -73427,8 +73907,11 @@
       <c r="CU47" s="15">
         <v>0</v>
       </c>
+      <c r="CV47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -73723,8 +74206,11 @@
       <c r="CU48" s="15">
         <v>12</v>
       </c>
+      <c r="CV48" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="49" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -74020,8 +74506,11 @@
       <c r="CU49" s="15">
         <v>5</v>
       </c>
+      <c r="CV49" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="50" spans="1:99" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -74314,8 +74803,11 @@
       <c r="CU50" s="15">
         <v>29</v>
       </c>
+      <c r="CV50" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="51" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -74610,8 +75102,11 @@
       <c r="CU51" s="15">
         <v>0</v>
       </c>
+      <c r="CV51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -74906,8 +75401,11 @@
       <c r="CU52" s="15">
         <v>8</v>
       </c>
+      <c r="CV52" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="53" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -75202,8 +75700,11 @@
       <c r="CU53" s="15">
         <v>17</v>
       </c>
+      <c r="CV53" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="54" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -75498,8 +75999,11 @@
       <c r="CU54" s="15">
         <v>4</v>
       </c>
+      <c r="CV54" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -75794,8 +76298,11 @@
       <c r="CU55" s="15">
         <v>1</v>
       </c>
+      <c r="CV55" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -76090,8 +76597,11 @@
       <c r="CU56" s="15">
         <v>0</v>
       </c>
+      <c r="CV56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -76386,8 +76896,11 @@
       <c r="CU57" s="15">
         <v>0</v>
       </c>
+      <c r="CV57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -76657,7 +77170,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CU58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CV58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -76776,8 +77289,12 @@
         <f t="shared" si="8"/>
         <v>1203</v>
       </c>
+      <c r="CV58" s="14">
+        <f t="shared" si="8"/>
+        <v>1008</v>
+      </c>
     </row>
-    <row r="59" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -76810,7 +77327,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -76843,7 +77360,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:99" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -76877,9 +77394,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="BD2:CU2"/>
-    <mergeCell ref="CR3:CU3"/>
+  <mergeCells count="110">
+    <mergeCell ref="BD2:CV2"/>
+    <mergeCell ref="CR3:CV3"/>
+    <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D4:D5"/>
@@ -76901,7 +77419,6 @@
     <mergeCell ref="AZ4:AZ5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="W4:W5"/>
-    <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="P4:P5"/>
@@ -76939,6 +77456,7 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="X4:X5"/>
+    <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="CL4:CL5"/>
     <mergeCell ref="CK4:CK5"/>
     <mergeCell ref="CJ4:CJ5"/>
@@ -76989,7 +77507,7 @@
     <mergeCell ref="CM4:CM5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CU57">
+  <conditionalFormatting sqref="CH6:CV57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -76998,7 +77516,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="99" max="66" man="1"/>
+    <brk id="100" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -77015,7 +77533,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CU57</xm:sqref>
+          <xm:sqref>BP6:CV57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -77028,7 +77546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CZ61"/>
+  <dimension ref="A1:DA61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -77037,11 +77555,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="104" width="10.875" style="1" customWidth="1"/>
-    <col min="105" max="16384" width="8.625" style="1"/>
+    <col min="34" max="105" width="10.875" style="1" customWidth="1"/>
+    <col min="106" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:105" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -77115,12 +77633,13 @@
       <c r="CR1" s="19"/>
       <c r="CS1" s="19"/>
       <c r="CT1" s="19"/>
-      <c r="CU1" s="19" t="s">
+      <c r="CU1" s="19"/>
+      <c r="CV1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="CV1" s="19"/>
+      <c r="CW1" s="19"/>
     </row>
-    <row r="2" spans="1:104" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:105" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -77177,59 +77696,60 @@
       <c r="BA2" s="52"/>
       <c r="BB2" s="52"/>
       <c r="BC2" s="88"/>
-      <c r="BD2" s="47" t="s">
+      <c r="BD2" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="47"/>
-      <c r="BF2" s="47"/>
-      <c r="BG2" s="47"/>
-      <c r="BH2" s="47"/>
-      <c r="BI2" s="47"/>
-      <c r="BJ2" s="47"/>
-      <c r="BK2" s="47"/>
-      <c r="BL2" s="47"/>
-      <c r="BM2" s="47"/>
-      <c r="BN2" s="47"/>
-      <c r="BO2" s="47"/>
-      <c r="BP2" s="47"/>
-      <c r="BQ2" s="47"/>
-      <c r="BR2" s="47"/>
-      <c r="BS2" s="47"/>
-      <c r="BT2" s="47"/>
-      <c r="BU2" s="47"/>
-      <c r="BV2" s="47"/>
-      <c r="BW2" s="47"/>
-      <c r="BX2" s="47"/>
-      <c r="BY2" s="47"/>
-      <c r="BZ2" s="47"/>
-      <c r="CA2" s="47"/>
-      <c r="CB2" s="47"/>
-      <c r="CC2" s="47"/>
-      <c r="CD2" s="47"/>
-      <c r="CE2" s="47"/>
-      <c r="CF2" s="47"/>
-      <c r="CG2" s="47"/>
-      <c r="CH2" s="47"/>
-      <c r="CI2" s="47"/>
-      <c r="CJ2" s="47"/>
-      <c r="CK2" s="47"/>
-      <c r="CL2" s="47"/>
-      <c r="CM2" s="47"/>
-      <c r="CN2" s="47"/>
-      <c r="CO2" s="47"/>
-      <c r="CP2" s="47"/>
-      <c r="CQ2" s="47"/>
-      <c r="CR2" s="47"/>
-      <c r="CS2" s="47"/>
-      <c r="CT2" s="47"/>
-      <c r="CU2" s="47"/>
-      <c r="CV2" s="20"/>
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="44"/>
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="44"/>
+      <c r="BN2" s="44"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="44"/>
+      <c r="BQ2" s="44"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="44"/>
+      <c r="BT2" s="44"/>
+      <c r="BU2" s="44"/>
+      <c r="BV2" s="44"/>
+      <c r="BW2" s="44"/>
+      <c r="BX2" s="44"/>
+      <c r="BY2" s="44"/>
+      <c r="BZ2" s="44"/>
+      <c r="CA2" s="44"/>
+      <c r="CB2" s="44"/>
+      <c r="CC2" s="44"/>
+      <c r="CD2" s="44"/>
+      <c r="CE2" s="44"/>
+      <c r="CF2" s="44"/>
+      <c r="CG2" s="44"/>
+      <c r="CH2" s="44"/>
+      <c r="CI2" s="44"/>
+      <c r="CJ2" s="44"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
+      <c r="CN2" s="44"/>
+      <c r="CO2" s="44"/>
+      <c r="CP2" s="44"/>
+      <c r="CQ2" s="44"/>
+      <c r="CR2" s="44"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
+      <c r="CU2" s="44"/>
+      <c r="CV2" s="44"/>
       <c r="CW2" s="20"/>
       <c r="CX2" s="20"/>
       <c r="CY2" s="20"/>
       <c r="CZ2" s="20"/>
+      <c r="DA2" s="20"/>
     </row>
-    <row r="3" spans="1:104" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:105" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -77274,75 +77794,76 @@
       <c r="AO3" s="81"/>
       <c r="AP3" s="81"/>
       <c r="AQ3" s="81"/>
-      <c r="AR3" s="44" t="s">
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="44"/>
-      <c r="AW3" s="44"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="44"/>
-      <c r="BK3" s="44"/>
-      <c r="BL3" s="44"/>
-      <c r="BM3" s="44"/>
-      <c r="BN3" s="44"/>
-      <c r="BO3" s="44"/>
-      <c r="BP3" s="44"/>
-      <c r="BQ3" s="44"/>
-      <c r="BR3" s="44"/>
-      <c r="BS3" s="44"/>
-      <c r="BT3" s="44"/>
-      <c r="BU3" s="44"/>
-      <c r="BV3" s="44"/>
-      <c r="BW3" s="44"/>
-      <c r="BX3" s="44"/>
-      <c r="BY3" s="44"/>
-      <c r="BZ3" s="44"/>
-      <c r="CA3" s="44"/>
-      <c r="CB3" s="44"/>
-      <c r="CC3" s="44"/>
-      <c r="CD3" s="44"/>
-      <c r="CE3" s="44"/>
-      <c r="CF3" s="44"/>
-      <c r="CG3" s="44"/>
-      <c r="CH3" s="44"/>
-      <c r="CI3" s="44"/>
-      <c r="CJ3" s="44"/>
-      <c r="CK3" s="44"/>
-      <c r="CL3" s="44"/>
-      <c r="CM3" s="44"/>
-      <c r="CN3" s="44"/>
-      <c r="CO3" s="44"/>
-      <c r="CP3" s="44"/>
-      <c r="CQ3" s="44"/>
-      <c r="CR3" s="44" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="44"/>
-      <c r="CT3" s="44"/>
-      <c r="CU3" s="44"/>
-      <c r="CV3" s="21"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
       <c r="CW3" s="21"/>
       <c r="CX3" s="21"/>
       <c r="CY3" s="21"/>
       <c r="CZ3" s="21"/>
+      <c r="DA3" s="21"/>
     </row>
-    <row r="4" spans="1:104" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:105" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -77505,145 +78026,148 @@
       <c r="BC4" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="BD4" s="45" t="s">
+      <c r="BD4" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="BE4" s="45" t="s">
+      <c r="BE4" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="BF4" s="45" t="s">
+      <c r="BF4" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="BG4" s="45" t="s">
+      <c r="BG4" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="BH4" s="45" t="s">
+      <c r="BH4" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="BI4" s="45" t="s">
+      <c r="BI4" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="BJ4" s="45" t="s">
+      <c r="BJ4" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="BK4" s="45" t="s">
+      <c r="BK4" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="BL4" s="45" t="s">
+      <c r="BL4" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="BM4" s="45" t="s">
+      <c r="BM4" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="BN4" s="45" t="s">
+      <c r="BN4" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="BO4" s="45" t="s">
+      <c r="BO4" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="BP4" s="45" t="s">
+      <c r="BP4" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="BQ4" s="45" t="s">
+      <c r="BQ4" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="BR4" s="45" t="s">
+      <c r="BR4" s="46" t="s">
         <v>344</v>
       </c>
-      <c r="BS4" s="45" t="s">
+      <c r="BS4" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="BT4" s="45" t="s">
+      <c r="BT4" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="BU4" s="45" t="s">
+      <c r="BU4" s="46" t="s">
         <v>353</v>
       </c>
-      <c r="BV4" s="45" t="s">
+      <c r="BV4" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="BW4" s="45" t="s">
+      <c r="BW4" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="BX4" s="45" t="s">
+      <c r="BX4" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="BY4" s="45" t="s">
+      <c r="BY4" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="BZ4" s="45" t="s">
+      <c r="BZ4" s="46" t="s">
         <v>365</v>
       </c>
-      <c r="CA4" s="45" t="s">
+      <c r="CA4" s="46" t="s">
         <v>374</v>
       </c>
-      <c r="CB4" s="45" t="s">
+      <c r="CB4" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="CC4" s="45" t="s">
+      <c r="CC4" s="46" t="s">
         <v>378</v>
       </c>
-      <c r="CD4" s="45" t="s">
+      <c r="CD4" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="CE4" s="45" t="s">
+      <c r="CE4" s="46" t="s">
         <v>384</v>
       </c>
-      <c r="CF4" s="45" t="s">
+      <c r="CF4" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="CG4" s="45" t="s">
+      <c r="CG4" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="CH4" s="45" t="s">
+      <c r="CH4" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="CI4" s="45" t="s">
+      <c r="CI4" s="46" t="s">
         <v>394</v>
       </c>
-      <c r="CJ4" s="45" t="s">
+      <c r="CJ4" s="46" t="s">
         <v>395</v>
       </c>
-      <c r="CK4" s="45" t="s">
+      <c r="CK4" s="46" t="s">
         <v>398</v>
       </c>
-      <c r="CL4" s="45" t="s">
+      <c r="CL4" s="46" t="s">
         <v>400</v>
       </c>
-      <c r="CM4" s="45" t="s">
+      <c r="CM4" s="46" t="s">
         <v>402</v>
       </c>
-      <c r="CN4" s="45" t="s">
+      <c r="CN4" s="46" t="s">
         <v>405</v>
       </c>
-      <c r="CO4" s="45" t="s">
+      <c r="CO4" s="46" t="s">
         <v>407</v>
       </c>
-      <c r="CP4" s="45" t="s">
+      <c r="CP4" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="CQ4" s="45" t="s">
+      <c r="CQ4" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="CR4" s="45" t="s">
+      <c r="CR4" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="CS4" s="45" t="s">
+      <c r="CS4" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="CT4" s="45" t="s">
+      <c r="CT4" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="CU4" s="45" t="s">
+      <c r="CU4" s="46" t="s">
         <v>420</v>
       </c>
-      <c r="CV4" s="89"/>
+      <c r="CV4" s="46" t="s">
+        <v>422</v>
+      </c>
       <c r="CW4" s="89"/>
       <c r="CX4" s="89"/>
       <c r="CY4" s="89"/>
       <c r="CZ4" s="89"/>
+      <c r="DA4" s="89"/>
     </row>
-    <row r="5" spans="1:104" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:105" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -77673,82 +78197,83 @@
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
       <c r="AD5" s="56"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="46"/>
-      <c r="BM5" s="46"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
-      <c r="BQ5" s="45"/>
-      <c r="BR5" s="45"/>
-      <c r="BS5" s="45"/>
-      <c r="BT5" s="45"/>
-      <c r="BU5" s="45"/>
-      <c r="BV5" s="45"/>
-      <c r="BW5" s="45"/>
-      <c r="BX5" s="45"/>
-      <c r="BY5" s="45"/>
-      <c r="BZ5" s="45"/>
-      <c r="CA5" s="45"/>
-      <c r="CB5" s="45"/>
-      <c r="CC5" s="45"/>
-      <c r="CD5" s="45"/>
-      <c r="CE5" s="45"/>
-      <c r="CF5" s="45"/>
-      <c r="CG5" s="45"/>
-      <c r="CH5" s="45"/>
-      <c r="CI5" s="45"/>
-      <c r="CJ5" s="45"/>
-      <c r="CK5" s="45"/>
-      <c r="CL5" s="45"/>
-      <c r="CM5" s="45"/>
-      <c r="CN5" s="45"/>
-      <c r="CO5" s="45"/>
-      <c r="CP5" s="45"/>
-      <c r="CQ5" s="45"/>
-      <c r="CR5" s="45"/>
-      <c r="CS5" s="45"/>
-      <c r="CT5" s="45"/>
-      <c r="CU5" s="45"/>
-      <c r="CV5" s="89"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="47"/>
+      <c r="BO5" s="47"/>
+      <c r="BP5" s="47"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="46"/>
+      <c r="BV5" s="46"/>
+      <c r="BW5" s="46"/>
+      <c r="BX5" s="46"/>
+      <c r="BY5" s="46"/>
+      <c r="BZ5" s="46"/>
+      <c r="CA5" s="46"/>
+      <c r="CB5" s="46"/>
+      <c r="CC5" s="46"/>
+      <c r="CD5" s="46"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
       <c r="CW5" s="89"/>
       <c r="CX5" s="89"/>
       <c r="CY5" s="89"/>
       <c r="CZ5" s="89"/>
+      <c r="DA5" s="89"/>
     </row>
-    <row r="6" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -78044,13 +78569,16 @@
       <c r="CU6" s="28">
         <v>119</v>
       </c>
-      <c r="CV6" s="22"/>
+      <c r="CV6" s="28">
+        <v>93</v>
+      </c>
       <c r="CW6" s="22"/>
       <c r="CX6" s="22"/>
       <c r="CY6" s="22"/>
       <c r="CZ6" s="22"/>
+      <c r="DA6" s="22"/>
     </row>
-    <row r="7" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -78345,13 +78873,16 @@
       <c r="CU7" s="15">
         <v>2</v>
       </c>
-      <c r="CV7" s="23"/>
+      <c r="CV7" s="15">
+        <v>0</v>
+      </c>
       <c r="CW7" s="23"/>
       <c r="CX7" s="23"/>
       <c r="CY7" s="23"/>
       <c r="CZ7" s="23"/>
+      <c r="DA7" s="23"/>
     </row>
-    <row r="8" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -78646,13 +79177,16 @@
       <c r="CU8" s="28">
         <v>39</v>
       </c>
-      <c r="CV8" s="23"/>
+      <c r="CV8" s="28">
+        <v>32</v>
+      </c>
       <c r="CW8" s="23"/>
       <c r="CX8" s="23"/>
       <c r="CY8" s="23"/>
       <c r="CZ8" s="23"/>
+      <c r="DA8" s="23"/>
     </row>
-    <row r="9" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -78948,13 +79482,16 @@
       <c r="CU9" s="15">
         <v>115</v>
       </c>
-      <c r="CV9" s="23"/>
+      <c r="CV9" s="15">
+        <v>115</v>
+      </c>
       <c r="CW9" s="23"/>
       <c r="CX9" s="23"/>
       <c r="CY9" s="23"/>
       <c r="CZ9" s="23"/>
+      <c r="DA9" s="23"/>
     </row>
-    <row r="10" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -79249,13 +79786,16 @@
       <c r="CU10" s="15">
         <v>1</v>
       </c>
-      <c r="CV10" s="23"/>
+      <c r="CV10" s="15">
+        <v>3</v>
+      </c>
       <c r="CW10" s="23"/>
       <c r="CX10" s="23"/>
       <c r="CY10" s="23"/>
       <c r="CZ10" s="23"/>
+      <c r="DA10" s="23"/>
     </row>
-    <row r="11" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -79550,13 +80090,16 @@
       <c r="CU11" s="15">
         <v>10</v>
       </c>
-      <c r="CV11" s="23"/>
+      <c r="CV11" s="15">
+        <v>12</v>
+      </c>
       <c r="CW11" s="23"/>
       <c r="CX11" s="23"/>
       <c r="CY11" s="23"/>
       <c r="CZ11" s="23"/>
+      <c r="DA11" s="23"/>
     </row>
-    <row r="12" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -79851,13 +80394,16 @@
       <c r="CU12" s="15">
         <v>6</v>
       </c>
-      <c r="CV12" s="23"/>
+      <c r="CV12" s="15">
+        <v>11</v>
+      </c>
       <c r="CW12" s="23"/>
       <c r="CX12" s="23"/>
       <c r="CY12" s="23"/>
       <c r="CZ12" s="23"/>
+      <c r="DA12" s="23"/>
     </row>
-    <row r="13" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -80152,13 +80698,16 @@
       <c r="CU13" s="15">
         <v>29</v>
       </c>
-      <c r="CV13" s="22"/>
+      <c r="CV13" s="15">
+        <v>27</v>
+      </c>
       <c r="CW13" s="22"/>
       <c r="CX13" s="22"/>
       <c r="CY13" s="22"/>
       <c r="CZ13" s="22"/>
+      <c r="DA13" s="22"/>
     </row>
-    <row r="14" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -80453,13 +81002,16 @@
       <c r="CU14" s="15">
         <v>19</v>
       </c>
-      <c r="CV14" s="23"/>
+      <c r="CV14" s="15">
+        <v>24</v>
+      </c>
       <c r="CW14" s="23"/>
       <c r="CX14" s="23"/>
       <c r="CY14" s="23"/>
       <c r="CZ14" s="23"/>
+      <c r="DA14" s="23"/>
     </row>
-    <row r="15" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -80754,13 +81306,16 @@
       <c r="CU15" s="15">
         <v>6</v>
       </c>
-      <c r="CV15" s="23"/>
+      <c r="CV15" s="15">
+        <v>8</v>
+      </c>
       <c r="CW15" s="23"/>
       <c r="CX15" s="23"/>
       <c r="CY15" s="23"/>
       <c r="CZ15" s="23"/>
+      <c r="DA15" s="23"/>
     </row>
-    <row r="16" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -81056,13 +81611,16 @@
       <c r="CU16" s="28">
         <v>160</v>
       </c>
-      <c r="CV16" s="22"/>
+      <c r="CV16" s="28">
+        <v>168</v>
+      </c>
       <c r="CW16" s="22"/>
       <c r="CX16" s="22"/>
       <c r="CY16" s="22"/>
       <c r="CZ16" s="22"/>
+      <c r="DA16" s="22"/>
     </row>
-    <row r="17" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -81357,13 +81915,16 @@
       <c r="CU17" s="15">
         <v>165</v>
       </c>
-      <c r="CV17" s="22"/>
+      <c r="CV17" s="15">
+        <v>140</v>
+      </c>
       <c r="CW17" s="22"/>
       <c r="CX17" s="22"/>
       <c r="CY17" s="22"/>
       <c r="CZ17" s="22"/>
+      <c r="DA17" s="22"/>
     </row>
-    <row r="18" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -81659,13 +82220,16 @@
       <c r="CU18" s="34">
         <v>2081</v>
       </c>
-      <c r="CV18" s="22"/>
+      <c r="CV18" s="34">
+        <v>1853</v>
+      </c>
       <c r="CW18" s="22"/>
       <c r="CX18" s="22"/>
       <c r="CY18" s="22"/>
       <c r="CZ18" s="22"/>
+      <c r="DA18" s="22"/>
     </row>
-    <row r="19" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -81961,13 +82525,16 @@
       <c r="CU19" s="15">
         <v>45</v>
       </c>
-      <c r="CV19" s="22"/>
+      <c r="CV19" s="15">
+        <v>37</v>
+      </c>
       <c r="CW19" s="22"/>
       <c r="CX19" s="22"/>
       <c r="CY19" s="22"/>
       <c r="CZ19" s="22"/>
+      <c r="DA19" s="22"/>
     </row>
-    <row r="20" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -82261,13 +82828,16 @@
       <c r="CU20" s="28">
         <v>162</v>
       </c>
-      <c r="CV20" s="22"/>
+      <c r="CV20" s="28">
+        <v>164</v>
+      </c>
       <c r="CW20" s="22"/>
       <c r="CX20" s="22"/>
       <c r="CY20" s="22"/>
       <c r="CZ20" s="22"/>
+      <c r="DA20" s="22"/>
     </row>
-    <row r="21" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -82561,13 +83131,16 @@
       <c r="CU21" s="15">
         <v>47</v>
       </c>
-      <c r="CV21" s="22"/>
+      <c r="CV21" s="15">
+        <v>27</v>
+      </c>
       <c r="CW21" s="22"/>
       <c r="CX21" s="22"/>
       <c r="CY21" s="22"/>
       <c r="CZ21" s="22"/>
+      <c r="DA21" s="22"/>
     </row>
-    <row r="22" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -82862,13 +83435,16 @@
       <c r="CU22" s="15">
         <v>3</v>
       </c>
-      <c r="CV22" s="23"/>
+      <c r="CV22" s="15">
+        <v>3</v>
+      </c>
       <c r="CW22" s="23"/>
       <c r="CX22" s="23"/>
       <c r="CY22" s="23"/>
       <c r="CZ22" s="23"/>
+      <c r="DA22" s="23"/>
     </row>
-    <row r="23" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -83163,13 +83739,16 @@
       <c r="CU23" s="15">
         <v>10</v>
       </c>
-      <c r="CV23" s="23"/>
+      <c r="CV23" s="15">
+        <v>7</v>
+      </c>
       <c r="CW23" s="23"/>
       <c r="CX23" s="23"/>
       <c r="CY23" s="23"/>
       <c r="CZ23" s="23"/>
+      <c r="DA23" s="23"/>
     </row>
-    <row r="24" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -83464,13 +84043,16 @@
       <c r="CU24" s="15">
         <v>20</v>
       </c>
-      <c r="CV24" s="22"/>
+      <c r="CV24" s="15">
+        <v>15</v>
+      </c>
       <c r="CW24" s="22"/>
       <c r="CX24" s="22"/>
       <c r="CY24" s="22"/>
       <c r="CZ24" s="22"/>
+      <c r="DA24" s="22"/>
     </row>
-    <row r="25" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -83765,13 +84347,16 @@
       <c r="CU25" s="15">
         <v>0</v>
       </c>
-      <c r="CV25" s="23"/>
+      <c r="CV25" s="15">
+        <v>1</v>
+      </c>
       <c r="CW25" s="23"/>
       <c r="CX25" s="23"/>
       <c r="CY25" s="23"/>
       <c r="CZ25" s="23"/>
+      <c r="DA25" s="23"/>
     </row>
-    <row r="26" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -84066,13 +84651,16 @@
       <c r="CU26" s="15">
         <v>18</v>
       </c>
-      <c r="CV26" s="23"/>
+      <c r="CV26" s="15">
+        <v>12</v>
+      </c>
       <c r="CW26" s="23"/>
       <c r="CX26" s="23"/>
       <c r="CY26" s="23"/>
       <c r="CZ26" s="23"/>
+      <c r="DA26" s="23"/>
     </row>
-    <row r="27" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -84367,13 +84955,16 @@
       <c r="CU27" s="15">
         <v>0</v>
       </c>
-      <c r="CV27" s="23"/>
+      <c r="CV27" s="15">
+        <v>1</v>
+      </c>
       <c r="CW27" s="23"/>
       <c r="CX27" s="23"/>
       <c r="CY27" s="23"/>
       <c r="CZ27" s="23"/>
+      <c r="DA27" s="23"/>
     </row>
-    <row r="28" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -84668,13 +85259,16 @@
       <c r="CU28" s="15">
         <v>7</v>
       </c>
-      <c r="CV28" s="22"/>
+      <c r="CV28" s="15">
+        <v>2</v>
+      </c>
       <c r="CW28" s="22"/>
       <c r="CX28" s="22"/>
       <c r="CY28" s="22"/>
       <c r="CZ28" s="22"/>
+      <c r="DA28" s="22"/>
     </row>
-    <row r="29" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -84969,13 +85563,16 @@
       <c r="CU29" s="15">
         <v>2</v>
       </c>
-      <c r="CV29" s="23"/>
+      <c r="CV29" s="15">
+        <v>5</v>
+      </c>
       <c r="CW29" s="23"/>
       <c r="CX29" s="23"/>
       <c r="CY29" s="23"/>
       <c r="CZ29" s="23"/>
+      <c r="DA29" s="23"/>
     </row>
-    <row r="30" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -85268,13 +85865,16 @@
       <c r="CU30" s="15">
         <v>46</v>
       </c>
-      <c r="CV30" s="23"/>
+      <c r="CV30" s="15">
+        <v>26</v>
+      </c>
       <c r="CW30" s="23"/>
       <c r="CX30" s="23"/>
       <c r="CY30" s="23"/>
       <c r="CZ30" s="23"/>
+      <c r="DA30" s="23"/>
     </row>
-    <row r="31" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -85570,13 +86170,16 @@
       <c r="CU31" s="15">
         <v>132</v>
       </c>
-      <c r="CV31" s="22"/>
+      <c r="CV31" s="15">
+        <v>90</v>
+      </c>
       <c r="CW31" s="22"/>
       <c r="CX31" s="22"/>
       <c r="CY31" s="22"/>
       <c r="CZ31" s="22"/>
+      <c r="DA31" s="22"/>
     </row>
-    <row r="32" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -85871,13 +86474,16 @@
       <c r="CU32" s="15">
         <v>2</v>
       </c>
-      <c r="CV32" s="23"/>
+      <c r="CV32" s="15">
+        <v>1</v>
+      </c>
       <c r="CW32" s="23"/>
       <c r="CX32" s="23"/>
       <c r="CY32" s="23"/>
       <c r="CZ32" s="23"/>
+      <c r="DA32" s="23"/>
     </row>
-    <row r="33" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -86172,13 +86778,16 @@
       <c r="CU33" s="15">
         <v>0</v>
       </c>
-      <c r="CV33" s="23"/>
+      <c r="CV33" s="15">
+        <v>1</v>
+      </c>
       <c r="CW33" s="23"/>
       <c r="CX33" s="23"/>
       <c r="CY33" s="23"/>
       <c r="CZ33" s="23"/>
+      <c r="DA33" s="23"/>
     </row>
-    <row r="34" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -86474,13 +87083,16 @@
       <c r="CU34" s="15">
         <v>160</v>
       </c>
-      <c r="CV34" s="22"/>
+      <c r="CV34" s="15">
+        <v>142</v>
+      </c>
       <c r="CW34" s="22"/>
       <c r="CX34" s="22"/>
       <c r="CY34" s="22"/>
       <c r="CZ34" s="22"/>
+      <c r="DA34" s="22"/>
     </row>
-    <row r="35" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -86776,13 +87388,16 @@
       <c r="CU35" s="15">
         <v>314</v>
       </c>
-      <c r="CV35" s="22"/>
+      <c r="CV35" s="15">
+        <v>286</v>
+      </c>
       <c r="CW35" s="22"/>
       <c r="CX35" s="22"/>
       <c r="CY35" s="22"/>
       <c r="CZ35" s="22"/>
+      <c r="DA35" s="22"/>
     </row>
-    <row r="36" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -87075,13 +87690,16 @@
       <c r="CU36" s="28">
         <v>35</v>
       </c>
-      <c r="CV36" s="22"/>
+      <c r="CV36" s="28">
+        <v>23</v>
+      </c>
       <c r="CW36" s="22"/>
       <c r="CX36" s="22"/>
       <c r="CY36" s="22"/>
       <c r="CZ36" s="22"/>
+      <c r="DA36" s="22"/>
     </row>
-    <row r="37" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -87377,13 +87995,16 @@
       <c r="CU37" s="15">
         <v>127</v>
       </c>
-      <c r="CV37" s="22"/>
+      <c r="CV37" s="15">
+        <v>84</v>
+      </c>
       <c r="CW37" s="22"/>
       <c r="CX37" s="22"/>
       <c r="CY37" s="22"/>
       <c r="CZ37" s="22"/>
+      <c r="DA37" s="22"/>
     </row>
-    <row r="38" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -87678,13 +88299,16 @@
       <c r="CU38" s="15">
         <v>25</v>
       </c>
-      <c r="CV38" s="23"/>
+      <c r="CV38" s="15">
+        <v>12</v>
+      </c>
       <c r="CW38" s="23"/>
       <c r="CX38" s="23"/>
       <c r="CY38" s="23"/>
       <c r="CZ38" s="23"/>
+      <c r="DA38" s="23"/>
     </row>
-    <row r="39" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -87979,13 +88603,16 @@
       <c r="CU39" s="15">
         <v>14</v>
       </c>
-      <c r="CV39" s="23"/>
+      <c r="CV39" s="15">
+        <v>9</v>
+      </c>
       <c r="CW39" s="23"/>
       <c r="CX39" s="23"/>
       <c r="CY39" s="23"/>
       <c r="CZ39" s="23"/>
+      <c r="DA39" s="23"/>
     </row>
-    <row r="40" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -88280,13 +88907,16 @@
       <c r="CU40" s="15">
         <v>0</v>
       </c>
-      <c r="CV40" s="23"/>
+      <c r="CV40" s="15">
+        <v>0</v>
+      </c>
       <c r="CW40" s="23"/>
       <c r="CX40" s="23"/>
       <c r="CY40" s="23"/>
       <c r="CZ40" s="23"/>
+      <c r="DA40" s="23"/>
     </row>
-    <row r="41" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -88581,13 +89211,16 @@
       <c r="CU41" s="15">
         <v>0</v>
       </c>
-      <c r="CV41" s="23"/>
+      <c r="CV41" s="15">
+        <v>0</v>
+      </c>
       <c r="CW41" s="23"/>
       <c r="CX41" s="23"/>
       <c r="CY41" s="23"/>
       <c r="CZ41" s="23"/>
+      <c r="DA41" s="23"/>
     </row>
-    <row r="42" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -88882,13 +89515,16 @@
       <c r="CU42" s="15">
         <v>16</v>
       </c>
-      <c r="CV42" s="23"/>
+      <c r="CV42" s="15">
+        <v>13</v>
+      </c>
       <c r="CW42" s="23"/>
       <c r="CX42" s="23"/>
       <c r="CY42" s="23"/>
       <c r="CZ42" s="23"/>
+      <c r="DA42" s="23"/>
     </row>
-    <row r="43" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -89183,13 +89819,16 @@
       <c r="CU43" s="28">
         <v>78</v>
       </c>
-      <c r="CV43" s="23"/>
+      <c r="CV43" s="28">
+        <v>51</v>
+      </c>
       <c r="CW43" s="23"/>
       <c r="CX43" s="23"/>
       <c r="CY43" s="23"/>
       <c r="CZ43" s="23"/>
+      <c r="DA43" s="23"/>
     </row>
-    <row r="44" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -89484,13 +90123,16 @@
       <c r="CU44" s="15">
         <v>1</v>
       </c>
-      <c r="CV44" s="23"/>
+      <c r="CV44" s="15">
+        <v>6</v>
+      </c>
       <c r="CW44" s="23"/>
       <c r="CX44" s="23"/>
       <c r="CY44" s="23"/>
       <c r="CZ44" s="23"/>
+      <c r="DA44" s="23"/>
     </row>
-    <row r="45" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -89785,13 +90427,16 @@
       <c r="CU45" s="15">
         <v>18</v>
       </c>
-      <c r="CV45" s="22"/>
+      <c r="CV45" s="15">
+        <v>22</v>
+      </c>
       <c r="CW45" s="22"/>
       <c r="CX45" s="22"/>
       <c r="CY45" s="22"/>
       <c r="CZ45" s="22"/>
+      <c r="DA45" s="22"/>
     </row>
-    <row r="46" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -90086,13 +90731,16 @@
       <c r="CU46" s="15">
         <v>11</v>
       </c>
-      <c r="CV46" s="23"/>
+      <c r="CV46" s="15">
+        <v>15</v>
+      </c>
       <c r="CW46" s="23"/>
       <c r="CX46" s="23"/>
       <c r="CY46" s="23"/>
       <c r="CZ46" s="23"/>
+      <c r="DA46" s="23"/>
     </row>
-    <row r="47" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -90387,13 +91035,16 @@
       <c r="CU47" s="15">
         <v>1</v>
       </c>
-      <c r="CV47" s="23"/>
+      <c r="CV47" s="15">
+        <v>3</v>
+      </c>
       <c r="CW47" s="23"/>
       <c r="CX47" s="23"/>
       <c r="CY47" s="23"/>
       <c r="CZ47" s="23"/>
+      <c r="DA47" s="23"/>
     </row>
-    <row r="48" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -90688,13 +91339,16 @@
       <c r="CU48" s="15">
         <v>10</v>
       </c>
-      <c r="CV48" s="23"/>
+      <c r="CV48" s="15">
+        <v>8</v>
+      </c>
       <c r="CW48" s="23"/>
       <c r="CX48" s="23"/>
       <c r="CY48" s="23"/>
       <c r="CZ48" s="23"/>
+      <c r="DA48" s="23"/>
     </row>
-    <row r="49" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -90990,13 +91644,16 @@
       <c r="CU49" s="15">
         <v>110</v>
       </c>
-      <c r="CV49" s="22"/>
+      <c r="CV49" s="15">
+        <v>54</v>
+      </c>
       <c r="CW49" s="22"/>
       <c r="CX49" s="22"/>
       <c r="CY49" s="22"/>
       <c r="CZ49" s="22"/>
+      <c r="DA49" s="22"/>
     </row>
-    <row r="50" spans="1:104" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -91289,13 +91946,16 @@
       <c r="CU50" s="15">
         <v>33</v>
       </c>
-      <c r="CV50" s="22"/>
+      <c r="CV50" s="15">
+        <v>13</v>
+      </c>
       <c r="CW50" s="22"/>
       <c r="CX50" s="22"/>
       <c r="CY50" s="22"/>
       <c r="CZ50" s="22"/>
+      <c r="DA50" s="22"/>
     </row>
-    <row r="51" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -91590,13 +92250,16 @@
       <c r="CU51" s="15">
         <v>20</v>
       </c>
-      <c r="CV51" s="23"/>
+      <c r="CV51" s="15">
+        <v>3</v>
+      </c>
       <c r="CW51" s="23"/>
       <c r="CX51" s="23"/>
       <c r="CY51" s="23"/>
       <c r="CZ51" s="23"/>
+      <c r="DA51" s="23"/>
     </row>
-    <row r="52" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -91891,13 +92554,16 @@
       <c r="CU52" s="15">
         <v>20</v>
       </c>
-      <c r="CV52" s="23"/>
+      <c r="CV52" s="15">
+        <v>19</v>
+      </c>
       <c r="CW52" s="23"/>
       <c r="CX52" s="23"/>
       <c r="CY52" s="23"/>
       <c r="CZ52" s="23"/>
+      <c r="DA52" s="23"/>
     </row>
-    <row r="53" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -92192,13 +92858,16 @@
       <c r="CU53" s="15">
         <v>47</v>
       </c>
-      <c r="CV53" s="23"/>
+      <c r="CV53" s="15">
+        <v>58</v>
+      </c>
       <c r="CW53" s="23"/>
       <c r="CX53" s="23"/>
       <c r="CY53" s="23"/>
       <c r="CZ53" s="23"/>
+      <c r="DA53" s="23"/>
     </row>
-    <row r="54" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -92493,13 +93162,16 @@
       <c r="CU54" s="15">
         <v>5</v>
       </c>
-      <c r="CV54" s="23"/>
+      <c r="CV54" s="15">
+        <v>4</v>
+      </c>
       <c r="CW54" s="23"/>
       <c r="CX54" s="23"/>
       <c r="CY54" s="23"/>
       <c r="CZ54" s="23"/>
+      <c r="DA54" s="23"/>
     </row>
-    <row r="55" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -92794,13 +93466,16 @@
       <c r="CU55" s="15">
         <v>18</v>
       </c>
-      <c r="CV55" s="23"/>
+      <c r="CV55" s="15">
+        <v>12</v>
+      </c>
       <c r="CW55" s="23"/>
       <c r="CX55" s="23"/>
       <c r="CY55" s="23"/>
       <c r="CZ55" s="23"/>
+      <c r="DA55" s="23"/>
     </row>
-    <row r="56" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -93095,13 +93770,16 @@
       <c r="CU56" s="15">
         <v>3</v>
       </c>
-      <c r="CV56" s="23"/>
+      <c r="CV56" s="15">
+        <v>1</v>
+      </c>
       <c r="CW56" s="23"/>
       <c r="CX56" s="23"/>
       <c r="CY56" s="23"/>
       <c r="CZ56" s="23"/>
+      <c r="DA56" s="23"/>
     </row>
-    <row r="57" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -93396,13 +94074,16 @@
       <c r="CU57" s="15">
         <v>4</v>
       </c>
-      <c r="CV57" s="23"/>
+      <c r="CV57" s="15">
+        <v>0</v>
+      </c>
       <c r="CW57" s="23"/>
       <c r="CX57" s="23"/>
       <c r="CY57" s="23"/>
       <c r="CZ57" s="23"/>
+      <c r="DA57" s="23"/>
     </row>
-    <row r="58" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -93672,7 +94353,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CU58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CV58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -93791,13 +94472,17 @@
         <f t="shared" si="4"/>
         <v>4316</v>
       </c>
-      <c r="CV58" s="24"/>
+      <c r="CV58" s="14">
+        <f t="shared" si="4"/>
+        <v>3716</v>
+      </c>
       <c r="CW58" s="24"/>
       <c r="CX58" s="24"/>
       <c r="CY58" s="24"/>
       <c r="CZ58" s="24"/>
+      <c r="DA58" s="24"/>
     </row>
-    <row r="59" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -93830,7 +94515,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -93863,7 +94548,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:104" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -93897,22 +94582,25 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="114">
-    <mergeCell ref="CZ4:CZ5"/>
+  <mergeCells count="115">
+    <mergeCell ref="BD2:CV2"/>
+    <mergeCell ref="CR3:CV3"/>
+    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="CF4:CF5"/>
@@ -93964,17 +94652,6 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AM4:AM5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
     <mergeCell ref="BZ4:BZ5"/>
@@ -93988,9 +94665,19 @@
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="BD2:CU2"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CL4:CL5"/>
@@ -94009,9 +94696,8 @@
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="CR3:CU3"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="BW4:BW5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -94035,7 +94721,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CU57</xm:sqref>
+          <xm:sqref>BP6:CV57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050207-2\ＪＯＢ050207-2\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050214-3\ＪＯＢ050214-3\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13110" windowHeight="10680"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CV$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CV$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EV$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EV$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CW$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CW$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EW$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EW$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="427">
   <si>
     <t>都道府県</t>
   </si>
@@ -4562,6 +4562,24 @@
 2/6(日)分
 【1月第6週
 2月第1週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2/6(月)～
+2/12(日)分
+【2月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2/7(月)～
+2/13(日)分
+【2月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2/6(月)～
+2/12(日)分
+【2月第2週】</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9364,7 +9382,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EW61"/>
+  <dimension ref="A1:EX61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9378,11 +9396,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="152" width="10.875" style="1" customWidth="1"/>
-    <col min="153" max="16384" width="8.625" style="1"/>
+    <col min="106" max="153" width="10.875" style="1" customWidth="1"/>
+    <col min="154" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:153" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:154" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9461,11 +9479,12 @@
       <c r="ES1" s="19"/>
       <c r="ET1" s="19"/>
       <c r="EU1" s="19"/>
-      <c r="EV1" s="19" t="s">
+      <c r="EV1" s="19"/>
+      <c r="EW1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:153" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:154" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -9623,8 +9642,9 @@
       <c r="ET2" s="44"/>
       <c r="EU2" s="44"/>
       <c r="EV2" s="44"/>
+      <c r="EW2" s="44"/>
     </row>
-    <row r="3" spans="1:153" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:154" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="45" t="s">
@@ -9788,8 +9808,9 @@
       <c r="ET3" s="45"/>
       <c r="EU3" s="45"/>
       <c r="EV3" s="45"/>
+      <c r="EW3" s="45"/>
     </row>
-    <row r="4" spans="1:153" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:154" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -10243,8 +10264,11 @@
       <c r="EV4" s="46" t="s">
         <v>422</v>
       </c>
+      <c r="EW4" s="46" t="s">
+        <v>424</v>
+      </c>
     </row>
-    <row r="5" spans="1:153" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:154" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="55"/>
@@ -10396,8 +10420,9 @@
       <c r="ET5" s="46"/>
       <c r="EU5" s="46"/>
       <c r="EV5" s="46"/>
+      <c r="EW5" s="46"/>
     </row>
-    <row r="6" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10852,9 +10877,12 @@
       <c r="EV6" s="28">
         <v>114</v>
       </c>
-      <c r="EW6" s="1"/>
+      <c r="EW6" s="28">
+        <v>141</v>
+      </c>
+      <c r="EX6" s="1"/>
     </row>
-    <row r="7" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11308,8 +11336,11 @@
       <c r="EV7" s="15">
         <v>0</v>
       </c>
+      <c r="EW7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11763,8 +11794,11 @@
       <c r="EV8" s="28">
         <v>33</v>
       </c>
+      <c r="EW8" s="28">
+        <v>26</v>
+      </c>
     </row>
-    <row r="9" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12219,8 +12253,11 @@
       <c r="EV9" s="15">
         <v>130</v>
       </c>
+      <c r="EW9" s="15">
+        <v>119</v>
+      </c>
     </row>
-    <row r="10" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12672,8 +12709,11 @@
       <c r="EV10" s="15">
         <v>3</v>
       </c>
+      <c r="EW10" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13127,8 +13167,11 @@
       <c r="EV11" s="15">
         <v>18</v>
       </c>
+      <c r="EW11" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="12" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13582,8 +13625,11 @@
       <c r="EV12" s="15">
         <v>11</v>
       </c>
+      <c r="EW12" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14037,9 +14083,12 @@
       <c r="EV13" s="15">
         <v>45</v>
       </c>
-      <c r="EW13" s="1"/>
+      <c r="EW13" s="15">
+        <v>40</v>
+      </c>
+      <c r="EX13" s="1"/>
     </row>
-    <row r="14" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14493,8 +14542,11 @@
       <c r="EV14" s="15">
         <v>37</v>
       </c>
+      <c r="EW14" s="15">
+        <v>40</v>
+      </c>
     </row>
-    <row r="15" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -14948,8 +15000,11 @@
       <c r="EV15" s="15">
         <v>14</v>
       </c>
+      <c r="EW15" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="16" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15404,9 +15459,12 @@
       <c r="EV16" s="28">
         <v>171</v>
       </c>
-      <c r="EW16" s="1"/>
+      <c r="EW16" s="28">
+        <v>168</v>
+      </c>
+      <c r="EX16" s="1"/>
     </row>
-    <row r="17" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15860,9 +15918,12 @@
       <c r="EV17" s="15">
         <v>181</v>
       </c>
-      <c r="EW17" s="1"/>
+      <c r="EW17" s="15">
+        <v>163</v>
+      </c>
+      <c r="EX17" s="1"/>
     </row>
-    <row r="18" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16317,9 +16378,12 @@
       <c r="EV18" s="34">
         <v>2199</v>
       </c>
-      <c r="EW18" s="1"/>
+      <c r="EW18" s="34">
+        <v>2220</v>
+      </c>
+      <c r="EX18" s="1"/>
     </row>
-    <row r="19" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="70" t="s">
         <v>27</v>
@@ -16774,9 +16838,12 @@
       <c r="EV19" s="15">
         <v>72</v>
       </c>
-      <c r="EW19" s="1"/>
+      <c r="EW19" s="15">
+        <v>82</v>
+      </c>
+      <c r="EX19" s="1"/>
     </row>
-    <row r="20" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
@@ -17229,9 +17296,12 @@
       <c r="EV20" s="28">
         <v>269</v>
       </c>
-      <c r="EW20" s="1"/>
+      <c r="EW20" s="28">
+        <v>209</v>
+      </c>
+      <c r="EX20" s="1"/>
     </row>
-    <row r="21" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
@@ -17684,9 +17754,12 @@
       <c r="EV21" s="15">
         <v>38</v>
       </c>
-      <c r="EW21" s="1"/>
+      <c r="EW21" s="15">
+        <v>26</v>
+      </c>
+      <c r="EX21" s="1"/>
     </row>
-    <row r="22" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18140,8 +18213,11 @@
       <c r="EV22" s="15">
         <v>4</v>
       </c>
+      <c r="EW22" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18595,8 +18671,11 @@
       <c r="EV23" s="15">
         <v>8</v>
       </c>
+      <c r="EW23" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19050,9 +19129,12 @@
       <c r="EV24" s="15">
         <v>18</v>
       </c>
-      <c r="EW24" s="1"/>
+      <c r="EW24" s="15">
+        <v>15</v>
+      </c>
+      <c r="EX24" s="1"/>
     </row>
-    <row r="25" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19506,8 +19588,11 @@
       <c r="EV25" s="15">
         <v>1</v>
       </c>
+      <c r="EW25" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -19961,8 +20046,11 @@
       <c r="EV26" s="15">
         <v>23</v>
       </c>
+      <c r="EW26" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="27" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20416,8 +20504,11 @@
       <c r="EV27" s="15">
         <v>1</v>
       </c>
+      <c r="EW27" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -20871,9 +20962,12 @@
       <c r="EV28" s="15">
         <v>2</v>
       </c>
-      <c r="EW28" s="1"/>
+      <c r="EW28" s="15">
+        <v>0</v>
+      </c>
+      <c r="EX28" s="1"/>
     </row>
-    <row r="29" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -21327,8 +21421,11 @@
       <c r="EV29" s="15">
         <v>7</v>
       </c>
+      <c r="EW29" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="30" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -21780,8 +21877,11 @@
       <c r="EV30" s="15">
         <v>46</v>
       </c>
+      <c r="EW30" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="31" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -22236,9 +22336,12 @@
       <c r="EV31" s="15">
         <v>133</v>
       </c>
-      <c r="EW31" s="1"/>
+      <c r="EW31" s="15">
+        <v>114</v>
+      </c>
+      <c r="EX31" s="1"/>
     </row>
-    <row r="32" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22692,8 +22795,11 @@
       <c r="EV32" s="15">
         <v>1</v>
       </c>
+      <c r="EW32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -23147,8 +23253,11 @@
       <c r="EV33" s="15">
         <v>1</v>
       </c>
+      <c r="EW33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23603,9 +23712,12 @@
       <c r="EV34" s="15">
         <v>163</v>
       </c>
-      <c r="EW34" s="1"/>
+      <c r="EW34" s="15">
+        <v>171</v>
+      </c>
+      <c r="EX34" s="1"/>
     </row>
-    <row r="35" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="70" t="s">
         <v>56</v>
@@ -24060,9 +24172,12 @@
       <c r="EV35" s="15">
         <v>385</v>
       </c>
-      <c r="EW35" s="1"/>
+      <c r="EW35" s="15">
+        <v>379</v>
+      </c>
+      <c r="EX35" s="1"/>
     </row>
-    <row r="36" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -24514,9 +24629,12 @@
       <c r="EV36" s="28">
         <v>45</v>
       </c>
-      <c r="EW36" s="1"/>
+      <c r="EW36" s="28">
+        <v>33</v>
+      </c>
+      <c r="EX36" s="1"/>
     </row>
-    <row r="37" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -24971,9 +25089,12 @@
       <c r="EV37" s="15">
         <v>97</v>
       </c>
-      <c r="EW37" s="1"/>
+      <c r="EW37" s="15">
+        <v>96</v>
+      </c>
+      <c r="EX37" s="1"/>
     </row>
-    <row r="38" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -25427,8 +25548,11 @@
       <c r="EV38" s="15">
         <v>26</v>
       </c>
+      <c r="EW38" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="39" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -25882,8 +26006,11 @@
       <c r="EV39" s="15">
         <v>14</v>
       </c>
+      <c r="EW39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -26337,8 +26464,11 @@
       <c r="EV40" s="15">
         <v>0</v>
       </c>
+      <c r="EW40" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -26792,8 +26922,11 @@
       <c r="EV41" s="15">
         <v>0</v>
       </c>
+      <c r="EW41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -27247,8 +27380,11 @@
       <c r="EV42" s="15">
         <v>20</v>
       </c>
+      <c r="EW42" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="43" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27702,8 +27838,11 @@
       <c r="EV43" s="28">
         <v>91</v>
       </c>
+      <c r="EW43" s="28">
+        <v>83</v>
+      </c>
     </row>
-    <row r="44" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -28157,8 +28296,11 @@
       <c r="EV44" s="15">
         <v>8</v>
       </c>
+      <c r="EW44" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28612,9 +28754,12 @@
       <c r="EV45" s="15">
         <v>32</v>
       </c>
-      <c r="EW45" s="1"/>
+      <c r="EW45" s="15">
+        <v>23</v>
+      </c>
+      <c r="EX45" s="1"/>
     </row>
-    <row r="46" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -29068,8 +29213,11 @@
       <c r="EV46" s="15">
         <v>20</v>
       </c>
+      <c r="EW46" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="47" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -29523,8 +29671,11 @@
       <c r="EV47" s="15">
         <v>4</v>
       </c>
+      <c r="EW47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -29978,8 +30129,11 @@
       <c r="EV48" s="15">
         <v>25</v>
       </c>
+      <c r="EW48" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="49" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="70" t="s">
         <v>83</v>
@@ -30434,9 +30588,12 @@
       <c r="EV49" s="15">
         <v>61</v>
       </c>
-      <c r="EW49" s="1"/>
+      <c r="EW49" s="15">
+        <v>104</v>
+      </c>
+      <c r="EX49" s="1"/>
     </row>
-    <row r="50" spans="1:153" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:154" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -30888,9 +31045,12 @@
       <c r="EV50" s="15">
         <v>30</v>
       </c>
-      <c r="EW50" s="1"/>
+      <c r="EW50" s="15">
+        <v>27</v>
+      </c>
+      <c r="EX50" s="1"/>
     </row>
-    <row r="51" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -31344,8 +31504,11 @@
       <c r="EV51" s="15">
         <v>3</v>
       </c>
+      <c r="EW51" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="52" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -31799,8 +31962,11 @@
       <c r="EV52" s="15">
         <v>25</v>
       </c>
+      <c r="EW52" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="53" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -32254,8 +32420,11 @@
       <c r="EV53" s="15">
         <v>75</v>
       </c>
+      <c r="EW53" s="15">
+        <v>87</v>
+      </c>
     </row>
-    <row r="54" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -32709,8 +32878,11 @@
       <c r="EV54" s="15">
         <v>6</v>
       </c>
+      <c r="EW54" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -33164,8 +33336,11 @@
       <c r="EV55" s="15">
         <v>12</v>
       </c>
+      <c r="EW55" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="56" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -33619,8 +33794,11 @@
       <c r="EV56" s="15">
         <v>1</v>
       </c>
+      <c r="EW56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -34074,8 +34252,11 @@
       <c r="EV57" s="15">
         <v>1</v>
       </c>
+      <c r="EW57" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -34553,7 +34734,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:EV58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:EW58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -34676,8 +34857,12 @@
         <f t="shared" si="10"/>
         <v>4724</v>
       </c>
+      <c r="EW58" s="14">
+        <f t="shared" si="10"/>
+        <v>4649</v>
+      </c>
     </row>
-    <row r="59" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -34761,7 +34946,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -34845,7 +35030,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:153" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:154" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -34930,7 +35115,7 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="167">
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -35080,8 +35265,9 @@
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="DE2:EV2"/>
-    <mergeCell ref="ER3:EV3"/>
+    <mergeCell ref="DE2:EW2"/>
+    <mergeCell ref="ER3:EW3"/>
+    <mergeCell ref="EW4:EW5"/>
     <mergeCell ref="EV4:EV5"/>
     <mergeCell ref="DE3:EQ3"/>
     <mergeCell ref="DT4:DT5"/>
@@ -35109,7 +35295,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:EV57">
+  <conditionalFormatting sqref="DP6:EW57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -35129,7 +35315,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:EV58"/>
+  <dimension ref="B1:EW58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -35152,11 +35338,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="152" width="10.875" style="1" customWidth="1"/>
-    <col min="153" max="16384" width="8.625" style="1"/>
+    <col min="106" max="153" width="10.875" style="1" customWidth="1"/>
+    <col min="154" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:152" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:153" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="82" t="s">
         <v>323</v>
       </c>
@@ -35235,11 +35421,12 @@
       <c r="ES1" s="19"/>
       <c r="ET1" s="19"/>
       <c r="EU1" s="19"/>
-      <c r="EV1" s="19" t="s">
+      <c r="EV1" s="19"/>
+      <c r="EW1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:152" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:153" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="44" t="s">
@@ -35397,8 +35584,9 @@
       <c r="ET2" s="44"/>
       <c r="EU2" s="44"/>
       <c r="EV2" s="44"/>
+      <c r="EW2" s="44"/>
     </row>
-    <row r="3" spans="2:152" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:153" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -35562,8 +35750,9 @@
       <c r="ET3" s="45"/>
       <c r="EU3" s="45"/>
       <c r="EV3" s="45"/>
+      <c r="EW3" s="45"/>
     </row>
-    <row r="4" spans="2:152" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:153" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -36017,8 +36206,11 @@
       <c r="EV4" s="46" t="s">
         <v>423</v>
       </c>
+      <c r="EW4" s="46" t="s">
+        <v>425</v>
+      </c>
     </row>
-    <row r="5" spans="2:152" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:153" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="49"/>
@@ -36170,8 +36362,9 @@
       <c r="ET5" s="46"/>
       <c r="EU5" s="46"/>
       <c r="EV5" s="46"/>
+      <c r="EW5" s="46"/>
     </row>
-    <row r="6" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -36625,8 +36818,11 @@
       <c r="EV6" s="28">
         <v>161</v>
       </c>
+      <c r="EW6" s="28">
+        <v>166</v>
+      </c>
     </row>
-    <row r="7" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -37080,8 +37276,11 @@
       <c r="EV7" s="15">
         <v>2</v>
       </c>
+      <c r="EW7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -37535,8 +37734,11 @@
       <c r="EV8" s="28">
         <v>7</v>
       </c>
+      <c r="EW8" s="28">
+        <v>15</v>
+      </c>
     </row>
-    <row r="9" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -37990,8 +38192,11 @@
       <c r="EV9" s="15">
         <v>77</v>
       </c>
+      <c r="EW9" s="15">
+        <v>79</v>
+      </c>
     </row>
-    <row r="10" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -38445,8 +38650,11 @@
       <c r="EV10" s="15">
         <v>0</v>
       </c>
+      <c r="EW10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -38900,8 +39108,11 @@
       <c r="EV11" s="15">
         <v>11</v>
       </c>
+      <c r="EW11" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -39355,8 +39566,11 @@
       <c r="EV12" s="15">
         <v>5</v>
       </c>
+      <c r="EW12" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -39810,8 +40024,11 @@
       <c r="EV13" s="15">
         <v>24</v>
       </c>
+      <c r="EW13" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="14" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -40265,8 +40482,11 @@
       <c r="EV14" s="15">
         <v>52</v>
       </c>
+      <c r="EW14" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="15" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -40720,8 +40940,11 @@
       <c r="EV15" s="15">
         <v>6</v>
       </c>
+      <c r="EW15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -41175,8 +41398,11 @@
       <c r="EV16" s="28">
         <v>185</v>
       </c>
+      <c r="EW16" s="28">
+        <v>171</v>
+      </c>
     </row>
-    <row r="17" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -41630,8 +41856,11 @@
       <c r="EV17" s="15">
         <v>227</v>
       </c>
+      <c r="EW17" s="15">
+        <v>205</v>
+      </c>
     </row>
-    <row r="18" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -42085,8 +42314,11 @@
       <c r="EV18" s="34">
         <v>2666</v>
       </c>
+      <c r="EW18" s="34">
+        <v>2662</v>
+      </c>
     </row>
-    <row r="19" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="70" t="s">
         <v>27</v>
       </c>
@@ -42540,8 +42772,11 @@
       <c r="EV19" s="15">
         <v>102</v>
       </c>
+      <c r="EW19" s="15">
+        <v>128</v>
+      </c>
     </row>
-    <row r="20" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="70"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -42993,8 +43228,11 @@
       <c r="EV20" s="28">
         <v>369</v>
       </c>
+      <c r="EW20" s="28">
+        <v>436</v>
+      </c>
     </row>
-    <row r="21" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="70"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -43446,8 +43684,11 @@
       <c r="EV21" s="15">
         <v>51</v>
       </c>
+      <c r="EW21" s="15">
+        <v>68</v>
+      </c>
     </row>
-    <row r="22" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -43901,8 +44142,11 @@
       <c r="EV22" s="15">
         <v>21</v>
       </c>
+      <c r="EW22" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -44356,8 +44600,11 @@
       <c r="EV23" s="15">
         <v>1</v>
       </c>
+      <c r="EW23" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -44811,8 +45058,11 @@
       <c r="EV24" s="15">
         <v>9</v>
       </c>
+      <c r="EW24" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="25" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -45266,8 +45516,11 @@
       <c r="EV25" s="15">
         <v>0</v>
       </c>
+      <c r="EW25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -45721,8 +45974,11 @@
       <c r="EV26" s="15">
         <v>18</v>
       </c>
+      <c r="EW26" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="27" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -46176,8 +46432,11 @@
       <c r="EV27" s="15">
         <v>1</v>
       </c>
+      <c r="EW27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -46631,8 +46890,11 @@
       <c r="EV28" s="15">
         <v>5</v>
       </c>
+      <c r="EW28" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="71" t="s">
         <v>45</v>
       </c>
@@ -47086,8 +47348,11 @@
       <c r="EV29" s="15">
         <v>5</v>
       </c>
+      <c r="EW29" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="71"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -47539,8 +47804,11 @@
       <c r="EV30" s="15">
         <v>10</v>
       </c>
+      <c r="EW30" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="31" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -47994,8 +48262,11 @@
       <c r="EV31" s="15">
         <v>143</v>
       </c>
+      <c r="EW31" s="15">
+        <v>209</v>
+      </c>
     </row>
-    <row r="32" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -48449,8 +48720,11 @@
       <c r="EV32" s="15">
         <v>0</v>
       </c>
+      <c r="EW32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -48904,8 +49178,11 @@
       <c r="EV33" s="15">
         <v>2</v>
       </c>
+      <c r="EW33" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -49359,8 +49636,11 @@
       <c r="EV34" s="15">
         <v>136</v>
       </c>
+      <c r="EW34" s="15">
+        <v>123</v>
+      </c>
     </row>
-    <row r="35" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="70" t="s">
         <v>56</v>
       </c>
@@ -49814,8 +50094,11 @@
       <c r="EV35" s="15">
         <v>730</v>
       </c>
+      <c r="EW35" s="15">
+        <v>741</v>
+      </c>
     </row>
-    <row r="36" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="70"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -50267,8 +50550,11 @@
       <c r="EV36" s="28">
         <v>131</v>
       </c>
+      <c r="EW36" s="28">
+        <v>131</v>
+      </c>
     </row>
-    <row r="37" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -50722,8 +51008,11 @@
       <c r="EV37" s="15">
         <v>163</v>
       </c>
+      <c r="EW37" s="15">
+        <v>187</v>
+      </c>
     </row>
-    <row r="38" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -51177,8 +51466,11 @@
       <c r="EV38" s="15">
         <v>33</v>
       </c>
+      <c r="EW38" s="15">
+        <v>54</v>
+      </c>
     </row>
-    <row r="39" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -51632,8 +51924,11 @@
       <c r="EV39" s="15">
         <v>8</v>
       </c>
+      <c r="EW39" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="40" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -52087,8 +52382,11 @@
       <c r="EV40" s="15">
         <v>0</v>
       </c>
+      <c r="EW40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -52542,8 +52840,11 @@
       <c r="EV41" s="15">
         <v>0</v>
       </c>
+      <c r="EW41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -52997,8 +53298,11 @@
       <c r="EV42" s="15">
         <v>19</v>
       </c>
+      <c r="EW42" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="43" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -53452,8 +53756,11 @@
       <c r="EV43" s="28">
         <v>65</v>
       </c>
+      <c r="EW43" s="28">
+        <v>67</v>
+      </c>
     </row>
-    <row r="44" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -53907,8 +54214,11 @@
       <c r="EV44" s="15">
         <v>3</v>
       </c>
+      <c r="EW44" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="45" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -54362,8 +54672,11 @@
       <c r="EV45" s="15">
         <v>7</v>
       </c>
+      <c r="EW45" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="46" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -54817,8 +55130,11 @@
       <c r="EV46" s="15">
         <v>30</v>
       </c>
+      <c r="EW46" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="47" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -55272,8 +55588,11 @@
       <c r="EV47" s="15">
         <v>2</v>
       </c>
+      <c r="EW47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -55727,8 +56046,11 @@
       <c r="EV48" s="15">
         <v>18</v>
       </c>
+      <c r="EW48" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="49" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="70" t="s">
         <v>83</v>
       </c>
@@ -56182,8 +56504,11 @@
       <c r="EV49" s="15">
         <v>86</v>
       </c>
+      <c r="EW49" s="15">
+        <v>109</v>
+      </c>
     </row>
-    <row r="50" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="70"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -56635,8 +56960,11 @@
       <c r="EV50" s="15">
         <v>27</v>
       </c>
+      <c r="EW50" s="15">
+        <v>89</v>
+      </c>
     </row>
-    <row r="51" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -57090,8 +57418,11 @@
       <c r="EV51" s="15">
         <v>9</v>
       </c>
+      <c r="EW51" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="52" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -57545,8 +57876,11 @@
       <c r="EV52" s="15">
         <v>20</v>
       </c>
+      <c r="EW52" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="53" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -58000,8 +58334,11 @@
       <c r="EV53" s="15">
         <v>33</v>
       </c>
+      <c r="EW53" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="54" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -58455,8 +58792,11 @@
       <c r="EV54" s="15">
         <v>9</v>
       </c>
+      <c r="EW54" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -58910,8 +59250,11 @@
       <c r="EV55" s="15">
         <v>14</v>
       </c>
+      <c r="EW55" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="56" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -59365,8 +59708,11 @@
       <c r="EV56" s="15">
         <v>2</v>
       </c>
+      <c r="EW56" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="57" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -59820,8 +60166,11 @@
       <c r="EV57" s="15">
         <v>0</v>
       </c>
+      <c r="EW57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="2:152" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:153" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -60290,7 +60639,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:EV58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:EW58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -60421,11 +60770,16 @@
         <f t="shared" si="8"/>
         <v>5705</v>
       </c>
+      <c r="EW58" s="14">
+        <f t="shared" si="8"/>
+        <v>5934</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="166">
-    <mergeCell ref="DD2:EV2"/>
-    <mergeCell ref="ER3:EV3"/>
+  <mergeCells count="167">
+    <mergeCell ref="DD2:EW2"/>
+    <mergeCell ref="ER3:EW3"/>
+    <mergeCell ref="EW4:EW5"/>
     <mergeCell ref="EV4:EV5"/>
     <mergeCell ref="EU4:EU5"/>
     <mergeCell ref="CD4:CD5"/>
@@ -60602,7 +60956,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:EV57">
+  <conditionalFormatting sqref="EH6:EW57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -60642,7 +60996,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CV61"/>
+  <dimension ref="A1:CW61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -60653,11 +61007,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="100" width="10.875" style="1" customWidth="1"/>
-    <col min="101" max="16384" width="8.625" style="1"/>
+    <col min="54" max="101" width="10.875" style="1" customWidth="1"/>
+    <col min="102" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:101" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -60732,11 +61086,12 @@
       <c r="CS1" s="19"/>
       <c r="CT1" s="19"/>
       <c r="CU1" s="19"/>
-      <c r="CV1" s="19" t="s">
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:100" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:101" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -60840,8 +61195,9 @@
       <c r="CT2" s="44"/>
       <c r="CU2" s="44"/>
       <c r="CV2" s="44"/>
+      <c r="CW2" s="44"/>
     </row>
-    <row r="3" spans="1:100" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:101" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -60949,8 +61305,9 @@
       <c r="CT3" s="45"/>
       <c r="CU3" s="45"/>
       <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
     </row>
-    <row r="4" spans="1:100" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:101" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -61248,8 +61605,11 @@
       <c r="CV4" s="46" t="s">
         <v>422</v>
       </c>
+      <c r="CW4" s="46" t="s">
+        <v>426</v>
+      </c>
     </row>
-    <row r="5" spans="1:100" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:101" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -61349,8 +61709,9 @@
       <c r="CT5" s="46"/>
       <c r="CU5" s="46"/>
       <c r="CV5" s="46"/>
+      <c r="CW5" s="46"/>
     </row>
-    <row r="6" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -61649,8 +62010,11 @@
       <c r="CV6" s="28">
         <v>21</v>
       </c>
+      <c r="CW6" s="28">
+        <v>28</v>
+      </c>
     </row>
-    <row r="7" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -61948,8 +62312,11 @@
       <c r="CV7" s="15">
         <v>0</v>
       </c>
+      <c r="CW7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -62247,8 +62614,11 @@
       <c r="CV8" s="28">
         <v>1</v>
       </c>
+      <c r="CW8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -62547,8 +62917,11 @@
       <c r="CV9" s="15">
         <v>15</v>
       </c>
+      <c r="CW9" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -62846,8 +63219,11 @@
       <c r="CV10" s="15">
         <v>0</v>
       </c>
+      <c r="CW10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -63145,8 +63521,11 @@
       <c r="CV11" s="15">
         <v>6</v>
       </c>
+      <c r="CW11" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -63444,8 +63823,11 @@
       <c r="CV12" s="15">
         <v>0</v>
       </c>
+      <c r="CW12" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -63743,8 +64125,11 @@
       <c r="CV13" s="15">
         <v>18</v>
       </c>
+      <c r="CW13" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="14" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -64042,8 +64427,11 @@
       <c r="CV14" s="15">
         <v>13</v>
       </c>
+      <c r="CW14" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -64341,8 +64729,11 @@
       <c r="CV15" s="15">
         <v>6</v>
       </c>
+      <c r="CW15" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -64641,8 +65032,11 @@
       <c r="CV16" s="28">
         <v>3</v>
       </c>
+      <c r="CW16" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -64940,8 +65334,11 @@
       <c r="CV17" s="15">
         <v>41</v>
       </c>
+      <c r="CW17" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="18" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -65240,8 +65637,11 @@
       <c r="CV18" s="34">
         <v>346</v>
       </c>
+      <c r="CW18" s="34">
+        <v>392</v>
+      </c>
     </row>
-    <row r="19" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -65540,8 +65940,11 @@
       <c r="CV19" s="15">
         <v>35</v>
       </c>
+      <c r="CW19" s="15">
+        <v>39</v>
+      </c>
     </row>
-    <row r="20" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -65838,8 +66241,11 @@
       <c r="CV20" s="28">
         <v>105</v>
       </c>
+      <c r="CW20" s="28">
+        <v>92</v>
+      </c>
     </row>
-    <row r="21" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -66136,8 +66542,11 @@
       <c r="CV21" s="15">
         <v>11</v>
       </c>
+      <c r="CW21" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="22" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -66435,8 +66844,11 @@
       <c r="CV22" s="15">
         <v>1</v>
       </c>
+      <c r="CW22" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -66734,8 +67146,11 @@
       <c r="CV23" s="15">
         <v>1</v>
       </c>
+      <c r="CW23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -67033,8 +67448,11 @@
       <c r="CV24" s="15">
         <v>3</v>
       </c>
+      <c r="CW24" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -67332,8 +67750,11 @@
       <c r="CV25" s="15">
         <v>0</v>
       </c>
+      <c r="CW25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -67631,8 +68052,11 @@
       <c r="CV26" s="15">
         <v>11</v>
       </c>
+      <c r="CW26" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="27" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -67930,8 +68354,11 @@
       <c r="CV27" s="15">
         <v>0</v>
       </c>
+      <c r="CW27" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -68229,8 +68656,11 @@
       <c r="CV28" s="15">
         <v>0</v>
       </c>
+      <c r="CW28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -68528,8 +68958,11 @@
       <c r="CV29" s="15">
         <v>2</v>
       </c>
+      <c r="CW29" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -68825,8 +69258,11 @@
       <c r="CV30" s="15">
         <v>20</v>
       </c>
+      <c r="CW30" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="31" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -69125,8 +69561,11 @@
       <c r="CV31" s="15">
         <v>43</v>
       </c>
+      <c r="CW31" s="15">
+        <v>42</v>
+      </c>
     </row>
-    <row r="32" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -69424,8 +69863,11 @@
       <c r="CV32" s="15">
         <v>0</v>
       </c>
+      <c r="CW32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -69723,8 +70165,11 @@
       <c r="CV33" s="15">
         <v>0</v>
       </c>
+      <c r="CW33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -70023,8 +70468,11 @@
       <c r="CV34" s="15">
         <v>21</v>
       </c>
+      <c r="CW34" s="15">
+        <v>44</v>
+      </c>
     </row>
-    <row r="35" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -70323,8 +70771,11 @@
       <c r="CV35" s="15">
         <v>99</v>
       </c>
+      <c r="CW35" s="15">
+        <v>80</v>
+      </c>
     </row>
-    <row r="36" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -70620,8 +71071,11 @@
       <c r="CV36" s="28">
         <v>22</v>
       </c>
+      <c r="CW36" s="28">
+        <v>13</v>
+      </c>
     </row>
-    <row r="37" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -70920,8 +71374,11 @@
       <c r="CV37" s="15">
         <v>13</v>
       </c>
+      <c r="CW37" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="38" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -71219,8 +71676,11 @@
       <c r="CV38" s="15">
         <v>14</v>
       </c>
+      <c r="CW38" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="39" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -71518,8 +71978,11 @@
       <c r="CV39" s="15">
         <v>5</v>
       </c>
+      <c r="CW39" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -71817,8 +72280,11 @@
       <c r="CV40" s="15">
         <v>0</v>
       </c>
+      <c r="CW40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -72116,8 +72582,11 @@
       <c r="CV41" s="15">
         <v>0</v>
       </c>
+      <c r="CW41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -72415,8 +72884,11 @@
       <c r="CV42" s="15">
         <v>7</v>
       </c>
+      <c r="CW42" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="43" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -72714,8 +73186,11 @@
       <c r="CV43" s="28">
         <v>40</v>
       </c>
+      <c r="CW43" s="28">
+        <v>49</v>
+      </c>
     </row>
-    <row r="44" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -73013,8 +73488,11 @@
       <c r="CV44" s="15">
         <v>2</v>
       </c>
+      <c r="CW44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -73312,8 +73790,11 @@
       <c r="CV45" s="15">
         <v>10</v>
       </c>
+      <c r="CW45" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -73611,8 +74092,11 @@
       <c r="CV46" s="15">
         <v>5</v>
       </c>
+      <c r="CW46" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="47" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -73910,8 +74394,11 @@
       <c r="CV47" s="15">
         <v>1</v>
       </c>
+      <c r="CW47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -74209,8 +74696,11 @@
       <c r="CV48" s="15">
         <v>17</v>
       </c>
+      <c r="CW48" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="49" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -74509,8 +74999,11 @@
       <c r="CV49" s="15">
         <v>7</v>
       </c>
+      <c r="CW49" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="1:100" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:101" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -74806,8 +75299,11 @@
       <c r="CV50" s="15">
         <v>17</v>
       </c>
+      <c r="CW50" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="51" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -75105,8 +75601,11 @@
       <c r="CV51" s="15">
         <v>0</v>
       </c>
+      <c r="CW51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -75404,8 +75903,11 @@
       <c r="CV52" s="15">
         <v>6</v>
       </c>
+      <c r="CW52" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -75703,8 +76205,11 @@
       <c r="CV53" s="15">
         <v>17</v>
       </c>
+      <c r="CW53" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="54" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -76002,8 +76507,11 @@
       <c r="CV54" s="15">
         <v>2</v>
       </c>
+      <c r="CW54" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -76301,8 +76809,11 @@
       <c r="CV55" s="15">
         <v>0</v>
       </c>
+      <c r="CW55" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -76600,8 +77111,11 @@
       <c r="CV56" s="15">
         <v>0</v>
       </c>
+      <c r="CW56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -76899,8 +77413,11 @@
       <c r="CV57" s="15">
         <v>1</v>
       </c>
+      <c r="CW57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -77170,7 +77687,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CV58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CW58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -77293,8 +77810,12 @@
         <f t="shared" si="8"/>
         <v>1008</v>
       </c>
+      <c r="CW58" s="14">
+        <f t="shared" si="8"/>
+        <v>1023</v>
+      </c>
     </row>
-    <row r="59" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -77327,7 +77848,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -77360,7 +77881,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:100" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:101" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -77394,9 +77915,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="BD2:CV2"/>
-    <mergeCell ref="CR3:CV3"/>
+  <mergeCells count="111">
+    <mergeCell ref="BD2:CW2"/>
+    <mergeCell ref="CR3:CW3"/>
+    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="B2:C3"/>
@@ -77418,7 +77940,6 @@
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="AZ4:AZ5"/>
     <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="P4:P5"/>
@@ -77457,6 +77978,7 @@
     <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="X4:X5"/>
     <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="W4:W5"/>
     <mergeCell ref="CL4:CL5"/>
     <mergeCell ref="CK4:CK5"/>
     <mergeCell ref="CJ4:CJ5"/>
@@ -77507,7 +78029,7 @@
     <mergeCell ref="CM4:CM5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CV57">
+  <conditionalFormatting sqref="CH6:CW57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -77516,7 +78038,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="100" max="66" man="1"/>
+    <brk id="101" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -77533,7 +78055,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CV57</xm:sqref>
+          <xm:sqref>BP6:CW57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -77546,7 +78068,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DA61"/>
+  <dimension ref="A1:DB61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -77555,11 +78077,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="105" width="10.875" style="1" customWidth="1"/>
-    <col min="106" max="16384" width="8.625" style="1"/>
+    <col min="34" max="106" width="10.875" style="1" customWidth="1"/>
+    <col min="107" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:105" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:106" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -77634,12 +78156,13 @@
       <c r="CS1" s="19"/>
       <c r="CT1" s="19"/>
       <c r="CU1" s="19"/>
-      <c r="CV1" s="19" t="s">
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="CW1" s="19"/>
+      <c r="CX1" s="19"/>
     </row>
-    <row r="2" spans="1:105" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:106" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="60"/>
       <c r="C2" s="61"/>
       <c r="D2" s="59" t="s">
@@ -77743,13 +78266,14 @@
       <c r="CT2" s="44"/>
       <c r="CU2" s="44"/>
       <c r="CV2" s="44"/>
-      <c r="CW2" s="20"/>
+      <c r="CW2" s="44"/>
       <c r="CX2" s="20"/>
       <c r="CY2" s="20"/>
       <c r="CZ2" s="20"/>
       <c r="DA2" s="20"/>
+      <c r="DB2" s="20"/>
     </row>
-    <row r="3" spans="1:105" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:106" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
       <c r="D3" s="81" t="s">
@@ -77857,13 +78381,14 @@
       <c r="CT3" s="45"/>
       <c r="CU3" s="45"/>
       <c r="CV3" s="45"/>
-      <c r="CW3" s="21"/>
+      <c r="CW3" s="45"/>
       <c r="CX3" s="21"/>
       <c r="CY3" s="21"/>
       <c r="CZ3" s="21"/>
       <c r="DA3" s="21"/>
+      <c r="DB3" s="21"/>
     </row>
-    <row r="4" spans="1:105" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:106" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
@@ -78161,13 +78686,16 @@
       <c r="CV4" s="46" t="s">
         <v>422</v>
       </c>
-      <c r="CW4" s="89"/>
+      <c r="CW4" s="46" t="s">
+        <v>426</v>
+      </c>
       <c r="CX4" s="89"/>
       <c r="CY4" s="89"/>
       <c r="CZ4" s="89"/>
       <c r="DA4" s="89"/>
+      <c r="DB4" s="89"/>
     </row>
-    <row r="5" spans="1:105" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:106" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="67"/>
       <c r="C5" s="73"/>
       <c r="D5" s="56"/>
@@ -78267,13 +78795,14 @@
       <c r="CT5" s="46"/>
       <c r="CU5" s="46"/>
       <c r="CV5" s="46"/>
-      <c r="CW5" s="89"/>
+      <c r="CW5" s="46"/>
       <c r="CX5" s="89"/>
       <c r="CY5" s="89"/>
       <c r="CZ5" s="89"/>
       <c r="DA5" s="89"/>
+      <c r="DB5" s="89"/>
     </row>
-    <row r="6" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -78572,13 +79101,16 @@
       <c r="CV6" s="28">
         <v>93</v>
       </c>
-      <c r="CW6" s="22"/>
+      <c r="CW6" s="28">
+        <v>113</v>
+      </c>
       <c r="CX6" s="22"/>
       <c r="CY6" s="22"/>
       <c r="CZ6" s="22"/>
       <c r="DA6" s="22"/>
+      <c r="DB6" s="22"/>
     </row>
-    <row r="7" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -78876,13 +79408,16 @@
       <c r="CV7" s="15">
         <v>0</v>
       </c>
-      <c r="CW7" s="23"/>
+      <c r="CW7" s="15">
+        <v>0</v>
+      </c>
       <c r="CX7" s="23"/>
       <c r="CY7" s="23"/>
       <c r="CZ7" s="23"/>
       <c r="DA7" s="23"/>
+      <c r="DB7" s="23"/>
     </row>
-    <row r="8" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -79180,13 +79715,16 @@
       <c r="CV8" s="28">
         <v>32</v>
       </c>
-      <c r="CW8" s="23"/>
+      <c r="CW8" s="28">
+        <v>26</v>
+      </c>
       <c r="CX8" s="23"/>
       <c r="CY8" s="23"/>
       <c r="CZ8" s="23"/>
       <c r="DA8" s="23"/>
+      <c r="DB8" s="23"/>
     </row>
-    <row r="9" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -79485,13 +80023,16 @@
       <c r="CV9" s="15">
         <v>115</v>
       </c>
-      <c r="CW9" s="23"/>
+      <c r="CW9" s="15">
+        <v>104</v>
+      </c>
       <c r="CX9" s="23"/>
       <c r="CY9" s="23"/>
       <c r="CZ9" s="23"/>
       <c r="DA9" s="23"/>
+      <c r="DB9" s="23"/>
     </row>
-    <row r="10" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -79789,13 +80330,16 @@
       <c r="CV10" s="15">
         <v>3</v>
       </c>
-      <c r="CW10" s="23"/>
+      <c r="CW10" s="15">
+        <v>2</v>
+      </c>
       <c r="CX10" s="23"/>
       <c r="CY10" s="23"/>
       <c r="CZ10" s="23"/>
       <c r="DA10" s="23"/>
+      <c r="DB10" s="23"/>
     </row>
-    <row r="11" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -80093,13 +80637,16 @@
       <c r="CV11" s="15">
         <v>12</v>
       </c>
-      <c r="CW11" s="23"/>
+      <c r="CW11" s="15">
+        <v>5</v>
+      </c>
       <c r="CX11" s="23"/>
       <c r="CY11" s="23"/>
       <c r="CZ11" s="23"/>
       <c r="DA11" s="23"/>
+      <c r="DB11" s="23"/>
     </row>
-    <row r="12" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -80397,13 +80944,16 @@
       <c r="CV12" s="15">
         <v>11</v>
       </c>
-      <c r="CW12" s="23"/>
+      <c r="CW12" s="15">
+        <v>6</v>
+      </c>
       <c r="CX12" s="23"/>
       <c r="CY12" s="23"/>
       <c r="CZ12" s="23"/>
       <c r="DA12" s="23"/>
+      <c r="DB12" s="23"/>
     </row>
-    <row r="13" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -80701,13 +81251,16 @@
       <c r="CV13" s="15">
         <v>27</v>
       </c>
-      <c r="CW13" s="22"/>
+      <c r="CW13" s="15">
+        <v>25</v>
+      </c>
       <c r="CX13" s="22"/>
       <c r="CY13" s="22"/>
       <c r="CZ13" s="22"/>
       <c r="DA13" s="22"/>
+      <c r="DB13" s="22"/>
     </row>
-    <row r="14" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -81005,13 +81558,16 @@
       <c r="CV14" s="15">
         <v>24</v>
       </c>
-      <c r="CW14" s="23"/>
+      <c r="CW14" s="15">
+        <v>27</v>
+      </c>
       <c r="CX14" s="23"/>
       <c r="CY14" s="23"/>
       <c r="CZ14" s="23"/>
       <c r="DA14" s="23"/>
+      <c r="DB14" s="23"/>
     </row>
-    <row r="15" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -81309,13 +81865,16 @@
       <c r="CV15" s="15">
         <v>8</v>
       </c>
-      <c r="CW15" s="23"/>
+      <c r="CW15" s="15">
+        <v>8</v>
+      </c>
       <c r="CX15" s="23"/>
       <c r="CY15" s="23"/>
       <c r="CZ15" s="23"/>
       <c r="DA15" s="23"/>
+      <c r="DB15" s="23"/>
     </row>
-    <row r="16" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -81614,13 +82173,16 @@
       <c r="CV16" s="28">
         <v>168</v>
       </c>
-      <c r="CW16" s="22"/>
+      <c r="CW16" s="28">
+        <v>166</v>
+      </c>
       <c r="CX16" s="22"/>
       <c r="CY16" s="22"/>
       <c r="CZ16" s="22"/>
       <c r="DA16" s="22"/>
+      <c r="DB16" s="22"/>
     </row>
-    <row r="17" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -81918,13 +82480,16 @@
       <c r="CV17" s="15">
         <v>140</v>
       </c>
-      <c r="CW17" s="22"/>
+      <c r="CW17" s="15">
+        <v>120</v>
+      </c>
       <c r="CX17" s="22"/>
       <c r="CY17" s="22"/>
       <c r="CZ17" s="22"/>
       <c r="DA17" s="22"/>
+      <c r="DB17" s="22"/>
     </row>
-    <row r="18" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -82223,13 +82788,16 @@
       <c r="CV18" s="34">
         <v>1853</v>
       </c>
-      <c r="CW18" s="22"/>
+      <c r="CW18" s="34">
+        <v>1828</v>
+      </c>
       <c r="CX18" s="22"/>
       <c r="CY18" s="22"/>
       <c r="CZ18" s="22"/>
       <c r="DA18" s="22"/>
+      <c r="DB18" s="22"/>
     </row>
-    <row r="19" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="83" t="s">
         <v>27</v>
@@ -82528,13 +83096,16 @@
       <c r="CV19" s="15">
         <v>37</v>
       </c>
-      <c r="CW19" s="22"/>
+      <c r="CW19" s="15">
+        <v>43</v>
+      </c>
       <c r="CX19" s="22"/>
       <c r="CY19" s="22"/>
       <c r="CZ19" s="22"/>
       <c r="DA19" s="22"/>
+      <c r="DB19" s="22"/>
     </row>
-    <row r="20" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="87"/>
       <c r="C20" s="9" t="s">
@@ -82831,13 +83402,16 @@
       <c r="CV20" s="28">
         <v>164</v>
       </c>
-      <c r="CW20" s="22"/>
+      <c r="CW20" s="28">
+        <v>117</v>
+      </c>
       <c r="CX20" s="22"/>
       <c r="CY20" s="22"/>
       <c r="CZ20" s="22"/>
       <c r="DA20" s="22"/>
+      <c r="DB20" s="22"/>
     </row>
-    <row r="21" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="84"/>
       <c r="C21" s="9" t="s">
@@ -83134,13 +83708,16 @@
       <c r="CV21" s="15">
         <v>27</v>
       </c>
-      <c r="CW21" s="22"/>
+      <c r="CW21" s="15">
+        <v>20</v>
+      </c>
       <c r="CX21" s="22"/>
       <c r="CY21" s="22"/>
       <c r="CZ21" s="22"/>
       <c r="DA21" s="22"/>
+      <c r="DB21" s="22"/>
     </row>
-    <row r="22" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -83438,13 +84015,16 @@
       <c r="CV22" s="15">
         <v>3</v>
       </c>
-      <c r="CW22" s="23"/>
+      <c r="CW22" s="15">
+        <v>6</v>
+      </c>
       <c r="CX22" s="23"/>
       <c r="CY22" s="23"/>
       <c r="CZ22" s="23"/>
       <c r="DA22" s="23"/>
+      <c r="DB22" s="23"/>
     </row>
-    <row r="23" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -83742,13 +84322,16 @@
       <c r="CV23" s="15">
         <v>7</v>
       </c>
-      <c r="CW23" s="23"/>
+      <c r="CW23" s="15">
+        <v>7</v>
+      </c>
       <c r="CX23" s="23"/>
       <c r="CY23" s="23"/>
       <c r="CZ23" s="23"/>
       <c r="DA23" s="23"/>
+      <c r="DB23" s="23"/>
     </row>
-    <row r="24" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -84046,13 +84629,16 @@
       <c r="CV24" s="15">
         <v>15</v>
       </c>
-      <c r="CW24" s="22"/>
+      <c r="CW24" s="15">
+        <v>13</v>
+      </c>
       <c r="CX24" s="22"/>
       <c r="CY24" s="22"/>
       <c r="CZ24" s="22"/>
       <c r="DA24" s="22"/>
+      <c r="DB24" s="22"/>
     </row>
-    <row r="25" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -84350,13 +84936,16 @@
       <c r="CV25" s="15">
         <v>1</v>
       </c>
-      <c r="CW25" s="23"/>
+      <c r="CW25" s="15">
+        <v>3</v>
+      </c>
       <c r="CX25" s="23"/>
       <c r="CY25" s="23"/>
       <c r="CZ25" s="23"/>
       <c r="DA25" s="23"/>
+      <c r="DB25" s="23"/>
     </row>
-    <row r="26" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -84654,13 +85243,16 @@
       <c r="CV26" s="15">
         <v>12</v>
       </c>
-      <c r="CW26" s="23"/>
+      <c r="CW26" s="15">
+        <v>14</v>
+      </c>
       <c r="CX26" s="23"/>
       <c r="CY26" s="23"/>
       <c r="CZ26" s="23"/>
       <c r="DA26" s="23"/>
+      <c r="DB26" s="23"/>
     </row>
-    <row r="27" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -84958,13 +85550,16 @@
       <c r="CV27" s="15">
         <v>1</v>
       </c>
-      <c r="CW27" s="23"/>
+      <c r="CW27" s="15">
+        <v>1</v>
+      </c>
       <c r="CX27" s="23"/>
       <c r="CY27" s="23"/>
       <c r="CZ27" s="23"/>
       <c r="DA27" s="23"/>
+      <c r="DB27" s="23"/>
     </row>
-    <row r="28" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -85262,13 +85857,16 @@
       <c r="CV28" s="15">
         <v>2</v>
       </c>
-      <c r="CW28" s="22"/>
+      <c r="CW28" s="15">
+        <v>0</v>
+      </c>
       <c r="CX28" s="22"/>
       <c r="CY28" s="22"/>
       <c r="CZ28" s="22"/>
       <c r="DA28" s="22"/>
+      <c r="DB28" s="22"/>
     </row>
-    <row r="29" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
@@ -85566,13 +86164,16 @@
       <c r="CV29" s="15">
         <v>5</v>
       </c>
-      <c r="CW29" s="23"/>
+      <c r="CW29" s="15">
+        <v>2</v>
+      </c>
       <c r="CX29" s="23"/>
       <c r="CY29" s="23"/>
       <c r="CZ29" s="23"/>
       <c r="DA29" s="23"/>
+      <c r="DB29" s="23"/>
     </row>
-    <row r="30" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -85868,13 +86469,16 @@
       <c r="CV30" s="15">
         <v>26</v>
       </c>
-      <c r="CW30" s="23"/>
+      <c r="CW30" s="15">
+        <v>13</v>
+      </c>
       <c r="CX30" s="23"/>
       <c r="CY30" s="23"/>
       <c r="CZ30" s="23"/>
       <c r="DA30" s="23"/>
+      <c r="DB30" s="23"/>
     </row>
-    <row r="31" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -86173,13 +86777,16 @@
       <c r="CV31" s="15">
         <v>90</v>
       </c>
-      <c r="CW31" s="22"/>
+      <c r="CW31" s="15">
+        <v>72</v>
+      </c>
       <c r="CX31" s="22"/>
       <c r="CY31" s="22"/>
       <c r="CZ31" s="22"/>
       <c r="DA31" s="22"/>
+      <c r="DB31" s="22"/>
     </row>
-    <row r="32" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -86477,13 +87084,16 @@
       <c r="CV32" s="15">
         <v>1</v>
       </c>
-      <c r="CW32" s="23"/>
+      <c r="CW32" s="15">
+        <v>1</v>
+      </c>
       <c r="CX32" s="23"/>
       <c r="CY32" s="23"/>
       <c r="CZ32" s="23"/>
       <c r="DA32" s="23"/>
+      <c r="DB32" s="23"/>
     </row>
-    <row r="33" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -86781,13 +87391,16 @@
       <c r="CV33" s="15">
         <v>1</v>
       </c>
-      <c r="CW33" s="23"/>
+      <c r="CW33" s="15">
+        <v>0</v>
+      </c>
       <c r="CX33" s="23"/>
       <c r="CY33" s="23"/>
       <c r="CZ33" s="23"/>
       <c r="DA33" s="23"/>
+      <c r="DB33" s="23"/>
     </row>
-    <row r="34" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -87086,13 +87699,16 @@
       <c r="CV34" s="15">
         <v>142</v>
       </c>
-      <c r="CW34" s="22"/>
+      <c r="CW34" s="15">
+        <v>127</v>
+      </c>
       <c r="CX34" s="22"/>
       <c r="CY34" s="22"/>
       <c r="CZ34" s="22"/>
       <c r="DA34" s="22"/>
+      <c r="DB34" s="22"/>
     </row>
-    <row r="35" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="83" t="s">
         <v>56</v>
@@ -87391,13 +88007,16 @@
       <c r="CV35" s="15">
         <v>286</v>
       </c>
-      <c r="CW35" s="22"/>
+      <c r="CW35" s="15">
+        <v>299</v>
+      </c>
       <c r="CX35" s="22"/>
       <c r="CY35" s="22"/>
       <c r="CZ35" s="22"/>
       <c r="DA35" s="22"/>
+      <c r="DB35" s="22"/>
     </row>
-    <row r="36" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="84"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -87693,13 +88312,16 @@
       <c r="CV36" s="28">
         <v>23</v>
       </c>
-      <c r="CW36" s="22"/>
+      <c r="CW36" s="28">
+        <v>20</v>
+      </c>
       <c r="CX36" s="22"/>
       <c r="CY36" s="22"/>
       <c r="CZ36" s="22"/>
       <c r="DA36" s="22"/>
+      <c r="DB36" s="22"/>
     </row>
-    <row r="37" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -87998,13 +88620,16 @@
       <c r="CV37" s="15">
         <v>84</v>
       </c>
-      <c r="CW37" s="22"/>
+      <c r="CW37" s="15">
+        <v>74</v>
+      </c>
       <c r="CX37" s="22"/>
       <c r="CY37" s="22"/>
       <c r="CZ37" s="22"/>
       <c r="DA37" s="22"/>
+      <c r="DB37" s="22"/>
     </row>
-    <row r="38" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -88302,13 +88927,16 @@
       <c r="CV38" s="15">
         <v>12</v>
       </c>
-      <c r="CW38" s="23"/>
+      <c r="CW38" s="15">
+        <v>30</v>
+      </c>
       <c r="CX38" s="23"/>
       <c r="CY38" s="23"/>
       <c r="CZ38" s="23"/>
       <c r="DA38" s="23"/>
+      <c r="DB38" s="23"/>
     </row>
-    <row r="39" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -88606,13 +89234,16 @@
       <c r="CV39" s="15">
         <v>9</v>
       </c>
-      <c r="CW39" s="23"/>
+      <c r="CW39" s="15">
+        <v>7</v>
+      </c>
       <c r="CX39" s="23"/>
       <c r="CY39" s="23"/>
       <c r="CZ39" s="23"/>
       <c r="DA39" s="23"/>
+      <c r="DB39" s="23"/>
     </row>
-    <row r="40" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -88910,13 +89541,16 @@
       <c r="CV40" s="15">
         <v>0</v>
       </c>
-      <c r="CW40" s="23"/>
+      <c r="CW40" s="15">
+        <v>1</v>
+      </c>
       <c r="CX40" s="23"/>
       <c r="CY40" s="23"/>
       <c r="CZ40" s="23"/>
       <c r="DA40" s="23"/>
+      <c r="DB40" s="23"/>
     </row>
-    <row r="41" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -89214,13 +89848,16 @@
       <c r="CV41" s="15">
         <v>0</v>
       </c>
-      <c r="CW41" s="23"/>
+      <c r="CW41" s="15">
+        <v>0</v>
+      </c>
       <c r="CX41" s="23"/>
       <c r="CY41" s="23"/>
       <c r="CZ41" s="23"/>
       <c r="DA41" s="23"/>
+      <c r="DB41" s="23"/>
     </row>
-    <row r="42" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -89518,13 +90155,16 @@
       <c r="CV42" s="15">
         <v>13</v>
       </c>
-      <c r="CW42" s="23"/>
+      <c r="CW42" s="15">
+        <v>11</v>
+      </c>
       <c r="CX42" s="23"/>
       <c r="CY42" s="23"/>
       <c r="CZ42" s="23"/>
       <c r="DA42" s="23"/>
+      <c r="DB42" s="23"/>
     </row>
-    <row r="43" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -89822,13 +90462,16 @@
       <c r="CV43" s="28">
         <v>51</v>
       </c>
-      <c r="CW43" s="23"/>
+      <c r="CW43" s="28">
+        <v>34</v>
+      </c>
       <c r="CX43" s="23"/>
       <c r="CY43" s="23"/>
       <c r="CZ43" s="23"/>
       <c r="DA43" s="23"/>
+      <c r="DB43" s="23"/>
     </row>
-    <row r="44" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -90126,13 +90769,16 @@
       <c r="CV44" s="15">
         <v>6</v>
       </c>
-      <c r="CW44" s="23"/>
+      <c r="CW44" s="15">
+        <v>1</v>
+      </c>
       <c r="CX44" s="23"/>
       <c r="CY44" s="23"/>
       <c r="CZ44" s="23"/>
       <c r="DA44" s="23"/>
+      <c r="DB44" s="23"/>
     </row>
-    <row r="45" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -90430,13 +91076,16 @@
       <c r="CV45" s="15">
         <v>22</v>
       </c>
-      <c r="CW45" s="22"/>
+      <c r="CW45" s="15">
+        <v>19</v>
+      </c>
       <c r="CX45" s="22"/>
       <c r="CY45" s="22"/>
       <c r="CZ45" s="22"/>
       <c r="DA45" s="22"/>
+      <c r="DB45" s="22"/>
     </row>
-    <row r="46" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -90734,13 +91383,16 @@
       <c r="CV46" s="15">
         <v>15</v>
       </c>
-      <c r="CW46" s="23"/>
+      <c r="CW46" s="15">
+        <v>15</v>
+      </c>
       <c r="CX46" s="23"/>
       <c r="CY46" s="23"/>
       <c r="CZ46" s="23"/>
       <c r="DA46" s="23"/>
+      <c r="DB46" s="23"/>
     </row>
-    <row r="47" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -91038,13 +91690,16 @@
       <c r="CV47" s="15">
         <v>3</v>
       </c>
-      <c r="CW47" s="23"/>
+      <c r="CW47" s="15">
+        <v>2</v>
+      </c>
       <c r="CX47" s="23"/>
       <c r="CY47" s="23"/>
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
+      <c r="DB47" s="23"/>
     </row>
-    <row r="48" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -91342,13 +91997,16 @@
       <c r="CV48" s="15">
         <v>8</v>
       </c>
-      <c r="CW48" s="23"/>
+      <c r="CW48" s="15">
+        <v>11</v>
+      </c>
       <c r="CX48" s="23"/>
       <c r="CY48" s="23"/>
       <c r="CZ48" s="23"/>
       <c r="DA48" s="23"/>
+      <c r="DB48" s="23"/>
     </row>
-    <row r="49" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="83" t="s">
         <v>83</v>
@@ -91647,13 +92305,16 @@
       <c r="CV49" s="15">
         <v>54</v>
       </c>
-      <c r="CW49" s="22"/>
+      <c r="CW49" s="15">
+        <v>101</v>
+      </c>
       <c r="CX49" s="22"/>
       <c r="CY49" s="22"/>
       <c r="CZ49" s="22"/>
       <c r="DA49" s="22"/>
+      <c r="DB49" s="22"/>
     </row>
-    <row r="50" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="84"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -91949,13 +92610,16 @@
       <c r="CV50" s="15">
         <v>13</v>
       </c>
-      <c r="CW50" s="22"/>
+      <c r="CW50" s="15">
+        <v>15</v>
+      </c>
       <c r="CX50" s="22"/>
       <c r="CY50" s="22"/>
       <c r="CZ50" s="22"/>
       <c r="DA50" s="22"/>
+      <c r="DB50" s="22"/>
     </row>
-    <row r="51" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -92253,13 +92917,16 @@
       <c r="CV51" s="15">
         <v>3</v>
       </c>
-      <c r="CW51" s="23"/>
+      <c r="CW51" s="15">
+        <v>6</v>
+      </c>
       <c r="CX51" s="23"/>
       <c r="CY51" s="23"/>
       <c r="CZ51" s="23"/>
       <c r="DA51" s="23"/>
+      <c r="DB51" s="23"/>
     </row>
-    <row r="52" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -92557,13 +93224,16 @@
       <c r="CV52" s="15">
         <v>19</v>
       </c>
-      <c r="CW52" s="23"/>
+      <c r="CW52" s="15">
+        <v>17</v>
+      </c>
       <c r="CX52" s="23"/>
       <c r="CY52" s="23"/>
       <c r="CZ52" s="23"/>
       <c r="DA52" s="23"/>
+      <c r="DB52" s="23"/>
     </row>
-    <row r="53" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -92861,13 +93531,16 @@
       <c r="CV53" s="15">
         <v>58</v>
       </c>
-      <c r="CW53" s="23"/>
+      <c r="CW53" s="15">
+        <v>68</v>
+      </c>
       <c r="CX53" s="23"/>
       <c r="CY53" s="23"/>
       <c r="CZ53" s="23"/>
       <c r="DA53" s="23"/>
+      <c r="DB53" s="23"/>
     </row>
-    <row r="54" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -93165,13 +93838,16 @@
       <c r="CV54" s="15">
         <v>4</v>
       </c>
-      <c r="CW54" s="23"/>
+      <c r="CW54" s="15">
+        <v>6</v>
+      </c>
       <c r="CX54" s="23"/>
       <c r="CY54" s="23"/>
       <c r="CZ54" s="23"/>
       <c r="DA54" s="23"/>
+      <c r="DB54" s="23"/>
     </row>
-    <row r="55" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -93469,13 +94145,16 @@
       <c r="CV55" s="15">
         <v>12</v>
       </c>
-      <c r="CW55" s="23"/>
+      <c r="CW55" s="15">
+        <v>17</v>
+      </c>
       <c r="CX55" s="23"/>
       <c r="CY55" s="23"/>
       <c r="CZ55" s="23"/>
       <c r="DA55" s="23"/>
+      <c r="DB55" s="23"/>
     </row>
-    <row r="56" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -93773,13 +94452,16 @@
       <c r="CV56" s="15">
         <v>1</v>
       </c>
-      <c r="CW56" s="23"/>
+      <c r="CW56" s="15">
+        <v>0</v>
+      </c>
       <c r="CX56" s="23"/>
       <c r="CY56" s="23"/>
       <c r="CZ56" s="23"/>
       <c r="DA56" s="23"/>
+      <c r="DB56" s="23"/>
     </row>
-    <row r="57" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -94077,13 +94759,16 @@
       <c r="CV57" s="15">
         <v>0</v>
       </c>
-      <c r="CW57" s="23"/>
+      <c r="CW57" s="15">
+        <v>3</v>
+      </c>
       <c r="CX57" s="23"/>
       <c r="CY57" s="23"/>
       <c r="CZ57" s="23"/>
       <c r="DA57" s="23"/>
+      <c r="DB57" s="23"/>
     </row>
-    <row r="58" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -94353,7 +95038,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CV58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CW58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -94476,13 +95161,17 @@
         <f t="shared" si="4"/>
         <v>3716</v>
       </c>
-      <c r="CW58" s="24"/>
+      <c r="CW58" s="14">
+        <f t="shared" si="4"/>
+        <v>3626</v>
+      </c>
       <c r="CX58" s="24"/>
       <c r="CY58" s="24"/>
       <c r="CZ58" s="24"/>
       <c r="DA58" s="24"/>
+      <c r="DB58" s="24"/>
     </row>
-    <row r="59" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -94515,7 +95204,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -94548,7 +95237,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -94582,34 +95271,33 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="115">
-    <mergeCell ref="BD2:CV2"/>
-    <mergeCell ref="CR3:CV3"/>
+  <mergeCells count="116">
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="BD2:CW2"/>
+    <mergeCell ref="CR3:CW3"/>
+    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="CP4:CP5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CE4:CE5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="T4:T5"/>
@@ -94652,8 +95340,18 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="BY4:BY5"/>
     <mergeCell ref="BJ4:BJ5"/>
@@ -94666,18 +95364,6 @@
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CL4:CL5"/>
@@ -94698,6 +95384,10 @@
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="BD3:CQ3"/>
     <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CE4:CE5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -94721,7 +95411,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CV57</xm:sqref>
+          <xm:sqref>BP6:CW57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050221-1\ＪＯＢ050221-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050228-1\ＪＯＢ050228-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16005" windowHeight="10680"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CX$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CX$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EX$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EX$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$CY$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$CY$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$EY$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$EY$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="431">
   <si>
     <t>都道府県</t>
   </si>
@@ -4594,6 +4594,18 @@
 【2月第3週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>2/20(月)～
+2/26(日)分
+【2月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2/21(月)～
+2/27(日)分
+【2月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5171,13 +5183,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5189,16 +5201,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9394,7 +9406,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EY61"/>
+  <dimension ref="A1:EZ61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9408,11 +9420,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="154" width="10.875" style="1" customWidth="1"/>
-    <col min="155" max="16384" width="8.625" style="1"/>
+    <col min="106" max="155" width="10.875" style="1" customWidth="1"/>
+    <col min="156" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:155" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:156" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9493,11 +9505,12 @@
       <c r="EU1" s="19"/>
       <c r="EV1" s="19"/>
       <c r="EW1" s="19"/>
-      <c r="EX1" s="19" t="s">
+      <c r="EX1" s="19"/>
+      <c r="EY1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:155" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:156" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="67" t="s">
@@ -9609,56 +9622,57 @@
       <c r="DB2" s="68"/>
       <c r="DC2" s="68"/>
       <c r="DD2" s="68"/>
-      <c r="DE2" s="73" t="s">
+      <c r="DE2" s="71" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="73"/>
-      <c r="DG2" s="73"/>
-      <c r="DH2" s="73"/>
-      <c r="DI2" s="73"/>
-      <c r="DJ2" s="73"/>
-      <c r="DK2" s="73"/>
-      <c r="DL2" s="73"/>
-      <c r="DM2" s="73"/>
-      <c r="DN2" s="73"/>
-      <c r="DO2" s="73"/>
-      <c r="DP2" s="73"/>
-      <c r="DQ2" s="73"/>
-      <c r="DR2" s="73"/>
-      <c r="DS2" s="73"/>
-      <c r="DT2" s="73"/>
-      <c r="DU2" s="73"/>
-      <c r="DV2" s="73"/>
-      <c r="DW2" s="73"/>
-      <c r="DX2" s="73"/>
-      <c r="DY2" s="73"/>
-      <c r="DZ2" s="73"/>
-      <c r="EA2" s="73"/>
-      <c r="EB2" s="73"/>
-      <c r="EC2" s="73"/>
-      <c r="ED2" s="73"/>
-      <c r="EE2" s="73"/>
-      <c r="EF2" s="73"/>
-      <c r="EG2" s="73"/>
-      <c r="EH2" s="73"/>
-      <c r="EI2" s="73"/>
-      <c r="EJ2" s="73"/>
-      <c r="EK2" s="73"/>
-      <c r="EL2" s="73"/>
-      <c r="EM2" s="73"/>
-      <c r="EN2" s="73"/>
-      <c r="EO2" s="73"/>
-      <c r="EP2" s="73"/>
-      <c r="EQ2" s="73"/>
-      <c r="ER2" s="73"/>
-      <c r="ES2" s="73"/>
-      <c r="ET2" s="73"/>
-      <c r="EU2" s="73"/>
-      <c r="EV2" s="73"/>
-      <c r="EW2" s="73"/>
-      <c r="EX2" s="73"/>
+      <c r="DF2" s="71"/>
+      <c r="DG2" s="71"/>
+      <c r="DH2" s="71"/>
+      <c r="DI2" s="71"/>
+      <c r="DJ2" s="71"/>
+      <c r="DK2" s="71"/>
+      <c r="DL2" s="71"/>
+      <c r="DM2" s="71"/>
+      <c r="DN2" s="71"/>
+      <c r="DO2" s="71"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="71"/>
+      <c r="DR2" s="71"/>
+      <c r="DS2" s="71"/>
+      <c r="DT2" s="71"/>
+      <c r="DU2" s="71"/>
+      <c r="DV2" s="71"/>
+      <c r="DW2" s="71"/>
+      <c r="DX2" s="71"/>
+      <c r="DY2" s="71"/>
+      <c r="DZ2" s="71"/>
+      <c r="EA2" s="71"/>
+      <c r="EB2" s="71"/>
+      <c r="EC2" s="71"/>
+      <c r="ED2" s="71"/>
+      <c r="EE2" s="71"/>
+      <c r="EF2" s="71"/>
+      <c r="EG2" s="71"/>
+      <c r="EH2" s="71"/>
+      <c r="EI2" s="71"/>
+      <c r="EJ2" s="71"/>
+      <c r="EK2" s="71"/>
+      <c r="EL2" s="71"/>
+      <c r="EM2" s="71"/>
+      <c r="EN2" s="71"/>
+      <c r="EO2" s="71"/>
+      <c r="EP2" s="71"/>
+      <c r="EQ2" s="71"/>
+      <c r="ER2" s="71"/>
+      <c r="ES2" s="71"/>
+      <c r="ET2" s="71"/>
+      <c r="EU2" s="71"/>
+      <c r="EV2" s="71"/>
+      <c r="EW2" s="71"/>
+      <c r="EX2" s="71"/>
+      <c r="EY2" s="71"/>
     </row>
-    <row r="3" spans="1:155" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:156" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
       <c r="D3" s="64" t="s">
@@ -9824,8 +9838,9 @@
       <c r="EV3" s="64"/>
       <c r="EW3" s="64"/>
       <c r="EX3" s="64"/>
+      <c r="EY3" s="64"/>
     </row>
-    <row r="4" spans="1:155" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:156" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="62" t="s">
         <v>0</v>
       </c>
@@ -10144,7 +10159,7 @@
       <c r="DC4" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="71" t="s">
+      <c r="DD4" s="72" t="s">
         <v>305</v>
       </c>
       <c r="DE4" s="69" t="s">
@@ -10285,8 +10300,11 @@
       <c r="EX4" s="69" t="s">
         <v>427</v>
       </c>
+      <c r="EY4" s="69" t="s">
+        <v>429</v>
+      </c>
     </row>
-    <row r="5" spans="1:155" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:156" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63"/>
       <c r="C5" s="56"/>
       <c r="D5" s="45"/>
@@ -10393,7 +10411,7 @@
       <c r="DA5" s="48"/>
       <c r="DB5" s="48"/>
       <c r="DC5" s="48"/>
-      <c r="DD5" s="72"/>
+      <c r="DD5" s="73"/>
       <c r="DE5" s="48"/>
       <c r="DF5" s="48"/>
       <c r="DG5" s="48"/>
@@ -10440,8 +10458,9 @@
       <c r="EV5" s="69"/>
       <c r="EW5" s="69"/>
       <c r="EX5" s="69"/>
+      <c r="EY5" s="69"/>
     </row>
-    <row r="6" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -10902,9 +10921,12 @@
       <c r="EX6" s="28">
         <v>125</v>
       </c>
-      <c r="EY6" s="1"/>
+      <c r="EY6" s="28">
+        <v>112</v>
+      </c>
+      <c r="EZ6" s="1"/>
     </row>
-    <row r="7" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11364,8 +11386,11 @@
       <c r="EX7" s="15">
         <v>3</v>
       </c>
+      <c r="EY7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -11825,8 +11850,11 @@
       <c r="EX8" s="28">
         <v>20</v>
       </c>
+      <c r="EY8" s="28">
+        <v>27</v>
+      </c>
     </row>
-    <row r="9" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12287,8 +12315,11 @@
       <c r="EX9" s="15">
         <v>118</v>
       </c>
+      <c r="EY9" s="15">
+        <v>111</v>
+      </c>
     </row>
-    <row r="10" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12746,8 +12777,11 @@
       <c r="EX10" s="15">
         <v>2</v>
       </c>
+      <c r="EY10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13207,8 +13241,11 @@
       <c r="EX11" s="15">
         <v>11</v>
       </c>
+      <c r="EY11" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="12" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13668,8 +13705,11 @@
       <c r="EX12" s="15">
         <v>13</v>
       </c>
+      <c r="EY12" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14129,9 +14169,12 @@
       <c r="EX13" s="15">
         <v>42</v>
       </c>
-      <c r="EY13" s="1"/>
+      <c r="EY13" s="15">
+        <v>24</v>
+      </c>
+      <c r="EZ13" s="1"/>
     </row>
-    <row r="14" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14591,8 +14634,11 @@
       <c r="EX14" s="15">
         <v>26</v>
       </c>
+      <c r="EY14" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -15052,8 +15098,11 @@
       <c r="EX15" s="15">
         <v>6</v>
       </c>
+      <c r="EY15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15514,9 +15563,12 @@
       <c r="EX16" s="28">
         <v>121</v>
       </c>
-      <c r="EY16" s="1"/>
+      <c r="EY16" s="28">
+        <v>125</v>
+      </c>
+      <c r="EZ16" s="1"/>
     </row>
-    <row r="17" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -15976,9 +16028,12 @@
       <c r="EX17" s="15">
         <v>173</v>
       </c>
-      <c r="EY17" s="1"/>
+      <c r="EY17" s="15">
+        <v>168</v>
+      </c>
+      <c r="EZ17" s="1"/>
     </row>
-    <row r="18" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16439,9 +16494,12 @@
       <c r="EX18" s="34">
         <v>2012</v>
       </c>
-      <c r="EY18" s="1"/>
+      <c r="EY18" s="34">
+        <v>1716</v>
+      </c>
+      <c r="EZ18" s="1"/>
     </row>
-    <row r="19" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="53" t="s">
         <v>27</v>
@@ -16902,9 +16960,12 @@
       <c r="EX19" s="15">
         <v>65</v>
       </c>
-      <c r="EY19" s="1"/>
+      <c r="EY19" s="15">
+        <v>72</v>
+      </c>
+      <c r="EZ19" s="1"/>
     </row>
-    <row r="20" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="53"/>
       <c r="C20" s="9" t="s">
@@ -17363,9 +17424,12 @@
       <c r="EX20" s="28">
         <v>157</v>
       </c>
-      <c r="EY20" s="1"/>
+      <c r="EY20" s="28">
+        <v>142</v>
+      </c>
+      <c r="EZ20" s="1"/>
     </row>
-    <row r="21" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="53"/>
       <c r="C21" s="9" t="s">
@@ -17824,9 +17888,12 @@
       <c r="EX21" s="15">
         <v>34</v>
       </c>
-      <c r="EY21" s="1"/>
+      <c r="EY21" s="15">
+        <v>31</v>
+      </c>
+      <c r="EZ21" s="1"/>
     </row>
-    <row r="22" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18286,8 +18353,11 @@
       <c r="EX22" s="15">
         <v>3</v>
       </c>
+      <c r="EY22" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -18747,8 +18817,11 @@
       <c r="EX23" s="15">
         <v>2</v>
       </c>
+      <c r="EY23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19208,9 +19281,12 @@
       <c r="EX24" s="15">
         <v>12</v>
       </c>
-      <c r="EY24" s="1"/>
+      <c r="EY24" s="15">
+        <v>13</v>
+      </c>
+      <c r="EZ24" s="1"/>
     </row>
-    <row r="25" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -19670,8 +19746,11 @@
       <c r="EX25" s="15">
         <v>1</v>
       </c>
+      <c r="EY25" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -20131,8 +20210,11 @@
       <c r="EX26" s="15">
         <v>17</v>
       </c>
+      <c r="EY26" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="27" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -20592,8 +20674,11 @@
       <c r="EX27" s="15">
         <v>3</v>
       </c>
+      <c r="EY27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -21053,9 +21138,12 @@
       <c r="EX28" s="15">
         <v>2</v>
       </c>
-      <c r="EY28" s="1"/>
+      <c r="EY28" s="15">
+        <v>0</v>
+      </c>
+      <c r="EZ28" s="1"/>
     </row>
-    <row r="29" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="54" t="s">
         <v>45</v>
       </c>
@@ -21515,8 +21603,11 @@
       <c r="EX29" s="15">
         <v>0</v>
       </c>
+      <c r="EY29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="54"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -21974,8 +22065,11 @@
       <c r="EX30" s="15">
         <v>22</v>
       </c>
+      <c r="EY30" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="31" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -22436,9 +22530,12 @@
       <c r="EX31" s="15">
         <v>109</v>
       </c>
-      <c r="EY31" s="1"/>
+      <c r="EY31" s="15">
+        <v>61</v>
+      </c>
+      <c r="EZ31" s="1"/>
     </row>
-    <row r="32" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -22898,8 +22995,11 @@
       <c r="EX32" s="15">
         <v>1</v>
       </c>
+      <c r="EY32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -23359,8 +23459,11 @@
       <c r="EX33" s="15">
         <v>0</v>
       </c>
+      <c r="EY33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -23821,9 +23924,12 @@
       <c r="EX34" s="15">
         <v>131</v>
       </c>
-      <c r="EY34" s="1"/>
+      <c r="EY34" s="15">
+        <v>71</v>
+      </c>
+      <c r="EZ34" s="1"/>
     </row>
-    <row r="35" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="53" t="s">
         <v>56</v>
@@ -24284,9 +24390,12 @@
       <c r="EX35" s="15">
         <v>319</v>
       </c>
-      <c r="EY35" s="1"/>
+      <c r="EY35" s="15">
+        <v>318</v>
+      </c>
+      <c r="EZ35" s="1"/>
     </row>
-    <row r="36" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="53"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -24744,9 +24853,12 @@
       <c r="EX36" s="28">
         <v>37</v>
       </c>
-      <c r="EY36" s="1"/>
+      <c r="EY36" s="28">
+        <v>36</v>
+      </c>
+      <c r="EZ36" s="1"/>
     </row>
-    <row r="37" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -25207,9 +25319,12 @@
       <c r="EX37" s="15">
         <v>52</v>
       </c>
-      <c r="EY37" s="1"/>
+      <c r="EY37" s="15">
+        <v>51</v>
+      </c>
+      <c r="EZ37" s="1"/>
     </row>
-    <row r="38" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -25669,8 +25784,11 @@
       <c r="EX38" s="15">
         <v>18</v>
       </c>
+      <c r="EY38" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="39" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -26130,8 +26248,11 @@
       <c r="EX39" s="15">
         <v>8</v>
       </c>
+      <c r="EY39" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="40" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -26591,8 +26712,11 @@
       <c r="EX40" s="15">
         <v>0</v>
       </c>
+      <c r="EY40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -27052,8 +27176,11 @@
       <c r="EX41" s="15">
         <v>0</v>
       </c>
+      <c r="EY41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -27513,8 +27640,11 @@
       <c r="EX42" s="15">
         <v>16</v>
       </c>
+      <c r="EY42" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="43" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -27974,8 +28104,11 @@
       <c r="EX43" s="28">
         <v>78</v>
       </c>
+      <c r="EY43" s="28">
+        <v>66</v>
+      </c>
     </row>
-    <row r="44" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -28435,8 +28568,11 @@
       <c r="EX44" s="15">
         <v>4</v>
       </c>
+      <c r="EY44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -28896,9 +29032,12 @@
       <c r="EX45" s="15">
         <v>15</v>
       </c>
-      <c r="EY45" s="1"/>
+      <c r="EY45" s="15">
+        <v>30</v>
+      </c>
+      <c r="EZ45" s="1"/>
     </row>
-    <row r="46" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -29358,8 +29497,11 @@
       <c r="EX46" s="15">
         <v>17</v>
       </c>
+      <c r="EY46" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="47" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -29819,8 +29961,11 @@
       <c r="EX47" s="15">
         <v>3</v>
       </c>
+      <c r="EY47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -30280,8 +30425,11 @@
       <c r="EX48" s="15">
         <v>19</v>
       </c>
+      <c r="EY48" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="53" t="s">
         <v>83</v>
@@ -30742,9 +30890,12 @@
       <c r="EX49" s="15">
         <v>103</v>
       </c>
-      <c r="EY49" s="1"/>
+      <c r="EY49" s="15">
+        <v>46</v>
+      </c>
+      <c r="EZ49" s="1"/>
     </row>
-    <row r="50" spans="1:155" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:156" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="53"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -31202,9 +31353,12 @@
       <c r="EX50" s="15">
         <v>40</v>
       </c>
-      <c r="EY50" s="1"/>
+      <c r="EY50" s="15">
+        <v>25</v>
+      </c>
+      <c r="EZ50" s="1"/>
     </row>
-    <row r="51" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -31664,8 +31818,11 @@
       <c r="EX51" s="15">
         <v>4</v>
       </c>
+      <c r="EY51" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="52" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -32125,8 +32282,11 @@
       <c r="EX52" s="15">
         <v>17</v>
       </c>
+      <c r="EY52" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="53" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -32586,8 +32746,11 @@
       <c r="EX53" s="15">
         <v>68</v>
       </c>
+      <c r="EY53" s="15">
+        <v>39</v>
+      </c>
     </row>
-    <row r="54" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -33047,8 +33210,11 @@
       <c r="EX54" s="15">
         <v>16</v>
       </c>
+      <c r="EY54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -33508,8 +33674,11 @@
       <c r="EX55" s="15">
         <v>16</v>
       </c>
+      <c r="EY55" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="56" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -33969,8 +34138,11 @@
       <c r="EX56" s="15">
         <v>1</v>
       </c>
+      <c r="EY56" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -34430,8 +34602,11 @@
       <c r="EX57" s="15">
         <v>0</v>
       </c>
+      <c r="EY57" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -34909,7 +35084,7 @@
         <v>2812</v>
       </c>
       <c r="DR58" s="14">
-        <f t="shared" ref="DR58:EX58" si="10">SUM(DR6:DR57)</f>
+        <f t="shared" ref="DR58:EY58" si="10">SUM(DR6:DR57)</f>
         <v>2887</v>
       </c>
       <c r="DS58" s="14">
@@ -35040,8 +35215,12 @@
         <f t="shared" si="10"/>
         <v>4082</v>
       </c>
+      <c r="EY58" s="14">
+        <f t="shared" si="10"/>
+        <v>3474</v>
+      </c>
     </row>
-    <row r="59" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -35125,7 +35304,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -35209,7 +35388,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:155" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:156" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -35294,11 +35473,7 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
-    <mergeCell ref="DE2:EX2"/>
-    <mergeCell ref="ER3:EX3"/>
-    <mergeCell ref="EX4:EX5"/>
-    <mergeCell ref="EW4:EW5"/>
+  <mergeCells count="169">
     <mergeCell ref="EV4:EV5"/>
     <mergeCell ref="DE3:EQ3"/>
     <mergeCell ref="DT4:DT5"/>
@@ -35314,6 +35489,8 @@
     <mergeCell ref="EL4:EL5"/>
     <mergeCell ref="EJ4:EJ5"/>
     <mergeCell ref="ER4:ER5"/>
+    <mergeCell ref="DU4:DU5"/>
+    <mergeCell ref="EY4:EY5"/>
     <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="DD4:DD5"/>
@@ -35335,8 +35512,8 @@
     <mergeCell ref="DG4:DG5"/>
     <mergeCell ref="DE4:DE5"/>
     <mergeCell ref="DC4:DC5"/>
-    <mergeCell ref="DB4:DB5"/>
-    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="EX4:EX5"/>
+    <mergeCell ref="EW4:EW5"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="BD2:DD2"/>
     <mergeCell ref="BD3:CQ3"/>
@@ -35359,9 +35536,8 @@
     <mergeCell ref="DX4:DX5"/>
     <mergeCell ref="DW4:DW5"/>
     <mergeCell ref="DV4:DV5"/>
-    <mergeCell ref="DU4:DU5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="DE2:EY2"/>
+    <mergeCell ref="ER3:EY3"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="D2:BC2"/>
     <mergeCell ref="DO4:DO5"/>
@@ -35384,8 +35560,8 @@
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="BK4:BK5"/>
     <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="X4:X5"/>
     <mergeCell ref="AL4:AL5"/>
@@ -35452,6 +35628,9 @@
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -35463,6 +35642,7 @@
     <mergeCell ref="AS4:AS5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="BQ4:BQ5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -35475,7 +35655,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:EX57">
+  <conditionalFormatting sqref="DP6:EY57">
     <cfRule type="containsBlanks" dxfId="7" priority="1">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
@@ -35495,7 +35675,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:EX58"/>
+  <dimension ref="B1:EY58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -35514,17 +35694,17 @@
     <col min="43" max="43" width="11" style="1" customWidth="1"/>
     <col min="44" max="44" width="11" style="4" customWidth="1"/>
     <col min="45" max="49" width="11" style="1" customWidth="1"/>
-    <col min="50" max="50" width="11" style="4" customWidth="1"/>
-    <col min="51" max="55" width="11" style="1" customWidth="1"/>
+    <col min="50" max="51" width="11" style="4" customWidth="1"/>
+    <col min="52" max="55" width="11" style="1" customWidth="1"/>
     <col min="56" max="82" width="10.875" style="1" customWidth="1"/>
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="154" width="10.875" style="1" customWidth="1"/>
-    <col min="155" max="16384" width="8.625" style="1"/>
+    <col min="106" max="155" width="10.875" style="1" customWidth="1"/>
+    <col min="156" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:154" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:155" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="76" t="s">
         <v>323</v>
       </c>
@@ -35605,216 +35785,218 @@
       <c r="EU1" s="19"/>
       <c r="EV1" s="19"/>
       <c r="EW1" s="19"/>
-      <c r="EX1" s="19" t="s">
+      <c r="EX1" s="19"/>
+      <c r="EY1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:154" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:155" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="71" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73"/>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="73"/>
-      <c r="AD2" s="73"/>
-      <c r="AE2" s="73"/>
-      <c r="AF2" s="73"/>
-      <c r="AG2" s="73"/>
-      <c r="AH2" s="73"/>
-      <c r="AI2" s="73"/>
-      <c r="AJ2" s="73"/>
-      <c r="AK2" s="73"/>
-      <c r="AL2" s="73"/>
-      <c r="AM2" s="73"/>
-      <c r="AN2" s="73"/>
-      <c r="AO2" s="73"/>
-      <c r="AP2" s="73"/>
-      <c r="AQ2" s="73"/>
-      <c r="AR2" s="73"/>
-      <c r="AS2" s="73"/>
-      <c r="AT2" s="73"/>
-      <c r="AU2" s="73"/>
-      <c r="AV2" s="73"/>
-      <c r="AW2" s="73"/>
-      <c r="AX2" s="73"/>
-      <c r="AY2" s="73"/>
-      <c r="AZ2" s="73"/>
-      <c r="BA2" s="73"/>
-      <c r="BB2" s="73"/>
-      <c r="BC2" s="73"/>
-      <c r="BD2" s="73" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="71"/>
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="71"/>
+      <c r="AE2" s="71"/>
+      <c r="AF2" s="71"/>
+      <c r="AG2" s="71"/>
+      <c r="AH2" s="71"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="71"/>
+      <c r="AK2" s="71"/>
+      <c r="AL2" s="71"/>
+      <c r="AM2" s="71"/>
+      <c r="AN2" s="71"/>
+      <c r="AO2" s="71"/>
+      <c r="AP2" s="71"/>
+      <c r="AQ2" s="71"/>
+      <c r="AR2" s="71"/>
+      <c r="AS2" s="71"/>
+      <c r="AT2" s="71"/>
+      <c r="AU2" s="71"/>
+      <c r="AV2" s="71"/>
+      <c r="AW2" s="71"/>
+      <c r="AX2" s="71"/>
+      <c r="AY2" s="71"/>
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71"/>
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71"/>
+      <c r="BD2" s="71" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="73"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="73"/>
-      <c r="BH2" s="73"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="73"/>
-      <c r="BM2" s="73"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="73"/>
-      <c r="BS2" s="73"/>
-      <c r="BT2" s="73"/>
-      <c r="BU2" s="73"/>
-      <c r="BV2" s="73"/>
-      <c r="BW2" s="73"/>
-      <c r="BX2" s="73"/>
-      <c r="BY2" s="73"/>
-      <c r="BZ2" s="73"/>
-      <c r="CA2" s="73"/>
-      <c r="CB2" s="73"/>
-      <c r="CC2" s="73"/>
-      <c r="CD2" s="73"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="73"/>
-      <c r="CG2" s="73"/>
-      <c r="CH2" s="73"/>
-      <c r="CI2" s="73"/>
-      <c r="CJ2" s="73"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="73"/>
-      <c r="CM2" s="73"/>
-      <c r="CN2" s="73"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="73"/>
-      <c r="CQ2" s="73"/>
-      <c r="CR2" s="73"/>
-      <c r="CS2" s="73"/>
-      <c r="CT2" s="73"/>
-      <c r="CU2" s="73"/>
-      <c r="CV2" s="73"/>
-      <c r="CW2" s="73"/>
-      <c r="CX2" s="73"/>
-      <c r="CY2" s="73"/>
-      <c r="CZ2" s="73"/>
-      <c r="DA2" s="73"/>
-      <c r="DB2" s="73"/>
-      <c r="DC2" s="73"/>
-      <c r="DD2" s="73" t="s">
+      <c r="BE2" s="71"/>
+      <c r="BF2" s="71"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="71"/>
+      <c r="BI2" s="71"/>
+      <c r="BJ2" s="71"/>
+      <c r="BK2" s="71"/>
+      <c r="BL2" s="71"/>
+      <c r="BM2" s="71"/>
+      <c r="BN2" s="71"/>
+      <c r="BO2" s="71"/>
+      <c r="BP2" s="71"/>
+      <c r="BQ2" s="71"/>
+      <c r="BR2" s="71"/>
+      <c r="BS2" s="71"/>
+      <c r="BT2" s="71"/>
+      <c r="BU2" s="71"/>
+      <c r="BV2" s="71"/>
+      <c r="BW2" s="71"/>
+      <c r="BX2" s="71"/>
+      <c r="BY2" s="71"/>
+      <c r="BZ2" s="71"/>
+      <c r="CA2" s="71"/>
+      <c r="CB2" s="71"/>
+      <c r="CC2" s="71"/>
+      <c r="CD2" s="71"/>
+      <c r="CE2" s="71"/>
+      <c r="CF2" s="71"/>
+      <c r="CG2" s="71"/>
+      <c r="CH2" s="71"/>
+      <c r="CI2" s="71"/>
+      <c r="CJ2" s="71"/>
+      <c r="CK2" s="71"/>
+      <c r="CL2" s="71"/>
+      <c r="CM2" s="71"/>
+      <c r="CN2" s="71"/>
+      <c r="CO2" s="71"/>
+      <c r="CP2" s="71"/>
+      <c r="CQ2" s="71"/>
+      <c r="CR2" s="71"/>
+      <c r="CS2" s="71"/>
+      <c r="CT2" s="71"/>
+      <c r="CU2" s="71"/>
+      <c r="CV2" s="71"/>
+      <c r="CW2" s="71"/>
+      <c r="CX2" s="71"/>
+      <c r="CY2" s="71"/>
+      <c r="CZ2" s="71"/>
+      <c r="DA2" s="71"/>
+      <c r="DB2" s="71"/>
+      <c r="DC2" s="71"/>
+      <c r="DD2" s="71" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="73"/>
-      <c r="DF2" s="73"/>
-      <c r="DG2" s="73"/>
-      <c r="DH2" s="73"/>
-      <c r="DI2" s="73"/>
-      <c r="DJ2" s="73"/>
-      <c r="DK2" s="73"/>
-      <c r="DL2" s="73"/>
-      <c r="DM2" s="73"/>
-      <c r="DN2" s="73"/>
-      <c r="DO2" s="73"/>
-      <c r="DP2" s="73"/>
-      <c r="DQ2" s="73"/>
-      <c r="DR2" s="73"/>
-      <c r="DS2" s="73"/>
-      <c r="DT2" s="73"/>
-      <c r="DU2" s="73"/>
-      <c r="DV2" s="73"/>
-      <c r="DW2" s="73"/>
-      <c r="DX2" s="73"/>
-      <c r="DY2" s="73"/>
-      <c r="DZ2" s="73"/>
-      <c r="EA2" s="73"/>
-      <c r="EB2" s="73"/>
-      <c r="EC2" s="73"/>
-      <c r="ED2" s="73"/>
-      <c r="EE2" s="73"/>
-      <c r="EF2" s="73"/>
-      <c r="EG2" s="73"/>
-      <c r="EH2" s="73"/>
-      <c r="EI2" s="73"/>
-      <c r="EJ2" s="73"/>
-      <c r="EK2" s="73"/>
-      <c r="EL2" s="73"/>
-      <c r="EM2" s="73"/>
-      <c r="EN2" s="73"/>
-      <c r="EO2" s="73"/>
-      <c r="EP2" s="73"/>
-      <c r="EQ2" s="73"/>
-      <c r="ER2" s="73"/>
-      <c r="ES2" s="73"/>
-      <c r="ET2" s="73"/>
-      <c r="EU2" s="73"/>
-      <c r="EV2" s="73"/>
-      <c r="EW2" s="73"/>
-      <c r="EX2" s="73"/>
+      <c r="DE2" s="71"/>
+      <c r="DF2" s="71"/>
+      <c r="DG2" s="71"/>
+      <c r="DH2" s="71"/>
+      <c r="DI2" s="71"/>
+      <c r="DJ2" s="71"/>
+      <c r="DK2" s="71"/>
+      <c r="DL2" s="71"/>
+      <c r="DM2" s="71"/>
+      <c r="DN2" s="71"/>
+      <c r="DO2" s="71"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="71"/>
+      <c r="DR2" s="71"/>
+      <c r="DS2" s="71"/>
+      <c r="DT2" s="71"/>
+      <c r="DU2" s="71"/>
+      <c r="DV2" s="71"/>
+      <c r="DW2" s="71"/>
+      <c r="DX2" s="71"/>
+      <c r="DY2" s="71"/>
+      <c r="DZ2" s="71"/>
+      <c r="EA2" s="71"/>
+      <c r="EB2" s="71"/>
+      <c r="EC2" s="71"/>
+      <c r="ED2" s="71"/>
+      <c r="EE2" s="71"/>
+      <c r="EF2" s="71"/>
+      <c r="EG2" s="71"/>
+      <c r="EH2" s="71"/>
+      <c r="EI2" s="71"/>
+      <c r="EJ2" s="71"/>
+      <c r="EK2" s="71"/>
+      <c r="EL2" s="71"/>
+      <c r="EM2" s="71"/>
+      <c r="EN2" s="71"/>
+      <c r="EO2" s="71"/>
+      <c r="EP2" s="71"/>
+      <c r="EQ2" s="71"/>
+      <c r="ER2" s="71"/>
+      <c r="ES2" s="71"/>
+      <c r="ET2" s="71"/>
+      <c r="EU2" s="71"/>
+      <c r="EV2" s="71"/>
+      <c r="EW2" s="71"/>
+      <c r="EX2" s="71"/>
+      <c r="EY2" s="71"/>
     </row>
-    <row r="3" spans="2:154" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:155" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="77" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="77"/>
+      <c r="AC3" s="77"/>
+      <c r="AD3" s="77"/>
+      <c r="AE3" s="77"/>
+      <c r="AF3" s="77"/>
+      <c r="AG3" s="77"/>
+      <c r="AH3" s="77"/>
+      <c r="AI3" s="77"/>
+      <c r="AJ3" s="77"/>
+      <c r="AK3" s="77"/>
+      <c r="AL3" s="77"/>
+      <c r="AM3" s="77"/>
+      <c r="AN3" s="77"/>
+      <c r="AO3" s="77"/>
+      <c r="AP3" s="77"/>
+      <c r="AQ3" s="77"/>
       <c r="AR3" s="64" t="s">
         <v>282</v>
       </c>
@@ -35936,168 +36118,169 @@
       <c r="EV3" s="64"/>
       <c r="EW3" s="64"/>
       <c r="EX3" s="64"/>
+      <c r="EY3" s="64"/>
     </row>
-    <row r="4" spans="2:154" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:155" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="62" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="D4" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="78" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="80" t="s">
+      <c r="H4" s="78" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="L4" s="80" t="s">
+      <c r="L4" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="80" t="s">
+      <c r="M4" s="78" t="s">
         <v>192</v>
       </c>
-      <c r="N4" s="80" t="s">
+      <c r="N4" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="O4" s="80" t="s">
+      <c r="O4" s="78" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="80" t="s">
+      <c r="P4" s="78" t="s">
         <v>195</v>
       </c>
-      <c r="Q4" s="80" t="s">
+      <c r="Q4" s="78" t="s">
         <v>185</v>
       </c>
       <c r="R4" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="S4" s="80" t="s">
+      <c r="S4" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="T4" s="80" t="s">
+      <c r="T4" s="78" t="s">
         <v>198</v>
       </c>
-      <c r="U4" s="80" t="s">
+      <c r="U4" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="V4" s="80" t="s">
+      <c r="V4" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="W4" s="80" t="s">
+      <c r="W4" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="X4" s="80" t="s">
+      <c r="X4" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="77" t="s">
+      <c r="Y4" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="Z4" s="80" t="s">
+      <c r="Z4" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" s="80" t="s">
+      <c r="AA4" s="78" t="s">
         <v>163</v>
       </c>
-      <c r="AB4" s="80" t="s">
+      <c r="AB4" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="AC4" s="77" t="s">
+      <c r="AC4" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="AD4" s="80" t="s">
+      <c r="AD4" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="AE4" s="80" t="s">
+      <c r="AE4" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="AF4" s="80" t="s">
+      <c r="AF4" s="78" t="s">
         <v>200</v>
       </c>
-      <c r="AG4" s="80" t="s">
+      <c r="AG4" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="AH4" s="80" t="s">
+      <c r="AH4" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="AI4" s="77" t="s">
+      <c r="AI4" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="AJ4" s="77" t="s">
+      <c r="AJ4" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="AK4" s="77" t="s">
+      <c r="AK4" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="AL4" s="77" t="s">
+      <c r="AL4" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="AM4" s="77" t="s">
+      <c r="AM4" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="AN4" s="80" t="s">
+      <c r="AN4" s="78" t="s">
         <v>171</v>
       </c>
-      <c r="AO4" s="77" t="s">
+      <c r="AO4" s="79" t="s">
         <v>172</v>
       </c>
-      <c r="AP4" s="77" t="s">
+      <c r="AP4" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="AQ4" s="80" t="s">
+      <c r="AQ4" s="78" t="s">
         <v>174</v>
       </c>
-      <c r="AR4" s="77" t="s">
+      <c r="AR4" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="AS4" s="80" t="s">
+      <c r="AS4" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="AT4" s="80" t="s">
+      <c r="AT4" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="AU4" s="80" t="s">
+      <c r="AU4" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="AV4" s="80" t="s">
+      <c r="AV4" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="AW4" s="80" t="s">
+      <c r="AW4" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="77" t="s">
+      <c r="AX4" s="79" t="s">
         <v>203</v>
       </c>
-      <c r="AY4" s="80" t="s">
+      <c r="AY4" s="79" t="s">
         <v>204</v>
       </c>
-      <c r="AZ4" s="80" t="s">
+      <c r="AZ4" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="BA4" s="80" t="s">
+      <c r="BA4" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="BB4" s="80" t="s">
+      <c r="BB4" s="78" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="80" t="s">
+      <c r="BC4" s="78" t="s">
         <v>184</v>
       </c>
       <c r="BD4" s="45" t="s">
@@ -36397,8 +36580,11 @@
       <c r="EX4" s="69" t="s">
         <v>428</v>
       </c>
+      <c r="EY4" s="69" t="s">
+        <v>430</v>
+      </c>
     </row>
-    <row r="5" spans="2:154" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:155" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63"/>
       <c r="C5" s="56"/>
       <c r="D5" s="47"/>
@@ -36422,33 +36608,33 @@
       <c r="V5" s="47"/>
       <c r="W5" s="47"/>
       <c r="X5" s="47"/>
-      <c r="Y5" s="78"/>
+      <c r="Y5" s="80"/>
       <c r="Z5" s="47"/>
       <c r="AA5" s="47"/>
       <c r="AB5" s="47"/>
-      <c r="AC5" s="78"/>
+      <c r="AC5" s="80"/>
       <c r="AD5" s="47"/>
       <c r="AE5" s="47"/>
       <c r="AF5" s="47"/>
       <c r="AG5" s="47"/>
       <c r="AH5" s="47"/>
-      <c r="AI5" s="78"/>
-      <c r="AJ5" s="78"/>
-      <c r="AK5" s="78"/>
-      <c r="AL5" s="78"/>
-      <c r="AM5" s="78"/>
+      <c r="AI5" s="80"/>
+      <c r="AJ5" s="80"/>
+      <c r="AK5" s="80"/>
+      <c r="AL5" s="80"/>
+      <c r="AM5" s="80"/>
       <c r="AN5" s="47"/>
-      <c r="AO5" s="78"/>
-      <c r="AP5" s="78"/>
+      <c r="AO5" s="80"/>
+      <c r="AP5" s="80"/>
       <c r="AQ5" s="47"/>
-      <c r="AR5" s="78"/>
+      <c r="AR5" s="80"/>
       <c r="AS5" s="47"/>
       <c r="AT5" s="47"/>
       <c r="AU5" s="47"/>
       <c r="AV5" s="47"/>
       <c r="AW5" s="47"/>
-      <c r="AX5" s="78"/>
-      <c r="AY5" s="47"/>
+      <c r="AX5" s="80"/>
+      <c r="AY5" s="80"/>
       <c r="AZ5" s="47"/>
       <c r="BA5" s="47"/>
       <c r="BB5" s="47"/>
@@ -36552,8 +36738,9 @@
       <c r="EV5" s="69"/>
       <c r="EW5" s="69"/>
       <c r="EX5" s="69"/>
+      <c r="EY5" s="69"/>
     </row>
-    <row r="6" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -36701,7 +36888,7 @@
       <c r="AX6" s="28">
         <v>58</v>
       </c>
-      <c r="AY6" s="26">
+      <c r="AY6" s="28">
         <v>49</v>
       </c>
       <c r="AZ6" s="26">
@@ -37013,8 +37200,11 @@
       <c r="EX6" s="28">
         <v>164</v>
       </c>
+      <c r="EY6" s="28">
+        <v>158</v>
+      </c>
     </row>
-    <row r="7" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -37162,7 +37352,7 @@
       <c r="AX7" s="28">
         <v>1</v>
       </c>
-      <c r="AY7" s="26">
+      <c r="AY7" s="28">
         <v>2</v>
       </c>
       <c r="AZ7" s="26">
@@ -37474,8 +37664,11 @@
       <c r="EX7" s="15">
         <v>0</v>
       </c>
+      <c r="EY7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -37623,7 +37816,7 @@
       <c r="AX8" s="28">
         <v>6</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="28">
         <v>2</v>
       </c>
       <c r="AZ8" s="26">
@@ -37935,8 +38128,11 @@
       <c r="EX8" s="28">
         <v>15</v>
       </c>
+      <c r="EY8" s="28">
+        <v>17</v>
+      </c>
     </row>
-    <row r="9" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -38084,7 +38280,7 @@
       <c r="AX9" s="28">
         <v>28</v>
       </c>
-      <c r="AY9" s="26">
+      <c r="AY9" s="28">
         <v>34</v>
       </c>
       <c r="AZ9" s="26">
@@ -38396,8 +38592,11 @@
       <c r="EX9" s="15">
         <v>97</v>
       </c>
+      <c r="EY9" s="15">
+        <v>94</v>
+      </c>
     </row>
-    <row r="10" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -38545,7 +38744,7 @@
       <c r="AX10" s="28">
         <v>0</v>
       </c>
-      <c r="AY10" s="26">
+      <c r="AY10" s="28">
         <v>1</v>
       </c>
       <c r="AZ10" s="26">
@@ -38857,8 +39056,11 @@
       <c r="EX10" s="15">
         <v>0</v>
       </c>
+      <c r="EY10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -39006,7 +39208,7 @@
       <c r="AX11" s="28">
         <v>1</v>
       </c>
-      <c r="AY11" s="26">
+      <c r="AY11" s="28">
         <v>5</v>
       </c>
       <c r="AZ11" s="26">
@@ -39318,8 +39520,11 @@
       <c r="EX11" s="15">
         <v>10</v>
       </c>
+      <c r="EY11" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -39467,7 +39672,7 @@
       <c r="AX12" s="28">
         <v>4</v>
       </c>
-      <c r="AY12" s="26">
+      <c r="AY12" s="28">
         <v>1</v>
       </c>
       <c r="AZ12" s="26">
@@ -39779,8 +39984,11 @@
       <c r="EX12" s="15">
         <v>5</v>
       </c>
+      <c r="EY12" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -39928,7 +40136,7 @@
       <c r="AX13" s="28">
         <v>17</v>
       </c>
-      <c r="AY13" s="26">
+      <c r="AY13" s="28">
         <v>21</v>
       </c>
       <c r="AZ13" s="26">
@@ -40240,8 +40448,11 @@
       <c r="EX13" s="15">
         <v>23</v>
       </c>
+      <c r="EY13" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="14" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -40389,7 +40600,7 @@
       <c r="AX14" s="28">
         <v>4</v>
       </c>
-      <c r="AY14" s="26">
+      <c r="AY14" s="28">
         <v>7</v>
       </c>
       <c r="AZ14" s="26">
@@ -40701,8 +40912,11 @@
       <c r="EX14" s="15">
         <v>23</v>
       </c>
+      <c r="EY14" s="15">
+        <v>35</v>
+      </c>
     </row>
-    <row r="15" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -40850,7 +41064,7 @@
       <c r="AX15" s="28">
         <v>2</v>
       </c>
-      <c r="AY15" s="26">
+      <c r="AY15" s="28">
         <v>0</v>
       </c>
       <c r="AZ15" s="26">
@@ -41162,8 +41376,11 @@
       <c r="EX15" s="15">
         <v>3</v>
       </c>
+      <c r="EY15" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -41311,7 +41528,7 @@
       <c r="AX16" s="28">
         <v>48</v>
       </c>
-      <c r="AY16" s="26">
+      <c r="AY16" s="28">
         <v>33</v>
       </c>
       <c r="AZ16" s="26">
@@ -41623,8 +41840,11 @@
       <c r="EX16" s="28">
         <v>214</v>
       </c>
+      <c r="EY16" s="28">
+        <v>167</v>
+      </c>
     </row>
-    <row r="17" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -41772,7 +41992,7 @@
       <c r="AX17" s="28">
         <v>93</v>
       </c>
-      <c r="AY17" s="26">
+      <c r="AY17" s="28">
         <v>79</v>
       </c>
       <c r="AZ17" s="26">
@@ -42084,8 +42304,11 @@
       <c r="EX17" s="15">
         <v>226</v>
       </c>
+      <c r="EY17" s="15">
+        <v>191</v>
+      </c>
     </row>
-    <row r="18" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -42233,7 +42456,7 @@
       <c r="AX18" s="28">
         <v>569</v>
       </c>
-      <c r="AY18" s="26">
+      <c r="AY18" s="28">
         <v>544</v>
       </c>
       <c r="AZ18" s="26">
@@ -42545,8 +42768,11 @@
       <c r="EX18" s="34">
         <v>2849</v>
       </c>
+      <c r="EY18" s="34">
+        <v>2549</v>
+      </c>
     </row>
-    <row r="19" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="53" t="s">
         <v>27</v>
       </c>
@@ -42694,7 +42920,7 @@
       <c r="AX19" s="28">
         <v>20</v>
       </c>
-      <c r="AY19" s="26">
+      <c r="AY19" s="28">
         <v>9</v>
       </c>
       <c r="AZ19" s="26">
@@ -43006,8 +43232,11 @@
       <c r="EX19" s="15">
         <v>168</v>
       </c>
+      <c r="EY19" s="15">
+        <v>105</v>
+      </c>
     </row>
-    <row r="20" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="53"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -43153,7 +43382,7 @@
       <c r="AX20" s="28">
         <v>76</v>
       </c>
-      <c r="AY20" s="26">
+      <c r="AY20" s="28">
         <v>60</v>
       </c>
       <c r="AZ20" s="26">
@@ -43465,8 +43694,11 @@
       <c r="EX20" s="28">
         <v>457</v>
       </c>
+      <c r="EY20" s="28">
+        <v>414</v>
+      </c>
     </row>
-    <row r="21" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="53"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -43612,7 +43844,7 @@
       <c r="AX21" s="28">
         <v>11</v>
       </c>
-      <c r="AY21" s="26">
+      <c r="AY21" s="28">
         <v>20</v>
       </c>
       <c r="AZ21" s="26">
@@ -43924,8 +44156,11 @@
       <c r="EX21" s="15">
         <v>71</v>
       </c>
+      <c r="EY21" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="22" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -44073,7 +44308,7 @@
       <c r="AX22" s="28">
         <v>21</v>
       </c>
-      <c r="AY22" s="26">
+      <c r="AY22" s="28">
         <v>23</v>
       </c>
       <c r="AZ22" s="26">
@@ -44385,8 +44620,11 @@
       <c r="EX22" s="15">
         <v>11</v>
       </c>
+      <c r="EY22" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="23" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -44534,7 +44772,7 @@
       <c r="AX23" s="28">
         <v>1</v>
       </c>
-      <c r="AY23" s="26">
+      <c r="AY23" s="28">
         <v>0</v>
       </c>
       <c r="AZ23" s="26">
@@ -44846,8 +45084,11 @@
       <c r="EX23" s="15">
         <v>1</v>
       </c>
+      <c r="EY23" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -44995,7 +45236,7 @@
       <c r="AX24" s="28">
         <v>2</v>
       </c>
-      <c r="AY24" s="26">
+      <c r="AY24" s="28">
         <v>1</v>
       </c>
       <c r="AZ24" s="26">
@@ -45307,8 +45548,11 @@
       <c r="EX24" s="15">
         <v>14</v>
       </c>
+      <c r="EY24" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -45456,7 +45700,7 @@
       <c r="AX25" s="28">
         <v>0</v>
       </c>
-      <c r="AY25" s="26">
+      <c r="AY25" s="28">
         <v>0</v>
       </c>
       <c r="AZ25" s="26">
@@ -45768,8 +46012,11 @@
       <c r="EX25" s="15">
         <v>0</v>
       </c>
+      <c r="EY25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -45917,7 +46164,7 @@
       <c r="AX26" s="28">
         <v>5</v>
       </c>
-      <c r="AY26" s="26">
+      <c r="AY26" s="28">
         <v>2</v>
       </c>
       <c r="AZ26" s="26">
@@ -46229,8 +46476,11 @@
       <c r="EX26" s="15">
         <v>21</v>
       </c>
+      <c r="EY26" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="27" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -46378,7 +46628,7 @@
       <c r="AX27" s="28">
         <v>0</v>
       </c>
-      <c r="AY27" s="26">
+      <c r="AY27" s="28">
         <v>0</v>
       </c>
       <c r="AZ27" s="26">
@@ -46690,8 +46940,11 @@
       <c r="EX27" s="15">
         <v>0</v>
       </c>
+      <c r="EY27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -46839,7 +47092,7 @@
       <c r="AX28" s="28">
         <v>1</v>
       </c>
-      <c r="AY28" s="26">
+      <c r="AY28" s="28">
         <v>1</v>
       </c>
       <c r="AZ28" s="26">
@@ -47151,8 +47404,11 @@
       <c r="EX28" s="15">
         <v>3</v>
       </c>
+      <c r="EY28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="54" t="s">
         <v>45</v>
       </c>
@@ -47300,7 +47556,7 @@
       <c r="AX29" s="28">
         <v>4</v>
       </c>
-      <c r="AY29" s="26">
+      <c r="AY29" s="28">
         <v>2</v>
       </c>
       <c r="AZ29" s="26">
@@ -47612,8 +47868,11 @@
       <c r="EX29" s="15">
         <v>5</v>
       </c>
+      <c r="EY29" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="54"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -47759,7 +48018,7 @@
       <c r="AX30" s="28">
         <v>1</v>
       </c>
-      <c r="AY30" s="26">
+      <c r="AY30" s="28">
         <v>6</v>
       </c>
       <c r="AZ30" s="26">
@@ -48071,8 +48330,11 @@
       <c r="EX30" s="15">
         <v>21</v>
       </c>
+      <c r="EY30" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="31" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -48220,7 +48482,7 @@
       <c r="AX31" s="28">
         <v>15</v>
       </c>
-      <c r="AY31" s="26">
+      <c r="AY31" s="28">
         <v>8</v>
       </c>
       <c r="AZ31" s="26">
@@ -48532,8 +48794,11 @@
       <c r="EX31" s="15">
         <v>148</v>
       </c>
+      <c r="EY31" s="15">
+        <v>79</v>
+      </c>
     </row>
-    <row r="32" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -48681,7 +48946,7 @@
       <c r="AX32" s="28">
         <v>1</v>
       </c>
-      <c r="AY32" s="26">
+      <c r="AY32" s="28">
         <v>0</v>
       </c>
       <c r="AZ32" s="26">
@@ -48993,8 +49258,11 @@
       <c r="EX32" s="15">
         <v>0</v>
       </c>
+      <c r="EY32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -49142,7 +49410,7 @@
       <c r="AX33" s="28">
         <v>0</v>
       </c>
-      <c r="AY33" s="26">
+      <c r="AY33" s="28">
         <v>0</v>
       </c>
       <c r="AZ33" s="26">
@@ -49454,8 +49722,11 @@
       <c r="EX33" s="15">
         <v>1</v>
       </c>
+      <c r="EY33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -49603,7 +49874,7 @@
       <c r="AX34" s="28">
         <v>24</v>
       </c>
-      <c r="AY34" s="26">
+      <c r="AY34" s="28">
         <v>16</v>
       </c>
       <c r="AZ34" s="26">
@@ -49915,8 +50186,11 @@
       <c r="EX34" s="15">
         <v>164</v>
       </c>
+      <c r="EY34" s="15">
+        <v>117</v>
+      </c>
     </row>
-    <row r="35" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="53" t="s">
         <v>56</v>
       </c>
@@ -50064,7 +50338,7 @@
       <c r="AX35" s="28">
         <v>143</v>
       </c>
-      <c r="AY35" s="26">
+      <c r="AY35" s="28">
         <v>129</v>
       </c>
       <c r="AZ35" s="26">
@@ -50376,8 +50650,11 @@
       <c r="EX35" s="15">
         <v>676</v>
       </c>
+      <c r="EY35" s="15">
+        <v>660</v>
+      </c>
     </row>
-    <row r="36" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="53"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -50523,7 +50800,7 @@
       <c r="AX36" s="28">
         <v>19</v>
       </c>
-      <c r="AY36" s="26">
+      <c r="AY36" s="28">
         <v>20</v>
       </c>
       <c r="AZ36" s="26">
@@ -50835,8 +51112,11 @@
       <c r="EX36" s="28">
         <v>120</v>
       </c>
+      <c r="EY36" s="28">
+        <v>81</v>
+      </c>
     </row>
-    <row r="37" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -50984,7 +51264,7 @@
       <c r="AX37" s="28">
         <v>15</v>
       </c>
-      <c r="AY37" s="26">
+      <c r="AY37" s="28">
         <v>9</v>
       </c>
       <c r="AZ37" s="26">
@@ -51296,8 +51576,11 @@
       <c r="EX37" s="15">
         <v>150</v>
       </c>
+      <c r="EY37" s="15">
+        <v>113</v>
+      </c>
     </row>
-    <row r="38" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -51445,7 +51728,7 @@
       <c r="AX38" s="28">
         <v>1</v>
       </c>
-      <c r="AY38" s="26">
+      <c r="AY38" s="28">
         <v>8</v>
       </c>
       <c r="AZ38" s="26">
@@ -51757,8 +52040,11 @@
       <c r="EX38" s="15">
         <v>42</v>
       </c>
+      <c r="EY38" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="39" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -51906,7 +52192,7 @@
       <c r="AX39" s="28">
         <v>4</v>
       </c>
-      <c r="AY39" s="26">
+      <c r="AY39" s="28">
         <v>6</v>
       </c>
       <c r="AZ39" s="26">
@@ -52218,8 +52504,11 @@
       <c r="EX39" s="15">
         <v>10</v>
       </c>
+      <c r="EY39" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="40" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -52367,7 +52656,7 @@
       <c r="AX40" s="28">
         <v>0</v>
       </c>
-      <c r="AY40" s="26">
+      <c r="AY40" s="28">
         <v>0</v>
       </c>
       <c r="AZ40" s="26">
@@ -52679,8 +52968,11 @@
       <c r="EX40" s="15">
         <v>0</v>
       </c>
+      <c r="EY40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -52828,7 +53120,7 @@
       <c r="AX41" s="28">
         <v>0</v>
       </c>
-      <c r="AY41" s="26">
+      <c r="AY41" s="28">
         <v>0</v>
       </c>
       <c r="AZ41" s="26">
@@ -53140,8 +53432,11 @@
       <c r="EX41" s="15">
         <v>0</v>
       </c>
+      <c r="EY41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -53289,7 +53584,7 @@
       <c r="AX42" s="28">
         <v>3</v>
       </c>
-      <c r="AY42" s="26">
+      <c r="AY42" s="28">
         <v>0</v>
       </c>
       <c r="AZ42" s="26">
@@ -53601,8 +53896,11 @@
       <c r="EX42" s="15">
         <v>32</v>
       </c>
+      <c r="EY42" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="43" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -53750,7 +54048,7 @@
       <c r="AX43" s="28">
         <v>37</v>
       </c>
-      <c r="AY43" s="26">
+      <c r="AY43" s="28">
         <v>24</v>
       </c>
       <c r="AZ43" s="26">
@@ -54062,8 +54360,11 @@
       <c r="EX43" s="28">
         <v>86</v>
       </c>
+      <c r="EY43" s="28">
+        <v>57</v>
+      </c>
     </row>
-    <row r="44" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -54211,7 +54512,7 @@
       <c r="AX44" s="28">
         <v>2</v>
       </c>
-      <c r="AY44" s="26">
+      <c r="AY44" s="28">
         <v>2</v>
       </c>
       <c r="AZ44" s="26">
@@ -54523,8 +54824,11 @@
       <c r="EX44" s="15">
         <v>9</v>
       </c>
+      <c r="EY44" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -54672,7 +54976,7 @@
       <c r="AX45" s="28">
         <v>0</v>
       </c>
-      <c r="AY45" s="26">
+      <c r="AY45" s="28">
         <v>4</v>
       </c>
       <c r="AZ45" s="26">
@@ -54984,8 +55288,11 @@
       <c r="EX45" s="15">
         <v>10</v>
       </c>
+      <c r="EY45" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="46" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -55133,7 +55440,7 @@
       <c r="AX46" s="28">
         <v>4</v>
       </c>
-      <c r="AY46" s="26">
+      <c r="AY46" s="28">
         <v>5</v>
       </c>
       <c r="AZ46" s="26">
@@ -55445,8 +55752,11 @@
       <c r="EX46" s="15">
         <v>18</v>
       </c>
+      <c r="EY46" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="47" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -55594,7 +55904,7 @@
       <c r="AX47" s="28">
         <v>0</v>
       </c>
-      <c r="AY47" s="26">
+      <c r="AY47" s="28">
         <v>3</v>
       </c>
       <c r="AZ47" s="26">
@@ -55906,8 +56216,11 @@
       <c r="EX47" s="15">
         <v>1</v>
       </c>
+      <c r="EY47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -56055,7 +56368,7 @@
       <c r="AX48" s="28">
         <v>9</v>
       </c>
-      <c r="AY48" s="26">
+      <c r="AY48" s="28">
         <v>8</v>
       </c>
       <c r="AZ48" s="26">
@@ -56367,8 +56680,11 @@
       <c r="EX48" s="15">
         <v>23</v>
       </c>
+      <c r="EY48" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="53" t="s">
         <v>83</v>
       </c>
@@ -56516,7 +56832,7 @@
       <c r="AX49" s="28">
         <v>11</v>
       </c>
-      <c r="AY49" s="26">
+      <c r="AY49" s="28">
         <v>9</v>
       </c>
       <c r="AZ49" s="26">
@@ -56828,8 +57144,11 @@
       <c r="EX49" s="15">
         <v>109</v>
       </c>
+      <c r="EY49" s="15">
+        <v>84</v>
+      </c>
     </row>
-    <row r="50" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="53"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -56975,7 +57294,7 @@
       <c r="AX50" s="28">
         <v>2</v>
       </c>
-      <c r="AY50" s="26">
+      <c r="AY50" s="28">
         <v>1</v>
       </c>
       <c r="AZ50" s="26">
@@ -57287,8 +57606,11 @@
       <c r="EX50" s="15">
         <v>131</v>
       </c>
+      <c r="EY50" s="15">
+        <v>80</v>
+      </c>
     </row>
-    <row r="51" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -57436,7 +57758,7 @@
       <c r="AX51" s="28">
         <v>3</v>
       </c>
-      <c r="AY51" s="26">
+      <c r="AY51" s="28">
         <v>3</v>
       </c>
       <c r="AZ51" s="26">
@@ -57748,8 +58070,11 @@
       <c r="EX51" s="15">
         <v>3</v>
       </c>
+      <c r="EY51" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="52" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -57897,7 +58222,7 @@
       <c r="AX52" s="28">
         <v>5</v>
       </c>
-      <c r="AY52" s="26">
+      <c r="AY52" s="28">
         <v>2</v>
       </c>
       <c r="AZ52" s="26">
@@ -58209,8 +58534,11 @@
       <c r="EX52" s="15">
         <v>18</v>
       </c>
+      <c r="EY52" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="53" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -58358,7 +58686,7 @@
       <c r="AX53" s="28">
         <v>10</v>
       </c>
-      <c r="AY53" s="26">
+      <c r="AY53" s="28">
         <v>12</v>
       </c>
       <c r="AZ53" s="26">
@@ -58670,8 +58998,11 @@
       <c r="EX53" s="15">
         <v>35</v>
       </c>
+      <c r="EY53" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="54" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -58819,7 +59150,7 @@
       <c r="AX54" s="28">
         <v>4</v>
       </c>
-      <c r="AY54" s="26">
+      <c r="AY54" s="28">
         <v>3</v>
       </c>
       <c r="AZ54" s="26">
@@ -59131,8 +59462,11 @@
       <c r="EX54" s="15">
         <v>28</v>
       </c>
+      <c r="EY54" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="55" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -59280,7 +59614,7 @@
       <c r="AX55" s="28">
         <v>8</v>
       </c>
-      <c r="AY55" s="26">
+      <c r="AY55" s="28">
         <v>6</v>
       </c>
       <c r="AZ55" s="26">
@@ -59592,8 +59926,11 @@
       <c r="EX55" s="15">
         <v>16</v>
       </c>
+      <c r="EY55" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="56" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -59741,7 +60078,7 @@
       <c r="AX56" s="28">
         <v>3</v>
       </c>
-      <c r="AY56" s="26">
+      <c r="AY56" s="28">
         <v>2</v>
       </c>
       <c r="AZ56" s="26">
@@ -60053,8 +60390,11 @@
       <c r="EX56" s="15">
         <v>6</v>
       </c>
+      <c r="EY56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -60202,7 +60542,7 @@
       <c r="AX57" s="28">
         <v>0</v>
       </c>
-      <c r="AY57" s="26">
+      <c r="AY57" s="28">
         <v>0</v>
       </c>
       <c r="AZ57" s="26">
@@ -60514,8 +60854,11 @@
       <c r="EX57" s="15">
         <v>0</v>
       </c>
+      <c r="EY57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="2:154" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:155" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -60708,7 +61051,7 @@
         <f t="shared" si="0"/>
         <v>1296</v>
       </c>
-      <c r="AY58" s="27">
+      <c r="AY58" s="43">
         <f t="shared" si="0"/>
         <v>1182</v>
       </c>
@@ -60984,7 +61327,7 @@
         <v>1266</v>
       </c>
       <c r="DP58" s="14">
-        <f t="shared" ref="DP58:EX58" si="8">SUM(DP6:DP57)</f>
+        <f t="shared" ref="DP58:EY58" si="8">SUM(DP6:DP57)</f>
         <v>1312</v>
       </c>
       <c r="DQ58" s="14">
@@ -61123,9 +61466,16 @@
         <f t="shared" si="8"/>
         <v>6237</v>
       </c>
+      <c r="EY58" s="14">
+        <f t="shared" si="8"/>
+        <v>5358</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="169">
+    <mergeCell ref="DD2:EY2"/>
+    <mergeCell ref="ER3:EY3"/>
+    <mergeCell ref="EY4:EY5"/>
     <mergeCell ref="EG4:EG5"/>
     <mergeCell ref="EE4:EE5"/>
     <mergeCell ref="DS4:DS5"/>
@@ -61171,8 +61521,6 @@
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="DX4:DX5"/>
-    <mergeCell ref="DZ4:DZ5"/>
-    <mergeCell ref="DP4:DP5"/>
     <mergeCell ref="DO4:DO5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AO4:AO5"/>
@@ -61180,6 +61528,13 @@
     <mergeCell ref="CE4:CE5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="EA4:EA5"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="DR4:DR5"/>
+    <mergeCell ref="DQ4:DQ5"/>
     <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="BD2:DC2"/>
     <mergeCell ref="AU4:AU5"/>
@@ -61201,6 +61556,9 @@
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="BY4:BY5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="D4:D5"/>
@@ -61220,11 +61578,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D3:AQ3"/>
     <mergeCell ref="X4:X5"/>
@@ -61246,11 +61599,6 @@
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="DR4:DR5"/>
-    <mergeCell ref="DQ4:DQ5"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -61270,8 +61618,6 @@
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BE4:BE5"/>
     <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="DD2:EX2"/>
-    <mergeCell ref="ER3:EX3"/>
     <mergeCell ref="EX4:EX5"/>
     <mergeCell ref="EW4:EW5"/>
     <mergeCell ref="EV4:EV5"/>
@@ -61294,6 +61640,8 @@
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="CN4:CN5"/>
     <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="DZ4:DZ5"/>
+    <mergeCell ref="DP4:DP5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
@@ -61306,7 +61654,7 @@
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH6:EX57">
+  <conditionalFormatting sqref="EH6:EY57">
     <cfRule type="containsBlanks" dxfId="4" priority="8">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
@@ -61346,7 +61694,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CX61"/>
+  <dimension ref="A1:CY61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -61357,11 +61705,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="102" width="10.875" style="1" customWidth="1"/>
-    <col min="103" max="16384" width="8.625" style="1"/>
+    <col min="54" max="103" width="10.875" style="1" customWidth="1"/>
+    <col min="104" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:103" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -61438,11 +61786,12 @@
       <c r="CU1" s="19"/>
       <c r="CV1" s="19"/>
       <c r="CW1" s="19"/>
-      <c r="CX1" s="19" t="s">
+      <c r="CX1" s="19"/>
+      <c r="CY1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:102" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:103" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="67" t="s">
@@ -61499,101 +61848,102 @@
       <c r="BA2" s="68"/>
       <c r="BB2" s="68"/>
       <c r="BC2" s="83"/>
-      <c r="BD2" s="73" t="s">
+      <c r="BD2" s="71" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="73"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="73"/>
-      <c r="BH2" s="73"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="73"/>
-      <c r="BM2" s="73"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="73"/>
-      <c r="BS2" s="73"/>
-      <c r="BT2" s="73"/>
-      <c r="BU2" s="73"/>
-      <c r="BV2" s="73"/>
-      <c r="BW2" s="73"/>
-      <c r="BX2" s="73"/>
-      <c r="BY2" s="73"/>
-      <c r="BZ2" s="73"/>
-      <c r="CA2" s="73"/>
-      <c r="CB2" s="73"/>
-      <c r="CC2" s="73"/>
-      <c r="CD2" s="73"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="73"/>
-      <c r="CG2" s="73"/>
-      <c r="CH2" s="73"/>
-      <c r="CI2" s="73"/>
-      <c r="CJ2" s="73"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="73"/>
-      <c r="CM2" s="73"/>
-      <c r="CN2" s="73"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="73"/>
-      <c r="CQ2" s="73"/>
-      <c r="CR2" s="73"/>
-      <c r="CS2" s="73"/>
-      <c r="CT2" s="73"/>
-      <c r="CU2" s="73"/>
-      <c r="CV2" s="73"/>
-      <c r="CW2" s="73"/>
-      <c r="CX2" s="73"/>
+      <c r="BE2" s="71"/>
+      <c r="BF2" s="71"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="71"/>
+      <c r="BI2" s="71"/>
+      <c r="BJ2" s="71"/>
+      <c r="BK2" s="71"/>
+      <c r="BL2" s="71"/>
+      <c r="BM2" s="71"/>
+      <c r="BN2" s="71"/>
+      <c r="BO2" s="71"/>
+      <c r="BP2" s="71"/>
+      <c r="BQ2" s="71"/>
+      <c r="BR2" s="71"/>
+      <c r="BS2" s="71"/>
+      <c r="BT2" s="71"/>
+      <c r="BU2" s="71"/>
+      <c r="BV2" s="71"/>
+      <c r="BW2" s="71"/>
+      <c r="BX2" s="71"/>
+      <c r="BY2" s="71"/>
+      <c r="BZ2" s="71"/>
+      <c r="CA2" s="71"/>
+      <c r="CB2" s="71"/>
+      <c r="CC2" s="71"/>
+      <c r="CD2" s="71"/>
+      <c r="CE2" s="71"/>
+      <c r="CF2" s="71"/>
+      <c r="CG2" s="71"/>
+      <c r="CH2" s="71"/>
+      <c r="CI2" s="71"/>
+      <c r="CJ2" s="71"/>
+      <c r="CK2" s="71"/>
+      <c r="CL2" s="71"/>
+      <c r="CM2" s="71"/>
+      <c r="CN2" s="71"/>
+      <c r="CO2" s="71"/>
+      <c r="CP2" s="71"/>
+      <c r="CQ2" s="71"/>
+      <c r="CR2" s="71"/>
+      <c r="CS2" s="71"/>
+      <c r="CT2" s="71"/>
+      <c r="CU2" s="71"/>
+      <c r="CV2" s="71"/>
+      <c r="CW2" s="71"/>
+      <c r="CX2" s="71"/>
+      <c r="CY2" s="71"/>
     </row>
-    <row r="3" spans="1:102" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:103" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="77"/>
+      <c r="AC3" s="77"/>
+      <c r="AD3" s="77"/>
+      <c r="AE3" s="77"/>
+      <c r="AF3" s="77"/>
+      <c r="AG3" s="77"/>
+      <c r="AH3" s="77"/>
+      <c r="AI3" s="77"/>
+      <c r="AJ3" s="77"/>
+      <c r="AK3" s="77"/>
+      <c r="AL3" s="77"/>
+      <c r="AM3" s="77"/>
+      <c r="AN3" s="77"/>
+      <c r="AO3" s="77"/>
+      <c r="AP3" s="77"/>
+      <c r="AQ3" s="77"/>
       <c r="AR3" s="64" t="s">
         <v>278</v>
       </c>
@@ -61659,8 +62009,9 @@
       <c r="CV3" s="64"/>
       <c r="CW3" s="64"/>
       <c r="CX3" s="64"/>
+      <c r="CY3" s="64"/>
     </row>
-    <row r="4" spans="1:102" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:103" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="62" t="s">
         <v>0</v>
       </c>
@@ -61964,8 +62315,11 @@
       <c r="CX4" s="69" t="s">
         <v>427</v>
       </c>
+      <c r="CY4" s="69" t="s">
+        <v>429</v>
+      </c>
     </row>
-    <row r="5" spans="1:102" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:103" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63"/>
       <c r="C5" s="56"/>
       <c r="D5" s="46"/>
@@ -62067,8 +62421,9 @@
       <c r="CV5" s="69"/>
       <c r="CW5" s="69"/>
       <c r="CX5" s="69"/>
+      <c r="CY5" s="69"/>
     </row>
-    <row r="6" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -62373,8 +62728,11 @@
       <c r="CX6" s="28">
         <v>17</v>
       </c>
+      <c r="CY6" s="28">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -62678,8 +63036,11 @@
       <c r="CX7" s="15">
         <v>1</v>
       </c>
+      <c r="CY7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -62983,8 +63344,11 @@
       <c r="CX8" s="28">
         <v>0</v>
       </c>
+      <c r="CY8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -63289,8 +63653,11 @@
       <c r="CX9" s="15">
         <v>22</v>
       </c>
+      <c r="CY9" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -63594,8 +63961,11 @@
       <c r="CX10" s="15">
         <v>0</v>
       </c>
+      <c r="CY10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -63899,8 +64269,11 @@
       <c r="CX11" s="15">
         <v>3</v>
       </c>
+      <c r="CY11" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -64204,8 +64577,11 @@
       <c r="CX12" s="15">
         <v>1</v>
       </c>
+      <c r="CY12" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -64509,8 +64885,11 @@
       <c r="CX13" s="15">
         <v>17</v>
       </c>
+      <c r="CY13" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="14" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -64814,8 +65193,11 @@
       <c r="CX14" s="15">
         <v>8</v>
       </c>
+      <c r="CY14" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -65119,8 +65501,11 @@
       <c r="CX15" s="15">
         <v>3</v>
       </c>
+      <c r="CY15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -65425,8 +65810,11 @@
       <c r="CX16" s="28">
         <v>2</v>
       </c>
+      <c r="CY16" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -65730,8 +66118,11 @@
       <c r="CX17" s="15">
         <v>46</v>
       </c>
+      <c r="CY17" s="15">
+        <v>40</v>
+      </c>
     </row>
-    <row r="18" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -66036,8 +66427,11 @@
       <c r="CX18" s="34">
         <v>307</v>
       </c>
+      <c r="CY18" s="34">
+        <v>261</v>
+      </c>
     </row>
-    <row r="19" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="84" t="s">
         <v>27</v>
@@ -66342,8 +66736,11 @@
       <c r="CX19" s="15">
         <v>28</v>
       </c>
+      <c r="CY19" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="20" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="88"/>
       <c r="C20" s="9" t="s">
@@ -66646,8 +67043,11 @@
       <c r="CX20" s="28">
         <v>59</v>
       </c>
+      <c r="CY20" s="28">
+        <v>56</v>
+      </c>
     </row>
-    <row r="21" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="85"/>
       <c r="C21" s="9" t="s">
@@ -66950,8 +67350,11 @@
       <c r="CX21" s="15">
         <v>11</v>
       </c>
+      <c r="CY21" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="22" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -67255,8 +67658,11 @@
       <c r="CX22" s="15">
         <v>1</v>
       </c>
+      <c r="CY22" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -67560,8 +67966,11 @@
       <c r="CX23" s="15">
         <v>0</v>
       </c>
+      <c r="CY23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -67865,8 +68274,11 @@
       <c r="CX24" s="15">
         <v>1</v>
       </c>
+      <c r="CY24" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -68170,8 +68582,11 @@
       <c r="CX25" s="15">
         <v>0</v>
       </c>
+      <c r="CY25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -68475,8 +68890,11 @@
       <c r="CX26" s="15">
         <v>8</v>
       </c>
+      <c r="CY26" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -68780,8 +69198,11 @@
       <c r="CX27" s="15">
         <v>1</v>
       </c>
+      <c r="CY27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -69085,8 +69506,11 @@
       <c r="CX28" s="15">
         <v>0</v>
       </c>
+      <c r="CY28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="86" t="s">
         <v>45</v>
       </c>
@@ -69390,8 +69814,11 @@
       <c r="CX29" s="15">
         <v>0</v>
       </c>
+      <c r="CY29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="87"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -69693,8 +70120,11 @@
       <c r="CX30" s="15">
         <v>7</v>
       </c>
+      <c r="CY30" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -69999,8 +70429,11 @@
       <c r="CX31" s="15">
         <v>32</v>
       </c>
+      <c r="CY31" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="32" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -70304,8 +70737,11 @@
       <c r="CX32" s="15">
         <v>0</v>
       </c>
+      <c r="CY32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -70609,8 +71045,11 @@
       <c r="CX33" s="15">
         <v>0</v>
       </c>
+      <c r="CY33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -70915,8 +71354,11 @@
       <c r="CX34" s="15">
         <v>21</v>
       </c>
+      <c r="CY34" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="35" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="84" t="s">
         <v>56</v>
@@ -71221,8 +71663,11 @@
       <c r="CX35" s="15">
         <v>59</v>
       </c>
+      <c r="CY35" s="15">
+        <v>57</v>
+      </c>
     </row>
-    <row r="36" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="85"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -71524,8 +71969,11 @@
       <c r="CX36" s="28">
         <v>11</v>
       </c>
+      <c r="CY36" s="28">
+        <v>4</v>
+      </c>
     </row>
-    <row r="37" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -71830,8 +72278,11 @@
       <c r="CX37" s="15">
         <v>7</v>
       </c>
+      <c r="CY37" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="38" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -72135,8 +72586,11 @@
       <c r="CX38" s="15">
         <v>8</v>
       </c>
+      <c r="CY38" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -72440,8 +72894,11 @@
       <c r="CX39" s="15">
         <v>2</v>
       </c>
+      <c r="CY39" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="40" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -72745,8 +73202,11 @@
       <c r="CX40" s="15">
         <v>0</v>
       </c>
+      <c r="CY40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -73050,8 +73510,11 @@
       <c r="CX41" s="15">
         <v>0</v>
       </c>
+      <c r="CY41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -73355,8 +73818,11 @@
       <c r="CX42" s="15">
         <v>4</v>
       </c>
+      <c r="CY42" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -73660,8 +74126,11 @@
       <c r="CX43" s="28">
         <v>36</v>
       </c>
+      <c r="CY43" s="28">
+        <v>32</v>
+      </c>
     </row>
-    <row r="44" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -73965,8 +74434,11 @@
       <c r="CX44" s="15">
         <v>0</v>
       </c>
+      <c r="CY44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -74270,8 +74742,11 @@
       <c r="CX45" s="15">
         <v>3</v>
       </c>
+      <c r="CY45" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -74575,8 +75050,11 @@
       <c r="CX46" s="15">
         <v>1</v>
       </c>
+      <c r="CY46" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -74880,8 +75358,11 @@
       <c r="CX47" s="15">
         <v>1</v>
       </c>
+      <c r="CY47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -75185,8 +75666,11 @@
       <c r="CX48" s="15">
         <v>9</v>
       </c>
+      <c r="CY48" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="84" t="s">
         <v>83</v>
@@ -75491,8 +75975,11 @@
       <c r="CX49" s="15">
         <v>4</v>
       </c>
+      <c r="CY49" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:102" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:103" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="85"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -75794,8 +76281,11 @@
       <c r="CX50" s="15">
         <v>14</v>
       </c>
+      <c r="CY50" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="51" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -76099,8 +76589,11 @@
       <c r="CX51" s="15">
         <v>1</v>
       </c>
+      <c r="CY51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -76404,8 +76897,11 @@
       <c r="CX52" s="15">
         <v>5</v>
       </c>
+      <c r="CY52" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -76709,8 +77205,11 @@
       <c r="CX53" s="15">
         <v>15</v>
       </c>
+      <c r="CY53" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="54" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -77014,8 +77513,11 @@
       <c r="CX54" s="15">
         <v>6</v>
       </c>
+      <c r="CY54" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -77319,8 +77821,11 @@
       <c r="CX55" s="15">
         <v>4</v>
       </c>
+      <c r="CY55" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -77624,8 +78129,11 @@
       <c r="CX56" s="15">
         <v>0</v>
       </c>
+      <c r="CY56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -77929,8 +78437,11 @@
       <c r="CX57" s="15">
         <v>0</v>
       </c>
+      <c r="CY57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -78200,7 +78711,7 @@
         <v>680</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CX58" si="8">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CY58" si="8">SUM(BR6:BR57)</f>
         <v>855</v>
       </c>
       <c r="BS58" s="14">
@@ -78331,8 +78842,12 @@
         <f t="shared" si="8"/>
         <v>786</v>
       </c>
+      <c r="CY58" s="14">
+        <f t="shared" si="8"/>
+        <v>644</v>
+      </c>
     </row>
-    <row r="59" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -78365,7 +78880,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -78398,7 +78913,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:102" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:103" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -78432,7 +78947,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="113">
+    <mergeCell ref="BD2:CY2"/>
+    <mergeCell ref="CR3:CY3"/>
+    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="BD3:CQ3"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -78440,10 +78958,20 @@
     <mergeCell ref="AL4:AL5"/>
     <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="BH4:BH5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="BI4:BI5"/>
+    <mergeCell ref="BK4:BK5"/>
+    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="BT4:BT5"/>
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AW4:AW5"/>
@@ -78464,22 +78992,6 @@
     <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="BH4:BH5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="CE4:CE5"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="BI4:BI5"/>
-    <mergeCell ref="BK4:BK5"/>
-    <mergeCell ref="BJ4:BJ5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="BT4:BT5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="BR4:BR5"/>
     <mergeCell ref="BG4:BG5"/>
@@ -78500,6 +79012,10 @@
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BV4:BV5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="P4:P5"/>
@@ -78521,8 +79037,6 @@
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B19:B21"/>
-    <mergeCell ref="BD2:CX2"/>
-    <mergeCell ref="CR3:CX3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
@@ -78545,9 +79059,11 @@
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="BN4:BN5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="CH6:CX57">
+  <conditionalFormatting sqref="CH6:CY57">
     <cfRule type="containsBlanks" dxfId="2" priority="1">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
@@ -78556,7 +79072,7 @@
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
-    <brk id="102" max="66" man="1"/>
+    <brk id="103" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -78573,7 +79089,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CX57</xm:sqref>
+          <xm:sqref>BP6:CY57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -78586,7 +79102,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DC61"/>
+  <dimension ref="A1:DD61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -78595,11 +79111,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="107" width="10.875" style="1" customWidth="1"/>
-    <col min="108" max="16384" width="8.625" style="1"/>
+    <col min="34" max="108" width="10.875" style="1" customWidth="1"/>
+    <col min="109" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:108" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -78676,12 +79192,13 @@
       <c r="CU1" s="19"/>
       <c r="CV1" s="19"/>
       <c r="CW1" s="19"/>
-      <c r="CX1" s="19" t="s">
+      <c r="CX1" s="19"/>
+      <c r="CY1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="CY1" s="19"/>
+      <c r="CZ1" s="19"/>
     </row>
-    <row r="2" spans="1:107" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:108" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="67" t="s">
@@ -78738,106 +79255,107 @@
       <c r="BA2" s="68"/>
       <c r="BB2" s="68"/>
       <c r="BC2" s="83"/>
-      <c r="BD2" s="73" t="s">
+      <c r="BD2" s="71" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="73"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="73"/>
-      <c r="BH2" s="73"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="73"/>
-      <c r="BM2" s="73"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="73"/>
-      <c r="BS2" s="73"/>
-      <c r="BT2" s="73"/>
-      <c r="BU2" s="73"/>
-      <c r="BV2" s="73"/>
-      <c r="BW2" s="73"/>
-      <c r="BX2" s="73"/>
-      <c r="BY2" s="73"/>
-      <c r="BZ2" s="73"/>
-      <c r="CA2" s="73"/>
-      <c r="CB2" s="73"/>
-      <c r="CC2" s="73"/>
-      <c r="CD2" s="73"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="73"/>
-      <c r="CG2" s="73"/>
-      <c r="CH2" s="73"/>
-      <c r="CI2" s="73"/>
-      <c r="CJ2" s="73"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="73"/>
-      <c r="CM2" s="73"/>
-      <c r="CN2" s="73"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="73"/>
-      <c r="CQ2" s="73"/>
-      <c r="CR2" s="73"/>
-      <c r="CS2" s="73"/>
-      <c r="CT2" s="73"/>
-      <c r="CU2" s="73"/>
-      <c r="CV2" s="73"/>
-      <c r="CW2" s="73"/>
-      <c r="CX2" s="73"/>
-      <c r="CY2" s="20"/>
+      <c r="BE2" s="71"/>
+      <c r="BF2" s="71"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="71"/>
+      <c r="BI2" s="71"/>
+      <c r="BJ2" s="71"/>
+      <c r="BK2" s="71"/>
+      <c r="BL2" s="71"/>
+      <c r="BM2" s="71"/>
+      <c r="BN2" s="71"/>
+      <c r="BO2" s="71"/>
+      <c r="BP2" s="71"/>
+      <c r="BQ2" s="71"/>
+      <c r="BR2" s="71"/>
+      <c r="BS2" s="71"/>
+      <c r="BT2" s="71"/>
+      <c r="BU2" s="71"/>
+      <c r="BV2" s="71"/>
+      <c r="BW2" s="71"/>
+      <c r="BX2" s="71"/>
+      <c r="BY2" s="71"/>
+      <c r="BZ2" s="71"/>
+      <c r="CA2" s="71"/>
+      <c r="CB2" s="71"/>
+      <c r="CC2" s="71"/>
+      <c r="CD2" s="71"/>
+      <c r="CE2" s="71"/>
+      <c r="CF2" s="71"/>
+      <c r="CG2" s="71"/>
+      <c r="CH2" s="71"/>
+      <c r="CI2" s="71"/>
+      <c r="CJ2" s="71"/>
+      <c r="CK2" s="71"/>
+      <c r="CL2" s="71"/>
+      <c r="CM2" s="71"/>
+      <c r="CN2" s="71"/>
+      <c r="CO2" s="71"/>
+      <c r="CP2" s="71"/>
+      <c r="CQ2" s="71"/>
+      <c r="CR2" s="71"/>
+      <c r="CS2" s="71"/>
+      <c r="CT2" s="71"/>
+      <c r="CU2" s="71"/>
+      <c r="CV2" s="71"/>
+      <c r="CW2" s="71"/>
+      <c r="CX2" s="71"/>
+      <c r="CY2" s="71"/>
       <c r="CZ2" s="20"/>
       <c r="DA2" s="20"/>
       <c r="DB2" s="20"/>
       <c r="DC2" s="20"/>
+      <c r="DD2" s="20"/>
     </row>
-    <row r="3" spans="1:107" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:108" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="77"/>
+      <c r="AC3" s="77"/>
+      <c r="AD3" s="77"/>
+      <c r="AE3" s="77"/>
+      <c r="AF3" s="77"/>
+      <c r="AG3" s="77"/>
+      <c r="AH3" s="77"/>
+      <c r="AI3" s="77"/>
+      <c r="AJ3" s="77"/>
+      <c r="AK3" s="77"/>
+      <c r="AL3" s="77"/>
+      <c r="AM3" s="77"/>
+      <c r="AN3" s="77"/>
+      <c r="AO3" s="77"/>
+      <c r="AP3" s="77"/>
+      <c r="AQ3" s="77"/>
       <c r="AR3" s="64" t="s">
         <v>278</v>
       </c>
@@ -78903,13 +79421,14 @@
       <c r="CV3" s="64"/>
       <c r="CW3" s="64"/>
       <c r="CX3" s="64"/>
-      <c r="CY3" s="21"/>
+      <c r="CY3" s="64"/>
       <c r="CZ3" s="21"/>
       <c r="DA3" s="21"/>
       <c r="DB3" s="21"/>
       <c r="DC3" s="21"/>
+      <c r="DD3" s="21"/>
     </row>
-    <row r="4" spans="1:107" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:108" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="62" t="s">
         <v>0</v>
       </c>
@@ -79213,13 +79732,16 @@
       <c r="CX4" s="69" t="s">
         <v>427</v>
       </c>
-      <c r="CY4" s="89"/>
+      <c r="CY4" s="69" t="s">
+        <v>429</v>
+      </c>
       <c r="CZ4" s="89"/>
       <c r="DA4" s="89"/>
       <c r="DB4" s="89"/>
       <c r="DC4" s="89"/>
+      <c r="DD4" s="89"/>
     </row>
-    <row r="5" spans="1:107" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:108" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63"/>
       <c r="C5" s="56"/>
       <c r="D5" s="46"/>
@@ -79321,13 +79843,14 @@
       <c r="CV5" s="69"/>
       <c r="CW5" s="69"/>
       <c r="CX5" s="69"/>
-      <c r="CY5" s="89"/>
+      <c r="CY5" s="69"/>
       <c r="CZ5" s="89"/>
       <c r="DA5" s="89"/>
       <c r="DB5" s="89"/>
       <c r="DC5" s="89"/>
+      <c r="DD5" s="89"/>
     </row>
-    <row r="6" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -79632,13 +80155,16 @@
       <c r="CX6" s="28">
         <v>108</v>
       </c>
-      <c r="CY6" s="22"/>
+      <c r="CY6" s="28">
+        <v>95</v>
+      </c>
       <c r="CZ6" s="22"/>
       <c r="DA6" s="22"/>
       <c r="DB6" s="22"/>
       <c r="DC6" s="22"/>
+      <c r="DD6" s="22"/>
     </row>
-    <row r="7" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -79942,13 +80468,16 @@
       <c r="CX7" s="15">
         <v>2</v>
       </c>
-      <c r="CY7" s="23"/>
+      <c r="CY7" s="15">
+        <v>1</v>
+      </c>
       <c r="CZ7" s="23"/>
       <c r="DA7" s="23"/>
       <c r="DB7" s="23"/>
       <c r="DC7" s="23"/>
+      <c r="DD7" s="23"/>
     </row>
-    <row r="8" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -80252,13 +80781,16 @@
       <c r="CX8" s="28">
         <v>20</v>
       </c>
-      <c r="CY8" s="23"/>
+      <c r="CY8" s="28">
+        <v>27</v>
+      </c>
       <c r="CZ8" s="23"/>
       <c r="DA8" s="23"/>
       <c r="DB8" s="23"/>
       <c r="DC8" s="23"/>
+      <c r="DD8" s="23"/>
     </row>
-    <row r="9" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -80563,13 +81095,16 @@
       <c r="CX9" s="15">
         <v>96</v>
       </c>
-      <c r="CY9" s="23"/>
+      <c r="CY9" s="15">
+        <v>96</v>
+      </c>
       <c r="CZ9" s="23"/>
       <c r="DA9" s="23"/>
       <c r="DB9" s="23"/>
       <c r="DC9" s="23"/>
+      <c r="DD9" s="23"/>
     </row>
-    <row r="10" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -80873,13 +81408,16 @@
       <c r="CX10" s="15">
         <v>2</v>
       </c>
-      <c r="CY10" s="23"/>
+      <c r="CY10" s="15">
+        <v>1</v>
+      </c>
       <c r="CZ10" s="23"/>
       <c r="DA10" s="23"/>
       <c r="DB10" s="23"/>
       <c r="DC10" s="23"/>
+      <c r="DD10" s="23"/>
     </row>
-    <row r="11" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -81183,13 +81721,16 @@
       <c r="CX11" s="15">
         <v>8</v>
       </c>
-      <c r="CY11" s="23"/>
+      <c r="CY11" s="15">
+        <v>11</v>
+      </c>
       <c r="CZ11" s="23"/>
       <c r="DA11" s="23"/>
       <c r="DB11" s="23"/>
       <c r="DC11" s="23"/>
+      <c r="DD11" s="23"/>
     </row>
-    <row r="12" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -81493,13 +82034,16 @@
       <c r="CX12" s="15">
         <v>12</v>
       </c>
-      <c r="CY12" s="23"/>
+      <c r="CY12" s="15">
+        <v>6</v>
+      </c>
       <c r="CZ12" s="23"/>
       <c r="DA12" s="23"/>
       <c r="DB12" s="23"/>
       <c r="DC12" s="23"/>
+      <c r="DD12" s="23"/>
     </row>
-    <row r="13" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -81803,13 +82347,16 @@
       <c r="CX13" s="15">
         <v>25</v>
       </c>
-      <c r="CY13" s="22"/>
+      <c r="CY13" s="15">
+        <v>16</v>
+      </c>
       <c r="CZ13" s="22"/>
       <c r="DA13" s="22"/>
       <c r="DB13" s="22"/>
       <c r="DC13" s="22"/>
+      <c r="DD13" s="22"/>
     </row>
-    <row r="14" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -82113,13 +82660,16 @@
       <c r="CX14" s="15">
         <v>18</v>
       </c>
-      <c r="CY14" s="23"/>
+      <c r="CY14" s="15">
+        <v>8</v>
+      </c>
       <c r="CZ14" s="23"/>
       <c r="DA14" s="23"/>
       <c r="DB14" s="23"/>
       <c r="DC14" s="23"/>
+      <c r="DD14" s="23"/>
     </row>
-    <row r="15" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -82423,13 +82973,16 @@
       <c r="CX15" s="15">
         <v>3</v>
       </c>
-      <c r="CY15" s="23"/>
+      <c r="CY15" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ15" s="23"/>
       <c r="DA15" s="23"/>
       <c r="DB15" s="23"/>
       <c r="DC15" s="23"/>
+      <c r="DD15" s="23"/>
     </row>
-    <row r="16" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -82734,13 +83287,16 @@
       <c r="CX16" s="28">
         <v>119</v>
       </c>
-      <c r="CY16" s="22"/>
+      <c r="CY16" s="28">
+        <v>123</v>
+      </c>
       <c r="CZ16" s="22"/>
       <c r="DA16" s="22"/>
       <c r="DB16" s="22"/>
       <c r="DC16" s="22"/>
+      <c r="DD16" s="22"/>
     </row>
-    <row r="17" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -83044,13 +83600,16 @@
       <c r="CX17" s="15">
         <v>127</v>
       </c>
-      <c r="CY17" s="22"/>
+      <c r="CY17" s="15">
+        <v>128</v>
+      </c>
       <c r="CZ17" s="22"/>
       <c r="DA17" s="22"/>
       <c r="DB17" s="22"/>
       <c r="DC17" s="22"/>
+      <c r="DD17" s="22"/>
     </row>
-    <row r="18" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -83355,13 +83914,16 @@
       <c r="CX18" s="34">
         <v>1705</v>
       </c>
-      <c r="CY18" s="22"/>
+      <c r="CY18" s="34">
+        <v>1455</v>
+      </c>
       <c r="CZ18" s="22"/>
       <c r="DA18" s="22"/>
       <c r="DB18" s="22"/>
       <c r="DC18" s="22"/>
+      <c r="DD18" s="22"/>
     </row>
-    <row r="19" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="84" t="s">
         <v>27</v>
@@ -83666,13 +84228,16 @@
       <c r="CX19" s="15">
         <v>37</v>
       </c>
-      <c r="CY19" s="22"/>
+      <c r="CY19" s="15">
+        <v>43</v>
+      </c>
       <c r="CZ19" s="22"/>
       <c r="DA19" s="22"/>
       <c r="DB19" s="22"/>
       <c r="DC19" s="22"/>
+      <c r="DD19" s="22"/>
     </row>
-    <row r="20" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="88"/>
       <c r="C20" s="9" t="s">
@@ -83975,13 +84540,16 @@
       <c r="CX20" s="28">
         <v>98</v>
       </c>
-      <c r="CY20" s="22"/>
+      <c r="CY20" s="28">
+        <v>86</v>
+      </c>
       <c r="CZ20" s="22"/>
       <c r="DA20" s="22"/>
       <c r="DB20" s="22"/>
       <c r="DC20" s="22"/>
+      <c r="DD20" s="22"/>
     </row>
-    <row r="21" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="85"/>
       <c r="C21" s="9" t="s">
@@ -84284,13 +84852,16 @@
       <c r="CX21" s="15">
         <v>23</v>
       </c>
-      <c r="CY21" s="22"/>
+      <c r="CY21" s="15">
+        <v>21</v>
+      </c>
       <c r="CZ21" s="22"/>
       <c r="DA21" s="22"/>
       <c r="DB21" s="22"/>
       <c r="DC21" s="22"/>
+      <c r="DD21" s="22"/>
     </row>
-    <row r="22" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -84594,13 +85165,16 @@
       <c r="CX22" s="15">
         <v>2</v>
       </c>
-      <c r="CY22" s="23"/>
+      <c r="CY22" s="15">
+        <v>4</v>
+      </c>
       <c r="CZ22" s="23"/>
       <c r="DA22" s="23"/>
       <c r="DB22" s="23"/>
       <c r="DC22" s="23"/>
+      <c r="DD22" s="23"/>
     </row>
-    <row r="23" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -84904,13 +85478,16 @@
       <c r="CX23" s="15">
         <v>2</v>
       </c>
-      <c r="CY23" s="23"/>
+      <c r="CY23" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ23" s="23"/>
       <c r="DA23" s="23"/>
       <c r="DB23" s="23"/>
       <c r="DC23" s="23"/>
+      <c r="DD23" s="23"/>
     </row>
-    <row r="24" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -85214,13 +85791,16 @@
       <c r="CX24" s="15">
         <v>11</v>
       </c>
-      <c r="CY24" s="22"/>
+      <c r="CY24" s="15">
+        <v>12</v>
+      </c>
       <c r="CZ24" s="22"/>
       <c r="DA24" s="22"/>
       <c r="DB24" s="22"/>
       <c r="DC24" s="22"/>
+      <c r="DD24" s="22"/>
     </row>
-    <row r="25" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -85524,13 +86104,16 @@
       <c r="CX25" s="15">
         <v>1</v>
       </c>
-      <c r="CY25" s="23"/>
+      <c r="CY25" s="15">
+        <v>2</v>
+      </c>
       <c r="CZ25" s="23"/>
       <c r="DA25" s="23"/>
       <c r="DB25" s="23"/>
       <c r="DC25" s="23"/>
+      <c r="DD25" s="23"/>
     </row>
-    <row r="26" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -85834,13 +86417,16 @@
       <c r="CX26" s="15">
         <v>9</v>
       </c>
-      <c r="CY26" s="23"/>
+      <c r="CY26" s="15">
+        <v>12</v>
+      </c>
       <c r="CZ26" s="23"/>
       <c r="DA26" s="23"/>
       <c r="DB26" s="23"/>
       <c r="DC26" s="23"/>
+      <c r="DD26" s="23"/>
     </row>
-    <row r="27" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -86144,13 +86730,16 @@
       <c r="CX27" s="15">
         <v>2</v>
       </c>
-      <c r="CY27" s="23"/>
+      <c r="CY27" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ27" s="23"/>
       <c r="DA27" s="23"/>
       <c r="DB27" s="23"/>
       <c r="DC27" s="23"/>
+      <c r="DD27" s="23"/>
     </row>
-    <row r="28" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -86454,13 +87043,16 @@
       <c r="CX28" s="15">
         <v>2</v>
       </c>
-      <c r="CY28" s="22"/>
+      <c r="CY28" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ28" s="22"/>
       <c r="DA28" s="22"/>
       <c r="DB28" s="22"/>
       <c r="DC28" s="22"/>
+      <c r="DD28" s="22"/>
     </row>
-    <row r="29" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="86" t="s">
         <v>45</v>
       </c>
@@ -86764,13 +87356,16 @@
       <c r="CX29" s="15">
         <v>0</v>
       </c>
-      <c r="CY29" s="23"/>
+      <c r="CY29" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ29" s="23"/>
       <c r="DA29" s="23"/>
       <c r="DB29" s="23"/>
       <c r="DC29" s="23"/>
+      <c r="DD29" s="23"/>
     </row>
-    <row r="30" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="87"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -87072,13 +87667,16 @@
       <c r="CX30" s="15">
         <v>15</v>
       </c>
-      <c r="CY30" s="23"/>
+      <c r="CY30" s="15">
+        <v>16</v>
+      </c>
       <c r="CZ30" s="23"/>
       <c r="DA30" s="23"/>
       <c r="DB30" s="23"/>
       <c r="DC30" s="23"/>
+      <c r="DD30" s="23"/>
     </row>
-    <row r="31" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -87383,13 +87981,16 @@
       <c r="CX31" s="15">
         <v>77</v>
       </c>
-      <c r="CY31" s="22"/>
+      <c r="CY31" s="15">
+        <v>44</v>
+      </c>
       <c r="CZ31" s="22"/>
       <c r="DA31" s="22"/>
       <c r="DB31" s="22"/>
       <c r="DC31" s="22"/>
+      <c r="DD31" s="22"/>
     </row>
-    <row r="32" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -87693,13 +88294,16 @@
       <c r="CX32" s="15">
         <v>1</v>
       </c>
-      <c r="CY32" s="23"/>
+      <c r="CY32" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ32" s="23"/>
       <c r="DA32" s="23"/>
       <c r="DB32" s="23"/>
       <c r="DC32" s="23"/>
+      <c r="DD32" s="23"/>
     </row>
-    <row r="33" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -88003,13 +88607,16 @@
       <c r="CX33" s="15">
         <v>0</v>
       </c>
-      <c r="CY33" s="23"/>
+      <c r="CY33" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ33" s="23"/>
       <c r="DA33" s="23"/>
       <c r="DB33" s="23"/>
       <c r="DC33" s="23"/>
+      <c r="DD33" s="23"/>
     </row>
-    <row r="34" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -88314,13 +88921,16 @@
       <c r="CX34" s="15">
         <v>110</v>
       </c>
-      <c r="CY34" s="22"/>
+      <c r="CY34" s="15">
+        <v>61</v>
+      </c>
       <c r="CZ34" s="22"/>
       <c r="DA34" s="22"/>
       <c r="DB34" s="22"/>
       <c r="DC34" s="22"/>
+      <c r="DD34" s="22"/>
     </row>
-    <row r="35" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="84" t="s">
         <v>56</v>
@@ -88625,13 +89235,16 @@
       <c r="CX35" s="15">
         <v>260</v>
       </c>
-      <c r="CY35" s="22"/>
+      <c r="CY35" s="15">
+        <v>261</v>
+      </c>
       <c r="CZ35" s="22"/>
       <c r="DA35" s="22"/>
       <c r="DB35" s="22"/>
       <c r="DC35" s="22"/>
+      <c r="DD35" s="22"/>
     </row>
-    <row r="36" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="85"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -88933,13 +89546,16 @@
       <c r="CX36" s="28">
         <v>26</v>
       </c>
-      <c r="CY36" s="22"/>
+      <c r="CY36" s="28">
+        <v>32</v>
+      </c>
       <c r="CZ36" s="22"/>
       <c r="DA36" s="22"/>
       <c r="DB36" s="22"/>
       <c r="DC36" s="22"/>
+      <c r="DD36" s="22"/>
     </row>
-    <row r="37" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -89244,13 +89860,16 @@
       <c r="CX37" s="15">
         <v>45</v>
       </c>
-      <c r="CY37" s="22"/>
+      <c r="CY37" s="15">
+        <v>37</v>
+      </c>
       <c r="CZ37" s="22"/>
       <c r="DA37" s="22"/>
       <c r="DB37" s="22"/>
       <c r="DC37" s="22"/>
+      <c r="DD37" s="22"/>
     </row>
-    <row r="38" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -89554,13 +90173,16 @@
       <c r="CX38" s="15">
         <v>10</v>
       </c>
-      <c r="CY38" s="23"/>
+      <c r="CY38" s="15">
+        <v>6</v>
+      </c>
       <c r="CZ38" s="23"/>
       <c r="DA38" s="23"/>
       <c r="DB38" s="23"/>
       <c r="DC38" s="23"/>
+      <c r="DD38" s="23"/>
     </row>
-    <row r="39" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -89864,13 +90486,16 @@
       <c r="CX39" s="15">
         <v>6</v>
       </c>
-      <c r="CY39" s="23"/>
+      <c r="CY39" s="15">
+        <v>9</v>
+      </c>
       <c r="CZ39" s="23"/>
       <c r="DA39" s="23"/>
       <c r="DB39" s="23"/>
       <c r="DC39" s="23"/>
+      <c r="DD39" s="23"/>
     </row>
-    <row r="40" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -90174,13 +90799,16 @@
       <c r="CX40" s="15">
         <v>0</v>
       </c>
-      <c r="CY40" s="23"/>
+      <c r="CY40" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ40" s="23"/>
       <c r="DA40" s="23"/>
       <c r="DB40" s="23"/>
       <c r="DC40" s="23"/>
+      <c r="DD40" s="23"/>
     </row>
-    <row r="41" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -90484,13 +91112,16 @@
       <c r="CX41" s="15">
         <v>0</v>
       </c>
-      <c r="CY41" s="23"/>
+      <c r="CY41" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ41" s="23"/>
       <c r="DA41" s="23"/>
       <c r="DB41" s="23"/>
       <c r="DC41" s="23"/>
+      <c r="DD41" s="23"/>
     </row>
-    <row r="42" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -90794,13 +91425,16 @@
       <c r="CX42" s="15">
         <v>12</v>
       </c>
-      <c r="CY42" s="23"/>
+      <c r="CY42" s="15">
+        <v>5</v>
+      </c>
       <c r="CZ42" s="23"/>
       <c r="DA42" s="23"/>
       <c r="DB42" s="23"/>
       <c r="DC42" s="23"/>
+      <c r="DD42" s="23"/>
     </row>
-    <row r="43" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -91104,13 +91738,16 @@
       <c r="CX43" s="28">
         <v>42</v>
       </c>
-      <c r="CY43" s="23"/>
+      <c r="CY43" s="28">
+        <v>34</v>
+      </c>
       <c r="CZ43" s="23"/>
       <c r="DA43" s="23"/>
       <c r="DB43" s="23"/>
       <c r="DC43" s="23"/>
+      <c r="DD43" s="23"/>
     </row>
-    <row r="44" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -91414,13 +92051,16 @@
       <c r="CX44" s="15">
         <v>4</v>
       </c>
-      <c r="CY44" s="23"/>
+      <c r="CY44" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ44" s="23"/>
       <c r="DA44" s="23"/>
       <c r="DB44" s="23"/>
       <c r="DC44" s="23"/>
+      <c r="DD44" s="23"/>
     </row>
-    <row r="45" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -91724,13 +92364,16 @@
       <c r="CX45" s="15">
         <v>12</v>
       </c>
-      <c r="CY45" s="22"/>
+      <c r="CY45" s="15">
+        <v>25</v>
+      </c>
       <c r="CZ45" s="22"/>
       <c r="DA45" s="22"/>
       <c r="DB45" s="22"/>
       <c r="DC45" s="22"/>
+      <c r="DD45" s="22"/>
     </row>
-    <row r="46" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -92034,13 +92677,16 @@
       <c r="CX46" s="15">
         <v>16</v>
       </c>
-      <c r="CY46" s="23"/>
+      <c r="CY46" s="15">
+        <v>12</v>
+      </c>
       <c r="CZ46" s="23"/>
       <c r="DA46" s="23"/>
       <c r="DB46" s="23"/>
       <c r="DC46" s="23"/>
+      <c r="DD46" s="23"/>
     </row>
-    <row r="47" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -92344,13 +92990,16 @@
       <c r="CX47" s="15">
         <v>2</v>
       </c>
-      <c r="CY47" s="23"/>
+      <c r="CY47" s="15">
+        <v>0</v>
+      </c>
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
       <c r="DB47" s="23"/>
       <c r="DC47" s="23"/>
+      <c r="DD47" s="23"/>
     </row>
-    <row r="48" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -92654,13 +93303,16 @@
       <c r="CX48" s="15">
         <v>10</v>
       </c>
-      <c r="CY48" s="23"/>
+      <c r="CY48" s="15">
+        <v>6</v>
+      </c>
       <c r="CZ48" s="23"/>
       <c r="DA48" s="23"/>
       <c r="DB48" s="23"/>
       <c r="DC48" s="23"/>
+      <c r="DD48" s="23"/>
     </row>
-    <row r="49" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="84" t="s">
         <v>83</v>
@@ -92965,13 +93617,16 @@
       <c r="CX49" s="15">
         <v>99</v>
       </c>
-      <c r="CY49" s="22"/>
+      <c r="CY49" s="15">
+        <v>46</v>
+      </c>
       <c r="CZ49" s="22"/>
       <c r="DA49" s="22"/>
       <c r="DB49" s="22"/>
       <c r="DC49" s="22"/>
+      <c r="DD49" s="22"/>
     </row>
-    <row r="50" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="85"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -93273,13 +93928,16 @@
       <c r="CX50" s="15">
         <v>26</v>
       </c>
-      <c r="CY50" s="22"/>
+      <c r="CY50" s="15">
+        <v>17</v>
+      </c>
       <c r="CZ50" s="22"/>
       <c r="DA50" s="22"/>
       <c r="DB50" s="22"/>
       <c r="DC50" s="22"/>
+      <c r="DD50" s="22"/>
     </row>
-    <row r="51" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -93583,13 +94241,16 @@
       <c r="CX51" s="15">
         <v>3</v>
       </c>
-      <c r="CY51" s="23"/>
+      <c r="CY51" s="15">
+        <v>4</v>
+      </c>
       <c r="CZ51" s="23"/>
       <c r="DA51" s="23"/>
       <c r="DB51" s="23"/>
       <c r="DC51" s="23"/>
+      <c r="DD51" s="23"/>
     </row>
-    <row r="52" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -93893,13 +94554,16 @@
       <c r="CX52" s="15">
         <v>12</v>
       </c>
-      <c r="CY52" s="23"/>
+      <c r="CY52" s="15">
+        <v>13</v>
+      </c>
       <c r="CZ52" s="23"/>
       <c r="DA52" s="23"/>
       <c r="DB52" s="23"/>
       <c r="DC52" s="23"/>
+      <c r="DD52" s="23"/>
     </row>
-    <row r="53" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -94203,13 +94867,16 @@
       <c r="CX53" s="15">
         <v>53</v>
       </c>
-      <c r="CY53" s="23"/>
+      <c r="CY53" s="15">
+        <v>34</v>
+      </c>
       <c r="CZ53" s="23"/>
       <c r="DA53" s="23"/>
       <c r="DB53" s="23"/>
       <c r="DC53" s="23"/>
+      <c r="DD53" s="23"/>
     </row>
-    <row r="54" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -94513,13 +95180,16 @@
       <c r="CX54" s="15">
         <v>10</v>
       </c>
-      <c r="CY54" s="23"/>
+      <c r="CY54" s="15">
+        <v>2</v>
+      </c>
       <c r="CZ54" s="23"/>
       <c r="DA54" s="23"/>
       <c r="DB54" s="23"/>
       <c r="DC54" s="23"/>
+      <c r="DD54" s="23"/>
     </row>
-    <row r="55" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -94823,13 +95493,16 @@
       <c r="CX55" s="15">
         <v>12</v>
       </c>
-      <c r="CY55" s="23"/>
+      <c r="CY55" s="15">
+        <v>15</v>
+      </c>
       <c r="CZ55" s="23"/>
       <c r="DA55" s="23"/>
       <c r="DB55" s="23"/>
       <c r="DC55" s="23"/>
+      <c r="DD55" s="23"/>
     </row>
-    <row r="56" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -95133,13 +95806,16 @@
       <c r="CX56" s="15">
         <v>1</v>
       </c>
-      <c r="CY56" s="23"/>
+      <c r="CY56" s="15">
+        <v>2</v>
+      </c>
       <c r="CZ56" s="23"/>
       <c r="DA56" s="23"/>
       <c r="DB56" s="23"/>
       <c r="DC56" s="23"/>
+      <c r="DD56" s="23"/>
     </row>
-    <row r="57" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -95443,13 +96119,16 @@
       <c r="CX57" s="15">
         <v>0</v>
       </c>
-      <c r="CY57" s="23"/>
+      <c r="CY57" s="15">
+        <v>2</v>
+      </c>
       <c r="CZ57" s="23"/>
       <c r="DA57" s="23"/>
       <c r="DB57" s="23"/>
       <c r="DC57" s="23"/>
+      <c r="DD57" s="23"/>
     </row>
-    <row r="58" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -95719,7 +96398,7 @@
         <v>2132</v>
       </c>
       <c r="BR58" s="14">
-        <f t="shared" ref="BR58:CX58" si="4">SUM(BR6:BR57)</f>
+        <f t="shared" ref="BR58:CY58" si="4">SUM(BR6:BR57)</f>
         <v>2032</v>
       </c>
       <c r="BS58" s="14">
@@ -95850,13 +96529,17 @@
         <f t="shared" si="4"/>
         <v>3296</v>
       </c>
-      <c r="CY58" s="24"/>
+      <c r="CY58" s="14">
+        <f t="shared" si="4"/>
+        <v>2830</v>
+      </c>
       <c r="CZ58" s="24"/>
       <c r="DA58" s="24"/>
       <c r="DB58" s="24"/>
       <c r="DC58" s="24"/>
+      <c r="DD58" s="24"/>
     </row>
-    <row r="59" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -95889,7 +96572,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -95922,7 +96605,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -95956,7 +96639,10 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="118">
+    <mergeCell ref="BD2:CY2"/>
+    <mergeCell ref="CR3:CY3"/>
+    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CL4:CL5"/>
@@ -96026,8 +96712,6 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="CG4:CG5"/>
     <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="Z4:Z5"/>
@@ -96050,30 +96734,30 @@
     <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="BD2:CX2"/>
-    <mergeCell ref="CR3:CX3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
     <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="DD4:DD5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="CF4:CF5"/>
+    <mergeCell ref="CG4:CG5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -96097,7 +96781,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CX57</xm:sqref>
+          <xm:sqref>BP6:CY57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050314-2\ＪＯＢ050314-2\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050322-1\ＪＯＢ050322-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="10680"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DA$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DA$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FA$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FA$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DB$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DB$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FB$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FB$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="437">
   <si>
     <t>都道府県</t>
   </si>
@@ -4632,6 +4632,18 @@
 【3月第2週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>3/13(月)～
+3/19(日)分
+【3月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3/14(月)～
+3/20(日)分
+【3月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4995,7 +5007,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5218,6 +5230,9 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5267,7 +5282,21 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5344,6 +5373,21 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -9498,8 +9542,8 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="157" width="10.875" style="1" customWidth="1"/>
-    <col min="158" max="16384" width="8.625" style="1"/>
+    <col min="106" max="158" width="10.875" style="1" customWidth="1"/>
+    <col min="159" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:158" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
@@ -9586,7 +9630,8 @@
       <c r="EX1" s="19"/>
       <c r="EY1" s="19"/>
       <c r="EZ1" s="19"/>
-      <c r="FA1" s="19" t="s">
+      <c r="FA1" s="19"/>
+      <c r="FB1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
@@ -9753,6 +9798,7 @@
       <c r="EY2" s="73"/>
       <c r="EZ2" s="73"/>
       <c r="FA2" s="73"/>
+      <c r="FB2" s="73"/>
     </row>
     <row r="3" spans="1:158" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
@@ -9923,6 +9969,7 @@
       <c r="EY3" s="45"/>
       <c r="EZ3" s="45"/>
       <c r="FA3" s="45"/>
+      <c r="FB3" s="45"/>
     </row>
     <row r="4" spans="1:158" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
@@ -10392,6 +10439,9 @@
       </c>
       <c r="FA4" s="44" t="s">
         <v>433</v>
+      </c>
+      <c r="FB4" s="44" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:158" ht="54" customHeight="1" x14ac:dyDescent="0.4">
@@ -10551,6 +10601,7 @@
       <c r="EY5" s="44"/>
       <c r="EZ5" s="44"/>
       <c r="FA5" s="44"/>
+      <c r="FB5" s="44"/>
     </row>
     <row r="6" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
@@ -11022,7 +11073,9 @@
       <c r="FA6" s="28">
         <v>106</v>
       </c>
-      <c r="FB6" s="1"/>
+      <c r="FB6" s="28">
+        <v>117</v>
+      </c>
     </row>
     <row r="7" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
@@ -11492,6 +11545,9 @@
       </c>
       <c r="FA7" s="15">
         <v>0</v>
+      </c>
+      <c r="FB7" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -11962,6 +12018,9 @@
       </c>
       <c r="FA8" s="28">
         <v>20</v>
+      </c>
+      <c r="FB8" s="28">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -12434,6 +12493,9 @@
       <c r="FA9" s="15">
         <v>83</v>
       </c>
+      <c r="FB9" s="15">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
@@ -12902,6 +12964,9 @@
       <c r="FA10" s="15">
         <v>0</v>
       </c>
+      <c r="FB10" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
@@ -13372,6 +13437,9 @@
       <c r="FA11" s="15">
         <v>7</v>
       </c>
+      <c r="FB11" s="15">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
@@ -13842,6 +13910,9 @@
       <c r="FA12" s="15">
         <v>10</v>
       </c>
+      <c r="FB12" s="15">
+        <v>6</v>
+      </c>
     </row>
     <row r="13" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
@@ -14312,7 +14383,9 @@
       <c r="FA13" s="15">
         <v>19</v>
       </c>
-      <c r="FB13" s="1"/>
+      <c r="FB13" s="15">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
@@ -14783,6 +14856,9 @@
       <c r="FA14" s="15">
         <v>14</v>
       </c>
+      <c r="FB14" s="15">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
@@ -15252,6 +15328,9 @@
       </c>
       <c r="FA15" s="15">
         <v>6</v>
+      </c>
+      <c r="FB15" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -15724,7 +15803,9 @@
       <c r="FA16" s="28">
         <v>136</v>
       </c>
-      <c r="FB16" s="1"/>
+      <c r="FB16" s="28">
+        <v>102</v>
+      </c>
     </row>
     <row r="17" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
@@ -16195,7 +16276,9 @@
       <c r="FA17" s="15">
         <v>158</v>
       </c>
-      <c r="FB17" s="1"/>
+      <c r="FB17" s="15">
+        <v>136</v>
+      </c>
     </row>
     <row r="18" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
@@ -16667,7 +16750,9 @@
       <c r="FA18" s="34">
         <v>1733</v>
       </c>
-      <c r="FB18" s="1"/>
+      <c r="FB18" s="34">
+        <v>1597</v>
+      </c>
     </row>
     <row r="19" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
@@ -17139,7 +17224,9 @@
       <c r="FA19" s="15">
         <v>68</v>
       </c>
-      <c r="FB19" s="1"/>
+      <c r="FB19" s="15">
+        <v>55</v>
+      </c>
     </row>
     <row r="20" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
@@ -17609,7 +17696,9 @@
       <c r="FA20" s="28">
         <v>114</v>
       </c>
-      <c r="FB20" s="1"/>
+      <c r="FB20" s="28">
+        <v>115</v>
+      </c>
     </row>
     <row r="21" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
@@ -18079,7 +18168,9 @@
       <c r="FA21" s="15">
         <v>32</v>
       </c>
-      <c r="FB21" s="1"/>
+      <c r="FB21" s="15">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
@@ -18550,6 +18641,9 @@
       <c r="FA22" s="15">
         <v>1</v>
       </c>
+      <c r="FB22" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
@@ -19020,6 +19114,9 @@
       <c r="FA23" s="15">
         <v>0</v>
       </c>
+      <c r="FB23" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
@@ -19490,7 +19587,9 @@
       <c r="FA24" s="15">
         <v>5</v>
       </c>
-      <c r="FB24" s="1"/>
+      <c r="FB24" s="15">
+        <v>12</v>
+      </c>
     </row>
     <row r="25" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
@@ -19961,6 +20060,9 @@
       <c r="FA25" s="15">
         <v>0</v>
       </c>
+      <c r="FB25" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
@@ -20431,6 +20533,9 @@
       <c r="FA26" s="15">
         <v>13</v>
       </c>
+      <c r="FB26" s="15">
+        <v>14</v>
+      </c>
     </row>
     <row r="27" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
@@ -20901,6 +21006,9 @@
       <c r="FA27" s="15">
         <v>0</v>
       </c>
+      <c r="FB27" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
@@ -21371,7 +21479,9 @@
       <c r="FA28" s="15">
         <v>1</v>
       </c>
-      <c r="FB28" s="1"/>
+      <c r="FB28" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="70" t="s">
@@ -21841,6 +21951,9 @@
       </c>
       <c r="FA29" s="15">
         <v>0</v>
+      </c>
+      <c r="FB29" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -22310,6 +22423,9 @@
       <c r="FA30" s="15">
         <v>24</v>
       </c>
+      <c r="FB30" s="15">
+        <v>21</v>
+      </c>
     </row>
     <row r="31" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
@@ -22781,7 +22897,9 @@
       <c r="FA31" s="15">
         <v>57</v>
       </c>
-      <c r="FB31" s="1"/>
+      <c r="FB31" s="15">
+        <v>50</v>
+      </c>
     </row>
     <row r="32" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
@@ -23252,6 +23370,9 @@
       <c r="FA32" s="15">
         <v>0</v>
       </c>
+      <c r="FB32" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
@@ -23720,6 +23841,9 @@
         <v>0</v>
       </c>
       <c r="FA33" s="15">
+        <v>0</v>
+      </c>
+      <c r="FB33" s="15">
         <v>0</v>
       </c>
     </row>
@@ -24193,7 +24317,9 @@
       <c r="FA34" s="15">
         <v>83</v>
       </c>
-      <c r="FB34" s="1"/>
+      <c r="FB34" s="15">
+        <v>70</v>
+      </c>
     </row>
     <row r="35" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
@@ -24665,7 +24791,9 @@
       <c r="FA35" s="15">
         <v>274</v>
       </c>
-      <c r="FB35" s="1"/>
+      <c r="FB35" s="15">
+        <v>289</v>
+      </c>
     </row>
     <row r="36" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="69"/>
@@ -25134,7 +25262,9 @@
       <c r="FA36" s="28">
         <v>43</v>
       </c>
-      <c r="FB36" s="1"/>
+      <c r="FB36" s="28">
+        <v>33</v>
+      </c>
     </row>
     <row r="37" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
@@ -25606,7 +25736,9 @@
       <c r="FA37" s="15">
         <v>49</v>
       </c>
-      <c r="FB37" s="1"/>
+      <c r="FB37" s="15">
+        <v>67</v>
+      </c>
     </row>
     <row r="38" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
@@ -26077,6 +26209,9 @@
       <c r="FA38" s="15">
         <v>9</v>
       </c>
+      <c r="FB38" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="39" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
@@ -26547,6 +26682,9 @@
       <c r="FA39" s="15">
         <v>6</v>
       </c>
+      <c r="FB39" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="40" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
@@ -27017,6 +27155,9 @@
       <c r="FA40" s="15">
         <v>1</v>
       </c>
+      <c r="FB40" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
@@ -27487,6 +27628,9 @@
       <c r="FA41" s="15">
         <v>0</v>
       </c>
+      <c r="FB41" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
@@ -27957,6 +28101,9 @@
       <c r="FA42" s="15">
         <v>13</v>
       </c>
+      <c r="FB42" s="15">
+        <v>11</v>
+      </c>
     </row>
     <row r="43" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
@@ -28427,6 +28574,9 @@
       <c r="FA43" s="28">
         <v>46</v>
       </c>
+      <c r="FB43" s="28">
+        <v>57</v>
+      </c>
     </row>
     <row r="44" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
@@ -28897,6 +29047,9 @@
       <c r="FA44" s="15">
         <v>3</v>
       </c>
+      <c r="FB44" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
@@ -29367,7 +29520,9 @@
       <c r="FA45" s="15">
         <v>25</v>
       </c>
-      <c r="FB45" s="1"/>
+      <c r="FB45" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="46" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
@@ -29838,6 +29993,9 @@
       <c r="FA46" s="15">
         <v>28</v>
       </c>
+      <c r="FB46" s="15">
+        <v>17</v>
+      </c>
     </row>
     <row r="47" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
@@ -30308,6 +30466,9 @@
       <c r="FA47" s="15">
         <v>1</v>
       </c>
+      <c r="FB47" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
@@ -30777,6 +30938,9 @@
       </c>
       <c r="FA48" s="15">
         <v>9</v>
+      </c>
+      <c r="FB48" s="15">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -31249,7 +31413,9 @@
       <c r="FA49" s="15">
         <v>44</v>
       </c>
-      <c r="FB49" s="1"/>
+      <c r="FB49" s="15">
+        <v>40</v>
+      </c>
     </row>
     <row r="50" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="69"/>
@@ -31718,7 +31884,9 @@
       <c r="FA50" s="15">
         <v>16</v>
       </c>
-      <c r="FB50" s="1"/>
+      <c r="FB50" s="15">
+        <v>27</v>
+      </c>
     </row>
     <row r="51" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
@@ -32189,6 +32357,9 @@
       <c r="FA51" s="15">
         <v>8</v>
       </c>
+      <c r="FB51" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="52" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
@@ -32659,6 +32830,9 @@
       <c r="FA52" s="15">
         <v>30</v>
       </c>
+      <c r="FB52" s="15">
+        <v>25</v>
+      </c>
     </row>
     <row r="53" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
@@ -33129,6 +33303,9 @@
       <c r="FA53" s="15">
         <v>56</v>
       </c>
+      <c r="FB53" s="15">
+        <v>52</v>
+      </c>
     </row>
     <row r="54" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
@@ -33599,6 +33776,9 @@
       <c r="FA54" s="15">
         <v>9</v>
       </c>
+      <c r="FB54" s="15">
+        <v>3</v>
+      </c>
     </row>
     <row r="55" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
@@ -34069,6 +34249,9 @@
       <c r="FA55" s="15">
         <v>19</v>
       </c>
+      <c r="FB55" s="15">
+        <v>25</v>
+      </c>
     </row>
     <row r="56" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
@@ -34539,6 +34722,9 @@
       <c r="FA56" s="15">
         <v>1</v>
       </c>
+      <c r="FB56" s="15">
+        <v>3</v>
+      </c>
     </row>
     <row r="57" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
@@ -35008,6 +35194,9 @@
       </c>
       <c r="FA57" s="15">
         <v>5</v>
+      </c>
+      <c r="FB57" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -35628,8 +35817,12 @@
         <v>3510</v>
       </c>
       <c r="FA58" s="14">
-        <f t="shared" ref="FA58" si="12">SUM(FA6:FA57)</f>
+        <f t="shared" ref="FA58:FB58" si="12">SUM(FA6:FA57)</f>
         <v>3385</v>
+      </c>
+      <c r="FB58" s="14">
+        <f t="shared" si="12"/>
+        <v>3189</v>
       </c>
     </row>
     <row r="59" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
@@ -35885,10 +36078,11 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="171">
+  <mergeCells count="172">
+    <mergeCell ref="FB4:FB5"/>
+    <mergeCell ref="DE2:FB2"/>
+    <mergeCell ref="ER3:FB3"/>
     <mergeCell ref="FA4:FA5"/>
-    <mergeCell ref="DE2:FA2"/>
-    <mergeCell ref="ER3:FA3"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -36060,28 +36254,33 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="17" priority="5">
+    <cfRule type="containsBlanks" dxfId="21" priority="6">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="16" priority="4">
+    <cfRule type="containsBlanks" dxfId="20" priority="5">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="15" priority="3">
+    <cfRule type="containsBlanks" dxfId="19" priority="4">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="14" priority="2">
+    <cfRule type="containsBlanks" dxfId="18" priority="3">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="13" priority="1">
+    <cfRule type="containsBlanks" dxfId="17" priority="2">
       <formula>LEN(TRIM(FA6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FB6:FB57">
+    <cfRule type="containsBlanks" dxfId="16" priority="1">
+      <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -36100,7 +36299,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:FA58"/>
+  <dimension ref="B1:FB58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -36125,15 +36324,15 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="157" width="10.875" style="1" customWidth="1"/>
-    <col min="158" max="16384" width="8.625" style="1"/>
+    <col min="106" max="158" width="10.875" style="1" customWidth="1"/>
+    <col min="159" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:157" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="BB1" s="85" t="s">
+    <row r="1" spans="2:158" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BB1" s="86" t="s">
         <v>323</v>
       </c>
-      <c r="BC1" s="85"/>
+      <c r="BC1" s="86"/>
       <c r="BI1" s="18"/>
       <c r="CC1" s="29"/>
       <c r="CD1" s="29"/>
@@ -36213,11 +36412,12 @@
       <c r="EX1" s="19"/>
       <c r="EY1" s="19"/>
       <c r="EZ1" s="19"/>
-      <c r="FA1" s="19" t="s">
+      <c r="FA1" s="19"/>
+      <c r="FB1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:157" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:158" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
       <c r="C2" s="60"/>
       <c r="D2" s="58" t="s">
@@ -36273,7 +36473,7 @@
       <c r="AZ2" s="51"/>
       <c r="BA2" s="51"/>
       <c r="BB2" s="51"/>
-      <c r="BC2" s="84"/>
+      <c r="BC2" s="85"/>
       <c r="BD2" s="58" t="s">
         <v>321</v>
       </c>
@@ -36327,61 +36527,62 @@
       <c r="CZ2" s="51"/>
       <c r="DA2" s="51"/>
       <c r="DB2" s="51"/>
-      <c r="DC2" s="84"/>
-      <c r="DD2" s="58" t="s">
+      <c r="DC2" s="85"/>
+      <c r="DD2" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="51"/>
-      <c r="DF2" s="51"/>
-      <c r="DG2" s="51"/>
-      <c r="DH2" s="51"/>
-      <c r="DI2" s="51"/>
-      <c r="DJ2" s="51"/>
-      <c r="DK2" s="51"/>
-      <c r="DL2" s="51"/>
-      <c r="DM2" s="51"/>
-      <c r="DN2" s="51"/>
-      <c r="DO2" s="51"/>
-      <c r="DP2" s="51"/>
-      <c r="DQ2" s="51"/>
-      <c r="DR2" s="51"/>
-      <c r="DS2" s="51"/>
-      <c r="DT2" s="51"/>
-      <c r="DU2" s="51"/>
-      <c r="DV2" s="51"/>
-      <c r="DW2" s="51"/>
-      <c r="DX2" s="51"/>
-      <c r="DY2" s="51"/>
-      <c r="DZ2" s="51"/>
-      <c r="EA2" s="51"/>
-      <c r="EB2" s="51"/>
-      <c r="EC2" s="51"/>
-      <c r="ED2" s="51"/>
-      <c r="EE2" s="51"/>
-      <c r="EF2" s="51"/>
-      <c r="EG2" s="51"/>
-      <c r="EH2" s="51"/>
-      <c r="EI2" s="51"/>
-      <c r="EJ2" s="51"/>
-      <c r="EK2" s="51"/>
-      <c r="EL2" s="51"/>
-      <c r="EM2" s="51"/>
-      <c r="EN2" s="51"/>
-      <c r="EO2" s="51"/>
-      <c r="EP2" s="51"/>
-      <c r="EQ2" s="51"/>
-      <c r="ER2" s="51"/>
-      <c r="ES2" s="51"/>
-      <c r="ET2" s="51"/>
-      <c r="EU2" s="51"/>
-      <c r="EV2" s="51"/>
-      <c r="EW2" s="51"/>
-      <c r="EX2" s="51"/>
-      <c r="EY2" s="51"/>
-      <c r="EZ2" s="51"/>
-      <c r="FA2" s="84"/>
+      <c r="DE2" s="73"/>
+      <c r="DF2" s="73"/>
+      <c r="DG2" s="73"/>
+      <c r="DH2" s="73"/>
+      <c r="DI2" s="73"/>
+      <c r="DJ2" s="73"/>
+      <c r="DK2" s="73"/>
+      <c r="DL2" s="73"/>
+      <c r="DM2" s="73"/>
+      <c r="DN2" s="73"/>
+      <c r="DO2" s="73"/>
+      <c r="DP2" s="73"/>
+      <c r="DQ2" s="73"/>
+      <c r="DR2" s="73"/>
+      <c r="DS2" s="73"/>
+      <c r="DT2" s="73"/>
+      <c r="DU2" s="73"/>
+      <c r="DV2" s="73"/>
+      <c r="DW2" s="73"/>
+      <c r="DX2" s="73"/>
+      <c r="DY2" s="73"/>
+      <c r="DZ2" s="73"/>
+      <c r="EA2" s="73"/>
+      <c r="EB2" s="73"/>
+      <c r="EC2" s="73"/>
+      <c r="ED2" s="73"/>
+      <c r="EE2" s="73"/>
+      <c r="EF2" s="73"/>
+      <c r="EG2" s="73"/>
+      <c r="EH2" s="73"/>
+      <c r="EI2" s="73"/>
+      <c r="EJ2" s="73"/>
+      <c r="EK2" s="73"/>
+      <c r="EL2" s="73"/>
+      <c r="EM2" s="73"/>
+      <c r="EN2" s="73"/>
+      <c r="EO2" s="73"/>
+      <c r="EP2" s="73"/>
+      <c r="EQ2" s="73"/>
+      <c r="ER2" s="73"/>
+      <c r="ES2" s="73"/>
+      <c r="ET2" s="73"/>
+      <c r="EU2" s="73"/>
+      <c r="EV2" s="73"/>
+      <c r="EW2" s="73"/>
+      <c r="EX2" s="73"/>
+      <c r="EY2" s="73"/>
+      <c r="EZ2" s="73"/>
+      <c r="FA2" s="73"/>
+      <c r="FB2" s="73"/>
     </row>
-    <row r="3" spans="2:157" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:158" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="47" t="s">
@@ -36496,222 +36697,223 @@
       <c r="DA3" s="52"/>
       <c r="DB3" s="52"/>
       <c r="DC3" s="53"/>
-      <c r="DD3" s="47" t="s">
+      <c r="DD3" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="52"/>
-      <c r="DF3" s="52"/>
-      <c r="DG3" s="52"/>
-      <c r="DH3" s="52"/>
-      <c r="DI3" s="52"/>
-      <c r="DJ3" s="52"/>
-      <c r="DK3" s="52"/>
-      <c r="DL3" s="52"/>
-      <c r="DM3" s="52"/>
-      <c r="DN3" s="52"/>
-      <c r="DO3" s="52"/>
-      <c r="DP3" s="52"/>
-      <c r="DQ3" s="52"/>
-      <c r="DR3" s="52"/>
-      <c r="DS3" s="52"/>
-      <c r="DT3" s="52"/>
-      <c r="DU3" s="52"/>
-      <c r="DV3" s="52"/>
-      <c r="DW3" s="52"/>
-      <c r="DX3" s="52"/>
-      <c r="DY3" s="52"/>
-      <c r="DZ3" s="52"/>
-      <c r="EA3" s="52"/>
-      <c r="EB3" s="52"/>
-      <c r="EC3" s="52"/>
-      <c r="ED3" s="52"/>
-      <c r="EE3" s="52"/>
-      <c r="EF3" s="52"/>
-      <c r="EG3" s="52"/>
-      <c r="EH3" s="52"/>
-      <c r="EI3" s="52"/>
-      <c r="EJ3" s="52"/>
-      <c r="EK3" s="52"/>
-      <c r="EL3" s="52"/>
-      <c r="EM3" s="52"/>
-      <c r="EN3" s="52"/>
-      <c r="EO3" s="52"/>
-      <c r="EP3" s="52"/>
-      <c r="EQ3" s="53"/>
-      <c r="ER3" s="47" t="s">
+      <c r="DE3" s="45"/>
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="52"/>
-      <c r="ET3" s="52"/>
-      <c r="EU3" s="52"/>
-      <c r="EV3" s="52"/>
-      <c r="EW3" s="52"/>
-      <c r="EX3" s="52"/>
-      <c r="EY3" s="52"/>
-      <c r="EZ3" s="52"/>
-      <c r="FA3" s="53"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
+      <c r="EU3" s="45"/>
+      <c r="EV3" s="45"/>
+      <c r="EW3" s="45"/>
+      <c r="EX3" s="45"/>
+      <c r="EY3" s="45"/>
+      <c r="EZ3" s="45"/>
+      <c r="FA3" s="45"/>
+      <c r="FB3" s="45"/>
     </row>
-    <row r="4" spans="2:157" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:158" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="74" t="s">
+      <c r="E4" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="75" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="74" t="s">
+      <c r="H4" s="75" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="J4" s="74" t="s">
+      <c r="J4" s="75" t="s">
         <v>189</v>
       </c>
-      <c r="K4" s="74" t="s">
+      <c r="K4" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="L4" s="74" t="s">
+      <c r="L4" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="74" t="s">
+      <c r="M4" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="N4" s="74" t="s">
+      <c r="N4" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="O4" s="74" t="s">
+      <c r="O4" s="75" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="74" t="s">
+      <c r="P4" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="Q4" s="74" t="s">
+      <c r="Q4" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="79" t="s">
+      <c r="R4" s="80" t="s">
         <v>196</v>
       </c>
-      <c r="S4" s="74" t="s">
+      <c r="S4" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="T4" s="74" t="s">
+      <c r="T4" s="75" t="s">
         <v>198</v>
       </c>
-      <c r="U4" s="74" t="s">
+      <c r="U4" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="V4" s="74" t="s">
+      <c r="V4" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="W4" s="74" t="s">
+      <c r="W4" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="X4" s="74" t="s">
+      <c r="X4" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="75" t="s">
+      <c r="Y4" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="Z4" s="74" t="s">
+      <c r="Z4" s="75" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" s="74" t="s">
+      <c r="AA4" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="AB4" s="74" t="s">
+      <c r="AB4" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="AC4" s="75" t="s">
+      <c r="AC4" s="76" t="s">
         <v>165</v>
       </c>
-      <c r="AD4" s="74" t="s">
+      <c r="AD4" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="AE4" s="74" t="s">
+      <c r="AE4" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="AF4" s="74" t="s">
+      <c r="AF4" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="AG4" s="74" t="s">
+      <c r="AG4" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="AH4" s="74" t="s">
+      <c r="AH4" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="AI4" s="75" t="s">
+      <c r="AI4" s="76" t="s">
         <v>167</v>
       </c>
-      <c r="AJ4" s="75" t="s">
+      <c r="AJ4" s="76" t="s">
         <v>168</v>
       </c>
-      <c r="AK4" s="75" t="s">
+      <c r="AK4" s="76" t="s">
         <v>169</v>
       </c>
-      <c r="AL4" s="75" t="s">
+      <c r="AL4" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="AM4" s="75" t="s">
+      <c r="AM4" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="AN4" s="74" t="s">
+      <c r="AN4" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="AO4" s="75" t="s">
+      <c r="AO4" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="AP4" s="75" t="s">
+      <c r="AP4" s="76" t="s">
         <v>173</v>
       </c>
-      <c r="AQ4" s="74" t="s">
+      <c r="AQ4" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="AR4" s="75" t="s">
+      <c r="AR4" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="AS4" s="74" t="s">
+      <c r="AS4" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="AT4" s="74" t="s">
+      <c r="AT4" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="AU4" s="74" t="s">
+      <c r="AU4" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="AV4" s="74" t="s">
+      <c r="AV4" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="AW4" s="74" t="s">
+      <c r="AW4" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="75" t="s">
+      <c r="AX4" s="76" t="s">
         <v>203</v>
       </c>
-      <c r="AY4" s="75" t="s">
+      <c r="AY4" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="AZ4" s="74" t="s">
+      <c r="AZ4" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="BA4" s="74" t="s">
+      <c r="BA4" s="75" t="s">
         <v>182</v>
       </c>
-      <c r="BB4" s="74" t="s">
+      <c r="BB4" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="74" t="s">
+      <c r="BC4" s="75" t="s">
         <v>184</v>
       </c>
       <c r="BD4" s="64" t="s">
@@ -36795,233 +36997,236 @@
       <c r="CD4" s="64" t="s">
         <v>239</v>
       </c>
-      <c r="CE4" s="74" t="s">
+      <c r="CE4" s="75" t="s">
         <v>253</v>
       </c>
-      <c r="CF4" s="74" t="s">
+      <c r="CF4" s="75" t="s">
         <v>255</v>
       </c>
-      <c r="CG4" s="74" t="s">
+      <c r="CG4" s="75" t="s">
         <v>257</v>
       </c>
-      <c r="CH4" s="74" t="s">
+      <c r="CH4" s="75" t="s">
         <v>259</v>
       </c>
-      <c r="CI4" s="74" t="s">
+      <c r="CI4" s="75" t="s">
         <v>261</v>
       </c>
-      <c r="CJ4" s="74" t="s">
+      <c r="CJ4" s="75" t="s">
         <v>263</v>
       </c>
-      <c r="CK4" s="74" t="s">
+      <c r="CK4" s="75" t="s">
         <v>265</v>
       </c>
-      <c r="CL4" s="74" t="s">
+      <c r="CL4" s="75" t="s">
         <v>267</v>
       </c>
-      <c r="CM4" s="74" t="s">
+      <c r="CM4" s="75" t="s">
         <v>269</v>
       </c>
-      <c r="CN4" s="74" t="s">
+      <c r="CN4" s="75" t="s">
         <v>271</v>
       </c>
-      <c r="CO4" s="74" t="s">
+      <c r="CO4" s="75" t="s">
         <v>273</v>
       </c>
-      <c r="CP4" s="74" t="s">
+      <c r="CP4" s="75" t="s">
         <v>275</v>
       </c>
-      <c r="CQ4" s="74" t="s">
+      <c r="CQ4" s="75" t="s">
         <v>277</v>
       </c>
-      <c r="CR4" s="74" t="s">
+      <c r="CR4" s="75" t="s">
         <v>283</v>
       </c>
-      <c r="CS4" s="74" t="s">
+      <c r="CS4" s="75" t="s">
         <v>285</v>
       </c>
-      <c r="CT4" s="74" t="s">
+      <c r="CT4" s="75" t="s">
         <v>287</v>
       </c>
-      <c r="CU4" s="74" t="s">
+      <c r="CU4" s="75" t="s">
         <v>289</v>
       </c>
-      <c r="CV4" s="74" t="s">
+      <c r="CV4" s="75" t="s">
         <v>372</v>
       </c>
-      <c r="CW4" s="74" t="s">
+      <c r="CW4" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="CX4" s="74" t="s">
+      <c r="CX4" s="75" t="s">
         <v>295</v>
       </c>
-      <c r="CY4" s="74" t="s">
+      <c r="CY4" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="CZ4" s="74" t="s">
+      <c r="CZ4" s="75" t="s">
         <v>298</v>
       </c>
-      <c r="DA4" s="74" t="s">
+      <c r="DA4" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="DB4" s="74" t="s">
+      <c r="DB4" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="DC4" s="74" t="s">
+      <c r="DC4" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="DD4" s="74" t="s">
+      <c r="DD4" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="DE4" s="74" t="s">
+      <c r="DE4" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="DF4" s="74" t="s">
+      <c r="DF4" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="DG4" s="74" t="s">
+      <c r="DG4" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="DH4" s="74" t="s">
+      <c r="DH4" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="DI4" s="74" t="s">
+      <c r="DI4" s="44" t="s">
         <v>317</v>
       </c>
-      <c r="DJ4" s="74" t="s">
+      <c r="DJ4" s="44" t="s">
         <v>319</v>
       </c>
-      <c r="DK4" s="74" t="s">
+      <c r="DK4" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="DL4" s="74" t="s">
+      <c r="DL4" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="DM4" s="75" t="s">
+      <c r="DM4" s="74" t="s">
         <v>331</v>
       </c>
-      <c r="DN4" s="74" t="s">
+      <c r="DN4" s="44" t="s">
         <v>333</v>
       </c>
-      <c r="DO4" s="74" t="s">
+      <c r="DO4" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="DP4" s="74" t="s">
+      <c r="DP4" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="DQ4" s="74" t="s">
+      <c r="DQ4" s="44" t="s">
         <v>339</v>
       </c>
-      <c r="DR4" s="74" t="s">
+      <c r="DR4" s="44" t="s">
         <v>342</v>
       </c>
-      <c r="DS4" s="74" t="s">
+      <c r="DS4" s="44" t="s">
         <v>346</v>
       </c>
-      <c r="DT4" s="74" t="s">
+      <c r="DT4" s="44" t="s">
         <v>350</v>
       </c>
-      <c r="DU4" s="75" t="s">
+      <c r="DU4" s="74" t="s">
         <v>366</v>
       </c>
-      <c r="DV4" s="75" t="s">
+      <c r="DV4" s="74" t="s">
         <v>367</v>
       </c>
-      <c r="DW4" s="75" t="s">
+      <c r="DW4" s="74" t="s">
         <v>368</v>
       </c>
-      <c r="DX4" s="75" t="s">
+      <c r="DX4" s="74" t="s">
         <v>369</v>
       </c>
-      <c r="DY4" s="75" t="s">
+      <c r="DY4" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="DZ4" s="74" t="s">
+      <c r="DZ4" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="EA4" s="74" t="s">
+      <c r="EA4" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="EB4" s="74" t="s">
+      <c r="EB4" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="EC4" s="74" t="s">
+      <c r="EC4" s="44" t="s">
         <v>380</v>
       </c>
-      <c r="ED4" s="74" t="s">
+      <c r="ED4" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="EE4" s="74" t="s">
+      <c r="EE4" s="44" t="s">
         <v>385</v>
       </c>
-      <c r="EF4" s="74" t="s">
+      <c r="EF4" s="44" t="s">
         <v>387</v>
       </c>
-      <c r="EG4" s="74" t="s">
+      <c r="EG4" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="EH4" s="74" t="s">
+      <c r="EH4" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="EI4" s="74" t="s">
+      <c r="EI4" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="EJ4" s="74" t="s">
+      <c r="EJ4" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="EK4" s="74" t="s">
+      <c r="EK4" s="44" t="s">
         <v>397</v>
       </c>
-      <c r="EL4" s="74" t="s">
+      <c r="EL4" s="44" t="s">
         <v>399</v>
       </c>
-      <c r="EM4" s="74" t="s">
+      <c r="EM4" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="EN4" s="74" t="s">
+      <c r="EN4" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="EO4" s="74" t="s">
+      <c r="EO4" s="44" t="s">
         <v>406</v>
       </c>
-      <c r="EP4" s="74" t="s">
+      <c r="EP4" s="44" t="s">
         <v>408</v>
       </c>
-      <c r="EQ4" s="74" t="s">
+      <c r="EQ4" s="44" t="s">
         <v>410</v>
       </c>
-      <c r="ER4" s="74" t="s">
+      <c r="ER4" s="44" t="s">
         <v>413</v>
       </c>
-      <c r="ES4" s="74" t="s">
+      <c r="ES4" s="44" t="s">
         <v>417</v>
       </c>
-      <c r="ET4" s="74" t="s">
+      <c r="ET4" s="44" t="s">
         <v>419</v>
       </c>
-      <c r="EU4" s="74" t="s">
+      <c r="EU4" s="44" t="s">
         <v>421</v>
       </c>
-      <c r="EV4" s="74" t="s">
+      <c r="EV4" s="44" t="s">
         <v>423</v>
       </c>
-      <c r="EW4" s="74" t="s">
+      <c r="EW4" s="44" t="s">
         <v>425</v>
       </c>
-      <c r="EX4" s="74" t="s">
+      <c r="EX4" s="44" t="s">
         <v>428</v>
       </c>
-      <c r="EY4" s="74" t="s">
+      <c r="EY4" s="44" t="s">
         <v>430</v>
       </c>
-      <c r="EZ4" s="74" t="s">
+      <c r="EZ4" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="FA4" s="74" t="s">
+      <c r="FA4" s="44" t="s">
         <v>434</v>
       </c>
+      <c r="FB4" s="44" t="s">
+        <v>436</v>
+      </c>
     </row>
-    <row r="5" spans="2:157" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:158" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
       <c r="D5" s="48"/>
@@ -37038,40 +37243,40 @@
       <c r="O5" s="48"/>
       <c r="P5" s="48"/>
       <c r="Q5" s="48"/>
-      <c r="R5" s="80"/>
+      <c r="R5" s="81"/>
       <c r="S5" s="48"/>
       <c r="T5" s="48"/>
       <c r="U5" s="48"/>
       <c r="V5" s="48"/>
       <c r="W5" s="48"/>
       <c r="X5" s="48"/>
-      <c r="Y5" s="76"/>
+      <c r="Y5" s="77"/>
       <c r="Z5" s="48"/>
       <c r="AA5" s="48"/>
       <c r="AB5" s="48"/>
-      <c r="AC5" s="76"/>
+      <c r="AC5" s="77"/>
       <c r="AD5" s="48"/>
       <c r="AE5" s="48"/>
       <c r="AF5" s="48"/>
       <c r="AG5" s="48"/>
       <c r="AH5" s="48"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="76"/>
-      <c r="AK5" s="76"/>
-      <c r="AL5" s="76"/>
-      <c r="AM5" s="76"/>
+      <c r="AI5" s="77"/>
+      <c r="AJ5" s="77"/>
+      <c r="AK5" s="77"/>
+      <c r="AL5" s="77"/>
+      <c r="AM5" s="77"/>
       <c r="AN5" s="48"/>
-      <c r="AO5" s="76"/>
-      <c r="AP5" s="76"/>
+      <c r="AO5" s="77"/>
+      <c r="AP5" s="77"/>
       <c r="AQ5" s="48"/>
-      <c r="AR5" s="76"/>
+      <c r="AR5" s="77"/>
       <c r="AS5" s="48"/>
       <c r="AT5" s="48"/>
       <c r="AU5" s="48"/>
       <c r="AV5" s="48"/>
       <c r="AW5" s="48"/>
-      <c r="AX5" s="76"/>
-      <c r="AY5" s="76"/>
+      <c r="AX5" s="77"/>
+      <c r="AY5" s="77"/>
       <c r="AZ5" s="48"/>
       <c r="BA5" s="48"/>
       <c r="BB5" s="48"/>
@@ -37128,58 +37333,59 @@
       <c r="DA5" s="48"/>
       <c r="DB5" s="48"/>
       <c r="DC5" s="48"/>
-      <c r="DD5" s="48"/>
-      <c r="DE5" s="48"/>
-      <c r="DF5" s="48"/>
-      <c r="DG5" s="48"/>
-      <c r="DH5" s="48"/>
-      <c r="DI5" s="48"/>
-      <c r="DJ5" s="48"/>
-      <c r="DK5" s="48"/>
-      <c r="DL5" s="48"/>
-      <c r="DM5" s="76"/>
-      <c r="DN5" s="48"/>
-      <c r="DO5" s="48"/>
-      <c r="DP5" s="48"/>
-      <c r="DQ5" s="48"/>
-      <c r="DR5" s="48"/>
-      <c r="DS5" s="48"/>
-      <c r="DT5" s="48"/>
-      <c r="DU5" s="76"/>
-      <c r="DV5" s="76"/>
-      <c r="DW5" s="76"/>
-      <c r="DX5" s="76"/>
-      <c r="DY5" s="76"/>
-      <c r="DZ5" s="48"/>
-      <c r="EA5" s="48"/>
-      <c r="EB5" s="48"/>
-      <c r="EC5" s="48"/>
-      <c r="ED5" s="48"/>
-      <c r="EE5" s="48"/>
-      <c r="EF5" s="48"/>
-      <c r="EG5" s="48"/>
-      <c r="EH5" s="48"/>
-      <c r="EI5" s="48"/>
-      <c r="EJ5" s="48"/>
-      <c r="EK5" s="48"/>
-      <c r="EL5" s="48"/>
-      <c r="EM5" s="48"/>
-      <c r="EN5" s="48"/>
-      <c r="EO5" s="48"/>
-      <c r="EP5" s="48"/>
-      <c r="EQ5" s="48"/>
-      <c r="ER5" s="48"/>
-      <c r="ES5" s="48"/>
-      <c r="ET5" s="48"/>
-      <c r="EU5" s="48"/>
-      <c r="EV5" s="48"/>
-      <c r="EW5" s="48"/>
-      <c r="EX5" s="48"/>
-      <c r="EY5" s="48"/>
-      <c r="EZ5" s="48"/>
-      <c r="FA5" s="48"/>
+      <c r="DD5" s="44"/>
+      <c r="DE5" s="44"/>
+      <c r="DF5" s="44"/>
+      <c r="DG5" s="44"/>
+      <c r="DH5" s="44"/>
+      <c r="DI5" s="44"/>
+      <c r="DJ5" s="44"/>
+      <c r="DK5" s="44"/>
+      <c r="DL5" s="44"/>
+      <c r="DM5" s="74"/>
+      <c r="DN5" s="44"/>
+      <c r="DO5" s="44"/>
+      <c r="DP5" s="44"/>
+      <c r="DQ5" s="44"/>
+      <c r="DR5" s="44"/>
+      <c r="DS5" s="44"/>
+      <c r="DT5" s="44"/>
+      <c r="DU5" s="74"/>
+      <c r="DV5" s="74"/>
+      <c r="DW5" s="74"/>
+      <c r="DX5" s="74"/>
+      <c r="DY5" s="74"/>
+      <c r="DZ5" s="44"/>
+      <c r="EA5" s="44"/>
+      <c r="EB5" s="44"/>
+      <c r="EC5" s="44"/>
+      <c r="ED5" s="44"/>
+      <c r="EE5" s="44"/>
+      <c r="EF5" s="44"/>
+      <c r="EG5" s="44"/>
+      <c r="EH5" s="44"/>
+      <c r="EI5" s="44"/>
+      <c r="EJ5" s="44"/>
+      <c r="EK5" s="44"/>
+      <c r="EL5" s="44"/>
+      <c r="EM5" s="44"/>
+      <c r="EN5" s="44"/>
+      <c r="EO5" s="44"/>
+      <c r="EP5" s="44"/>
+      <c r="EQ5" s="44"/>
+      <c r="ER5" s="44"/>
+      <c r="ES5" s="44"/>
+      <c r="ET5" s="44"/>
+      <c r="EU5" s="44"/>
+      <c r="EV5" s="44"/>
+      <c r="EW5" s="44"/>
+      <c r="EX5" s="44"/>
+      <c r="EY5" s="44"/>
+      <c r="EZ5" s="44"/>
+      <c r="FA5" s="44"/>
+      <c r="FB5" s="44"/>
     </row>
-    <row r="6" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -37648,8 +37854,11 @@
       <c r="FA6" s="28">
         <v>103</v>
       </c>
+      <c r="FB6" s="28">
+        <v>117</v>
+      </c>
     </row>
-    <row r="7" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -38118,8 +38327,11 @@
       <c r="FA7" s="15">
         <v>3</v>
       </c>
+      <c r="FB7" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -38588,8 +38800,11 @@
       <c r="FA8" s="28">
         <v>11</v>
       </c>
+      <c r="FB8" s="28">
+        <v>23</v>
+      </c>
     </row>
-    <row r="9" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -39058,8 +39273,11 @@
       <c r="FA9" s="15">
         <v>89</v>
       </c>
+      <c r="FB9" s="15">
+        <v>85</v>
+      </c>
     </row>
-    <row r="10" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -39528,8 +39746,11 @@
       <c r="FA10" s="15">
         <v>0</v>
       </c>
+      <c r="FB10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -39998,8 +40219,11 @@
       <c r="FA11" s="15">
         <v>6</v>
       </c>
+      <c r="FB11" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="12" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -40468,8 +40692,11 @@
       <c r="FA12" s="15">
         <v>7</v>
       </c>
+      <c r="FB12" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -40938,8 +41165,11 @@
       <c r="FA13" s="15">
         <v>19</v>
       </c>
+      <c r="FB13" s="15">
+        <v>30</v>
+      </c>
     </row>
-    <row r="14" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -41408,8 +41638,11 @@
       <c r="FA14" s="15">
         <v>19</v>
       </c>
+      <c r="FB14" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="15" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -41878,8 +42111,11 @@
       <c r="FA15" s="15">
         <v>2</v>
       </c>
+      <c r="FB15" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -42348,8 +42584,11 @@
       <c r="FA16" s="28">
         <v>154</v>
       </c>
+      <c r="FB16" s="28">
+        <v>144</v>
+      </c>
     </row>
-    <row r="17" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -42818,8 +43057,11 @@
       <c r="FA17" s="15">
         <v>138</v>
       </c>
+      <c r="FB17" s="15">
+        <v>147</v>
+      </c>
     </row>
-    <row r="18" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -43288,9 +43530,12 @@
       <c r="FA18" s="34">
         <v>1942</v>
       </c>
+      <c r="FB18" s="34">
+        <v>1780</v>
+      </c>
     </row>
-    <row r="19" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="77" t="s">
+    <row r="19" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -43758,9 +44003,12 @@
       <c r="FA19" s="15">
         <v>74</v>
       </c>
+      <c r="FB19" s="15">
+        <v>67</v>
+      </c>
     </row>
-    <row r="20" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="81"/>
+    <row r="20" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -44226,9 +44474,12 @@
       <c r="FA20" s="28">
         <v>299</v>
       </c>
+      <c r="FB20" s="28">
+        <v>216</v>
+      </c>
     </row>
-    <row r="21" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="78"/>
+    <row r="21" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -44694,8 +44945,11 @@
       <c r="FA21" s="15">
         <v>59</v>
       </c>
+      <c r="FB21" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -45164,8 +45418,11 @@
       <c r="FA22" s="15">
         <v>15</v>
       </c>
+      <c r="FB22" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="23" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -45634,8 +45891,11 @@
       <c r="FA23" s="15">
         <v>1</v>
       </c>
+      <c r="FB23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -46104,8 +46364,11 @@
       <c r="FA24" s="15">
         <v>20</v>
       </c>
+      <c r="FB24" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="25" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -46574,8 +46837,11 @@
       <c r="FA25" s="15">
         <v>0</v>
       </c>
+      <c r="FB25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -47044,8 +47310,11 @@
       <c r="FA26" s="15">
         <v>10</v>
       </c>
+      <c r="FB26" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="27" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -47514,8 +47783,11 @@
       <c r="FA27" s="15">
         <v>0</v>
       </c>
+      <c r="FB27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -47984,9 +48256,12 @@
       <c r="FA28" s="15">
         <v>3</v>
       </c>
+      <c r="FB28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="82" t="s">
+    <row r="29" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -48454,9 +48729,12 @@
       <c r="FA29" s="15">
         <v>2</v>
       </c>
+      <c r="FB29" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="83"/>
+    <row r="30" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -48922,8 +49200,11 @@
       <c r="FA30" s="15">
         <v>25</v>
       </c>
+      <c r="FB30" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="31" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -49392,8 +49673,11 @@
       <c r="FA31" s="15">
         <v>64</v>
       </c>
+      <c r="FB31" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="32" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -49862,8 +50146,11 @@
       <c r="FA32" s="15">
         <v>0</v>
       </c>
+      <c r="FB32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -50332,8 +50619,11 @@
       <c r="FA33" s="15">
         <v>0</v>
       </c>
+      <c r="FB33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -50802,9 +51092,12 @@
       <c r="FA34" s="15">
         <v>88</v>
       </c>
+      <c r="FB34" s="15">
+        <v>71</v>
+      </c>
     </row>
-    <row r="35" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="77" t="s">
+    <row r="35" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -51272,9 +51565,12 @@
       <c r="FA35" s="15">
         <v>605</v>
       </c>
+      <c r="FB35" s="15">
+        <v>460</v>
+      </c>
     </row>
-    <row r="36" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="78"/>
+    <row r="36" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -51740,8 +52036,11 @@
       <c r="FA36" s="28">
         <v>102</v>
       </c>
+      <c r="FB36" s="28">
+        <v>67</v>
+      </c>
     </row>
-    <row r="37" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -52210,8 +52509,11 @@
       <c r="FA37" s="15">
         <v>105</v>
       </c>
+      <c r="FB37" s="15">
+        <v>89</v>
+      </c>
     </row>
-    <row r="38" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -52680,8 +52982,11 @@
       <c r="FA38" s="15">
         <v>35</v>
       </c>
+      <c r="FB38" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="39" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -53150,8 +53455,11 @@
       <c r="FA39" s="15">
         <v>10</v>
       </c>
+      <c r="FB39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -53620,8 +53928,11 @@
       <c r="FA40" s="15">
         <v>0</v>
       </c>
+      <c r="FB40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -54090,8 +54401,11 @@
       <c r="FA41" s="15">
         <v>0</v>
       </c>
+      <c r="FB41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -54560,8 +54874,11 @@
       <c r="FA42" s="15">
         <v>16</v>
       </c>
+      <c r="FB42" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -55030,8 +55347,11 @@
       <c r="FA43" s="28">
         <v>52</v>
       </c>
+      <c r="FB43" s="28">
+        <v>63</v>
+      </c>
     </row>
-    <row r="44" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -55500,8 +55820,11 @@
       <c r="FA44" s="15">
         <v>9</v>
       </c>
+      <c r="FB44" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="45" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -55970,8 +56293,11 @@
       <c r="FA45" s="15">
         <v>9</v>
       </c>
+      <c r="FB45" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -56440,8 +56766,11 @@
       <c r="FA46" s="15">
         <v>17</v>
       </c>
+      <c r="FB46" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="47" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -56910,8 +57239,11 @@
       <c r="FA47" s="15">
         <v>1</v>
       </c>
+      <c r="FB47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -57380,9 +57712,12 @@
       <c r="FA48" s="15">
         <v>6</v>
       </c>
+      <c r="FB48" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="49" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="77" t="s">
+    <row r="49" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -57850,9 +58185,12 @@
       <c r="FA49" s="15">
         <v>52</v>
       </c>
+      <c r="FB49" s="15">
+        <v>42</v>
+      </c>
     </row>
-    <row r="50" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="78"/>
+    <row r="50" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -58318,8 +58656,11 @@
       <c r="FA50" s="15">
         <v>12</v>
       </c>
+      <c r="FB50" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="51" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -58788,8 +59129,11 @@
       <c r="FA51" s="15">
         <v>3</v>
       </c>
+      <c r="FB51" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="52" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -59258,8 +59602,11 @@
       <c r="FA52" s="15">
         <v>18</v>
       </c>
+      <c r="FB52" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="53" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -59728,8 +60075,11 @@
       <c r="FA53" s="15">
         <v>45</v>
       </c>
+      <c r="FB53" s="15">
+        <v>38</v>
+      </c>
     </row>
-    <row r="54" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -60198,8 +60548,11 @@
       <c r="FA54" s="15">
         <v>9</v>
       </c>
+      <c r="FB54" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -60668,8 +61021,11 @@
       <c r="FA55" s="15">
         <v>13</v>
       </c>
+      <c r="FB55" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="56" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -61138,8 +61494,11 @@
       <c r="FA56" s="15">
         <v>1</v>
       </c>
+      <c r="FB56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -61608,8 +61967,11 @@
       <c r="FA57" s="15">
         <v>2</v>
       </c>
+      <c r="FB57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="2:157" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -62226,17 +62588,22 @@
         <v>4841</v>
       </c>
       <c r="FA58" s="14">
-        <f t="shared" ref="FA58" si="10">SUM(FA6:FA57)</f>
+        <f t="shared" ref="FA58:FB58" si="10">SUM(FA6:FA57)</f>
         <v>4275</v>
+      </c>
+      <c r="FB58" s="14">
+        <f t="shared" si="10"/>
+        <v>3793</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="171">
+  <mergeCells count="172">
+    <mergeCell ref="FB4:FB5"/>
+    <mergeCell ref="DD2:FB2"/>
+    <mergeCell ref="ER3:FB3"/>
     <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="BD2:DC2"/>
     <mergeCell ref="FA4:FA5"/>
-    <mergeCell ref="DD2:FA2"/>
-    <mergeCell ref="ER3:FA3"/>
     <mergeCell ref="EX4:EX5"/>
     <mergeCell ref="EW4:EW5"/>
     <mergeCell ref="EV4:EV5"/>
@@ -62255,7 +62622,6 @@
     <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="DD4:DD5"/>
-    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -62303,7 +62669,6 @@
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="D2:BC2"/>
     <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="D4:D5"/>
@@ -62323,7 +62688,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
     <mergeCell ref="AL4:AL5"/>
@@ -62338,6 +62702,8 @@
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="CE4:CE5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="EA4:EA5"/>
@@ -62371,6 +62737,7 @@
     <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="EY4:EY5"/>
     <mergeCell ref="EZ4:EZ5"/>
     <mergeCell ref="EG4:EG5"/>
@@ -62406,28 +62773,33 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="12" priority="9">
+    <cfRule type="containsBlanks" dxfId="15" priority="10">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="11" priority="8">
+    <cfRule type="containsBlanks" dxfId="14" priority="9">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EH6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="10" priority="10">
+    <cfRule type="containsBlanks" dxfId="13" priority="11">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="9" priority="2">
+    <cfRule type="containsBlanks" dxfId="12" priority="3">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="8" priority="1">
+    <cfRule type="containsBlanks" dxfId="11" priority="2">
       <formula>LEN(TRIM(FA6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FB6:FB57">
+    <cfRule type="containsBlanks" dxfId="10" priority="1">
+      <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -62443,7 +62815,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="7" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
+          <x14:cfRule type="containsBlanks" priority="8" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -62466,7 +62838,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DA61"/>
+  <dimension ref="A1:DB61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -62477,11 +62849,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="105" width="10.875" style="1" customWidth="1"/>
-    <col min="106" max="16384" width="8.625" style="1"/>
+    <col min="54" max="106" width="10.875" style="1" customWidth="1"/>
+    <col min="107" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:105" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:106" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -62561,11 +62933,12 @@
       <c r="CX1" s="19"/>
       <c r="CY1" s="19"/>
       <c r="CZ1" s="19"/>
-      <c r="DA1" s="19" t="s">
+      <c r="DA1" s="19"/>
+      <c r="DB1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:105" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:106" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
       <c r="C2" s="60"/>
       <c r="D2" s="58" t="s">
@@ -62621,7 +62994,7 @@
       <c r="AZ2" s="51"/>
       <c r="BA2" s="51"/>
       <c r="BB2" s="51"/>
-      <c r="BC2" s="84"/>
+      <c r="BC2" s="85"/>
       <c r="BD2" s="73" t="s">
         <v>324</v>
       </c>
@@ -62674,52 +63047,53 @@
       <c r="CY2" s="73"/>
       <c r="CZ2" s="73"/>
       <c r="DA2" s="73"/>
+      <c r="DB2" s="73"/>
     </row>
-    <row r="3" spans="1:105" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:106" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86"/>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="86"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="86"/>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86"/>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="86"/>
-      <c r="AM3" s="86"/>
-      <c r="AN3" s="86"/>
-      <c r="AO3" s="86"/>
-      <c r="AP3" s="86"/>
-      <c r="AQ3" s="86"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
+      <c r="U3" s="87"/>
+      <c r="V3" s="87"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="87"/>
+      <c r="AM3" s="87"/>
+      <c r="AN3" s="87"/>
+      <c r="AO3" s="87"/>
+      <c r="AP3" s="87"/>
+      <c r="AQ3" s="87"/>
       <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
@@ -62788,8 +63162,9 @@
       <c r="CY3" s="45"/>
       <c r="CZ3" s="45"/>
       <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
     </row>
-    <row r="4" spans="1:105" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:106" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
         <v>0</v>
       </c>
@@ -63102,8 +63477,11 @@
       <c r="DA4" s="44" t="s">
         <v>433</v>
       </c>
+      <c r="DB4" s="44" t="s">
+        <v>435</v>
+      </c>
     </row>
-    <row r="5" spans="1:105" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:106" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
       <c r="D5" s="55"/>
@@ -63208,8 +63586,9 @@
       <c r="CY5" s="44"/>
       <c r="CZ5" s="44"/>
       <c r="DA5" s="44"/>
+      <c r="DB5" s="44"/>
     </row>
-    <row r="6" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -63523,8 +63902,11 @@
       <c r="DA6" s="28">
         <v>15</v>
       </c>
+      <c r="DB6" s="28">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -63837,8 +64219,11 @@
       <c r="DA7" s="15">
         <v>0</v>
       </c>
+      <c r="DB7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -64151,8 +64536,11 @@
       <c r="DA8" s="28">
         <v>0</v>
       </c>
+      <c r="DB8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -64466,8 +64854,11 @@
       <c r="DA9" s="28">
         <v>13</v>
       </c>
+      <c r="DB9" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -64780,8 +65171,11 @@
       <c r="DA10" s="15">
         <v>0</v>
       </c>
+      <c r="DB10" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -65094,8 +65488,11 @@
       <c r="DA11" s="28">
         <v>3</v>
       </c>
+      <c r="DB11" s="28">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -65408,8 +65805,11 @@
       <c r="DA12" s="15">
         <v>0</v>
       </c>
+      <c r="DB12" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -65722,8 +66122,11 @@
       <c r="DA13" s="15">
         <v>6</v>
       </c>
+      <c r="DB13" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -66036,8 +66439,11 @@
       <c r="DA14" s="15">
         <v>4</v>
       </c>
+      <c r="DB14" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -66350,8 +66756,11 @@
       <c r="DA15" s="15">
         <v>2</v>
       </c>
+      <c r="DB15" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -66665,8 +67074,11 @@
       <c r="DA16" s="28">
         <v>0</v>
       </c>
+      <c r="DB16" s="28">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -66979,8 +67391,11 @@
       <c r="DA17" s="15">
         <v>28</v>
       </c>
+      <c r="DB17" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="18" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -67294,10 +67709,13 @@
       <c r="DA18" s="34">
         <v>257</v>
       </c>
+      <c r="DB18" s="34">
+        <v>228</v>
+      </c>
     </row>
-    <row r="19" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -67609,10 +68027,13 @@
       <c r="DA19" s="15">
         <v>33</v>
       </c>
+      <c r="DB19" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="20" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="81"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -67922,10 +68343,13 @@
       <c r="DA20" s="28">
         <v>46</v>
       </c>
+      <c r="DB20" s="28">
+        <v>52</v>
+      </c>
     </row>
-    <row r="21" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="78"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -68235,8 +68659,11 @@
       <c r="DA21" s="15">
         <v>12</v>
       </c>
+      <c r="DB21" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="22" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -68549,8 +68976,11 @@
       <c r="DA22" s="15">
         <v>0</v>
       </c>
+      <c r="DB22" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -68863,8 +69293,11 @@
       <c r="DA23" s="15">
         <v>0</v>
       </c>
+      <c r="DB23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -69177,8 +69610,11 @@
       <c r="DA24" s="15">
         <v>2</v>
       </c>
+      <c r="DB24" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -69491,8 +69927,11 @@
       <c r="DA25" s="15">
         <v>0</v>
       </c>
+      <c r="DB25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -69805,8 +70244,11 @@
       <c r="DA26" s="15">
         <v>2</v>
       </c>
+      <c r="DB26" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -70119,8 +70561,11 @@
       <c r="DA27" s="15">
         <v>0</v>
       </c>
+      <c r="DB27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -70433,9 +70878,12 @@
       <c r="DA28" s="15">
         <v>0</v>
       </c>
+      <c r="DB28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="82" t="s">
+    <row r="29" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -70747,9 +71195,12 @@
       <c r="DA29" s="15">
         <v>0</v>
       </c>
+      <c r="DB29" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="83"/>
+    <row r="30" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -71059,8 +71510,11 @@
       <c r="DA30" s="15">
         <v>12</v>
       </c>
+      <c r="DB30" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -71374,8 +71828,11 @@
       <c r="DA31" s="15">
         <v>15</v>
       </c>
+      <c r="DB31" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="32" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -71688,8 +72145,11 @@
       <c r="DA32" s="15">
         <v>0</v>
       </c>
+      <c r="DB32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -72002,8 +72462,11 @@
       <c r="DA33" s="15">
         <v>0</v>
       </c>
+      <c r="DB33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -72317,10 +72780,13 @@
       <c r="DA34" s="15">
         <v>16</v>
       </c>
+      <c r="DB34" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="35" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -72632,9 +73098,12 @@
       <c r="DA35" s="15">
         <v>51</v>
       </c>
+      <c r="DB35" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="36" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="78"/>
+    <row r="36" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -72944,8 +73413,11 @@
       <c r="DA36" s="28">
         <v>12</v>
       </c>
+      <c r="DB36" s="28">
+        <v>15</v>
+      </c>
     </row>
-    <row r="37" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -73259,8 +73731,11 @@
       <c r="DA37" s="15">
         <v>10</v>
       </c>
+      <c r="DB37" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="38" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -73573,8 +74048,11 @@
       <c r="DA38" s="15">
         <v>2</v>
       </c>
+      <c r="DB38" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -73887,8 +74365,11 @@
       <c r="DA39" s="15">
         <v>2</v>
       </c>
+      <c r="DB39" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="40" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -74201,8 +74682,11 @@
       <c r="DA40" s="15">
         <v>1</v>
       </c>
+      <c r="DB40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -74515,8 +74999,11 @@
       <c r="DA41" s="15">
         <v>0</v>
       </c>
+      <c r="DB41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -74829,8 +75316,11 @@
       <c r="DA42" s="15">
         <v>8</v>
       </c>
+      <c r="DB42" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -75143,8 +75633,11 @@
       <c r="DA43" s="28">
         <v>16</v>
       </c>
+      <c r="DB43" s="28">
+        <v>25</v>
+      </c>
     </row>
-    <row r="44" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -75457,8 +75950,11 @@
       <c r="DA44" s="15">
         <v>1</v>
       </c>
+      <c r="DB44" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -75771,8 +76267,11 @@
       <c r="DA45" s="15">
         <v>10</v>
       </c>
+      <c r="DB45" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="46" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -76085,8 +76584,11 @@
       <c r="DA46" s="15">
         <v>9</v>
       </c>
+      <c r="DB46" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -76399,8 +76901,11 @@
       <c r="DA47" s="15">
         <v>0</v>
       </c>
+      <c r="DB47" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -76713,10 +77218,13 @@
       <c r="DA48" s="15">
         <v>7</v>
       </c>
+      <c r="DB48" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="77" t="s">
+      <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -77028,9 +77536,12 @@
       <c r="DA49" s="15">
         <v>0</v>
       </c>
+      <c r="DB49" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:105" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="78"/>
+    <row r="50" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -77340,8 +77851,11 @@
       <c r="DA50" s="15">
         <v>8</v>
       </c>
+      <c r="DB50" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="51" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -77654,8 +78168,11 @@
       <c r="DA51" s="15">
         <v>0</v>
       </c>
+      <c r="DB51" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -77968,8 +78485,11 @@
       <c r="DA52" s="15">
         <v>8</v>
       </c>
+      <c r="DB52" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -78282,8 +78802,11 @@
       <c r="DA53" s="15">
         <v>14</v>
       </c>
+      <c r="DB53" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="54" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -78596,8 +79119,11 @@
       <c r="DA54" s="15">
         <v>4</v>
       </c>
+      <c r="DB54" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -78910,8 +79436,11 @@
       <c r="DA55" s="15">
         <v>3</v>
       </c>
+      <c r="DB55" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -79224,8 +79753,11 @@
       <c r="DA56" s="15">
         <v>0</v>
       </c>
+      <c r="DB56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -79538,8 +80070,11 @@
       <c r="DA57" s="15">
         <v>0</v>
       </c>
+      <c r="DB57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -79952,8 +80487,12 @@
         <f t="shared" si="8"/>
         <v>632</v>
       </c>
+      <c r="DB58" s="14">
+        <f t="shared" ref="DB58" si="10">SUM(DB6:DB57)</f>
+        <v>578</v>
+      </c>
     </row>
-    <row r="59" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -79986,7 +80525,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -80019,7 +80558,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:105" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -80053,10 +80592,11 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="115">
+  <mergeCells count="116">
+    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="BD2:DB2"/>
+    <mergeCell ref="CR3:DB3"/>
     <mergeCell ref="DA4:DA5"/>
-    <mergeCell ref="BD2:DA2"/>
-    <mergeCell ref="CR3:DA3"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CW4:CW5"/>
@@ -80077,6 +80617,8 @@
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="BC4:BC5"/>
     <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BF4:BF5"/>
+    <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="AS4:AS5"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="AB4:AB5"/>
@@ -80099,8 +80641,6 @@
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="X4:X5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BT4:BT5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="AU4:AU5"/>
@@ -80121,8 +80661,13 @@
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="BF4:BF5"/>
-    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="BY4:BY5"/>
+    <mergeCell ref="BL4:BL5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="CP4:CP5"/>
     <mergeCell ref="CG4:CG5"/>
@@ -80138,15 +80683,8 @@
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="CH4:CH5"/>
     <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="BM4:BM5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="CY4:CY5"/>
-    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BT4:BT5"/>
     <mergeCell ref="BD3:CQ3"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AM4:AM5"/>
@@ -80169,31 +80707,32 @@
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="AW4:AW5"/>
     <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="BR4:BR5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="CH6:CX57 CZ6:CZ57 DA10">
-    <cfRule type="containsBlanks" dxfId="6" priority="4">
+    <cfRule type="containsBlanks" dxfId="8" priority="7">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY6:CY57">
-    <cfRule type="containsBlanks" dxfId="5" priority="2">
+    <cfRule type="containsBlanks" dxfId="7" priority="5">
       <formula>LEN(TRIM(CY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
-  <colBreaks count="3" manualBreakCount="3">
+  <colBreaks count="2" manualBreakCount="2">
     <brk id="55" max="66" man="1"/>
     <brk id="95" max="66" man="1"/>
-    <brk id="105" max="66" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="5" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="8" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -80206,7 +80745,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="15" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="18" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -80217,6 +80756,19 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="2" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DB6:DB57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -80322,10 +80874,10 @@
       <c r="CX1" s="19"/>
       <c r="CY1" s="19"/>
       <c r="CZ1" s="19"/>
-      <c r="DA1" s="19" t="s">
+      <c r="DA1" s="19"/>
+      <c r="DB1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="DB1" s="19"/>
     </row>
     <row r="2" spans="1:110" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
@@ -80383,7 +80935,7 @@
       <c r="AZ2" s="51"/>
       <c r="BA2" s="51"/>
       <c r="BB2" s="51"/>
-      <c r="BC2" s="84"/>
+      <c r="BC2" s="85"/>
       <c r="BD2" s="73" t="s">
         <v>325</v>
       </c>
@@ -80436,7 +80988,7 @@
       <c r="CY2" s="73"/>
       <c r="CZ2" s="73"/>
       <c r="DA2" s="73"/>
-      <c r="DB2" s="20"/>
+      <c r="DB2" s="73"/>
       <c r="DC2" s="20"/>
       <c r="DD2" s="20"/>
       <c r="DE2" s="20"/>
@@ -80445,48 +80997,48 @@
     <row r="3" spans="1:110" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86"/>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="86"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="86"/>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86"/>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="86"/>
-      <c r="AM3" s="86"/>
-      <c r="AN3" s="86"/>
-      <c r="AO3" s="86"/>
-      <c r="AP3" s="86"/>
-      <c r="AQ3" s="86"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
+      <c r="U3" s="87"/>
+      <c r="V3" s="87"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="87"/>
+      <c r="AM3" s="87"/>
+      <c r="AN3" s="87"/>
+      <c r="AO3" s="87"/>
+      <c r="AP3" s="87"/>
+      <c r="AQ3" s="87"/>
       <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
@@ -80555,7 +81107,7 @@
       <c r="CY3" s="45"/>
       <c r="CZ3" s="45"/>
       <c r="DA3" s="45"/>
-      <c r="DB3" s="21"/>
+      <c r="DB3" s="45"/>
       <c r="DC3" s="21"/>
       <c r="DD3" s="21"/>
       <c r="DE3" s="21"/>
@@ -80874,11 +81426,13 @@
       <c r="DA4" s="44" t="s">
         <v>433</v>
       </c>
-      <c r="DB4" s="87"/>
-      <c r="DC4" s="87"/>
-      <c r="DD4" s="87"/>
-      <c r="DE4" s="87"/>
-      <c r="DF4" s="87"/>
+      <c r="DB4" s="44" t="s">
+        <v>435</v>
+      </c>
+      <c r="DC4" s="88"/>
+      <c r="DD4" s="88"/>
+      <c r="DE4" s="88"/>
+      <c r="DF4" s="88"/>
     </row>
     <row r="5" spans="1:110" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
@@ -80985,11 +81539,11 @@
       <c r="CY5" s="44"/>
       <c r="CZ5" s="44"/>
       <c r="DA5" s="44"/>
-      <c r="DB5" s="87"/>
-      <c r="DC5" s="87"/>
-      <c r="DD5" s="87"/>
-      <c r="DE5" s="87"/>
-      <c r="DF5" s="87"/>
+      <c r="DB5" s="44"/>
+      <c r="DC5" s="88"/>
+      <c r="DD5" s="88"/>
+      <c r="DE5" s="88"/>
+      <c r="DF5" s="88"/>
     </row>
     <row r="6" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
@@ -81305,7 +81859,9 @@
       <c r="DA6" s="28">
         <v>91</v>
       </c>
-      <c r="DB6" s="22"/>
+      <c r="DB6" s="28">
+        <v>90</v>
+      </c>
       <c r="DC6" s="22"/>
       <c r="DD6" s="22"/>
       <c r="DE6" s="22"/>
@@ -81624,7 +82180,9 @@
       <c r="DA7" s="15">
         <v>0</v>
       </c>
-      <c r="DB7" s="23"/>
+      <c r="DB7" s="15">
+        <v>1</v>
+      </c>
       <c r="DC7" s="23"/>
       <c r="DD7" s="23"/>
       <c r="DE7" s="23"/>
@@ -81943,7 +82501,9 @@
       <c r="DA8" s="28">
         <v>20</v>
       </c>
-      <c r="DB8" s="23"/>
+      <c r="DB8" s="28">
+        <v>21</v>
+      </c>
       <c r="DC8" s="23"/>
       <c r="DD8" s="23"/>
       <c r="DE8" s="23"/>
@@ -82263,7 +82823,9 @@
       <c r="DA9" s="28">
         <v>70</v>
       </c>
-      <c r="DB9" s="23"/>
+      <c r="DB9" s="28">
+        <v>63</v>
+      </c>
       <c r="DC9" s="23"/>
       <c r="DD9" s="23"/>
       <c r="DE9" s="23"/>
@@ -82582,7 +83144,9 @@
       <c r="DA10" s="15">
         <v>0</v>
       </c>
-      <c r="DB10" s="23"/>
+      <c r="DB10" s="28">
+        <v>0</v>
+      </c>
       <c r="DC10" s="23"/>
       <c r="DD10" s="23"/>
       <c r="DE10" s="23"/>
@@ -82901,7 +83465,9 @@
       <c r="DA11" s="28">
         <v>4</v>
       </c>
-      <c r="DB11" s="23"/>
+      <c r="DB11" s="28">
+        <v>5</v>
+      </c>
       <c r="DC11" s="23"/>
       <c r="DD11" s="23"/>
       <c r="DE11" s="23"/>
@@ -83220,7 +83786,9 @@
       <c r="DA12" s="15">
         <v>10</v>
       </c>
-      <c r="DB12" s="23"/>
+      <c r="DB12" s="15">
+        <v>6</v>
+      </c>
       <c r="DC12" s="23"/>
       <c r="DD12" s="23"/>
       <c r="DE12" s="23"/>
@@ -83539,7 +84107,9 @@
       <c r="DA13" s="15">
         <v>13</v>
       </c>
-      <c r="DB13" s="22"/>
+      <c r="DB13" s="15">
+        <v>15</v>
+      </c>
       <c r="DC13" s="22"/>
       <c r="DD13" s="22"/>
       <c r="DE13" s="22"/>
@@ -83858,7 +84428,9 @@
       <c r="DA14" s="15">
         <v>10</v>
       </c>
-      <c r="DB14" s="23"/>
+      <c r="DB14" s="15">
+        <v>16</v>
+      </c>
       <c r="DC14" s="23"/>
       <c r="DD14" s="23"/>
       <c r="DE14" s="23"/>
@@ -84177,7 +84749,9 @@
       <c r="DA15" s="15">
         <v>4</v>
       </c>
-      <c r="DB15" s="23"/>
+      <c r="DB15" s="15">
+        <v>5</v>
+      </c>
       <c r="DC15" s="23"/>
       <c r="DD15" s="23"/>
       <c r="DE15" s="23"/>
@@ -84497,7 +85071,9 @@
       <c r="DA16" s="28">
         <v>136</v>
       </c>
-      <c r="DB16" s="22"/>
+      <c r="DB16" s="28">
+        <v>101</v>
+      </c>
       <c r="DC16" s="22"/>
       <c r="DD16" s="22"/>
       <c r="DE16" s="22"/>
@@ -84816,7 +85392,9 @@
       <c r="DA17" s="15">
         <v>130</v>
       </c>
-      <c r="DB17" s="22"/>
+      <c r="DB17" s="15">
+        <v>100</v>
+      </c>
       <c r="DC17" s="22"/>
       <c r="DD17" s="22"/>
       <c r="DE17" s="22"/>
@@ -85136,7 +85714,9 @@
       <c r="DA18" s="34">
         <v>1476</v>
       </c>
-      <c r="DB18" s="22"/>
+      <c r="DB18" s="34">
+        <v>1369</v>
+      </c>
       <c r="DC18" s="22"/>
       <c r="DD18" s="22"/>
       <c r="DE18" s="22"/>
@@ -85144,7 +85724,7 @@
     </row>
     <row r="19" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -85456,7 +86036,9 @@
       <c r="DA19" s="15">
         <v>35</v>
       </c>
-      <c r="DB19" s="22"/>
+      <c r="DB19" s="15">
+        <v>31</v>
+      </c>
       <c r="DC19" s="22"/>
       <c r="DD19" s="22"/>
       <c r="DE19" s="22"/>
@@ -85464,7 +86046,7 @@
     </row>
     <row r="20" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="81"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -85774,7 +86356,9 @@
       <c r="DA20" s="28">
         <v>68</v>
       </c>
-      <c r="DB20" s="22"/>
+      <c r="DB20" s="28">
+        <v>63</v>
+      </c>
       <c r="DC20" s="22"/>
       <c r="DD20" s="22"/>
       <c r="DE20" s="22"/>
@@ -85782,7 +86366,7 @@
     </row>
     <row r="21" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="78"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -86092,7 +86676,9 @@
       <c r="DA21" s="15">
         <v>20</v>
       </c>
-      <c r="DB21" s="22"/>
+      <c r="DB21" s="15">
+        <v>11</v>
+      </c>
       <c r="DC21" s="22"/>
       <c r="DD21" s="22"/>
       <c r="DE21" s="22"/>
@@ -86411,7 +86997,9 @@
       <c r="DA22" s="15">
         <v>1</v>
       </c>
-      <c r="DB22" s="23"/>
+      <c r="DB22" s="15">
+        <v>4</v>
+      </c>
       <c r="DC22" s="23"/>
       <c r="DD22" s="23"/>
       <c r="DE22" s="23"/>
@@ -86730,7 +87318,9 @@
       <c r="DA23" s="15">
         <v>0</v>
       </c>
-      <c r="DB23" s="23"/>
+      <c r="DB23" s="15">
+        <v>0</v>
+      </c>
       <c r="DC23" s="23"/>
       <c r="DD23" s="23"/>
       <c r="DE23" s="23"/>
@@ -87049,7 +87639,9 @@
       <c r="DA24" s="15">
         <v>3</v>
       </c>
-      <c r="DB24" s="22"/>
+      <c r="DB24" s="15">
+        <v>11</v>
+      </c>
       <c r="DC24" s="22"/>
       <c r="DD24" s="22"/>
       <c r="DE24" s="22"/>
@@ -87368,7 +87960,9 @@
       <c r="DA25" s="15">
         <v>0</v>
       </c>
-      <c r="DB25" s="23"/>
+      <c r="DB25" s="15">
+        <v>1</v>
+      </c>
       <c r="DC25" s="23"/>
       <c r="DD25" s="23"/>
       <c r="DE25" s="23"/>
@@ -87687,7 +88281,9 @@
       <c r="DA26" s="15">
         <v>11</v>
       </c>
-      <c r="DB26" s="23"/>
+      <c r="DB26" s="15">
+        <v>12</v>
+      </c>
       <c r="DC26" s="23"/>
       <c r="DD26" s="23"/>
       <c r="DE26" s="23"/>
@@ -88006,7 +88602,9 @@
       <c r="DA27" s="15">
         <v>0</v>
       </c>
-      <c r="DB27" s="23"/>
+      <c r="DB27" s="15">
+        <v>0</v>
+      </c>
       <c r="DC27" s="23"/>
       <c r="DD27" s="23"/>
       <c r="DE27" s="23"/>
@@ -88325,14 +88923,16 @@
       <c r="DA28" s="15">
         <v>1</v>
       </c>
-      <c r="DB28" s="22"/>
+      <c r="DB28" s="15">
+        <v>2</v>
+      </c>
       <c r="DC28" s="22"/>
       <c r="DD28" s="22"/>
       <c r="DE28" s="22"/>
       <c r="DF28" s="22"/>
     </row>
     <row r="29" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -88644,14 +89244,16 @@
       <c r="DA29" s="15">
         <v>0</v>
       </c>
-      <c r="DB29" s="23"/>
+      <c r="DB29" s="15">
+        <v>1</v>
+      </c>
       <c r="DC29" s="23"/>
       <c r="DD29" s="23"/>
       <c r="DE29" s="23"/>
       <c r="DF29" s="23"/>
     </row>
     <row r="30" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="83"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -88961,7 +89563,9 @@
       <c r="DA30" s="15">
         <v>12</v>
       </c>
-      <c r="DB30" s="23"/>
+      <c r="DB30" s="15">
+        <v>18</v>
+      </c>
       <c r="DC30" s="23"/>
       <c r="DD30" s="23"/>
       <c r="DE30" s="23"/>
@@ -89281,7 +89885,9 @@
       <c r="DA31" s="15">
         <v>42</v>
       </c>
-      <c r="DB31" s="22"/>
+      <c r="DB31" s="15">
+        <v>37</v>
+      </c>
       <c r="DC31" s="22"/>
       <c r="DD31" s="22"/>
       <c r="DE31" s="22"/>
@@ -89600,7 +90206,9 @@
       <c r="DA32" s="15">
         <v>0</v>
       </c>
-      <c r="DB32" s="23"/>
+      <c r="DB32" s="15">
+        <v>1</v>
+      </c>
       <c r="DC32" s="23"/>
       <c r="DD32" s="23"/>
       <c r="DE32" s="23"/>
@@ -89919,7 +90527,9 @@
       <c r="DA33" s="15">
         <v>0</v>
       </c>
-      <c r="DB33" s="23"/>
+      <c r="DB33" s="15">
+        <v>0</v>
+      </c>
       <c r="DC33" s="23"/>
       <c r="DD33" s="23"/>
       <c r="DE33" s="23"/>
@@ -90239,7 +90849,9 @@
       <c r="DA34" s="15">
         <v>67</v>
       </c>
-      <c r="DB34" s="22"/>
+      <c r="DB34" s="15">
+        <v>62</v>
+      </c>
       <c r="DC34" s="22"/>
       <c r="DD34" s="22"/>
       <c r="DE34" s="22"/>
@@ -90247,7 +90859,7 @@
     </row>
     <row r="35" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -90559,14 +91171,16 @@
       <c r="DA35" s="15">
         <v>223</v>
       </c>
-      <c r="DB35" s="22"/>
+      <c r="DB35" s="15">
+        <v>238</v>
+      </c>
       <c r="DC35" s="22"/>
       <c r="DD35" s="22"/>
       <c r="DE35" s="22"/>
       <c r="DF35" s="22"/>
     </row>
     <row r="36" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="78"/>
+      <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -90876,7 +91490,9 @@
       <c r="DA36" s="28">
         <v>31</v>
       </c>
-      <c r="DB36" s="22"/>
+      <c r="DB36" s="28">
+        <v>18</v>
+      </c>
       <c r="DC36" s="22"/>
       <c r="DD36" s="22"/>
       <c r="DE36" s="22"/>
@@ -91196,7 +91812,9 @@
       <c r="DA37" s="15">
         <v>39</v>
       </c>
-      <c r="DB37" s="22"/>
+      <c r="DB37" s="15">
+        <v>57</v>
+      </c>
       <c r="DC37" s="22"/>
       <c r="DD37" s="22"/>
       <c r="DE37" s="22"/>
@@ -91515,7 +92133,9 @@
       <c r="DA38" s="15">
         <v>7</v>
       </c>
-      <c r="DB38" s="23"/>
+      <c r="DB38" s="15">
+        <v>6</v>
+      </c>
       <c r="DC38" s="23"/>
       <c r="DD38" s="23"/>
       <c r="DE38" s="23"/>
@@ -91834,7 +92454,9 @@
       <c r="DA39" s="15">
         <v>4</v>
       </c>
-      <c r="DB39" s="23"/>
+      <c r="DB39" s="15">
+        <v>5</v>
+      </c>
       <c r="DC39" s="23"/>
       <c r="DD39" s="23"/>
       <c r="DE39" s="23"/>
@@ -92153,7 +92775,9 @@
       <c r="DA40" s="15">
         <v>0</v>
       </c>
-      <c r="DB40" s="23"/>
+      <c r="DB40" s="15">
+        <v>0</v>
+      </c>
       <c r="DC40" s="23"/>
       <c r="DD40" s="23"/>
       <c r="DE40" s="23"/>
@@ -92472,7 +93096,9 @@
       <c r="DA41" s="15">
         <v>0</v>
       </c>
-      <c r="DB41" s="23"/>
+      <c r="DB41" s="15">
+        <v>0</v>
+      </c>
       <c r="DC41" s="23"/>
       <c r="DD41" s="23"/>
       <c r="DE41" s="23"/>
@@ -92791,7 +93417,9 @@
       <c r="DA42" s="15">
         <v>5</v>
       </c>
-      <c r="DB42" s="23"/>
+      <c r="DB42" s="15">
+        <v>9</v>
+      </c>
       <c r="DC42" s="23"/>
       <c r="DD42" s="23"/>
       <c r="DE42" s="23"/>
@@ -93110,7 +93738,9 @@
       <c r="DA43" s="28">
         <v>30</v>
       </c>
-      <c r="DB43" s="23"/>
+      <c r="DB43" s="28">
+        <v>32</v>
+      </c>
       <c r="DC43" s="23"/>
       <c r="DD43" s="23"/>
       <c r="DE43" s="23"/>
@@ -93429,7 +94059,9 @@
       <c r="DA44" s="15">
         <v>2</v>
       </c>
-      <c r="DB44" s="23"/>
+      <c r="DB44" s="15">
+        <v>1</v>
+      </c>
       <c r="DC44" s="23"/>
       <c r="DD44" s="23"/>
       <c r="DE44" s="23"/>
@@ -93748,7 +94380,9 @@
       <c r="DA45" s="15">
         <v>15</v>
       </c>
-      <c r="DB45" s="22"/>
+      <c r="DB45" s="15">
+        <v>13</v>
+      </c>
       <c r="DC45" s="22"/>
       <c r="DD45" s="22"/>
       <c r="DE45" s="22"/>
@@ -94067,7 +94701,9 @@
       <c r="DA46" s="15">
         <v>19</v>
       </c>
-      <c r="DB46" s="23"/>
+      <c r="DB46" s="15">
+        <v>15</v>
+      </c>
       <c r="DC46" s="23"/>
       <c r="DD46" s="23"/>
       <c r="DE46" s="23"/>
@@ -94386,7 +95022,9 @@
       <c r="DA47" s="15">
         <v>1</v>
       </c>
-      <c r="DB47" s="23"/>
+      <c r="DB47" s="15">
+        <v>1</v>
+      </c>
       <c r="DC47" s="23"/>
       <c r="DD47" s="23"/>
       <c r="DE47" s="23"/>
@@ -94705,7 +95343,9 @@
       <c r="DA48" s="15">
         <v>2</v>
       </c>
-      <c r="DB48" s="23"/>
+      <c r="DB48" s="15">
+        <v>13</v>
+      </c>
       <c r="DC48" s="23"/>
       <c r="DD48" s="23"/>
       <c r="DE48" s="23"/>
@@ -94713,7 +95353,7 @@
     </row>
     <row r="49" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="77" t="s">
+      <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -95025,14 +95665,16 @@
       <c r="DA49" s="15">
         <v>44</v>
       </c>
-      <c r="DB49" s="22"/>
+      <c r="DB49" s="15">
+        <v>39</v>
+      </c>
       <c r="DC49" s="22"/>
       <c r="DD49" s="22"/>
       <c r="DE49" s="22"/>
       <c r="DF49" s="22"/>
     </row>
     <row r="50" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="78"/>
+      <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -95342,7 +95984,9 @@
       <c r="DA50" s="15">
         <v>8</v>
       </c>
-      <c r="DB50" s="22"/>
+      <c r="DB50" s="15">
+        <v>19</v>
+      </c>
       <c r="DC50" s="22"/>
       <c r="DD50" s="22"/>
       <c r="DE50" s="22"/>
@@ -95661,7 +96305,9 @@
       <c r="DA51" s="15">
         <v>8</v>
       </c>
-      <c r="DB51" s="23"/>
+      <c r="DB51" s="15">
+        <v>7</v>
+      </c>
       <c r="DC51" s="23"/>
       <c r="DD51" s="23"/>
       <c r="DE51" s="23"/>
@@ -95980,7 +96626,9 @@
       <c r="DA52" s="15">
         <v>22</v>
       </c>
-      <c r="DB52" s="23"/>
+      <c r="DB52" s="15">
+        <v>22</v>
+      </c>
       <c r="DC52" s="23"/>
       <c r="DD52" s="23"/>
       <c r="DE52" s="23"/>
@@ -96299,7 +96947,9 @@
       <c r="DA53" s="15">
         <v>42</v>
       </c>
-      <c r="DB53" s="23"/>
+      <c r="DB53" s="15">
+        <v>41</v>
+      </c>
       <c r="DC53" s="23"/>
       <c r="DD53" s="23"/>
       <c r="DE53" s="23"/>
@@ -96618,7 +97268,9 @@
       <c r="DA54" s="15">
         <v>5</v>
       </c>
-      <c r="DB54" s="23"/>
+      <c r="DB54" s="15">
+        <v>2</v>
+      </c>
       <c r="DC54" s="23"/>
       <c r="DD54" s="23"/>
       <c r="DE54" s="23"/>
@@ -96937,7 +97589,9 @@
       <c r="DA55" s="15">
         <v>16</v>
       </c>
-      <c r="DB55" s="23"/>
+      <c r="DB55" s="15">
+        <v>24</v>
+      </c>
       <c r="DC55" s="23"/>
       <c r="DD55" s="23"/>
       <c r="DE55" s="23"/>
@@ -97256,7 +97910,9 @@
       <c r="DA56" s="15">
         <v>1</v>
       </c>
-      <c r="DB56" s="23"/>
+      <c r="DB56" s="15">
+        <v>3</v>
+      </c>
       <c r="DC56" s="23"/>
       <c r="DD56" s="23"/>
       <c r="DE56" s="23"/>
@@ -97575,7 +98231,9 @@
       <c r="DA57" s="15">
         <v>5</v>
       </c>
-      <c r="DB57" s="23"/>
+      <c r="DB57" s="15">
+        <v>0</v>
+      </c>
       <c r="DC57" s="23"/>
       <c r="DD57" s="23"/>
       <c r="DE57" s="23"/>
@@ -97994,7 +98652,10 @@
         <f t="shared" si="4"/>
         <v>2753</v>
       </c>
-      <c r="DB58" s="24"/>
+      <c r="DB58" s="14">
+        <f t="shared" ref="DB58" si="6">SUM(DB6:DB57)</f>
+        <v>2611</v>
+      </c>
       <c r="DC58" s="24"/>
       <c r="DD58" s="24"/>
       <c r="DE58" s="24"/>
@@ -98101,8 +98762,8 @@
     </row>
   </sheetData>
   <mergeCells count="120">
-    <mergeCell ref="BD2:DA2"/>
-    <mergeCell ref="CR3:DA3"/>
+    <mergeCell ref="BD2:DB2"/>
+    <mergeCell ref="CR3:DB3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -98234,7 +98895,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="5" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="8" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98247,7 +98908,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="24" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="27" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98260,7 +98921,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="1" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
+          <x14:cfRule type="containsBlanks" priority="4" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
             <xm:f>LEN(TRIM('うちコロナ疑い事案（今回）'!DA10))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98272,6 +98933,19 @@
           </x14:cfRule>
           <xm:sqref>DA10</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="2" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DB6:DB57</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050322-1\ＪＯＢ050322-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050328-1\ＪＯＢ050328-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="11055"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DB$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DB$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FB$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FB$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DC$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DC$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FC$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FC$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="439">
   <si>
     <t>都道府県</t>
   </si>
@@ -4644,6 +4644,18 @@
 【3月第3週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>3/20(月)～
+3/26(日)分
+【3月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3/21(月)～
+3/27(日)分
+【3月第4週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5282,7 +5294,21 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5381,6 +5407,21 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -9528,7 +9569,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FB61"/>
+  <dimension ref="A1:FC61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9542,11 +9583,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="158" width="10.875" style="1" customWidth="1"/>
-    <col min="159" max="16384" width="8.625" style="1"/>
+    <col min="106" max="159" width="10.875" style="1" customWidth="1"/>
+    <col min="160" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:158" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:159" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9631,11 +9672,12 @@
       <c r="EY1" s="19"/>
       <c r="EZ1" s="19"/>
       <c r="FA1" s="19"/>
-      <c r="FB1" s="19" t="s">
+      <c r="FB1" s="19"/>
+      <c r="FC1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:158" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:159" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
       <c r="C2" s="60"/>
       <c r="D2" s="58" t="s">
@@ -9799,8 +9841,9 @@
       <c r="EZ2" s="73"/>
       <c r="FA2" s="73"/>
       <c r="FB2" s="73"/>
+      <c r="FC2" s="73"/>
     </row>
-    <row r="3" spans="1:158" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:159" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="45" t="s">
@@ -9970,8 +10013,9 @@
       <c r="EZ3" s="45"/>
       <c r="FA3" s="45"/>
       <c r="FB3" s="45"/>
+      <c r="FC3" s="45"/>
     </row>
-    <row r="4" spans="1:158" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:159" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
         <v>0</v>
       </c>
@@ -10443,8 +10487,11 @@
       <c r="FB4" s="44" t="s">
         <v>435</v>
       </c>
+      <c r="FC4" s="44" t="s">
+        <v>437</v>
+      </c>
     </row>
-    <row r="5" spans="1:158" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:159" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
       <c r="D5" s="54"/>
@@ -10602,8 +10649,9 @@
       <c r="EZ5" s="44"/>
       <c r="FA5" s="44"/>
       <c r="FB5" s="44"/>
+      <c r="FC5" s="44"/>
     </row>
-    <row r="6" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -11076,8 +11124,11 @@
       <c r="FB6" s="28">
         <v>117</v>
       </c>
+      <c r="FC6" s="28">
+        <v>99</v>
+      </c>
     </row>
-    <row r="7" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11549,8 +11600,11 @@
       <c r="FB7" s="15">
         <v>1</v>
       </c>
+      <c r="FC7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -12022,8 +12076,11 @@
       <c r="FB8" s="28">
         <v>21</v>
       </c>
+      <c r="FC8" s="28">
+        <v>17</v>
+      </c>
     </row>
-    <row r="9" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12496,8 +12553,11 @@
       <c r="FB9" s="15">
         <v>65</v>
       </c>
+      <c r="FC9" s="15">
+        <v>63</v>
+      </c>
     </row>
-    <row r="10" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -12967,8 +13027,11 @@
       <c r="FB10" s="15">
         <v>0</v>
       </c>
+      <c r="FC10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13440,8 +13503,11 @@
       <c r="FB11" s="15">
         <v>6</v>
       </c>
+      <c r="FC11" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13913,8 +13979,11 @@
       <c r="FB12" s="15">
         <v>6</v>
       </c>
+      <c r="FC12" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14386,8 +14455,11 @@
       <c r="FB13" s="15">
         <v>24</v>
       </c>
+      <c r="FC13" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="14" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14859,8 +14931,11 @@
       <c r="FB14" s="15">
         <v>21</v>
       </c>
+      <c r="FC14" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -15332,8 +15407,11 @@
       <c r="FB15" s="15">
         <v>7</v>
       </c>
+      <c r="FC15" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15806,8 +15884,11 @@
       <c r="FB16" s="28">
         <v>102</v>
       </c>
+      <c r="FC16" s="28">
+        <v>110</v>
+      </c>
     </row>
-    <row r="17" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -16279,8 +16360,11 @@
       <c r="FB17" s="15">
         <v>136</v>
       </c>
+      <c r="FC17" s="15">
+        <v>130</v>
+      </c>
     </row>
-    <row r="18" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16753,8 +16837,11 @@
       <c r="FB18" s="34">
         <v>1597</v>
       </c>
+      <c r="FC18" s="34">
+        <v>1778</v>
+      </c>
     </row>
-    <row r="19" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="69" t="s">
         <v>27</v>
@@ -17227,8 +17314,11 @@
       <c r="FB19" s="15">
         <v>55</v>
       </c>
+      <c r="FC19" s="15">
+        <v>58</v>
+      </c>
     </row>
-    <row r="20" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="69"/>
       <c r="C20" s="9" t="s">
@@ -17699,8 +17789,11 @@
       <c r="FB20" s="28">
         <v>115</v>
       </c>
+      <c r="FC20" s="28">
+        <v>107</v>
+      </c>
     </row>
-    <row r="21" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="69"/>
       <c r="C21" s="9" t="s">
@@ -18171,8 +18264,11 @@
       <c r="FB21" s="15">
         <v>22</v>
       </c>
+      <c r="FC21" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="22" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18644,8 +18740,11 @@
       <c r="FB22" s="15">
         <v>4</v>
       </c>
+      <c r="FC22" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -19117,8 +19216,11 @@
       <c r="FB23" s="15">
         <v>0</v>
       </c>
+      <c r="FC23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19590,8 +19692,11 @@
       <c r="FB24" s="15">
         <v>12</v>
       </c>
+      <c r="FC24" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -20063,8 +20168,11 @@
       <c r="FB25" s="15">
         <v>1</v>
       </c>
+      <c r="FC25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -20536,8 +20644,11 @@
       <c r="FB26" s="15">
         <v>14</v>
       </c>
+      <c r="FC26" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="27" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -21009,8 +21120,11 @@
       <c r="FB27" s="15">
         <v>0</v>
       </c>
+      <c r="FC27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -21482,8 +21596,11 @@
       <c r="FB28" s="15">
         <v>2</v>
       </c>
+      <c r="FC28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="70" t="s">
         <v>45</v>
       </c>
@@ -21955,8 +22072,11 @@
       <c r="FB29" s="15">
         <v>1</v>
       </c>
+      <c r="FC29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="70"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -22426,8 +22546,11 @@
       <c r="FB30" s="15">
         <v>21</v>
       </c>
+      <c r="FC30" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="31" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -22900,8 +23023,11 @@
       <c r="FB31" s="15">
         <v>50</v>
       </c>
+      <c r="FC31" s="15">
+        <v>46</v>
+      </c>
     </row>
-    <row r="32" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -23373,8 +23499,11 @@
       <c r="FB32" s="15">
         <v>1</v>
       </c>
+      <c r="FC32" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -23846,8 +23975,11 @@
       <c r="FB33" s="15">
         <v>0</v>
       </c>
+      <c r="FC33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -24320,8 +24452,11 @@
       <c r="FB34" s="15">
         <v>70</v>
       </c>
+      <c r="FC34" s="15">
+        <v>85</v>
+      </c>
     </row>
-    <row r="35" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="69" t="s">
         <v>56</v>
@@ -24794,8 +24929,11 @@
       <c r="FB35" s="15">
         <v>289</v>
       </c>
+      <c r="FC35" s="15">
+        <v>277</v>
+      </c>
     </row>
-    <row r="36" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="69"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -25265,8 +25403,11 @@
       <c r="FB36" s="28">
         <v>33</v>
       </c>
+      <c r="FC36" s="28">
+        <v>24</v>
+      </c>
     </row>
-    <row r="37" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -25739,8 +25880,11 @@
       <c r="FB37" s="15">
         <v>67</v>
       </c>
+      <c r="FC37" s="15">
+        <v>48</v>
+      </c>
     </row>
-    <row r="38" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -26212,8 +26356,11 @@
       <c r="FB38" s="15">
         <v>7</v>
       </c>
+      <c r="FC38" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="39" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -26685,8 +26832,11 @@
       <c r="FB39" s="15">
         <v>8</v>
       </c>
+      <c r="FC39" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="40" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -27158,8 +27308,11 @@
       <c r="FB40" s="15">
         <v>0</v>
       </c>
+      <c r="FC40" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -27631,8 +27784,11 @@
       <c r="FB41" s="15">
         <v>0</v>
       </c>
+      <c r="FC41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -28104,8 +28260,11 @@
       <c r="FB42" s="15">
         <v>11</v>
       </c>
+      <c r="FC42" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -28577,8 +28736,11 @@
       <c r="FB43" s="28">
         <v>57</v>
       </c>
+      <c r="FC43" s="28">
+        <v>47</v>
+      </c>
     </row>
-    <row r="44" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -29050,8 +29212,11 @@
       <c r="FB44" s="15">
         <v>1</v>
       </c>
+      <c r="FC44" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -29523,8 +29688,11 @@
       <c r="FB45" s="15">
         <v>20</v>
       </c>
+      <c r="FC45" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="46" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -29996,8 +30164,11 @@
       <c r="FB46" s="15">
         <v>17</v>
       </c>
+      <c r="FC46" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="47" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -30469,8 +30640,11 @@
       <c r="FB47" s="15">
         <v>2</v>
       </c>
+      <c r="FC47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -30942,8 +31116,11 @@
       <c r="FB48" s="15">
         <v>23</v>
       </c>
+      <c r="FC48" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="49" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="69" t="s">
         <v>83</v>
@@ -31416,8 +31593,11 @@
       <c r="FB49" s="15">
         <v>40</v>
       </c>
+      <c r="FC49" s="15">
+        <v>39</v>
+      </c>
     </row>
-    <row r="50" spans="1:158" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="69"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -31887,8 +32067,11 @@
       <c r="FB50" s="15">
         <v>27</v>
       </c>
+      <c r="FC50" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="51" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -32360,8 +32543,11 @@
       <c r="FB51" s="15">
         <v>8</v>
       </c>
+      <c r="FC51" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="52" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -32833,8 +33019,11 @@
       <c r="FB52" s="15">
         <v>25</v>
       </c>
+      <c r="FC52" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -33306,8 +33495,11 @@
       <c r="FB53" s="15">
         <v>52</v>
       </c>
+      <c r="FC53" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="54" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -33779,8 +33971,11 @@
       <c r="FB54" s="15">
         <v>3</v>
       </c>
+      <c r="FC54" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -34252,8 +34447,11 @@
       <c r="FB55" s="15">
         <v>25</v>
       </c>
+      <c r="FC55" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="56" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -34725,8 +34923,11 @@
       <c r="FB56" s="15">
         <v>3</v>
       </c>
+      <c r="FC56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -35198,8 +35399,11 @@
       <c r="FB57" s="15">
         <v>0</v>
       </c>
+      <c r="FC57" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -35824,8 +36028,12 @@
         <f t="shared" si="12"/>
         <v>3189</v>
       </c>
+      <c r="FC58" s="14">
+        <f t="shared" ref="FC58" si="13">SUM(FC6:FC57)</f>
+        <v>3254</v>
+      </c>
     </row>
-    <row r="59" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -35909,7 +36117,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -35993,7 +36201,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:158" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -36078,10 +36286,11 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="172">
+  <mergeCells count="173">
+    <mergeCell ref="FC4:FC5"/>
+    <mergeCell ref="DE2:FC2"/>
+    <mergeCell ref="ER3:FC3"/>
     <mergeCell ref="FB4:FB5"/>
-    <mergeCell ref="DE2:FB2"/>
-    <mergeCell ref="ER3:FB3"/>
     <mergeCell ref="FA4:FA5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
@@ -36254,33 +36463,38 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="21" priority="6">
+    <cfRule type="containsBlanks" dxfId="25" priority="7">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="20" priority="5">
+    <cfRule type="containsBlanks" dxfId="24" priority="6">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="19" priority="4">
+    <cfRule type="containsBlanks" dxfId="23" priority="5">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="18" priority="3">
+    <cfRule type="containsBlanks" dxfId="22" priority="4">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="17" priority="2">
+    <cfRule type="containsBlanks" dxfId="21" priority="3">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="16" priority="1">
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
       <formula>LEN(TRIM(FB6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FC6:FC57">
+    <cfRule type="containsBlanks" dxfId="19" priority="1">
+      <formula>LEN(TRIM(FC6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -36299,7 +36513,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:FB58"/>
+  <dimension ref="B1:FC58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -36319,16 +36533,17 @@
     <col min="44" max="44" width="11" style="4" customWidth="1"/>
     <col min="45" max="49" width="11" style="1" customWidth="1"/>
     <col min="50" max="51" width="11" style="4" customWidth="1"/>
-    <col min="52" max="55" width="11" style="1" customWidth="1"/>
+    <col min="52" max="54" width="11" style="1" customWidth="1"/>
+    <col min="55" max="55" width="11" style="4" customWidth="1"/>
     <col min="56" max="82" width="10.875" style="1" customWidth="1"/>
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="158" width="10.875" style="1" customWidth="1"/>
-    <col min="159" max="16384" width="8.625" style="1"/>
+    <col min="106" max="159" width="10.875" style="1" customWidth="1"/>
+    <col min="160" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:158" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:159" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="86" t="s">
         <v>323</v>
       </c>
@@ -36413,11 +36628,12 @@
       <c r="EY1" s="19"/>
       <c r="EZ1" s="19"/>
       <c r="FA1" s="19"/>
-      <c r="FB1" s="19" t="s">
+      <c r="FB1" s="19"/>
+      <c r="FC1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:158" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:159" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
       <c r="C2" s="60"/>
       <c r="D2" s="58" t="s">
@@ -36581,8 +36797,9 @@
       <c r="EZ2" s="73"/>
       <c r="FA2" s="73"/>
       <c r="FB2" s="73"/>
+      <c r="FC2" s="73"/>
     </row>
-    <row r="3" spans="2:158" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:159" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="47" t="s">
@@ -36752,8 +36969,9 @@
       <c r="EZ3" s="45"/>
       <c r="FA3" s="45"/>
       <c r="FB3" s="45"/>
+      <c r="FC3" s="45"/>
     </row>
-    <row r="4" spans="2:158" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:159" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
         <v>0</v>
       </c>
@@ -36913,7 +37131,7 @@
       <c r="BB4" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="75" t="s">
+      <c r="BC4" s="76" t="s">
         <v>184</v>
       </c>
       <c r="BD4" s="64" t="s">
@@ -37225,8 +37443,11 @@
       <c r="FB4" s="44" t="s">
         <v>436</v>
       </c>
+      <c r="FC4" s="44" t="s">
+        <v>438</v>
+      </c>
     </row>
-    <row r="5" spans="2:158" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:159" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
       <c r="D5" s="48"/>
@@ -37280,7 +37501,7 @@
       <c r="AZ5" s="48"/>
       <c r="BA5" s="48"/>
       <c r="BB5" s="48"/>
-      <c r="BC5" s="48"/>
+      <c r="BC5" s="77"/>
       <c r="BD5" s="54"/>
       <c r="BE5" s="54"/>
       <c r="BF5" s="54"/>
@@ -37384,8 +37605,9 @@
       <c r="EZ5" s="44"/>
       <c r="FA5" s="44"/>
       <c r="FB5" s="44"/>
+      <c r="FC5" s="44"/>
     </row>
-    <row r="6" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -37545,7 +37767,7 @@
       <c r="BB6" s="26">
         <v>47</v>
       </c>
-      <c r="BC6" s="26">
+      <c r="BC6" s="28">
         <v>36</v>
       </c>
       <c r="BD6" s="8">
@@ -37857,8 +38079,11 @@
       <c r="FB6" s="28">
         <v>117</v>
       </c>
+      <c r="FC6" s="28">
+        <v>88</v>
+      </c>
     </row>
-    <row r="7" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -38018,7 +38243,7 @@
       <c r="BB7" s="26">
         <v>0</v>
       </c>
-      <c r="BC7" s="26">
+      <c r="BC7" s="28">
         <v>1</v>
       </c>
       <c r="BD7" s="8">
@@ -38330,8 +38555,11 @@
       <c r="FB7" s="15">
         <v>4</v>
       </c>
+      <c r="FC7" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -38491,7 +38719,7 @@
       <c r="BB8" s="26">
         <v>3</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="28">
         <v>2</v>
       </c>
       <c r="BD8" s="8">
@@ -38803,8 +39031,11 @@
       <c r="FB8" s="28">
         <v>23</v>
       </c>
+      <c r="FC8" s="28">
+        <v>11</v>
+      </c>
     </row>
-    <row r="9" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -38964,7 +39195,7 @@
       <c r="BB9" s="26">
         <v>32</v>
       </c>
-      <c r="BC9" s="26">
+      <c r="BC9" s="28">
         <v>28</v>
       </c>
       <c r="BD9" s="8">
@@ -39276,8 +39507,11 @@
       <c r="FB9" s="15">
         <v>85</v>
       </c>
+      <c r="FC9" s="15">
+        <v>107</v>
+      </c>
     </row>
-    <row r="10" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -39437,7 +39671,7 @@
       <c r="BB10" s="26">
         <v>0</v>
       </c>
-      <c r="BC10" s="26">
+      <c r="BC10" s="28">
         <v>0</v>
       </c>
       <c r="BD10" s="8">
@@ -39749,8 +39983,11 @@
       <c r="FB10" s="15">
         <v>1</v>
       </c>
+      <c r="FC10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -39910,7 +40147,7 @@
       <c r="BB11" s="26">
         <v>3</v>
       </c>
-      <c r="BC11" s="26">
+      <c r="BC11" s="28">
         <v>3</v>
       </c>
       <c r="BD11" s="8">
@@ -40222,8 +40459,11 @@
       <c r="FB11" s="15">
         <v>8</v>
       </c>
+      <c r="FC11" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="12" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -40383,7 +40623,7 @@
       <c r="BB12" s="26">
         <v>0</v>
       </c>
-      <c r="BC12" s="26">
+      <c r="BC12" s="28">
         <v>2</v>
       </c>
       <c r="BD12" s="8">
@@ -40695,8 +40935,11 @@
       <c r="FB12" s="15">
         <v>3</v>
       </c>
+      <c r="FC12" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="13" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -40856,7 +41099,7 @@
       <c r="BB13" s="26">
         <v>18</v>
       </c>
-      <c r="BC13" s="26">
+      <c r="BC13" s="28">
         <v>8</v>
       </c>
       <c r="BD13" s="8">
@@ -41168,8 +41411,11 @@
       <c r="FB13" s="15">
         <v>30</v>
       </c>
+      <c r="FC13" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="14" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -41329,7 +41575,7 @@
       <c r="BB14" s="26">
         <v>4</v>
       </c>
-      <c r="BC14" s="26">
+      <c r="BC14" s="28">
         <v>4</v>
       </c>
       <c r="BD14" s="8">
@@ -41641,8 +41887,11 @@
       <c r="FB14" s="15">
         <v>18</v>
       </c>
+      <c r="FC14" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="15" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -41802,7 +42051,7 @@
       <c r="BB15" s="26">
         <v>1</v>
       </c>
-      <c r="BC15" s="26">
+      <c r="BC15" s="28">
         <v>2</v>
       </c>
       <c r="BD15" s="8">
@@ -42114,8 +42363,11 @@
       <c r="FB15" s="15">
         <v>3</v>
       </c>
+      <c r="FC15" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -42275,7 +42527,7 @@
       <c r="BB16" s="26">
         <v>25</v>
       </c>
-      <c r="BC16" s="26">
+      <c r="BC16" s="28">
         <v>25</v>
       </c>
       <c r="BD16" s="8">
@@ -42587,8 +42839,11 @@
       <c r="FB16" s="28">
         <v>144</v>
       </c>
+      <c r="FC16" s="28">
+        <v>109</v>
+      </c>
     </row>
-    <row r="17" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -42748,7 +43003,7 @@
       <c r="BB17" s="26">
         <v>63</v>
       </c>
-      <c r="BC17" s="26">
+      <c r="BC17" s="28">
         <v>79</v>
       </c>
       <c r="BD17" s="8">
@@ -43060,8 +43315,11 @@
       <c r="FB17" s="15">
         <v>147</v>
       </c>
+      <c r="FC17" s="15">
+        <v>150</v>
+      </c>
     </row>
-    <row r="18" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -43221,7 +43479,7 @@
       <c r="BB18" s="26">
         <v>449</v>
       </c>
-      <c r="BC18" s="26">
+      <c r="BC18" s="28">
         <v>497</v>
       </c>
       <c r="BD18" s="8">
@@ -43533,8 +43791,11 @@
       <c r="FB18" s="34">
         <v>1780</v>
       </c>
+      <c r="FC18" s="34">
+        <v>1751</v>
+      </c>
     </row>
-    <row r="19" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
@@ -43694,7 +43955,7 @@
       <c r="BB19" s="26">
         <v>13</v>
       </c>
-      <c r="BC19" s="26">
+      <c r="BC19" s="28">
         <v>9</v>
       </c>
       <c r="BD19" s="8">
@@ -44006,8 +44267,11 @@
       <c r="FB19" s="15">
         <v>67</v>
       </c>
+      <c r="FC19" s="15">
+        <v>53</v>
+      </c>
     </row>
-    <row r="20" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -44165,7 +44429,7 @@
       <c r="BB20" s="26">
         <v>42</v>
       </c>
-      <c r="BC20" s="26">
+      <c r="BC20" s="28">
         <v>57</v>
       </c>
       <c r="BD20" s="8">
@@ -44477,8 +44741,11 @@
       <c r="FB20" s="28">
         <v>216</v>
       </c>
+      <c r="FC20" s="28">
+        <v>192</v>
+      </c>
     </row>
-    <row r="21" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -44636,7 +44903,7 @@
       <c r="BB21" s="26">
         <v>20</v>
       </c>
-      <c r="BC21" s="26">
+      <c r="BC21" s="28">
         <v>9</v>
       </c>
       <c r="BD21" s="8">
@@ -44948,8 +45215,11 @@
       <c r="FB21" s="15">
         <v>51</v>
       </c>
+      <c r="FC21" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -45109,7 +45379,7 @@
       <c r="BB22" s="26">
         <v>20</v>
       </c>
-      <c r="BC22" s="26">
+      <c r="BC22" s="28">
         <v>11</v>
       </c>
       <c r="BD22" s="8">
@@ -45421,8 +45691,11 @@
       <c r="FB22" s="15">
         <v>16</v>
       </c>
+      <c r="FC22" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -45582,7 +45855,7 @@
       <c r="BB23" s="26">
         <v>0</v>
       </c>
-      <c r="BC23" s="26">
+      <c r="BC23" s="28">
         <v>1</v>
       </c>
       <c r="BD23" s="8">
@@ -45894,8 +46167,11 @@
       <c r="FB23" s="15">
         <v>0</v>
       </c>
+      <c r="FC23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -46055,7 +46331,7 @@
       <c r="BB24" s="26">
         <v>1</v>
       </c>
-      <c r="BC24" s="26">
+      <c r="BC24" s="28">
         <v>3</v>
       </c>
       <c r="BD24" s="8">
@@ -46367,8 +46643,11 @@
       <c r="FB24" s="15">
         <v>17</v>
       </c>
+      <c r="FC24" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="25" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -46528,7 +46807,7 @@
       <c r="BB25" s="26">
         <v>0</v>
       </c>
-      <c r="BC25" s="26">
+      <c r="BC25" s="28">
         <v>0</v>
       </c>
       <c r="BD25" s="8">
@@ -46840,8 +47119,11 @@
       <c r="FB25" s="15">
         <v>0</v>
       </c>
+      <c r="FC25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -47001,7 +47283,7 @@
       <c r="BB26" s="26">
         <v>11</v>
       </c>
-      <c r="BC26" s="26">
+      <c r="BC26" s="28">
         <v>5</v>
       </c>
       <c r="BD26" s="8">
@@ -47313,8 +47595,11 @@
       <c r="FB26" s="15">
         <v>19</v>
       </c>
+      <c r="FC26" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="27" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -47474,7 +47759,7 @@
       <c r="BB27" s="26">
         <v>0</v>
       </c>
-      <c r="BC27" s="26">
+      <c r="BC27" s="28">
         <v>0</v>
       </c>
       <c r="BD27" s="8">
@@ -47786,8 +48071,11 @@
       <c r="FB27" s="15">
         <v>0</v>
       </c>
+      <c r="FC27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -47947,7 +48235,7 @@
       <c r="BB28" s="26">
         <v>0</v>
       </c>
-      <c r="BC28" s="26">
+      <c r="BC28" s="28">
         <v>2</v>
       </c>
       <c r="BD28" s="8">
@@ -48259,8 +48547,11 @@
       <c r="FB28" s="15">
         <v>0</v>
       </c>
+      <c r="FC28" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -48420,7 +48711,7 @@
       <c r="BB29" s="26">
         <v>2</v>
       </c>
-      <c r="BC29" s="26">
+      <c r="BC29" s="28">
         <v>4</v>
       </c>
       <c r="BD29" s="8">
@@ -48732,8 +49023,11 @@
       <c r="FB29" s="15">
         <v>5</v>
       </c>
+      <c r="FC29" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -48891,7 +49185,7 @@
       <c r="BB30" s="26">
         <v>0</v>
       </c>
-      <c r="BC30" s="26">
+      <c r="BC30" s="28">
         <v>1</v>
       </c>
       <c r="BD30" s="8">
@@ -49203,8 +49497,11 @@
       <c r="FB30" s="15">
         <v>12</v>
       </c>
+      <c r="FC30" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="31" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -49364,7 +49661,7 @@
       <c r="BB31" s="26">
         <v>18</v>
       </c>
-      <c r="BC31" s="26">
+      <c r="BC31" s="28">
         <v>17</v>
       </c>
       <c r="BD31" s="8">
@@ -49676,8 +49973,11 @@
       <c r="FB31" s="15">
         <v>36</v>
       </c>
+      <c r="FC31" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="32" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -49837,7 +50137,7 @@
       <c r="BB32" s="26">
         <v>0</v>
       </c>
-      <c r="BC32" s="26">
+      <c r="BC32" s="28">
         <v>1</v>
       </c>
       <c r="BD32" s="8">
@@ -50149,8 +50449,11 @@
       <c r="FB32" s="15">
         <v>0</v>
       </c>
+      <c r="FC32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -50310,7 +50613,7 @@
       <c r="BB33" s="26">
         <v>0</v>
       </c>
-      <c r="BC33" s="26">
+      <c r="BC33" s="28">
         <v>0</v>
       </c>
       <c r="BD33" s="8">
@@ -50622,8 +50925,11 @@
       <c r="FB33" s="15">
         <v>0</v>
       </c>
+      <c r="FC33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -50783,7 +51089,7 @@
       <c r="BB34" s="26">
         <v>13</v>
       </c>
-      <c r="BC34" s="26">
+      <c r="BC34" s="28">
         <v>19</v>
       </c>
       <c r="BD34" s="8">
@@ -51095,8 +51401,11 @@
       <c r="FB34" s="15">
         <v>71</v>
       </c>
+      <c r="FC34" s="15">
+        <v>60</v>
+      </c>
     </row>
-    <row r="35" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
@@ -51256,7 +51565,7 @@
       <c r="BB35" s="26">
         <v>150</v>
       </c>
-      <c r="BC35" s="26">
+      <c r="BC35" s="28">
         <v>147</v>
       </c>
       <c r="BD35" s="8">
@@ -51568,8 +51877,11 @@
       <c r="FB35" s="15">
         <v>460</v>
       </c>
+      <c r="FC35" s="15">
+        <v>432</v>
+      </c>
     </row>
-    <row r="36" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -51727,7 +52039,7 @@
       <c r="BB36" s="26">
         <v>15</v>
       </c>
-      <c r="BC36" s="26">
+      <c r="BC36" s="28">
         <v>24</v>
       </c>
       <c r="BD36" s="8">
@@ -52039,8 +52351,11 @@
       <c r="FB36" s="28">
         <v>67</v>
       </c>
+      <c r="FC36" s="28">
+        <v>64</v>
+      </c>
     </row>
-    <row r="37" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -52200,7 +52515,7 @@
       <c r="BB37" s="26">
         <v>10</v>
       </c>
-      <c r="BC37" s="26">
+      <c r="BC37" s="28">
         <v>13</v>
       </c>
       <c r="BD37" s="8">
@@ -52512,8 +52827,11 @@
       <c r="FB37" s="15">
         <v>89</v>
       </c>
+      <c r="FC37" s="15">
+        <v>77</v>
+      </c>
     </row>
-    <row r="38" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -52673,7 +52991,7 @@
       <c r="BB38" s="26">
         <v>7</v>
       </c>
-      <c r="BC38" s="26">
+      <c r="BC38" s="28">
         <v>2</v>
       </c>
       <c r="BD38" s="8">
@@ -52985,8 +53303,11 @@
       <c r="FB38" s="15">
         <v>25</v>
       </c>
+      <c r="FC38" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="39" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -53146,7 +53467,7 @@
       <c r="BB39" s="26">
         <v>5</v>
       </c>
-      <c r="BC39" s="26">
+      <c r="BC39" s="28">
         <v>4</v>
       </c>
       <c r="BD39" s="8">
@@ -53458,8 +53779,11 @@
       <c r="FB39" s="15">
         <v>8</v>
       </c>
+      <c r="FC39" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="40" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -53619,7 +53943,7 @@
       <c r="BB40" s="26">
         <v>0</v>
       </c>
-      <c r="BC40" s="26">
+      <c r="BC40" s="28">
         <v>0</v>
       </c>
       <c r="BD40" s="8">
@@ -53931,8 +54255,11 @@
       <c r="FB40" s="15">
         <v>0</v>
       </c>
+      <c r="FC40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -54092,7 +54419,7 @@
       <c r="BB41" s="26">
         <v>0</v>
       </c>
-      <c r="BC41" s="26">
+      <c r="BC41" s="28">
         <v>0</v>
       </c>
       <c r="BD41" s="8">
@@ -54404,8 +54731,11 @@
       <c r="FB41" s="15">
         <v>0</v>
       </c>
+      <c r="FC41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -54565,7 +54895,7 @@
       <c r="BB42" s="26">
         <v>2</v>
       </c>
-      <c r="BC42" s="26">
+      <c r="BC42" s="28">
         <v>0</v>
       </c>
       <c r="BD42" s="8">
@@ -54877,8 +55207,11 @@
       <c r="FB42" s="15">
         <v>16</v>
       </c>
+      <c r="FC42" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="43" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -55038,7 +55371,7 @@
       <c r="BB43" s="26">
         <v>44</v>
       </c>
-      <c r="BC43" s="26">
+      <c r="BC43" s="28">
         <v>24</v>
       </c>
       <c r="BD43" s="8">
@@ -55350,8 +55683,11 @@
       <c r="FB43" s="28">
         <v>63</v>
       </c>
+      <c r="FC43" s="28">
+        <v>58</v>
+      </c>
     </row>
-    <row r="44" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -55511,7 +55847,7 @@
       <c r="BB44" s="26">
         <v>3</v>
       </c>
-      <c r="BC44" s="26">
+      <c r="BC44" s="28">
         <v>0</v>
       </c>
       <c r="BD44" s="8">
@@ -55823,8 +56159,11 @@
       <c r="FB44" s="15">
         <v>4</v>
       </c>
+      <c r="FC44" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="45" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -55984,7 +56323,7 @@
       <c r="BB45" s="26">
         <v>4</v>
       </c>
-      <c r="BC45" s="26">
+      <c r="BC45" s="28">
         <v>1</v>
       </c>
       <c r="BD45" s="8">
@@ -56296,8 +56635,11 @@
       <c r="FB45" s="15">
         <v>8</v>
       </c>
+      <c r="FC45" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -56457,7 +56799,7 @@
       <c r="BB46" s="26">
         <v>4</v>
       </c>
-      <c r="BC46" s="26">
+      <c r="BC46" s="28">
         <v>7</v>
       </c>
       <c r="BD46" s="8">
@@ -56769,8 +57111,11 @@
       <c r="FB46" s="15">
         <v>29</v>
       </c>
+      <c r="FC46" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="47" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -56930,7 +57275,7 @@
       <c r="BB47" s="26">
         <v>0</v>
       </c>
-      <c r="BC47" s="26">
+      <c r="BC47" s="28">
         <v>0</v>
       </c>
       <c r="BD47" s="8">
@@ -57242,8 +57587,11 @@
       <c r="FB47" s="15">
         <v>0</v>
       </c>
+      <c r="FC47" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -57403,7 +57751,7 @@
       <c r="BB48" s="26">
         <v>9</v>
       </c>
-      <c r="BC48" s="26">
+      <c r="BC48" s="28">
         <v>3</v>
       </c>
       <c r="BD48" s="8">
@@ -57715,8 +58063,11 @@
       <c r="FB48" s="15">
         <v>21</v>
       </c>
+      <c r="FC48" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="49" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
@@ -57876,7 +58227,7 @@
       <c r="BB49" s="26">
         <v>6</v>
       </c>
-      <c r="BC49" s="26">
+      <c r="BC49" s="28">
         <v>3</v>
       </c>
       <c r="BD49" s="8">
@@ -58188,8 +58539,11 @@
       <c r="FB49" s="15">
         <v>42</v>
       </c>
+      <c r="FC49" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="50" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -58347,7 +58701,7 @@
       <c r="BB50" s="26">
         <v>2</v>
       </c>
-      <c r="BC50" s="26">
+      <c r="BC50" s="28">
         <v>0</v>
       </c>
       <c r="BD50" s="8">
@@ -58659,8 +59013,11 @@
       <c r="FB50" s="15">
         <v>10</v>
       </c>
+      <c r="FC50" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="51" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -58820,7 +59177,7 @@
       <c r="BB51" s="26">
         <v>1</v>
       </c>
-      <c r="BC51" s="26">
+      <c r="BC51" s="28">
         <v>5</v>
       </c>
       <c r="BD51" s="8">
@@ -59132,8 +59489,11 @@
       <c r="FB51" s="15">
         <v>5</v>
       </c>
+      <c r="FC51" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="52" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -59293,7 +59653,7 @@
       <c r="BB52" s="26">
         <v>4</v>
       </c>
-      <c r="BC52" s="26">
+      <c r="BC52" s="28">
         <v>4</v>
       </c>
       <c r="BD52" s="8">
@@ -59605,8 +59965,11 @@
       <c r="FB52" s="15">
         <v>18</v>
       </c>
+      <c r="FC52" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="53" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -59766,7 +60129,7 @@
       <c r="BB53" s="26">
         <v>10</v>
       </c>
-      <c r="BC53" s="26">
+      <c r="BC53" s="28">
         <v>8</v>
       </c>
       <c r="BD53" s="8">
@@ -60078,8 +60441,11 @@
       <c r="FB53" s="15">
         <v>38</v>
       </c>
+      <c r="FC53" s="15">
+        <v>30</v>
+      </c>
     </row>
-    <row r="54" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -60239,7 +60605,7 @@
       <c r="BB54" s="26">
         <v>2</v>
       </c>
-      <c r="BC54" s="26">
+      <c r="BC54" s="28">
         <v>1</v>
       </c>
       <c r="BD54" s="8">
@@ -60551,8 +60917,11 @@
       <c r="FB54" s="15">
         <v>5</v>
       </c>
+      <c r="FC54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -60712,7 +61081,7 @@
       <c r="BB55" s="26">
         <v>11</v>
       </c>
-      <c r="BC55" s="26">
+      <c r="BC55" s="28">
         <v>4</v>
       </c>
       <c r="BD55" s="8">
@@ -61024,8 +61393,11 @@
       <c r="FB55" s="15">
         <v>11</v>
       </c>
+      <c r="FC55" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -61185,7 +61557,7 @@
       <c r="BB56" s="26">
         <v>0</v>
       </c>
-      <c r="BC56" s="26">
+      <c r="BC56" s="28">
         <v>4</v>
       </c>
       <c r="BD56" s="8">
@@ -61497,8 +61869,11 @@
       <c r="FB56" s="15">
         <v>0</v>
       </c>
+      <c r="FC56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -61658,7 +62033,7 @@
       <c r="BB57" s="26">
         <v>0</v>
       </c>
-      <c r="BC57" s="26">
+      <c r="BC57" s="28">
         <v>0</v>
       </c>
       <c r="BD57" s="8">
@@ -61970,8 +62345,11 @@
       <c r="FB57" s="15">
         <v>1</v>
       </c>
+      <c r="FC57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="2:158" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -62180,7 +62558,7 @@
         <f t="shared" si="0"/>
         <v>1074</v>
       </c>
-      <c r="BC58" s="27">
+      <c r="BC58" s="43">
         <f>SUM(BC6:BC57)</f>
         <v>1080</v>
       </c>
@@ -62595,12 +62973,17 @@
         <f t="shared" si="10"/>
         <v>3793</v>
       </c>
+      <c r="FC58" s="14">
+        <f t="shared" ref="FC58" si="11">SUM(FC6:FC57)</f>
+        <v>3556</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="172">
+  <mergeCells count="173">
+    <mergeCell ref="FC4:FC5"/>
+    <mergeCell ref="DD2:FC2"/>
+    <mergeCell ref="ER3:FC3"/>
     <mergeCell ref="FB4:FB5"/>
-    <mergeCell ref="DD2:FB2"/>
-    <mergeCell ref="ER3:FB3"/>
     <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="BD2:DC2"/>
     <mergeCell ref="FA4:FA5"/>
@@ -62621,7 +63004,6 @@
     <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="DD4:DD5"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -62770,36 +63152,42 @@
     <mergeCell ref="DJ4:DJ5"/>
     <mergeCell ref="DI4:DI5"/>
     <mergeCell ref="DO4:DO5"/>
+    <mergeCell ref="DD4:DD5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="15" priority="10">
+    <cfRule type="containsBlanks" dxfId="18" priority="11">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="14" priority="9">
+    <cfRule type="containsBlanks" dxfId="17" priority="10">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EH6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="13" priority="11">
+    <cfRule type="containsBlanks" dxfId="16" priority="12">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="12" priority="3">
+    <cfRule type="containsBlanks" dxfId="15" priority="4">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="11" priority="2">
+    <cfRule type="containsBlanks" dxfId="14" priority="3">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="10" priority="1">
+    <cfRule type="containsBlanks" dxfId="13" priority="2">
       <formula>LEN(TRIM(FB6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FC6:FC57">
+    <cfRule type="containsBlanks" dxfId="12" priority="1">
+      <formula>LEN(TRIM(FC6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -62815,7 +63203,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="8" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
+          <x14:cfRule type="containsBlanks" priority="9" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -62838,7 +63226,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DB61"/>
+  <dimension ref="A1:DC61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -62849,11 +63237,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="106" width="10.875" style="1" customWidth="1"/>
-    <col min="107" max="16384" width="8.625" style="1"/>
+    <col min="54" max="107" width="10.875" style="1" customWidth="1"/>
+    <col min="108" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:107" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -62934,11 +63322,12 @@
       <c r="CY1" s="19"/>
       <c r="CZ1" s="19"/>
       <c r="DA1" s="19"/>
-      <c r="DB1" s="19" t="s">
+      <c r="DB1" s="19"/>
+      <c r="DC1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:107" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="59"/>
       <c r="C2" s="60"/>
       <c r="D2" s="58" t="s">
@@ -63048,8 +63437,9 @@
       <c r="CZ2" s="73"/>
       <c r="DA2" s="73"/>
       <c r="DB2" s="73"/>
+      <c r="DC2" s="73"/>
     </row>
-    <row r="3" spans="1:106" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:107" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="87" t="s">
@@ -63163,8 +63553,9 @@
       <c r="CZ3" s="45"/>
       <c r="DA3" s="45"/>
       <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
     </row>
-    <row r="4" spans="1:106" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:107" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="65" t="s">
         <v>0</v>
       </c>
@@ -63480,8 +63871,11 @@
       <c r="DB4" s="44" t="s">
         <v>435</v>
       </c>
+      <c r="DC4" s="44" t="s">
+        <v>437</v>
+      </c>
     </row>
-    <row r="5" spans="1:106" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:107" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
       <c r="D5" s="55"/>
@@ -63587,8 +63981,9 @@
       <c r="CZ5" s="44"/>
       <c r="DA5" s="44"/>
       <c r="DB5" s="44"/>
+      <c r="DC5" s="44"/>
     </row>
-    <row r="6" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -63905,8 +64300,11 @@
       <c r="DB6" s="28">
         <v>27</v>
       </c>
+      <c r="DC6" s="28">
+        <v>18</v>
+      </c>
     </row>
-    <row r="7" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -64222,8 +64620,11 @@
       <c r="DB7" s="15">
         <v>0</v>
       </c>
+      <c r="DC7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -64539,8 +64940,11 @@
       <c r="DB8" s="28">
         <v>0</v>
       </c>
+      <c r="DC8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -64857,8 +65261,11 @@
       <c r="DB9" s="28">
         <v>2</v>
       </c>
+      <c r="DC9" s="28">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -65174,8 +65581,11 @@
       <c r="DB10" s="28">
         <v>0</v>
       </c>
+      <c r="DC10" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -65491,8 +65901,11 @@
       <c r="DB11" s="28">
         <v>1</v>
       </c>
+      <c r="DC11" s="28">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -65808,8 +66221,11 @@
       <c r="DB12" s="15">
         <v>0</v>
       </c>
+      <c r="DC12" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -66125,8 +66541,11 @@
       <c r="DB13" s="15">
         <v>9</v>
       </c>
+      <c r="DC13" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="14" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -66442,8 +66861,11 @@
       <c r="DB14" s="15">
         <v>5</v>
       </c>
+      <c r="DC14" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -66759,8 +67181,11 @@
       <c r="DB15" s="15">
         <v>2</v>
       </c>
+      <c r="DC15" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -67077,8 +67502,11 @@
       <c r="DB16" s="28">
         <v>1</v>
       </c>
+      <c r="DC16" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -67394,8 +67822,11 @@
       <c r="DB17" s="15">
         <v>36</v>
       </c>
+      <c r="DC17" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="18" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -67712,8 +68143,11 @@
       <c r="DB18" s="34">
         <v>228</v>
       </c>
+      <c r="DC18" s="34">
+        <v>236</v>
+      </c>
     </row>
-    <row r="19" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="78" t="s">
         <v>27</v>
@@ -68030,8 +68464,11 @@
       <c r="DB19" s="15">
         <v>24</v>
       </c>
+      <c r="DC19" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="20" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
@@ -68346,8 +68783,11 @@
       <c r="DB20" s="28">
         <v>52</v>
       </c>
+      <c r="DC20" s="28">
+        <v>42</v>
+      </c>
     </row>
-    <row r="21" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
@@ -68662,8 +69102,11 @@
       <c r="DB21" s="15">
         <v>11</v>
       </c>
+      <c r="DC21" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -68979,8 +69422,11 @@
       <c r="DB22" s="15">
         <v>0</v>
       </c>
+      <c r="DC22" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -69296,8 +69742,11 @@
       <c r="DB23" s="15">
         <v>0</v>
       </c>
+      <c r="DC23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -69613,8 +70062,11 @@
       <c r="DB24" s="15">
         <v>1</v>
       </c>
+      <c r="DC24" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -69930,8 +70382,11 @@
       <c r="DB25" s="15">
         <v>0</v>
       </c>
+      <c r="DC25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -70247,8 +70702,11 @@
       <c r="DB26" s="15">
         <v>2</v>
       </c>
+      <c r="DC26" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -70564,8 +71022,11 @@
       <c r="DB27" s="15">
         <v>0</v>
       </c>
+      <c r="DC27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -70881,8 +71342,11 @@
       <c r="DB28" s="15">
         <v>0</v>
       </c>
+      <c r="DC28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -71198,8 +71662,11 @@
       <c r="DB29" s="15">
         <v>0</v>
       </c>
+      <c r="DC29" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -71513,8 +71980,11 @@
       <c r="DB30" s="15">
         <v>3</v>
       </c>
+      <c r="DC30" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -71831,8 +72301,11 @@
       <c r="DB31" s="15">
         <v>13</v>
       </c>
+      <c r="DC31" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="32" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -72148,8 +72621,11 @@
       <c r="DB32" s="15">
         <v>0</v>
       </c>
+      <c r="DC32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -72465,8 +72941,11 @@
       <c r="DB33" s="15">
         <v>0</v>
       </c>
+      <c r="DC33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -72783,8 +73262,11 @@
       <c r="DB34" s="15">
         <v>8</v>
       </c>
+      <c r="DC34" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="35" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="78" t="s">
         <v>56</v>
@@ -73101,8 +73583,11 @@
       <c r="DB35" s="15">
         <v>51</v>
       </c>
+      <c r="DC35" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="36" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -73416,8 +73901,11 @@
       <c r="DB36" s="28">
         <v>15</v>
       </c>
+      <c r="DC36" s="28">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -73734,8 +74222,11 @@
       <c r="DB37" s="15">
         <v>10</v>
       </c>
+      <c r="DC37" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="38" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -74051,8 +74542,11 @@
       <c r="DB38" s="15">
         <v>1</v>
       </c>
+      <c r="DC38" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -74368,8 +74862,11 @@
       <c r="DB39" s="15">
         <v>3</v>
       </c>
+      <c r="DC39" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="40" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -74685,8 +75182,11 @@
       <c r="DB40" s="15">
         <v>0</v>
       </c>
+      <c r="DC40" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -75002,8 +75502,11 @@
       <c r="DB41" s="15">
         <v>0</v>
       </c>
+      <c r="DC41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -75319,8 +75822,11 @@
       <c r="DB42" s="15">
         <v>2</v>
       </c>
+      <c r="DC42" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -75636,8 +76142,11 @@
       <c r="DB43" s="28">
         <v>25</v>
       </c>
+      <c r="DC43" s="28">
+        <v>17</v>
+      </c>
     </row>
-    <row r="44" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -75953,8 +76462,11 @@
       <c r="DB44" s="15">
         <v>0</v>
       </c>
+      <c r="DC44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -76270,8 +76782,11 @@
       <c r="DB45" s="15">
         <v>7</v>
       </c>
+      <c r="DC45" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -76587,8 +77102,11 @@
       <c r="DB46" s="15">
         <v>2</v>
       </c>
+      <c r="DC46" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -76904,8 +77422,11 @@
       <c r="DB47" s="15">
         <v>1</v>
       </c>
+      <c r="DC47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -77221,8 +77742,11 @@
       <c r="DB48" s="15">
         <v>10</v>
       </c>
+      <c r="DC48" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="78" t="s">
         <v>83</v>
@@ -77539,8 +78063,11 @@
       <c r="DB49" s="15">
         <v>1</v>
       </c>
+      <c r="DC49" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:106" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -77854,8 +78381,11 @@
       <c r="DB50" s="15">
         <v>8</v>
       </c>
+      <c r="DC50" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -78171,8 +78701,11 @@
       <c r="DB51" s="15">
         <v>1</v>
       </c>
+      <c r="DC51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -78488,8 +79021,11 @@
       <c r="DB52" s="15">
         <v>3</v>
       </c>
+      <c r="DC52" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -78805,8 +79341,11 @@
       <c r="DB53" s="15">
         <v>11</v>
       </c>
+      <c r="DC53" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="54" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -79122,8 +79661,11 @@
       <c r="DB54" s="15">
         <v>1</v>
       </c>
+      <c r="DC54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -79439,8 +79981,11 @@
       <c r="DB55" s="15">
         <v>1</v>
       </c>
+      <c r="DC55" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -79756,8 +80301,11 @@
       <c r="DB56" s="15">
         <v>0</v>
       </c>
+      <c r="DC56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -80073,8 +80621,11 @@
       <c r="DB57" s="15">
         <v>0</v>
       </c>
+      <c r="DC57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -80488,11 +81039,15 @@
         <v>632</v>
       </c>
       <c r="DB58" s="14">
-        <f t="shared" ref="DB58" si="10">SUM(DB6:DB57)</f>
+        <f t="shared" ref="DB58:DC58" si="10">SUM(DB6:DB57)</f>
         <v>578</v>
       </c>
+      <c r="DC58" s="14">
+        <f t="shared" si="10"/>
+        <v>538</v>
+      </c>
     </row>
-    <row r="59" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -80525,7 +81080,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -80558,7 +81113,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:106" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -80592,10 +81147,11 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="117">
+    <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="BD2:DC2"/>
+    <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="DB4:DB5"/>
-    <mergeCell ref="BD2:DB2"/>
-    <mergeCell ref="CR3:DB3"/>
     <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="CX4:CX5"/>
@@ -80616,7 +81172,6 @@
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="AS4:AS5"/>
@@ -80661,6 +81216,7 @@
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="BY4:BY5"/>
@@ -80712,12 +81268,12 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="CH6:CX57 CZ6:CZ57 DA10">
-    <cfRule type="containsBlanks" dxfId="8" priority="7">
+    <cfRule type="containsBlanks" dxfId="10" priority="8">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY6:CY57">
-    <cfRule type="containsBlanks" dxfId="7" priority="5">
+    <cfRule type="containsBlanks" dxfId="9" priority="6">
       <formula>LEN(TRIM(CY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -80732,7 +81288,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="8" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="9" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -80745,7 +81301,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="18" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="19" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -80758,7 +81314,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="2" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
+          <x14:cfRule type="containsBlanks" priority="3" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -80769,6 +81325,19 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>DB6:DB57</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="1" id="{DFAC2C1F-0AE8-46F8-BC08-A989DBFF9333}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DC6:DC57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -80875,7 +81444,8 @@
       <c r="CY1" s="19"/>
       <c r="CZ1" s="19"/>
       <c r="DA1" s="19"/>
-      <c r="DB1" s="19" t="s">
+      <c r="DB1" s="19"/>
+      <c r="DC1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
@@ -80989,7 +81559,7 @@
       <c r="CZ2" s="73"/>
       <c r="DA2" s="73"/>
       <c r="DB2" s="73"/>
-      <c r="DC2" s="20"/>
+      <c r="DC2" s="73"/>
       <c r="DD2" s="20"/>
       <c r="DE2" s="20"/>
       <c r="DF2" s="20"/>
@@ -81108,7 +81678,7 @@
       <c r="CZ3" s="45"/>
       <c r="DA3" s="45"/>
       <c r="DB3" s="45"/>
-      <c r="DC3" s="21"/>
+      <c r="DC3" s="45"/>
       <c r="DD3" s="21"/>
       <c r="DE3" s="21"/>
       <c r="DF3" s="21"/>
@@ -81429,7 +81999,9 @@
       <c r="DB4" s="44" t="s">
         <v>435</v>
       </c>
-      <c r="DC4" s="88"/>
+      <c r="DC4" s="44" t="s">
+        <v>437</v>
+      </c>
       <c r="DD4" s="88"/>
       <c r="DE4" s="88"/>
       <c r="DF4" s="88"/>
@@ -81540,7 +82112,7 @@
       <c r="CZ5" s="44"/>
       <c r="DA5" s="44"/>
       <c r="DB5" s="44"/>
-      <c r="DC5" s="88"/>
+      <c r="DC5" s="44"/>
       <c r="DD5" s="88"/>
       <c r="DE5" s="88"/>
       <c r="DF5" s="88"/>
@@ -81862,7 +82434,9 @@
       <c r="DB6" s="28">
         <v>90</v>
       </c>
-      <c r="DC6" s="22"/>
+      <c r="DC6" s="28">
+        <v>81</v>
+      </c>
       <c r="DD6" s="22"/>
       <c r="DE6" s="22"/>
       <c r="DF6" s="22"/>
@@ -82183,7 +82757,9 @@
       <c r="DB7" s="15">
         <v>1</v>
       </c>
-      <c r="DC7" s="23"/>
+      <c r="DC7" s="15">
+        <v>0</v>
+      </c>
       <c r="DD7" s="23"/>
       <c r="DE7" s="23"/>
       <c r="DF7" s="23"/>
@@ -82504,7 +83080,9 @@
       <c r="DB8" s="28">
         <v>21</v>
       </c>
-      <c r="DC8" s="23"/>
+      <c r="DC8" s="28">
+        <v>17</v>
+      </c>
       <c r="DD8" s="23"/>
       <c r="DE8" s="23"/>
       <c r="DF8" s="23"/>
@@ -82826,7 +83404,9 @@
       <c r="DB9" s="28">
         <v>63</v>
       </c>
-      <c r="DC9" s="23"/>
+      <c r="DC9" s="28">
+        <v>55</v>
+      </c>
       <c r="DD9" s="23"/>
       <c r="DE9" s="23"/>
       <c r="DF9" s="23"/>
@@ -83147,7 +83727,9 @@
       <c r="DB10" s="28">
         <v>0</v>
       </c>
-      <c r="DC10" s="23"/>
+      <c r="DC10" s="28">
+        <v>1</v>
+      </c>
       <c r="DD10" s="23"/>
       <c r="DE10" s="23"/>
       <c r="DF10" s="23"/>
@@ -83468,7 +84050,9 @@
       <c r="DB11" s="28">
         <v>5</v>
       </c>
-      <c r="DC11" s="23"/>
+      <c r="DC11" s="28">
+        <v>4</v>
+      </c>
       <c r="DD11" s="23"/>
       <c r="DE11" s="23"/>
       <c r="DF11" s="23"/>
@@ -83789,7 +84373,9 @@
       <c r="DB12" s="15">
         <v>6</v>
       </c>
-      <c r="DC12" s="23"/>
+      <c r="DC12" s="15">
+        <v>2</v>
+      </c>
       <c r="DD12" s="23"/>
       <c r="DE12" s="23"/>
       <c r="DF12" s="23"/>
@@ -84110,7 +84696,9 @@
       <c r="DB13" s="15">
         <v>15</v>
       </c>
-      <c r="DC13" s="22"/>
+      <c r="DC13" s="15">
+        <v>20</v>
+      </c>
       <c r="DD13" s="22"/>
       <c r="DE13" s="22"/>
       <c r="DF13" s="22"/>
@@ -84431,7 +85019,9 @@
       <c r="DB14" s="15">
         <v>16</v>
       </c>
-      <c r="DC14" s="23"/>
+      <c r="DC14" s="15">
+        <v>17</v>
+      </c>
       <c r="DD14" s="23"/>
       <c r="DE14" s="23"/>
       <c r="DF14" s="23"/>
@@ -84752,7 +85342,9 @@
       <c r="DB15" s="15">
         <v>5</v>
       </c>
-      <c r="DC15" s="23"/>
+      <c r="DC15" s="15">
+        <v>2</v>
+      </c>
       <c r="DD15" s="23"/>
       <c r="DE15" s="23"/>
       <c r="DF15" s="23"/>
@@ -85074,7 +85666,9 @@
       <c r="DB16" s="28">
         <v>101</v>
       </c>
-      <c r="DC16" s="22"/>
+      <c r="DC16" s="28">
+        <v>108</v>
+      </c>
       <c r="DD16" s="22"/>
       <c r="DE16" s="22"/>
       <c r="DF16" s="22"/>
@@ -85395,7 +85989,9 @@
       <c r="DB17" s="15">
         <v>100</v>
       </c>
-      <c r="DC17" s="22"/>
+      <c r="DC17" s="15">
+        <v>103</v>
+      </c>
       <c r="DD17" s="22"/>
       <c r="DE17" s="22"/>
       <c r="DF17" s="22"/>
@@ -85717,7 +86313,9 @@
       <c r="DB18" s="34">
         <v>1369</v>
       </c>
-      <c r="DC18" s="22"/>
+      <c r="DC18" s="34">
+        <v>1542</v>
+      </c>
       <c r="DD18" s="22"/>
       <c r="DE18" s="22"/>
       <c r="DF18" s="22"/>
@@ -86039,7 +86637,9 @@
       <c r="DB19" s="15">
         <v>31</v>
       </c>
-      <c r="DC19" s="22"/>
+      <c r="DC19" s="15">
+        <v>34</v>
+      </c>
       <c r="DD19" s="22"/>
       <c r="DE19" s="22"/>
       <c r="DF19" s="22"/>
@@ -86359,7 +86959,9 @@
       <c r="DB20" s="28">
         <v>63</v>
       </c>
-      <c r="DC20" s="22"/>
+      <c r="DC20" s="28">
+        <v>65</v>
+      </c>
       <c r="DD20" s="22"/>
       <c r="DE20" s="22"/>
       <c r="DF20" s="22"/>
@@ -86679,7 +87281,9 @@
       <c r="DB21" s="15">
         <v>11</v>
       </c>
-      <c r="DC21" s="22"/>
+      <c r="DC21" s="15">
+        <v>16</v>
+      </c>
       <c r="DD21" s="22"/>
       <c r="DE21" s="22"/>
       <c r="DF21" s="22"/>
@@ -87000,7 +87604,9 @@
       <c r="DB22" s="15">
         <v>4</v>
       </c>
-      <c r="DC22" s="23"/>
+      <c r="DC22" s="15">
+        <v>4</v>
+      </c>
       <c r="DD22" s="23"/>
       <c r="DE22" s="23"/>
       <c r="DF22" s="23"/>
@@ -87321,7 +87927,9 @@
       <c r="DB23" s="15">
         <v>0</v>
       </c>
-      <c r="DC23" s="23"/>
+      <c r="DC23" s="15">
+        <v>0</v>
+      </c>
       <c r="DD23" s="23"/>
       <c r="DE23" s="23"/>
       <c r="DF23" s="23"/>
@@ -87642,7 +88250,9 @@
       <c r="DB24" s="15">
         <v>11</v>
       </c>
-      <c r="DC24" s="22"/>
+      <c r="DC24" s="15">
+        <v>7</v>
+      </c>
       <c r="DD24" s="22"/>
       <c r="DE24" s="22"/>
       <c r="DF24" s="22"/>
@@ -87963,7 +88573,9 @@
       <c r="DB25" s="15">
         <v>1</v>
       </c>
-      <c r="DC25" s="23"/>
+      <c r="DC25" s="15">
+        <v>0</v>
+      </c>
       <c r="DD25" s="23"/>
       <c r="DE25" s="23"/>
       <c r="DF25" s="23"/>
@@ -88284,7 +88896,9 @@
       <c r="DB26" s="15">
         <v>12</v>
       </c>
-      <c r="DC26" s="23"/>
+      <c r="DC26" s="15">
+        <v>10</v>
+      </c>
       <c r="DD26" s="23"/>
       <c r="DE26" s="23"/>
       <c r="DF26" s="23"/>
@@ -88605,7 +89219,9 @@
       <c r="DB27" s="15">
         <v>0</v>
       </c>
-      <c r="DC27" s="23"/>
+      <c r="DC27" s="15">
+        <v>0</v>
+      </c>
       <c r="DD27" s="23"/>
       <c r="DE27" s="23"/>
       <c r="DF27" s="23"/>
@@ -88926,7 +89542,9 @@
       <c r="DB28" s="15">
         <v>2</v>
       </c>
-      <c r="DC28" s="22"/>
+      <c r="DC28" s="15">
+        <v>0</v>
+      </c>
       <c r="DD28" s="22"/>
       <c r="DE28" s="22"/>
       <c r="DF28" s="22"/>
@@ -89247,7 +89865,9 @@
       <c r="DB29" s="15">
         <v>1</v>
       </c>
-      <c r="DC29" s="23"/>
+      <c r="DC29" s="15">
+        <v>1</v>
+      </c>
       <c r="DD29" s="23"/>
       <c r="DE29" s="23"/>
       <c r="DF29" s="23"/>
@@ -89566,7 +90186,9 @@
       <c r="DB30" s="15">
         <v>18</v>
       </c>
-      <c r="DC30" s="23"/>
+      <c r="DC30" s="15">
+        <v>9</v>
+      </c>
       <c r="DD30" s="23"/>
       <c r="DE30" s="23"/>
       <c r="DF30" s="23"/>
@@ -89888,7 +90510,9 @@
       <c r="DB31" s="15">
         <v>37</v>
       </c>
-      <c r="DC31" s="22"/>
+      <c r="DC31" s="15">
+        <v>35</v>
+      </c>
       <c r="DD31" s="22"/>
       <c r="DE31" s="22"/>
       <c r="DF31" s="22"/>
@@ -90209,7 +90833,9 @@
       <c r="DB32" s="15">
         <v>1</v>
       </c>
-      <c r="DC32" s="23"/>
+      <c r="DC32" s="15">
+        <v>3</v>
+      </c>
       <c r="DD32" s="23"/>
       <c r="DE32" s="23"/>
       <c r="DF32" s="23"/>
@@ -90530,7 +91156,9 @@
       <c r="DB33" s="15">
         <v>0</v>
       </c>
-      <c r="DC33" s="23"/>
+      <c r="DC33" s="15">
+        <v>0</v>
+      </c>
       <c r="DD33" s="23"/>
       <c r="DE33" s="23"/>
       <c r="DF33" s="23"/>
@@ -90852,7 +91480,9 @@
       <c r="DB34" s="15">
         <v>62</v>
       </c>
-      <c r="DC34" s="22"/>
+      <c r="DC34" s="15">
+        <v>72</v>
+      </c>
       <c r="DD34" s="22"/>
       <c r="DE34" s="22"/>
       <c r="DF34" s="22"/>
@@ -91174,7 +91804,9 @@
       <c r="DB35" s="15">
         <v>238</v>
       </c>
-      <c r="DC35" s="22"/>
+      <c r="DC35" s="15">
+        <v>236</v>
+      </c>
       <c r="DD35" s="22"/>
       <c r="DE35" s="22"/>
       <c r="DF35" s="22"/>
@@ -91493,7 +92125,9 @@
       <c r="DB36" s="28">
         <v>18</v>
       </c>
-      <c r="DC36" s="22"/>
+      <c r="DC36" s="28">
+        <v>15</v>
+      </c>
       <c r="DD36" s="22"/>
       <c r="DE36" s="22"/>
       <c r="DF36" s="22"/>
@@ -91815,7 +92449,9 @@
       <c r="DB37" s="15">
         <v>57</v>
       </c>
-      <c r="DC37" s="22"/>
+      <c r="DC37" s="15">
+        <v>45</v>
+      </c>
       <c r="DD37" s="22"/>
       <c r="DE37" s="22"/>
       <c r="DF37" s="22"/>
@@ -92136,7 +92772,9 @@
       <c r="DB38" s="15">
         <v>6</v>
       </c>
-      <c r="DC38" s="23"/>
+      <c r="DC38" s="15">
+        <v>5</v>
+      </c>
       <c r="DD38" s="23"/>
       <c r="DE38" s="23"/>
       <c r="DF38" s="23"/>
@@ -92457,7 +93095,9 @@
       <c r="DB39" s="15">
         <v>5</v>
       </c>
-      <c r="DC39" s="23"/>
+      <c r="DC39" s="15">
+        <v>3</v>
+      </c>
       <c r="DD39" s="23"/>
       <c r="DE39" s="23"/>
       <c r="DF39" s="23"/>
@@ -92778,7 +93418,9 @@
       <c r="DB40" s="15">
         <v>0</v>
       </c>
-      <c r="DC40" s="23"/>
+      <c r="DC40" s="15">
+        <v>0</v>
+      </c>
       <c r="DD40" s="23"/>
       <c r="DE40" s="23"/>
       <c r="DF40" s="23"/>
@@ -93099,7 +93741,9 @@
       <c r="DB41" s="15">
         <v>0</v>
       </c>
-      <c r="DC41" s="23"/>
+      <c r="DC41" s="15">
+        <v>0</v>
+      </c>
       <c r="DD41" s="23"/>
       <c r="DE41" s="23"/>
       <c r="DF41" s="23"/>
@@ -93420,7 +94064,9 @@
       <c r="DB42" s="15">
         <v>9</v>
       </c>
-      <c r="DC42" s="23"/>
+      <c r="DC42" s="15">
+        <v>7</v>
+      </c>
       <c r="DD42" s="23"/>
       <c r="DE42" s="23"/>
       <c r="DF42" s="23"/>
@@ -93741,7 +94387,9 @@
       <c r="DB43" s="28">
         <v>32</v>
       </c>
-      <c r="DC43" s="23"/>
+      <c r="DC43" s="28">
+        <v>30</v>
+      </c>
       <c r="DD43" s="23"/>
       <c r="DE43" s="23"/>
       <c r="DF43" s="23"/>
@@ -94062,7 +94710,9 @@
       <c r="DB44" s="15">
         <v>1</v>
       </c>
-      <c r="DC44" s="23"/>
+      <c r="DC44" s="15">
+        <v>4</v>
+      </c>
       <c r="DD44" s="23"/>
       <c r="DE44" s="23"/>
       <c r="DF44" s="23"/>
@@ -94383,7 +95033,9 @@
       <c r="DB45" s="15">
         <v>13</v>
       </c>
-      <c r="DC45" s="22"/>
+      <c r="DC45" s="15">
+        <v>10</v>
+      </c>
       <c r="DD45" s="22"/>
       <c r="DE45" s="22"/>
       <c r="DF45" s="22"/>
@@ -94704,7 +95356,9 @@
       <c r="DB46" s="15">
         <v>15</v>
       </c>
-      <c r="DC46" s="23"/>
+      <c r="DC46" s="15">
+        <v>15</v>
+      </c>
       <c r="DD46" s="23"/>
       <c r="DE46" s="23"/>
       <c r="DF46" s="23"/>
@@ -95025,7 +95679,9 @@
       <c r="DB47" s="15">
         <v>1</v>
       </c>
-      <c r="DC47" s="23"/>
+      <c r="DC47" s="15">
+        <v>0</v>
+      </c>
       <c r="DD47" s="23"/>
       <c r="DE47" s="23"/>
       <c r="DF47" s="23"/>
@@ -95346,7 +96002,9 @@
       <c r="DB48" s="15">
         <v>13</v>
       </c>
-      <c r="DC48" s="23"/>
+      <c r="DC48" s="15">
+        <v>9</v>
+      </c>
       <c r="DD48" s="23"/>
       <c r="DE48" s="23"/>
       <c r="DF48" s="23"/>
@@ -95668,7 +96326,9 @@
       <c r="DB49" s="15">
         <v>39</v>
       </c>
-      <c r="DC49" s="22"/>
+      <c r="DC49" s="15">
+        <v>38</v>
+      </c>
       <c r="DD49" s="22"/>
       <c r="DE49" s="22"/>
       <c r="DF49" s="22"/>
@@ -95987,7 +96647,9 @@
       <c r="DB50" s="15">
         <v>19</v>
       </c>
-      <c r="DC50" s="22"/>
+      <c r="DC50" s="15">
+        <v>15</v>
+      </c>
       <c r="DD50" s="22"/>
       <c r="DE50" s="22"/>
       <c r="DF50" s="22"/>
@@ -96308,7 +96970,9 @@
       <c r="DB51" s="15">
         <v>7</v>
       </c>
-      <c r="DC51" s="23"/>
+      <c r="DC51" s="15">
+        <v>7</v>
+      </c>
       <c r="DD51" s="23"/>
       <c r="DE51" s="23"/>
       <c r="DF51" s="23"/>
@@ -96629,7 +97293,9 @@
       <c r="DB52" s="15">
         <v>22</v>
       </c>
-      <c r="DC52" s="23"/>
+      <c r="DC52" s="15">
+        <v>5</v>
+      </c>
       <c r="DD52" s="23"/>
       <c r="DE52" s="23"/>
       <c r="DF52" s="23"/>
@@ -96950,7 +97616,9 @@
       <c r="DB53" s="15">
         <v>41</v>
       </c>
-      <c r="DC53" s="23"/>
+      <c r="DC53" s="15">
+        <v>33</v>
+      </c>
       <c r="DD53" s="23"/>
       <c r="DE53" s="23"/>
       <c r="DF53" s="23"/>
@@ -97271,7 +97939,9 @@
       <c r="DB54" s="15">
         <v>2</v>
       </c>
-      <c r="DC54" s="23"/>
+      <c r="DC54" s="15">
+        <v>5</v>
+      </c>
       <c r="DD54" s="23"/>
       <c r="DE54" s="23"/>
       <c r="DF54" s="23"/>
@@ -97592,7 +98262,9 @@
       <c r="DB55" s="15">
         <v>24</v>
       </c>
-      <c r="DC55" s="23"/>
+      <c r="DC55" s="15">
+        <v>22</v>
+      </c>
       <c r="DD55" s="23"/>
       <c r="DE55" s="23"/>
       <c r="DF55" s="23"/>
@@ -97913,7 +98585,9 @@
       <c r="DB56" s="15">
         <v>3</v>
       </c>
-      <c r="DC56" s="23"/>
+      <c r="DC56" s="15">
+        <v>1</v>
+      </c>
       <c r="DD56" s="23"/>
       <c r="DE56" s="23"/>
       <c r="DF56" s="23"/>
@@ -98234,7 +98908,9 @@
       <c r="DB57" s="15">
         <v>0</v>
       </c>
-      <c r="DC57" s="23"/>
+      <c r="DC57" s="15">
+        <v>3</v>
+      </c>
       <c r="DD57" s="23"/>
       <c r="DE57" s="23"/>
       <c r="DF57" s="23"/>
@@ -98653,10 +99329,13 @@
         <v>2753</v>
       </c>
       <c r="DB58" s="14">
-        <f t="shared" ref="DB58" si="6">SUM(DB6:DB57)</f>
+        <f t="shared" ref="DB58:DC58" si="6">SUM(DB6:DB57)</f>
         <v>2611</v>
       </c>
-      <c r="DC58" s="24"/>
+      <c r="DC58" s="14">
+        <f t="shared" si="6"/>
+        <v>2716</v>
+      </c>
       <c r="DD58" s="24"/>
       <c r="DE58" s="24"/>
       <c r="DF58" s="24"/>
@@ -98762,8 +99441,8 @@
     </row>
   </sheetData>
   <mergeCells count="120">
-    <mergeCell ref="BD2:DB2"/>
-    <mergeCell ref="CR3:DB3"/>
+    <mergeCell ref="BD2:DC2"/>
+    <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -98895,7 +99574,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="8" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="9" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98908,7 +99587,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="27" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="28" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98921,7 +99600,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="4" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
+          <x14:cfRule type="containsBlanks" priority="5" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
             <xm:f>LEN(TRIM('うちコロナ疑い事案（今回）'!DA10))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98934,7 +99613,7 @@
           <xm:sqref>DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="2" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
+          <x14:cfRule type="containsBlanks" priority="3" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -98946,6 +99625,19 @@
           </x14:cfRule>
           <xm:sqref>DB6:DB57</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="1" id="{D5FC4B6E-10B3-44DA-A1D6-DEA44453D2A7}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DC6:DC57</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\201904_W-119_2019年度消防庁HP更新\03_支給資材・原稿\JOB050328-1\ＪＯＢ050328-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\W-119_消防庁HP更新\03_支給資材・原稿\JOB050404-1\ＪＯＢ050404-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11085"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DC$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DC$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FC$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FC$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DD$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DD$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FD$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FD$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="441">
   <si>
     <t>都道府県</t>
   </si>
@@ -4656,6 +4656,20 @@
 【3月第4週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>3/28(月)～
+4/3(日)分
+【3月第5週
+4月第1週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3/27(月)～
+4/2(日)分
+【3月第5週
+4月第1週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5155,23 +5169,35 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5180,21 +5206,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5240,6 +5251,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5294,7 +5308,21 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="30">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5415,6 +5443,21 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -9569,7 +9612,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FC61"/>
+  <dimension ref="A1:FD61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9583,11 +9626,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="159" width="10.875" style="1" customWidth="1"/>
-    <col min="160" max="16384" width="8.625" style="1"/>
+    <col min="106" max="160" width="10.875" style="1" customWidth="1"/>
+    <col min="161" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:159" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:160" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9673,668 +9716,671 @@
       <c r="EZ1" s="19"/>
       <c r="FA1" s="19"/>
       <c r="FB1" s="19"/>
-      <c r="FC1" s="19" t="s">
+      <c r="FC1" s="19"/>
+      <c r="FD1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:159" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="58" t="s">
+    <row r="2" spans="1:160" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
-      <c r="BC2" s="51"/>
-      <c r="BD2" s="51" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="55"/>
+      <c r="BD2" s="55" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="51"/>
-      <c r="BO2" s="51"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="51"/>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
-      <c r="BV2" s="51"/>
-      <c r="BW2" s="51"/>
-      <c r="BX2" s="51"/>
-      <c r="BY2" s="51"/>
-      <c r="BZ2" s="51"/>
-      <c r="CA2" s="51"/>
-      <c r="CB2" s="51"/>
-      <c r="CC2" s="51"/>
-      <c r="CD2" s="51"/>
-      <c r="CE2" s="51"/>
-      <c r="CF2" s="51"/>
-      <c r="CG2" s="51"/>
-      <c r="CH2" s="51"/>
-      <c r="CI2" s="51"/>
-      <c r="CJ2" s="51"/>
-      <c r="CK2" s="51"/>
-      <c r="CL2" s="51"/>
-      <c r="CM2" s="51"/>
-      <c r="CN2" s="51"/>
-      <c r="CO2" s="51"/>
-      <c r="CP2" s="51"/>
-      <c r="CQ2" s="51"/>
-      <c r="CR2" s="51"/>
-      <c r="CS2" s="51"/>
-      <c r="CT2" s="51"/>
-      <c r="CU2" s="51"/>
-      <c r="CV2" s="51"/>
-      <c r="CW2" s="51"/>
-      <c r="CX2" s="51"/>
-      <c r="CY2" s="51"/>
-      <c r="CZ2" s="51"/>
-      <c r="DA2" s="51"/>
-      <c r="DB2" s="51"/>
-      <c r="DC2" s="51"/>
-      <c r="DD2" s="51"/>
-      <c r="DE2" s="73" t="s">
+      <c r="BE2" s="55"/>
+      <c r="BF2" s="55"/>
+      <c r="BG2" s="55"/>
+      <c r="BH2" s="55"/>
+      <c r="BI2" s="55"/>
+      <c r="BJ2" s="55"/>
+      <c r="BK2" s="55"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="55"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="55"/>
+      <c r="BP2" s="55"/>
+      <c r="BQ2" s="55"/>
+      <c r="BR2" s="55"/>
+      <c r="BS2" s="55"/>
+      <c r="BT2" s="55"/>
+      <c r="BU2" s="55"/>
+      <c r="BV2" s="55"/>
+      <c r="BW2" s="55"/>
+      <c r="BX2" s="55"/>
+      <c r="BY2" s="55"/>
+      <c r="BZ2" s="55"/>
+      <c r="CA2" s="55"/>
+      <c r="CB2" s="55"/>
+      <c r="CC2" s="55"/>
+      <c r="CD2" s="55"/>
+      <c r="CE2" s="55"/>
+      <c r="CF2" s="55"/>
+      <c r="CG2" s="55"/>
+      <c r="CH2" s="55"/>
+      <c r="CI2" s="55"/>
+      <c r="CJ2" s="55"/>
+      <c r="CK2" s="55"/>
+      <c r="CL2" s="55"/>
+      <c r="CM2" s="55"/>
+      <c r="CN2" s="55"/>
+      <c r="CO2" s="55"/>
+      <c r="CP2" s="55"/>
+      <c r="CQ2" s="55"/>
+      <c r="CR2" s="55"/>
+      <c r="CS2" s="55"/>
+      <c r="CT2" s="55"/>
+      <c r="CU2" s="55"/>
+      <c r="CV2" s="55"/>
+      <c r="CW2" s="55"/>
+      <c r="CX2" s="55"/>
+      <c r="CY2" s="55"/>
+      <c r="CZ2" s="55"/>
+      <c r="DA2" s="55"/>
+      <c r="DB2" s="55"/>
+      <c r="DC2" s="55"/>
+      <c r="DD2" s="55"/>
+      <c r="DE2" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="73"/>
-      <c r="DG2" s="73"/>
-      <c r="DH2" s="73"/>
-      <c r="DI2" s="73"/>
-      <c r="DJ2" s="73"/>
-      <c r="DK2" s="73"/>
-      <c r="DL2" s="73"/>
-      <c r="DM2" s="73"/>
-      <c r="DN2" s="73"/>
-      <c r="DO2" s="73"/>
-      <c r="DP2" s="73"/>
-      <c r="DQ2" s="73"/>
-      <c r="DR2" s="73"/>
-      <c r="DS2" s="73"/>
-      <c r="DT2" s="73"/>
-      <c r="DU2" s="73"/>
-      <c r="DV2" s="73"/>
-      <c r="DW2" s="73"/>
-      <c r="DX2" s="73"/>
-      <c r="DY2" s="73"/>
-      <c r="DZ2" s="73"/>
-      <c r="EA2" s="73"/>
-      <c r="EB2" s="73"/>
-      <c r="EC2" s="73"/>
-      <c r="ED2" s="73"/>
-      <c r="EE2" s="73"/>
-      <c r="EF2" s="73"/>
-      <c r="EG2" s="73"/>
-      <c r="EH2" s="73"/>
-      <c r="EI2" s="73"/>
-      <c r="EJ2" s="73"/>
-      <c r="EK2" s="73"/>
-      <c r="EL2" s="73"/>
-      <c r="EM2" s="73"/>
-      <c r="EN2" s="73"/>
-      <c r="EO2" s="73"/>
-      <c r="EP2" s="73"/>
-      <c r="EQ2" s="73"/>
-      <c r="ER2" s="73"/>
-      <c r="ES2" s="73"/>
-      <c r="ET2" s="73"/>
-      <c r="EU2" s="73"/>
-      <c r="EV2" s="73"/>
-      <c r="EW2" s="73"/>
-      <c r="EX2" s="73"/>
-      <c r="EY2" s="73"/>
-      <c r="EZ2" s="73"/>
-      <c r="FA2" s="73"/>
-      <c r="FB2" s="73"/>
-      <c r="FC2" s="73"/>
+      <c r="DF2" s="72"/>
+      <c r="DG2" s="72"/>
+      <c r="DH2" s="72"/>
+      <c r="DI2" s="72"/>
+      <c r="DJ2" s="72"/>
+      <c r="DK2" s="72"/>
+      <c r="DL2" s="72"/>
+      <c r="DM2" s="72"/>
+      <c r="DN2" s="72"/>
+      <c r="DO2" s="72"/>
+      <c r="DP2" s="72"/>
+      <c r="DQ2" s="72"/>
+      <c r="DR2" s="72"/>
+      <c r="DS2" s="72"/>
+      <c r="DT2" s="72"/>
+      <c r="DU2" s="72"/>
+      <c r="DV2" s="72"/>
+      <c r="DW2" s="72"/>
+      <c r="DX2" s="72"/>
+      <c r="DY2" s="72"/>
+      <c r="DZ2" s="72"/>
+      <c r="EA2" s="72"/>
+      <c r="EB2" s="72"/>
+      <c r="EC2" s="72"/>
+      <c r="ED2" s="72"/>
+      <c r="EE2" s="72"/>
+      <c r="EF2" s="72"/>
+      <c r="EG2" s="72"/>
+      <c r="EH2" s="72"/>
+      <c r="EI2" s="72"/>
+      <c r="EJ2" s="72"/>
+      <c r="EK2" s="72"/>
+      <c r="EL2" s="72"/>
+      <c r="EM2" s="72"/>
+      <c r="EN2" s="72"/>
+      <c r="EO2" s="72"/>
+      <c r="EP2" s="72"/>
+      <c r="EQ2" s="72"/>
+      <c r="ER2" s="72"/>
+      <c r="ES2" s="72"/>
+      <c r="ET2" s="72"/>
+      <c r="EU2" s="72"/>
+      <c r="EV2" s="72"/>
+      <c r="EW2" s="72"/>
+      <c r="EX2" s="72"/>
+      <c r="EY2" s="72"/>
+      <c r="EZ2" s="72"/>
+      <c r="FA2" s="72"/>
+      <c r="FB2" s="72"/>
+      <c r="FC2" s="72"/>
+      <c r="FD2" s="72"/>
     </row>
-    <row r="3" spans="1:159" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="45" t="s">
+    <row r="3" spans="1:160" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="45"/>
-      <c r="AR3" s="47" t="s">
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="47"/>
+      <c r="AK3" s="47"/>
+      <c r="AL3" s="47"/>
+      <c r="AM3" s="47"/>
+      <c r="AN3" s="47"/>
+      <c r="AO3" s="47"/>
+      <c r="AP3" s="47"/>
+      <c r="AQ3" s="47"/>
+      <c r="AR3" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="52"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
-      <c r="BB3" s="52"/>
-      <c r="BC3" s="52"/>
-      <c r="BD3" s="52" t="s">
+      <c r="AS3" s="56"/>
+      <c r="AT3" s="56"/>
+      <c r="AU3" s="56"/>
+      <c r="AV3" s="56"/>
+      <c r="AW3" s="56"/>
+      <c r="AX3" s="56"/>
+      <c r="AY3" s="56"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="56"/>
+      <c r="BD3" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="52"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="52"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="52"/>
-      <c r="BP3" s="52"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="52"/>
-      <c r="BS3" s="52"/>
-      <c r="BT3" s="52"/>
-      <c r="BU3" s="52"/>
-      <c r="BV3" s="52"/>
-      <c r="BW3" s="52"/>
-      <c r="BX3" s="52"/>
-      <c r="BY3" s="52"/>
-      <c r="BZ3" s="52"/>
-      <c r="CA3" s="52"/>
-      <c r="CB3" s="52"/>
-      <c r="CC3" s="52"/>
-      <c r="CD3" s="52"/>
-      <c r="CE3" s="52"/>
-      <c r="CF3" s="52"/>
-      <c r="CG3" s="52"/>
-      <c r="CH3" s="52"/>
-      <c r="CI3" s="52"/>
-      <c r="CJ3" s="52"/>
-      <c r="CK3" s="52"/>
-      <c r="CL3" s="52"/>
-      <c r="CM3" s="52"/>
-      <c r="CN3" s="52"/>
-      <c r="CO3" s="52"/>
-      <c r="CP3" s="52"/>
-      <c r="CQ3" s="53"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="56"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="56"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="56"/>
+      <c r="BL3" s="56"/>
+      <c r="BM3" s="56"/>
+      <c r="BN3" s="56"/>
+      <c r="BO3" s="56"/>
+      <c r="BP3" s="56"/>
+      <c r="BQ3" s="56"/>
+      <c r="BR3" s="56"/>
+      <c r="BS3" s="56"/>
+      <c r="BT3" s="56"/>
+      <c r="BU3" s="56"/>
+      <c r="BV3" s="56"/>
+      <c r="BW3" s="56"/>
+      <c r="BX3" s="56"/>
+      <c r="BY3" s="56"/>
+      <c r="BZ3" s="56"/>
+      <c r="CA3" s="56"/>
+      <c r="CB3" s="56"/>
+      <c r="CC3" s="56"/>
+      <c r="CD3" s="56"/>
+      <c r="CE3" s="56"/>
+      <c r="CF3" s="56"/>
+      <c r="CG3" s="56"/>
+      <c r="CH3" s="56"/>
+      <c r="CI3" s="56"/>
+      <c r="CJ3" s="56"/>
+      <c r="CK3" s="56"/>
+      <c r="CL3" s="56"/>
+      <c r="CM3" s="56"/>
+      <c r="CN3" s="56"/>
+      <c r="CO3" s="56"/>
+      <c r="CP3" s="56"/>
+      <c r="CQ3" s="57"/>
+      <c r="CR3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
-      <c r="DD3" s="47"/>
-      <c r="DE3" s="45" t="s">
+      <c r="CS3" s="47"/>
+      <c r="CT3" s="47"/>
+      <c r="CU3" s="47"/>
+      <c r="CV3" s="47"/>
+      <c r="CW3" s="47"/>
+      <c r="CX3" s="47"/>
+      <c r="CY3" s="47"/>
+      <c r="CZ3" s="47"/>
+      <c r="DA3" s="47"/>
+      <c r="DB3" s="47"/>
+      <c r="DC3" s="47"/>
+      <c r="DD3" s="50"/>
+      <c r="DE3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DF3" s="47"/>
+      <c r="DG3" s="47"/>
+      <c r="DH3" s="47"/>
+      <c r="DI3" s="47"/>
+      <c r="DJ3" s="47"/>
+      <c r="DK3" s="47"/>
+      <c r="DL3" s="47"/>
+      <c r="DM3" s="47"/>
+      <c r="DN3" s="47"/>
+      <c r="DO3" s="47"/>
+      <c r="DP3" s="47"/>
+      <c r="DQ3" s="47"/>
+      <c r="DR3" s="47"/>
+      <c r="DS3" s="47"/>
+      <c r="DT3" s="47"/>
+      <c r="DU3" s="47"/>
+      <c r="DV3" s="47"/>
+      <c r="DW3" s="47"/>
+      <c r="DX3" s="47"/>
+      <c r="DY3" s="47"/>
+      <c r="DZ3" s="47"/>
+      <c r="EA3" s="47"/>
+      <c r="EB3" s="47"/>
+      <c r="EC3" s="47"/>
+      <c r="ED3" s="47"/>
+      <c r="EE3" s="47"/>
+      <c r="EF3" s="47"/>
+      <c r="EG3" s="47"/>
+      <c r="EH3" s="47"/>
+      <c r="EI3" s="47"/>
+      <c r="EJ3" s="47"/>
+      <c r="EK3" s="47"/>
+      <c r="EL3" s="47"/>
+      <c r="EM3" s="47"/>
+      <c r="EN3" s="47"/>
+      <c r="EO3" s="47"/>
+      <c r="EP3" s="47"/>
+      <c r="EQ3" s="47"/>
+      <c r="ER3" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
-      <c r="EU3" s="45"/>
-      <c r="EV3" s="45"/>
-      <c r="EW3" s="45"/>
-      <c r="EX3" s="45"/>
-      <c r="EY3" s="45"/>
-      <c r="EZ3" s="45"/>
-      <c r="FA3" s="45"/>
-      <c r="FB3" s="45"/>
-      <c r="FC3" s="45"/>
+      <c r="ES3" s="47"/>
+      <c r="ET3" s="47"/>
+      <c r="EU3" s="47"/>
+      <c r="EV3" s="47"/>
+      <c r="EW3" s="47"/>
+      <c r="EX3" s="47"/>
+      <c r="EY3" s="47"/>
+      <c r="EZ3" s="47"/>
+      <c r="FA3" s="47"/>
+      <c r="FB3" s="47"/>
+      <c r="FC3" s="47"/>
+      <c r="FD3" s="47"/>
     </row>
-    <row r="4" spans="1:159" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="64" t="s">
+    <row r="4" spans="1:160" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="64" t="s">
+      <c r="K4" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="64" t="s">
+      <c r="L4" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="64" t="s">
+      <c r="M4" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="O4" s="64" t="s">
+      <c r="O4" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="Q4" s="64" t="s">
+      <c r="Q4" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="R4" s="63" t="s">
+      <c r="R4" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="64" t="s">
+      <c r="S4" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="64" t="s">
+      <c r="T4" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="U4" s="63" t="s">
+      <c r="U4" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="63" t="s">
+      <c r="V4" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="W4" s="63" t="s">
+      <c r="W4" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="X4" s="63" t="s">
+      <c r="X4" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="Y4" s="63" t="s">
+      <c r="Y4" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="63" t="s">
+      <c r="Z4" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="AA4" s="64" t="s">
+      <c r="AA4" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="64" t="s">
+      <c r="AB4" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="64" t="s">
+      <c r="AC4" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="AD4" s="64" t="s">
+      <c r="AD4" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="AE4" s="64" t="s">
+      <c r="AE4" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="AF4" s="64" t="s">
+      <c r="AF4" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="AG4" s="64" t="s">
+      <c r="AG4" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AH4" s="64" t="s">
+      <c r="AH4" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="AI4" s="64" t="s">
+      <c r="AI4" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AJ4" s="64" t="s">
+      <c r="AJ4" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AK4" s="64" t="s">
+      <c r="AK4" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AL4" s="64" t="s">
+      <c r="AL4" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AM4" s="64" t="s">
+      <c r="AM4" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="AN4" s="64" t="s">
+      <c r="AN4" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="AO4" s="64" t="s">
+      <c r="AO4" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="AP4" s="64" t="s">
+      <c r="AP4" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="AQ4" s="64" t="s">
+      <c r="AQ4" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" s="55" t="s">
+      <c r="AR4" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="AS4" s="55" t="s">
+      <c r="AS4" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="55" t="s">
+      <c r="AT4" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="55" t="s">
+      <c r="AU4" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="55" t="s">
+      <c r="AV4" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="55" t="s">
+      <c r="AW4" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="AX4" s="55" t="s">
+      <c r="AX4" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="AY4" s="55" t="s">
+      <c r="AY4" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="AZ4" s="55" t="s">
+      <c r="AZ4" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="BA4" s="55" t="s">
+      <c r="BA4" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="BB4" s="55" t="s">
+      <c r="BB4" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="BC4" s="55" t="s">
+      <c r="BC4" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="BD4" s="54" t="s">
+      <c r="BD4" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="BE4" s="54" t="s">
+      <c r="BE4" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="54" t="s">
+      <c r="BF4" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="54" t="s">
+      <c r="BG4" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="BH4" s="54" t="s">
+      <c r="BH4" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="BI4" s="54" t="s">
+      <c r="BI4" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="54" t="s">
+      <c r="BJ4" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="54" t="s">
+      <c r="BK4" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="56" t="s">
+      <c r="BL4" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="56" t="s">
+      <c r="BM4" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="BN4" s="54" t="s">
+      <c r="BN4" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="BO4" s="54" t="s">
+      <c r="BO4" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="BP4" s="54" t="s">
+      <c r="BP4" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="BQ4" s="54" t="s">
+      <c r="BQ4" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="BR4" s="54" t="s">
+      <c r="BR4" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="BS4" s="54" t="s">
+      <c r="BS4" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="BT4" s="54" t="s">
+      <c r="BT4" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="BU4" s="56" t="s">
+      <c r="BU4" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="BV4" s="56" t="s">
+      <c r="BV4" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="BW4" s="56" t="s">
+      <c r="BW4" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="BX4" s="56" t="s">
+      <c r="BX4" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="56" t="s">
+      <c r="BY4" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="BZ4" s="54" t="s">
+      <c r="BZ4" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="CA4" s="54" t="s">
+      <c r="CA4" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="CB4" s="54" t="s">
+      <c r="CB4" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="CC4" s="54" t="s">
+      <c r="CC4" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="CD4" s="54" t="s">
+      <c r="CD4" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="CE4" s="48" t="s">
+      <c r="CE4" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="CF4" s="48" t="s">
+      <c r="CF4" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="CG4" s="48" t="s">
+      <c r="CG4" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="CH4" s="48" t="s">
+      <c r="CH4" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="CI4" s="48" t="s">
+      <c r="CI4" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="CJ4" s="48" t="s">
+      <c r="CJ4" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="CK4" s="48" t="s">
+      <c r="CK4" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="CL4" s="48" t="s">
+      <c r="CL4" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="CM4" s="48" t="s">
+      <c r="CM4" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="CN4" s="48" t="s">
+      <c r="CN4" s="46" t="s">
         <v>270</v>
       </c>
-      <c r="CO4" s="48" t="s">
+      <c r="CO4" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="CP4" s="48" t="s">
+      <c r="CP4" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="CQ4" s="48" t="s">
+      <c r="CQ4" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="CR4" s="48" t="s">
+      <c r="CR4" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="CS4" s="48" t="s">
+      <c r="CS4" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="CT4" s="48" t="s">
+      <c r="CT4" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="CU4" s="48" t="s">
+      <c r="CU4" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="CV4" s="48" t="s">
+      <c r="CV4" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="CW4" s="48" t="s">
+      <c r="CW4" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="CX4" s="48" t="s">
+      <c r="CX4" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="CY4" s="48" t="s">
+      <c r="CY4" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="CZ4" s="48" t="s">
+      <c r="CZ4" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="DA4" s="48" t="s">
+      <c r="DA4" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="DB4" s="48" t="s">
+      <c r="DB4" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="DC4" s="48" t="s">
+      <c r="DC4" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="49" t="s">
+      <c r="DD4" s="51" t="s">
         <v>305</v>
       </c>
       <c r="DE4" s="44" t="s">
@@ -10490,139 +10536,142 @@
       <c r="FC4" s="44" t="s">
         <v>437</v>
       </c>
+      <c r="FD4" s="44" t="s">
+        <v>440</v>
+      </c>
     </row>
-    <row r="5" spans="1:159" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="66"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="54"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="54"/>
-      <c r="AG5" s="54"/>
-      <c r="AH5" s="54"/>
-      <c r="AI5" s="54"/>
-      <c r="AJ5" s="54"/>
-      <c r="AK5" s="54"/>
-      <c r="AL5" s="54"/>
-      <c r="AM5" s="54"/>
-      <c r="AN5" s="54"/>
-      <c r="AO5" s="54"/>
-      <c r="AP5" s="54"/>
-      <c r="AQ5" s="54"/>
-      <c r="AR5" s="55"/>
-      <c r="AS5" s="55"/>
-      <c r="AT5" s="55"/>
-      <c r="AU5" s="55"/>
-      <c r="AV5" s="55"/>
-      <c r="AW5" s="55"/>
-      <c r="AX5" s="55"/>
-      <c r="AY5" s="55"/>
-      <c r="AZ5" s="55"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="55"/>
-      <c r="BC5" s="55"/>
-      <c r="BD5" s="55"/>
-      <c r="BE5" s="55"/>
-      <c r="BF5" s="55"/>
-      <c r="BG5" s="55"/>
-      <c r="BH5" s="55"/>
-      <c r="BI5" s="55"/>
-      <c r="BJ5" s="55"/>
-      <c r="BK5" s="55"/>
-      <c r="BL5" s="57"/>
-      <c r="BM5" s="57"/>
-      <c r="BN5" s="55"/>
-      <c r="BO5" s="55"/>
-      <c r="BP5" s="55"/>
-      <c r="BQ5" s="55"/>
-      <c r="BR5" s="55"/>
-      <c r="BS5" s="55"/>
-      <c r="BT5" s="55"/>
-      <c r="BU5" s="57"/>
-      <c r="BV5" s="57"/>
-      <c r="BW5" s="57"/>
-      <c r="BX5" s="57"/>
-      <c r="BY5" s="57"/>
-      <c r="BZ5" s="55"/>
-      <c r="CA5" s="55"/>
-      <c r="CB5" s="55"/>
-      <c r="CC5" s="55"/>
-      <c r="CD5" s="55"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="46"/>
-      <c r="CV5" s="46"/>
-      <c r="CW5" s="46"/>
-      <c r="CX5" s="46"/>
-      <c r="CY5" s="46"/>
-      <c r="CZ5" s="46"/>
-      <c r="DA5" s="46"/>
-      <c r="DB5" s="46"/>
-      <c r="DC5" s="46"/>
-      <c r="DD5" s="50"/>
-      <c r="DE5" s="46"/>
-      <c r="DF5" s="46"/>
-      <c r="DG5" s="46"/>
-      <c r="DH5" s="46"/>
-      <c r="DI5" s="46"/>
-      <c r="DJ5" s="46"/>
-      <c r="DK5" s="46"/>
-      <c r="DL5" s="46"/>
-      <c r="DM5" s="46"/>
-      <c r="DN5" s="46"/>
-      <c r="DO5" s="46"/>
-      <c r="DP5" s="46"/>
-      <c r="DQ5" s="46"/>
-      <c r="DR5" s="46"/>
-      <c r="DS5" s="46"/>
-      <c r="DT5" s="46"/>
-      <c r="DU5" s="46"/>
-      <c r="DV5" s="46"/>
-      <c r="DW5" s="46"/>
-      <c r="DX5" s="46"/>
-      <c r="DY5" s="46"/>
-      <c r="DZ5" s="46"/>
-      <c r="EA5" s="46"/>
-      <c r="EB5" s="46"/>
+    <row r="5" spans="1:160" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="65"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="48"/>
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="48"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="49"/>
+      <c r="AS5" s="49"/>
+      <c r="AT5" s="49"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
+      <c r="AW5" s="49"/>
+      <c r="AX5" s="49"/>
+      <c r="AY5" s="49"/>
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="49"/>
+      <c r="BC5" s="49"/>
+      <c r="BD5" s="49"/>
+      <c r="BE5" s="49"/>
+      <c r="BF5" s="49"/>
+      <c r="BG5" s="49"/>
+      <c r="BH5" s="49"/>
+      <c r="BI5" s="49"/>
+      <c r="BJ5" s="49"/>
+      <c r="BK5" s="49"/>
+      <c r="BL5" s="54"/>
+      <c r="BM5" s="54"/>
+      <c r="BN5" s="49"/>
+      <c r="BO5" s="49"/>
+      <c r="BP5" s="49"/>
+      <c r="BQ5" s="49"/>
+      <c r="BR5" s="49"/>
+      <c r="BS5" s="49"/>
+      <c r="BT5" s="49"/>
+      <c r="BU5" s="54"/>
+      <c r="BV5" s="54"/>
+      <c r="BW5" s="54"/>
+      <c r="BX5" s="54"/>
+      <c r="BY5" s="54"/>
+      <c r="BZ5" s="49"/>
+      <c r="CA5" s="49"/>
+      <c r="CB5" s="49"/>
+      <c r="CC5" s="49"/>
+      <c r="CD5" s="49"/>
+      <c r="CE5" s="45"/>
+      <c r="CF5" s="45"/>
+      <c r="CG5" s="45"/>
+      <c r="CH5" s="45"/>
+      <c r="CI5" s="45"/>
+      <c r="CJ5" s="45"/>
+      <c r="CK5" s="45"/>
+      <c r="CL5" s="45"/>
+      <c r="CM5" s="45"/>
+      <c r="CN5" s="45"/>
+      <c r="CO5" s="45"/>
+      <c r="CP5" s="45"/>
+      <c r="CQ5" s="45"/>
+      <c r="CR5" s="45"/>
+      <c r="CS5" s="45"/>
+      <c r="CT5" s="45"/>
+      <c r="CU5" s="45"/>
+      <c r="CV5" s="45"/>
+      <c r="CW5" s="45"/>
+      <c r="CX5" s="45"/>
+      <c r="CY5" s="45"/>
+      <c r="CZ5" s="45"/>
+      <c r="DA5" s="45"/>
+      <c r="DB5" s="45"/>
+      <c r="DC5" s="45"/>
+      <c r="DD5" s="52"/>
+      <c r="DE5" s="45"/>
+      <c r="DF5" s="45"/>
+      <c r="DG5" s="45"/>
+      <c r="DH5" s="45"/>
+      <c r="DI5" s="45"/>
+      <c r="DJ5" s="45"/>
+      <c r="DK5" s="45"/>
+      <c r="DL5" s="45"/>
+      <c r="DM5" s="45"/>
+      <c r="DN5" s="45"/>
+      <c r="DO5" s="45"/>
+      <c r="DP5" s="45"/>
+      <c r="DQ5" s="45"/>
+      <c r="DR5" s="45"/>
+      <c r="DS5" s="45"/>
+      <c r="DT5" s="45"/>
+      <c r="DU5" s="45"/>
+      <c r="DV5" s="45"/>
+      <c r="DW5" s="45"/>
+      <c r="DX5" s="45"/>
+      <c r="DY5" s="45"/>
+      <c r="DZ5" s="45"/>
+      <c r="EA5" s="45"/>
+      <c r="EB5" s="45"/>
       <c r="EC5" s="44"/>
       <c r="ED5" s="44"/>
       <c r="EE5" s="44"/>
@@ -10650,8 +10699,9 @@
       <c r="FA5" s="44"/>
       <c r="FB5" s="44"/>
       <c r="FC5" s="44"/>
+      <c r="FD5" s="44"/>
     </row>
-    <row r="6" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -11127,8 +11177,11 @@
       <c r="FC6" s="28">
         <v>99</v>
       </c>
+      <c r="FD6" s="28">
+        <v>81</v>
+      </c>
     </row>
-    <row r="7" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11603,8 +11656,11 @@
       <c r="FC7" s="15">
         <v>0</v>
       </c>
+      <c r="FD7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -12079,8 +12135,11 @@
       <c r="FC8" s="28">
         <v>17</v>
       </c>
+      <c r="FD8" s="28">
+        <v>14</v>
+      </c>
     </row>
-    <row r="9" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12556,8 +12615,11 @@
       <c r="FC9" s="15">
         <v>63</v>
       </c>
+      <c r="FD9" s="15">
+        <v>79</v>
+      </c>
     </row>
-    <row r="10" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -13030,8 +13092,11 @@
       <c r="FC10" s="15">
         <v>1</v>
       </c>
+      <c r="FD10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13506,8 +13571,11 @@
       <c r="FC11" s="15">
         <v>7</v>
       </c>
+      <c r="FD11" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="12" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -13982,8 +14050,11 @@
       <c r="FC12" s="15">
         <v>4</v>
       </c>
+      <c r="FD12" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14458,8 +14529,11 @@
       <c r="FC13" s="15">
         <v>36</v>
       </c>
+      <c r="FD13" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="14" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -14934,8 +15008,11 @@
       <c r="FC14" s="15">
         <v>27</v>
       </c>
+      <c r="FD14" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="15" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -15410,8 +15487,11 @@
       <c r="FC15" s="15">
         <v>2</v>
       </c>
+      <c r="FD15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15887,8 +15967,11 @@
       <c r="FC16" s="28">
         <v>110</v>
       </c>
+      <c r="FD16" s="28">
+        <v>104</v>
+      </c>
     </row>
-    <row r="17" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -16363,8 +16446,11 @@
       <c r="FC17" s="15">
         <v>130</v>
       </c>
+      <c r="FD17" s="15">
+        <v>121</v>
+      </c>
     </row>
-    <row r="18" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16840,10 +16926,13 @@
       <c r="FC18" s="34">
         <v>1778</v>
       </c>
+      <c r="FD18" s="34">
+        <v>1543</v>
+      </c>
     </row>
-    <row r="19" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="68" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -17317,10 +17406,13 @@
       <c r="FC19" s="15">
         <v>58</v>
       </c>
+      <c r="FD19" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="20" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="69"/>
+      <c r="B20" s="68"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -17792,10 +17884,13 @@
       <c r="FC20" s="28">
         <v>107</v>
       </c>
+      <c r="FD20" s="28">
+        <v>102</v>
+      </c>
     </row>
-    <row r="21" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="69"/>
+      <c r="B21" s="68"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -18267,8 +18362,11 @@
       <c r="FC21" s="15">
         <v>20</v>
       </c>
+      <c r="FD21" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="22" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18743,8 +18841,11 @@
       <c r="FC22" s="15">
         <v>5</v>
       </c>
+      <c r="FD22" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -19219,8 +19320,11 @@
       <c r="FC23" s="15">
         <v>0</v>
       </c>
+      <c r="FD23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19695,8 +19799,11 @@
       <c r="FC24" s="15">
         <v>7</v>
       </c>
+      <c r="FD24" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="25" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -20171,8 +20278,11 @@
       <c r="FC25" s="15">
         <v>0</v>
       </c>
+      <c r="FD25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -20647,8 +20757,11 @@
       <c r="FC26" s="15">
         <v>14</v>
       </c>
+      <c r="FD26" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="27" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -21123,8 +21236,11 @@
       <c r="FC27" s="15">
         <v>0</v>
       </c>
+      <c r="FD27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -21599,9 +21715,12 @@
       <c r="FC28" s="15">
         <v>0</v>
       </c>
+      <c r="FD28" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="70" t="s">
+    <row r="29" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="69" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -22075,9 +22194,12 @@
       <c r="FC29" s="15">
         <v>1</v>
       </c>
+      <c r="FD29" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="70"/>
+    <row r="30" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="69"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -22549,8 +22671,11 @@
       <c r="FC30" s="15">
         <v>18</v>
       </c>
+      <c r="FD30" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="31" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -23026,8 +23151,11 @@
       <c r="FC31" s="15">
         <v>46</v>
       </c>
+      <c r="FD31" s="15">
+        <v>44</v>
+      </c>
     </row>
-    <row r="32" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -23502,8 +23630,11 @@
       <c r="FC32" s="15">
         <v>3</v>
       </c>
+      <c r="FD32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -23978,8 +24109,11 @@
       <c r="FC33" s="15">
         <v>0</v>
       </c>
+      <c r="FD33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -24455,10 +24589,13 @@
       <c r="FC34" s="15">
         <v>85</v>
       </c>
+      <c r="FD34" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="35" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="68" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -24932,9 +25069,12 @@
       <c r="FC35" s="15">
         <v>277</v>
       </c>
+      <c r="FD35" s="15">
+        <v>263</v>
+      </c>
     </row>
-    <row r="36" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="69"/>
+    <row r="36" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="68"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -25406,8 +25546,11 @@
       <c r="FC36" s="28">
         <v>24</v>
       </c>
+      <c r="FD36" s="28">
+        <v>19</v>
+      </c>
     </row>
-    <row r="37" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -25883,8 +26026,11 @@
       <c r="FC37" s="15">
         <v>48</v>
       </c>
+      <c r="FD37" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="38" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -26359,8 +26505,11 @@
       <c r="FC38" s="15">
         <v>6</v>
       </c>
+      <c r="FD38" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="39" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -26835,8 +26984,11 @@
       <c r="FC39" s="15">
         <v>6</v>
       </c>
+      <c r="FD39" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="40" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -27311,8 +27463,11 @@
       <c r="FC40" s="15">
         <v>1</v>
       </c>
+      <c r="FD40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -27787,8 +27942,11 @@
       <c r="FC41" s="15">
         <v>0</v>
       </c>
+      <c r="FD41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -28263,8 +28421,11 @@
       <c r="FC42" s="15">
         <v>9</v>
       </c>
+      <c r="FD42" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -28739,8 +28900,11 @@
       <c r="FC43" s="28">
         <v>47</v>
       </c>
+      <c r="FD43" s="28">
+        <v>37</v>
+      </c>
     </row>
-    <row r="44" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -29215,8 +29379,11 @@
       <c r="FC44" s="15">
         <v>5</v>
       </c>
+      <c r="FD44" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="45" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -29691,8 +29858,11 @@
       <c r="FC45" s="15">
         <v>15</v>
       </c>
+      <c r="FD45" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="46" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -30167,8 +30337,11 @@
       <c r="FC46" s="15">
         <v>15</v>
       </c>
+      <c r="FD46" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="47" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -30643,8 +30816,11 @@
       <c r="FC47" s="15">
         <v>0</v>
       </c>
+      <c r="FD47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -31119,10 +31295,13 @@
       <c r="FC48" s="15">
         <v>14</v>
       </c>
+      <c r="FD48" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="49" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="68" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -31596,9 +31775,12 @@
       <c r="FC49" s="15">
         <v>39</v>
       </c>
+      <c r="FD49" s="15">
+        <v>40</v>
+      </c>
     </row>
-    <row r="50" spans="1:159" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="69"/>
+    <row r="50" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="68"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -32070,8 +32252,11 @@
       <c r="FC50" s="15">
         <v>16</v>
       </c>
+      <c r="FD50" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="51" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -32546,8 +32731,11 @@
       <c r="FC51" s="15">
         <v>7</v>
       </c>
+      <c r="FD51" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="52" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -33022,8 +33210,11 @@
       <c r="FC52" s="15">
         <v>8</v>
       </c>
+      <c r="FD52" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="53" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -33498,8 +33689,11 @@
       <c r="FC53" s="15">
         <v>43</v>
       </c>
+      <c r="FD53" s="15">
+        <v>37</v>
+      </c>
     </row>
-    <row r="54" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -33974,8 +34168,11 @@
       <c r="FC54" s="15">
         <v>9</v>
       </c>
+      <c r="FD54" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="55" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -34450,8 +34647,11 @@
       <c r="FC55" s="15">
         <v>23</v>
       </c>
+      <c r="FD55" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="56" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -34926,8 +35126,11 @@
       <c r="FC56" s="15">
         <v>1</v>
       </c>
+      <c r="FD56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -35402,8 +35605,11 @@
       <c r="FC57" s="15">
         <v>3</v>
       </c>
+      <c r="FD57" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -36029,11 +36235,15 @@
         <v>3189</v>
       </c>
       <c r="FC58" s="14">
-        <f t="shared" ref="FC58" si="13">SUM(FC6:FC57)</f>
+        <f t="shared" ref="FC58:FD58" si="13">SUM(FC6:FC57)</f>
         <v>3254</v>
       </c>
+      <c r="FD58" s="14">
+        <f t="shared" si="13"/>
+        <v>2901</v>
+      </c>
     </row>
-    <row r="59" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -36117,7 +36327,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -36201,30 +36411,30 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:159" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="68"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="68"/>
-      <c r="M61" s="68"/>
-      <c r="N61" s="68"/>
-      <c r="O61" s="68"/>
-      <c r="P61" s="68"/>
-      <c r="Q61" s="68"/>
-      <c r="R61" s="68"/>
-      <c r="S61" s="68"/>
-      <c r="T61" s="68"/>
-      <c r="U61" s="68"/>
-      <c r="V61" s="68"/>
-      <c r="W61" s="68"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="67"/>
+      <c r="L61" s="67"/>
+      <c r="M61" s="67"/>
+      <c r="N61" s="67"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="67"/>
+      <c r="Q61" s="67"/>
+      <c r="R61" s="67"/>
+      <c r="S61" s="67"/>
+      <c r="T61" s="67"/>
+      <c r="U61" s="67"/>
+      <c r="V61" s="67"/>
+      <c r="W61" s="67"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -36286,15 +36496,31 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="174">
+    <mergeCell ref="FD4:FD5"/>
+    <mergeCell ref="ER3:FD3"/>
+    <mergeCell ref="DE2:FD2"/>
     <mergeCell ref="FC4:FC5"/>
-    <mergeCell ref="DE2:FC2"/>
-    <mergeCell ref="ER3:FC3"/>
     <mergeCell ref="FB4:FB5"/>
     <mergeCell ref="FA4:FA5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
     <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="AR3:BC3"/>
+    <mergeCell ref="D2:BC2"/>
+    <mergeCell ref="DO4:DO5"/>
+    <mergeCell ref="DN4:DN5"/>
+    <mergeCell ref="DS4:DS5"/>
+    <mergeCell ref="DR4:DR5"/>
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CF4:CF5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="CI4:CI5"/>
@@ -36304,17 +36530,11 @@
     <mergeCell ref="AX4:AX5"/>
     <mergeCell ref="BJ4:BJ5"/>
     <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="CZ4:CZ5"/>
-    <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
     <mergeCell ref="AW4:AW5"/>
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="CO4:CO5"/>
     <mergeCell ref="AY4:AY5"/>
     <mergeCell ref="AU4:AU5"/>
     <mergeCell ref="BC4:BC5"/>
@@ -36325,7 +36545,6 @@
     <mergeCell ref="BW4:BW5"/>
     <mergeCell ref="CG4:CG5"/>
     <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="D61:W61"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="S4:S5"/>
@@ -36371,15 +36590,6 @@
     <mergeCell ref="AQ4:AQ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="D2:BC2"/>
-    <mergeCell ref="DO4:DO5"/>
-    <mergeCell ref="DN4:DN5"/>
-    <mergeCell ref="DS4:DS5"/>
-    <mergeCell ref="DR4:DR5"/>
-    <mergeCell ref="CY4:CY5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="BI4:BI5"/>
     <mergeCell ref="BE4:BE5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="BV4:BV5"/>
@@ -36390,7 +36600,6 @@
     <mergeCell ref="BT4:BT5"/>
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="BY4:BY5"/>
-    <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="BK4:BK5"/>
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="DB4:DB5"/>
@@ -36414,8 +36623,7 @@
     <mergeCell ref="CA4:CA5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="DX4:DX5"/>
-    <mergeCell ref="DW4:DW5"/>
+    <mergeCell ref="BI4:BI5"/>
     <mergeCell ref="DV4:DV5"/>
     <mergeCell ref="BR4:BR5"/>
     <mergeCell ref="CK4:CK5"/>
@@ -36438,6 +36646,7 @@
     <mergeCell ref="DZ4:DZ5"/>
     <mergeCell ref="DJ4:DJ5"/>
     <mergeCell ref="DI4:DI5"/>
+    <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="DG4:DG5"/>
     <mergeCell ref="DE4:DE5"/>
     <mergeCell ref="DC4:DC5"/>
@@ -36460,48 +36669,57 @@
     <mergeCell ref="EJ4:EJ5"/>
     <mergeCell ref="ER4:ER5"/>
     <mergeCell ref="DU4:DU5"/>
+    <mergeCell ref="DX4:DX5"/>
+    <mergeCell ref="DW4:DW5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="25" priority="7">
+    <cfRule type="containsBlanks" dxfId="29" priority="8">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="24" priority="6">
+    <cfRule type="containsBlanks" dxfId="28" priority="7">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="23" priority="5">
+    <cfRule type="containsBlanks" dxfId="27" priority="6">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="22" priority="4">
+    <cfRule type="containsBlanks" dxfId="26" priority="5">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="21" priority="3">
+    <cfRule type="containsBlanks" dxfId="25" priority="4">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="20" priority="2">
+    <cfRule type="containsBlanks" dxfId="24" priority="3">
       <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FC6:FC57">
-    <cfRule type="containsBlanks" dxfId="19" priority="1">
+    <cfRule type="containsBlanks" dxfId="23" priority="2">
       <formula>LEN(TRIM(FC6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FD6:FD57">
+    <cfRule type="containsBlanks" dxfId="22" priority="1">
+      <formula>LEN(TRIM(FD6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="31" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
-  <colBreaks count="3" manualBreakCount="3">
+  <colBreaks count="5" manualBreakCount="5">
     <brk id="55" max="64" man="1"/>
+    <brk id="99" max="64" man="1"/>
     <brk id="108" max="64" man="1"/>
+    <brk id="130" max="64" man="1"/>
     <brk id="147" max="64" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
@@ -36513,7 +36731,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:FC58"/>
+  <dimension ref="B1:FD58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -36539,11 +36757,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="159" width="10.875" style="1" customWidth="1"/>
-    <col min="160" max="16384" width="8.625" style="1"/>
+    <col min="106" max="160" width="10.875" style="1" customWidth="1"/>
+    <col min="161" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:159" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="86" t="s">
         <v>323</v>
       </c>
@@ -36629,353 +36847,356 @@
       <c r="EZ1" s="19"/>
       <c r="FA1" s="19"/>
       <c r="FB1" s="19"/>
-      <c r="FC1" s="19" t="s">
+      <c r="FC1" s="19"/>
+      <c r="FD1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:159" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="58" t="s">
+    <row r="2" spans="2:160" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="73" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
       <c r="BC2" s="85"/>
-      <c r="BD2" s="58" t="s">
+      <c r="BD2" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="51"/>
-      <c r="BO2" s="51"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="51"/>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
-      <c r="BV2" s="51"/>
-      <c r="BW2" s="51"/>
-      <c r="BX2" s="51"/>
-      <c r="BY2" s="51"/>
-      <c r="BZ2" s="51"/>
-      <c r="CA2" s="51"/>
-      <c r="CB2" s="51"/>
-      <c r="CC2" s="51"/>
-      <c r="CD2" s="51"/>
-      <c r="CE2" s="51"/>
-      <c r="CF2" s="51"/>
-      <c r="CG2" s="51"/>
-      <c r="CH2" s="51"/>
-      <c r="CI2" s="51"/>
-      <c r="CJ2" s="51"/>
-      <c r="CK2" s="51"/>
-      <c r="CL2" s="51"/>
-      <c r="CM2" s="51"/>
-      <c r="CN2" s="51"/>
-      <c r="CO2" s="51"/>
-      <c r="CP2" s="51"/>
-      <c r="CQ2" s="51"/>
-      <c r="CR2" s="51"/>
-      <c r="CS2" s="51"/>
-      <c r="CT2" s="51"/>
-      <c r="CU2" s="51"/>
-      <c r="CV2" s="51"/>
-      <c r="CW2" s="51"/>
-      <c r="CX2" s="51"/>
-      <c r="CY2" s="51"/>
-      <c r="CZ2" s="51"/>
-      <c r="DA2" s="51"/>
-      <c r="DB2" s="51"/>
+      <c r="BE2" s="55"/>
+      <c r="BF2" s="55"/>
+      <c r="BG2" s="55"/>
+      <c r="BH2" s="55"/>
+      <c r="BI2" s="55"/>
+      <c r="BJ2" s="55"/>
+      <c r="BK2" s="55"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="55"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="55"/>
+      <c r="BP2" s="55"/>
+      <c r="BQ2" s="55"/>
+      <c r="BR2" s="55"/>
+      <c r="BS2" s="55"/>
+      <c r="BT2" s="55"/>
+      <c r="BU2" s="55"/>
+      <c r="BV2" s="55"/>
+      <c r="BW2" s="55"/>
+      <c r="BX2" s="55"/>
+      <c r="BY2" s="55"/>
+      <c r="BZ2" s="55"/>
+      <c r="CA2" s="55"/>
+      <c r="CB2" s="55"/>
+      <c r="CC2" s="55"/>
+      <c r="CD2" s="55"/>
+      <c r="CE2" s="55"/>
+      <c r="CF2" s="55"/>
+      <c r="CG2" s="55"/>
+      <c r="CH2" s="55"/>
+      <c r="CI2" s="55"/>
+      <c r="CJ2" s="55"/>
+      <c r="CK2" s="55"/>
+      <c r="CL2" s="55"/>
+      <c r="CM2" s="55"/>
+      <c r="CN2" s="55"/>
+      <c r="CO2" s="55"/>
+      <c r="CP2" s="55"/>
+      <c r="CQ2" s="55"/>
+      <c r="CR2" s="55"/>
+      <c r="CS2" s="55"/>
+      <c r="CT2" s="55"/>
+      <c r="CU2" s="55"/>
+      <c r="CV2" s="55"/>
+      <c r="CW2" s="55"/>
+      <c r="CX2" s="55"/>
+      <c r="CY2" s="55"/>
+      <c r="CZ2" s="55"/>
+      <c r="DA2" s="55"/>
+      <c r="DB2" s="55"/>
       <c r="DC2" s="85"/>
-      <c r="DD2" s="73" t="s">
+      <c r="DD2" s="72" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="73"/>
-      <c r="DF2" s="73"/>
-      <c r="DG2" s="73"/>
-      <c r="DH2" s="73"/>
-      <c r="DI2" s="73"/>
-      <c r="DJ2" s="73"/>
-      <c r="DK2" s="73"/>
-      <c r="DL2" s="73"/>
-      <c r="DM2" s="73"/>
-      <c r="DN2" s="73"/>
-      <c r="DO2" s="73"/>
-      <c r="DP2" s="73"/>
-      <c r="DQ2" s="73"/>
-      <c r="DR2" s="73"/>
-      <c r="DS2" s="73"/>
-      <c r="DT2" s="73"/>
-      <c r="DU2" s="73"/>
-      <c r="DV2" s="73"/>
-      <c r="DW2" s="73"/>
-      <c r="DX2" s="73"/>
-      <c r="DY2" s="73"/>
-      <c r="DZ2" s="73"/>
-      <c r="EA2" s="73"/>
-      <c r="EB2" s="73"/>
-      <c r="EC2" s="73"/>
-      <c r="ED2" s="73"/>
-      <c r="EE2" s="73"/>
-      <c r="EF2" s="73"/>
-      <c r="EG2" s="73"/>
-      <c r="EH2" s="73"/>
-      <c r="EI2" s="73"/>
-      <c r="EJ2" s="73"/>
-      <c r="EK2" s="73"/>
-      <c r="EL2" s="73"/>
-      <c r="EM2" s="73"/>
-      <c r="EN2" s="73"/>
-      <c r="EO2" s="73"/>
-      <c r="EP2" s="73"/>
-      <c r="EQ2" s="73"/>
-      <c r="ER2" s="73"/>
-      <c r="ES2" s="73"/>
-      <c r="ET2" s="73"/>
-      <c r="EU2" s="73"/>
-      <c r="EV2" s="73"/>
-      <c r="EW2" s="73"/>
-      <c r="EX2" s="73"/>
-      <c r="EY2" s="73"/>
-      <c r="EZ2" s="73"/>
-      <c r="FA2" s="73"/>
-      <c r="FB2" s="73"/>
-      <c r="FC2" s="73"/>
+      <c r="DE2" s="72"/>
+      <c r="DF2" s="72"/>
+      <c r="DG2" s="72"/>
+      <c r="DH2" s="72"/>
+      <c r="DI2" s="72"/>
+      <c r="DJ2" s="72"/>
+      <c r="DK2" s="72"/>
+      <c r="DL2" s="72"/>
+      <c r="DM2" s="72"/>
+      <c r="DN2" s="72"/>
+      <c r="DO2" s="72"/>
+      <c r="DP2" s="72"/>
+      <c r="DQ2" s="72"/>
+      <c r="DR2" s="72"/>
+      <c r="DS2" s="72"/>
+      <c r="DT2" s="72"/>
+      <c r="DU2" s="72"/>
+      <c r="DV2" s="72"/>
+      <c r="DW2" s="72"/>
+      <c r="DX2" s="72"/>
+      <c r="DY2" s="72"/>
+      <c r="DZ2" s="72"/>
+      <c r="EA2" s="72"/>
+      <c r="EB2" s="72"/>
+      <c r="EC2" s="72"/>
+      <c r="ED2" s="72"/>
+      <c r="EE2" s="72"/>
+      <c r="EF2" s="72"/>
+      <c r="EG2" s="72"/>
+      <c r="EH2" s="72"/>
+      <c r="EI2" s="72"/>
+      <c r="EJ2" s="72"/>
+      <c r="EK2" s="72"/>
+      <c r="EL2" s="72"/>
+      <c r="EM2" s="72"/>
+      <c r="EN2" s="72"/>
+      <c r="EO2" s="72"/>
+      <c r="EP2" s="72"/>
+      <c r="EQ2" s="72"/>
+      <c r="ER2" s="72"/>
+      <c r="ES2" s="72"/>
+      <c r="ET2" s="72"/>
+      <c r="EU2" s="72"/>
+      <c r="EV2" s="72"/>
+      <c r="EW2" s="72"/>
+      <c r="EX2" s="72"/>
+      <c r="EY2" s="72"/>
+      <c r="EZ2" s="72"/>
+      <c r="FA2" s="72"/>
+      <c r="FB2" s="72"/>
+      <c r="FC2" s="72"/>
+      <c r="FD2" s="72"/>
     </row>
-    <row r="3" spans="2:159" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="47" t="s">
+    <row r="3" spans="2:160" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="52"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="52"/>
-      <c r="AO3" s="52"/>
-      <c r="AP3" s="52"/>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="47" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="56"/>
+      <c r="AH3" s="56"/>
+      <c r="AI3" s="56"/>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56"/>
+      <c r="AN3" s="56"/>
+      <c r="AO3" s="56"/>
+      <c r="AP3" s="56"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="52"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
-      <c r="BB3" s="52"/>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="47" t="s">
+      <c r="AS3" s="56"/>
+      <c r="AT3" s="56"/>
+      <c r="AU3" s="56"/>
+      <c r="AV3" s="56"/>
+      <c r="AW3" s="56"/>
+      <c r="AX3" s="56"/>
+      <c r="AY3" s="56"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="57"/>
+      <c r="BD3" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="52"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="52"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="52"/>
-      <c r="BP3" s="52"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="52"/>
-      <c r="BS3" s="52"/>
-      <c r="BT3" s="52"/>
-      <c r="BU3" s="52"/>
-      <c r="BV3" s="52"/>
-      <c r="BW3" s="52"/>
-      <c r="BX3" s="52"/>
-      <c r="BY3" s="52"/>
-      <c r="BZ3" s="52"/>
-      <c r="CA3" s="52"/>
-      <c r="CB3" s="52"/>
-      <c r="CC3" s="52"/>
-      <c r="CD3" s="52"/>
-      <c r="CE3" s="52"/>
-      <c r="CF3" s="52"/>
-      <c r="CG3" s="52"/>
-      <c r="CH3" s="52"/>
-      <c r="CI3" s="52"/>
-      <c r="CJ3" s="52"/>
-      <c r="CK3" s="52"/>
-      <c r="CL3" s="52"/>
-      <c r="CM3" s="52"/>
-      <c r="CN3" s="52"/>
-      <c r="CO3" s="52"/>
-      <c r="CP3" s="52"/>
-      <c r="CQ3" s="53"/>
-      <c r="CR3" s="47" t="s">
+      <c r="BE3" s="56"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="56"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="56"/>
+      <c r="BL3" s="56"/>
+      <c r="BM3" s="56"/>
+      <c r="BN3" s="56"/>
+      <c r="BO3" s="56"/>
+      <c r="BP3" s="56"/>
+      <c r="BQ3" s="56"/>
+      <c r="BR3" s="56"/>
+      <c r="BS3" s="56"/>
+      <c r="BT3" s="56"/>
+      <c r="BU3" s="56"/>
+      <c r="BV3" s="56"/>
+      <c r="BW3" s="56"/>
+      <c r="BX3" s="56"/>
+      <c r="BY3" s="56"/>
+      <c r="BZ3" s="56"/>
+      <c r="CA3" s="56"/>
+      <c r="CB3" s="56"/>
+      <c r="CC3" s="56"/>
+      <c r="CD3" s="56"/>
+      <c r="CE3" s="56"/>
+      <c r="CF3" s="56"/>
+      <c r="CG3" s="56"/>
+      <c r="CH3" s="56"/>
+      <c r="CI3" s="56"/>
+      <c r="CJ3" s="56"/>
+      <c r="CK3" s="56"/>
+      <c r="CL3" s="56"/>
+      <c r="CM3" s="56"/>
+      <c r="CN3" s="56"/>
+      <c r="CO3" s="56"/>
+      <c r="CP3" s="56"/>
+      <c r="CQ3" s="57"/>
+      <c r="CR3" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="52"/>
-      <c r="CT3" s="52"/>
-      <c r="CU3" s="52"/>
-      <c r="CV3" s="52"/>
-      <c r="CW3" s="52"/>
-      <c r="CX3" s="52"/>
-      <c r="CY3" s="52"/>
-      <c r="CZ3" s="52"/>
-      <c r="DA3" s="52"/>
-      <c r="DB3" s="52"/>
-      <c r="DC3" s="53"/>
-      <c r="DD3" s="45" t="s">
+      <c r="CS3" s="56"/>
+      <c r="CT3" s="56"/>
+      <c r="CU3" s="56"/>
+      <c r="CV3" s="56"/>
+      <c r="CW3" s="56"/>
+      <c r="CX3" s="56"/>
+      <c r="CY3" s="56"/>
+      <c r="CZ3" s="56"/>
+      <c r="DA3" s="56"/>
+      <c r="DB3" s="56"/>
+      <c r="DC3" s="57"/>
+      <c r="DD3" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="45"/>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DE3" s="47"/>
+      <c r="DF3" s="47"/>
+      <c r="DG3" s="47"/>
+      <c r="DH3" s="47"/>
+      <c r="DI3" s="47"/>
+      <c r="DJ3" s="47"/>
+      <c r="DK3" s="47"/>
+      <c r="DL3" s="47"/>
+      <c r="DM3" s="47"/>
+      <c r="DN3" s="47"/>
+      <c r="DO3" s="47"/>
+      <c r="DP3" s="47"/>
+      <c r="DQ3" s="47"/>
+      <c r="DR3" s="47"/>
+      <c r="DS3" s="47"/>
+      <c r="DT3" s="47"/>
+      <c r="DU3" s="47"/>
+      <c r="DV3" s="47"/>
+      <c r="DW3" s="47"/>
+      <c r="DX3" s="47"/>
+      <c r="DY3" s="47"/>
+      <c r="DZ3" s="47"/>
+      <c r="EA3" s="47"/>
+      <c r="EB3" s="47"/>
+      <c r="EC3" s="47"/>
+      <c r="ED3" s="47"/>
+      <c r="EE3" s="47"/>
+      <c r="EF3" s="47"/>
+      <c r="EG3" s="47"/>
+      <c r="EH3" s="47"/>
+      <c r="EI3" s="47"/>
+      <c r="EJ3" s="47"/>
+      <c r="EK3" s="47"/>
+      <c r="EL3" s="47"/>
+      <c r="EM3" s="47"/>
+      <c r="EN3" s="47"/>
+      <c r="EO3" s="47"/>
+      <c r="EP3" s="47"/>
+      <c r="EQ3" s="47"/>
+      <c r="ER3" s="47" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
-      <c r="EU3" s="45"/>
-      <c r="EV3" s="45"/>
-      <c r="EW3" s="45"/>
-      <c r="EX3" s="45"/>
-      <c r="EY3" s="45"/>
-      <c r="EZ3" s="45"/>
-      <c r="FA3" s="45"/>
-      <c r="FB3" s="45"/>
-      <c r="FC3" s="45"/>
+      <c r="ES3" s="47"/>
+      <c r="ET3" s="47"/>
+      <c r="EU3" s="47"/>
+      <c r="EV3" s="47"/>
+      <c r="EW3" s="47"/>
+      <c r="EX3" s="47"/>
+      <c r="EY3" s="47"/>
+      <c r="EZ3" s="47"/>
+      <c r="FA3" s="47"/>
+      <c r="FB3" s="47"/>
+      <c r="FC3" s="47"/>
+      <c r="FD3" s="47"/>
     </row>
-    <row r="4" spans="2:159" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="71" t="s">
+    <row r="4" spans="2:160" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="70" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="75" t="s">
@@ -37134,85 +37355,85 @@
       <c r="BC4" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="BD4" s="64" t="s">
+      <c r="BD4" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="BE4" s="64" t="s">
+      <c r="BE4" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="BF4" s="64" t="s">
+      <c r="BF4" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="BG4" s="64" t="s">
+      <c r="BG4" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="BH4" s="64" t="s">
+      <c r="BH4" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="BI4" s="64" t="s">
+      <c r="BI4" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="BJ4" s="64" t="s">
+      <c r="BJ4" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="BK4" s="64" t="s">
+      <c r="BK4" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="BL4" s="64" t="s">
+      <c r="BL4" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="BM4" s="64" t="s">
+      <c r="BM4" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="BN4" s="64" t="s">
+      <c r="BN4" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="BO4" s="64" t="s">
+      <c r="BO4" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="BP4" s="64" t="s">
+      <c r="BP4" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="BQ4" s="64" t="s">
+      <c r="BQ4" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="BR4" s="64" t="s">
+      <c r="BR4" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="BS4" s="64" t="s">
+      <c r="BS4" s="63" t="s">
         <v>234</v>
       </c>
-      <c r="BT4" s="64" t="s">
+      <c r="BT4" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="BU4" s="63" t="s">
+      <c r="BU4" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="BV4" s="63" t="s">
+      <c r="BV4" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="BW4" s="63" t="s">
+      <c r="BW4" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="BX4" s="63" t="s">
+      <c r="BX4" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="BY4" s="63" t="s">
+      <c r="BY4" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="BZ4" s="63" t="s">
+      <c r="BZ4" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="CA4" s="64" t="s">
+      <c r="CA4" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="CB4" s="64" t="s">
+      <c r="CB4" s="63" t="s">
         <v>237</v>
       </c>
-      <c r="CC4" s="64" t="s">
+      <c r="CC4" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="CD4" s="64" t="s">
+      <c r="CD4" s="63" t="s">
         <v>239</v>
       </c>
       <c r="CE4" s="75" t="s">
@@ -37446,114 +37667,117 @@
       <c r="FC4" s="44" t="s">
         <v>438</v>
       </c>
+      <c r="FD4" s="44" t="s">
+        <v>439</v>
+      </c>
     </row>
-    <row r="5" spans="2:159" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="66"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
+    <row r="5" spans="2:160" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="65"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
       <c r="R5" s="81"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
       <c r="Y5" s="77"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
       <c r="AC5" s="77"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
       <c r="AI5" s="77"/>
       <c r="AJ5" s="77"/>
       <c r="AK5" s="77"/>
       <c r="AL5" s="77"/>
       <c r="AM5" s="77"/>
-      <c r="AN5" s="48"/>
+      <c r="AN5" s="46"/>
       <c r="AO5" s="77"/>
       <c r="AP5" s="77"/>
-      <c r="AQ5" s="48"/>
+      <c r="AQ5" s="46"/>
       <c r="AR5" s="77"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
       <c r="AX5" s="77"/>
       <c r="AY5" s="77"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
       <c r="BC5" s="77"/>
-      <c r="BD5" s="54"/>
-      <c r="BE5" s="54"/>
-      <c r="BF5" s="54"/>
-      <c r="BG5" s="54"/>
-      <c r="BH5" s="54"/>
-      <c r="BI5" s="54"/>
-      <c r="BJ5" s="54"/>
-      <c r="BK5" s="54"/>
-      <c r="BL5" s="54"/>
-      <c r="BM5" s="54"/>
-      <c r="BN5" s="54"/>
-      <c r="BO5" s="54"/>
-      <c r="BP5" s="54"/>
-      <c r="BQ5" s="54"/>
-      <c r="BR5" s="54"/>
-      <c r="BS5" s="54"/>
-      <c r="BT5" s="54"/>
-      <c r="BU5" s="56"/>
-      <c r="BV5" s="56"/>
-      <c r="BW5" s="56"/>
-      <c r="BX5" s="56"/>
-      <c r="BY5" s="56"/>
-      <c r="BZ5" s="56"/>
-      <c r="CA5" s="54"/>
-      <c r="CB5" s="54"/>
-      <c r="CC5" s="54"/>
-      <c r="CD5" s="54"/>
-      <c r="CE5" s="48"/>
-      <c r="CF5" s="48"/>
-      <c r="CG5" s="48"/>
-      <c r="CH5" s="48"/>
-      <c r="CI5" s="48"/>
-      <c r="CJ5" s="48"/>
-      <c r="CK5" s="48"/>
-      <c r="CL5" s="48"/>
-      <c r="CM5" s="48"/>
-      <c r="CN5" s="48"/>
-      <c r="CO5" s="48"/>
-      <c r="CP5" s="48"/>
-      <c r="CQ5" s="48"/>
-      <c r="CR5" s="48"/>
-      <c r="CS5" s="48"/>
-      <c r="CT5" s="48"/>
-      <c r="CU5" s="48"/>
-      <c r="CV5" s="48"/>
-      <c r="CW5" s="48"/>
-      <c r="CX5" s="48"/>
-      <c r="CY5" s="48"/>
-      <c r="CZ5" s="48"/>
-      <c r="DA5" s="48"/>
-      <c r="DB5" s="48"/>
-      <c r="DC5" s="48"/>
+      <c r="BD5" s="48"/>
+      <c r="BE5" s="48"/>
+      <c r="BF5" s="48"/>
+      <c r="BG5" s="48"/>
+      <c r="BH5" s="48"/>
+      <c r="BI5" s="48"/>
+      <c r="BJ5" s="48"/>
+      <c r="BK5" s="48"/>
+      <c r="BL5" s="48"/>
+      <c r="BM5" s="48"/>
+      <c r="BN5" s="48"/>
+      <c r="BO5" s="48"/>
+      <c r="BP5" s="48"/>
+      <c r="BQ5" s="48"/>
+      <c r="BR5" s="48"/>
+      <c r="BS5" s="48"/>
+      <c r="BT5" s="48"/>
+      <c r="BU5" s="53"/>
+      <c r="BV5" s="53"/>
+      <c r="BW5" s="53"/>
+      <c r="BX5" s="53"/>
+      <c r="BY5" s="53"/>
+      <c r="BZ5" s="53"/>
+      <c r="CA5" s="48"/>
+      <c r="CB5" s="48"/>
+      <c r="CC5" s="48"/>
+      <c r="CD5" s="48"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
+      <c r="CW5" s="46"/>
+      <c r="CX5" s="46"/>
+      <c r="CY5" s="46"/>
+      <c r="CZ5" s="46"/>
+      <c r="DA5" s="46"/>
+      <c r="DB5" s="46"/>
+      <c r="DC5" s="46"/>
       <c r="DD5" s="44"/>
       <c r="DE5" s="44"/>
       <c r="DF5" s="44"/>
@@ -37606,8 +37830,9 @@
       <c r="FA5" s="44"/>
       <c r="FB5" s="44"/>
       <c r="FC5" s="44"/>
+      <c r="FD5" s="44"/>
     </row>
-    <row r="6" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -38082,8 +38307,11 @@
       <c r="FC6" s="28">
         <v>88</v>
       </c>
+      <c r="FD6" s="28">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -38558,8 +38786,11 @@
       <c r="FC7" s="15">
         <v>3</v>
       </c>
+      <c r="FD7" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -39034,8 +39265,11 @@
       <c r="FC8" s="28">
         <v>11</v>
       </c>
+      <c r="FD8" s="28">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -39510,8 +39744,11 @@
       <c r="FC9" s="15">
         <v>107</v>
       </c>
+      <c r="FD9" s="15">
+        <v>93</v>
+      </c>
     </row>
-    <row r="10" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -39986,8 +40223,11 @@
       <c r="FC10" s="15">
         <v>0</v>
       </c>
+      <c r="FD10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -40462,8 +40702,11 @@
       <c r="FC11" s="15">
         <v>8</v>
       </c>
+      <c r="FD11" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -40938,8 +41181,11 @@
       <c r="FC12" s="15">
         <v>12</v>
       </c>
+      <c r="FD12" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="13" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -41414,8 +41660,11 @@
       <c r="FC13" s="15">
         <v>24</v>
       </c>
+      <c r="FD13" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="14" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -41890,8 +42139,11 @@
       <c r="FC14" s="15">
         <v>24</v>
       </c>
+      <c r="FD14" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="15" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -42366,8 +42618,11 @@
       <c r="FC15" s="15">
         <v>3</v>
       </c>
+      <c r="FD15" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -42842,8 +43097,11 @@
       <c r="FC16" s="28">
         <v>109</v>
       </c>
+      <c r="FD16" s="28">
+        <v>93</v>
+      </c>
     </row>
-    <row r="17" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -43318,8 +43576,11 @@
       <c r="FC17" s="15">
         <v>150</v>
       </c>
+      <c r="FD17" s="15">
+        <v>160</v>
+      </c>
     </row>
-    <row r="18" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -43794,8 +44055,11 @@
       <c r="FC18" s="34">
         <v>1751</v>
       </c>
+      <c r="FD18" s="34">
+        <v>1618</v>
+      </c>
     </row>
-    <row r="19" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
@@ -44270,8 +44534,11 @@
       <c r="FC19" s="15">
         <v>53</v>
       </c>
+      <c r="FD19" s="15">
+        <v>51</v>
+      </c>
     </row>
-    <row r="20" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -44744,8 +45011,11 @@
       <c r="FC20" s="28">
         <v>192</v>
       </c>
+      <c r="FD20" s="28">
+        <v>143</v>
+      </c>
     </row>
-    <row r="21" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -45218,8 +45488,11 @@
       <c r="FC21" s="15">
         <v>51</v>
       </c>
+      <c r="FD21" s="15">
+        <v>35</v>
+      </c>
     </row>
-    <row r="22" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -45694,8 +45967,11 @@
       <c r="FC22" s="15">
         <v>9</v>
       </c>
+      <c r="FD22" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -46170,8 +46446,11 @@
       <c r="FC23" s="15">
         <v>0</v>
       </c>
+      <c r="FD23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -46646,8 +46925,11 @@
       <c r="FC24" s="15">
         <v>11</v>
       </c>
+      <c r="FD24" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -47122,8 +47404,11 @@
       <c r="FC25" s="15">
         <v>0</v>
       </c>
+      <c r="FD25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -47598,8 +47883,11 @@
       <c r="FC26" s="15">
         <v>8</v>
       </c>
+      <c r="FD26" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="27" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -48074,8 +48362,11 @@
       <c r="FC27" s="15">
         <v>0</v>
       </c>
+      <c r="FD27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -48550,8 +48841,11 @@
       <c r="FC28" s="15">
         <v>1</v>
       </c>
+      <c r="FD28" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -49026,8 +49320,11 @@
       <c r="FC29" s="15">
         <v>2</v>
       </c>
+      <c r="FD29" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -49500,8 +49797,11 @@
       <c r="FC30" s="15">
         <v>17</v>
       </c>
+      <c r="FD30" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="31" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -49976,8 +50276,11 @@
       <c r="FC31" s="15">
         <v>36</v>
       </c>
+      <c r="FD31" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="32" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -50452,8 +50755,11 @@
       <c r="FC32" s="15">
         <v>0</v>
       </c>
+      <c r="FD32" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -50928,8 +51234,11 @@
       <c r="FC33" s="15">
         <v>0</v>
       </c>
+      <c r="FD33" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -51404,8 +51713,11 @@
       <c r="FC34" s="15">
         <v>60</v>
       </c>
+      <c r="FD34" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="35" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
@@ -51880,8 +52192,11 @@
       <c r="FC35" s="15">
         <v>432</v>
       </c>
+      <c r="FD35" s="15">
+        <v>345</v>
+      </c>
     </row>
-    <row r="36" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -52354,8 +52669,11 @@
       <c r="FC36" s="28">
         <v>64</v>
       </c>
+      <c r="FD36" s="28">
+        <v>35</v>
+      </c>
     </row>
-    <row r="37" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -52830,8 +53148,11 @@
       <c r="FC37" s="15">
         <v>77</v>
       </c>
+      <c r="FD37" s="15">
+        <v>45</v>
+      </c>
     </row>
-    <row r="38" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -53306,8 +53627,11 @@
       <c r="FC38" s="15">
         <v>15</v>
       </c>
+      <c r="FD38" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="39" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -53782,8 +54106,11 @@
       <c r="FC39" s="15">
         <v>13</v>
       </c>
+      <c r="FD39" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="40" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -54258,8 +54585,11 @@
       <c r="FC40" s="15">
         <v>0</v>
       </c>
+      <c r="FD40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -54734,8 +55064,11 @@
       <c r="FC41" s="15">
         <v>0</v>
       </c>
+      <c r="FD41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -55210,8 +55543,11 @@
       <c r="FC42" s="15">
         <v>12</v>
       </c>
+      <c r="FD42" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="43" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -55686,8 +56022,11 @@
       <c r="FC43" s="28">
         <v>58</v>
       </c>
+      <c r="FD43" s="28">
+        <v>41</v>
+      </c>
     </row>
-    <row r="44" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -56162,8 +56501,11 @@
       <c r="FC44" s="15">
         <v>6</v>
       </c>
+      <c r="FD44" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -56638,8 +56980,11 @@
       <c r="FC45" s="15">
         <v>5</v>
       </c>
+      <c r="FD45" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="46" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -57114,8 +57459,11 @@
       <c r="FC46" s="15">
         <v>20</v>
       </c>
+      <c r="FD46" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="47" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -57590,8 +57938,11 @@
       <c r="FC47" s="15">
         <v>3</v>
       </c>
+      <c r="FD47" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -58066,8 +58417,11 @@
       <c r="FC48" s="15">
         <v>12</v>
       </c>
+      <c r="FD48" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
@@ -58542,8 +58896,11 @@
       <c r="FC49" s="15">
         <v>27</v>
       </c>
+      <c r="FD49" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="50" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -59016,8 +59373,11 @@
       <c r="FC50" s="15">
         <v>10</v>
       </c>
+      <c r="FD50" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="51" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -59492,8 +59852,11 @@
       <c r="FC51" s="15">
         <v>4</v>
       </c>
+      <c r="FD51" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -59968,8 +60331,11 @@
       <c r="FC52" s="15">
         <v>24</v>
       </c>
+      <c r="FD52" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="53" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -60444,8 +60810,11 @@
       <c r="FC53" s="15">
         <v>30</v>
       </c>
+      <c r="FD53" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="54" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -60920,8 +61289,11 @@
       <c r="FC54" s="15">
         <v>4</v>
       </c>
+      <c r="FD54" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -61396,8 +61768,11 @@
       <c r="FC55" s="15">
         <v>9</v>
       </c>
+      <c r="FD55" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -61872,8 +62247,11 @@
       <c r="FC56" s="15">
         <v>1</v>
       </c>
+      <c r="FD56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -62348,8 +62726,11 @@
       <c r="FC57" s="15">
         <v>0</v>
       </c>
+      <c r="FD57" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="2:159" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -62974,15 +63355,20 @@
         <v>3793</v>
       </c>
       <c r="FC58" s="14">
-        <f t="shared" ref="FC58" si="11">SUM(FC6:FC57)</f>
+        <f t="shared" ref="FC58:FD58" si="11">SUM(FC6:FC57)</f>
         <v>3556</v>
+      </c>
+      <c r="FD58" s="14">
+        <f t="shared" si="11"/>
+        <v>3075</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="174">
+    <mergeCell ref="FD4:FD5"/>
+    <mergeCell ref="DD2:FD2"/>
+    <mergeCell ref="ER3:FD3"/>
     <mergeCell ref="FC4:FC5"/>
-    <mergeCell ref="DD2:FC2"/>
-    <mergeCell ref="ER3:FC3"/>
     <mergeCell ref="FB4:FB5"/>
     <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="BD2:DC2"/>
@@ -63003,7 +63389,6 @@
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="CW4:CW5"/>
-    <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -63120,6 +63505,7 @@
     <mergeCell ref="CQ4:CQ5"/>
     <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CV4:CV5"/>
     <mergeCell ref="EY4:EY5"/>
     <mergeCell ref="EZ4:EZ5"/>
     <mergeCell ref="EG4:EG5"/>
@@ -63156,38 +63542,43 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="18" priority="11">
+    <cfRule type="containsBlanks" dxfId="21" priority="12">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="17" priority="10">
+    <cfRule type="containsBlanks" dxfId="20" priority="11">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EH6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="16" priority="12">
+    <cfRule type="containsBlanks" dxfId="19" priority="13">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="15" priority="4">
+    <cfRule type="containsBlanks" dxfId="18" priority="5">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="14" priority="3">
+    <cfRule type="containsBlanks" dxfId="17" priority="4">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="13" priority="2">
+    <cfRule type="containsBlanks" dxfId="16" priority="3">
       <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FC6:FC57">
-    <cfRule type="containsBlanks" dxfId="12" priority="1">
+    <cfRule type="containsBlanks" dxfId="15" priority="2">
       <formula>LEN(TRIM(FC6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FD6:FD57">
+    <cfRule type="containsBlanks" dxfId="14" priority="1">
+      <formula>LEN(TRIM(FD6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -63203,7 +63594,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="9" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
+          <x14:cfRule type="containsBlanks" priority="10" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -63226,7 +63617,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DC61"/>
+  <dimension ref="A1:DD61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -63237,11 +63628,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="107" width="10.875" style="1" customWidth="1"/>
-    <col min="108" max="16384" width="8.625" style="1"/>
+    <col min="54" max="108" width="10.875" style="1" customWidth="1"/>
+    <col min="109" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:108" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -63323,125 +63714,127 @@
       <c r="CZ1" s="19"/>
       <c r="DA1" s="19"/>
       <c r="DB1" s="19"/>
-      <c r="DC1" s="19" t="s">
+      <c r="DC1" s="19"/>
+      <c r="DD1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:107" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="58" t="s">
+    <row r="2" spans="1:108" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
       <c r="BC2" s="85"/>
-      <c r="BD2" s="73" t="s">
+      <c r="BD2" s="72" t="s">
         <v>324</v>
       </c>
-      <c r="BE2" s="73"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="73"/>
-      <c r="BH2" s="73"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="73"/>
-      <c r="BM2" s="73"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="73"/>
-      <c r="BS2" s="73"/>
-      <c r="BT2" s="73"/>
-      <c r="BU2" s="73"/>
-      <c r="BV2" s="73"/>
-      <c r="BW2" s="73"/>
-      <c r="BX2" s="73"/>
-      <c r="BY2" s="73"/>
-      <c r="BZ2" s="73"/>
-      <c r="CA2" s="73"/>
-      <c r="CB2" s="73"/>
-      <c r="CC2" s="73"/>
-      <c r="CD2" s="73"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="73"/>
-      <c r="CG2" s="73"/>
-      <c r="CH2" s="73"/>
-      <c r="CI2" s="73"/>
-      <c r="CJ2" s="73"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="73"/>
-      <c r="CM2" s="73"/>
-      <c r="CN2" s="73"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="73"/>
-      <c r="CQ2" s="73"/>
-      <c r="CR2" s="73"/>
-      <c r="CS2" s="73"/>
-      <c r="CT2" s="73"/>
-      <c r="CU2" s="73"/>
-      <c r="CV2" s="73"/>
-      <c r="CW2" s="73"/>
-      <c r="CX2" s="73"/>
-      <c r="CY2" s="73"/>
-      <c r="CZ2" s="73"/>
-      <c r="DA2" s="73"/>
-      <c r="DB2" s="73"/>
-      <c r="DC2" s="73"/>
+      <c r="BE2" s="72"/>
+      <c r="BF2" s="72"/>
+      <c r="BG2" s="72"/>
+      <c r="BH2" s="72"/>
+      <c r="BI2" s="72"/>
+      <c r="BJ2" s="72"/>
+      <c r="BK2" s="72"/>
+      <c r="BL2" s="72"/>
+      <c r="BM2" s="72"/>
+      <c r="BN2" s="72"/>
+      <c r="BO2" s="72"/>
+      <c r="BP2" s="72"/>
+      <c r="BQ2" s="72"/>
+      <c r="BR2" s="72"/>
+      <c r="BS2" s="72"/>
+      <c r="BT2" s="72"/>
+      <c r="BU2" s="72"/>
+      <c r="BV2" s="72"/>
+      <c r="BW2" s="72"/>
+      <c r="BX2" s="72"/>
+      <c r="BY2" s="72"/>
+      <c r="BZ2" s="72"/>
+      <c r="CA2" s="72"/>
+      <c r="CB2" s="72"/>
+      <c r="CC2" s="72"/>
+      <c r="CD2" s="72"/>
+      <c r="CE2" s="72"/>
+      <c r="CF2" s="72"/>
+      <c r="CG2" s="72"/>
+      <c r="CH2" s="72"/>
+      <c r="CI2" s="72"/>
+      <c r="CJ2" s="72"/>
+      <c r="CK2" s="72"/>
+      <c r="CL2" s="72"/>
+      <c r="CM2" s="72"/>
+      <c r="CN2" s="72"/>
+      <c r="CO2" s="72"/>
+      <c r="CP2" s="72"/>
+      <c r="CQ2" s="72"/>
+      <c r="CR2" s="72"/>
+      <c r="CS2" s="72"/>
+      <c r="CT2" s="72"/>
+      <c r="CU2" s="72"/>
+      <c r="CV2" s="72"/>
+      <c r="CW2" s="72"/>
+      <c r="CX2" s="72"/>
+      <c r="CY2" s="72"/>
+      <c r="CZ2" s="72"/>
+      <c r="DA2" s="72"/>
+      <c r="DB2" s="72"/>
+      <c r="DC2" s="72"/>
+      <c r="DD2" s="72"/>
     </row>
-    <row r="3" spans="1:107" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
+    <row r="3" spans="1:108" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="87" t="s">
         <v>216</v>
       </c>
@@ -63484,238 +63877,239 @@
       <c r="AO3" s="87"/>
       <c r="AP3" s="87"/>
       <c r="AQ3" s="87"/>
-      <c r="AR3" s="45" t="s">
+      <c r="AR3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="45" t="s">
+      <c r="AS3" s="47"/>
+      <c r="AT3" s="47"/>
+      <c r="AU3" s="47"/>
+      <c r="AV3" s="47"/>
+      <c r="AW3" s="47"/>
+      <c r="AX3" s="47"/>
+      <c r="AY3" s="47"/>
+      <c r="AZ3" s="47"/>
+      <c r="BA3" s="47"/>
+      <c r="BB3" s="47"/>
+      <c r="BC3" s="47"/>
+      <c r="BD3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="45"/>
-      <c r="BF3" s="45"/>
-      <c r="BG3" s="45"/>
-      <c r="BH3" s="45"/>
-      <c r="BI3" s="45"/>
-      <c r="BJ3" s="45"/>
-      <c r="BK3" s="45"/>
-      <c r="BL3" s="45"/>
-      <c r="BM3" s="45"/>
-      <c r="BN3" s="45"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="45"/>
-      <c r="BQ3" s="45"/>
-      <c r="BR3" s="45"/>
-      <c r="BS3" s="45"/>
-      <c r="BT3" s="45"/>
-      <c r="BU3" s="45"/>
-      <c r="BV3" s="45"/>
-      <c r="BW3" s="45"/>
-      <c r="BX3" s="45"/>
-      <c r="BY3" s="45"/>
-      <c r="BZ3" s="45"/>
-      <c r="CA3" s="45"/>
-      <c r="CB3" s="45"/>
-      <c r="CC3" s="45"/>
-      <c r="CD3" s="45"/>
-      <c r="CE3" s="45"/>
-      <c r="CF3" s="45"/>
-      <c r="CG3" s="45"/>
-      <c r="CH3" s="45"/>
-      <c r="CI3" s="45"/>
-      <c r="CJ3" s="45"/>
-      <c r="CK3" s="45"/>
-      <c r="CL3" s="45"/>
-      <c r="CM3" s="45"/>
-      <c r="CN3" s="45"/>
-      <c r="CO3" s="45"/>
-      <c r="CP3" s="45"/>
-      <c r="CQ3" s="45"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="47"/>
+      <c r="BF3" s="47"/>
+      <c r="BG3" s="47"/>
+      <c r="BH3" s="47"/>
+      <c r="BI3" s="47"/>
+      <c r="BJ3" s="47"/>
+      <c r="BK3" s="47"/>
+      <c r="BL3" s="47"/>
+      <c r="BM3" s="47"/>
+      <c r="BN3" s="47"/>
+      <c r="BO3" s="47"/>
+      <c r="BP3" s="47"/>
+      <c r="BQ3" s="47"/>
+      <c r="BR3" s="47"/>
+      <c r="BS3" s="47"/>
+      <c r="BT3" s="47"/>
+      <c r="BU3" s="47"/>
+      <c r="BV3" s="47"/>
+      <c r="BW3" s="47"/>
+      <c r="BX3" s="47"/>
+      <c r="BY3" s="47"/>
+      <c r="BZ3" s="47"/>
+      <c r="CA3" s="47"/>
+      <c r="CB3" s="47"/>
+      <c r="CC3" s="47"/>
+      <c r="CD3" s="47"/>
+      <c r="CE3" s="47"/>
+      <c r="CF3" s="47"/>
+      <c r="CG3" s="47"/>
+      <c r="CH3" s="47"/>
+      <c r="CI3" s="47"/>
+      <c r="CJ3" s="47"/>
+      <c r="CK3" s="47"/>
+      <c r="CL3" s="47"/>
+      <c r="CM3" s="47"/>
+      <c r="CN3" s="47"/>
+      <c r="CO3" s="47"/>
+      <c r="CP3" s="47"/>
+      <c r="CQ3" s="47"/>
+      <c r="CR3" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
+      <c r="CS3" s="47"/>
+      <c r="CT3" s="47"/>
+      <c r="CU3" s="47"/>
+      <c r="CV3" s="47"/>
+      <c r="CW3" s="47"/>
+      <c r="CX3" s="47"/>
+      <c r="CY3" s="47"/>
+      <c r="CZ3" s="47"/>
+      <c r="DA3" s="47"/>
+      <c r="DB3" s="47"/>
+      <c r="DC3" s="47"/>
+      <c r="DD3" s="47"/>
     </row>
-    <row r="4" spans="1:107" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="54" t="s">
+    <row r="4" spans="1:108" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="54" t="s">
+      <c r="L4" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="54" t="s">
+      <c r="M4" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="54" t="s">
+      <c r="N4" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="54" t="s">
+      <c r="P4" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="54" t="s">
+      <c r="Q4" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="54" t="s">
+      <c r="R4" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="54" t="s">
+      <c r="S4" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="54" t="s">
+      <c r="T4" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="54" t="s">
+      <c r="U4" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="54" t="s">
+      <c r="V4" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="54" t="s">
+      <c r="W4" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="54" t="s">
+      <c r="X4" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="54" t="s">
+      <c r="Y4" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="54" t="s">
+      <c r="Z4" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="54" t="s">
+      <c r="AA4" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="54" t="s">
+      <c r="AB4" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="54" t="s">
+      <c r="AC4" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="54" t="s">
+      <c r="AD4" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="48" t="s">
+      <c r="AE4" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="48" t="s">
+      <c r="AF4" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="48" t="s">
+      <c r="AG4" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="48" t="s">
+      <c r="AI4" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="48" t="s">
+      <c r="AJ4" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="48" t="s">
+      <c r="AL4" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="48" t="s">
+      <c r="AM4" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="46" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="48" t="s">
+      <c r="AO4" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="48" t="s">
+      <c r="AP4" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="48" t="s">
+      <c r="AR4" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="48" t="s">
+      <c r="AS4" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="48" t="s">
+      <c r="AT4" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="48" t="s">
+      <c r="AU4" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="48" t="s">
+      <c r="AV4" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="48" t="s">
+      <c r="AW4" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="48" t="s">
+      <c r="AX4" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="48" t="s">
+      <c r="AY4" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="48" t="s">
+      <c r="AZ4" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="48" t="s">
+      <c r="BA4" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="48" t="s">
+      <c r="BC4" s="46" t="s">
         <v>303</v>
       </c>
       <c r="BD4" s="44" t="s">
@@ -63874,84 +64268,87 @@
       <c r="DC4" s="44" t="s">
         <v>437</v>
       </c>
+      <c r="DD4" s="44" t="s">
+        <v>440</v>
+      </c>
     </row>
-    <row r="5" spans="1:107" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="66"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="46"/>
-      <c r="BM5" s="46"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
-      <c r="BQ5" s="46"/>
-      <c r="BR5" s="46"/>
-      <c r="BS5" s="46"/>
-      <c r="BT5" s="46"/>
-      <c r="BU5" s="46"/>
-      <c r="BV5" s="46"/>
-      <c r="BW5" s="46"/>
-      <c r="BX5" s="46"/>
-      <c r="BY5" s="46"/>
+    <row r="5" spans="1:108" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="65"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AQ5" s="45"/>
+      <c r="AR5" s="45"/>
+      <c r="AS5" s="45"/>
+      <c r="AT5" s="45"/>
+      <c r="AU5" s="45"/>
+      <c r="AV5" s="45"/>
+      <c r="AW5" s="45"/>
+      <c r="AX5" s="45"/>
+      <c r="AY5" s="45"/>
+      <c r="AZ5" s="45"/>
+      <c r="BA5" s="45"/>
+      <c r="BB5" s="45"/>
+      <c r="BC5" s="45"/>
+      <c r="BD5" s="45"/>
+      <c r="BE5" s="45"/>
+      <c r="BF5" s="45"/>
+      <c r="BG5" s="45"/>
+      <c r="BH5" s="45"/>
+      <c r="BI5" s="45"/>
+      <c r="BJ5" s="45"/>
+      <c r="BK5" s="45"/>
+      <c r="BL5" s="45"/>
+      <c r="BM5" s="45"/>
+      <c r="BN5" s="45"/>
+      <c r="BO5" s="45"/>
+      <c r="BP5" s="45"/>
+      <c r="BQ5" s="45"/>
+      <c r="BR5" s="45"/>
+      <c r="BS5" s="45"/>
+      <c r="BT5" s="45"/>
+      <c r="BU5" s="45"/>
+      <c r="BV5" s="45"/>
+      <c r="BW5" s="45"/>
+      <c r="BX5" s="45"/>
+      <c r="BY5" s="45"/>
       <c r="BZ5" s="44"/>
       <c r="CA5" s="44"/>
       <c r="CB5" s="44"/>
@@ -63982,8 +64379,9 @@
       <c r="DA5" s="44"/>
       <c r="DB5" s="44"/>
       <c r="DC5" s="44"/>
+      <c r="DD5" s="44"/>
     </row>
-    <row r="6" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -64303,8 +64701,11 @@
       <c r="DC6" s="28">
         <v>18</v>
       </c>
+      <c r="DD6" s="28">
+        <v>19</v>
+      </c>
     </row>
-    <row r="7" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -64623,8 +65024,11 @@
       <c r="DC7" s="15">
         <v>0</v>
       </c>
+      <c r="DD7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -64943,8 +65347,11 @@
       <c r="DC8" s="28">
         <v>0</v>
       </c>
+      <c r="DD8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -65264,8 +65671,11 @@
       <c r="DC9" s="28">
         <v>8</v>
       </c>
+      <c r="DD9" s="28">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -65584,8 +65994,11 @@
       <c r="DC10" s="28">
         <v>0</v>
       </c>
+      <c r="DD10" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -65904,8 +66317,11 @@
       <c r="DC11" s="28">
         <v>3</v>
       </c>
+      <c r="DD11" s="28">
+        <v>8</v>
+      </c>
     </row>
-    <row r="12" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -66224,8 +66640,11 @@
       <c r="DC12" s="15">
         <v>2</v>
       </c>
+      <c r="DD12" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -66544,8 +66963,11 @@
       <c r="DC13" s="15">
         <v>16</v>
       </c>
+      <c r="DD13" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="14" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -66864,8 +67286,11 @@
       <c r="DC14" s="15">
         <v>10</v>
       </c>
+      <c r="DD14" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -67184,8 +67609,11 @@
       <c r="DC15" s="15">
         <v>0</v>
       </c>
+      <c r="DD15" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -67505,8 +67933,11 @@
       <c r="DC16" s="28">
         <v>2</v>
       </c>
+      <c r="DD16" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -67825,8 +68256,11 @@
       <c r="DC17" s="15">
         <v>27</v>
       </c>
+      <c r="DD17" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="18" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -68146,8 +68580,11 @@
       <c r="DC18" s="34">
         <v>236</v>
       </c>
+      <c r="DD18" s="34">
+        <v>201</v>
+      </c>
     </row>
-    <row r="19" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="78" t="s">
         <v>27</v>
@@ -68467,8 +68904,11 @@
       <c r="DC19" s="15">
         <v>24</v>
       </c>
+      <c r="DD19" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="20" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
@@ -68786,8 +69226,11 @@
       <c r="DC20" s="28">
         <v>42</v>
       </c>
+      <c r="DD20" s="28">
+        <v>26</v>
+      </c>
     </row>
-    <row r="21" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
@@ -69105,8 +69548,11 @@
       <c r="DC21" s="15">
         <v>4</v>
       </c>
+      <c r="DD21" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -69425,8 +69871,11 @@
       <c r="DC22" s="15">
         <v>1</v>
       </c>
+      <c r="DD22" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -69745,8 +70194,11 @@
       <c r="DC23" s="15">
         <v>0</v>
       </c>
+      <c r="DD23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -70065,8 +70517,11 @@
       <c r="DC24" s="15">
         <v>0</v>
       </c>
+      <c r="DD24" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -70385,8 +70840,11 @@
       <c r="DC25" s="15">
         <v>0</v>
       </c>
+      <c r="DD25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -70705,8 +71163,11 @@
       <c r="DC26" s="15">
         <v>4</v>
       </c>
+      <c r="DD26" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -71025,8 +71486,11 @@
       <c r="DC27" s="15">
         <v>0</v>
       </c>
+      <c r="DD27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -71345,8 +71809,11 @@
       <c r="DC28" s="15">
         <v>0</v>
       </c>
+      <c r="DD28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -71665,8 +72132,11 @@
       <c r="DC29" s="15">
         <v>0</v>
       </c>
+      <c r="DD29" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -71983,8 +72453,11 @@
       <c r="DC30" s="15">
         <v>9</v>
       </c>
+      <c r="DD30" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -72304,8 +72777,11 @@
       <c r="DC31" s="15">
         <v>11</v>
       </c>
+      <c r="DD31" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="32" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -72624,8 +73100,11 @@
       <c r="DC32" s="15">
         <v>0</v>
       </c>
+      <c r="DD32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -72944,8 +73423,11 @@
       <c r="DC33" s="15">
         <v>0</v>
       </c>
+      <c r="DD33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -73265,8 +73747,11 @@
       <c r="DC34" s="15">
         <v>13</v>
       </c>
+      <c r="DD34" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="35" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="78" t="s">
         <v>56</v>
@@ -73586,8 +74071,11 @@
       <c r="DC35" s="15">
         <v>41</v>
       </c>
+      <c r="DD35" s="15">
+        <v>53</v>
+      </c>
     </row>
-    <row r="36" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -73904,8 +74392,11 @@
       <c r="DC36" s="28">
         <v>9</v>
       </c>
+      <c r="DD36" s="28">
+        <v>4</v>
+      </c>
     </row>
-    <row r="37" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -74225,8 +74716,11 @@
       <c r="DC37" s="15">
         <v>3</v>
       </c>
+      <c r="DD37" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="38" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -74545,8 +75039,11 @@
       <c r="DC38" s="15">
         <v>1</v>
       </c>
+      <c r="DD38" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -74865,8 +75362,11 @@
       <c r="DC39" s="15">
         <v>3</v>
       </c>
+      <c r="DD39" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -75185,8 +75685,11 @@
       <c r="DC40" s="15">
         <v>1</v>
       </c>
+      <c r="DD40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -75505,8 +76008,11 @@
       <c r="DC41" s="15">
         <v>0</v>
       </c>
+      <c r="DD41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -75825,8 +76331,11 @@
       <c r="DC42" s="15">
         <v>2</v>
       </c>
+      <c r="DD42" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -76145,8 +76654,11 @@
       <c r="DC43" s="28">
         <v>17</v>
       </c>
+      <c r="DD43" s="28">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -76465,8 +76977,11 @@
       <c r="DC44" s="15">
         <v>1</v>
       </c>
+      <c r="DD44" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -76785,8 +77300,11 @@
       <c r="DC45" s="15">
         <v>5</v>
       </c>
+      <c r="DD45" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -77105,8 +77623,11 @@
       <c r="DC46" s="15">
         <v>0</v>
       </c>
+      <c r="DD46" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -77425,8 +77946,11 @@
       <c r="DC47" s="15">
         <v>0</v>
       </c>
+      <c r="DD47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -77745,8 +78269,11 @@
       <c r="DC48" s="15">
         <v>5</v>
       </c>
+      <c r="DD48" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="49" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="78" t="s">
         <v>83</v>
@@ -78066,8 +78593,11 @@
       <c r="DC49" s="15">
         <v>1</v>
       </c>
+      <c r="DD49" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:107" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -78384,8 +78914,11 @@
       <c r="DC50" s="15">
         <v>1</v>
       </c>
+      <c r="DD50" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="51" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -78704,8 +79237,11 @@
       <c r="DC51" s="15">
         <v>0</v>
       </c>
+      <c r="DD51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -79024,8 +79560,11 @@
       <c r="DC52" s="15">
         <v>3</v>
       </c>
+      <c r="DD52" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -79344,8 +79883,11 @@
       <c r="DC53" s="15">
         <v>10</v>
       </c>
+      <c r="DD53" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="54" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -79664,8 +80206,11 @@
       <c r="DC54" s="15">
         <v>4</v>
       </c>
+      <c r="DD54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -79984,8 +80529,11 @@
       <c r="DC55" s="15">
         <v>1</v>
       </c>
+      <c r="DD55" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -80304,8 +80852,11 @@
       <c r="DC56" s="15">
         <v>0</v>
       </c>
+      <c r="DD56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -80624,8 +81175,11 @@
       <c r="DC57" s="15">
         <v>0</v>
       </c>
+      <c r="DD57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -81046,8 +81600,12 @@
         <f t="shared" si="10"/>
         <v>538</v>
       </c>
+      <c r="DD58" s="14">
+        <f t="shared" ref="DD58" si="11">SUM(DD6:DD57)</f>
+        <v>486</v>
+      </c>
     </row>
-    <row r="59" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -81080,7 +81638,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -81113,7 +81671,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:107" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -81147,10 +81705,11 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="118">
+    <mergeCell ref="DD4:DD5"/>
+    <mergeCell ref="BD2:DD2"/>
+    <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="DC4:DC5"/>
-    <mergeCell ref="BD2:DC2"/>
-    <mergeCell ref="CR3:DC3"/>
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="DA4:DA5"/>
     <mergeCell ref="B19:B21"/>
@@ -81171,7 +81730,6 @@
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="BC4:BC5"/>
     <mergeCell ref="BF4:BF5"/>
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="AS4:AS5"/>
@@ -81217,6 +81775,7 @@
     <mergeCell ref="AJ4:AJ5"/>
     <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BC4:BC5"/>
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="BY4:BY5"/>
@@ -81268,12 +81827,12 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="CH6:CX57 CZ6:CZ57 DA10">
-    <cfRule type="containsBlanks" dxfId="10" priority="8">
+    <cfRule type="containsBlanks" dxfId="12" priority="9">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY6:CY57">
-    <cfRule type="containsBlanks" dxfId="9" priority="6">
+    <cfRule type="containsBlanks" dxfId="11" priority="7">
       <formula>LEN(TRIM(CY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -81288,7 +81847,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="9" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="10" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81301,7 +81860,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="19" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="20" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81314,7 +81873,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="3" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
+          <x14:cfRule type="containsBlanks" priority="4" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81327,7 +81886,7 @@
           <xm:sqref>DB6:DB57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="1" id="{DFAC2C1F-0AE8-46F8-BC08-A989DBFF9333}">
+          <x14:cfRule type="containsBlanks" priority="2" id="{DFAC2C1F-0AE8-46F8-BC08-A989DBFF9333}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81337,7 +81896,20 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>DC6:DC57</xm:sqref>
+          <xm:sqref>DC6:DC57 DD56</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="1" id="{1D86A354-19E7-4BAA-A9D3-CC06A45CD35E}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DD6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DD6:DD55 DD57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -81445,128 +82017,129 @@
       <c r="CZ1" s="19"/>
       <c r="DA1" s="19"/>
       <c r="DB1" s="19"/>
-      <c r="DC1" s="19" t="s">
+      <c r="DC1" s="19"/>
+      <c r="DD1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:110" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="58" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="73" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
       <c r="BC2" s="85"/>
-      <c r="BD2" s="73" t="s">
+      <c r="BD2" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="73"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="73"/>
-      <c r="BH2" s="73"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="73"/>
-      <c r="BM2" s="73"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="73"/>
-      <c r="BS2" s="73"/>
-      <c r="BT2" s="73"/>
-      <c r="BU2" s="73"/>
-      <c r="BV2" s="73"/>
-      <c r="BW2" s="73"/>
-      <c r="BX2" s="73"/>
-      <c r="BY2" s="73"/>
-      <c r="BZ2" s="73"/>
-      <c r="CA2" s="73"/>
-      <c r="CB2" s="73"/>
-      <c r="CC2" s="73"/>
-      <c r="CD2" s="73"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="73"/>
-      <c r="CG2" s="73"/>
-      <c r="CH2" s="73"/>
-      <c r="CI2" s="73"/>
-      <c r="CJ2" s="73"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="73"/>
-      <c r="CM2" s="73"/>
-      <c r="CN2" s="73"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="73"/>
-      <c r="CQ2" s="73"/>
-      <c r="CR2" s="73"/>
-      <c r="CS2" s="73"/>
-      <c r="CT2" s="73"/>
-      <c r="CU2" s="73"/>
-      <c r="CV2" s="73"/>
-      <c r="CW2" s="73"/>
-      <c r="CX2" s="73"/>
-      <c r="CY2" s="73"/>
-      <c r="CZ2" s="73"/>
-      <c r="DA2" s="73"/>
-      <c r="DB2" s="73"/>
-      <c r="DC2" s="73"/>
-      <c r="DD2" s="20"/>
+      <c r="BE2" s="72"/>
+      <c r="BF2" s="72"/>
+      <c r="BG2" s="72"/>
+      <c r="BH2" s="72"/>
+      <c r="BI2" s="72"/>
+      <c r="BJ2" s="72"/>
+      <c r="BK2" s="72"/>
+      <c r="BL2" s="72"/>
+      <c r="BM2" s="72"/>
+      <c r="BN2" s="72"/>
+      <c r="BO2" s="72"/>
+      <c r="BP2" s="72"/>
+      <c r="BQ2" s="72"/>
+      <c r="BR2" s="72"/>
+      <c r="BS2" s="72"/>
+      <c r="BT2" s="72"/>
+      <c r="BU2" s="72"/>
+      <c r="BV2" s="72"/>
+      <c r="BW2" s="72"/>
+      <c r="BX2" s="72"/>
+      <c r="BY2" s="72"/>
+      <c r="BZ2" s="72"/>
+      <c r="CA2" s="72"/>
+      <c r="CB2" s="72"/>
+      <c r="CC2" s="72"/>
+      <c r="CD2" s="72"/>
+      <c r="CE2" s="72"/>
+      <c r="CF2" s="72"/>
+      <c r="CG2" s="72"/>
+      <c r="CH2" s="72"/>
+      <c r="CI2" s="72"/>
+      <c r="CJ2" s="72"/>
+      <c r="CK2" s="72"/>
+      <c r="CL2" s="72"/>
+      <c r="CM2" s="72"/>
+      <c r="CN2" s="72"/>
+      <c r="CO2" s="72"/>
+      <c r="CP2" s="72"/>
+      <c r="CQ2" s="72"/>
+      <c r="CR2" s="72"/>
+      <c r="CS2" s="72"/>
+      <c r="CT2" s="72"/>
+      <c r="CU2" s="72"/>
+      <c r="CV2" s="72"/>
+      <c r="CW2" s="72"/>
+      <c r="CX2" s="72"/>
+      <c r="CY2" s="72"/>
+      <c r="CZ2" s="72"/>
+      <c r="DA2" s="72"/>
+      <c r="DB2" s="72"/>
+      <c r="DC2" s="72"/>
+      <c r="DD2" s="72"/>
       <c r="DE2" s="20"/>
       <c r="DF2" s="20"/>
     </row>
     <row r="3" spans="1:110" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="87" t="s">
         <v>216</v>
       </c>
@@ -81609,241 +82182,241 @@
       <c r="AO3" s="87"/>
       <c r="AP3" s="87"/>
       <c r="AQ3" s="87"/>
-      <c r="AR3" s="45" t="s">
+      <c r="AR3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="45" t="s">
+      <c r="AS3" s="47"/>
+      <c r="AT3" s="47"/>
+      <c r="AU3" s="47"/>
+      <c r="AV3" s="47"/>
+      <c r="AW3" s="47"/>
+      <c r="AX3" s="47"/>
+      <c r="AY3" s="47"/>
+      <c r="AZ3" s="47"/>
+      <c r="BA3" s="47"/>
+      <c r="BB3" s="47"/>
+      <c r="BC3" s="47"/>
+      <c r="BD3" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="45"/>
-      <c r="BF3" s="45"/>
-      <c r="BG3" s="45"/>
-      <c r="BH3" s="45"/>
-      <c r="BI3" s="45"/>
-      <c r="BJ3" s="45"/>
-      <c r="BK3" s="45"/>
-      <c r="BL3" s="45"/>
-      <c r="BM3" s="45"/>
-      <c r="BN3" s="45"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="45"/>
-      <c r="BQ3" s="45"/>
-      <c r="BR3" s="45"/>
-      <c r="BS3" s="45"/>
-      <c r="BT3" s="45"/>
-      <c r="BU3" s="45"/>
-      <c r="BV3" s="45"/>
-      <c r="BW3" s="45"/>
-      <c r="BX3" s="45"/>
-      <c r="BY3" s="45"/>
-      <c r="BZ3" s="45"/>
-      <c r="CA3" s="45"/>
-      <c r="CB3" s="45"/>
-      <c r="CC3" s="45"/>
-      <c r="CD3" s="45"/>
-      <c r="CE3" s="45"/>
-      <c r="CF3" s="45"/>
-      <c r="CG3" s="45"/>
-      <c r="CH3" s="45"/>
-      <c r="CI3" s="45"/>
-      <c r="CJ3" s="45"/>
-      <c r="CK3" s="45"/>
-      <c r="CL3" s="45"/>
-      <c r="CM3" s="45"/>
-      <c r="CN3" s="45"/>
-      <c r="CO3" s="45"/>
-      <c r="CP3" s="45"/>
-      <c r="CQ3" s="45"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="47"/>
+      <c r="BF3" s="47"/>
+      <c r="BG3" s="47"/>
+      <c r="BH3" s="47"/>
+      <c r="BI3" s="47"/>
+      <c r="BJ3" s="47"/>
+      <c r="BK3" s="47"/>
+      <c r="BL3" s="47"/>
+      <c r="BM3" s="47"/>
+      <c r="BN3" s="47"/>
+      <c r="BO3" s="47"/>
+      <c r="BP3" s="47"/>
+      <c r="BQ3" s="47"/>
+      <c r="BR3" s="47"/>
+      <c r="BS3" s="47"/>
+      <c r="BT3" s="47"/>
+      <c r="BU3" s="47"/>
+      <c r="BV3" s="47"/>
+      <c r="BW3" s="47"/>
+      <c r="BX3" s="47"/>
+      <c r="BY3" s="47"/>
+      <c r="BZ3" s="47"/>
+      <c r="CA3" s="47"/>
+      <c r="CB3" s="47"/>
+      <c r="CC3" s="47"/>
+      <c r="CD3" s="47"/>
+      <c r="CE3" s="47"/>
+      <c r="CF3" s="47"/>
+      <c r="CG3" s="47"/>
+      <c r="CH3" s="47"/>
+      <c r="CI3" s="47"/>
+      <c r="CJ3" s="47"/>
+      <c r="CK3" s="47"/>
+      <c r="CL3" s="47"/>
+      <c r="CM3" s="47"/>
+      <c r="CN3" s="47"/>
+      <c r="CO3" s="47"/>
+      <c r="CP3" s="47"/>
+      <c r="CQ3" s="47"/>
+      <c r="CR3" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
-      <c r="DD3" s="21"/>
+      <c r="CS3" s="47"/>
+      <c r="CT3" s="47"/>
+      <c r="CU3" s="47"/>
+      <c r="CV3" s="47"/>
+      <c r="CW3" s="47"/>
+      <c r="CX3" s="47"/>
+      <c r="CY3" s="47"/>
+      <c r="CZ3" s="47"/>
+      <c r="DA3" s="47"/>
+      <c r="DB3" s="47"/>
+      <c r="DC3" s="47"/>
+      <c r="DD3" s="47"/>
       <c r="DE3" s="21"/>
       <c r="DF3" s="21"/>
     </row>
     <row r="4" spans="1:110" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="54" t="s">
+      <c r="L4" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="54" t="s">
+      <c r="M4" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="54" t="s">
+      <c r="N4" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="54" t="s">
+      <c r="P4" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="54" t="s">
+      <c r="Q4" s="48" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="54" t="s">
+      <c r="R4" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="54" t="s">
+      <c r="S4" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="54" t="s">
+      <c r="T4" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="54" t="s">
+      <c r="U4" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="54" t="s">
+      <c r="V4" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="54" t="s">
+      <c r="W4" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="54" t="s">
+      <c r="X4" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="54" t="s">
+      <c r="Y4" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="54" t="s">
+      <c r="Z4" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="54" t="s">
+      <c r="AA4" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="54" t="s">
+      <c r="AB4" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="54" t="s">
+      <c r="AC4" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="54" t="s">
+      <c r="AD4" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="48" t="s">
+      <c r="AE4" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="48" t="s">
+      <c r="AF4" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="48" t="s">
+      <c r="AG4" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="48" t="s">
+      <c r="AI4" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="48" t="s">
+      <c r="AJ4" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="48" t="s">
+      <c r="AL4" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="48" t="s">
+      <c r="AM4" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="46" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="48" t="s">
+      <c r="AO4" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="48" t="s">
+      <c r="AP4" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="48" t="s">
+      <c r="AR4" s="46" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="48" t="s">
+      <c r="AS4" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="48" t="s">
+      <c r="AT4" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="48" t="s">
+      <c r="AU4" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="48" t="s">
+      <c r="AV4" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="48" t="s">
+      <c r="AW4" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="48" t="s">
+      <c r="AX4" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="48" t="s">
+      <c r="AY4" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="48" t="s">
+      <c r="AZ4" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="48" t="s">
+      <c r="BA4" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="48" t="s">
+      <c r="BC4" s="46" t="s">
         <v>303</v>
       </c>
       <c r="BD4" s="44" t="s">
@@ -82002,78 +82575,80 @@
       <c r="DC4" s="44" t="s">
         <v>437</v>
       </c>
-      <c r="DD4" s="88"/>
+      <c r="DD4" s="44" t="s">
+        <v>440</v>
+      </c>
       <c r="DE4" s="88"/>
       <c r="DF4" s="88"/>
     </row>
     <row r="5" spans="1:110" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="66"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
-      <c r="BH5" s="46"/>
-      <c r="BI5" s="46"/>
-      <c r="BJ5" s="46"/>
-      <c r="BK5" s="46"/>
-      <c r="BL5" s="46"/>
-      <c r="BM5" s="46"/>
-      <c r="BN5" s="46"/>
-      <c r="BO5" s="46"/>
-      <c r="BP5" s="46"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AQ5" s="45"/>
+      <c r="AR5" s="45"/>
+      <c r="AS5" s="45"/>
+      <c r="AT5" s="45"/>
+      <c r="AU5" s="45"/>
+      <c r="AV5" s="45"/>
+      <c r="AW5" s="45"/>
+      <c r="AX5" s="45"/>
+      <c r="AY5" s="45"/>
+      <c r="AZ5" s="45"/>
+      <c r="BA5" s="45"/>
+      <c r="BB5" s="45"/>
+      <c r="BC5" s="45"/>
+      <c r="BD5" s="45"/>
+      <c r="BE5" s="45"/>
+      <c r="BF5" s="45"/>
+      <c r="BG5" s="45"/>
+      <c r="BH5" s="45"/>
+      <c r="BI5" s="45"/>
+      <c r="BJ5" s="45"/>
+      <c r="BK5" s="45"/>
+      <c r="BL5" s="45"/>
+      <c r="BM5" s="45"/>
+      <c r="BN5" s="45"/>
+      <c r="BO5" s="45"/>
+      <c r="BP5" s="45"/>
       <c r="BQ5" s="44"/>
       <c r="BR5" s="44"/>
       <c r="BS5" s="44"/>
@@ -82113,7 +82688,7 @@
       <c r="DA5" s="44"/>
       <c r="DB5" s="44"/>
       <c r="DC5" s="44"/>
-      <c r="DD5" s="88"/>
+      <c r="DD5" s="44"/>
       <c r="DE5" s="88"/>
       <c r="DF5" s="88"/>
     </row>
@@ -82437,7 +83012,9 @@
       <c r="DC6" s="28">
         <v>81</v>
       </c>
-      <c r="DD6" s="22"/>
+      <c r="DD6" s="28">
+        <v>62</v>
+      </c>
       <c r="DE6" s="22"/>
       <c r="DF6" s="22"/>
     </row>
@@ -82760,7 +83337,9 @@
       <c r="DC7" s="15">
         <v>0</v>
       </c>
-      <c r="DD7" s="23"/>
+      <c r="DD7" s="15">
+        <v>0</v>
+      </c>
       <c r="DE7" s="23"/>
       <c r="DF7" s="23"/>
     </row>
@@ -83083,7 +83662,9 @@
       <c r="DC8" s="28">
         <v>17</v>
       </c>
-      <c r="DD8" s="23"/>
+      <c r="DD8" s="28">
+        <v>14</v>
+      </c>
       <c r="DE8" s="23"/>
       <c r="DF8" s="23"/>
     </row>
@@ -83407,7 +83988,9 @@
       <c r="DC9" s="28">
         <v>55</v>
       </c>
-      <c r="DD9" s="23"/>
+      <c r="DD9" s="28">
+        <v>71</v>
+      </c>
       <c r="DE9" s="23"/>
       <c r="DF9" s="23"/>
     </row>
@@ -83730,7 +84313,9 @@
       <c r="DC10" s="28">
         <v>1</v>
       </c>
-      <c r="DD10" s="23"/>
+      <c r="DD10" s="28">
+        <v>0</v>
+      </c>
       <c r="DE10" s="23"/>
       <c r="DF10" s="23"/>
     </row>
@@ -84053,7 +84638,9 @@
       <c r="DC11" s="28">
         <v>4</v>
       </c>
-      <c r="DD11" s="23"/>
+      <c r="DD11" s="28">
+        <v>9</v>
+      </c>
       <c r="DE11" s="23"/>
       <c r="DF11" s="23"/>
     </row>
@@ -84376,7 +84963,9 @@
       <c r="DC12" s="15">
         <v>2</v>
       </c>
-      <c r="DD12" s="23"/>
+      <c r="DD12" s="15">
+        <v>3</v>
+      </c>
       <c r="DE12" s="23"/>
       <c r="DF12" s="23"/>
     </row>
@@ -84699,7 +85288,9 @@
       <c r="DC13" s="15">
         <v>20</v>
       </c>
-      <c r="DD13" s="22"/>
+      <c r="DD13" s="15">
+        <v>15</v>
+      </c>
       <c r="DE13" s="22"/>
       <c r="DF13" s="22"/>
     </row>
@@ -85022,7 +85613,9 @@
       <c r="DC14" s="15">
         <v>17</v>
       </c>
-      <c r="DD14" s="23"/>
+      <c r="DD14" s="15">
+        <v>15</v>
+      </c>
       <c r="DE14" s="23"/>
       <c r="DF14" s="23"/>
     </row>
@@ -85345,7 +85938,9 @@
       <c r="DC15" s="15">
         <v>2</v>
       </c>
-      <c r="DD15" s="23"/>
+      <c r="DD15" s="15">
+        <v>1</v>
+      </c>
       <c r="DE15" s="23"/>
       <c r="DF15" s="23"/>
     </row>
@@ -85669,7 +86264,9 @@
       <c r="DC16" s="28">
         <v>108</v>
       </c>
-      <c r="DD16" s="22"/>
+      <c r="DD16" s="28">
+        <v>104</v>
+      </c>
       <c r="DE16" s="22"/>
       <c r="DF16" s="22"/>
     </row>
@@ -85992,7 +86589,9 @@
       <c r="DC17" s="15">
         <v>103</v>
       </c>
-      <c r="DD17" s="22"/>
+      <c r="DD17" s="15">
+        <v>96</v>
+      </c>
       <c r="DE17" s="22"/>
       <c r="DF17" s="22"/>
     </row>
@@ -86316,7 +86915,9 @@
       <c r="DC18" s="34">
         <v>1542</v>
       </c>
-      <c r="DD18" s="22"/>
+      <c r="DD18" s="34">
+        <v>1342</v>
+      </c>
       <c r="DE18" s="22"/>
       <c r="DF18" s="22"/>
     </row>
@@ -86640,7 +87241,9 @@
       <c r="DC19" s="15">
         <v>34</v>
       </c>
-      <c r="DD19" s="22"/>
+      <c r="DD19" s="15">
+        <v>34</v>
+      </c>
       <c r="DE19" s="22"/>
       <c r="DF19" s="22"/>
     </row>
@@ -86962,7 +87565,9 @@
       <c r="DC20" s="28">
         <v>65</v>
       </c>
-      <c r="DD20" s="22"/>
+      <c r="DD20" s="28">
+        <v>76</v>
+      </c>
       <c r="DE20" s="22"/>
       <c r="DF20" s="22"/>
     </row>
@@ -87284,7 +87889,9 @@
       <c r="DC21" s="15">
         <v>16</v>
       </c>
-      <c r="DD21" s="22"/>
+      <c r="DD21" s="15">
+        <v>19</v>
+      </c>
       <c r="DE21" s="22"/>
       <c r="DF21" s="22"/>
     </row>
@@ -87607,7 +88214,9 @@
       <c r="DC22" s="15">
         <v>4</v>
       </c>
-      <c r="DD22" s="23"/>
+      <c r="DD22" s="15">
+        <v>2</v>
+      </c>
       <c r="DE22" s="23"/>
       <c r="DF22" s="23"/>
     </row>
@@ -87930,7 +88539,9 @@
       <c r="DC23" s="15">
         <v>0</v>
       </c>
-      <c r="DD23" s="23"/>
+      <c r="DD23" s="15">
+        <v>0</v>
+      </c>
       <c r="DE23" s="23"/>
       <c r="DF23" s="23"/>
     </row>
@@ -88253,7 +88864,9 @@
       <c r="DC24" s="15">
         <v>7</v>
       </c>
-      <c r="DD24" s="22"/>
+      <c r="DD24" s="15">
+        <v>8</v>
+      </c>
       <c r="DE24" s="22"/>
       <c r="DF24" s="22"/>
     </row>
@@ -88576,7 +89189,9 @@
       <c r="DC25" s="15">
         <v>0</v>
       </c>
-      <c r="DD25" s="23"/>
+      <c r="DD25" s="15">
+        <v>0</v>
+      </c>
       <c r="DE25" s="23"/>
       <c r="DF25" s="23"/>
     </row>
@@ -88899,7 +89514,9 @@
       <c r="DC26" s="15">
         <v>10</v>
       </c>
-      <c r="DD26" s="23"/>
+      <c r="DD26" s="15">
+        <v>7</v>
+      </c>
       <c r="DE26" s="23"/>
       <c r="DF26" s="23"/>
     </row>
@@ -89222,7 +89839,9 @@
       <c r="DC27" s="15">
         <v>0</v>
       </c>
-      <c r="DD27" s="23"/>
+      <c r="DD27" s="15">
+        <v>0</v>
+      </c>
       <c r="DE27" s="23"/>
       <c r="DF27" s="23"/>
     </row>
@@ -89545,7 +90164,9 @@
       <c r="DC28" s="15">
         <v>0</v>
       </c>
-      <c r="DD28" s="22"/>
+      <c r="DD28" s="15">
+        <v>2</v>
+      </c>
       <c r="DE28" s="22"/>
       <c r="DF28" s="22"/>
     </row>
@@ -89868,7 +90489,9 @@
       <c r="DC29" s="15">
         <v>1</v>
       </c>
-      <c r="DD29" s="23"/>
+      <c r="DD29" s="15">
+        <v>0</v>
+      </c>
       <c r="DE29" s="23"/>
       <c r="DF29" s="23"/>
     </row>
@@ -90189,7 +90812,9 @@
       <c r="DC30" s="15">
         <v>9</v>
       </c>
-      <c r="DD30" s="23"/>
+      <c r="DD30" s="15">
+        <v>8</v>
+      </c>
       <c r="DE30" s="23"/>
       <c r="DF30" s="23"/>
     </row>
@@ -90513,7 +91138,9 @@
       <c r="DC31" s="15">
         <v>35</v>
       </c>
-      <c r="DD31" s="22"/>
+      <c r="DD31" s="15">
+        <v>33</v>
+      </c>
       <c r="DE31" s="22"/>
       <c r="DF31" s="22"/>
     </row>
@@ -90836,7 +91463,9 @@
       <c r="DC32" s="15">
         <v>3</v>
       </c>
-      <c r="DD32" s="23"/>
+      <c r="DD32" s="15">
+        <v>0</v>
+      </c>
       <c r="DE32" s="23"/>
       <c r="DF32" s="23"/>
     </row>
@@ -91159,7 +91788,9 @@
       <c r="DC33" s="15">
         <v>0</v>
       </c>
-      <c r="DD33" s="23"/>
+      <c r="DD33" s="15">
+        <v>0</v>
+      </c>
       <c r="DE33" s="23"/>
       <c r="DF33" s="23"/>
     </row>
@@ -91483,7 +92114,9 @@
       <c r="DC34" s="15">
         <v>72</v>
       </c>
-      <c r="DD34" s="22"/>
+      <c r="DD34" s="15">
+        <v>45</v>
+      </c>
       <c r="DE34" s="22"/>
       <c r="DF34" s="22"/>
     </row>
@@ -91807,7 +92440,9 @@
       <c r="DC35" s="15">
         <v>236</v>
       </c>
-      <c r="DD35" s="22"/>
+      <c r="DD35" s="15">
+        <v>210</v>
+      </c>
       <c r="DE35" s="22"/>
       <c r="DF35" s="22"/>
     </row>
@@ -92128,7 +92763,9 @@
       <c r="DC36" s="28">
         <v>15</v>
       </c>
-      <c r="DD36" s="22"/>
+      <c r="DD36" s="28">
+        <v>15</v>
+      </c>
       <c r="DE36" s="22"/>
       <c r="DF36" s="22"/>
     </row>
@@ -92452,7 +93089,9 @@
       <c r="DC37" s="15">
         <v>45</v>
       </c>
-      <c r="DD37" s="22"/>
+      <c r="DD37" s="15">
+        <v>36</v>
+      </c>
       <c r="DE37" s="22"/>
       <c r="DF37" s="22"/>
     </row>
@@ -92775,7 +93414,9 @@
       <c r="DC38" s="15">
         <v>5</v>
       </c>
-      <c r="DD38" s="23"/>
+      <c r="DD38" s="15">
+        <v>4</v>
+      </c>
       <c r="DE38" s="23"/>
       <c r="DF38" s="23"/>
     </row>
@@ -93098,7 +93739,9 @@
       <c r="DC39" s="15">
         <v>3</v>
       </c>
-      <c r="DD39" s="23"/>
+      <c r="DD39" s="15">
+        <v>3</v>
+      </c>
       <c r="DE39" s="23"/>
       <c r="DF39" s="23"/>
     </row>
@@ -93421,7 +94064,9 @@
       <c r="DC40" s="15">
         <v>0</v>
       </c>
-      <c r="DD40" s="23"/>
+      <c r="DD40" s="15">
+        <v>0</v>
+      </c>
       <c r="DE40" s="23"/>
       <c r="DF40" s="23"/>
     </row>
@@ -93744,7 +94389,9 @@
       <c r="DC41" s="15">
         <v>0</v>
       </c>
-      <c r="DD41" s="23"/>
+      <c r="DD41" s="15">
+        <v>0</v>
+      </c>
       <c r="DE41" s="23"/>
       <c r="DF41" s="23"/>
     </row>
@@ -94067,7 +94714,9 @@
       <c r="DC42" s="15">
         <v>7</v>
       </c>
-      <c r="DD42" s="23"/>
+      <c r="DD42" s="15">
+        <v>7</v>
+      </c>
       <c r="DE42" s="23"/>
       <c r="DF42" s="23"/>
     </row>
@@ -94390,7 +95039,9 @@
       <c r="DC43" s="28">
         <v>30</v>
       </c>
-      <c r="DD43" s="23"/>
+      <c r="DD43" s="28">
+        <v>21</v>
+      </c>
       <c r="DE43" s="23"/>
       <c r="DF43" s="23"/>
     </row>
@@ -94713,7 +95364,9 @@
       <c r="DC44" s="15">
         <v>4</v>
       </c>
-      <c r="DD44" s="23"/>
+      <c r="DD44" s="15">
+        <v>3</v>
+      </c>
       <c r="DE44" s="23"/>
       <c r="DF44" s="23"/>
     </row>
@@ -95036,7 +95689,9 @@
       <c r="DC45" s="15">
         <v>10</v>
       </c>
-      <c r="DD45" s="22"/>
+      <c r="DD45" s="15">
+        <v>10</v>
+      </c>
       <c r="DE45" s="22"/>
       <c r="DF45" s="22"/>
     </row>
@@ -95359,7 +96014,9 @@
       <c r="DC46" s="15">
         <v>15</v>
       </c>
-      <c r="DD46" s="23"/>
+      <c r="DD46" s="15">
+        <v>17</v>
+      </c>
       <c r="DE46" s="23"/>
       <c r="DF46" s="23"/>
     </row>
@@ -95682,7 +96339,9 @@
       <c r="DC47" s="15">
         <v>0</v>
       </c>
-      <c r="DD47" s="23"/>
+      <c r="DD47" s="15">
+        <v>0</v>
+      </c>
       <c r="DE47" s="23"/>
       <c r="DF47" s="23"/>
     </row>
@@ -96005,7 +96664,9 @@
       <c r="DC48" s="15">
         <v>9</v>
       </c>
-      <c r="DD48" s="23"/>
+      <c r="DD48" s="15">
+        <v>14</v>
+      </c>
       <c r="DE48" s="23"/>
       <c r="DF48" s="23"/>
     </row>
@@ -96329,7 +96990,9 @@
       <c r="DC49" s="15">
         <v>38</v>
       </c>
-      <c r="DD49" s="22"/>
+      <c r="DD49" s="15">
+        <v>38</v>
+      </c>
       <c r="DE49" s="22"/>
       <c r="DF49" s="22"/>
     </row>
@@ -96650,7 +97313,9 @@
       <c r="DC50" s="15">
         <v>15</v>
       </c>
-      <c r="DD50" s="22"/>
+      <c r="DD50" s="15">
+        <v>7</v>
+      </c>
       <c r="DE50" s="22"/>
       <c r="DF50" s="22"/>
     </row>
@@ -96973,7 +97638,9 @@
       <c r="DC51" s="15">
         <v>7</v>
       </c>
-      <c r="DD51" s="23"/>
+      <c r="DD51" s="15">
+        <v>8</v>
+      </c>
       <c r="DE51" s="23"/>
       <c r="DF51" s="23"/>
     </row>
@@ -97296,7 +97963,9 @@
       <c r="DC52" s="15">
         <v>5</v>
       </c>
-      <c r="DD52" s="23"/>
+      <c r="DD52" s="15">
+        <v>10</v>
+      </c>
       <c r="DE52" s="23"/>
       <c r="DF52" s="23"/>
     </row>
@@ -97619,7 +98288,9 @@
       <c r="DC53" s="15">
         <v>33</v>
       </c>
-      <c r="DD53" s="23"/>
+      <c r="DD53" s="15">
+        <v>25</v>
+      </c>
       <c r="DE53" s="23"/>
       <c r="DF53" s="23"/>
     </row>
@@ -97942,7 +98613,9 @@
       <c r="DC54" s="15">
         <v>5</v>
       </c>
-      <c r="DD54" s="23"/>
+      <c r="DD54" s="15">
+        <v>2</v>
+      </c>
       <c r="DE54" s="23"/>
       <c r="DF54" s="23"/>
     </row>
@@ -98265,7 +98938,9 @@
       <c r="DC55" s="15">
         <v>22</v>
       </c>
-      <c r="DD55" s="23"/>
+      <c r="DD55" s="15">
+        <v>16</v>
+      </c>
       <c r="DE55" s="23"/>
       <c r="DF55" s="23"/>
     </row>
@@ -98588,7 +99263,9 @@
       <c r="DC56" s="15">
         <v>1</v>
       </c>
-      <c r="DD56" s="23"/>
+      <c r="DD56" s="15">
+        <v>1</v>
+      </c>
       <c r="DE56" s="23"/>
       <c r="DF56" s="23"/>
     </row>
@@ -98911,7 +99588,9 @@
       <c r="DC57" s="15">
         <v>3</v>
       </c>
-      <c r="DD57" s="23"/>
+      <c r="DD57" s="15">
+        <v>2</v>
+      </c>
       <c r="DE57" s="23"/>
       <c r="DF57" s="23"/>
     </row>
@@ -99336,7 +100015,10 @@
         <f t="shared" si="6"/>
         <v>2716</v>
       </c>
-      <c r="DD58" s="24"/>
+      <c r="DD58" s="14">
+        <f t="shared" ref="DD58" si="7">SUM(DD6:DD57)</f>
+        <v>2415</v>
+      </c>
       <c r="DE58" s="24"/>
       <c r="DF58" s="24"/>
     </row>
@@ -99441,8 +100123,8 @@
     </row>
   </sheetData>
   <mergeCells count="120">
-    <mergeCell ref="BD2:DC2"/>
-    <mergeCell ref="CR3:DC3"/>
+    <mergeCell ref="BD2:DD2"/>
+    <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -99574,7 +100256,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="9" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="10" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -99587,7 +100269,7 @@
           <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="28" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="29" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -99600,7 +100282,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="5" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
+          <x14:cfRule type="containsBlanks" priority="6" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
             <xm:f>LEN(TRIM('うちコロナ疑い事案（今回）'!DA10))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -99613,7 +100295,7 @@
           <xm:sqref>DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="3" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
+          <x14:cfRule type="containsBlanks" priority="4" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -99626,7 +100308,7 @@
           <xm:sqref>DB6:DB57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="1" id="{D5FC4B6E-10B3-44DA-A1D6-DEA44453D2A7}">
+          <x14:cfRule type="containsBlanks" priority="2" id="{D5FC4B6E-10B3-44DA-A1D6-DEA44453D2A7}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -99638,6 +100320,19 @@
           </x14:cfRule>
           <xm:sqref>DC6:DC57</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsBlanks" priority="1" id="{1D4A68F6-7D4E-438E-9CA3-77DF5B1688C9}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DD6))=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>DD6:DD57</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\W-119_消防庁HP更新\03_支給資材・原稿\JOB050404-1\ＪＯＢ050404-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\W-119_消防庁HP更新\03_支給資材・原稿\JOB050411-1\ＪＯＢ050411-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11085"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="搬送困難事案（今回）" sheetId="42" r:id="rId1"/>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DD$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DD$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FD$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FD$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DE$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DE$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FE$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FE$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="444">
   <si>
     <t>都道府県</t>
   </si>
@@ -4670,6 +4670,24 @@
 4月第1週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>4/3(月)～
+4/9(日)分
+【4月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4/4(月)～
+4/10(日)分
+【4月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4/3(月)～
+4/9(日)分
+【4月第2週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5169,35 +5187,23 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5207,6 +5213,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5308,42 +5326,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="30">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill>
@@ -5451,6 +5434,21 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -9612,7 +9610,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FD61"/>
+  <dimension ref="A1:FE61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9626,11 +9624,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="160" width="10.875" style="1" customWidth="1"/>
-    <col min="161" max="16384" width="8.625" style="1"/>
+    <col min="106" max="161" width="10.875" style="1" customWidth="1"/>
+    <col min="162" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:160" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:161" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9717,122 +9715,123 @@
       <c r="FA1" s="19"/>
       <c r="FB1" s="19"/>
       <c r="FC1" s="19"/>
-      <c r="FD1" s="19" t="s">
+      <c r="FD1" s="19"/>
+      <c r="FE1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:160" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:161" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="55"/>
-      <c r="BD2" s="55" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="51"/>
+      <c r="BA2" s="51"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="51"/>
+      <c r="BD2" s="51" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="55"/>
-      <c r="BF2" s="55"/>
-      <c r="BG2" s="55"/>
-      <c r="BH2" s="55"/>
-      <c r="BI2" s="55"/>
-      <c r="BJ2" s="55"/>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="55"/>
-      <c r="BP2" s="55"/>
-      <c r="BQ2" s="55"/>
-      <c r="BR2" s="55"/>
-      <c r="BS2" s="55"/>
-      <c r="BT2" s="55"/>
-      <c r="BU2" s="55"/>
-      <c r="BV2" s="55"/>
-      <c r="BW2" s="55"/>
-      <c r="BX2" s="55"/>
-      <c r="BY2" s="55"/>
-      <c r="BZ2" s="55"/>
-      <c r="CA2" s="55"/>
-      <c r="CB2" s="55"/>
-      <c r="CC2" s="55"/>
-      <c r="CD2" s="55"/>
-      <c r="CE2" s="55"/>
-      <c r="CF2" s="55"/>
-      <c r="CG2" s="55"/>
-      <c r="CH2" s="55"/>
-      <c r="CI2" s="55"/>
-      <c r="CJ2" s="55"/>
-      <c r="CK2" s="55"/>
-      <c r="CL2" s="55"/>
-      <c r="CM2" s="55"/>
-      <c r="CN2" s="55"/>
-      <c r="CO2" s="55"/>
-      <c r="CP2" s="55"/>
-      <c r="CQ2" s="55"/>
-      <c r="CR2" s="55"/>
-      <c r="CS2" s="55"/>
-      <c r="CT2" s="55"/>
-      <c r="CU2" s="55"/>
-      <c r="CV2" s="55"/>
-      <c r="CW2" s="55"/>
-      <c r="CX2" s="55"/>
-      <c r="CY2" s="55"/>
-      <c r="CZ2" s="55"/>
-      <c r="DA2" s="55"/>
-      <c r="DB2" s="55"/>
-      <c r="DC2" s="55"/>
-      <c r="DD2" s="55"/>
+      <c r="BE2" s="51"/>
+      <c r="BF2" s="51"/>
+      <c r="BG2" s="51"/>
+      <c r="BH2" s="51"/>
+      <c r="BI2" s="51"/>
+      <c r="BJ2" s="51"/>
+      <c r="BK2" s="51"/>
+      <c r="BL2" s="51"/>
+      <c r="BM2" s="51"/>
+      <c r="BN2" s="51"/>
+      <c r="BO2" s="51"/>
+      <c r="BP2" s="51"/>
+      <c r="BQ2" s="51"/>
+      <c r="BR2" s="51"/>
+      <c r="BS2" s="51"/>
+      <c r="BT2" s="51"/>
+      <c r="BU2" s="51"/>
+      <c r="BV2" s="51"/>
+      <c r="BW2" s="51"/>
+      <c r="BX2" s="51"/>
+      <c r="BY2" s="51"/>
+      <c r="BZ2" s="51"/>
+      <c r="CA2" s="51"/>
+      <c r="CB2" s="51"/>
+      <c r="CC2" s="51"/>
+      <c r="CD2" s="51"/>
+      <c r="CE2" s="51"/>
+      <c r="CF2" s="51"/>
+      <c r="CG2" s="51"/>
+      <c r="CH2" s="51"/>
+      <c r="CI2" s="51"/>
+      <c r="CJ2" s="51"/>
+      <c r="CK2" s="51"/>
+      <c r="CL2" s="51"/>
+      <c r="CM2" s="51"/>
+      <c r="CN2" s="51"/>
+      <c r="CO2" s="51"/>
+      <c r="CP2" s="51"/>
+      <c r="CQ2" s="51"/>
+      <c r="CR2" s="51"/>
+      <c r="CS2" s="51"/>
+      <c r="CT2" s="51"/>
+      <c r="CU2" s="51"/>
+      <c r="CV2" s="51"/>
+      <c r="CW2" s="51"/>
+      <c r="CX2" s="51"/>
+      <c r="CY2" s="51"/>
+      <c r="CZ2" s="51"/>
+      <c r="DA2" s="51"/>
+      <c r="DB2" s="51"/>
+      <c r="DC2" s="51"/>
+      <c r="DD2" s="51"/>
       <c r="DE2" s="72" t="s">
         <v>320</v>
       </c>
@@ -9887,181 +9886,183 @@
       <c r="FB2" s="72"/>
       <c r="FC2" s="72"/>
       <c r="FD2" s="72"/>
+      <c r="FE2" s="72"/>
     </row>
-    <row r="3" spans="1:160" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:161" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="47"/>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="47"/>
-      <c r="AG3" s="47"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="47"/>
-      <c r="AK3" s="47"/>
-      <c r="AL3" s="47"/>
-      <c r="AM3" s="47"/>
-      <c r="AN3" s="47"/>
-      <c r="AO3" s="47"/>
-      <c r="AP3" s="47"/>
-      <c r="AQ3" s="47"/>
-      <c r="AR3" s="50" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
+      <c r="AR3" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="AS3" s="56"/>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="56"/>
-      <c r="AV3" s="56"/>
-      <c r="AW3" s="56"/>
-      <c r="AX3" s="56"/>
-      <c r="AY3" s="56"/>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="56"/>
-      <c r="BB3" s="56"/>
-      <c r="BC3" s="56"/>
-      <c r="BD3" s="56" t="s">
+      <c r="AS3" s="52"/>
+      <c r="AT3" s="52"/>
+      <c r="AU3" s="52"/>
+      <c r="AV3" s="52"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="52"/>
+      <c r="AY3" s="52"/>
+      <c r="AZ3" s="52"/>
+      <c r="BA3" s="52"/>
+      <c r="BB3" s="52"/>
+      <c r="BC3" s="52"/>
+      <c r="BD3" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="BE3" s="56"/>
-      <c r="BF3" s="56"/>
-      <c r="BG3" s="56"/>
-      <c r="BH3" s="56"/>
-      <c r="BI3" s="56"/>
-      <c r="BJ3" s="56"/>
-      <c r="BK3" s="56"/>
-      <c r="BL3" s="56"/>
-      <c r="BM3" s="56"/>
-      <c r="BN3" s="56"/>
-      <c r="BO3" s="56"/>
-      <c r="BP3" s="56"/>
-      <c r="BQ3" s="56"/>
-      <c r="BR3" s="56"/>
-      <c r="BS3" s="56"/>
-      <c r="BT3" s="56"/>
-      <c r="BU3" s="56"/>
-      <c r="BV3" s="56"/>
-      <c r="BW3" s="56"/>
-      <c r="BX3" s="56"/>
-      <c r="BY3" s="56"/>
-      <c r="BZ3" s="56"/>
-      <c r="CA3" s="56"/>
-      <c r="CB3" s="56"/>
-      <c r="CC3" s="56"/>
-      <c r="CD3" s="56"/>
-      <c r="CE3" s="56"/>
-      <c r="CF3" s="56"/>
-      <c r="CG3" s="56"/>
-      <c r="CH3" s="56"/>
-      <c r="CI3" s="56"/>
-      <c r="CJ3" s="56"/>
-      <c r="CK3" s="56"/>
-      <c r="CL3" s="56"/>
-      <c r="CM3" s="56"/>
-      <c r="CN3" s="56"/>
-      <c r="CO3" s="56"/>
-      <c r="CP3" s="56"/>
-      <c r="CQ3" s="57"/>
-      <c r="CR3" s="47" t="s">
+      <c r="BE3" s="52"/>
+      <c r="BF3" s="52"/>
+      <c r="BG3" s="52"/>
+      <c r="BH3" s="52"/>
+      <c r="BI3" s="52"/>
+      <c r="BJ3" s="52"/>
+      <c r="BK3" s="52"/>
+      <c r="BL3" s="52"/>
+      <c r="BM3" s="52"/>
+      <c r="BN3" s="52"/>
+      <c r="BO3" s="52"/>
+      <c r="BP3" s="52"/>
+      <c r="BQ3" s="52"/>
+      <c r="BR3" s="52"/>
+      <c r="BS3" s="52"/>
+      <c r="BT3" s="52"/>
+      <c r="BU3" s="52"/>
+      <c r="BV3" s="52"/>
+      <c r="BW3" s="52"/>
+      <c r="BX3" s="52"/>
+      <c r="BY3" s="52"/>
+      <c r="BZ3" s="52"/>
+      <c r="CA3" s="52"/>
+      <c r="CB3" s="52"/>
+      <c r="CC3" s="52"/>
+      <c r="CD3" s="52"/>
+      <c r="CE3" s="52"/>
+      <c r="CF3" s="52"/>
+      <c r="CG3" s="52"/>
+      <c r="CH3" s="52"/>
+      <c r="CI3" s="52"/>
+      <c r="CJ3" s="52"/>
+      <c r="CK3" s="52"/>
+      <c r="CL3" s="52"/>
+      <c r="CM3" s="52"/>
+      <c r="CN3" s="52"/>
+      <c r="CO3" s="52"/>
+      <c r="CP3" s="52"/>
+      <c r="CQ3" s="53"/>
+      <c r="CR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="47"/>
-      <c r="CT3" s="47"/>
-      <c r="CU3" s="47"/>
-      <c r="CV3" s="47"/>
-      <c r="CW3" s="47"/>
-      <c r="CX3" s="47"/>
-      <c r="CY3" s="47"/>
-      <c r="CZ3" s="47"/>
-      <c r="DA3" s="47"/>
-      <c r="DB3" s="47"/>
-      <c r="DC3" s="47"/>
-      <c r="DD3" s="50"/>
-      <c r="DE3" s="47" t="s">
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="47"/>
+      <c r="DE3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="47"/>
-      <c r="DG3" s="47"/>
-      <c r="DH3" s="47"/>
-      <c r="DI3" s="47"/>
-      <c r="DJ3" s="47"/>
-      <c r="DK3" s="47"/>
-      <c r="DL3" s="47"/>
-      <c r="DM3" s="47"/>
-      <c r="DN3" s="47"/>
-      <c r="DO3" s="47"/>
-      <c r="DP3" s="47"/>
-      <c r="DQ3" s="47"/>
-      <c r="DR3" s="47"/>
-      <c r="DS3" s="47"/>
-      <c r="DT3" s="47"/>
-      <c r="DU3" s="47"/>
-      <c r="DV3" s="47"/>
-      <c r="DW3" s="47"/>
-      <c r="DX3" s="47"/>
-      <c r="DY3" s="47"/>
-      <c r="DZ3" s="47"/>
-      <c r="EA3" s="47"/>
-      <c r="EB3" s="47"/>
-      <c r="EC3" s="47"/>
-      <c r="ED3" s="47"/>
-      <c r="EE3" s="47"/>
-      <c r="EF3" s="47"/>
-      <c r="EG3" s="47"/>
-      <c r="EH3" s="47"/>
-      <c r="EI3" s="47"/>
-      <c r="EJ3" s="47"/>
-      <c r="EK3" s="47"/>
-      <c r="EL3" s="47"/>
-      <c r="EM3" s="47"/>
-      <c r="EN3" s="47"/>
-      <c r="EO3" s="47"/>
-      <c r="EP3" s="47"/>
-      <c r="EQ3" s="47"/>
-      <c r="ER3" s="47" t="s">
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="47"/>
-      <c r="ET3" s="47"/>
-      <c r="EU3" s="47"/>
-      <c r="EV3" s="47"/>
-      <c r="EW3" s="47"/>
-      <c r="EX3" s="47"/>
-      <c r="EY3" s="47"/>
-      <c r="EZ3" s="47"/>
-      <c r="FA3" s="47"/>
-      <c r="FB3" s="47"/>
-      <c r="FC3" s="47"/>
-      <c r="FD3" s="47"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
+      <c r="EU3" s="45"/>
+      <c r="EV3" s="45"/>
+      <c r="EW3" s="45"/>
+      <c r="EX3" s="45"/>
+      <c r="EY3" s="45"/>
+      <c r="EZ3" s="45"/>
+      <c r="FA3" s="45"/>
+      <c r="FB3" s="45"/>
+      <c r="FC3" s="45"/>
+      <c r="FD3" s="45"/>
+      <c r="FE3" s="45"/>
     </row>
-    <row r="4" spans="1:160" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:161" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="64" t="s">
         <v>0</v>
       </c>
@@ -10188,199 +10189,199 @@
       <c r="AQ4" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" s="49" t="s">
+      <c r="AR4" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="AS4" s="49" t="s">
+      <c r="AS4" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="49" t="s">
+      <c r="AT4" s="55" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="49" t="s">
+      <c r="AU4" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="49" t="s">
+      <c r="AV4" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="49" t="s">
+      <c r="AW4" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="AX4" s="49" t="s">
+      <c r="AX4" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="AY4" s="49" t="s">
+      <c r="AY4" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="AZ4" s="49" t="s">
+      <c r="AZ4" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="BA4" s="49" t="s">
+      <c r="BA4" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="BB4" s="49" t="s">
+      <c r="BB4" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="BC4" s="49" t="s">
+      <c r="BC4" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="BD4" s="48" t="s">
+      <c r="BD4" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="BE4" s="48" t="s">
+      <c r="BE4" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="48" t="s">
+      <c r="BF4" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="48" t="s">
+      <c r="BG4" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="BH4" s="48" t="s">
+      <c r="BH4" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="BI4" s="48" t="s">
+      <c r="BI4" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="48" t="s">
+      <c r="BJ4" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="48" t="s">
+      <c r="BK4" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="53" t="s">
+      <c r="BL4" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="53" t="s">
+      <c r="BM4" s="56" t="s">
         <v>243</v>
       </c>
-      <c r="BN4" s="48" t="s">
+      <c r="BN4" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="BO4" s="48" t="s">
+      <c r="BO4" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="BP4" s="48" t="s">
+      <c r="BP4" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="BQ4" s="48" t="s">
+      <c r="BQ4" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="BR4" s="48" t="s">
+      <c r="BR4" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="BS4" s="48" t="s">
+      <c r="BS4" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="BT4" s="48" t="s">
+      <c r="BT4" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="BU4" s="53" t="s">
+      <c r="BU4" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="BV4" s="53" t="s">
+      <c r="BV4" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="BW4" s="53" t="s">
+      <c r="BW4" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="BX4" s="53" t="s">
+      <c r="BX4" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="53" t="s">
+      <c r="BY4" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="BZ4" s="48" t="s">
+      <c r="BZ4" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="CA4" s="48" t="s">
+      <c r="CA4" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="CB4" s="48" t="s">
+      <c r="CB4" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="CC4" s="48" t="s">
+      <c r="CC4" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="CD4" s="48" t="s">
+      <c r="CD4" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="CE4" s="46" t="s">
+      <c r="CE4" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="CF4" s="46" t="s">
+      <c r="CF4" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="CG4" s="46" t="s">
+      <c r="CG4" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="CH4" s="46" t="s">
+      <c r="CH4" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="CI4" s="46" t="s">
+      <c r="CI4" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="CJ4" s="46" t="s">
+      <c r="CJ4" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="CK4" s="46" t="s">
+      <c r="CK4" s="48" t="s">
         <v>264</v>
       </c>
-      <c r="CL4" s="46" t="s">
+      <c r="CL4" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="CM4" s="46" t="s">
+      <c r="CM4" s="48" t="s">
         <v>268</v>
       </c>
-      <c r="CN4" s="46" t="s">
+      <c r="CN4" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="CO4" s="46" t="s">
+      <c r="CO4" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="CP4" s="46" t="s">
+      <c r="CP4" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="CQ4" s="46" t="s">
+      <c r="CQ4" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="CR4" s="46" t="s">
+      <c r="CR4" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="CS4" s="46" t="s">
+      <c r="CS4" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="CT4" s="46" t="s">
+      <c r="CT4" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="CU4" s="46" t="s">
+      <c r="CU4" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="CV4" s="46" t="s">
+      <c r="CV4" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="CW4" s="46" t="s">
+      <c r="CW4" s="48" t="s">
         <v>292</v>
       </c>
-      <c r="CX4" s="46" t="s">
+      <c r="CX4" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="CY4" s="46" t="s">
+      <c r="CY4" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="CZ4" s="46" t="s">
+      <c r="CZ4" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="DA4" s="46" t="s">
+      <c r="DA4" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="DB4" s="46" t="s">
+      <c r="DB4" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="DC4" s="46" t="s">
+      <c r="DC4" s="48" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="51" t="s">
+      <c r="DD4" s="49" t="s">
         <v>305</v>
       </c>
       <c r="DE4" s="44" t="s">
@@ -10539,139 +10540,142 @@
       <c r="FD4" s="44" t="s">
         <v>440</v>
       </c>
+      <c r="FE4" s="44" t="s">
+        <v>441</v>
+      </c>
     </row>
-    <row r="5" spans="1:160" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:161" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="65"/>
       <c r="C5" s="71"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="53"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="53"/>
-      <c r="X5" s="53"/>
-      <c r="Y5" s="53"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="49"/>
-      <c r="AS5" s="49"/>
-      <c r="AT5" s="49"/>
-      <c r="AU5" s="49"/>
-      <c r="AV5" s="49"/>
-      <c r="AW5" s="49"/>
-      <c r="AX5" s="49"/>
-      <c r="AY5" s="49"/>
-      <c r="AZ5" s="49"/>
-      <c r="BA5" s="49"/>
-      <c r="BB5" s="49"/>
-      <c r="BC5" s="49"/>
-      <c r="BD5" s="49"/>
-      <c r="BE5" s="49"/>
-      <c r="BF5" s="49"/>
-      <c r="BG5" s="49"/>
-      <c r="BH5" s="49"/>
-      <c r="BI5" s="49"/>
-      <c r="BJ5" s="49"/>
-      <c r="BK5" s="49"/>
-      <c r="BL5" s="54"/>
-      <c r="BM5" s="54"/>
-      <c r="BN5" s="49"/>
-      <c r="BO5" s="49"/>
-      <c r="BP5" s="49"/>
-      <c r="BQ5" s="49"/>
-      <c r="BR5" s="49"/>
-      <c r="BS5" s="49"/>
-      <c r="BT5" s="49"/>
-      <c r="BU5" s="54"/>
-      <c r="BV5" s="54"/>
-      <c r="BW5" s="54"/>
-      <c r="BX5" s="54"/>
-      <c r="BY5" s="54"/>
-      <c r="BZ5" s="49"/>
-      <c r="CA5" s="49"/>
-      <c r="CB5" s="49"/>
-      <c r="CC5" s="49"/>
-      <c r="CD5" s="49"/>
-      <c r="CE5" s="45"/>
-      <c r="CF5" s="45"/>
-      <c r="CG5" s="45"/>
-      <c r="CH5" s="45"/>
-      <c r="CI5" s="45"/>
-      <c r="CJ5" s="45"/>
-      <c r="CK5" s="45"/>
-      <c r="CL5" s="45"/>
-      <c r="CM5" s="45"/>
-      <c r="CN5" s="45"/>
-      <c r="CO5" s="45"/>
-      <c r="CP5" s="45"/>
-      <c r="CQ5" s="45"/>
-      <c r="CR5" s="45"/>
-      <c r="CS5" s="45"/>
-      <c r="CT5" s="45"/>
-      <c r="CU5" s="45"/>
-      <c r="CV5" s="45"/>
-      <c r="CW5" s="45"/>
-      <c r="CX5" s="45"/>
-      <c r="CY5" s="45"/>
-      <c r="CZ5" s="45"/>
-      <c r="DA5" s="45"/>
-      <c r="DB5" s="45"/>
-      <c r="DC5" s="45"/>
-      <c r="DD5" s="52"/>
-      <c r="DE5" s="45"/>
-      <c r="DF5" s="45"/>
-      <c r="DG5" s="45"/>
-      <c r="DH5" s="45"/>
-      <c r="DI5" s="45"/>
-      <c r="DJ5" s="45"/>
-      <c r="DK5" s="45"/>
-      <c r="DL5" s="45"/>
-      <c r="DM5" s="45"/>
-      <c r="DN5" s="45"/>
-      <c r="DO5" s="45"/>
-      <c r="DP5" s="45"/>
-      <c r="DQ5" s="45"/>
-      <c r="DR5" s="45"/>
-      <c r="DS5" s="45"/>
-      <c r="DT5" s="45"/>
-      <c r="DU5" s="45"/>
-      <c r="DV5" s="45"/>
-      <c r="DW5" s="45"/>
-      <c r="DX5" s="45"/>
-      <c r="DY5" s="45"/>
-      <c r="DZ5" s="45"/>
-      <c r="EA5" s="45"/>
-      <c r="EB5" s="45"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="54"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="54"/>
+      <c r="AH5" s="54"/>
+      <c r="AI5" s="54"/>
+      <c r="AJ5" s="54"/>
+      <c r="AK5" s="54"/>
+      <c r="AL5" s="54"/>
+      <c r="AM5" s="54"/>
+      <c r="AN5" s="54"/>
+      <c r="AO5" s="54"/>
+      <c r="AP5" s="54"/>
+      <c r="AQ5" s="54"/>
+      <c r="AR5" s="55"/>
+      <c r="AS5" s="55"/>
+      <c r="AT5" s="55"/>
+      <c r="AU5" s="55"/>
+      <c r="AV5" s="55"/>
+      <c r="AW5" s="55"/>
+      <c r="AX5" s="55"/>
+      <c r="AY5" s="55"/>
+      <c r="AZ5" s="55"/>
+      <c r="BA5" s="55"/>
+      <c r="BB5" s="55"/>
+      <c r="BC5" s="55"/>
+      <c r="BD5" s="55"/>
+      <c r="BE5" s="55"/>
+      <c r="BF5" s="55"/>
+      <c r="BG5" s="55"/>
+      <c r="BH5" s="55"/>
+      <c r="BI5" s="55"/>
+      <c r="BJ5" s="55"/>
+      <c r="BK5" s="55"/>
+      <c r="BL5" s="57"/>
+      <c r="BM5" s="57"/>
+      <c r="BN5" s="55"/>
+      <c r="BO5" s="55"/>
+      <c r="BP5" s="55"/>
+      <c r="BQ5" s="55"/>
+      <c r="BR5" s="55"/>
+      <c r="BS5" s="55"/>
+      <c r="BT5" s="55"/>
+      <c r="BU5" s="57"/>
+      <c r="BV5" s="57"/>
+      <c r="BW5" s="57"/>
+      <c r="BX5" s="57"/>
+      <c r="BY5" s="57"/>
+      <c r="BZ5" s="55"/>
+      <c r="CA5" s="55"/>
+      <c r="CB5" s="55"/>
+      <c r="CC5" s="55"/>
+      <c r="CD5" s="55"/>
+      <c r="CE5" s="46"/>
+      <c r="CF5" s="46"/>
+      <c r="CG5" s="46"/>
+      <c r="CH5" s="46"/>
+      <c r="CI5" s="46"/>
+      <c r="CJ5" s="46"/>
+      <c r="CK5" s="46"/>
+      <c r="CL5" s="46"/>
+      <c r="CM5" s="46"/>
+      <c r="CN5" s="46"/>
+      <c r="CO5" s="46"/>
+      <c r="CP5" s="46"/>
+      <c r="CQ5" s="46"/>
+      <c r="CR5" s="46"/>
+      <c r="CS5" s="46"/>
+      <c r="CT5" s="46"/>
+      <c r="CU5" s="46"/>
+      <c r="CV5" s="46"/>
+      <c r="CW5" s="46"/>
+      <c r="CX5" s="46"/>
+      <c r="CY5" s="46"/>
+      <c r="CZ5" s="46"/>
+      <c r="DA5" s="46"/>
+      <c r="DB5" s="46"/>
+      <c r="DC5" s="46"/>
+      <c r="DD5" s="50"/>
+      <c r="DE5" s="46"/>
+      <c r="DF5" s="46"/>
+      <c r="DG5" s="46"/>
+      <c r="DH5" s="46"/>
+      <c r="DI5" s="46"/>
+      <c r="DJ5" s="46"/>
+      <c r="DK5" s="46"/>
+      <c r="DL5" s="46"/>
+      <c r="DM5" s="46"/>
+      <c r="DN5" s="46"/>
+      <c r="DO5" s="46"/>
+      <c r="DP5" s="46"/>
+      <c r="DQ5" s="46"/>
+      <c r="DR5" s="46"/>
+      <c r="DS5" s="46"/>
+      <c r="DT5" s="46"/>
+      <c r="DU5" s="46"/>
+      <c r="DV5" s="46"/>
+      <c r="DW5" s="46"/>
+      <c r="DX5" s="46"/>
+      <c r="DY5" s="46"/>
+      <c r="DZ5" s="46"/>
+      <c r="EA5" s="46"/>
+      <c r="EB5" s="46"/>
       <c r="EC5" s="44"/>
       <c r="ED5" s="44"/>
       <c r="EE5" s="44"/>
@@ -10700,8 +10704,9 @@
       <c r="FB5" s="44"/>
       <c r="FC5" s="44"/>
       <c r="FD5" s="44"/>
+      <c r="FE5" s="44"/>
     </row>
-    <row r="6" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -11180,8 +11185,11 @@
       <c r="FD6" s="28">
         <v>81</v>
       </c>
+      <c r="FE6" s="28">
+        <v>77</v>
+      </c>
     </row>
-    <row r="7" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11659,8 +11667,11 @@
       <c r="FD7" s="15">
         <v>0</v>
       </c>
+      <c r="FE7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -12138,8 +12149,11 @@
       <c r="FD8" s="28">
         <v>14</v>
       </c>
+      <c r="FE8" s="28">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12618,8 +12632,11 @@
       <c r="FD9" s="15">
         <v>79</v>
       </c>
+      <c r="FE9" s="15">
+        <v>59</v>
+      </c>
     </row>
-    <row r="10" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -13095,8 +13112,11 @@
       <c r="FD10" s="15">
         <v>0</v>
       </c>
+      <c r="FE10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13574,8 +13594,11 @@
       <c r="FD11" s="15">
         <v>17</v>
       </c>
+      <c r="FE11" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -14053,8 +14076,11 @@
       <c r="FD12" s="15">
         <v>3</v>
       </c>
+      <c r="FE12" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14532,8 +14558,11 @@
       <c r="FD13" s="15">
         <v>25</v>
       </c>
+      <c r="FE13" s="15">
+        <v>27</v>
+      </c>
     </row>
-    <row r="14" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -15011,8 +15040,11 @@
       <c r="FD14" s="15">
         <v>20</v>
       </c>
+      <c r="FE14" s="15">
+        <v>19</v>
+      </c>
     </row>
-    <row r="15" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -15490,8 +15522,11 @@
       <c r="FD15" s="15">
         <v>1</v>
       </c>
+      <c r="FE15" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -15970,8 +16005,11 @@
       <c r="FD16" s="28">
         <v>104</v>
       </c>
+      <c r="FE16" s="28">
+        <v>104</v>
+      </c>
     </row>
-    <row r="17" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -16449,8 +16487,11 @@
       <c r="FD17" s="15">
         <v>121</v>
       </c>
+      <c r="FE17" s="15">
+        <v>128</v>
+      </c>
     </row>
-    <row r="18" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16929,8 +16970,11 @@
       <c r="FD18" s="34">
         <v>1543</v>
       </c>
+      <c r="FE18" s="34">
+        <v>1332</v>
+      </c>
     </row>
-    <row r="19" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="68" t="s">
         <v>27</v>
@@ -17409,8 +17453,11 @@
       <c r="FD19" s="15">
         <v>49</v>
       </c>
+      <c r="FE19" s="15">
+        <v>41</v>
+      </c>
     </row>
-    <row r="20" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="68"/>
       <c r="C20" s="9" t="s">
@@ -17887,8 +17934,11 @@
       <c r="FD20" s="28">
         <v>102</v>
       </c>
+      <c r="FE20" s="28">
+        <v>61</v>
+      </c>
     </row>
-    <row r="21" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="68"/>
       <c r="C21" s="9" t="s">
@@ -18365,8 +18415,11 @@
       <c r="FD21" s="15">
         <v>28</v>
       </c>
+      <c r="FE21" s="15">
+        <v>18</v>
+      </c>
     </row>
-    <row r="22" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18844,8 +18897,11 @@
       <c r="FD22" s="15">
         <v>2</v>
       </c>
+      <c r="FE22" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -19323,8 +19379,11 @@
       <c r="FD23" s="15">
         <v>0</v>
       </c>
+      <c r="FE23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19802,8 +19861,11 @@
       <c r="FD24" s="15">
         <v>8</v>
       </c>
+      <c r="FE24" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -20281,8 +20343,11 @@
       <c r="FD25" s="15">
         <v>1</v>
       </c>
+      <c r="FE25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -20760,8 +20825,11 @@
       <c r="FD26" s="15">
         <v>10</v>
       </c>
+      <c r="FE26" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="27" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -21239,8 +21307,11 @@
       <c r="FD27" s="15">
         <v>0</v>
       </c>
+      <c r="FE27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -21718,8 +21789,11 @@
       <c r="FD28" s="15">
         <v>2</v>
       </c>
+      <c r="FE28" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="69" t="s">
         <v>45</v>
       </c>
@@ -22197,8 +22271,11 @@
       <c r="FD29" s="15">
         <v>0</v>
       </c>
+      <c r="FE29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="69"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -22674,8 +22751,11 @@
       <c r="FD30" s="15">
         <v>11</v>
       </c>
+      <c r="FE30" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="31" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -23154,8 +23234,11 @@
       <c r="FD31" s="15">
         <v>44</v>
       </c>
+      <c r="FE31" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="32" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -23633,8 +23716,11 @@
       <c r="FD32" s="15">
         <v>0</v>
       </c>
+      <c r="FE32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -24112,8 +24198,11 @@
       <c r="FD33" s="15">
         <v>0</v>
       </c>
+      <c r="FE33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -24592,8 +24681,11 @@
       <c r="FD34" s="15">
         <v>51</v>
       </c>
+      <c r="FE34" s="15">
+        <v>45</v>
+      </c>
     </row>
-    <row r="35" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="68" t="s">
         <v>56</v>
@@ -25072,8 +25164,11 @@
       <c r="FD35" s="15">
         <v>263</v>
       </c>
+      <c r="FE35" s="15">
+        <v>244</v>
+      </c>
     </row>
-    <row r="36" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="68"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -25549,8 +25644,11 @@
       <c r="FD36" s="28">
         <v>19</v>
       </c>
+      <c r="FE36" s="28">
+        <v>21</v>
+      </c>
     </row>
-    <row r="37" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -26029,8 +26127,11 @@
       <c r="FD37" s="15">
         <v>51</v>
       </c>
+      <c r="FE37" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="38" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -26508,8 +26609,11 @@
       <c r="FD38" s="15">
         <v>6</v>
       </c>
+      <c r="FE38" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="39" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -26987,8 +27091,11 @@
       <c r="FD39" s="15">
         <v>4</v>
       </c>
+      <c r="FE39" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="40" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -27466,8 +27573,11 @@
       <c r="FD40" s="15">
         <v>0</v>
       </c>
+      <c r="FE40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -27945,8 +28055,11 @@
       <c r="FD41" s="15">
         <v>0</v>
       </c>
+      <c r="FE41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -28424,8 +28537,11 @@
       <c r="FD42" s="15">
         <v>8</v>
       </c>
+      <c r="FE42" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -28903,8 +29019,11 @@
       <c r="FD43" s="28">
         <v>37</v>
       </c>
+      <c r="FE43" s="28">
+        <v>48</v>
+      </c>
     </row>
-    <row r="44" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -29382,8 +29501,11 @@
       <c r="FD44" s="15">
         <v>4</v>
       </c>
+      <c r="FE44" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -29861,8 +29983,11 @@
       <c r="FD45" s="15">
         <v>18</v>
       </c>
+      <c r="FE45" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="46" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -30340,8 +30465,11 @@
       <c r="FD46" s="15">
         <v>21</v>
       </c>
+      <c r="FE46" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="47" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -30819,8 +30947,11 @@
       <c r="FD47" s="15">
         <v>0</v>
       </c>
+      <c r="FE47" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -31298,8 +31429,11 @@
       <c r="FD48" s="15">
         <v>20</v>
       </c>
+      <c r="FE48" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="49" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="68" t="s">
         <v>83</v>
@@ -31778,8 +31912,11 @@
       <c r="FD49" s="15">
         <v>40</v>
       </c>
+      <c r="FE49" s="15">
+        <v>24</v>
+      </c>
     </row>
-    <row r="50" spans="1:160" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="68"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -32255,8 +32392,11 @@
       <c r="FD50" s="15">
         <v>11</v>
       </c>
+      <c r="FE50" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="51" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -32734,8 +32874,11 @@
       <c r="FD51" s="15">
         <v>8</v>
       </c>
+      <c r="FE51" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="52" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -33213,8 +33356,11 @@
       <c r="FD52" s="15">
         <v>13</v>
       </c>
+      <c r="FE52" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="53" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -33692,8 +33838,11 @@
       <c r="FD53" s="15">
         <v>37</v>
       </c>
+      <c r="FE53" s="15">
+        <v>44</v>
+      </c>
     </row>
-    <row r="54" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -34171,8 +34320,11 @@
       <c r="FD54" s="15">
         <v>6</v>
       </c>
+      <c r="FE54" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -34650,8 +34802,11 @@
       <c r="FD55" s="15">
         <v>16</v>
       </c>
+      <c r="FE55" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="56" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -35129,8 +35284,11 @@
       <c r="FD56" s="15">
         <v>1</v>
       </c>
+      <c r="FE56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -35608,8 +35766,11 @@
       <c r="FD57" s="15">
         <v>2</v>
       </c>
+      <c r="FE57" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -36242,8 +36403,12 @@
         <f t="shared" si="13"/>
         <v>2901</v>
       </c>
+      <c r="FE58" s="14">
+        <f t="shared" ref="FE58" si="14">SUM(FE6:FE57)</f>
+        <v>2514</v>
+      </c>
     </row>
-    <row r="59" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -36327,7 +36492,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -36411,7 +36576,7 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:160" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -36496,32 +36661,34 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="175">
+    <mergeCell ref="FE4:FE5"/>
+    <mergeCell ref="DE2:FE2"/>
+    <mergeCell ref="ER3:FE3"/>
     <mergeCell ref="FD4:FD5"/>
-    <mergeCell ref="ER3:FD3"/>
-    <mergeCell ref="DE2:FD2"/>
     <mergeCell ref="FC4:FC5"/>
     <mergeCell ref="FB4:FB5"/>
     <mergeCell ref="FA4:FA5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="CZ4:CZ5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="D2:BC2"/>
     <mergeCell ref="DO4:DO5"/>
     <mergeCell ref="DN4:DN5"/>
     <mergeCell ref="DS4:DS5"/>
     <mergeCell ref="DR4:DR5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="BW4:BW5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="AR3:BC3"/>
     <mergeCell ref="CY4:CY5"/>
     <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="BN4:BN5"/>
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="BG4:BG5"/>
@@ -36535,16 +36702,16 @@
     <mergeCell ref="AW4:AW5"/>
     <mergeCell ref="CD4:CD5"/>
     <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CJ4:CJ5"/>
     <mergeCell ref="D61:W61"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="S4:S5"/>
@@ -36590,8 +36757,6 @@
     <mergeCell ref="AQ4:AQ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="BV4:BV5"/>
     <mergeCell ref="BL4:BL5"/>
     <mergeCell ref="BH4:BH5"/>
@@ -36602,6 +36767,8 @@
     <mergeCell ref="BY4:BY5"/>
     <mergeCell ref="BK4:BK5"/>
     <mergeCell ref="BM4:BM5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="BX4:BX5"/>
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="CU4:CU5"/>
     <mergeCell ref="CR4:CR5"/>
@@ -36626,7 +36793,6 @@
     <mergeCell ref="BI4:BI5"/>
     <mergeCell ref="DV4:DV5"/>
     <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="CK4:CK5"/>
     <mergeCell ref="EZ4:EZ5"/>
     <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="CS4:CS5"/>
@@ -36674,43 +36840,48 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="29" priority="8">
+    <cfRule type="containsBlanks" dxfId="26" priority="9">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="28" priority="7">
+    <cfRule type="containsBlanks" dxfId="25" priority="8">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="27" priority="6">
+    <cfRule type="containsBlanks" dxfId="24" priority="7">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="26" priority="5">
+    <cfRule type="containsBlanks" dxfId="23" priority="6">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="25" priority="4">
+    <cfRule type="containsBlanks" dxfId="22" priority="5">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="24" priority="3">
+    <cfRule type="containsBlanks" dxfId="21" priority="4">
       <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FC6:FC57">
-    <cfRule type="containsBlanks" dxfId="23" priority="2">
+    <cfRule type="containsBlanks" dxfId="20" priority="3">
       <formula>LEN(TRIM(FC6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FD6:FD57">
-    <cfRule type="containsBlanks" dxfId="22" priority="1">
+    <cfRule type="containsBlanks" dxfId="19" priority="2">
       <formula>LEN(TRIM(FD6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FE6:FE57">
+    <cfRule type="containsBlanks" dxfId="18" priority="1">
+      <formula>LEN(TRIM(FE6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -36731,7 +36902,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:FD58"/>
+  <dimension ref="B1:FE58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -36757,11 +36928,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="160" width="10.875" style="1" customWidth="1"/>
-    <col min="161" max="16384" width="8.625" style="1"/>
+    <col min="106" max="161" width="10.875" style="1" customWidth="1"/>
+    <col min="162" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:161" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="BB1" s="86" t="s">
         <v>323</v>
       </c>
@@ -36848,120 +37019,121 @@
       <c r="FA1" s="19"/>
       <c r="FB1" s="19"/>
       <c r="FC1" s="19"/>
-      <c r="FD1" s="19" t="s">
+      <c r="FD1" s="19"/>
+      <c r="FE1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:160" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:161" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="73" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="51"/>
+      <c r="BA2" s="51"/>
+      <c r="BB2" s="51"/>
       <c r="BC2" s="85"/>
       <c r="BD2" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="55"/>
-      <c r="BF2" s="55"/>
-      <c r="BG2" s="55"/>
-      <c r="BH2" s="55"/>
-      <c r="BI2" s="55"/>
-      <c r="BJ2" s="55"/>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="55"/>
-      <c r="BP2" s="55"/>
-      <c r="BQ2" s="55"/>
-      <c r="BR2" s="55"/>
-      <c r="BS2" s="55"/>
-      <c r="BT2" s="55"/>
-      <c r="BU2" s="55"/>
-      <c r="BV2" s="55"/>
-      <c r="BW2" s="55"/>
-      <c r="BX2" s="55"/>
-      <c r="BY2" s="55"/>
-      <c r="BZ2" s="55"/>
-      <c r="CA2" s="55"/>
-      <c r="CB2" s="55"/>
-      <c r="CC2" s="55"/>
-      <c r="CD2" s="55"/>
-      <c r="CE2" s="55"/>
-      <c r="CF2" s="55"/>
-      <c r="CG2" s="55"/>
-      <c r="CH2" s="55"/>
-      <c r="CI2" s="55"/>
-      <c r="CJ2" s="55"/>
-      <c r="CK2" s="55"/>
-      <c r="CL2" s="55"/>
-      <c r="CM2" s="55"/>
-      <c r="CN2" s="55"/>
-      <c r="CO2" s="55"/>
-      <c r="CP2" s="55"/>
-      <c r="CQ2" s="55"/>
-      <c r="CR2" s="55"/>
-      <c r="CS2" s="55"/>
-      <c r="CT2" s="55"/>
-      <c r="CU2" s="55"/>
-      <c r="CV2" s="55"/>
-      <c r="CW2" s="55"/>
-      <c r="CX2" s="55"/>
-      <c r="CY2" s="55"/>
-      <c r="CZ2" s="55"/>
-      <c r="DA2" s="55"/>
-      <c r="DB2" s="55"/>
+      <c r="BE2" s="51"/>
+      <c r="BF2" s="51"/>
+      <c r="BG2" s="51"/>
+      <c r="BH2" s="51"/>
+      <c r="BI2" s="51"/>
+      <c r="BJ2" s="51"/>
+      <c r="BK2" s="51"/>
+      <c r="BL2" s="51"/>
+      <c r="BM2" s="51"/>
+      <c r="BN2" s="51"/>
+      <c r="BO2" s="51"/>
+      <c r="BP2" s="51"/>
+      <c r="BQ2" s="51"/>
+      <c r="BR2" s="51"/>
+      <c r="BS2" s="51"/>
+      <c r="BT2" s="51"/>
+      <c r="BU2" s="51"/>
+      <c r="BV2" s="51"/>
+      <c r="BW2" s="51"/>
+      <c r="BX2" s="51"/>
+      <c r="BY2" s="51"/>
+      <c r="BZ2" s="51"/>
+      <c r="CA2" s="51"/>
+      <c r="CB2" s="51"/>
+      <c r="CC2" s="51"/>
+      <c r="CD2" s="51"/>
+      <c r="CE2" s="51"/>
+      <c r="CF2" s="51"/>
+      <c r="CG2" s="51"/>
+      <c r="CH2" s="51"/>
+      <c r="CI2" s="51"/>
+      <c r="CJ2" s="51"/>
+      <c r="CK2" s="51"/>
+      <c r="CL2" s="51"/>
+      <c r="CM2" s="51"/>
+      <c r="CN2" s="51"/>
+      <c r="CO2" s="51"/>
+      <c r="CP2" s="51"/>
+      <c r="CQ2" s="51"/>
+      <c r="CR2" s="51"/>
+      <c r="CS2" s="51"/>
+      <c r="CT2" s="51"/>
+      <c r="CU2" s="51"/>
+      <c r="CV2" s="51"/>
+      <c r="CW2" s="51"/>
+      <c r="CX2" s="51"/>
+      <c r="CY2" s="51"/>
+      <c r="CZ2" s="51"/>
+      <c r="DA2" s="51"/>
+      <c r="DB2" s="51"/>
       <c r="DC2" s="85"/>
       <c r="DD2" s="72" t="s">
         <v>321</v>
@@ -37018,181 +37190,183 @@
       <c r="FB2" s="72"/>
       <c r="FC2" s="72"/>
       <c r="FD2" s="72"/>
+      <c r="FE2" s="72"/>
     </row>
-    <row r="3" spans="2:160" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:161" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="56"/>
-      <c r="AC3" s="56"/>
-      <c r="AD3" s="56"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="56"/>
-      <c r="AH3" s="56"/>
-      <c r="AI3" s="56"/>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="56"/>
-      <c r="AL3" s="56"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="56"/>
-      <c r="AO3" s="56"/>
-      <c r="AP3" s="56"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="50" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="52"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="52"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="52"/>
+      <c r="AK3" s="52"/>
+      <c r="AL3" s="52"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="52"/>
+      <c r="AO3" s="52"/>
+      <c r="AP3" s="52"/>
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="56"/>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="56"/>
-      <c r="AV3" s="56"/>
-      <c r="AW3" s="56"/>
-      <c r="AX3" s="56"/>
-      <c r="AY3" s="56"/>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="56"/>
-      <c r="BB3" s="56"/>
-      <c r="BC3" s="57"/>
-      <c r="BD3" s="50" t="s">
+      <c r="AS3" s="52"/>
+      <c r="AT3" s="52"/>
+      <c r="AU3" s="52"/>
+      <c r="AV3" s="52"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="52"/>
+      <c r="AY3" s="52"/>
+      <c r="AZ3" s="52"/>
+      <c r="BA3" s="52"/>
+      <c r="BB3" s="52"/>
+      <c r="BC3" s="53"/>
+      <c r="BD3" s="47" t="s">
         <v>322</v>
       </c>
-      <c r="BE3" s="56"/>
-      <c r="BF3" s="56"/>
-      <c r="BG3" s="56"/>
-      <c r="BH3" s="56"/>
-      <c r="BI3" s="56"/>
-      <c r="BJ3" s="56"/>
-      <c r="BK3" s="56"/>
-      <c r="BL3" s="56"/>
-      <c r="BM3" s="56"/>
-      <c r="BN3" s="56"/>
-      <c r="BO3" s="56"/>
-      <c r="BP3" s="56"/>
-      <c r="BQ3" s="56"/>
-      <c r="BR3" s="56"/>
-      <c r="BS3" s="56"/>
-      <c r="BT3" s="56"/>
-      <c r="BU3" s="56"/>
-      <c r="BV3" s="56"/>
-      <c r="BW3" s="56"/>
-      <c r="BX3" s="56"/>
-      <c r="BY3" s="56"/>
-      <c r="BZ3" s="56"/>
-      <c r="CA3" s="56"/>
-      <c r="CB3" s="56"/>
-      <c r="CC3" s="56"/>
-      <c r="CD3" s="56"/>
-      <c r="CE3" s="56"/>
-      <c r="CF3" s="56"/>
-      <c r="CG3" s="56"/>
-      <c r="CH3" s="56"/>
-      <c r="CI3" s="56"/>
-      <c r="CJ3" s="56"/>
-      <c r="CK3" s="56"/>
-      <c r="CL3" s="56"/>
-      <c r="CM3" s="56"/>
-      <c r="CN3" s="56"/>
-      <c r="CO3" s="56"/>
-      <c r="CP3" s="56"/>
-      <c r="CQ3" s="57"/>
-      <c r="CR3" s="50" t="s">
+      <c r="BE3" s="52"/>
+      <c r="BF3" s="52"/>
+      <c r="BG3" s="52"/>
+      <c r="BH3" s="52"/>
+      <c r="BI3" s="52"/>
+      <c r="BJ3" s="52"/>
+      <c r="BK3" s="52"/>
+      <c r="BL3" s="52"/>
+      <c r="BM3" s="52"/>
+      <c r="BN3" s="52"/>
+      <c r="BO3" s="52"/>
+      <c r="BP3" s="52"/>
+      <c r="BQ3" s="52"/>
+      <c r="BR3" s="52"/>
+      <c r="BS3" s="52"/>
+      <c r="BT3" s="52"/>
+      <c r="BU3" s="52"/>
+      <c r="BV3" s="52"/>
+      <c r="BW3" s="52"/>
+      <c r="BX3" s="52"/>
+      <c r="BY3" s="52"/>
+      <c r="BZ3" s="52"/>
+      <c r="CA3" s="52"/>
+      <c r="CB3" s="52"/>
+      <c r="CC3" s="52"/>
+      <c r="CD3" s="52"/>
+      <c r="CE3" s="52"/>
+      <c r="CF3" s="52"/>
+      <c r="CG3" s="52"/>
+      <c r="CH3" s="52"/>
+      <c r="CI3" s="52"/>
+      <c r="CJ3" s="52"/>
+      <c r="CK3" s="52"/>
+      <c r="CL3" s="52"/>
+      <c r="CM3" s="52"/>
+      <c r="CN3" s="52"/>
+      <c r="CO3" s="52"/>
+      <c r="CP3" s="52"/>
+      <c r="CQ3" s="53"/>
+      <c r="CR3" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="56"/>
-      <c r="CT3" s="56"/>
-      <c r="CU3" s="56"/>
-      <c r="CV3" s="56"/>
-      <c r="CW3" s="56"/>
-      <c r="CX3" s="56"/>
-      <c r="CY3" s="56"/>
-      <c r="CZ3" s="56"/>
-      <c r="DA3" s="56"/>
-      <c r="DB3" s="56"/>
-      <c r="DC3" s="57"/>
-      <c r="DD3" s="47" t="s">
+      <c r="CS3" s="52"/>
+      <c r="CT3" s="52"/>
+      <c r="CU3" s="52"/>
+      <c r="CV3" s="52"/>
+      <c r="CW3" s="52"/>
+      <c r="CX3" s="52"/>
+      <c r="CY3" s="52"/>
+      <c r="CZ3" s="52"/>
+      <c r="DA3" s="52"/>
+      <c r="DB3" s="52"/>
+      <c r="DC3" s="53"/>
+      <c r="DD3" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="47"/>
-      <c r="DF3" s="47"/>
-      <c r="DG3" s="47"/>
-      <c r="DH3" s="47"/>
-      <c r="DI3" s="47"/>
-      <c r="DJ3" s="47"/>
-      <c r="DK3" s="47"/>
-      <c r="DL3" s="47"/>
-      <c r="DM3" s="47"/>
-      <c r="DN3" s="47"/>
-      <c r="DO3" s="47"/>
-      <c r="DP3" s="47"/>
-      <c r="DQ3" s="47"/>
-      <c r="DR3" s="47"/>
-      <c r="DS3" s="47"/>
-      <c r="DT3" s="47"/>
-      <c r="DU3" s="47"/>
-      <c r="DV3" s="47"/>
-      <c r="DW3" s="47"/>
-      <c r="DX3" s="47"/>
-      <c r="DY3" s="47"/>
-      <c r="DZ3" s="47"/>
-      <c r="EA3" s="47"/>
-      <c r="EB3" s="47"/>
-      <c r="EC3" s="47"/>
-      <c r="ED3" s="47"/>
-      <c r="EE3" s="47"/>
-      <c r="EF3" s="47"/>
-      <c r="EG3" s="47"/>
-      <c r="EH3" s="47"/>
-      <c r="EI3" s="47"/>
-      <c r="EJ3" s="47"/>
-      <c r="EK3" s="47"/>
-      <c r="EL3" s="47"/>
-      <c r="EM3" s="47"/>
-      <c r="EN3" s="47"/>
-      <c r="EO3" s="47"/>
-      <c r="EP3" s="47"/>
-      <c r="EQ3" s="47"/>
-      <c r="ER3" s="47" t="s">
+      <c r="DE3" s="45"/>
+      <c r="DF3" s="45"/>
+      <c r="DG3" s="45"/>
+      <c r="DH3" s="45"/>
+      <c r="DI3" s="45"/>
+      <c r="DJ3" s="45"/>
+      <c r="DK3" s="45"/>
+      <c r="DL3" s="45"/>
+      <c r="DM3" s="45"/>
+      <c r="DN3" s="45"/>
+      <c r="DO3" s="45"/>
+      <c r="DP3" s="45"/>
+      <c r="DQ3" s="45"/>
+      <c r="DR3" s="45"/>
+      <c r="DS3" s="45"/>
+      <c r="DT3" s="45"/>
+      <c r="DU3" s="45"/>
+      <c r="DV3" s="45"/>
+      <c r="DW3" s="45"/>
+      <c r="DX3" s="45"/>
+      <c r="DY3" s="45"/>
+      <c r="DZ3" s="45"/>
+      <c r="EA3" s="45"/>
+      <c r="EB3" s="45"/>
+      <c r="EC3" s="45"/>
+      <c r="ED3" s="45"/>
+      <c r="EE3" s="45"/>
+      <c r="EF3" s="45"/>
+      <c r="EG3" s="45"/>
+      <c r="EH3" s="45"/>
+      <c r="EI3" s="45"/>
+      <c r="EJ3" s="45"/>
+      <c r="EK3" s="45"/>
+      <c r="EL3" s="45"/>
+      <c r="EM3" s="45"/>
+      <c r="EN3" s="45"/>
+      <c r="EO3" s="45"/>
+      <c r="EP3" s="45"/>
+      <c r="EQ3" s="45"/>
+      <c r="ER3" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="47"/>
-      <c r="ET3" s="47"/>
-      <c r="EU3" s="47"/>
-      <c r="EV3" s="47"/>
-      <c r="EW3" s="47"/>
-      <c r="EX3" s="47"/>
-      <c r="EY3" s="47"/>
-      <c r="EZ3" s="47"/>
-      <c r="FA3" s="47"/>
-      <c r="FB3" s="47"/>
-      <c r="FC3" s="47"/>
-      <c r="FD3" s="47"/>
+      <c r="ES3" s="45"/>
+      <c r="ET3" s="45"/>
+      <c r="EU3" s="45"/>
+      <c r="EV3" s="45"/>
+      <c r="EW3" s="45"/>
+      <c r="EX3" s="45"/>
+      <c r="EY3" s="45"/>
+      <c r="EZ3" s="45"/>
+      <c r="FA3" s="45"/>
+      <c r="FB3" s="45"/>
+      <c r="FC3" s="45"/>
+      <c r="FD3" s="45"/>
+      <c r="FE3" s="45"/>
     </row>
-    <row r="4" spans="2:160" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:161" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="64" t="s">
         <v>0</v>
       </c>
@@ -37670,114 +37844,117 @@
       <c r="FD4" s="44" t="s">
         <v>439</v>
       </c>
+      <c r="FE4" s="44" t="s">
+        <v>442</v>
+      </c>
     </row>
-    <row r="5" spans="2:160" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:161" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="65"/>
       <c r="C5" s="71"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
       <c r="R5" s="81"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
       <c r="Y5" s="77"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="48"/>
       <c r="AC5" s="77"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
       <c r="AI5" s="77"/>
       <c r="AJ5" s="77"/>
       <c r="AK5" s="77"/>
       <c r="AL5" s="77"/>
       <c r="AM5" s="77"/>
-      <c r="AN5" s="46"/>
+      <c r="AN5" s="48"/>
       <c r="AO5" s="77"/>
       <c r="AP5" s="77"/>
-      <c r="AQ5" s="46"/>
+      <c r="AQ5" s="48"/>
       <c r="AR5" s="77"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="48"/>
+      <c r="AU5" s="48"/>
+      <c r="AV5" s="48"/>
+      <c r="AW5" s="48"/>
       <c r="AX5" s="77"/>
       <c r="AY5" s="77"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
+      <c r="AZ5" s="48"/>
+      <c r="BA5" s="48"/>
+      <c r="BB5" s="48"/>
       <c r="BC5" s="77"/>
-      <c r="BD5" s="48"/>
-      <c r="BE5" s="48"/>
-      <c r="BF5" s="48"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="48"/>
-      <c r="BJ5" s="48"/>
-      <c r="BK5" s="48"/>
-      <c r="BL5" s="48"/>
-      <c r="BM5" s="48"/>
-      <c r="BN5" s="48"/>
-      <c r="BO5" s="48"/>
-      <c r="BP5" s="48"/>
-      <c r="BQ5" s="48"/>
-      <c r="BR5" s="48"/>
-      <c r="BS5" s="48"/>
-      <c r="BT5" s="48"/>
-      <c r="BU5" s="53"/>
-      <c r="BV5" s="53"/>
-      <c r="BW5" s="53"/>
-      <c r="BX5" s="53"/>
-      <c r="BY5" s="53"/>
-      <c r="BZ5" s="53"/>
-      <c r="CA5" s="48"/>
-      <c r="CB5" s="48"/>
-      <c r="CC5" s="48"/>
-      <c r="CD5" s="48"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="46"/>
-      <c r="CV5" s="46"/>
-      <c r="CW5" s="46"/>
-      <c r="CX5" s="46"/>
-      <c r="CY5" s="46"/>
-      <c r="CZ5" s="46"/>
-      <c r="DA5" s="46"/>
-      <c r="DB5" s="46"/>
-      <c r="DC5" s="46"/>
+      <c r="BD5" s="54"/>
+      <c r="BE5" s="54"/>
+      <c r="BF5" s="54"/>
+      <c r="BG5" s="54"/>
+      <c r="BH5" s="54"/>
+      <c r="BI5" s="54"/>
+      <c r="BJ5" s="54"/>
+      <c r="BK5" s="54"/>
+      <c r="BL5" s="54"/>
+      <c r="BM5" s="54"/>
+      <c r="BN5" s="54"/>
+      <c r="BO5" s="54"/>
+      <c r="BP5" s="54"/>
+      <c r="BQ5" s="54"/>
+      <c r="BR5" s="54"/>
+      <c r="BS5" s="54"/>
+      <c r="BT5" s="54"/>
+      <c r="BU5" s="56"/>
+      <c r="BV5" s="56"/>
+      <c r="BW5" s="56"/>
+      <c r="BX5" s="56"/>
+      <c r="BY5" s="56"/>
+      <c r="BZ5" s="56"/>
+      <c r="CA5" s="54"/>
+      <c r="CB5" s="54"/>
+      <c r="CC5" s="54"/>
+      <c r="CD5" s="54"/>
+      <c r="CE5" s="48"/>
+      <c r="CF5" s="48"/>
+      <c r="CG5" s="48"/>
+      <c r="CH5" s="48"/>
+      <c r="CI5" s="48"/>
+      <c r="CJ5" s="48"/>
+      <c r="CK5" s="48"/>
+      <c r="CL5" s="48"/>
+      <c r="CM5" s="48"/>
+      <c r="CN5" s="48"/>
+      <c r="CO5" s="48"/>
+      <c r="CP5" s="48"/>
+      <c r="CQ5" s="48"/>
+      <c r="CR5" s="48"/>
+      <c r="CS5" s="48"/>
+      <c r="CT5" s="48"/>
+      <c r="CU5" s="48"/>
+      <c r="CV5" s="48"/>
+      <c r="CW5" s="48"/>
+      <c r="CX5" s="48"/>
+      <c r="CY5" s="48"/>
+      <c r="CZ5" s="48"/>
+      <c r="DA5" s="48"/>
+      <c r="DB5" s="48"/>
+      <c r="DC5" s="48"/>
       <c r="DD5" s="44"/>
       <c r="DE5" s="44"/>
       <c r="DF5" s="44"/>
@@ -37831,8 +38008,9 @@
       <c r="FB5" s="44"/>
       <c r="FC5" s="44"/>
       <c r="FD5" s="44"/>
+      <c r="FE5" s="44"/>
     </row>
-    <row r="6" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -38310,8 +38488,11 @@
       <c r="FD6" s="28">
         <v>100</v>
       </c>
+      <c r="FE6" s="28">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -38789,8 +38970,11 @@
       <c r="FD7" s="15">
         <v>3</v>
       </c>
+      <c r="FE7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -39268,8 +39452,11 @@
       <c r="FD8" s="28">
         <v>10</v>
       </c>
+      <c r="FE8" s="28">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -39747,8 +39934,11 @@
       <c r="FD9" s="15">
         <v>93</v>
       </c>
+      <c r="FE9" s="15">
+        <v>59</v>
+      </c>
     </row>
-    <row r="10" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -40226,8 +40416,11 @@
       <c r="FD10" s="15">
         <v>1</v>
       </c>
+      <c r="FE10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -40705,8 +40898,11 @@
       <c r="FD11" s="15">
         <v>10</v>
       </c>
+      <c r="FE11" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="12" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -41184,8 +41380,11 @@
       <c r="FD12" s="15">
         <v>12</v>
       </c>
+      <c r="FE12" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -41663,8 +41862,11 @@
       <c r="FD13" s="15">
         <v>16</v>
       </c>
+      <c r="FE13" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="14" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -42142,8 +42344,11 @@
       <c r="FD14" s="15">
         <v>17</v>
       </c>
+      <c r="FE14" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="15" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -42621,8 +42826,11 @@
       <c r="FD15" s="15">
         <v>0</v>
       </c>
+      <c r="FE15" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -43100,8 +43308,11 @@
       <c r="FD16" s="28">
         <v>93</v>
       </c>
+      <c r="FE16" s="28">
+        <v>119</v>
+      </c>
     </row>
-    <row r="17" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -43579,8 +43790,11 @@
       <c r="FD17" s="15">
         <v>160</v>
       </c>
+      <c r="FE17" s="15">
+        <v>119</v>
+      </c>
     </row>
-    <row r="18" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -44058,8 +44272,11 @@
       <c r="FD18" s="34">
         <v>1618</v>
       </c>
+      <c r="FE18" s="34">
+        <v>1536</v>
+      </c>
     </row>
-    <row r="19" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="78" t="s">
         <v>27</v>
       </c>
@@ -44537,8 +44754,11 @@
       <c r="FD19" s="15">
         <v>51</v>
       </c>
+      <c r="FE19" s="15">
+        <v>49</v>
+      </c>
     </row>
-    <row r="20" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
@@ -45014,8 +45234,11 @@
       <c r="FD20" s="28">
         <v>143</v>
       </c>
+      <c r="FE20" s="28">
+        <v>147</v>
+      </c>
     </row>
-    <row r="21" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
@@ -45491,8 +45714,11 @@
       <c r="FD21" s="15">
         <v>35</v>
       </c>
+      <c r="FE21" s="15">
+        <v>23</v>
+      </c>
     </row>
-    <row r="22" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -45970,8 +46196,11 @@
       <c r="FD22" s="15">
         <v>8</v>
       </c>
+      <c r="FE22" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="23" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -46449,8 +46678,11 @@
       <c r="FD23" s="15">
         <v>0</v>
       </c>
+      <c r="FE23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -46928,8 +47160,11 @@
       <c r="FD24" s="15">
         <v>2</v>
       </c>
+      <c r="FE24" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="25" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -47407,8 +47642,11 @@
       <c r="FD25" s="15">
         <v>0</v>
       </c>
+      <c r="FE25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -47886,8 +48124,11 @@
       <c r="FD26" s="15">
         <v>14</v>
       </c>
+      <c r="FE26" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="27" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -48365,8 +48606,11 @@
       <c r="FD27" s="15">
         <v>0</v>
       </c>
+      <c r="FE27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -48844,8 +49088,11 @@
       <c r="FD28" s="15">
         <v>1</v>
       </c>
+      <c r="FE28" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -49323,8 +49570,11 @@
       <c r="FD29" s="15">
         <v>3</v>
       </c>
+      <c r="FE29" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -49800,8 +50050,11 @@
       <c r="FD30" s="15">
         <v>10</v>
       </c>
+      <c r="FE30" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="31" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -50279,8 +50532,11 @@
       <c r="FD31" s="15">
         <v>16</v>
       </c>
+      <c r="FE31" s="15">
+        <v>17</v>
+      </c>
     </row>
-    <row r="32" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -50758,8 +51014,11 @@
       <c r="FD32" s="15">
         <v>1</v>
       </c>
+      <c r="FE32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -51237,8 +51496,11 @@
       <c r="FD33" s="15">
         <v>2</v>
       </c>
+      <c r="FE33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -51716,8 +51978,11 @@
       <c r="FD34" s="15">
         <v>41</v>
       </c>
+      <c r="FE34" s="15">
+        <v>42</v>
+      </c>
     </row>
-    <row r="35" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="78" t="s">
         <v>56</v>
       </c>
@@ -52195,8 +52460,11 @@
       <c r="FD35" s="15">
         <v>345</v>
       </c>
+      <c r="FE35" s="15">
+        <v>337</v>
+      </c>
     </row>
-    <row r="36" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -52672,8 +52940,11 @@
       <c r="FD36" s="28">
         <v>35</v>
       </c>
+      <c r="FE36" s="28">
+        <v>45</v>
+      </c>
     </row>
-    <row r="37" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="11" t="s">
         <v>59</v>
       </c>
@@ -53151,8 +53422,11 @@
       <c r="FD37" s="15">
         <v>45</v>
       </c>
+      <c r="FE37" s="15">
+        <v>45</v>
+      </c>
     </row>
-    <row r="38" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -53630,8 +53904,11 @@
       <c r="FD38" s="15">
         <v>11</v>
       </c>
+      <c r="FE38" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="39" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -54109,8 +54386,11 @@
       <c r="FD39" s="15">
         <v>8</v>
       </c>
+      <c r="FE39" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="40" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -54588,8 +54868,11 @@
       <c r="FD40" s="15">
         <v>0</v>
       </c>
+      <c r="FE40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -55067,8 +55350,11 @@
       <c r="FD41" s="15">
         <v>0</v>
       </c>
+      <c r="FE41" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -55546,8 +55832,11 @@
       <c r="FD42" s="15">
         <v>6</v>
       </c>
+      <c r="FE42" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="43" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -56025,8 +56314,11 @@
       <c r="FD43" s="28">
         <v>41</v>
       </c>
+      <c r="FE43" s="28">
+        <v>44</v>
+      </c>
     </row>
-    <row r="44" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -56504,8 +56796,11 @@
       <c r="FD44" s="15">
         <v>5</v>
       </c>
+      <c r="FE44" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -56983,8 +57278,11 @@
       <c r="FD45" s="15">
         <v>13</v>
       </c>
+      <c r="FE45" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -57462,8 +57760,11 @@
       <c r="FD46" s="15">
         <v>11</v>
       </c>
+      <c r="FE46" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="47" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -57941,8 +58242,11 @@
       <c r="FD47" s="15">
         <v>3</v>
       </c>
+      <c r="FE47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -58420,8 +58724,11 @@
       <c r="FD48" s="15">
         <v>1</v>
       </c>
+      <c r="FE48" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B49" s="78" t="s">
         <v>83</v>
       </c>
@@ -58899,8 +59206,11 @@
       <c r="FD49" s="15">
         <v>24</v>
       </c>
+      <c r="FE49" s="15">
+        <v>38</v>
+      </c>
     </row>
-    <row r="50" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -59376,8 +59686,11 @@
       <c r="FD50" s="15">
         <v>8</v>
       </c>
+      <c r="FE50" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="51" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -59855,8 +60168,11 @@
       <c r="FD51" s="15">
         <v>2</v>
       </c>
+      <c r="FE51" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="52" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -60334,8 +60650,11 @@
       <c r="FD52" s="15">
         <v>11</v>
       </c>
+      <c r="FE52" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -60813,8 +61132,11 @@
       <c r="FD53" s="15">
         <v>26</v>
       </c>
+      <c r="FE53" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="54" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -61292,8 +61614,11 @@
       <c r="FD54" s="15">
         <v>10</v>
       </c>
+      <c r="FE54" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="55" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -61771,8 +62096,11 @@
       <c r="FD55" s="15">
         <v>9</v>
       </c>
+      <c r="FE55" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="56" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -62250,8 +62578,11 @@
       <c r="FD56" s="15">
         <v>0</v>
       </c>
+      <c r="FE56" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -62729,8 +63060,11 @@
       <c r="FD57" s="15">
         <v>1</v>
       </c>
+      <c r="FE57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="2:160" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
         <v>140</v>
@@ -63362,12 +63696,17 @@
         <f t="shared" si="11"/>
         <v>3075</v>
       </c>
+      <c r="FE58" s="14">
+        <f t="shared" ref="FE58" si="12">SUM(FE6:FE57)</f>
+        <v>2946</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="175">
+    <mergeCell ref="FE4:FE5"/>
+    <mergeCell ref="DD2:FE2"/>
+    <mergeCell ref="ER3:FE3"/>
     <mergeCell ref="FD4:FD5"/>
-    <mergeCell ref="DD2:FD2"/>
-    <mergeCell ref="ER3:FD3"/>
     <mergeCell ref="FC4:FC5"/>
     <mergeCell ref="FB4:FB5"/>
     <mergeCell ref="CR3:DC3"/>
@@ -63388,7 +63727,6 @@
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CI4:CI5"/>
     <mergeCell ref="DA4:DA5"/>
-    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BZ4:BZ5"/>
     <mergeCell ref="CA4:CA5"/>
@@ -63506,6 +63844,7 @@
     <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="EY4:EY5"/>
     <mergeCell ref="EZ4:EZ5"/>
     <mergeCell ref="EG4:EG5"/>
@@ -63542,43 +63881,48 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="21" priority="12">
+    <cfRule type="containsBlanks" dxfId="17" priority="13">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="20" priority="11">
+    <cfRule type="containsBlanks" dxfId="16" priority="12">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EH6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="19" priority="13">
+    <cfRule type="containsBlanks" dxfId="15" priority="14">
       <formula>LEN(TRIM(EH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="18" priority="5">
+    <cfRule type="containsBlanks" dxfId="14" priority="6">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="17" priority="4">
+    <cfRule type="containsBlanks" dxfId="13" priority="5">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="16" priority="3">
+    <cfRule type="containsBlanks" dxfId="12" priority="4">
       <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FC6:FC57">
-    <cfRule type="containsBlanks" dxfId="15" priority="2">
+    <cfRule type="containsBlanks" dxfId="11" priority="3">
       <formula>LEN(TRIM(FC6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FD6:FD57">
-    <cfRule type="containsBlanks" dxfId="14" priority="1">
+    <cfRule type="containsBlanks" dxfId="10" priority="2">
       <formula>LEN(TRIM(FD6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FE6:FE57">
+    <cfRule type="containsBlanks" dxfId="9" priority="1">
+      <formula>LEN(TRIM(FE6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -63594,7 +63938,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="10" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
+          <x14:cfRule type="containsBlanks" priority="11" id="{9841EE6F-D4E1-4BA5-8210-FC069633BFF3}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!DP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -63617,7 +63961,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DD61"/>
+  <dimension ref="A1:DE61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -63628,11 +63972,11 @@
     <col min="34" max="34" width="11" style="1" customWidth="1"/>
     <col min="35" max="48" width="10.875" style="1" customWidth="1"/>
     <col min="49" max="53" width="11.125" style="1" customWidth="1"/>
-    <col min="54" max="108" width="10.875" style="1" customWidth="1"/>
-    <col min="109" max="16384" width="8.625" style="1"/>
+    <col min="54" max="109" width="10.875" style="1" customWidth="1"/>
+    <col min="110" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:108" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:109" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -63715,66 +64059,67 @@
       <c r="DA1" s="19"/>
       <c r="DB1" s="19"/>
       <c r="DC1" s="19"/>
-      <c r="DD1" s="19" t="s">
+      <c r="DD1" s="19"/>
+      <c r="DE1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:108" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:109" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="51"/>
+      <c r="BA2" s="51"/>
+      <c r="BB2" s="51"/>
       <c r="BC2" s="85"/>
       <c r="BD2" s="72" t="s">
         <v>324</v>
@@ -63831,8 +64176,9 @@
       <c r="DB2" s="72"/>
       <c r="DC2" s="72"/>
       <c r="DD2" s="72"/>
+      <c r="DE2" s="72"/>
     </row>
-    <row r="3" spans="1:108" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:109" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
       <c r="D3" s="87" t="s">
@@ -63877,239 +64223,240 @@
       <c r="AO3" s="87"/>
       <c r="AP3" s="87"/>
       <c r="AQ3" s="87"/>
-      <c r="AR3" s="47" t="s">
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="47"/>
-      <c r="AT3" s="47"/>
-      <c r="AU3" s="47"/>
-      <c r="AV3" s="47"/>
-      <c r="AW3" s="47"/>
-      <c r="AX3" s="47"/>
-      <c r="AY3" s="47"/>
-      <c r="AZ3" s="47"/>
-      <c r="BA3" s="47"/>
-      <c r="BB3" s="47"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="47" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="47"/>
-      <c r="BI3" s="47"/>
-      <c r="BJ3" s="47"/>
-      <c r="BK3" s="47"/>
-      <c r="BL3" s="47"/>
-      <c r="BM3" s="47"/>
-      <c r="BN3" s="47"/>
-      <c r="BO3" s="47"/>
-      <c r="BP3" s="47"/>
-      <c r="BQ3" s="47"/>
-      <c r="BR3" s="47"/>
-      <c r="BS3" s="47"/>
-      <c r="BT3" s="47"/>
-      <c r="BU3" s="47"/>
-      <c r="BV3" s="47"/>
-      <c r="BW3" s="47"/>
-      <c r="BX3" s="47"/>
-      <c r="BY3" s="47"/>
-      <c r="BZ3" s="47"/>
-      <c r="CA3" s="47"/>
-      <c r="CB3" s="47"/>
-      <c r="CC3" s="47"/>
-      <c r="CD3" s="47"/>
-      <c r="CE3" s="47"/>
-      <c r="CF3" s="47"/>
-      <c r="CG3" s="47"/>
-      <c r="CH3" s="47"/>
-      <c r="CI3" s="47"/>
-      <c r="CJ3" s="47"/>
-      <c r="CK3" s="47"/>
-      <c r="CL3" s="47"/>
-      <c r="CM3" s="47"/>
-      <c r="CN3" s="47"/>
-      <c r="CO3" s="47"/>
-      <c r="CP3" s="47"/>
-      <c r="CQ3" s="47"/>
-      <c r="CR3" s="47" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="47"/>
-      <c r="CT3" s="47"/>
-      <c r="CU3" s="47"/>
-      <c r="CV3" s="47"/>
-      <c r="CW3" s="47"/>
-      <c r="CX3" s="47"/>
-      <c r="CY3" s="47"/>
-      <c r="CZ3" s="47"/>
-      <c r="DA3" s="47"/>
-      <c r="DB3" s="47"/>
-      <c r="DC3" s="47"/>
-      <c r="DD3" s="47"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="45"/>
+      <c r="DE3" s="45"/>
     </row>
-    <row r="4" spans="1:108" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:109" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="64" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="48" t="s">
+      <c r="T4" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="48" t="s">
+      <c r="U4" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="48" t="s">
+      <c r="W4" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="48" t="s">
+      <c r="X4" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="48" t="s">
+      <c r="Z4" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="48" t="s">
+      <c r="AA4" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="48" t="s">
+      <c r="AC4" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="48" t="s">
+      <c r="AD4" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="46" t="s">
+      <c r="AE4" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="46" t="s">
+      <c r="AF4" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="46" t="s">
+      <c r="AG4" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="46" t="s">
+      <c r="AH4" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="46" t="s">
+      <c r="AI4" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="46" t="s">
+      <c r="AJ4" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="46" t="s">
+      <c r="AK4" s="48" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="46" t="s">
+      <c r="AL4" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="46" t="s">
+      <c r="AM4" s="48" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="46" t="s">
+      <c r="AN4" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="46" t="s">
+      <c r="AO4" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="46" t="s">
+      <c r="AP4" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="46" t="s">
+      <c r="AQ4" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="46" t="s">
+      <c r="AR4" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="46" t="s">
+      <c r="AS4" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="46" t="s">
+      <c r="AT4" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="46" t="s">
+      <c r="AU4" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="46" t="s">
+      <c r="AV4" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="46" t="s">
+      <c r="AW4" s="48" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="46" t="s">
+      <c r="AX4" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="46" t="s">
+      <c r="AY4" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="46" t="s">
+      <c r="AZ4" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="46" t="s">
+      <c r="BA4" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="46" t="s">
+      <c r="BB4" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="46" t="s">
+      <c r="BC4" s="48" t="s">
         <v>303</v>
       </c>
       <c r="BD4" s="44" t="s">
@@ -64271,84 +64618,87 @@
       <c r="DD4" s="44" t="s">
         <v>440</v>
       </c>
+      <c r="DE4" s="44" t="s">
+        <v>443</v>
+      </c>
     </row>
-    <row r="5" spans="1:108" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:109" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="65"/>
       <c r="C5" s="71"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="49"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="49"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="45"/>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="45"/>
-      <c r="AS5" s="45"/>
-      <c r="AT5" s="45"/>
-      <c r="AU5" s="45"/>
-      <c r="AV5" s="45"/>
-      <c r="AW5" s="45"/>
-      <c r="AX5" s="45"/>
-      <c r="AY5" s="45"/>
-      <c r="AZ5" s="45"/>
-      <c r="BA5" s="45"/>
-      <c r="BB5" s="45"/>
-      <c r="BC5" s="45"/>
-      <c r="BD5" s="45"/>
-      <c r="BE5" s="45"/>
-      <c r="BF5" s="45"/>
-      <c r="BG5" s="45"/>
-      <c r="BH5" s="45"/>
-      <c r="BI5" s="45"/>
-      <c r="BJ5" s="45"/>
-      <c r="BK5" s="45"/>
-      <c r="BL5" s="45"/>
-      <c r="BM5" s="45"/>
-      <c r="BN5" s="45"/>
-      <c r="BO5" s="45"/>
-      <c r="BP5" s="45"/>
-      <c r="BQ5" s="45"/>
-      <c r="BR5" s="45"/>
-      <c r="BS5" s="45"/>
-      <c r="BT5" s="45"/>
-      <c r="BU5" s="45"/>
-      <c r="BV5" s="45"/>
-      <c r="BW5" s="45"/>
-      <c r="BX5" s="45"/>
-      <c r="BY5" s="45"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="46"/>
+      <c r="BM5" s="46"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
+      <c r="BQ5" s="46"/>
+      <c r="BR5" s="46"/>
+      <c r="BS5" s="46"/>
+      <c r="BT5" s="46"/>
+      <c r="BU5" s="46"/>
+      <c r="BV5" s="46"/>
+      <c r="BW5" s="46"/>
+      <c r="BX5" s="46"/>
+      <c r="BY5" s="46"/>
       <c r="BZ5" s="44"/>
       <c r="CA5" s="44"/>
       <c r="CB5" s="44"/>
@@ -64380,8 +64730,9 @@
       <c r="DB5" s="44"/>
       <c r="DC5" s="44"/>
       <c r="DD5" s="44"/>
+      <c r="DE5" s="44"/>
     </row>
-    <row r="6" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -64704,8 +65055,11 @@
       <c r="DD6" s="28">
         <v>19</v>
       </c>
+      <c r="DE6" s="28">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -65027,8 +65381,11 @@
       <c r="DD7" s="15">
         <v>0</v>
       </c>
+      <c r="DE7" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -65350,8 +65707,11 @@
       <c r="DD8" s="28">
         <v>0</v>
       </c>
+      <c r="DE8" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -65674,8 +66034,11 @@
       <c r="DD9" s="28">
         <v>8</v>
       </c>
+      <c r="DE9" s="28">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -65997,8 +66360,11 @@
       <c r="DD10" s="28">
         <v>0</v>
       </c>
+      <c r="DE10" s="28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -66320,8 +66686,11 @@
       <c r="DD11" s="28">
         <v>8</v>
       </c>
+      <c r="DE11" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -66643,8 +67012,11 @@
       <c r="DD12" s="15">
         <v>0</v>
       </c>
+      <c r="DE12" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -66966,8 +67338,11 @@
       <c r="DD13" s="15">
         <v>10</v>
       </c>
+      <c r="DE13" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="14" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -67289,8 +67664,11 @@
       <c r="DD14" s="15">
         <v>5</v>
       </c>
+      <c r="DE14" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -67612,8 +67990,11 @@
       <c r="DD15" s="15">
         <v>0</v>
       </c>
+      <c r="DE15" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -67936,8 +68317,11 @@
       <c r="DD16" s="28">
         <v>0</v>
       </c>
+      <c r="DE16" s="28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -68259,8 +68643,11 @@
       <c r="DD17" s="15">
         <v>25</v>
       </c>
+      <c r="DE17" s="15">
+        <v>25</v>
+      </c>
     </row>
-    <row r="18" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -68583,8 +68970,11 @@
       <c r="DD18" s="34">
         <v>201</v>
       </c>
+      <c r="DE18" s="34">
+        <v>196</v>
+      </c>
     </row>
-    <row r="19" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="78" t="s">
         <v>27</v>
@@ -68907,8 +69297,11 @@
       <c r="DD19" s="15">
         <v>15</v>
       </c>
+      <c r="DE19" s="15">
+        <v>12</v>
+      </c>
     </row>
-    <row r="20" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
@@ -69229,8 +69622,11 @@
       <c r="DD20" s="28">
         <v>26</v>
       </c>
+      <c r="DE20" s="28">
+        <v>20</v>
+      </c>
     </row>
-    <row r="21" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
@@ -69551,8 +69947,11 @@
       <c r="DD21" s="15">
         <v>9</v>
       </c>
+      <c r="DE21" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -69874,8 +70273,11 @@
       <c r="DD22" s="15">
         <v>0</v>
       </c>
+      <c r="DE22" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -70197,8 +70599,11 @@
       <c r="DD23" s="15">
         <v>0</v>
       </c>
+      <c r="DE23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -70520,8 +70925,11 @@
       <c r="DD24" s="15">
         <v>0</v>
       </c>
+      <c r="DE24" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -70843,8 +71251,11 @@
       <c r="DD25" s="15">
         <v>1</v>
       </c>
+      <c r="DE25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -71166,8 +71577,11 @@
       <c r="DD26" s="15">
         <v>3</v>
       </c>
+      <c r="DE26" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -71489,8 +71903,11 @@
       <c r="DD27" s="15">
         <v>0</v>
       </c>
+      <c r="DE27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -71812,8 +72229,11 @@
       <c r="DD28" s="15">
         <v>0</v>
       </c>
+      <c r="DE28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -72135,8 +72555,11 @@
       <c r="DD29" s="15">
         <v>0</v>
       </c>
+      <c r="DE29" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -72456,8 +72879,11 @@
       <c r="DD30" s="15">
         <v>3</v>
       </c>
+      <c r="DE30" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -72780,8 +73206,11 @@
       <c r="DD31" s="15">
         <v>11</v>
       </c>
+      <c r="DE31" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -73103,8 +73532,11 @@
       <c r="DD32" s="15">
         <v>0</v>
       </c>
+      <c r="DE32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -73426,8 +73858,11 @@
       <c r="DD33" s="15">
         <v>0</v>
       </c>
+      <c r="DE33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -73750,8 +74185,11 @@
       <c r="DD34" s="15">
         <v>6</v>
       </c>
+      <c r="DE34" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="35" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="78" t="s">
         <v>56</v>
@@ -74074,8 +74512,11 @@
       <c r="DD35" s="15">
         <v>53</v>
       </c>
+      <c r="DE35" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="36" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -74395,8 +74836,11 @@
       <c r="DD36" s="28">
         <v>4</v>
       </c>
+      <c r="DE36" s="28">
+        <v>11</v>
+      </c>
     </row>
-    <row r="37" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -74719,8 +75163,11 @@
       <c r="DD37" s="15">
         <v>15</v>
       </c>
+      <c r="DE37" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="38" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -75042,8 +75489,11 @@
       <c r="DD38" s="15">
         <v>2</v>
       </c>
+      <c r="DE38" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -75365,8 +75815,11 @@
       <c r="DD39" s="15">
         <v>1</v>
       </c>
+      <c r="DE39" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -75688,8 +76141,11 @@
       <c r="DD40" s="15">
         <v>0</v>
       </c>
+      <c r="DE40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -76011,8 +76467,11 @@
       <c r="DD41" s="15">
         <v>0</v>
       </c>
+      <c r="DE41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -76334,8 +76793,11 @@
       <c r="DD42" s="15">
         <v>1</v>
       </c>
+      <c r="DE42" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -76657,8 +77119,11 @@
       <c r="DD43" s="28">
         <v>16</v>
       </c>
+      <c r="DE43" s="28">
+        <v>18</v>
+      </c>
     </row>
-    <row r="44" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -76980,8 +77445,11 @@
       <c r="DD44" s="15">
         <v>1</v>
       </c>
+      <c r="DE44" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -77303,8 +77771,11 @@
       <c r="DD45" s="15">
         <v>8</v>
       </c>
+      <c r="DE45" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -77626,8 +78097,11 @@
       <c r="DD46" s="15">
         <v>4</v>
       </c>
+      <c r="DE46" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -77949,8 +78423,11 @@
       <c r="DD47" s="15">
         <v>0</v>
       </c>
+      <c r="DE47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -78272,8 +78749,11 @@
       <c r="DD48" s="15">
         <v>6</v>
       </c>
+      <c r="DE48" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="78" t="s">
         <v>83</v>
@@ -78596,8 +79076,11 @@
       <c r="DD49" s="15">
         <v>2</v>
       </c>
+      <c r="DE49" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:108" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:109" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -78917,8 +79400,11 @@
       <c r="DD50" s="15">
         <v>4</v>
       </c>
+      <c r="DE50" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -79240,8 +79726,11 @@
       <c r="DD51" s="15">
         <v>0</v>
       </c>
+      <c r="DE51" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -79563,8 +80052,11 @@
       <c r="DD52" s="15">
         <v>3</v>
       </c>
+      <c r="DE52" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -79886,8 +80378,11 @@
       <c r="DD53" s="15">
         <v>12</v>
       </c>
+      <c r="DE53" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -80209,8 +80704,11 @@
       <c r="DD54" s="15">
         <v>4</v>
       </c>
+      <c r="DE54" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -80532,8 +81030,11 @@
       <c r="DD55" s="15">
         <v>0</v>
       </c>
+      <c r="DE55" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -80855,8 +81356,11 @@
       <c r="DD56" s="15">
         <v>0</v>
       </c>
+      <c r="DE56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -81178,8 +81682,11 @@
       <c r="DD57" s="15">
         <v>0</v>
       </c>
+      <c r="DE57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -81601,11 +82108,15 @@
         <v>538</v>
       </c>
       <c r="DD58" s="14">
-        <f t="shared" ref="DD58" si="11">SUM(DD6:DD57)</f>
+        <f t="shared" ref="DD58:DE58" si="11">SUM(DD6:DD57)</f>
         <v>486</v>
       </c>
+      <c r="DE58" s="14">
+        <f t="shared" si="11"/>
+        <v>431</v>
+      </c>
     </row>
-    <row r="59" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -81638,7 +82149,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -81671,7 +82182,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:108" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:109" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -81705,10 +82216,11 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="119">
+    <mergeCell ref="DE4:DE5"/>
+    <mergeCell ref="BD2:DE2"/>
+    <mergeCell ref="CR3:DE3"/>
     <mergeCell ref="DD4:DD5"/>
-    <mergeCell ref="BD2:DD2"/>
-    <mergeCell ref="CR3:DD3"/>
     <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="DA4:DA5"/>
@@ -81827,12 +82339,12 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="CH6:CX57 CZ6:CZ57 DA10">
-    <cfRule type="containsBlanks" dxfId="12" priority="9">
+    <cfRule type="containsBlanks" dxfId="7" priority="10">
       <formula>LEN(TRIM(CH6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY6:CY57">
-    <cfRule type="containsBlanks" dxfId="11" priority="7">
+    <cfRule type="containsBlanks" dxfId="6" priority="8">
       <formula>LEN(TRIM(CY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -81847,7 +82359,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="10" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="11" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81857,10 +82369,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
+          <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57 DB6:DE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="20" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
+          <x14:cfRule type="containsBlanks" priority="21" id="{5602503B-0E77-43D2-A987-5DC3B78222DE}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -81871,45 +82383,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="4" id="{1C01E9CA-62F3-4D9D-8B62-2B20CFCD9EA2}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>DB6:DB57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="2" id="{DFAC2C1F-0AE8-46F8-BC08-A989DBFF9333}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>DC6:DC57 DD56</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="1" id="{1D86A354-19E7-4BAA-A9D3-CC06A45CD35E}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DD6))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>DD6:DD55 DD57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -81922,7 +82395,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DF61"/>
+  <dimension ref="A1:DG61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -81931,11 +82404,11 @@
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="31" width="10.875" style="1" customWidth="1"/>
     <col min="32" max="33" width="11.125" style="1" customWidth="1"/>
-    <col min="34" max="110" width="10.875" style="1" customWidth="1"/>
-    <col min="111" max="16384" width="8.625" style="1"/>
+    <col min="34" max="111" width="10.875" style="1" customWidth="1"/>
+    <col min="112" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:111" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D1" s="19"/>
       <c r="AC1" s="19"/>
       <c r="AD1" s="19"/>
@@ -82018,66 +82491,67 @@
       <c r="DA1" s="19"/>
       <c r="DB1" s="19"/>
       <c r="DC1" s="19"/>
-      <c r="DD1" s="19" t="s">
+      <c r="DD1" s="19"/>
+      <c r="DE1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="33" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:111" ht="33" x14ac:dyDescent="0.4">
       <c r="B2" s="58"/>
       <c r="C2" s="59"/>
       <c r="D2" s="73" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="51"/>
+      <c r="BA2" s="51"/>
+      <c r="BB2" s="51"/>
       <c r="BC2" s="85"/>
       <c r="BD2" s="72" t="s">
         <v>325</v>
@@ -82134,10 +82608,11 @@
       <c r="DB2" s="72"/>
       <c r="DC2" s="72"/>
       <c r="DD2" s="72"/>
-      <c r="DE2" s="20"/>
+      <c r="DE2" s="72"/>
       <c r="DF2" s="20"/>
+      <c r="DG2" s="20"/>
     </row>
-    <row r="3" spans="1:110" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:111" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="60"/>
       <c r="C3" s="61"/>
       <c r="D3" s="87" t="s">
@@ -82182,241 +82657,242 @@
       <c r="AO3" s="87"/>
       <c r="AP3" s="87"/>
       <c r="AQ3" s="87"/>
-      <c r="AR3" s="47" t="s">
+      <c r="AR3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="AS3" s="47"/>
-      <c r="AT3" s="47"/>
-      <c r="AU3" s="47"/>
-      <c r="AV3" s="47"/>
-      <c r="AW3" s="47"/>
-      <c r="AX3" s="47"/>
-      <c r="AY3" s="47"/>
-      <c r="AZ3" s="47"/>
-      <c r="BA3" s="47"/>
-      <c r="BB3" s="47"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="47" t="s">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="47"/>
-      <c r="BI3" s="47"/>
-      <c r="BJ3" s="47"/>
-      <c r="BK3" s="47"/>
-      <c r="BL3" s="47"/>
-      <c r="BM3" s="47"/>
-      <c r="BN3" s="47"/>
-      <c r="BO3" s="47"/>
-      <c r="BP3" s="47"/>
-      <c r="BQ3" s="47"/>
-      <c r="BR3" s="47"/>
-      <c r="BS3" s="47"/>
-      <c r="BT3" s="47"/>
-      <c r="BU3" s="47"/>
-      <c r="BV3" s="47"/>
-      <c r="BW3" s="47"/>
-      <c r="BX3" s="47"/>
-      <c r="BY3" s="47"/>
-      <c r="BZ3" s="47"/>
-      <c r="CA3" s="47"/>
-      <c r="CB3" s="47"/>
-      <c r="CC3" s="47"/>
-      <c r="CD3" s="47"/>
-      <c r="CE3" s="47"/>
-      <c r="CF3" s="47"/>
-      <c r="CG3" s="47"/>
-      <c r="CH3" s="47"/>
-      <c r="CI3" s="47"/>
-      <c r="CJ3" s="47"/>
-      <c r="CK3" s="47"/>
-      <c r="CL3" s="47"/>
-      <c r="CM3" s="47"/>
-      <c r="CN3" s="47"/>
-      <c r="CO3" s="47"/>
-      <c r="CP3" s="47"/>
-      <c r="CQ3" s="47"/>
-      <c r="CR3" s="47" t="s">
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="45"/>
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="45"/>
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="45"/>
+      <c r="CC3" s="45"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="45"/>
+      <c r="CF3" s="45"/>
+      <c r="CG3" s="45"/>
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="45"/>
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="45"/>
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="45"/>
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="45"/>
+      <c r="CP3" s="45"/>
+      <c r="CQ3" s="45"/>
+      <c r="CR3" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="CS3" s="47"/>
-      <c r="CT3" s="47"/>
-      <c r="CU3" s="47"/>
-      <c r="CV3" s="47"/>
-      <c r="CW3" s="47"/>
-      <c r="CX3" s="47"/>
-      <c r="CY3" s="47"/>
-      <c r="CZ3" s="47"/>
-      <c r="DA3" s="47"/>
-      <c r="DB3" s="47"/>
-      <c r="DC3" s="47"/>
-      <c r="DD3" s="47"/>
-      <c r="DE3" s="21"/>
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="45"/>
+      <c r="CU3" s="45"/>
+      <c r="CV3" s="45"/>
+      <c r="CW3" s="45"/>
+      <c r="CX3" s="45"/>
+      <c r="CY3" s="45"/>
+      <c r="CZ3" s="45"/>
+      <c r="DA3" s="45"/>
+      <c r="DB3" s="45"/>
+      <c r="DC3" s="45"/>
+      <c r="DD3" s="45"/>
+      <c r="DE3" s="45"/>
       <c r="DF3" s="21"/>
+      <c r="DG3" s="21"/>
     </row>
-    <row r="4" spans="1:110" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:111" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="64" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="48" t="s">
+      <c r="T4" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="U4" s="48" t="s">
+      <c r="U4" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="W4" s="48" t="s">
+      <c r="W4" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="X4" s="48" t="s">
+      <c r="X4" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="Z4" s="48" t="s">
+      <c r="Z4" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="48" t="s">
+      <c r="AA4" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="AC4" s="48" t="s">
+      <c r="AC4" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="AD4" s="48" t="s">
+      <c r="AD4" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="AE4" s="46" t="s">
+      <c r="AE4" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="AF4" s="46" t="s">
+      <c r="AF4" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="AG4" s="46" t="s">
+      <c r="AG4" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="AH4" s="46" t="s">
+      <c r="AH4" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="AI4" s="46" t="s">
+      <c r="AI4" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="AJ4" s="46" t="s">
+      <c r="AJ4" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="AK4" s="46" t="s">
+      <c r="AK4" s="48" t="s">
         <v>264</v>
       </c>
-      <c r="AL4" s="46" t="s">
+      <c r="AL4" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="AM4" s="46" t="s">
+      <c r="AM4" s="48" t="s">
         <v>268</v>
       </c>
-      <c r="AN4" s="46" t="s">
+      <c r="AN4" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="AO4" s="46" t="s">
+      <c r="AO4" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="AP4" s="46" t="s">
+      <c r="AP4" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="AQ4" s="46" t="s">
+      <c r="AQ4" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="AR4" s="46" t="s">
+      <c r="AR4" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="AS4" s="46" t="s">
+      <c r="AS4" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="AT4" s="46" t="s">
+      <c r="AT4" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="AU4" s="46" t="s">
+      <c r="AU4" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="AV4" s="46" t="s">
+      <c r="AV4" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="AW4" s="46" t="s">
+      <c r="AW4" s="48" t="s">
         <v>292</v>
       </c>
-      <c r="AX4" s="46" t="s">
+      <c r="AX4" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="AY4" s="46" t="s">
+      <c r="AY4" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="AZ4" s="46" t="s">
+      <c r="AZ4" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="BA4" s="46" t="s">
+      <c r="BA4" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="BB4" s="46" t="s">
+      <c r="BB4" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="BC4" s="46" t="s">
+      <c r="BC4" s="48" t="s">
         <v>303</v>
       </c>
       <c r="BD4" s="44" t="s">
@@ -82578,77 +83054,80 @@
       <c r="DD4" s="44" t="s">
         <v>440</v>
       </c>
-      <c r="DE4" s="88"/>
+      <c r="DE4" s="44" t="s">
+        <v>441</v>
+      </c>
       <c r="DF4" s="88"/>
+      <c r="DG4" s="88"/>
     </row>
-    <row r="5" spans="1:110" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:111" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="65"/>
       <c r="C5" s="71"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="49"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="49"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="45"/>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="45"/>
-      <c r="AS5" s="45"/>
-      <c r="AT5" s="45"/>
-      <c r="AU5" s="45"/>
-      <c r="AV5" s="45"/>
-      <c r="AW5" s="45"/>
-      <c r="AX5" s="45"/>
-      <c r="AY5" s="45"/>
-      <c r="AZ5" s="45"/>
-      <c r="BA5" s="45"/>
-      <c r="BB5" s="45"/>
-      <c r="BC5" s="45"/>
-      <c r="BD5" s="45"/>
-      <c r="BE5" s="45"/>
-      <c r="BF5" s="45"/>
-      <c r="BG5" s="45"/>
-      <c r="BH5" s="45"/>
-      <c r="BI5" s="45"/>
-      <c r="BJ5" s="45"/>
-      <c r="BK5" s="45"/>
-      <c r="BL5" s="45"/>
-      <c r="BM5" s="45"/>
-      <c r="BN5" s="45"/>
-      <c r="BO5" s="45"/>
-      <c r="BP5" s="45"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+      <c r="BH5" s="46"/>
+      <c r="BI5" s="46"/>
+      <c r="BJ5" s="46"/>
+      <c r="BK5" s="46"/>
+      <c r="BL5" s="46"/>
+      <c r="BM5" s="46"/>
+      <c r="BN5" s="46"/>
+      <c r="BO5" s="46"/>
+      <c r="BP5" s="46"/>
       <c r="BQ5" s="44"/>
       <c r="BR5" s="44"/>
       <c r="BS5" s="44"/>
@@ -82689,10 +83168,11 @@
       <c r="DB5" s="44"/>
       <c r="DC5" s="44"/>
       <c r="DD5" s="44"/>
-      <c r="DE5" s="88"/>
+      <c r="DE5" s="44"/>
       <c r="DF5" s="88"/>
+      <c r="DG5" s="88"/>
     </row>
-    <row r="6" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -83015,10 +83495,13 @@
       <c r="DD6" s="28">
         <v>62</v>
       </c>
-      <c r="DE6" s="22"/>
+      <c r="DE6" s="28">
+        <v>62</v>
+      </c>
       <c r="DF6" s="22"/>
+      <c r="DG6" s="22"/>
     </row>
-    <row r="7" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -83340,10 +83823,13 @@
       <c r="DD7" s="15">
         <v>0</v>
       </c>
-      <c r="DE7" s="23"/>
+      <c r="DE7" s="15">
+        <v>1</v>
+      </c>
       <c r="DF7" s="23"/>
+      <c r="DG7" s="23"/>
     </row>
-    <row r="8" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -83665,10 +84151,13 @@
       <c r="DD8" s="28">
         <v>14</v>
       </c>
-      <c r="DE8" s="23"/>
+      <c r="DE8" s="28">
+        <v>7</v>
+      </c>
       <c r="DF8" s="23"/>
+      <c r="DG8" s="23"/>
     </row>
-    <row r="9" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -83991,10 +84480,13 @@
       <c r="DD9" s="28">
         <v>71</v>
       </c>
-      <c r="DE9" s="23"/>
+      <c r="DE9" s="28">
+        <v>54</v>
+      </c>
       <c r="DF9" s="23"/>
+      <c r="DG9" s="23"/>
     </row>
-    <row r="10" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -84316,10 +84808,13 @@
       <c r="DD10" s="28">
         <v>0</v>
       </c>
-      <c r="DE10" s="23"/>
+      <c r="DE10" s="28">
+        <v>0</v>
+      </c>
       <c r="DF10" s="23"/>
+      <c r="DG10" s="23"/>
     </row>
-    <row r="11" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -84641,10 +85136,13 @@
       <c r="DD11" s="28">
         <v>9</v>
       </c>
-      <c r="DE11" s="23"/>
+      <c r="DE11" s="28">
+        <v>7</v>
+      </c>
       <c r="DF11" s="23"/>
+      <c r="DG11" s="23"/>
     </row>
-    <row r="12" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -84966,10 +85464,13 @@
       <c r="DD12" s="15">
         <v>3</v>
       </c>
-      <c r="DE12" s="23"/>
+      <c r="DE12" s="15">
+        <v>3</v>
+      </c>
       <c r="DF12" s="23"/>
+      <c r="DG12" s="23"/>
     </row>
-    <row r="13" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -85291,10 +85792,13 @@
       <c r="DD13" s="15">
         <v>15</v>
       </c>
-      <c r="DE13" s="22"/>
+      <c r="DE13" s="15">
+        <v>17</v>
+      </c>
       <c r="DF13" s="22"/>
+      <c r="DG13" s="22"/>
     </row>
-    <row r="14" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -85616,10 +86120,13 @@
       <c r="DD14" s="15">
         <v>15</v>
       </c>
-      <c r="DE14" s="23"/>
+      <c r="DE14" s="15">
+        <v>12</v>
+      </c>
       <c r="DF14" s="23"/>
+      <c r="DG14" s="23"/>
     </row>
-    <row r="15" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -85941,10 +86448,13 @@
       <c r="DD15" s="15">
         <v>1</v>
       </c>
-      <c r="DE15" s="23"/>
+      <c r="DE15" s="15">
+        <v>0</v>
+      </c>
       <c r="DF15" s="23"/>
+      <c r="DG15" s="23"/>
     </row>
-    <row r="16" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -86267,10 +86777,13 @@
       <c r="DD16" s="28">
         <v>104</v>
       </c>
-      <c r="DE16" s="22"/>
+      <c r="DE16" s="28">
+        <v>102</v>
+      </c>
       <c r="DF16" s="22"/>
+      <c r="DG16" s="22"/>
     </row>
-    <row r="17" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -86592,10 +87105,13 @@
       <c r="DD17" s="15">
         <v>96</v>
       </c>
-      <c r="DE17" s="22"/>
+      <c r="DE17" s="15">
+        <v>103</v>
+      </c>
       <c r="DF17" s="22"/>
+      <c r="DG17" s="22"/>
     </row>
-    <row r="18" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -86918,10 +87434,13 @@
       <c r="DD18" s="34">
         <v>1342</v>
       </c>
-      <c r="DE18" s="22"/>
+      <c r="DE18" s="34">
+        <v>1136</v>
+      </c>
       <c r="DF18" s="22"/>
+      <c r="DG18" s="22"/>
     </row>
-    <row r="19" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
       <c r="B19" s="78" t="s">
         <v>27</v>
@@ -87244,10 +87763,13 @@
       <c r="DD19" s="15">
         <v>34</v>
       </c>
-      <c r="DE19" s="22"/>
+      <c r="DE19" s="15">
+        <v>29</v>
+      </c>
       <c r="DF19" s="22"/>
+      <c r="DG19" s="22"/>
     </row>
-    <row r="20" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
       <c r="B20" s="82"/>
       <c r="C20" s="9" t="s">
@@ -87568,10 +88090,13 @@
       <c r="DD20" s="28">
         <v>76</v>
       </c>
-      <c r="DE20" s="22"/>
+      <c r="DE20" s="28">
+        <v>41</v>
+      </c>
       <c r="DF20" s="22"/>
+      <c r="DG20" s="22"/>
     </row>
-    <row r="21" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
       <c r="B21" s="79"/>
       <c r="C21" s="9" t="s">
@@ -87892,10 +88417,13 @@
       <c r="DD21" s="15">
         <v>19</v>
       </c>
-      <c r="DE21" s="22"/>
+      <c r="DE21" s="15">
+        <v>11</v>
+      </c>
       <c r="DF21" s="22"/>
+      <c r="DG21" s="22"/>
     </row>
-    <row r="22" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -88217,10 +88745,13 @@
       <c r="DD22" s="15">
         <v>2</v>
       </c>
-      <c r="DE22" s="23"/>
+      <c r="DE22" s="15">
+        <v>1</v>
+      </c>
       <c r="DF22" s="23"/>
+      <c r="DG22" s="23"/>
     </row>
-    <row r="23" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -88542,10 +89073,13 @@
       <c r="DD23" s="15">
         <v>0</v>
       </c>
-      <c r="DE23" s="23"/>
+      <c r="DE23" s="15">
+        <v>0</v>
+      </c>
       <c r="DF23" s="23"/>
+      <c r="DG23" s="23"/>
     </row>
-    <row r="24" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -88867,10 +89401,13 @@
       <c r="DD24" s="15">
         <v>8</v>
       </c>
-      <c r="DE24" s="22"/>
+      <c r="DE24" s="15">
+        <v>2</v>
+      </c>
       <c r="DF24" s="22"/>
+      <c r="DG24" s="22"/>
     </row>
-    <row r="25" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -89192,10 +89729,13 @@
       <c r="DD25" s="15">
         <v>0</v>
       </c>
-      <c r="DE25" s="23"/>
+      <c r="DE25" s="15">
+        <v>0</v>
+      </c>
       <c r="DF25" s="23"/>
+      <c r="DG25" s="23"/>
     </row>
-    <row r="26" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -89517,10 +90057,13 @@
       <c r="DD26" s="15">
         <v>7</v>
       </c>
-      <c r="DE26" s="23"/>
+      <c r="DE26" s="15">
+        <v>8</v>
+      </c>
       <c r="DF26" s="23"/>
+      <c r="DG26" s="23"/>
     </row>
-    <row r="27" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -89842,10 +90385,13 @@
       <c r="DD27" s="15">
         <v>0</v>
       </c>
-      <c r="DE27" s="23"/>
+      <c r="DE27" s="15">
+        <v>0</v>
+      </c>
       <c r="DF27" s="23"/>
+      <c r="DG27" s="23"/>
     </row>
-    <row r="28" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -90167,10 +90713,13 @@
       <c r="DD28" s="15">
         <v>2</v>
       </c>
-      <c r="DE28" s="22"/>
+      <c r="DE28" s="15">
+        <v>1</v>
+      </c>
       <c r="DF28" s="22"/>
+      <c r="DG28" s="22"/>
     </row>
-    <row r="29" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="83" t="s">
         <v>45</v>
       </c>
@@ -90492,10 +91041,13 @@
       <c r="DD29" s="15">
         <v>0</v>
       </c>
-      <c r="DE29" s="23"/>
+      <c r="DE29" s="15">
+        <v>1</v>
+      </c>
       <c r="DF29" s="23"/>
+      <c r="DG29" s="23"/>
     </row>
-    <row r="30" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="84"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
@@ -90815,10 +91367,13 @@
       <c r="DD30" s="15">
         <v>8</v>
       </c>
-      <c r="DE30" s="23"/>
+      <c r="DE30" s="15">
+        <v>11</v>
+      </c>
       <c r="DF30" s="23"/>
+      <c r="DG30" s="23"/>
     </row>
-    <row r="31" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -91141,10 +91696,13 @@
       <c r="DD31" s="15">
         <v>33</v>
       </c>
-      <c r="DE31" s="22"/>
+      <c r="DE31" s="15">
+        <v>29</v>
+      </c>
       <c r="DF31" s="22"/>
+      <c r="DG31" s="22"/>
     </row>
-    <row r="32" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -91466,10 +92024,13 @@
       <c r="DD32" s="15">
         <v>0</v>
       </c>
-      <c r="DE32" s="23"/>
+      <c r="DE32" s="15">
+        <v>0</v>
+      </c>
       <c r="DF32" s="23"/>
+      <c r="DG32" s="23"/>
     </row>
-    <row r="33" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -91791,10 +92352,13 @@
       <c r="DD33" s="15">
         <v>0</v>
       </c>
-      <c r="DE33" s="23"/>
+      <c r="DE33" s="15">
+        <v>0</v>
+      </c>
       <c r="DF33" s="23"/>
+      <c r="DG33" s="23"/>
     </row>
-    <row r="34" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -92117,10 +92681,13 @@
       <c r="DD34" s="15">
         <v>45</v>
       </c>
-      <c r="DE34" s="22"/>
+      <c r="DE34" s="15">
+        <v>38</v>
+      </c>
       <c r="DF34" s="22"/>
+      <c r="DG34" s="22"/>
     </row>
-    <row r="35" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
       <c r="B35" s="78" t="s">
         <v>56</v>
@@ -92443,10 +93010,13 @@
       <c r="DD35" s="15">
         <v>210</v>
       </c>
-      <c r="DE35" s="22"/>
+      <c r="DE35" s="15">
+        <v>201</v>
+      </c>
       <c r="DF35" s="22"/>
+      <c r="DG35" s="22"/>
     </row>
-    <row r="36" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="79"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
@@ -92766,10 +93336,13 @@
       <c r="DD36" s="28">
         <v>15</v>
       </c>
-      <c r="DE36" s="22"/>
+      <c r="DE36" s="28">
+        <v>10</v>
+      </c>
       <c r="DF36" s="22"/>
+      <c r="DG36" s="22"/>
     </row>
-    <row r="37" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -93092,10 +93665,13 @@
       <c r="DD37" s="15">
         <v>36</v>
       </c>
-      <c r="DE37" s="22"/>
+      <c r="DE37" s="15">
+        <v>23</v>
+      </c>
       <c r="DF37" s="22"/>
+      <c r="DG37" s="22"/>
     </row>
-    <row r="38" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -93417,10 +93993,13 @@
       <c r="DD38" s="15">
         <v>4</v>
       </c>
-      <c r="DE38" s="23"/>
+      <c r="DE38" s="15">
+        <v>4</v>
+      </c>
       <c r="DF38" s="23"/>
+      <c r="DG38" s="23"/>
     </row>
-    <row r="39" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -93742,10 +94321,13 @@
       <c r="DD39" s="15">
         <v>3</v>
       </c>
-      <c r="DE39" s="23"/>
+      <c r="DE39" s="15">
+        <v>3</v>
+      </c>
       <c r="DF39" s="23"/>
+      <c r="DG39" s="23"/>
     </row>
-    <row r="40" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -94067,10 +94649,13 @@
       <c r="DD40" s="15">
         <v>0</v>
       </c>
-      <c r="DE40" s="23"/>
+      <c r="DE40" s="15">
+        <v>0</v>
+      </c>
       <c r="DF40" s="23"/>
+      <c r="DG40" s="23"/>
     </row>
-    <row r="41" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -94392,10 +94977,13 @@
       <c r="DD41" s="15">
         <v>0</v>
       </c>
-      <c r="DE41" s="23"/>
+      <c r="DE41" s="15">
+        <v>0</v>
+      </c>
       <c r="DF41" s="23"/>
+      <c r="DG41" s="23"/>
     </row>
-    <row r="42" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -94717,10 +95305,13 @@
       <c r="DD42" s="15">
         <v>7</v>
       </c>
-      <c r="DE42" s="23"/>
+      <c r="DE42" s="15">
+        <v>4</v>
+      </c>
       <c r="DF42" s="23"/>
+      <c r="DG42" s="23"/>
     </row>
-    <row r="43" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -95042,10 +95633,13 @@
       <c r="DD43" s="28">
         <v>21</v>
       </c>
-      <c r="DE43" s="23"/>
+      <c r="DE43" s="28">
+        <v>30</v>
+      </c>
       <c r="DF43" s="23"/>
+      <c r="DG43" s="23"/>
     </row>
-    <row r="44" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -95367,10 +95961,13 @@
       <c r="DD44" s="15">
         <v>3</v>
       </c>
-      <c r="DE44" s="23"/>
+      <c r="DE44" s="15">
+        <v>0</v>
+      </c>
       <c r="DF44" s="23"/>
+      <c r="DG44" s="23"/>
     </row>
-    <row r="45" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -95692,10 +96289,13 @@
       <c r="DD45" s="15">
         <v>10</v>
       </c>
-      <c r="DE45" s="22"/>
+      <c r="DE45" s="15">
+        <v>12</v>
+      </c>
       <c r="DF45" s="22"/>
+      <c r="DG45" s="22"/>
     </row>
-    <row r="46" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -96017,10 +96617,13 @@
       <c r="DD46" s="15">
         <v>17</v>
       </c>
-      <c r="DE46" s="23"/>
+      <c r="DE46" s="15">
+        <v>20</v>
+      </c>
       <c r="DF46" s="23"/>
+      <c r="DG46" s="23"/>
     </row>
-    <row r="47" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -96342,10 +96945,13 @@
       <c r="DD47" s="15">
         <v>0</v>
       </c>
-      <c r="DE47" s="23"/>
+      <c r="DE47" s="15">
+        <v>2</v>
+      </c>
       <c r="DF47" s="23"/>
+      <c r="DG47" s="23"/>
     </row>
-    <row r="48" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -96667,10 +97273,13 @@
       <c r="DD48" s="15">
         <v>14</v>
       </c>
-      <c r="DE48" s="23"/>
+      <c r="DE48" s="15">
+        <v>4</v>
+      </c>
       <c r="DF48" s="23"/>
+      <c r="DG48" s="23"/>
     </row>
-    <row r="49" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
       <c r="B49" s="78" t="s">
         <v>83</v>
@@ -96993,10 +97602,13 @@
       <c r="DD49" s="15">
         <v>38</v>
       </c>
-      <c r="DE49" s="22"/>
+      <c r="DE49" s="15">
+        <v>23</v>
+      </c>
       <c r="DF49" s="22"/>
+      <c r="DG49" s="22"/>
     </row>
-    <row r="50" spans="1:110" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:111" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" s="79"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
@@ -97316,10 +97928,13 @@
       <c r="DD50" s="15">
         <v>7</v>
       </c>
-      <c r="DE50" s="22"/>
+      <c r="DE50" s="15">
+        <v>4</v>
+      </c>
       <c r="DF50" s="22"/>
+      <c r="DG50" s="22"/>
     </row>
-    <row r="51" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -97641,10 +98256,13 @@
       <c r="DD51" s="15">
         <v>8</v>
       </c>
-      <c r="DE51" s="23"/>
+      <c r="DE51" s="15">
+        <v>3</v>
+      </c>
       <c r="DF51" s="23"/>
+      <c r="DG51" s="23"/>
     </row>
-    <row r="52" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -97966,10 +98584,13 @@
       <c r="DD52" s="15">
         <v>10</v>
       </c>
-      <c r="DE52" s="23"/>
+      <c r="DE52" s="15">
+        <v>12</v>
+      </c>
       <c r="DF52" s="23"/>
+      <c r="DG52" s="23"/>
     </row>
-    <row r="53" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -98291,10 +98912,13 @@
       <c r="DD53" s="15">
         <v>25</v>
       </c>
-      <c r="DE53" s="23"/>
+      <c r="DE53" s="15">
+        <v>35</v>
+      </c>
       <c r="DF53" s="23"/>
+      <c r="DG53" s="23"/>
     </row>
-    <row r="54" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -98616,10 +99240,13 @@
       <c r="DD54" s="15">
         <v>2</v>
       </c>
-      <c r="DE54" s="23"/>
+      <c r="DE54" s="15">
+        <v>2</v>
+      </c>
       <c r="DF54" s="23"/>
+      <c r="DG54" s="23"/>
     </row>
-    <row r="55" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -98941,10 +99568,13 @@
       <c r="DD55" s="15">
         <v>16</v>
       </c>
-      <c r="DE55" s="23"/>
+      <c r="DE55" s="15">
+        <v>12</v>
+      </c>
       <c r="DF55" s="23"/>
+      <c r="DG55" s="23"/>
     </row>
-    <row r="56" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -99266,10 +99896,13 @@
       <c r="DD56" s="15">
         <v>1</v>
       </c>
-      <c r="DE56" s="23"/>
+      <c r="DE56" s="15">
+        <v>0</v>
+      </c>
       <c r="DF56" s="23"/>
+      <c r="DG56" s="23"/>
     </row>
-    <row r="57" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -99591,10 +100224,13 @@
       <c r="DD57" s="15">
         <v>2</v>
       </c>
-      <c r="DE57" s="23"/>
+      <c r="DE57" s="15">
+        <v>3</v>
+      </c>
       <c r="DF57" s="23"/>
+      <c r="DG57" s="23"/>
     </row>
-    <row r="58" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -100016,13 +100652,17 @@
         <v>2716</v>
       </c>
       <c r="DD58" s="14">
-        <f t="shared" ref="DD58" si="7">SUM(DD6:DD57)</f>
+        <f t="shared" ref="DD58:DE58" si="7">SUM(DD6:DD57)</f>
         <v>2415</v>
       </c>
-      <c r="DE58" s="24"/>
+      <c r="DE58" s="14">
+        <f t="shared" si="7"/>
+        <v>2083</v>
+      </c>
       <c r="DF58" s="24"/>
+      <c r="DG58" s="24"/>
     </row>
-    <row r="59" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -100055,7 +100695,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="7"/>
     </row>
-    <row r="60" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -100088,7 +100728,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
     </row>
-    <row r="61" spans="1:110" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:111" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -100122,33 +100762,50 @@
       <c r="AE61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="120">
-    <mergeCell ref="BD2:DD2"/>
-    <mergeCell ref="CR3:DD3"/>
+  <mergeCells count="121">
+    <mergeCell ref="DE4:DE5"/>
+    <mergeCell ref="BD2:DE2"/>
+    <mergeCell ref="CR3:DE3"/>
     <mergeCell ref="CX4:CX5"/>
     <mergeCell ref="CB4:CB5"/>
     <mergeCell ref="CA4:CA5"/>
     <mergeCell ref="CW4:CW5"/>
     <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="DG4:DG5"/>
+    <mergeCell ref="DD4:DD5"/>
     <mergeCell ref="DF4:DF5"/>
-    <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="BV4:BV5"/>
+    <mergeCell ref="BT4:BT5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="BR4:BR5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CT4:CT5"/>
     <mergeCell ref="DB4:DB5"/>
     <mergeCell ref="DC4:DC5"/>
     <mergeCell ref="AV4:AV5"/>
     <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="DD4:DD5"/>
     <mergeCell ref="BA4:BA5"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="DE4:DE5"/>
     <mergeCell ref="BP4:BP5"/>
     <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="CF4:CF5"/>
     <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CR4:CR5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AJ4:AJ5"/>
@@ -100173,11 +100830,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CE4:CE5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="CN4:CN5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -100197,23 +100849,11 @@
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="CY4:CY5"/>
-    <mergeCell ref="CZ4:CZ5"/>
     <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="CK4:CK5"/>
-    <mergeCell ref="BV4:BV5"/>
-    <mergeCell ref="BT4:BT5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="AL4:AL5"/>
+    <mergeCell ref="AK4:AK5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AQ4:AQ5"/>
     <mergeCell ref="CS4:CS5"/>
     <mergeCell ref="BD4:BD5"/>
     <mergeCell ref="BZ4:BZ5"/>
@@ -100224,10 +100864,14 @@
     <mergeCell ref="AR4:AR5"/>
     <mergeCell ref="BD3:CQ3"/>
     <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="BX4:BX5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="CP4:CP5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AZ4:AZ5"/>
     <mergeCell ref="AM4:AM5"/>
     <mergeCell ref="AO4:AO5"/>
     <mergeCell ref="AP4:AP5"/>
@@ -100240,9 +100884,6 @@
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="BG4:BG5"/>
     <mergeCell ref="BL4:BL5"/>
-    <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="CP4:CP5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.59055118110236215" right="0.23622047244094488" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -100256,7 +100897,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="10" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="11" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!BP6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -100266,10 +100907,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57</xm:sqref>
+          <xm:sqref>BP6:CX57 DA6:DA9 DA11:DA57 DB6:DD57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="29" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
+          <x14:cfRule type="containsBlanks" priority="30" id="{74832A3D-3E58-4A3A-9E33-9D86EFCB7C6E}">
             <xm:f>LEN(TRIM('搬送困難事案（今回）'!CX6))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -100282,7 +100923,7 @@
           <xm:sqref>CY6:CZ57 DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="6" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
+          <x14:cfRule type="containsBlanks" priority="7" id="{1456D4A3-D80F-41C3-B33C-BFC0F10DC75A}">
             <xm:f>LEN(TRIM('うちコロナ疑い事案（今回）'!DA10))=0</xm:f>
             <x14:dxf>
               <fill>
@@ -100295,8 +100936,8 @@
           <xm:sqref>DA10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="4" id="{6D1CE7AC-F00B-4F35-A0D7-60994E6A744B}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DB6))=0</xm:f>
+          <x14:cfRule type="containsBlanks" priority="1" id="{2995E26B-BE3B-4694-90F1-7C5CA5B067CB}">
+            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DE6))=0</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -100305,33 +100946,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>DB6:DB57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="2" id="{D5FC4B6E-10B3-44DA-A1D6-DEA44453D2A7}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DC6))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>DC6:DC57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="1" id="{1D4A68F6-7D4E-438E-9CA3-77DF5B1688C9}">
-            <xm:f>LEN(TRIM('搬送困難事案（今回）'!DD6))=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>DD6:DD57</xm:sqref>
+          <xm:sqref>DE6:DE57</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/emergencytransport_difficult.xlsx
+++ b/emergencytransport_difficult.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\W-119_消防庁HP更新\03_支給資材・原稿\JOB050411-1\ＪＯＢ050411-1\アップ用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.177.108.11\daichi$\採用（自宅勤務者専用）\01_ITサービス事業部\01_案件フォルダ\3_グループ外案件\5004_消防庁\W-119_消防庁HP更新\03_支給資材・原稿\JOB050418-1\ＪＯＢ050418-1\アップ用\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'うち非コロナ疑い事案（今回）'!$A$6:$AE$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'搬送困難事案（今回）'!$A$6:$CD$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'搬送困難事案（前年同期）'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DE$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DE$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FE$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FE$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'うちコロナ疑い事案（今回）'!$A$1:$DF$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A$1:$DF$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'搬送困難事案（今回）'!$A$1:$FF$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'搬送困難事案（前年同期）'!$A$1:$FF$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'うちコロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'うち非コロナ疑い事案（今回）'!$A:$C</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'搬送困難事案（今回）'!$A:$C</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="446">
   <si>
     <t>都道府県</t>
   </si>
@@ -4688,6 +4688,18 @@
 【4月第2週】</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>4/10(月)～
+4/16(日)分
+【4月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4/11(月)～
+4/17(日)分
+【4月第3週】</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5187,35 +5199,26 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -5225,6 +5228,36 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5238,47 +5271,32 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5307,12 +5325,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5326,7 +5338,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="29">
     <dxf>
       <fill>
         <patternFill>
@@ -5442,6 +5454,21 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -9610,7 +9637,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FE61"/>
+  <dimension ref="A1:FF61"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -9624,11 +9651,11 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="102" width="10.875" style="1" customWidth="1"/>
     <col min="103" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="161" width="10.875" style="1" customWidth="1"/>
-    <col min="162" max="16384" width="8.625" style="1"/>
+    <col min="106" max="162" width="10.875" style="1" customWidth="1"/>
+    <col min="163" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:161" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:162" ht="29.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AQ1" s="36"/>
       <c r="BB1" s="36"/>
       <c r="BC1" s="19" t="s">
@@ -9716,672 +9743,675 @@
       <c r="FB1" s="19"/>
       <c r="FC1" s="19"/>
       <c r="FD1" s="19"/>
-      <c r="FE1" s="19" t="s">
+      <c r="FE1" s="19"/>
+      <c r="FF1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:161" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="73" t="s">
+    <row r="2" spans="1:162" ht="33" x14ac:dyDescent="0.4">
+      <c r="B2" s="65"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
-      <c r="BC2" s="51"/>
-      <c r="BD2" s="51" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="50"/>
+      <c r="BB2" s="50"/>
+      <c r="BC2" s="50"/>
+      <c r="BD2" s="50" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="51"/>
-      <c r="BO2" s="51"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="51"/>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
-      <c r="BV2" s="51"/>
-      <c r="BW2" s="51"/>
-      <c r="BX2" s="51"/>
-      <c r="BY2" s="51"/>
-      <c r="BZ2" s="51"/>
-      <c r="CA2" s="51"/>
-      <c r="CB2" s="51"/>
-      <c r="CC2" s="51"/>
-      <c r="CD2" s="51"/>
-      <c r="CE2" s="51"/>
-      <c r="CF2" s="51"/>
-      <c r="CG2" s="51"/>
-      <c r="CH2" s="51"/>
-      <c r="CI2" s="51"/>
-      <c r="CJ2" s="51"/>
-      <c r="CK2" s="51"/>
-      <c r="CL2" s="51"/>
-      <c r="CM2" s="51"/>
-      <c r="CN2" s="51"/>
-      <c r="CO2" s="51"/>
-      <c r="CP2" s="51"/>
-      <c r="CQ2" s="51"/>
-      <c r="CR2" s="51"/>
-      <c r="CS2" s="51"/>
-      <c r="CT2" s="51"/>
-      <c r="CU2" s="51"/>
-      <c r="CV2" s="51"/>
-      <c r="CW2" s="51"/>
-      <c r="CX2" s="51"/>
-      <c r="CY2" s="51"/>
-      <c r="CZ2" s="51"/>
-      <c r="DA2" s="51"/>
-      <c r="DB2" s="51"/>
-      <c r="DC2" s="51"/>
-      <c r="DD2" s="51"/>
-      <c r="DE2" s="72" t="s">
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="50"/>
+      <c r="BO2" s="50"/>
+      <c r="BP2" s="50"/>
+      <c r="BQ2" s="50"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="50"/>
+      <c r="CC2" s="50"/>
+      <c r="CD2" s="50"/>
+      <c r="CE2" s="50"/>
+      <c r="CF2" s="50"/>
+      <c r="CG2" s="50"/>
+      <c r="CH2" s="50"/>
+      <c r="CI2" s="50"/>
+      <c r="CJ2" s="50"/>
+      <c r="CK2" s="50"/>
+      <c r="CL2" s="50"/>
+      <c r="CM2" s="50"/>
+      <c r="CN2" s="50"/>
+      <c r="CO2" s="50"/>
+      <c r="CP2" s="50"/>
+      <c r="CQ2" s="50"/>
+      <c r="CR2" s="50"/>
+      <c r="CS2" s="50"/>
+      <c r="CT2" s="50"/>
+      <c r="CU2" s="50"/>
+      <c r="CV2" s="50"/>
+      <c r="CW2" s="50"/>
+      <c r="CX2" s="50"/>
+      <c r="CY2" s="50"/>
+      <c r="CZ2" s="50"/>
+      <c r="DA2" s="50"/>
+      <c r="DB2" s="50"/>
+      <c r="DC2" s="50"/>
+      <c r="DD2" s="50"/>
+      <c r="DE2" s="45" t="s">
         <v>320</v>
       </c>
-      <c r="DF2" s="72"/>
-      <c r="DG2" s="72"/>
-      <c r="DH2" s="72"/>
-      <c r="DI2" s="72"/>
-      <c r="DJ2" s="72"/>
-      <c r="DK2" s="72"/>
-      <c r="DL2" s="72"/>
-      <c r="DM2" s="72"/>
-      <c r="DN2" s="72"/>
-      <c r="DO2" s="72"/>
-      <c r="DP2" s="72"/>
-      <c r="DQ2" s="72"/>
-      <c r="DR2" s="72"/>
-      <c r="DS2" s="72"/>
-      <c r="DT2" s="72"/>
-      <c r="DU2" s="72"/>
-      <c r="DV2" s="72"/>
-      <c r="DW2" s="72"/>
-      <c r="DX2" s="72"/>
-      <c r="DY2" s="72"/>
-      <c r="DZ2" s="72"/>
-      <c r="EA2" s="72"/>
-      <c r="EB2" s="72"/>
-      <c r="EC2" s="72"/>
-      <c r="ED2" s="72"/>
-      <c r="EE2" s="72"/>
-      <c r="EF2" s="72"/>
-      <c r="EG2" s="72"/>
-      <c r="EH2" s="72"/>
-      <c r="EI2" s="72"/>
-      <c r="EJ2" s="72"/>
-      <c r="EK2" s="72"/>
-      <c r="EL2" s="72"/>
-      <c r="EM2" s="72"/>
-      <c r="EN2" s="72"/>
-      <c r="EO2" s="72"/>
-      <c r="EP2" s="72"/>
-      <c r="EQ2" s="72"/>
-      <c r="ER2" s="72"/>
-      <c r="ES2" s="72"/>
-      <c r="ET2" s="72"/>
-      <c r="EU2" s="72"/>
-      <c r="EV2" s="72"/>
-      <c r="EW2" s="72"/>
-      <c r="EX2" s="72"/>
-      <c r="EY2" s="72"/>
-      <c r="EZ2" s="72"/>
-      <c r="FA2" s="72"/>
-      <c r="FB2" s="72"/>
-      <c r="FC2" s="72"/>
-      <c r="FD2" s="72"/>
-      <c r="FE2" s="72"/>
+      <c r="DF2" s="45"/>
+      <c r="DG2" s="45"/>
+      <c r="DH2" s="45"/>
+      <c r="DI2" s="45"/>
+      <c r="DJ2" s="45"/>
+      <c r="DK2" s="45"/>
+      <c r="DL2" s="45"/>
+      <c r="DM2" s="45"/>
+      <c r="DN2" s="45"/>
+      <c r="DO2" s="45"/>
+      <c r="DP2" s="45"/>
+      <c r="DQ2" s="45"/>
+      <c r="DR2" s="45"/>
+      <c r="DS2" s="45"/>
+      <c r="DT2" s="45"/>
+      <c r="DU2" s="45"/>
+      <c r="DV2" s="45"/>
+      <c r="DW2" s="45"/>
+      <c r="DX2" s="45"/>
+      <c r="DY2" s="45"/>
+      <c r="DZ2" s="45"/>
+      <c r="EA2" s="45"/>
+      <c r="EB2" s="45"/>
+      <c r="EC2" s="45"/>
+      <c r="ED2" s="45"/>
+      <c r="EE2" s="45"/>
+      <c r="EF2" s="45"/>
+      <c r="EG2" s="45"/>
+      <c r="EH2" s="45"/>
+      <c r="EI2" s="45"/>
+      <c r="EJ2" s="45"/>
+      <c r="EK2" s="45"/>
+      <c r="EL2" s="45"/>
+      <c r="EM2" s="45"/>
+      <c r="EN2" s="45"/>
+      <c r="EO2" s="45"/>
+      <c r="EP2" s="45"/>
+      <c r="EQ2" s="45"/>
+      <c r="ER2" s="45"/>
+      <c r="ES2" s="45"/>
+      <c r="ET2" s="45"/>
+      <c r="EU2" s="45"/>
+      <c r="EV2" s="45"/>
+      <c r="EW2" s="45"/>
+      <c r="EX2" s="45"/>
+      <c r="EY2" s="45"/>
+      <c r="EZ2" s="45"/>
+      <c r="FA2" s="45"/>
+      <c r="FB2" s="45"/>
+      <c r="FC2" s="45"/>
+      <c r="FD2" s="45"/>
+      <c r="FE2" s="45"/>
+      <c r="FF2" s="45"/>
     </row>
-    <row r="3" spans="1:161" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="45" t="s">
+    <row r="3" spans="1:162" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="45"/>
-      <c r="AR3" s="47" t="s">
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="46"/>
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="46"/>
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="46"/>
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="46"/>
+      <c r="AH3" s="46"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="46"/>
+      <c r="AO3" s="46"/>
+      <c r="AP3" s="46"/>
+      <c r="AQ3" s="46"/>
+      <c r="AR3" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="52"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
-      <c r="BB3" s="52"/>
-      <c r="BC3" s="52"/>
-      <c r="BD3" s="52" t="s">
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="57"/>
+      <c r="AZ3" s="57"/>
+      <c r="BA3" s="57"/>
+      <c r="BB3" s="57"/>
+      <c r="BC3" s="57"/>
+      <c r="BD3" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="52"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="52"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="52"/>
-      <c r="BP3" s="52"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="52"/>
-      <c r="BS3" s="52"/>
-      <c r="BT3" s="52"/>
-      <c r="BU3" s="52"/>
-      <c r="BV3" s="52"/>
-      <c r="BW3" s="52"/>
-      <c r="BX3" s="52"/>
-      <c r="BY3" s="52"/>
-      <c r="BZ3" s="52"/>
-      <c r="CA3" s="52"/>
-      <c r="CB3" s="52"/>
-      <c r="CC3" s="52"/>
-      <c r="CD3" s="52"/>
-      <c r="CE3" s="52"/>
-      <c r="CF3" s="52"/>
-      <c r="CG3" s="52"/>
-      <c r="CH3" s="52"/>
-      <c r="CI3" s="52"/>
-      <c r="CJ3" s="52"/>
-      <c r="CK3" s="52"/>
-      <c r="CL3" s="52"/>
-      <c r="CM3" s="52"/>
-      <c r="CN3" s="52"/>
-      <c r="CO3" s="52"/>
-      <c r="CP3" s="52"/>
-      <c r="CQ3" s="53"/>
-      <c r="CR3" s="45" t="s">
+      <c r="BE3" s="57"/>
+      <c r="BF3" s="57"/>
+      <c r="BG3" s="57"/>
+      <c r="BH3" s="57"/>
+      <c r="BI3" s="57"/>
+      <c r="BJ3" s="57"/>
+      <c r="BK3" s="57"/>
+      <c r="BL3" s="57"/>
+      <c r="BM3" s="57"/>
+      <c r="BN3" s="57"/>
+      <c r="BO3" s="57"/>
+      <c r="BP3" s="57"/>
+      <c r="BQ3" s="57"/>
+      <c r="BR3" s="57"/>
+      <c r="BS3" s="57"/>
+      <c r="BT3" s="57"/>
+      <c r="BU3" s="57"/>
+      <c r="BV3" s="57"/>
+      <c r="BW3" s="57"/>
+      <c r="BX3" s="57"/>
+      <c r="BY3" s="57"/>
+      <c r="BZ3" s="57"/>
+      <c r="CA3" s="57"/>
+      <c r="CB3" s="57"/>
+      <c r="CC3" s="57"/>
+      <c r="CD3" s="57"/>
+      <c r="CE3" s="57"/>
+      <c r="CF3" s="57"/>
+      <c r="CG3" s="57"/>
+      <c r="CH3" s="57"/>
+      <c r="CI3" s="57"/>
+      <c r="CJ3" s="57"/>
+      <c r="CK3" s="57"/>
+      <c r="CL3" s="57"/>
+      <c r="CM3" s="57"/>
+      <c r="CN3" s="57"/>
+      <c r="CO3" s="57"/>
+      <c r="CP3" s="57"/>
+      <c r="CQ3" s="71"/>
+      <c r="CR3" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="CS3" s="45"/>
-      <c r="CT3" s="45"/>
-      <c r="CU3" s="45"/>
-      <c r="CV3" s="45"/>
-      <c r="CW3" s="45"/>
-      <c r="CX3" s="45"/>
-      <c r="CY3" s="45"/>
-      <c r="CZ3" s="45"/>
-      <c r="DA3" s="45"/>
-      <c r="DB3" s="45"/>
-      <c r="DC3" s="45"/>
-      <c r="DD3" s="47"/>
-      <c r="DE3" s="45" t="s">
+      <c r="CS3" s="46"/>
+      <c r="CT3" s="46"/>
+      <c r="CU3" s="46"/>
+      <c r="CV3" s="46"/>
+      <c r="CW3" s="46"/>
+      <c r="CX3" s="46"/>
+      <c r="CY3" s="46"/>
+      <c r="CZ3" s="46"/>
+      <c r="DA3" s="46"/>
+      <c r="DB3" s="46"/>
+      <c r="DC3" s="46"/>
+      <c r="DD3" s="56"/>
+      <c r="DE3" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DF3" s="46"/>
+      <c r="DG3" s="46"/>
+      <c r="DH3" s="46"/>
+      <c r="DI3" s="46"/>
+      <c r="DJ3" s="46"/>
+      <c r="DK3" s="46"/>
+      <c r="DL3" s="46"/>
+      <c r="DM3" s="46"/>
+      <c r="DN3" s="46"/>
+      <c r="DO3" s="46"/>
+      <c r="DP3" s="46"/>
+      <c r="DQ3" s="46"/>
+      <c r="DR3" s="46"/>
+      <c r="DS3" s="46"/>
+      <c r="DT3" s="46"/>
+      <c r="DU3" s="46"/>
+      <c r="DV3" s="46"/>
+      <c r="DW3" s="46"/>
+      <c r="DX3" s="46"/>
+      <c r="DY3" s="46"/>
+      <c r="DZ3" s="46"/>
+      <c r="EA3" s="46"/>
+      <c r="EB3" s="46"/>
+      <c r="EC3" s="46"/>
+      <c r="ED3" s="46"/>
+      <c r="EE3" s="46"/>
+      <c r="EF3" s="46"/>
+      <c r="EG3" s="46"/>
+      <c r="EH3" s="46"/>
+      <c r="EI3" s="46"/>
+      <c r="EJ3" s="46"/>
+      <c r="EK3" s="46"/>
+      <c r="EL3" s="46"/>
+      <c r="EM3" s="46"/>
+      <c r="EN3" s="46"/>
+      <c r="EO3" s="46"/>
+      <c r="EP3" s="46"/>
+      <c r="EQ3" s="46"/>
+      <c r="ER3" s="46" t="s">
         <v>415</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
-      <c r="EU3" s="45"/>
-      <c r="EV3" s="45"/>
-      <c r="EW3" s="45"/>
-      <c r="EX3" s="45"/>
-      <c r="EY3" s="45"/>
-      <c r="EZ3" s="45"/>
-      <c r="FA3" s="45"/>
-      <c r="FB3" s="45"/>
-      <c r="FC3" s="45"/>
-      <c r="FD3" s="45"/>
-      <c r="FE3" s="45"/>
+      <c r="ES3" s="46"/>
+      <c r="ET3" s="46"/>
+      <c r="EU3" s="46"/>
+      <c r="EV3" s="46"/>
+      <c r="EW3" s="46"/>
+      <c r="EX3" s="46"/>
+      <c r="EY3" s="46"/>
+      <c r="EZ3" s="46"/>
+      <c r="FA3" s="46"/>
+      <c r="FB3" s="46"/>
+      <c r="FC3" s="46"/>
+      <c r="FD3" s="46"/>
+      <c r="FE3" s="46"/>
+      <c r="FF3" s="46"/>
     </row>
-    <row r="4" spans="1:161" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="63" t="s">
+    <row r="4" spans="1:162" ht="20.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="63" t="s">
+      <c r="F4" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="63" t="s">
+      <c r="G4" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="I4" s="63" t="s">
+      <c r="I4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="63" t="s">
+      <c r="J4" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="63" t="s">
+      <c r="K4" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="M4" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="R4" s="62" t="s">
+      <c r="R4" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="63" t="s">
+      <c r="T4" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="U4" s="62" t="s">
+      <c r="U4" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="62" t="s">
+      <c r="V4" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="W4" s="62" t="s">
+      <c r="W4" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="X4" s="62" t="s">
+      <c r="X4" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="Y4" s="62" t="s">
+      <c r="Y4" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="62" t="s">
+      <c r="Z4" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="AA4" s="63" t="s">
+      <c r="AA4" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="63" t="s">
+      <c r="AB4" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="63" t="s">
+      <c r="AC4" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="AD4" s="63" t="s">
+      <c r="AD4" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="AE4" s="63" t="s">
+      <c r="AE4" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="AF4" s="63" t="s">
+      <c r="AF4" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="AG4" s="63" t="s">
+      <c r="AG4" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AH4" s="63" t="s">
+      <c r="AH4" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="AI4" s="63" t="s">
+      <c r="AI4" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="AJ4" s="63" t="s">
+      <c r="AJ4" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="AK4" s="63" t="s">
+      <c r="AK4" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="AL4" s="63" t="s">
+      <c r="AL4" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="AM4" s="63" t="s">
+      <c r="AM4" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="AN4" s="63" t="s">
+      <c r="AN4" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="AO4" s="63" t="s">
+      <c r="AO4" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="AP4" s="63" t="s">
+      <c r="AP4" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="AQ4" s="63" t="s">
+      <c r="AQ4" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" s="55" t="s">
+      <c r="AR4" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="AS4" s="55" t="s">
+      <c r="AS4" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="55" t="s">
+      <c r="AT4" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="55" t="s">
+      <c r="AU4" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="55" t="s">
+      <c r="AV4" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="AW4" s="55" t="s">
+      <c r="AW4" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="AX4" s="55" t="s">
+      <c r="AX4" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="AY4" s="55" t="s">
+      <c r="AY4" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="AZ4" s="55" t="s">
+      <c r="AZ4" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="BA4" s="55" t="s">
+      <c r="BA4" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="BB4" s="55" t="s">
+      <c r="BB4" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="BC4" s="55" t="s">
+      <c r="BC4" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="BD4" s="54" t="s">
+      <c r="BD4" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="BE4" s="54" t="s">
+      <c r="BE4" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="54" t="s">
+      <c r="BF4" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="54" t="s">
+      <c r="BG4" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="BH4" s="54" t="s">
+      <c r="BH4" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="BI4" s="54" t="s">
+      <c r="BI4" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="54" t="s">
+      <c r="BJ4" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="54" t="s">
+      <c r="BK4" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="56" t="s">
+      <c r="BL4" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="56" t="s">
+      <c r="BM4" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="BN4" s="54" t="s">
+      <c r="BN4" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="BO4" s="54" t="s">
+      <c r="BO4" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="BP4" s="54" t="s">
+      <c r="BP4" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="BQ4" s="54" t="s">
+      <c r="BQ4" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="BR4" s="54" t="s">
+      <c r="BR4" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="BS4" s="54" t="s">
+      <c r="BS4" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="BT4" s="54" t="s">
+      <c r="BT4" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="BU4" s="56" t="s">
+      <c r="BU4" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="BV4" s="56" t="s">
+      <c r="BV4" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="BW4" s="56" t="s">
+      <c r="BW4" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="BX4" s="56" t="s">
+      <c r="BX4" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="56" t="s">
+      <c r="BY4" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="BZ4" s="54" t="s">
+      <c r="BZ4" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="CA4" s="54" t="s">
+      <c r="CA4" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="CB4" s="54" t="s">
+      <c r="CB4" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="CC4" s="54" t="s">
+      <c r="CC4" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="CD4" s="54" t="s">
+      <c r="CD4" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="CE4" s="48" t="s">
+      <c r="CE4" s="55" t="s">
         <v>252</v>
       </c>
-      <c r="CF4" s="48" t="s">
+      <c r="CF4" s="55" t="s">
         <v>254</v>
       </c>
-      <c r="CG4" s="48" t="s">
+      <c r="CG4" s="55" t="s">
         <v>256</v>
       </c>
-      <c r="CH4" s="48" t="s">
+      <c r="CH4" s="55" t="s">
         <v>258</v>
       </c>
-      <c r="CI4" s="48" t="s">
+      <c r="CI4" s="55" t="s">
         <v>260</v>
       </c>
-      <c r="CJ4" s="48" t="s">
+      <c r="CJ4" s="55" t="s">
         <v>262</v>
       </c>
-      <c r="CK4" s="48" t="s">
+      <c r="CK4" s="55" t="s">
         <v>264</v>
       </c>
-      <c r="CL4" s="48" t="s">
+      <c r="CL4" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="CM4" s="48" t="s">
+      <c r="CM4" s="55" t="s">
         <v>268</v>
       </c>
-      <c r="CN4" s="48" t="s">
+      <c r="CN4" s="55" t="s">
         <v>270</v>
       </c>
-      <c r="CO4" s="48" t="s">
+      <c r="CO4" s="55" t="s">
         <v>272</v>
       </c>
-      <c r="CP4" s="48" t="s">
+      <c r="CP4" s="55" t="s">
         <v>274</v>
       </c>
-      <c r="CQ4" s="48" t="s">
+      <c r="CQ4" s="55" t="s">
         <v>276</v>
       </c>
-      <c r="CR4" s="48" t="s">
+      <c r="CR4" s="55" t="s">
         <v>279</v>
       </c>
-      <c r="CS4" s="48" t="s">
+      <c r="CS4" s="55" t="s">
         <v>284</v>
       </c>
-      <c r="CT4" s="48" t="s">
+      <c r="CT4" s="55" t="s">
         <v>286</v>
       </c>
-      <c r="CU4" s="48" t="s">
+      <c r="CU4" s="55" t="s">
         <v>288</v>
       </c>
-      <c r="CV4" s="48" t="s">
+      <c r="CV4" s="55" t="s">
         <v>291</v>
       </c>
-      <c r="CW4" s="48" t="s">
+      <c r="CW4" s="55" t="s">
         <v>292</v>
       </c>
-      <c r="CX4" s="48" t="s">
+      <c r="CX4" s="55" t="s">
         <v>294</v>
       </c>
-      <c r="CY4" s="48" t="s">
+      <c r="CY4" s="55" t="s">
         <v>296</v>
       </c>
-      <c r="CZ4" s="48" t="s">
+      <c r="CZ4" s="55" t="s">
         <v>306</v>
       </c>
-      <c r="DA4" s="48" t="s">
+      <c r="DA4" s="55" t="s">
         <v>299</v>
       </c>
-      <c r="DB4" s="48" t="s">
+      <c r="DB4" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="DC4" s="48" t="s">
+      <c r="DC4" s="55" t="s">
         <v>303</v>
       </c>
-      <c r="DD4" s="49" t="s">
+      <c r="DD4" s="72" t="s">
         <v>305</v>
       </c>
       <c r="DE4" s="44" t="s">
@@ -10543,139 +10573,142 @@
       <c r="FE4" s="44" t="s">
         <v>441</v>
       </c>
+      <c r="FF4" s="44" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="5" spans="1:161" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="65"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="54"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="54"/>
-      <c r="AG5" s="54"/>
-      <c r="AH5" s="54"/>
-      <c r="AI5" s="54"/>
-      <c r="AJ5" s="54"/>
-      <c r="AK5" s="54"/>
-      <c r="AL5" s="54"/>
-      <c r="AM5" s="54"/>
-      <c r="AN5" s="54"/>
-      <c r="AO5" s="54"/>
-      <c r="AP5" s="54"/>
-      <c r="AQ5" s="54"/>
-      <c r="AR5" s="55"/>
-      <c r="AS5" s="55"/>
-      <c r="AT5" s="55"/>
-      <c r="AU5" s="55"/>
-      <c r="AV5" s="55"/>
-      <c r="AW5" s="55"/>
-      <c r="AX5" s="55"/>
-      <c r="AY5" s="55"/>
-      <c r="AZ5" s="55"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="55"/>
-      <c r="BC5" s="55"/>
-      <c r="BD5" s="55"/>
-      <c r="BE5" s="55"/>
-      <c r="BF5" s="55"/>
-      <c r="BG5" s="55"/>
-      <c r="BH5" s="55"/>
-      <c r="BI5" s="55"/>
-      <c r="BJ5" s="55"/>
-      <c r="BK5" s="55"/>
-      <c r="BL5" s="57"/>
-      <c r="BM5" s="57"/>
-      <c r="BN5" s="55"/>
-      <c r="BO5" s="55"/>
-      <c r="BP5" s="55"/>
-      <c r="BQ5" s="55"/>
-      <c r="BR5" s="55"/>
-      <c r="BS5" s="55"/>
-      <c r="BT5" s="55"/>
-      <c r="BU5" s="57"/>
-      <c r="BV5" s="57"/>
-      <c r="BW5" s="57"/>
-      <c r="BX5" s="57"/>
-      <c r="BY5" s="57"/>
-      <c r="BZ5" s="55"/>
-      <c r="CA5" s="55"/>
-      <c r="CB5" s="55"/>
-      <c r="CC5" s="55"/>
-      <c r="CD5" s="55"/>
-      <c r="CE5" s="46"/>
-      <c r="CF5" s="46"/>
-      <c r="CG5" s="46"/>
-      <c r="CH5" s="46"/>
-      <c r="CI5" s="46"/>
-      <c r="CJ5" s="46"/>
-      <c r="CK5" s="46"/>
-      <c r="CL5" s="46"/>
-      <c r="CM5" s="46"/>
-      <c r="CN5" s="46"/>
-      <c r="CO5" s="46"/>
-      <c r="CP5" s="46"/>
-      <c r="CQ5" s="46"/>
-      <c r="CR5" s="46"/>
-      <c r="CS5" s="46"/>
-      <c r="CT5" s="46"/>
-      <c r="CU5" s="46"/>
-      <c r="CV5" s="46"/>
-      <c r="CW5" s="46"/>
-      <c r="CX5" s="46"/>
-      <c r="CY5" s="46"/>
-      <c r="CZ5" s="46"/>
-      <c r="DA5" s="46"/>
-      <c r="DB5" s="46"/>
-      <c r="DC5" s="46"/>
-      <c r="DD5" s="50"/>
-      <c r="DE5" s="46"/>
-      <c r="DF5" s="46"/>
-      <c r="DG5" s="46"/>
-      <c r="DH5" s="46"/>
-      <c r="DI5" s="46"/>
-      <c r="DJ5" s="46"/>
-      <c r="DK5" s="46"/>
-      <c r="DL5" s="46"/>
-      <c r="DM5" s="46"/>
-      <c r="DN5" s="46"/>
-      <c r="DO5" s="46"/>
-      <c r="DP5" s="46"/>
-      <c r="DQ5" s="46"/>
-      <c r="DR5" s="46"/>
-      <c r="DS5" s="46"/>
-      <c r="DT5" s="46"/>
-      <c r="DU5" s="46"/>
-      <c r="DV5" s="46"/>
-      <c r="DW5" s="46"/>
-      <c r="DX5" s="46"/>
-      <c r="DY5" s="46"/>
-      <c r="DZ5" s="46"/>
-      <c r="EA5" s="46"/>
-      <c r="EB5" s="46"/>
+    <row r="5" spans="1:162" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="70"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="48"/>
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="48"/>
+      <c r="AQ5" s="48"/>
+      <c r="AR5" s="52"/>
+      <c r="AS5" s="52"/>
+      <c r="AT5" s="52"/>
+      <c r="AU5" s="52"/>
+      <c r="AV5" s="52"/>
+      <c r="AW5" s="52"/>
+      <c r="AX5" s="52"/>
+      <c r="AY5" s="52"/>
+      <c r="AZ5" s="52"/>
+      <c r="BA5" s="52"/>
+      <c r="BB5" s="52"/>
+      <c r="BC5" s="52"/>
+      <c r="BD5" s="52"/>
+      <c r="BE5" s="52"/>
+      <c r="BF5" s="52"/>
+      <c r="BG5" s="52"/>
+      <c r="BH5" s="52"/>
+      <c r="BI5" s="52"/>
+      <c r="BJ5" s="52"/>
+      <c r="BK5" s="52"/>
+      <c r="BL5" s="54"/>
+      <c r="BM5" s="54"/>
+      <c r="BN5" s="52"/>
+      <c r="BO5" s="52"/>
+      <c r="BP5" s="52"/>
+      <c r="BQ5" s="52"/>
+      <c r="BR5" s="52"/>
+      <c r="BS5" s="52"/>
+      <c r="BT5" s="52"/>
+      <c r="BU5" s="54"/>
+      <c r="BV5" s="54"/>
+      <c r="BW5" s="54"/>
+      <c r="BX5" s="54"/>
+      <c r="BY5" s="54"/>
+      <c r="BZ5" s="52"/>
+      <c r="CA5" s="52"/>
+      <c r="CB5" s="52"/>
+      <c r="CC5" s="52"/>
+      <c r="CD5" s="52"/>
+      <c r="CE5" s="51"/>
+      <c r="CF5" s="51"/>
+      <c r="CG5" s="51"/>
+      <c r="CH5" s="51"/>
+      <c r="CI5" s="51"/>
+      <c r="CJ5" s="51"/>
+      <c r="CK5" s="51"/>
+      <c r="CL5" s="51"/>
+      <c r="CM5" s="51"/>
+      <c r="CN5" s="51"/>
+      <c r="CO5" s="51"/>
+      <c r="CP5" s="51"/>
+      <c r="CQ5" s="51"/>
+      <c r="CR5" s="51"/>
+      <c r="CS5" s="51"/>
+      <c r="CT5" s="51"/>
+      <c r="CU5" s="51"/>
+      <c r="CV5" s="51"/>
+      <c r="CW5" s="51"/>
+      <c r="CX5" s="51"/>
+      <c r="CY5" s="51"/>
+      <c r="CZ5" s="51"/>
+      <c r="DA5" s="51"/>
+      <c r="DB5" s="51"/>
+      <c r="DC5" s="51"/>
+      <c r="DD5" s="73"/>
+      <c r="DE5" s="51"/>
+      <c r="DF5" s="51"/>
+      <c r="DG5" s="51"/>
+      <c r="DH5" s="51"/>
+      <c r="DI5" s="51"/>
+      <c r="DJ5" s="51"/>
+      <c r="DK5" s="51"/>
+      <c r="DL5" s="51"/>
+      <c r="DM5" s="51"/>
+      <c r="DN5" s="51"/>
+      <c r="DO5" s="51"/>
+      <c r="DP5" s="51"/>
+      <c r="DQ5" s="51"/>
+      <c r="DR5" s="51"/>
+      <c r="DS5" s="51"/>
+      <c r="DT5" s="51"/>
+      <c r="DU5" s="51"/>
+      <c r="DV5" s="51"/>
+      <c r="DW5" s="51"/>
+      <c r="DX5" s="51"/>
+      <c r="DY5" s="51"/>
+      <c r="DZ5" s="51"/>
+      <c r="EA5" s="51"/>
+      <c r="EB5" s="51"/>
       <c r="EC5" s="44"/>
       <c r="ED5" s="44"/>
       <c r="EE5" s="44"/>
@@ -10705,8 +10738,9 @@
       <c r="FC5" s="44"/>
       <c r="FD5" s="44"/>
       <c r="FE5" s="44"/>
+      <c r="FF5" s="44"/>
     </row>
-    <row r="6" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
       <c r="B6" s="11" t="s">
         <v>2</v>
@@ -11188,8 +11222,11 @@
       <c r="FE6" s="28">
         <v>77</v>
       </c>
+      <c r="FF6" s="28">
+        <v>102</v>
+      </c>
     </row>
-    <row r="7" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11670,8 +11707,11 @@
       <c r="FE7" s="15">
         <v>1</v>
       </c>
+      <c r="FF7" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -12152,8 +12192,11 @@
       <c r="FE8" s="28">
         <v>7</v>
       </c>
+      <c r="FF8" s="28">
+        <v>12</v>
+      </c>
     </row>
-    <row r="9" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -12635,8 +12678,11 @@
       <c r="FE9" s="15">
         <v>59</v>
       </c>
+      <c r="FF9" s="15">
+        <v>59</v>
+      </c>
     </row>
-    <row r="10" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -13115,8 +13161,11 @@
       <c r="FE10" s="15">
         <v>0</v>
       </c>
+      <c r="FF10" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -13597,8 +13646,11 @@
       <c r="FE11" s="15">
         <v>9</v>
       </c>
+      <c r="FF11" s="15">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -14079,8 +14131,11 @@
       <c r="FE12" s="15">
         <v>5</v>
       </c>
+      <c r="FF12" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -14561,8 +14616,11 @@
       <c r="FE13" s="15">
         <v>27</v>
       </c>
+      <c r="FF13" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="14" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -15043,8 +15101,11 @@
       <c r="FE14" s="15">
         <v>19</v>
       </c>
+      <c r="FF14" s="15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="15" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -15525,8 +15586,11 @@
       <c r="FE15" s="15">
         <v>0</v>
       </c>
+      <c r="FF15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>21</v>
@@ -16008,8 +16072,11 @@
       <c r="FE16" s="28">
         <v>104</v>
       </c>
+      <c r="FF16" s="28">
+        <v>97</v>
+      </c>
     </row>
-    <row r="17" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -16490,8 +16557,11 @@
       <c r="FE17" s="15">
         <v>128</v>
       </c>
+      <c r="FF17" s="15">
+        <v>125</v>
+      </c>
     </row>
-    <row r="18" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -16973,10 +17043,13 @@
       <c r="FE18" s="34">
         <v>1332</v>
       </c>
+      <c r="FF18" s="34">
+        <v>1355</v>
+      </c>
     </row>
-    <row r="19" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="61" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -17456,10 +17529,13 @@
       <c r="FE19" s="15">
         <v>41</v>
       </c>
+      <c r="FF19" s="15">
+        <v>33</v>
+      </c>
     </row>
-    <row r="20" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3"/>
-      <c r="B20" s="68"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -17937,10 +18013,13 @@
       <c r="FE20" s="28">
         <v>61</v>
       </c>
+      <c r="FF20" s="28">
+        <v>63</v>
+      </c>
     </row>
-    <row r="21" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3"/>
-      <c r="B21" s="68"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -18418,8 +18497,11 @@
       <c r="FE21" s="15">
         <v>18</v>
       </c>
+      <c r="FF21" s="15">
+        <v>21</v>
+      </c>
     </row>
-    <row r="22" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -18900,8 +18982,11 @@
       <c r="FE22" s="15">
         <v>1</v>
       </c>
+      <c r="FF22" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -19382,8 +19467,11 @@
       <c r="FE23" s="15">
         <v>0</v>
       </c>
+      <c r="FF23" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -19864,8 +19952,11 @@
       <c r="FE24" s="15">
         <v>3</v>
       </c>
+      <c r="FF24" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -20346,8 +20437,11 @@
       <c r="FE25" s="15">
         <v>0</v>
       </c>
+      <c r="FF25" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -20828,8 +20922,11 @@
       <c r="FE26" s="15">
         <v>15</v>
       </c>
+      <c r="FF26" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="27" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -21310,8 +21407,11 @@
       <c r="FE27" s="15">
         <v>0</v>
       </c>
+      <c r="FF27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -21792,9 +21892,12 @@
       <c r="FE28" s="15">
         <v>1</v>
       </c>
+      <c r="FF28" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="69" t="s">
+    <row r="29" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="62" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -22274,9 +22377,12 @@
       <c r="FE29" s="15">
         <v>1</v>
       </c>
+      <c r="FF29" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="69"/>
+    <row r="30" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="62"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -22754,8 +22860,11 @@
       <c r="FE30" s="15">
         <v>12</v>
       </c>
+      <c r="FF30" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="31" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3"/>
       <c r="B31" s="11" t="s">
         <v>48</v>
@@ -23237,8 +23346,11 @@
       <c r="FE31" s="15">
         <v>36</v>
       </c>
+      <c r="FF31" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="32" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -23719,8 +23831,11 @@
       <c r="FE32" s="15">
         <v>0</v>
       </c>
+      <c r="FF32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -24201,8 +24316,11 @@
       <c r="FE33" s="15">
         <v>0</v>
       </c>
+      <c r="FF33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3"/>
       <c r="B34" s="11" t="s">
         <v>54</v>
@@ -24684,10 +24802,13 @@
       <c r="FE34" s="15">
         <v>45</v>
       </c>
+      <c r="FF34" s="15">
+        <v>57</v>
+      </c>
     </row>
-    <row r="35" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3"/>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="61" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -25167,9 +25288,12 @@
       <c r="FE35" s="15">
         <v>244</v>
       </c>
+      <c r="FF35" s="15">
+        <v>243</v>
+      </c>
     </row>
-    <row r="36" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="68"/>
+    <row r="36" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="61"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -25647,8 +25771,11 @@
       <c r="FE36" s="28">
         <v>21</v>
       </c>
+      <c r="FF36" s="28">
+        <v>16</v>
+      </c>
     </row>
-    <row r="37" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3"/>
       <c r="B37" s="11" t="s">
         <v>59</v>
@@ -26130,8 +26257,11 @@
       <c r="FE37" s="15">
         <v>28</v>
       </c>
+      <c r="FF37" s="15">
+        <v>36</v>
+      </c>
     </row>
-    <row r="38" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="10" t="s">
         <v>61</v>
       </c>
@@ -26612,8 +26742,11 @@
       <c r="FE38" s="15">
         <v>7</v>
       </c>
+      <c r="FF38" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="39" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="10" t="s">
         <v>63</v>
       </c>
@@ -27094,8 +27227,11 @@
       <c r="FE39" s="15">
         <v>3</v>
       </c>
+      <c r="FF39" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="40" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
@@ -27576,8 +27712,11 @@
       <c r="FE40" s="15">
         <v>0</v>
       </c>
+      <c r="FF40" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
         <v>67</v>
       </c>
@@ -28058,8 +28197,11 @@
       <c r="FE41" s="15">
         <v>0</v>
       </c>
+      <c r="FF41" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="10" t="s">
         <v>69</v>
       </c>
@@ -28540,8 +28682,11 @@
       <c r="FE42" s="15">
         <v>8</v>
       </c>
+      <c r="FF42" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="10" t="s">
         <v>71</v>
       </c>
@@ -29022,8 +29167,11 @@
       <c r="FE43" s="28">
         <v>48</v>
       </c>
+      <c r="FF43" s="28">
+        <v>62</v>
+      </c>
     </row>
-    <row r="44" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="10" t="s">
         <v>73</v>
       </c>
@@ -29504,8 +29652,11 @@
       <c r="FE44" s="15">
         <v>0</v>
       </c>
+      <c r="FF44" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="45" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
         <v>75</v>
       </c>
@@ -29986,8 +30137,11 @@
       <c r="FE45" s="15">
         <v>14</v>
       </c>
+      <c r="FF45" s="15">
+        <v>15</v>
+      </c>
     </row>
-    <row r="46" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="10" t="s">
         <v>77</v>
       </c>
@@ -30468,8 +30622,11 @@
       <c r="FE46" s="15">
         <v>22</v>
       </c>
+      <c r="FF46" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
@@ -30950,8 +31107,11 @@
       <c r="FE47" s="15">
         <v>2</v>
       </c>
+      <c r="FF47" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="10" t="s">
         <v>81</v>
       </c>
@@ -31432,10 +31592,13 @@
       <c r="FE48" s="15">
         <v>7</v>
       </c>
+      <c r="FF48" s="15">
+        <v>11</v>
+      </c>
     </row>
-    <row r="49" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3"/>
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="61" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -31915,9 +32078,12 @@
       <c r="FE49" s="15">
         <v>24</v>
       </c>
+      <c r="FF49" s="15">
+        <v>31</v>
+      </c>
     </row>
-    <row r="50" spans="1:161" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="68"/>
+    <row r="50" spans="1:162" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="61"/>
       <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
@@ -32395,8 +32561,11 @@
       <c r="FE50" s="15">
         <v>4</v>
       </c>
+      <c r="FF50" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="51" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="10" t="s">
         <v>86</v>
       </c>
@@ -32877,8 +33046,11 @@
       <c r="FE51" s="15">
         <v>3</v>
       </c>
+      <c r="FF51" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="10" t="s">
         <v>88</v>
       </c>
@@ -33359,8 +33531,11 @@
       <c r="FE52" s="15">
         <v>14</v>
       </c>
+      <c r="FF52" s="15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="53" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="10" t="s">
         <v>90</v>
       </c>
@@ -33841,8 +34016,11 @@
       <c r="FE53" s="15">
         <v>44</v>
       </c>
+      <c r="FF53" s="15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="54" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
@@ -34323,8 +34501,11 @@
       <c r="FE54" s="15">
         <v>4</v>
       </c>
+      <c r="FF54" s="15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" s="10" t="s">
         <v>94</v>
       </c>
@@ -34805,8 +34986,11 @@
       <c r="FE55" s="15">
         <v>12</v>
       </c>
+      <c r="FF55" s="15">
+        <v>13</v>
+      </c>
     </row>
-    <row r="56" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="10" t="s">
         <v>96</v>
       </c>
@@ -35287,8 +35471,11 @@
       <c r="FE56" s="15">
         <v>0</v>
       </c>
+      <c r="FF56" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
@@ -35769,8 +35956,11 @@
       <c r="FE57" s="15">
         <v>3</v>
       </c>
+      <c r="FF57" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="12"/>
       <c r="C58" s="13" t="s">
@@ -36407,8 +36597,11 @@
         <f t="shared" ref="FE58" si="14">SUM(FE6:FE57)</f>
         <v>2514</v>
       </c>
+      <c r="FF58" s="14">
+        <v>2558</v>
+      </c>
     </row>
-    <row r="59" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -36492,7 +36685,7 @@
       <c r="CC59" s="7"/>
       <c r="CD59" s="7"/>
     </row>
-    <row r="60" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -36576,30 +36769,30 @@
       <c r="CC60" s="7"/>
       <c r="CD60" s="7"/>
     </row>
-    <row r="61" spans="1:161" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:162" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="67"/>
-      <c r="O61" s="67"/>
-      <c r="P61" s="67"/>
-      <c r="Q61" s="67"/>
-      <c r="R61" s="67"/>
-      <c r="S61" s="67"/>
-      <c r="T61" s="67"/>
-      <c r="U61" s="67"/>
-      <c r="V61" s="67"/>
-      <c r="W61" s="67"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="59"/>
+      <c r="W61" s="59"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -36661,78 +36854,75 @@
       <c r="CD61" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="175">
-    <mergeCell ref="FE4:FE5"/>
-    <mergeCell ref="DE2:FE2"/>
-    <mergeCell ref="ER3:FE3"/>
-    <mergeCell ref="FD4:FD5"/>
-    <mergeCell ref="FC4:FC5"/>
-    <mergeCell ref="FB4:FB5"/>
-    <mergeCell ref="FA4:FA5"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="D2:BC2"/>
-    <mergeCell ref="DO4:DO5"/>
-    <mergeCell ref="DN4:DN5"/>
-    <mergeCell ref="DS4:DS5"/>
-    <mergeCell ref="DR4:DR5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AY4:AY5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="BC4:BC5"/>
-    <mergeCell ref="BB4:BB5"/>
-    <mergeCell ref="AZ4:AZ5"/>
-    <mergeCell ref="BA4:BA5"/>
-    <mergeCell ref="BD4:BD5"/>
-    <mergeCell ref="BW4:BW5"/>
-    <mergeCell ref="CG4:CG5"/>
-    <mergeCell ref="AR3:BC3"/>
-    <mergeCell ref="CY4:CY5"/>
-    <mergeCell ref="CF4:CF5"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="CI4:CI5"/>
-    <mergeCell ref="BG4:BG5"/>
-    <mergeCell ref="AT4:AT5"/>
-    <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="BJ4:BJ5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="CD4:CD5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BE4:BE5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="CZ4:CZ5"/>
-    <mergeCell ref="CT4:CT5"/>
-    <mergeCell ref="CQ4:CQ5"/>
-    <mergeCell ref="CN4:CN5"/>
-    <mergeCell ref="CM4:CM5"/>
-    <mergeCell ref="CO4:CO5"/>
-    <mergeCell ref="CJ4:CJ5"/>
-    <mergeCell ref="D61:W61"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
+  <mergeCells count="176">
+    <mergeCell ref="EW4:EW5"/>
+    <mergeCell ref="EY4:EY5"/>
+    <mergeCell ref="EV4:EV5"/>
+    <mergeCell ref="DE3:EQ3"/>
+    <mergeCell ref="DT4:DT5"/>
+    <mergeCell ref="DP4:DP5"/>
+    <mergeCell ref="ES4:ES5"/>
+    <mergeCell ref="EU4:EU5"/>
+    <mergeCell ref="ET4:ET5"/>
+    <mergeCell ref="EQ4:EQ5"/>
+    <mergeCell ref="EP4:EP5"/>
+    <mergeCell ref="EO4:EO5"/>
+    <mergeCell ref="EN4:EN5"/>
+    <mergeCell ref="EM4:EM5"/>
+    <mergeCell ref="EL4:EL5"/>
+    <mergeCell ref="EJ4:EJ5"/>
+    <mergeCell ref="ER4:ER5"/>
+    <mergeCell ref="DU4:DU5"/>
+    <mergeCell ref="DX4:DX5"/>
+    <mergeCell ref="DW4:DW5"/>
+    <mergeCell ref="EZ4:EZ5"/>
+    <mergeCell ref="CR3:DD3"/>
+    <mergeCell ref="CS4:CS5"/>
+    <mergeCell ref="DD4:DD5"/>
+    <mergeCell ref="DA4:DA5"/>
+    <mergeCell ref="CV4:CV5"/>
+    <mergeCell ref="CW4:CW5"/>
+    <mergeCell ref="EI4:EI5"/>
+    <mergeCell ref="EH4:EH5"/>
+    <mergeCell ref="EC4:EC5"/>
+    <mergeCell ref="EB4:EB5"/>
+    <mergeCell ref="EA4:EA5"/>
+    <mergeCell ref="DF4:DF5"/>
+    <mergeCell ref="EG4:EG5"/>
+    <mergeCell ref="EF4:EF5"/>
+    <mergeCell ref="EE4:EE5"/>
+    <mergeCell ref="DZ4:DZ5"/>
+    <mergeCell ref="DJ4:DJ5"/>
+    <mergeCell ref="DI4:DI5"/>
+    <mergeCell ref="CX4:CX5"/>
+    <mergeCell ref="DG4:DG5"/>
+    <mergeCell ref="DE4:DE5"/>
+    <mergeCell ref="DC4:DC5"/>
+    <mergeCell ref="EX4:EX5"/>
+    <mergeCell ref="DB4:DB5"/>
+    <mergeCell ref="CU4:CU5"/>
+    <mergeCell ref="CR4:CR5"/>
+    <mergeCell ref="BD2:DD2"/>
+    <mergeCell ref="BD3:CQ3"/>
+    <mergeCell ref="EK4:EK5"/>
+    <mergeCell ref="BS4:BS5"/>
+    <mergeCell ref="DK4:DK5"/>
+    <mergeCell ref="DH4:DH5"/>
+    <mergeCell ref="DY4:DY5"/>
+    <mergeCell ref="BU4:BU5"/>
+    <mergeCell ref="CE4:CE5"/>
+    <mergeCell ref="CL4:CL5"/>
+    <mergeCell ref="DQ4:DQ5"/>
+    <mergeCell ref="DL4:DL5"/>
+    <mergeCell ref="DM4:DM5"/>
+    <mergeCell ref="ED4:ED5"/>
+    <mergeCell ref="BZ4:BZ5"/>
+    <mergeCell ref="CA4:CA5"/>
+    <mergeCell ref="CB4:CB5"/>
+    <mergeCell ref="CC4:CC5"/>
+    <mergeCell ref="BI4:BI5"/>
+    <mergeCell ref="DV4:DV5"/>
+    <mergeCell ref="BR4:BR5"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="X4:X5"/>
     <mergeCell ref="AL4:AL5"/>
@@ -36757,6 +36947,35 @@
     <mergeCell ref="AQ4:AQ5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CZ4:CZ5"/>
+    <mergeCell ref="CT4:CT5"/>
+    <mergeCell ref="CQ4:CQ5"/>
+    <mergeCell ref="CN4:CN5"/>
+    <mergeCell ref="CM4:CM5"/>
+    <mergeCell ref="CO4:CO5"/>
+    <mergeCell ref="CJ4:CJ5"/>
+    <mergeCell ref="D61:W61"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="R4:R5"/>
     <mergeCell ref="BV4:BV5"/>
     <mergeCell ref="BL4:BL5"/>
     <mergeCell ref="BH4:BH5"/>
@@ -36768,120 +36987,100 @@
     <mergeCell ref="BK4:BK5"/>
     <mergeCell ref="BM4:BM5"/>
     <mergeCell ref="CK4:CK5"/>
+    <mergeCell ref="CG4:CG5"/>
+    <mergeCell ref="AR3:BC3"/>
+    <mergeCell ref="CY4:CY5"/>
+    <mergeCell ref="CF4:CF5"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="BG4:BG5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="BJ4:BJ5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AV4:AV5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="CD4:CD5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BE4:BE5"/>
+    <mergeCell ref="BO4:BO5"/>
     <mergeCell ref="BX4:BX5"/>
-    <mergeCell ref="DB4:DB5"/>
-    <mergeCell ref="CU4:CU5"/>
-    <mergeCell ref="CR4:CR5"/>
-    <mergeCell ref="BD2:DD2"/>
-    <mergeCell ref="BD3:CQ3"/>
-    <mergeCell ref="EK4:EK5"/>
-    <mergeCell ref="BS4:BS5"/>
-    <mergeCell ref="DK4:DK5"/>
-    <mergeCell ref="DH4:DH5"/>
-    <mergeCell ref="DY4:DY5"/>
-    <mergeCell ref="BU4:BU5"/>
-    <mergeCell ref="CE4:CE5"/>
-    <mergeCell ref="CL4:CL5"/>
-    <mergeCell ref="DQ4:DQ5"/>
-    <mergeCell ref="DL4:DL5"/>
-    <mergeCell ref="DM4:DM5"/>
-    <mergeCell ref="ED4:ED5"/>
-    <mergeCell ref="BZ4:BZ5"/>
-    <mergeCell ref="CA4:CA5"/>
-    <mergeCell ref="CB4:CB5"/>
-    <mergeCell ref="CC4:CC5"/>
-    <mergeCell ref="BI4:BI5"/>
-    <mergeCell ref="DV4:DV5"/>
-    <mergeCell ref="BR4:BR5"/>
-    <mergeCell ref="EZ4:EZ5"/>
-    <mergeCell ref="CR3:DD3"/>
-    <mergeCell ref="CS4:CS5"/>
-    <mergeCell ref="DD4:DD5"/>
-    <mergeCell ref="DA4:DA5"/>
-    <mergeCell ref="CV4:CV5"/>
-    <mergeCell ref="CW4:CW5"/>
-    <mergeCell ref="EI4:EI5"/>
-    <mergeCell ref="EH4:EH5"/>
-    <mergeCell ref="EC4:EC5"/>
-    <mergeCell ref="EB4:EB5"/>
-    <mergeCell ref="EA4:EA5"/>
-    <mergeCell ref="DF4:DF5"/>
-    <mergeCell ref="EG4:EG5"/>
-    <mergeCell ref="EF4:EF5"/>
-    <mergeCell ref="EE4:EE5"/>
-    <mergeCell ref="DZ4:DZ5"/>
-    <mergeCell ref="DJ4:DJ5"/>
-    <mergeCell ref="DI4:DI5"/>
-    <mergeCell ref="CX4:CX5"/>
-    <mergeCell ref="DG4:DG5"/>
-    <mergeCell ref="DE4:DE5"/>
-    <mergeCell ref="DC4:DC5"/>
-    <mergeCell ref="EX4:EX5"/>
-    <mergeCell ref="EW4:EW5"/>
-    <mergeCell ref="EY4:EY5"/>
-    <mergeCell ref="EV4:EV5"/>
-    <mergeCell ref="DE3:EQ3"/>
-    <mergeCell ref="DT4:DT5"/>
-    <mergeCell ref="DP4:DP5"/>
-    <mergeCell ref="ES4:ES5"/>
-    <mergeCell ref="EU4:EU5"/>
-    <mergeCell ref="ET4:ET5"/>
-    <mergeCell ref="EQ4:EQ5"/>
-    <mergeCell ref="EP4:EP5"/>
-    <mergeCell ref="EO4:EO5"/>
-    <mergeCell ref="EN4:EN5"/>
-    <mergeCell ref="EM4:EM5"/>
-    <mergeCell ref="EL4:EL5"/>
-    <mergeCell ref="EJ4:EJ5"/>
-    <mergeCell ref="ER4:ER5"/>
-    <mergeCell ref="DU4:DU5"/>
-    <mergeCell ref="DX4:DX5"/>
-    <mergeCell ref="DW4:DW5"/>
+    <mergeCell ref="FF4:FF5"/>
+    <mergeCell ref="DE2:FF2"/>
+    <mergeCell ref="ER3:FF3"/>
+    <mergeCell ref="FE4:FE5"/>
+    <mergeCell ref="FD4:FD5"/>
+    <mergeCell ref="FC4:FC5"/>
+    <mergeCell ref="FB4:FB5"/>
+    <mergeCell ref="FA4:FA5"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="D2:BC2"/>
+    <mergeCell ref="DO4:DO5"/>
+    <mergeCell ref="DN4:DN5"/>
+    <mergeCell ref="DS4:DS5"/>
+    <mergeCell ref="DR4:DR5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AY4:AY5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="BC4:BC5"/>
+    <mergeCell ref="BB4:BB5"/>
+    <mergeCell ref="AZ4:AZ5"/>
+    <mergeCell ref="BA4:BA5"/>
+    <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="BW4:BW5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="DJ6:DN57">
-    <cfRule type="containsBlanks" dxfId="26" priority="9">
+    <cfRule type="containsBlanks" dxfId="28" priority="10">
       <formula>LEN(TRIM(DJ6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DO6:DO57">
-    <cfRule type="containsBlanks" dxfId="25" priority="8">
+    <cfRule type="containsBlanks" dxfId="27" priority="9">
       <formula>LEN(TRIM(DO6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP6:EX57 EZ6:EZ57">
-    <cfRule type="containsBlanks" dxfId="24" priority="7">
+    <cfRule type="containsBlanks" dxfId="26" priority="8">
       <formula>LEN(TRIM(DP6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EY6:EY57">
-    <cfRule type="containsBlanks" dxfId="23" priority="6">
+    <cfRule type="containsBlanks" dxfId="25" priority="7">
       <formula>LEN(TRIM(EY6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA6:FA57">
-    <cfRule type="containsBlanks" dxfId="22" priority="5">
+    <cfRule type="containsBlanks" dxfId="24" priority="6">
       <formula>LEN(TRIM(FA6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FB6:FB57">
-    <cfRule type="containsBlanks" dxfId="21" priority="4">
+    <cfRule type="containsBlanks" dxfId="23" priority="5">
       <formula>LEN(TRIM(FB6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FC6:FC57">
-    <cfRule type="containsBlanks" dxfId="20" priority="3">
+    <cfRule type="containsBlanks" dxfId="22" priority="4">
       <formula>LEN(TRIM(FC6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FD6:FD57">
-    <cfRule type="containsBlanks" dxfId="19" priority="2">
+    <cfRule type="containsBlanks" dxfId="21" priority="3">
       <formula>LEN(TRIM(FD6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FE6:FE57">
-    <cfRule type="containsBlanks" dxfId="18" priority="1">
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
       <formula>LEN(TRIM(FE6))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FF6:FF57">
+    <cfRule type="containsBlanks" dxfId="19" priority="1">
+      <formula>LEN(TRIM(FF6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -36902,7 +37101,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:FE58"/>
+  <dimension ref="B1:FF58"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -36928,15 +37127,15 @@
     <col min="83" max="90" width="11.125" style="1" customWidth="1"/>
     <col min="91" max="100" width="10.875" style="1" customWidth="1"/>
     <col min="101" max="105" width="11.125" style="1" customWidth="1"/>
-    <col min="106" max="161" width="10.875" style="1" customWidth="1"/>
-    <col min="162" max="16384" width="8.625" style="1"/>
+    <col min="106" max="162" width="10.875" style="1" customWidth="1"/>
+    <col min="163" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:161" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="BB1" s="86" t="s">
+    <row r="1" spans="2:162" ht="29.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BB1" s="77" t="s">
         <v>323</v>
       </c>
-      <c r="BC1" s="86"/>
+      <c r="BC1" s="77"/>
       <c r="BI1" s="18"/>
       <c r="CC1" s="29"/>
       <c r="CD1" s="29"/>
@@ -37020,357 +37219,360 @@
       <c r="FB1" s="19"/>
       <c r="FC1" s="19"/>
       <c r="FD1" s="19"/>
-      <c r="FE1" s="19" t="s">
+      <c r="FE1" s="19"/>
+      <c r="FF1" s="19" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="2:161" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="73" t="s">
+    <row r="2" spans="2:162" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="65"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="51"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="51"/>
-      <c r="BC2" s="85"/>
-      <c r="BD2" s="73" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="50"/>
+      <c r="BB2" s="50"/>
+      <c r="BC2" s="74"/>
+      <c r="BD2" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="51"/>
-      <c r="BO2" s="51"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="51"/>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
-      <c r="BV2" s="51"/>
-      <c r="BW2" s="51"/>
-      <c r="BX2" s="51"/>
-      <c r="BY2" s="51"/>
-      <c r="BZ2" s="51"/>
-      <c r="CA2" s="51"/>
-      <c r="CB2" s="51"/>
-      <c r="CC2" s="51"/>
-      <c r="CD2" s="51"/>
-      <c r="CE2" s="51"/>
-      <c r="CF2" s="51"/>
-      <c r="CG2" s="51"/>
-      <c r="CH2" s="51"/>
-      <c r="CI2" s="51"/>
-      <c r="CJ2" s="51"/>
-      <c r="CK2" s="51"/>
-      <c r="CL2" s="51"/>
-      <c r="CM2" s="51"/>
-      <c r="CN2" s="51"/>
-      <c r="CO2" s="51"/>
-      <c r="CP2" s="51"/>
-      <c r="CQ2" s="51"/>
-      <c r="CR2" s="51"/>
-      <c r="CS2" s="51"/>
-      <c r="CT2" s="51"/>
-      <c r="CU2" s="51"/>
-      <c r="CV2" s="51"/>
-      <c r="CW2" s="51"/>
-      <c r="CX2" s="51"/>
-      <c r="CY2" s="51"/>
-      <c r="CZ2" s="51"/>
-      <c r="DA2" s="51"/>
-      <c r="DB2" s="51"/>
-      <c r="DC2" s="85"/>
-      <c r="DD2" s="72" t="s">
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="50"/>
+      <c r="BO2" s="50"/>
+      <c r="BP2" s="50"/>
+      <c r="BQ2" s="50"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="50"/>
+      <c r="CC2" s="50"/>
+      <c r="CD2" s="50"/>
+      <c r="CE2" s="50"/>
+      <c r="CF2" s="50"/>
+      <c r="CG2" s="50"/>
+      <c r="CH2" s="50"/>
+      <c r="CI2" s="50"/>
+      <c r="CJ2" s="50"/>
+      <c r="CK2" s="50"/>
+      <c r="CL2" s="50"/>
+      <c r="CM2" s="50"/>
+      <c r="CN2" s="50"/>
+      <c r="CO2" s="50"/>
+      <c r="CP2" s="50"/>
+      <c r="CQ2" s="50"/>
+      <c r="CR2" s="50"/>
+      <c r="CS2" s="50"/>
+      <c r="CT2" s="50"/>
+      <c r="CU2" s="50"/>
+      <c r="CV2" s="50"/>
+      <c r="CW2" s="50"/>
+      <c r="CX2" s="50"/>
+      <c r="CY2" s="50"/>
+      <c r="CZ2" s="50"/>
+      <c r="DA2" s="50"/>
+      <c r="DB2" s="50"/>
+      <c r="DC2" s="74"/>
+      <c r="DD2" s="45" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="72"/>
-      <c r="DF2" s="72"/>
-      <c r="DG2" s="72"/>
-      <c r="DH2" s="72"/>
-      <c r="DI2" s="72"/>
-      <c r="DJ2" s="72"/>
-      <c r="DK2" s="72"/>
-      <c r="DL2" s="72"/>
-      <c r="DM2" s="72"/>
-      <c r="DN2" s="72"/>
-      <c r="DO2" s="72"/>
-      <c r="DP2" s="72"/>
-      <c r="DQ2" s="72"/>
-      <c r="DR2" s="72"/>
-      <c r="DS2" s="72"/>
-      <c r="DT2" s="72"/>
-      <c r="DU2" s="72"/>
-      <c r="DV2" s="72"/>
-      <c r="DW2" s="72"/>
-      <c r="DX2" s="72"/>
-      <c r="DY2" s="72"/>
-      <c r="DZ2" s="72"/>
-      <c r="EA2" s="72"/>
-      <c r="EB2" s="72"/>
-      <c r="EC2" s="72"/>
-      <c r="ED2" s="72"/>
-      <c r="EE2" s="72"/>
-      <c r="EF2" s="72"/>
-      <c r="EG2" s="72"/>
-      <c r="EH2" s="72"/>
-      <c r="EI2" s="72"/>
-      <c r="EJ2" s="72"/>
-      <c r="EK2" s="72"/>
-      <c r="EL2" s="72"/>
-      <c r="EM2" s="72"/>
-      <c r="EN2" s="72"/>
-      <c r="EO2" s="72"/>
-      <c r="EP2" s="72"/>
-      <c r="EQ2" s="72"/>
-      <c r="ER2" s="72"/>
-      <c r="ES2" s="72"/>
-      <c r="ET2" s="72"/>
-      <c r="EU2" s="72"/>
-      <c r="EV2" s="72"/>
-      <c r="EW2" s="72"/>
-      <c r="EX2" s="72"/>
-      <c r="EY2" s="72"/>
-      <c r="EZ2" s="72"/>
-      <c r="FA2" s="72"/>
-      <c r="FB2" s="72"/>
-      <c r="FC2" s="72"/>
-      <c r="FD2" s="72"/>
-      <c r="FE2" s="72"/>
+      <c r="DE2" s="45"/>
+      <c r="DF2" s="45"/>
+      <c r="DG2" s="45"/>
+      <c r="DH2" s="45"/>
+      <c r="DI2" s="45"/>
+      <c r="DJ2" s="45"/>
+      <c r="DK2" s="45"/>
+      <c r="DL2" s="45"/>
+      <c r="DM2" s="45"/>
+      <c r="DN2" s="45"/>
+      <c r="DO2" s="45"/>
+      <c r="DP2" s="45"/>
+      <c r="DQ2" s="45"/>
+      <c r="DR2" s="45"/>
+      <c r="DS2" s="45"/>
+      <c r="DT2" s="45"/>
+      <c r="DU2" s="45"/>
+      <c r="DV2" s="45"/>
+      <c r="DW2" s="45"/>
+      <c r="DX2" s="45"/>
+      <c r="DY2" s="45"/>
+      <c r="DZ2" s="45"/>
+      <c r="EA2" s="45"/>
+      <c r="EB2" s="45"/>
+      <c r="EC2" s="45"/>
+      <c r="ED2" s="45"/>
+      <c r="EE2" s="45"/>
+      <c r="EF2" s="45"/>
+      <c r="EG2" s="45"/>
+      <c r="EH2" s="45"/>
+      <c r="EI2" s="45"/>
+      <c r="EJ2" s="45"/>
+      <c r="EK2" s="45"/>
+      <c r="EL2" s="45"/>
+      <c r="EM2" s="45"/>
+      <c r="EN2" s="45"/>
+      <c r="EO2" s="45"/>
+      <c r="EP2" s="45"/>
+      <c r="EQ2" s="45"/>
+      <c r="ER2" s="45"/>
+      <c r="ES2" s="45"/>
+      <c r="ET2" s="45"/>
+      <c r="EU2" s="45"/>
+      <c r="EV2" s="45"/>
+      <c r="EW2" s="45"/>
+      <c r="EX2" s="45"/>
+      <c r="EY2" s="45"/>
+      <c r="EZ2" s="45"/>
+      <c r="FA2" s="45"/>
+      <c r="FB2" s="45"/>
+      <c r="FC2" s="45"/>
+      <c r="FD2" s="45"/>
+      <c r="FE2" s="45"/>
+      <c r="FF2" s="45"/>
     </row>
-    <row r="3" spans="2:161" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="47" t="s">
+    <row r="3" spans="2:162" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="56" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="52"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="52"/>
-      <c r="AO3" s="52"/>
-      <c r="AP3" s="52"/>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="47" t="s">
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="71"/>
+      <c r="AR3" s="56" t="s">
         <v>282</v>
       </c>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="52"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
-      <c r="BB3" s="52"/>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="47" t="s">
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="57"/>
+      <c r="AZ3" s="57"/>
+      <c r="BA3" s="57"/>
+      <c r="BB3" s="57"/>
+      <c r="BC3" s="71"/>
+      <c r="BD3" s="56" t="s">
         <v>322</v>
       </c>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="52"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="52"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="52"/>
-      <c r="BP3" s="52"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="52"/>
-      <c r="BS3" s="52"/>
-      <c r="BT3" s="52"/>
-      <c r="BU3" s="52"/>
-      <c r="BV3" s="52"/>
-      <c r="BW3" s="52"/>
-      <c r="BX3" s="52"/>
-      <c r="BY3" s="52"/>
-      <c r="BZ3" s="52"/>
-      <c r="CA3" s="52"/>
-      <c r="CB3" s="52"/>
-      <c r="CC3" s="52"/>
-      <c r="CD3" s="52"/>
-      <c r="CE3" s="52"/>
-      <c r="CF3" s="52"/>
-      <c r="CG3" s="52"/>
-      <c r="CH3" s="52"/>
-      <c r="CI3" s="52"/>
-      <c r="CJ3" s="52"/>
-      <c r="CK3" s="52"/>
-      <c r="CL3" s="52"/>
-      <c r="CM3" s="52"/>
-      <c r="CN3" s="52"/>
-      <c r="CO3" s="52"/>
-      <c r="CP3" s="52"/>
-      <c r="CQ3" s="53"/>
-      <c r="CR3" s="47" t="s">
+      <c r="BE3" s="57"/>
+      <c r="BF3" s="57"/>
+      <c r="BG3" s="57"/>
+      <c r="BH3" s="57"/>
+      <c r="BI3" s="57"/>
+      <c r="BJ3" s="57"/>
+      <c r="BK3" s="57"/>
+      <c r="BL3" s="57"/>
+      <c r="BM3" s="57"/>
+      <c r="BN3" s="57"/>
+      <c r="BO3" s="57"/>
+      <c r="BP3" s="57"/>
+      <c r="BQ3" s="57"/>
+      <c r="BR3" s="57"/>
+      <c r="BS3" s="57"/>
+      <c r="BT3" s="57"/>
+      <c r="BU3" s="57"/>
+      <c r="BV3" s="57"/>
+      <c r="BW3" s="57"/>
+      <c r="BX3" s="57"/>
+      <c r="BY3" s="57"/>
+      <c r="BZ3" s="57"/>
+      <c r="CA3" s="57"/>
+      <c r="CB3" s="57"/>
+      <c r="CC3" s="57"/>
+      <c r="CD3" s="57"/>
+      <c r="CE3" s="57"/>
+      <c r="CF3" s="57"/>
+      <c r="CG3" s="57"/>
+      <c r="CH3" s="57"/>
+      <c r="CI3" s="57"/>
+      <c r="CJ3" s="57"/>
+      <c r="CK3" s="57"/>
+      <c r="CL3" s="57"/>
+      <c r="CM3" s="57"/>
+      <c r="CN3" s="57"/>
+      <c r="CO3" s="57"/>
+      <c r="CP3" s="57"/>
+      <c r="CQ3" s="71"/>
+      <c r="CR3" s="56" t="s">
         <v>280</v>
       </c>
-      <c r="CS3" s="52"/>
-      <c r="CT3" s="52"/>
-      <c r="CU3" s="52"/>
-      <c r="CV3" s="52"/>
-      <c r="CW3" s="52"/>
-      <c r="CX3" s="52"/>
-      <c r="CY3" s="52"/>
-      <c r="CZ3" s="52"/>
-      <c r="DA3" s="52"/>
-      <c r="DB3" s="52"/>
-      <c r="DC3" s="53"/>
-      <c r="DD3" s="45" t="s">
+      <c r="CS3" s="57"/>
+      <c r="CT3" s="57"/>
+      <c r="CU3" s="57"/>
+      <c r="CV3" s="57"/>
+      <c r="CW3" s="57"/>
+      <c r="CX3" s="57"/>
+      <c r="CY3" s="57"/>
+      <c r="CZ3" s="57"/>
+      <c r="DA3" s="57"/>
+      <c r="DB3" s="57"/>
+      <c r="DC3" s="71"/>
+      <c r="DD3" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="DE3" s="45"/>
-      <c r="DF3" s="45"/>
-      <c r="DG3" s="45"/>
-      <c r="DH3" s="45"/>
-      <c r="DI3" s="45"/>
-      <c r="DJ3" s="45"/>
-      <c r="DK3" s="45"/>
-      <c r="DL3" s="45"/>
-      <c r="DM3" s="45"/>
-      <c r="DN3" s="45"/>
-      <c r="DO3" s="45"/>
-      <c r="DP3" s="45"/>
-      <c r="DQ3" s="45"/>
-      <c r="DR3" s="45"/>
-      <c r="DS3" s="45"/>
-      <c r="DT3" s="45"/>
-      <c r="DU3" s="45"/>
-      <c r="DV3" s="45"/>
-      <c r="DW3" s="45"/>
-      <c r="DX3" s="45"/>
-      <c r="DY3" s="45"/>
-      <c r="DZ3" s="45"/>
-      <c r="EA3" s="45"/>
-      <c r="EB3" s="45"/>
-      <c r="EC3" s="45"/>
-      <c r="ED3" s="45"/>
-      <c r="EE3" s="45"/>
-      <c r="EF3" s="45"/>
-      <c r="EG3" s="45"/>
-      <c r="EH3" s="45"/>
-      <c r="EI3" s="45"/>
-      <c r="EJ3" s="45"/>
-      <c r="EK3" s="45"/>
-      <c r="EL3" s="45"/>
-      <c r="EM3" s="45"/>
-      <c r="EN3" s="45"/>
-      <c r="EO3" s="45"/>
-      <c r="EP3" s="45"/>
-      <c r="EQ3" s="45"/>
-      <c r="ER3" s="45" t="s">
+      <c r="DE3" s="46"/>
+      <c r="DF3" s="46"/>
+      <c r="DG3" s="46"/>
+      <c r="DH3" s="46"/>
+      <c r="DI3" s="46"/>
+      <c r="DJ3" s="46"/>
+      <c r="DK3" s="46"/>
+      <c r="DL3" s="46"/>
+      <c r="DM3" s="46"/>
+      <c r="DN3" s="46"/>
+      <c r="DO3" s="46"/>
+      <c r="DP3" s="46"/>
+      <c r="DQ3" s="46"/>
+      <c r="DR3" s="46"/>
+      <c r="DS3" s="46"/>
+      <c r="DT3" s="46"/>
+      <c r="DU3" s="46"/>
+      <c r="DV3" s="46"/>
+      <c r="DW3" s="46"/>
+      <c r="DX3" s="46"/>
+      <c r="DY3" s="46"/>
+      <c r="DZ3" s="46"/>
+      <c r="EA3" s="46"/>
+      <c r="EB3" s="46"/>
+      <c r="EC3" s="46"/>
+      <c r="ED3" s="46"/>
+      <c r="EE3" s="46"/>
+      <c r="EF3" s="46"/>
+      <c r="EG3" s="46"/>
+      <c r="EH3" s="46"/>
+      <c r="EI3" s="46"/>
+      <c r="EJ3" s="46"/>
+      <c r="EK3" s="46"/>
+      <c r="EL3" s="46"/>
+      <c r="EM3" s="46"/>
+      <c r="EN3" s="46"/>
+      <c r="EO3" s="46"/>
+      <c r="EP3" s="46"/>
+      <c r="EQ3" s="46"/>
+      <c r="ER3" s="46" t="s">
         <v>414</v>
       </c>
-      <c r="ES3" s="45"/>
-      <c r="ET3" s="45"/>
-      <c r="EU3" s="45"/>
-      <c r="EV3" s="45"/>
-      <c r="EW3" s="45"/>
-      <c r="EX3" s="45"/>
-      <c r="EY3" s="45"/>
-      <c r="EZ3" s="45"/>
-      <c r="FA3" s="45"/>
-      <c r="FB3" s="45"/>
-      <c r="FC3" s="45"/>
-      <c r="FD3" s="45"/>
-      <c r="FE3" s="45"/>
+      <c r="ES3" s="46"/>
+      <c r="ET3" s="46"/>
+      <c r="EU3" s="46"/>
+      <c r="EV3" s="46"/>
+      <c r="EW3" s="46"/>
+      <c r="EX3" s="46"/>
+      <c r="EY3" s="46"/>
+      <c r="EZ3" s="46"/>
+      <c r="FA3" s="46"/>
+      <c r="FB3" s="46"/>
+      <c r="FC3" s="46"/>
+      <c r="FD3" s="46"/>
+      <c r="FE3" s="46"/>
+      <c r="FF3" s="46"/>
     </row>
-    <row r="4" spans="2:161" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="70" t="s">
+    <row r="4" spans="2:162" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="63" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="75" t="s">
@@ -37415,7 +37617,7 @@
       <c r="Q4" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="80" t="s">
+      <c r="R4" s="82" t="s">
         <v>196</v>
       </c>
       <c r="S4" s="75" t="s">
@@ -37436,7 +37638,7 @@
       <c r="X4" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="76" t="s">
+      <c r="Y4" s="78" t="s">
         <v>162</v>
       </c>
       <c r="Z4" s="75" t="s">
@@ -37448,7 +37650,7 @@
       <c r="AB4" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="AC4" s="76" t="s">
+      <c r="AC4" s="78" t="s">
         <v>165</v>
       </c>
       <c r="AD4" s="75" t="s">
@@ -37466,34 +37668,34 @@
       <c r="AH4" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="AI4" s="76" t="s">
+      <c r="AI4" s="78" t="s">
         <v>167</v>
       </c>
-      <c r="AJ4" s="76" t="s">
+      <c r="AJ4" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="AK4" s="76" t="s">
+      <c r="AK4" s="78" t="s">
         <v>169</v>
       </c>
-      <c r="AL4" s="76" t="s">
+      <c r="AL4" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="AM4" s="76" t="s">
+      <c r="AM4" s="78" t="s">
         <v>187</v>
       </c>
       <c r="AN4" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="AO4" s="76" t="s">
+      <c r="AO4" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="AP4" s="76" t="s">
+      <c r="AP4" s="78" t="s">
         <v>173</v>
       </c>
       <c r="AQ4" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="AR4" s="76" t="s">
+      <c r="AR4" s="78" t="s">
         <v>175</v>
       </c>
       <c r="AS4" s="75" t="s">
@@ -37511,10 +37713,10 @@
       <c r="AW4" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="76" t="s">
+      <c r="AX4" s="78" t="s">
         <v>203</v>
       </c>
-      <c r="AY4" s="76" t="s">
+      <c r="AY4" s="78" t="s">
         <v>204</v>
       </c>
       <c r="AZ4" s="75" t="s">
@@ -37526,88 +37728,88 @@
       <c r="BB4" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="BC4" s="76" t="s">
+      <c r="BC4" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="BD4" s="63" t="s">
+      <c r="BD4" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="BE4" s="63" t="s">
+      <c r="BE4" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="BF4" s="63" t="s">
+      <c r="BF4" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="BG4" s="63" t="s">
+      <c r="BG4" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="BH4" s="63" t="s">
+      <c r="BH4" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="BI4" s="63" t="s">
+      <c r="BI4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="BJ4" s="63" t="s">
+      <c r="BJ4" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="BK4" s="63" t="s">
+      <c r="BK4" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="BL4" s="63" t="s">
+      <c r="BL4" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="BM4" s="63" t="s">
+      <c r="BM4" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="BN4" s="63" t="s">
+      <c r="BN4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="BO4" s="63" t="s">
+      <c r="BO4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="BP4" s="63" t="s">
+      <c r="BP4" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="BQ4" s="63" t="s">
+      <c r="BQ4" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="BR4" s="63" t="s">
+      <c r="BR4" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="BS4" s="63" t="s">
+      <c r="BS4" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="BT4" s="63" t="s">
+      <c r="BT4" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="BU4" s="62" t="s">
+      <c r="BU4" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="BV4" s="62" t="s">
+      <c r="BV4" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="BW4" s="62" t="s">
+      <c r="BW4" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="BX4" s="62" t="s">
+      <c r="BX4" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="BY4" s="62" t="s">
+      <c r="BY4" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="BZ4" s="62" t="s">
+      <c r="BZ4" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="CA4" s="63" t="s">
+      <c r="CA4" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="CB4" s="63" t="s">
+      <c r="CB4" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="CC4" s="63" t="s">
+      <c r="CC4" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="CD4" s="63" t="s">
+      <c r="CD4" s="47" t="s">
         <v>239</v>
       </c>
       <c r="CE4" s="75" t="s">
@@ -37712,7 +37914,7 @@
       <c r="DL4" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="DM4" s="74" t="s">
+      <c r="DM4" s="76" t="s">
         <v>331</v>
       </c>
       <c r="DN4" s="44" t="s">
@@ -37736,19 +37938,19 @@
       <c r="DT4" s="44" t="s">
         <v>350</v>
       </c>
-      <c r="DU4" s="74" t="s">
+      <c r="DU4" s="76" t="s">
         <v>366</v>
       </c>
-      <c r="DV4" s="74" t="s">
+      <c r="DV4" s="76" t="s">
         <v>367</v>
       </c>
-      <c r="DW4" s="74" t="s">
+      <c r="DW4" s="76" t="s">
         <v>368</v>
       </c>
-      <c r="DX4" s="74" t="s">
+      <c r="DX4" s="76" t="s">
         <v>369</v>
       </c>
-      <c r="DY4" s="74" t="s">
+      <c r="DY4" s="76" t="s">
         <v>370</v>
       </c>
       <c r="DZ4" s="44" t="s">
@@ -37847,114 +38049,117 @@
       <c r="FE4" s="44" t="s">
         <v>442</v>
       </c>
+      <c r="FF4" s="44" t="s">
+        <v>445</v>
+      </c>
     </row>
-    <row r="5" spans="2:161" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="65"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="77"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="77"/>
-      <c r="AJ5" s="77"/>
-      <c r="AK5" s="77"/>
-      <c r="AL5" s="77"/>
-      <c r="AM5" s="77"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="77"/>
-      <c r="AP5" s="77"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="77"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="77"/>
-      <c r="AY5" s="77"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="77"/>
-      <c r="BD5" s="54"/>
-      <c r="BE5" s="54"/>
-      <c r="BF5" s="54"/>
-      <c r="BG5" s="54"/>
-      <c r="BH5" s="54"/>
-      <c r="BI5" s="54"/>
-      <c r="BJ5" s="54"/>
-      <c r="BK5" s="54"/>
-      <c r="BL5" s="54"/>
-      <c r="BM5" s="54"/>
-      <c r="BN5" s="54"/>
-      <c r="BO5" s="54"/>
-      <c r="BP5" s="54"/>
-      <c r="BQ5" s="54"/>
-      <c r="BR5" s="54"/>
-      <c r="BS5" s="54"/>
-      <c r="BT5" s="54"/>
-      <c r="BU5" s="56"/>
-      <c r="BV5" s="56"/>
-      <c r="BW5" s="56"/>
-      <c r="BX5" s="56"/>
-      <c r="BY5" s="56"/>
-      <c r="BZ5" s="56"/>
-      <c r="CA5" s="54"/>
-      <c r="CB5" s="54"/>
-      <c r="CC5" s="54"/>
-      <c r="CD5" s="54"/>
-      <c r="CE5" s="48"/>
-      <c r="CF5" s="48"/>
-      <c r="CG5" s="48"/>
-      <c r="CH5" s="48"/>
-      <c r="CI5" s="48"/>
-      <c r="CJ5" s="48"/>
-      <c r="CK5" s="48"/>
-      <c r="CL5" s="48"/>
-      <c r="CM5" s="48"/>
-      <c r="CN5" s="48"/>
-      <c r="CO5" s="48"/>
-      <c r="CP5" s="48"/>
-      <c r="CQ5" s="48"/>
-      <c r="CR5" s="48"/>
-      <c r="CS5" s="48"/>
-      <c r="CT5" s="48"/>
-      <c r="CU5" s="48"/>
-      <c r="CV5" s="48"/>
-      <c r="CW5" s="48"/>
-      <c r="CX5" s="48"/>
-      <c r="CY5" s="48"/>
-      <c r="CZ5" s="48"/>
-      <c r="DA5" s="48"/>
-      <c r="DB5" s="48"/>
-      <c r="DC5" s="48"/>
+    <row r="5" spans="2:162" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="70"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="79"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="79"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="55"/>
+      <c r="AH5" s="55"/>
+      <c r="AI5" s="79"/>
+      <c r="AJ5" s="79"/>
+      <c r="AK5" s="79"/>
+      <c r="AL5" s="79"/>
+      <c r="AM5" s="79"/>
+      <c r="AN5" s="55"/>
+      <c r="AO5" s="79"/>
+      <c r="AP5" s="79"/>
+      <c r="AQ5" s="55"/>
+      <c r="AR5" s="79"/>
+      <c r="AS5" s="55"/>
+      <c r="AT5" s="55"/>
+      <c r="AU5" s="55"/>
+      <c r="AV5" s="55"/>
+      <c r="AW5" s="55"/>
+      <c r="AX5" s="79"/>
+      <c r="AY5" s="79"/>
+      <c r="AZ5" s="55"/>
+      <c r="BA5" s="55"/>
+      <c r="BB5" s="55"/>
+      <c r="BC5" s="79"/>
+      <c r="BD5" s="48"/>
+      <c r="BE5" s="48"/>
+      <c r="BF5" s="48"/>
+      <c r="BG5" s="48"/>
+      <c r="BH5" s="48"/>
+      <c r="BI5" s="48"/>
+      <c r="BJ5" s="48"/>
+      <c r="BK5" s="48"/>
+      <c r="BL5" s="48"/>
+      <c r="BM5" s="48"/>
+      <c r="BN5" s="48"/>
+      <c r="BO5" s="48"/>
+      <c r="BP5" s="48"/>
+      <c r="BQ5" s="48"/>
+      <c r="BR5" s="48"/>
+      <c r="BS5" s="48"/>
+      <c r="BT5" s="48"/>
+      <c r="BU5" s="53"/>
+      <c r="BV5" s="53"/>
+      <c r="BW5" s="53"/>
+      <c r="BX5" s="53"/>
+      <c r="BY5" s="53"/>
+      <c r="BZ5" s="53"/>
+      <c r="CA5" s="48"/>
+      <c r="CB5" s="48"/>
+      <c r="CC5" s="48"/>
+      <c r="CD5" s="48"/>
+      <c r="CE5" s="55"/>
+      <c r="CF5" s="55"/>
+      <c r="CG5" s="55"/>
+      <c r="CH5" s="55"/>
+      <c r="CI5" s="55"/>
+      <c r="CJ5" s="55"/>
+      <c r="CK5" s="55"/>
+      <c r="CL5" s="55"/>
+      <c r="CM5" s="55"/>
+      <c r="CN5" s="55"/>
+      <c r="CO5" s="55"/>
+      <c r="CP5" s="55"/>
+      <c r="CQ5" s="55"/>
+      <c r="CR5" s="55"/>
+      <c r="CS5" s="55"/>
+      <c r="CT5" s="55"/>
+      <c r="CU5" s="55"/>
+      <c r="CV5" s="55"/>
+      <c r="CW5" s="55"/>
+      <c r="CX5" s="55"/>
+      <c r="CY5" s="55"/>
+      <c r="CZ5" s="55"/>
+      <c r="DA5" s="55"/>
+      <c r="DB5" s="55"/>
+      <c r="DC5" s="55"/>
       <c r="DD5" s="44"/>
       <c r="DE5" s="44"/>
       <c r="DF5" s="44"/>
@@ -37964,7 +38169,7 @@
       <c r="DJ5" s="44"/>
       <c r="DK5" s="44"/>
       <c r="DL5" s="44"/>
-      <c r="DM5" s="74"/>
+      <c r="DM5" s="76"/>
       <c r="DN5" s="44"/>
       <c r="DO5" s="44"/>
       <c r="DP5" s="44"/>
@@ -37972,11 +38177,11 @@
       <c r="DR5" s="44"/>
       <c r="DS5" s="44"/>
       <c r="DT5" s="44"/>
-      <c r="DU5" s="74"/>
-      <c r="DV5" s="74"/>
-      <c r="DW5" s="74"/>
-      <c r="DX5" s="74"/>
-      <c r="DY5" s="74"/>
+      <c r="DU5" s="76"/>
+      <c r="DV5" s="76"/>
+      <c r="DW5" s="76"/>
+      <c r="DX5" s="76"/>
+      <c r="DY5" s="76"/>
       <c r="DZ5" s="44"/>
       <c r="EA5" s="44"/>
       <c r="EB5" s="44"/>
@@ -38009,8 +38214,9 @@
       <c r="FC5" s="44"/>
       <c r="FD5" s="44"/>
       <c r="FE5" s="44"/>
+      <c r="FF5" s="44"/>
     </row>
-    <row r="6" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -38491,8 +38697,11 @@
       <c r="FE6" s="28">
         <v>100</v>
       </c>
+      <c r="FF6" s="28">
+        <v>124</v>
+      </c>
     </row>
-    <row r="7" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
@@ -38973,8 +39182,11 @@
       <c r="FE7" s="15">
         <v>2</v>
       </c>
+      <c r="FF7" s="15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
@@ -39455,8 +39667,11 @@
       <c r="FE8" s="28">
         <v>4</v>
       </c>
+      <c r="FF8" s="28">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -39937,8 +40152,11 @@
       <c r="FE9" s="15">
         <v>59</v>
       </c>
+      <c r="FF9" s="15">
+        <v>65</v>
+      </c>
     </row>
-    <row r="10" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
@@ -40419,8 +40637,11 @@
       <c r="FE10" s="15">
         <v>0</v>
       </c>
+      <c r="FF10" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
@@ -40901,8 +41122,11 @@
       <c r="FE11" s="15">
         <v>11</v>
       </c>
+      <c r="FF11" s="15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
@@ -41383,8 +41607,11 @@
       <c r="FE12" s="15">
         <v>6</v>
       </c>
+      <c r="FF12" s="15">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -41865,8 +42092,11 @@
       <c r="FE13" s="15">
         <v>15</v>
       </c>
+      <c r="FF13" s="15">
+        <v>20</v>
+      </c>
     </row>
-    <row r="14" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
@@ -42347,8 +42577,11 @@
       <c r="FE14" s="15">
         <v>20</v>
       </c>
+      <c r="FF14" s="15">
+        <v>29</v>
+      </c>
     </row>
-    <row r="15" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
@@ -42829,8 +43062,11 @@
       <c r="FE15" s="15">
         <v>3</v>
       </c>
+      <c r="FF15" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
@@ -43311,8 +43547,11 @@
       <c r="FE16" s="28">
         <v>119</v>
       </c>
+      <c r="FF16" s="28">
+        <v>126</v>
+      </c>
     </row>
-    <row r="17" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11" t="s">
         <v>23</v>
       </c>
@@ -43793,8 +44032,11 @@
       <c r="FE17" s="15">
         <v>119</v>
       </c>
+      <c r="FF17" s="15">
+        <v>148</v>
+      </c>
     </row>
-    <row r="18" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
@@ -44275,9 +44517,12 @@
       <c r="FE18" s="34">
         <v>1536</v>
       </c>
+      <c r="FF18" s="34">
+        <v>1497</v>
+      </c>
     </row>
-    <row r="19" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="78" t="s">
+    <row r="19" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="80" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -44757,9 +45002,12 @@
       <c r="FE19" s="15">
         <v>49</v>
       </c>
+      <c r="FF19" s="15">
+        <v>43</v>
+      </c>
     </row>
-    <row r="20" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="82"/>
+    <row r="20" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="84"/>
       <c r="C20" s="9" t="s">
         <v>29</v>
       </c>
@@ -45237,9 +45485,12 @@
       <c r="FE20" s="28">
         <v>147</v>
       </c>
+      <c r="FF20" s="28">
+        <v>135</v>
+      </c>
     </row>
-    <row r="21" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="79"/>
+    <row r="21" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="81"/>
       <c r="C21" s="9" t="s">
         <v>30</v>
       </c>
@@ -45717,8 +45968,11 @@
       <c r="FE21" s="15">
         <v>23</v>
       </c>
+      <c r="FF21" s="15">
+        <v>22</v>
+      </c>
     </row>
-    <row r="22" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
@@ -46199,8 +46453,11 @@
       <c r="FE22" s="15">
         <v>10</v>
       </c>
+      <c r="FF22" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
@@ -46681,8 +46938,11 @@
       <c r="FE23" s="15">
         <v>0</v>
       </c>
+      <c r="FF23" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="11" t="s">
         <v>35</v>
       </c>
@@ -47163,8 +47423,11 @@
       <c r="FE24" s="15">
         <v>8</v>
       </c>
+      <c r="FF24" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
@@ -47645,8 +47908,11 @@
       <c r="FE25" s="15">
         <v>0</v>
       </c>
+      <c r="FF25" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -48127,8 +48393,11 @@
       <c r="FE26" s="15">
         <v>5</v>
       </c>
+      <c r="FF26" s="15">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
@@ -48609,8 +48878,11 @@
       <c r="FE27" s="15">
         <v>0</v>
       </c>
+      <c r="FF27" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
@@ -49091,9 +49363,12 @@
       <c r="FE28" s="15">
         <v>1</v>
       </c>
+      <c r="FF28" s="15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="83" t="s">
+    <row r="29" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="85" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -49573,9 +49848,12 @@
       <c r="FE29" s="15">
         <v>2</v>
       </c>
+      <c r="FF29" s="15">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="84"/>
+    <row r="30" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="86"/>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
@@ -50053,8 +50331,11 @@
       <c r="FE30" s="15">
         <v>5</v>
       </c>
+      <c r="FF30" s="15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="31" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
@@ -50535,8 +50816,11 @@
       <c r="FE31" s="15">
         <v>17</v>
       </c>
+      <c r="FF31" s="15">
+        <v>26</v>
+      </c>
     </row>
-    <row r="32" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
@@ -51017,8 +51301,11 @@
       <c r="FE32" s="15">
         <v>0</v>
       </c>
+      <c r="FF32" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
@@ -51499,8 +51786,11 @@
       <c r="FE33" s="15">
         <v>0</v>
       </c>
+      <c r="FF33" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
@@ -51981,9 +52271,12 @@
       <c r="FE34" s="15">
         <v>42</v>
       </c>
+      <c r="FF34" s="15">
+        <v>42</v>
+      </c>
     </row>
-    <row r="35" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="78" t="s">
+    <row r="35" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="80" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -52463,9 +52756,12 @@
       <c r="FE35" s="15">
         <v>337</v>
       </c>
+      <c r="FF35" s="15">
+        <v>355</v>
+      </c>
     </row>
-    <row r="36" spans="2:161" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="79"/>
+    <row r="36" spans="2:162" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="81"/>
       <c r="C36" s="9" t="s">
         <v>58</v>
       </c>
@@ -52943,8 +53239,11 @@
       <c r="FE36" s="28">
         <v>45</v>
       </c>
+      <c r="FF36"